--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,16 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0F7488-990E-466D-B835-00559BC1FED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18C9073-4F5F-4CC9-A595-F773C4701ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lessons" sheetId="1" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
-    <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="Instructions" sheetId="2" r:id="rId3"/>
+    <sheet name="Lists" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -88,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="118">
   <si>
     <t>Категорија</t>
   </si>
@@ -291,14 +303,164 @@
     <t>Вкупен број редови</t>
   </si>
   <si>
-    <t>Moj naslov</t>
+    <t>Собирање и одземање броеви од кој еден е блиску до број делив со 10, 100 или 1000.</t>
+  </si>
+  <si>
+    <t>Собирање и одзема броеви до 1 000 000 ( или над 1 000 000).</t>
+  </si>
+  <si>
+    <t>Собирање и одзема броеви до 1 000 000 ( или над 1 000 000).-вежби</t>
+  </si>
+  <si>
+    <t>Множење број со полни десетки, стотки или илјади.</t>
+  </si>
+  <si>
+    <t>Множење два броја од кои едниот е блиску до полна десетка или стотка.</t>
+  </si>
+  <si>
+    <t>Множење со преполовување на еден број и удвојување на другиот број.</t>
+  </si>
+  <si>
+    <t>Множење на броеви</t>
+  </si>
+  <si>
+    <t>Множење на броеви - вежби</t>
+  </si>
+  <si>
+    <t>Делење со едноцифрен број</t>
+  </si>
+  <si>
+    <t>Делење со двоцифрен број</t>
+  </si>
+  <si>
+    <t>Делење со двоцифрен број-вежби</t>
+  </si>
+  <si>
+    <t>Својства на операциите</t>
+  </si>
+  <si>
+    <t>Својства на операциите вежби</t>
+  </si>
+  <si>
+    <t>Равенки</t>
+  </si>
+  <si>
+    <t>Решавање равенки</t>
+  </si>
+  <si>
+    <t>Вредност на броен израз</t>
+  </si>
+  <si>
+    <t>Вредност на броен израз-вежби</t>
+  </si>
+  <si>
+    <t>Проценување и пресметување на израз</t>
+  </si>
+  <si>
+    <t>Писмено проверување</t>
+  </si>
+  <si>
+    <t>КОНТРОЛЕН ТЕСТ</t>
+  </si>
+  <si>
+    <t>Деливост на природни броеви</t>
+  </si>
+  <si>
+    <t>Прости и сложени броеви</t>
+  </si>
+  <si>
+    <t>Разложување двоцифрен број на множители</t>
+  </si>
+  <si>
+    <t>Разложување двоцифрен број на множители - вежби</t>
+  </si>
+  <si>
+    <t>Претставување сложен број како производ од прости броеви</t>
+  </si>
+  <si>
+    <t>Претставување сложен број како производ од прости броеви -вежби</t>
+  </si>
+  <si>
+    <t>Признаци за деливост со 2, со 5 и со 10</t>
+  </si>
+  <si>
+    <t>Признаци за деливост со 3, со 6 и со 9</t>
+  </si>
+  <si>
+    <t>Признаци  за деливост со 4 и со 8</t>
+  </si>
+  <si>
+    <t>Признаците за деливост со 2, 3, 4, 5, 6, 8, 9, 10.</t>
+  </si>
+  <si>
+    <t>Содржатели и делители на даден природен број</t>
+  </si>
+  <si>
+    <t>Содржатели и делители на даден природен број - вежби</t>
+  </si>
+  <si>
+    <t>Заеднички делители. НЗД</t>
+  </si>
+  <si>
+    <t>Заеднички содржатели.НЗС</t>
+  </si>
+  <si>
+    <t>Задачи со НЗС и НЗД</t>
+  </si>
+  <si>
+    <t>Собирање и одземање дропки со ист именител</t>
+  </si>
+  <si>
+    <t>Собирање и одземање дропки со ист именител- вежби</t>
+  </si>
+  <si>
+    <t>Собирање на децимални броеви чиј збир е 1 или 10</t>
+  </si>
+  <si>
+    <t>Собирање на децимални броеви чиј збир е 1 или 10 - вежби</t>
+  </si>
+  <si>
+    <t>Стратегии за собирање на децимални броеви</t>
+  </si>
+  <si>
+    <t>Стратегии за собирање на децимални броеви - вежби</t>
+  </si>
+  <si>
+    <t>Собирање и одземање децимални броеви со една децимала</t>
+  </si>
+  <si>
+    <t>Собирање и одземање децимални броеви со една децимала -вежби</t>
+  </si>
+  <si>
+    <t>Собирање и одземање броеви со ист или различен број на децимали</t>
+  </si>
+  <si>
+    <t>Собирање и одземање броеви со ист или различен број на децимали - вежби</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbyg7vf8E7j9rsw3j1qNjQ9WeHXfAkKzFn1kzwr_gNfqQPNc4NGpcQXVioZI36r1oosA/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycby_isP_vyDHE3ZFKeDej4a1VaUVoFOXRYDGYOJpLxTG4fropgziKtDuZQ7EBaA4xBLCGg/exec</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -340,6 +502,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -374,7 +543,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -400,11 +569,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -438,6 +622,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -460,8 +647,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E721">
-  <autoFilter ref="A1:E721" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E728">
+  <autoFilter ref="A1:E728" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Алгебра"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="6"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E725">
+    <sortCondition ref="A1:A725"/>
+  </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Категорија"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Одделение"/>
@@ -758,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E721"/>
+  <dimension ref="A1:E728"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -767,7 +968,7 @@
     <col min="5" max="5" width="88" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -784,611 +985,609 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2">
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="4">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="D2" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="D3" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="11"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2">
+      <c r="D4" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="11"/>
+    </row>
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="4">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="4">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4">
+        <v>5</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="11"/>
+    </row>
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="4">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4">
+        <v>6</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="4">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4">
+        <v>7</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="11"/>
+    </row>
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="4">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4">
+        <v>8</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="4">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4">
+        <v>9</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="11"/>
+    </row>
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="4">
+        <v>6</v>
+      </c>
+      <c r="C11" s="4">
         <v>10</v>
       </c>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="D11" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="11"/>
+    </row>
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="4">
+        <v>6</v>
+      </c>
+      <c r="C12" s="4">
         <v>11</v>
       </c>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2">
-        <v>6</v>
-      </c>
-      <c r="C7" s="2">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="D12" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="11"/>
+    </row>
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="4">
+        <v>6</v>
+      </c>
+      <c r="C13" s="4">
         <v>12</v>
       </c>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="D13" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="4">
+        <v>6</v>
+      </c>
+      <c r="C14" s="4">
         <v>13</v>
       </c>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="D14" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="11"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="4">
+        <v>6</v>
+      </c>
+      <c r="C15" s="4">
         <v>14</v>
       </c>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="2">
-        <v>6</v>
-      </c>
-      <c r="C10" s="2">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="D15" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="4">
+        <v>6</v>
+      </c>
+      <c r="C16" s="4">
         <v>15</v>
       </c>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="2">
-        <v>6</v>
-      </c>
-      <c r="C11" s="2">
-        <v>10</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="D16" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="11"/>
+    </row>
+    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="4">
+        <v>6</v>
+      </c>
+      <c r="C17" s="4">
         <v>16</v>
       </c>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="2">
-        <v>6</v>
-      </c>
-      <c r="C12" s="2">
-        <v>11</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="D17" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="4">
+        <v>6</v>
+      </c>
+      <c r="C18" s="4">
         <v>17</v>
       </c>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="2">
-        <v>6</v>
-      </c>
-      <c r="C13" s="2">
-        <v>12</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="D18" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="11"/>
+    </row>
+    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="4">
+        <v>6</v>
+      </c>
+      <c r="C19" s="4">
         <v>18</v>
       </c>
-      <c r="E13" s="10"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="2">
-        <v>6</v>
-      </c>
-      <c r="C14" s="2">
-        <v>13</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="D19" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="11"/>
+    </row>
+    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="4">
+        <v>6</v>
+      </c>
+      <c r="C20" s="4">
         <v>19</v>
       </c>
-      <c r="E14" s="10"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="2">
-        <v>6</v>
-      </c>
-      <c r="C15" s="2">
-        <v>14</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="D20" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="11"/>
+    </row>
+    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="4">
+        <v>6</v>
+      </c>
+      <c r="C21" s="4">
         <v>20</v>
       </c>
-      <c r="E15" s="10"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="2">
-        <v>6</v>
-      </c>
-      <c r="C16" s="2">
-        <v>15</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="D21" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="4">
+        <v>6</v>
+      </c>
+      <c r="C22" s="4">
         <v>21</v>
       </c>
-      <c r="E16" s="10"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="2">
-        <v>6</v>
-      </c>
-      <c r="C17" s="2">
-        <v>16</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="D22" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="11"/>
+    </row>
+    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="4">
+        <v>6</v>
+      </c>
+      <c r="C23" s="4">
         <v>22</v>
       </c>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="2">
-        <v>6</v>
-      </c>
-      <c r="C18" s="2">
-        <v>17</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="10"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="2">
-        <v>6</v>
-      </c>
-      <c r="C19" s="2">
-        <v>18</v>
-      </c>
-      <c r="D19" s="3" t="s">
+      <c r="D23" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="11"/>
+    </row>
+    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="4">
+        <v>6</v>
+      </c>
+      <c r="C24" s="4">
         <v>23</v>
       </c>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="2">
-        <v>6</v>
-      </c>
-      <c r="C20" s="2">
-        <v>19</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="D24" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" s="11"/>
+    </row>
+    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="4">
+        <v>6</v>
+      </c>
+      <c r="C25" s="4">
         <v>24</v>
       </c>
-      <c r="E20" s="10"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="2">
-        <v>6</v>
-      </c>
-      <c r="C21" s="2">
-        <v>20</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="D25" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="11"/>
+    </row>
+    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="4">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4">
         <v>25</v>
       </c>
-      <c r="E21" s="10"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="2">
-        <v>6</v>
-      </c>
-      <c r="C22" s="2">
-        <v>21</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="D26" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="11"/>
+    </row>
+    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="4">
+        <v>6</v>
+      </c>
+      <c r="C27" s="4">
         <v>26</v>
       </c>
-      <c r="E22" s="10"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="2">
-        <v>6</v>
-      </c>
-      <c r="C23" s="2">
-        <v>22</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="D27" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="11"/>
+    </row>
+    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="4">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4">
         <v>27</v>
       </c>
-      <c r="E23" s="10"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="2">
-        <v>6</v>
-      </c>
-      <c r="C24" s="2">
-        <v>23</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="D28" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="11"/>
+    </row>
+    <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="4">
+        <v>6</v>
+      </c>
+      <c r="C29" s="4">
         <v>28</v>
       </c>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="2">
-        <v>6</v>
-      </c>
-      <c r="C25" s="2">
-        <v>24</v>
-      </c>
-      <c r="D25" s="3" t="s">
+      <c r="D29" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" s="11"/>
+    </row>
+    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="4">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4">
         <v>29</v>
       </c>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="2">
-        <v>6</v>
-      </c>
-      <c r="C26" s="2">
-        <v>25</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="D30" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="11"/>
+    </row>
+    <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="4">
+        <v>6</v>
+      </c>
+      <c r="C31" s="4">
         <v>30</v>
       </c>
-      <c r="E26" s="10"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="2">
-        <v>6</v>
-      </c>
-      <c r="C27" s="2">
-        <v>26</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="D31" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="11"/>
+    </row>
+    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="4">
+        <v>6</v>
+      </c>
+      <c r="C32" s="4">
         <v>31</v>
       </c>
-      <c r="E27" s="10"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="2">
-        <v>6</v>
-      </c>
-      <c r="C28" s="2">
-        <v>27</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="10"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="2">
-        <v>6</v>
-      </c>
-      <c r="C29" s="2">
-        <v>28</v>
-      </c>
-      <c r="D29" s="3" t="s">
+      <c r="D32" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" s="11"/>
+    </row>
+    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="4">
+        <v>6</v>
+      </c>
+      <c r="C33" s="4">
         <v>32</v>
       </c>
-      <c r="E29" s="10"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="2">
-        <v>6</v>
-      </c>
-      <c r="C30" s="2">
-        <v>29</v>
-      </c>
-      <c r="D30" s="3" t="s">
+      <c r="D33" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="11"/>
+    </row>
+    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="4">
+        <v>6</v>
+      </c>
+      <c r="C34" s="4">
         <v>33</v>
       </c>
-      <c r="E30" s="10"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" s="2">
-        <v>6</v>
-      </c>
-      <c r="C31" s="2">
-        <v>30</v>
-      </c>
-      <c r="D31" s="3" t="s">
+      <c r="D34" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E34" s="11"/>
+    </row>
+    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="4">
+        <v>6</v>
+      </c>
+      <c r="C35" s="4">
         <v>34</v>
       </c>
-      <c r="E31" s="10"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32" s="2">
-        <v>6</v>
-      </c>
-      <c r="C32" s="2">
-        <v>31</v>
-      </c>
-      <c r="D32" s="3" t="s">
+      <c r="D35" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E35" s="11"/>
+    </row>
+    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="4">
+        <v>6</v>
+      </c>
+      <c r="C36" s="4">
         <v>35</v>
       </c>
-      <c r="E32" s="10"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="2">
-        <v>6</v>
-      </c>
-      <c r="C33" s="2">
-        <v>32</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="D36" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E36" s="11"/>
+    </row>
+    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="4">
+        <v>6</v>
+      </c>
+      <c r="C37" s="4">
         <v>36</v>
       </c>
-      <c r="E33" s="10"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" s="2">
-        <v>6</v>
-      </c>
-      <c r="C34" s="2">
-        <v>33</v>
-      </c>
-      <c r="D34" s="3" t="s">
+      <c r="D37" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="11"/>
+    </row>
+    <row r="38" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="4">
+        <v>6</v>
+      </c>
+      <c r="C38" s="4">
         <v>37</v>
       </c>
-      <c r="E34" s="10"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="2">
-        <v>6</v>
-      </c>
-      <c r="C35" s="2">
-        <v>34</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="D38" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E38" s="11"/>
+    </row>
+    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="4">
+        <v>6</v>
+      </c>
+      <c r="C39" s="4">
         <v>38</v>
       </c>
-      <c r="E35" s="10"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" s="2">
-        <v>6</v>
-      </c>
-      <c r="C36" s="2">
-        <v>35</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="10"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B37" s="2">
-        <v>6</v>
-      </c>
-      <c r="C37" s="2">
-        <v>36</v>
-      </c>
-      <c r="D37" s="3" t="s">
+      <c r="D39" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" s="11"/>
+    </row>
+    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="4">
+        <v>6</v>
+      </c>
+      <c r="C40" s="4">
         <v>39</v>
       </c>
-      <c r="E37" s="10"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38" s="2">
-        <v>6</v>
-      </c>
-      <c r="C38" s="2">
-        <v>37</v>
-      </c>
-      <c r="D38" s="3" t="s">
+      <c r="D40" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="11"/>
+    </row>
+    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="4">
+        <v>6</v>
+      </c>
+      <c r="C41" s="4">
         <v>40</v>
       </c>
-      <c r="E38" s="10"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" s="2">
-        <v>6</v>
-      </c>
-      <c r="C39" s="2">
-        <v>38</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" s="10"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B40" s="2">
-        <v>6</v>
-      </c>
-      <c r="C40" s="2">
-        <v>39</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="10"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B41" s="2">
-        <v>6</v>
-      </c>
-      <c r="C41" s="2">
-        <v>40</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E41" s="10"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D41" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41" s="11"/>
+    </row>
+    <row r="42" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>5</v>
       </c>
@@ -1398,10 +1597,12 @@
       <c r="C42" s="4">
         <v>1</v>
       </c>
-      <c r="D42" s="5"/>
+      <c r="D42" s="13" t="s">
+        <v>105</v>
+      </c>
       <c r="E42" s="11"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
@@ -1411,10 +1612,12 @@
       <c r="C43" s="4">
         <v>2</v>
       </c>
-      <c r="D43" s="5"/>
+      <c r="D43" s="13" t="s">
+        <v>106</v>
+      </c>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -1424,10 +1627,12 @@
       <c r="C44" s="4">
         <v>3</v>
       </c>
-      <c r="D44" s="5"/>
+      <c r="D44" s="13" t="s">
+        <v>107</v>
+      </c>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>5</v>
       </c>
@@ -1437,10 +1642,12 @@
       <c r="C45" s="4">
         <v>4</v>
       </c>
-      <c r="D45" s="5"/>
+      <c r="D45" s="13" t="s">
+        <v>108</v>
+      </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1453,7 +1660,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1466,7 +1673,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1479,7 +1686,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1492,7 +1699,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -1505,7 +1712,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1518,7 +1725,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1531,7 +1738,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1544,7 +1751,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -1557,7 +1764,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="11"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1570,7 +1777,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="11"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -1583,7 +1790,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -1596,7 +1803,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -1609,7 +1816,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -1622,7 +1829,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -1635,7 +1842,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -1648,7 +1855,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -1661,7 +1868,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -1674,7 +1881,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -1687,7 +1894,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -1700,7 +1907,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -1713,7 +1920,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -1726,7 +1933,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -1739,7 +1946,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -1752,7 +1959,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -1765,7 +1972,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -1778,7 +1985,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -1791,7 +1998,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -1804,7 +2011,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -1817,7 +2024,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -1830,7 +2037,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -1843,7 +2050,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -1856,7 +2063,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -1869,7 +2076,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -1882,7 +2089,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -1895,7 +2102,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -1908,7 +2115,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -1921,7 +2128,7 @@
       <c r="D82" s="5"/>
       <c r="E82" s="11"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -1934,7 +2141,7 @@
       <c r="D83" s="5"/>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -1947,7 +2154,7 @@
       <c r="D84" s="5"/>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -1960,7 +2167,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -1973,7 +2180,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="11"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -1986,7 +2193,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="11"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -1999,7 +2206,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="11"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2012,7 +2219,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="11"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2025,7 +2232,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="11"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2038,7 +2245,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2051,7 +2258,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2064,7 +2271,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2077,7 +2284,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2090,7 +2297,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2103,7 +2310,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2116,7 +2323,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2129,7 +2336,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2142,7 +2349,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2155,7 +2362,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2168,7 +2375,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2181,7 +2388,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2194,7 +2401,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2207,7 +2414,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2220,7 +2427,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2233,7 +2440,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2246,7 +2453,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2259,7 +2466,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2272,7 +2479,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2285,7 +2492,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2298,7 +2505,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2311,7 +2518,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2324,7 +2531,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2337,7 +2544,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2350,7 +2557,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2363,7 +2570,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2376,7 +2583,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2389,7 +2596,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2402,7 +2609,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2415,7 +2622,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>
@@ -2428,7 +2635,7 @@
       <c r="D121" s="5"/>
       <c r="E121" s="11"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>5</v>
       </c>
@@ -2441,7 +2648,7 @@
       <c r="D122" s="5"/>
       <c r="E122" s="11"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>5</v>
       </c>
@@ -2454,7 +2661,7 @@
       <c r="D123" s="5"/>
       <c r="E123" s="11"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>5</v>
       </c>
@@ -2467,7 +2674,7 @@
       <c r="D124" s="5"/>
       <c r="E124" s="11"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>5</v>
       </c>
@@ -2480,7 +2687,7 @@
       <c r="D125" s="5"/>
       <c r="E125" s="11"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>5</v>
       </c>
@@ -2493,7 +2700,7 @@
       <c r="D126" s="5"/>
       <c r="E126" s="11"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>5</v>
       </c>
@@ -2506,7 +2713,7 @@
       <c r="D127" s="5"/>
       <c r="E127" s="11"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>5</v>
       </c>
@@ -2519,7 +2726,7 @@
       <c r="D128" s="5"/>
       <c r="E128" s="11"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>5</v>
       </c>
@@ -2532,7 +2739,7 @@
       <c r="D129" s="5"/>
       <c r="E129" s="11"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>5</v>
       </c>
@@ -2545,7 +2752,7 @@
       <c r="D130" s="5"/>
       <c r="E130" s="11"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>5</v>
       </c>
@@ -2558,7 +2765,7 @@
       <c r="D131" s="5"/>
       <c r="E131" s="11"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>5</v>
       </c>
@@ -2571,7 +2778,7 @@
       <c r="D132" s="5"/>
       <c r="E132" s="11"/>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>5</v>
       </c>
@@ -2584,7 +2791,7 @@
       <c r="D133" s="5"/>
       <c r="E133" s="11"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>5</v>
       </c>
@@ -2597,7 +2804,7 @@
       <c r="D134" s="5"/>
       <c r="E134" s="11"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>5</v>
       </c>
@@ -2610,7 +2817,7 @@
       <c r="D135" s="5"/>
       <c r="E135" s="11"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>5</v>
       </c>
@@ -2623,7 +2830,7 @@
       <c r="D136" s="5"/>
       <c r="E136" s="11"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>5</v>
       </c>
@@ -2636,7 +2843,7 @@
       <c r="D137" s="5"/>
       <c r="E137" s="11"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>5</v>
       </c>
@@ -2649,7 +2856,7 @@
       <c r="D138" s="5"/>
       <c r="E138" s="11"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>5</v>
       </c>
@@ -2662,7 +2869,7 @@
       <c r="D139" s="5"/>
       <c r="E139" s="11"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>5</v>
       </c>
@@ -2675,7 +2882,7 @@
       <c r="D140" s="5"/>
       <c r="E140" s="11"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>5</v>
       </c>
@@ -2688,7 +2895,7 @@
       <c r="D141" s="5"/>
       <c r="E141" s="11"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>5</v>
       </c>
@@ -2701,7 +2908,7 @@
       <c r="D142" s="5"/>
       <c r="E142" s="11"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>5</v>
       </c>
@@ -2714,7 +2921,7 @@
       <c r="D143" s="5"/>
       <c r="E143" s="11"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>5</v>
       </c>
@@ -2727,7 +2934,7 @@
       <c r="D144" s="5"/>
       <c r="E144" s="11"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>5</v>
       </c>
@@ -2740,7 +2947,7 @@
       <c r="D145" s="5"/>
       <c r="E145" s="11"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>5</v>
       </c>
@@ -2753,7 +2960,7 @@
       <c r="D146" s="5"/>
       <c r="E146" s="11"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>5</v>
       </c>
@@ -2766,7 +2973,7 @@
       <c r="D147" s="5"/>
       <c r="E147" s="11"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>5</v>
       </c>
@@ -2779,7 +2986,7 @@
       <c r="D148" s="5"/>
       <c r="E148" s="11"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>5</v>
       </c>
@@ -2792,7 +2999,7 @@
       <c r="D149" s="5"/>
       <c r="E149" s="11"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>5</v>
       </c>
@@ -2805,7 +3012,7 @@
       <c r="D150" s="5"/>
       <c r="E150" s="11"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>5</v>
       </c>
@@ -2818,7 +3025,7 @@
       <c r="D151" s="5"/>
       <c r="E151" s="11"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>5</v>
       </c>
@@ -2831,7 +3038,7 @@
       <c r="D152" s="5"/>
       <c r="E152" s="11"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>5</v>
       </c>
@@ -2844,7 +3051,7 @@
       <c r="D153" s="5"/>
       <c r="E153" s="11"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>5</v>
       </c>
@@ -2857,7 +3064,7 @@
       <c r="D154" s="5"/>
       <c r="E154" s="11"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>5</v>
       </c>
@@ -2870,7 +3077,7 @@
       <c r="D155" s="5"/>
       <c r="E155" s="11"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>5</v>
       </c>
@@ -2883,7 +3090,7 @@
       <c r="D156" s="5"/>
       <c r="E156" s="11"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>5</v>
       </c>
@@ -2896,7 +3103,7 @@
       <c r="D157" s="5"/>
       <c r="E157" s="11"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>5</v>
       </c>
@@ -2909,7 +3116,7 @@
       <c r="D158" s="5"/>
       <c r="E158" s="11"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>5</v>
       </c>
@@ -2922,7 +3129,7 @@
       <c r="D159" s="5"/>
       <c r="E159" s="11"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>5</v>
       </c>
@@ -2935,7 +3142,7 @@
       <c r="D160" s="5"/>
       <c r="E160" s="11"/>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>5</v>
       </c>
@@ -2948,7 +3155,7 @@
       <c r="D161" s="5"/>
       <c r="E161" s="11"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>43</v>
       </c>
@@ -2956,523 +3163,605 @@
         <v>6</v>
       </c>
       <c r="C162" s="4">
+        <v>41</v>
+      </c>
+      <c r="D162" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E162" s="11"/>
+    </row>
+    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B163" s="4">
+        <v>6</v>
+      </c>
+      <c r="C163" s="4">
+        <v>42</v>
+      </c>
+      <c r="D163" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E163" s="11"/>
+    </row>
+    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B164" s="4">
+        <v>6</v>
+      </c>
+      <c r="C164" s="4">
+        <v>43</v>
+      </c>
+      <c r="D164" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E164" s="11"/>
+    </row>
+    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B165" s="4">
+        <v>6</v>
+      </c>
+      <c r="C165" s="4">
+        <v>44</v>
+      </c>
+      <c r="D165" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E165" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B166" s="2">
+        <v>6</v>
+      </c>
+      <c r="C166" s="2">
         <v>1</v>
       </c>
-      <c r="D162" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E162" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A163" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B163" s="4">
-        <v>6</v>
-      </c>
-      <c r="C163" s="4">
+      <c r="D166" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E166" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B167" s="2">
+        <v>6</v>
+      </c>
+      <c r="C167" s="2">
         <v>2</v>
       </c>
-      <c r="D163" s="5"/>
-      <c r="E163" s="11"/>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A164" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B164" s="4">
-        <v>6</v>
-      </c>
-      <c r="C164" s="4">
+      <c r="D167" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E167" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B168" s="2">
+        <v>6</v>
+      </c>
+      <c r="C168" s="2">
         <v>3</v>
       </c>
-      <c r="D164" s="5"/>
-      <c r="E164" s="11"/>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A165" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B165" s="4">
-        <v>6</v>
-      </c>
-      <c r="C165" s="4">
+      <c r="D168" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" s="10"/>
+    </row>
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B169" s="2">
+        <v>6</v>
+      </c>
+      <c r="C169" s="2">
         <v>4</v>
       </c>
-      <c r="D165" s="5"/>
-      <c r="E165" s="11"/>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A166" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B166" s="4">
-        <v>6</v>
-      </c>
-      <c r="C166" s="4">
-        <v>5</v>
-      </c>
-      <c r="D166" s="5"/>
-      <c r="E166" s="11"/>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A167" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B167" s="4">
-        <v>6</v>
-      </c>
-      <c r="C167" s="4">
-        <v>6</v>
-      </c>
-      <c r="D167" s="5"/>
-      <c r="E167" s="11"/>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A168" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B168" s="4">
-        <v>6</v>
-      </c>
-      <c r="C168" s="4">
-        <v>7</v>
-      </c>
-      <c r="D168" s="5"/>
-      <c r="E168" s="11"/>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A169" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B169" s="4">
-        <v>6</v>
-      </c>
-      <c r="C169" s="4">
-        <v>8</v>
-      </c>
-      <c r="D169" s="5"/>
-      <c r="E169" s="11"/>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A170" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B170" s="4">
-        <v>6</v>
-      </c>
-      <c r="C170" s="4">
-        <v>9</v>
-      </c>
-      <c r="D170" s="5"/>
-      <c r="E170" s="11"/>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A171" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B171" s="4">
-        <v>6</v>
-      </c>
-      <c r="C171" s="4">
+      <c r="D169" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D171" s="5"/>
-      <c r="E171" s="11"/>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A172" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B172" s="4">
-        <v>6</v>
-      </c>
-      <c r="C172" s="4">
+      <c r="E169" s="10"/>
+    </row>
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B170" s="2">
+        <v>6</v>
+      </c>
+      <c r="C170" s="2">
+        <v>5</v>
+      </c>
+      <c r="D170" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D172" s="5"/>
-      <c r="E172" s="11"/>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A173" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B173" s="4">
-        <v>6</v>
-      </c>
-      <c r="C173" s="4">
+      <c r="E170" s="10"/>
+    </row>
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B171" s="2">
+        <v>6</v>
+      </c>
+      <c r="C171" s="2">
+        <v>6</v>
+      </c>
+      <c r="D171" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D173" s="5"/>
-      <c r="E173" s="11"/>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A174" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B174" s="4">
-        <v>6</v>
-      </c>
-      <c r="C174" s="4">
+      <c r="E171" s="10"/>
+    </row>
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B172" s="2">
+        <v>6</v>
+      </c>
+      <c r="C172" s="2">
+        <v>7</v>
+      </c>
+      <c r="D172" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D174" s="5"/>
-      <c r="E174" s="11"/>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A175" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B175" s="4">
-        <v>6</v>
-      </c>
-      <c r="C175" s="4">
+      <c r="E172" s="10"/>
+    </row>
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B173" s="2">
+        <v>6</v>
+      </c>
+      <c r="C173" s="2">
+        <v>8</v>
+      </c>
+      <c r="D173" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D175" s="5"/>
-      <c r="E175" s="11"/>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A176" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B176" s="4">
-        <v>6</v>
-      </c>
-      <c r="C176" s="4">
+      <c r="E173" s="10"/>
+    </row>
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B174" s="2">
+        <v>6</v>
+      </c>
+      <c r="C174" s="2">
+        <v>9</v>
+      </c>
+      <c r="D174" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D176" s="5"/>
-      <c r="E176" s="11"/>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A177" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B177" s="4">
-        <v>6</v>
-      </c>
-      <c r="C177" s="4">
+      <c r="E174" s="10"/>
+    </row>
+    <row r="175" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B175" s="2">
+        <v>6</v>
+      </c>
+      <c r="C175" s="2">
+        <v>10</v>
+      </c>
+      <c r="D175" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D177" s="5"/>
-      <c r="E177" s="11"/>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A178" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B178" s="4">
-        <v>6</v>
-      </c>
-      <c r="C178" s="4">
+      <c r="E175" s="10"/>
+    </row>
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B176" s="2">
+        <v>6</v>
+      </c>
+      <c r="C176" s="2">
+        <v>11</v>
+      </c>
+      <c r="D176" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D178" s="5"/>
-      <c r="E178" s="11"/>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A179" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B179" s="4">
-        <v>6</v>
-      </c>
-      <c r="C179" s="4">
+      <c r="E176" s="10"/>
+    </row>
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B177" s="2">
+        <v>6</v>
+      </c>
+      <c r="C177" s="2">
+        <v>12</v>
+      </c>
+      <c r="D177" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D179" s="5"/>
-      <c r="E179" s="11"/>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A180" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B180" s="4">
-        <v>6</v>
-      </c>
-      <c r="C180" s="4">
+      <c r="E177" s="10"/>
+    </row>
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B178" s="2">
+        <v>6</v>
+      </c>
+      <c r="C178" s="2">
+        <v>13</v>
+      </c>
+      <c r="D178" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D180" s="5"/>
-      <c r="E180" s="11"/>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A181" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B181" s="4">
-        <v>6</v>
-      </c>
-      <c r="C181" s="4">
+      <c r="E178" s="10"/>
+    </row>
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B179" s="2">
+        <v>6</v>
+      </c>
+      <c r="C179" s="2">
+        <v>14</v>
+      </c>
+      <c r="D179" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D181" s="5"/>
-      <c r="E181" s="11"/>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A182" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B182" s="4">
-        <v>6</v>
-      </c>
-      <c r="C182" s="4">
+      <c r="E179" s="10"/>
+    </row>
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B180" s="2">
+        <v>6</v>
+      </c>
+      <c r="C180" s="2">
+        <v>15</v>
+      </c>
+      <c r="D180" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D182" s="5"/>
-      <c r="E182" s="11"/>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A183" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B183" s="4">
-        <v>6</v>
-      </c>
-      <c r="C183" s="4">
+      <c r="E180" s="10"/>
+    </row>
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B181" s="2">
+        <v>6</v>
+      </c>
+      <c r="C181" s="2">
+        <v>16</v>
+      </c>
+      <c r="D181" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D183" s="5"/>
-      <c r="E183" s="11"/>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A184" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B184" s="4">
-        <v>6</v>
-      </c>
-      <c r="C184" s="4">
+      <c r="E181" s="10"/>
+    </row>
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B182" s="2">
+        <v>6</v>
+      </c>
+      <c r="C182" s="2">
+        <v>17</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E182" s="10"/>
+    </row>
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B183" s="2">
+        <v>6</v>
+      </c>
+      <c r="C183" s="2">
+        <v>18</v>
+      </c>
+      <c r="D183" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D184" s="5"/>
-      <c r="E184" s="11"/>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A185" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B185" s="4">
-        <v>6</v>
-      </c>
-      <c r="C185" s="4">
+      <c r="E183" s="10"/>
+    </row>
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B184" s="2">
+        <v>6</v>
+      </c>
+      <c r="C184" s="2">
+        <v>19</v>
+      </c>
+      <c r="D184" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D185" s="5"/>
-      <c r="E185" s="11"/>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A186" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B186" s="4">
-        <v>6</v>
-      </c>
-      <c r="C186" s="4">
+      <c r="E184" s="10"/>
+    </row>
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B185" s="2">
+        <v>6</v>
+      </c>
+      <c r="C185" s="2">
+        <v>20</v>
+      </c>
+      <c r="D185" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D186" s="5"/>
-      <c r="E186" s="11"/>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A187" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B187" s="4">
-        <v>6</v>
-      </c>
-      <c r="C187" s="4">
+      <c r="E185" s="10"/>
+    </row>
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B186" s="2">
+        <v>6</v>
+      </c>
+      <c r="C186" s="2">
+        <v>21</v>
+      </c>
+      <c r="D186" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D187" s="5"/>
-      <c r="E187" s="11"/>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A188" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B188" s="4">
-        <v>6</v>
-      </c>
-      <c r="C188" s="4">
+      <c r="E186" s="10"/>
+    </row>
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B187" s="2">
+        <v>6</v>
+      </c>
+      <c r="C187" s="2">
+        <v>22</v>
+      </c>
+      <c r="D187" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D188" s="5"/>
-      <c r="E188" s="11"/>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A189" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B189" s="4">
-        <v>6</v>
-      </c>
-      <c r="C189" s="4">
+      <c r="E187" s="10"/>
+    </row>
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B188" s="2">
+        <v>6</v>
+      </c>
+      <c r="C188" s="2">
+        <v>23</v>
+      </c>
+      <c r="D188" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D189" s="5"/>
-      <c r="E189" s="11"/>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A190" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B190" s="4">
-        <v>6</v>
-      </c>
-      <c r="C190" s="4">
+      <c r="E188" s="10"/>
+    </row>
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B189" s="2">
+        <v>6</v>
+      </c>
+      <c r="C189" s="2">
+        <v>24</v>
+      </c>
+      <c r="D189" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D190" s="5"/>
-      <c r="E190" s="11"/>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A191" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B191" s="4">
-        <v>6</v>
-      </c>
-      <c r="C191" s="4">
+      <c r="E189" s="10"/>
+    </row>
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B190" s="2">
+        <v>6</v>
+      </c>
+      <c r="C190" s="2">
+        <v>25</v>
+      </c>
+      <c r="D190" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D191" s="5"/>
-      <c r="E191" s="11"/>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A192" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B192" s="4">
-        <v>6</v>
-      </c>
-      <c r="C192" s="4">
+      <c r="E190" s="10"/>
+    </row>
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B191" s="2">
+        <v>6</v>
+      </c>
+      <c r="C191" s="2">
+        <v>26</v>
+      </c>
+      <c r="D191" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D192" s="5"/>
-      <c r="E192" s="11"/>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A193" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B193" s="4">
-        <v>6</v>
-      </c>
-      <c r="C193" s="4">
+      <c r="E191" s="10"/>
+    </row>
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B192" s="2">
+        <v>6</v>
+      </c>
+      <c r="C192" s="2">
+        <v>27</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E192" s="10"/>
+    </row>
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B193" s="2">
+        <v>6</v>
+      </c>
+      <c r="C193" s="2">
+        <v>28</v>
+      </c>
+      <c r="D193" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D193" s="5"/>
-      <c r="E193" s="11"/>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A194" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B194" s="4">
-        <v>6</v>
-      </c>
-      <c r="C194" s="4">
+      <c r="E193" s="10"/>
+    </row>
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B194" s="2">
+        <v>6</v>
+      </c>
+      <c r="C194" s="2">
+        <v>29</v>
+      </c>
+      <c r="D194" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D194" s="5"/>
-      <c r="E194" s="11"/>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A195" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B195" s="4">
-        <v>6</v>
-      </c>
-      <c r="C195" s="4">
+      <c r="E194" s="10"/>
+    </row>
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B195" s="2">
+        <v>6</v>
+      </c>
+      <c r="C195" s="2">
+        <v>30</v>
+      </c>
+      <c r="D195" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D195" s="5"/>
-      <c r="E195" s="11"/>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A196" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B196" s="4">
-        <v>6</v>
-      </c>
-      <c r="C196" s="4">
+      <c r="E195" s="10"/>
+    </row>
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B196" s="2">
+        <v>6</v>
+      </c>
+      <c r="C196" s="2">
+        <v>31</v>
+      </c>
+      <c r="D196" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D196" s="5"/>
-      <c r="E196" s="11"/>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A197" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B197" s="4">
-        <v>6</v>
-      </c>
-      <c r="C197" s="4">
+      <c r="E196" s="10"/>
+    </row>
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B197" s="2">
+        <v>6</v>
+      </c>
+      <c r="C197" s="2">
+        <v>32</v>
+      </c>
+      <c r="D197" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D197" s="5"/>
-      <c r="E197" s="11"/>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A198" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B198" s="4">
-        <v>6</v>
-      </c>
-      <c r="C198" s="4">
+      <c r="E197" s="10"/>
+    </row>
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B198" s="2">
+        <v>6</v>
+      </c>
+      <c r="C198" s="2">
+        <v>33</v>
+      </c>
+      <c r="D198" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D198" s="5"/>
-      <c r="E198" s="11"/>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A199" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B199" s="4">
-        <v>6</v>
-      </c>
-      <c r="C199" s="4">
+      <c r="E198" s="10"/>
+    </row>
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B199" s="2">
+        <v>6</v>
+      </c>
+      <c r="C199" s="2">
+        <v>34</v>
+      </c>
+      <c r="D199" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D199" s="5"/>
-      <c r="E199" s="11"/>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A200" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B200" s="4">
-        <v>6</v>
-      </c>
-      <c r="C200" s="4">
+      <c r="E199" s="10"/>
+    </row>
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B200" s="2">
+        <v>6</v>
+      </c>
+      <c r="C200" s="2">
+        <v>35</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E200" s="10"/>
+    </row>
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B201" s="2">
+        <v>6</v>
+      </c>
+      <c r="C201" s="2">
+        <v>36</v>
+      </c>
+      <c r="D201" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D200" s="5"/>
-      <c r="E200" s="11"/>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A201" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B201" s="4">
-        <v>6</v>
-      </c>
-      <c r="C201" s="4">
-        <v>40</v>
-      </c>
-      <c r="D201" s="5"/>
-      <c r="E201" s="11"/>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E201" s="10"/>
+    </row>
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
         <v>43</v>
       </c>
@@ -3485,7 +3774,7 @@
       <c r="D202" s="5"/>
       <c r="E202" s="11"/>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
         <v>43</v>
       </c>
@@ -3498,7 +3787,7 @@
       <c r="D203" s="5"/>
       <c r="E203" s="11"/>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
         <v>43</v>
       </c>
@@ -3511,7 +3800,7 @@
       <c r="D204" s="5"/>
       <c r="E204" s="11"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
         <v>43</v>
       </c>
@@ -3524,7 +3813,7 @@
       <c r="D205" s="5"/>
       <c r="E205" s="11"/>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
         <v>43</v>
       </c>
@@ -3537,7 +3826,7 @@
       <c r="D206" s="5"/>
       <c r="E206" s="11"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
         <v>43</v>
       </c>
@@ -3550,7 +3839,7 @@
       <c r="D207" s="5"/>
       <c r="E207" s="11"/>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
         <v>43</v>
       </c>
@@ -3563,7 +3852,7 @@
       <c r="D208" s="5"/>
       <c r="E208" s="11"/>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
         <v>43</v>
       </c>
@@ -3576,7 +3865,7 @@
       <c r="D209" s="5"/>
       <c r="E209" s="11"/>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
         <v>43</v>
       </c>
@@ -3589,7 +3878,7 @@
       <c r="D210" s="5"/>
       <c r="E210" s="11"/>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
         <v>43</v>
       </c>
@@ -3602,7 +3891,7 @@
       <c r="D211" s="5"/>
       <c r="E211" s="11"/>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
         <v>43</v>
       </c>
@@ -3615,7 +3904,7 @@
       <c r="D212" s="5"/>
       <c r="E212" s="11"/>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
         <v>43</v>
       </c>
@@ -3628,7 +3917,7 @@
       <c r="D213" s="5"/>
       <c r="E213" s="11"/>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
         <v>43</v>
       </c>
@@ -3641,7 +3930,7 @@
       <c r="D214" s="5"/>
       <c r="E214" s="11"/>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
         <v>43</v>
       </c>
@@ -3654,7 +3943,7 @@
       <c r="D215" s="5"/>
       <c r="E215" s="11"/>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
         <v>43</v>
       </c>
@@ -3667,7 +3956,7 @@
       <c r="D216" s="5"/>
       <c r="E216" s="11"/>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
         <v>43</v>
       </c>
@@ -3680,7 +3969,7 @@
       <c r="D217" s="5"/>
       <c r="E217" s="11"/>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
         <v>43</v>
       </c>
@@ -3693,7 +3982,7 @@
       <c r="D218" s="5"/>
       <c r="E218" s="11"/>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
         <v>43</v>
       </c>
@@ -3706,7 +3995,7 @@
       <c r="D219" s="5"/>
       <c r="E219" s="11"/>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
         <v>43</v>
       </c>
@@ -3719,7 +4008,7 @@
       <c r="D220" s="5"/>
       <c r="E220" s="11"/>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
         <v>43</v>
       </c>
@@ -3732,7 +4021,7 @@
       <c r="D221" s="5"/>
       <c r="E221" s="11"/>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
         <v>43</v>
       </c>
@@ -3745,7 +4034,7 @@
       <c r="D222" s="5"/>
       <c r="E222" s="11"/>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
         <v>43</v>
       </c>
@@ -3758,7 +4047,7 @@
       <c r="D223" s="5"/>
       <c r="E223" s="11"/>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
         <v>43</v>
       </c>
@@ -3771,7 +4060,7 @@
       <c r="D224" s="5"/>
       <c r="E224" s="11"/>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
         <v>43</v>
       </c>
@@ -3784,7 +4073,7 @@
       <c r="D225" s="5"/>
       <c r="E225" s="11"/>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
         <v>43</v>
       </c>
@@ -3797,7 +4086,7 @@
       <c r="D226" s="5"/>
       <c r="E226" s="11"/>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
         <v>43</v>
       </c>
@@ -3810,7 +4099,7 @@
       <c r="D227" s="5"/>
       <c r="E227" s="11"/>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
         <v>43</v>
       </c>
@@ -3823,7 +4112,7 @@
       <c r="D228" s="5"/>
       <c r="E228" s="11"/>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
         <v>43</v>
       </c>
@@ -3836,7 +4125,7 @@
       <c r="D229" s="5"/>
       <c r="E229" s="11"/>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
         <v>43</v>
       </c>
@@ -3849,7 +4138,7 @@
       <c r="D230" s="5"/>
       <c r="E230" s="11"/>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
         <v>43</v>
       </c>
@@ -3862,7 +4151,7 @@
       <c r="D231" s="5"/>
       <c r="E231" s="11"/>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
         <v>43</v>
       </c>
@@ -3875,7 +4164,7 @@
       <c r="D232" s="5"/>
       <c r="E232" s="11"/>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
         <v>43</v>
       </c>
@@ -3888,7 +4177,7 @@
       <c r="D233" s="5"/>
       <c r="E233" s="11"/>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
         <v>43</v>
       </c>
@@ -3901,7 +4190,7 @@
       <c r="D234" s="5"/>
       <c r="E234" s="11"/>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
         <v>43</v>
       </c>
@@ -3914,7 +4203,7 @@
       <c r="D235" s="5"/>
       <c r="E235" s="11"/>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
         <v>43</v>
       </c>
@@ -3927,7 +4216,7 @@
       <c r="D236" s="5"/>
       <c r="E236" s="11"/>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
         <v>43</v>
       </c>
@@ -3940,7 +4229,7 @@
       <c r="D237" s="5"/>
       <c r="E237" s="11"/>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
         <v>43</v>
       </c>
@@ -3953,7 +4242,7 @@
       <c r="D238" s="5"/>
       <c r="E238" s="11"/>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
         <v>43</v>
       </c>
@@ -3966,7 +4255,7 @@
       <c r="D239" s="5"/>
       <c r="E239" s="11"/>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
         <v>43</v>
       </c>
@@ -3979,7 +4268,7 @@
       <c r="D240" s="5"/>
       <c r="E240" s="11"/>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
         <v>43</v>
       </c>
@@ -3992,7 +4281,7 @@
       <c r="D241" s="5"/>
       <c r="E241" s="11"/>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
         <v>43</v>
       </c>
@@ -4005,7 +4294,7 @@
       <c r="D242" s="5"/>
       <c r="E242" s="11"/>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
         <v>43</v>
       </c>
@@ -4018,7 +4307,7 @@
       <c r="D243" s="5"/>
       <c r="E243" s="11"/>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
         <v>43</v>
       </c>
@@ -4031,7 +4320,7 @@
       <c r="D244" s="5"/>
       <c r="E244" s="11"/>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
         <v>43</v>
       </c>
@@ -4044,7 +4333,7 @@
       <c r="D245" s="5"/>
       <c r="E245" s="11"/>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
         <v>43</v>
       </c>
@@ -4057,7 +4346,7 @@
       <c r="D246" s="5"/>
       <c r="E246" s="11"/>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
         <v>43</v>
       </c>
@@ -4070,7 +4359,7 @@
       <c r="D247" s="5"/>
       <c r="E247" s="11"/>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
         <v>43</v>
       </c>
@@ -4083,7 +4372,7 @@
       <c r="D248" s="5"/>
       <c r="E248" s="11"/>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
         <v>43</v>
       </c>
@@ -4096,7 +4385,7 @@
       <c r="D249" s="5"/>
       <c r="E249" s="11"/>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
         <v>43</v>
       </c>
@@ -4109,7 +4398,7 @@
       <c r="D250" s="5"/>
       <c r="E250" s="11"/>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
         <v>43</v>
       </c>
@@ -4122,7 +4411,7 @@
       <c r="D251" s="5"/>
       <c r="E251" s="11"/>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
         <v>43</v>
       </c>
@@ -4135,7 +4424,7 @@
       <c r="D252" s="5"/>
       <c r="E252" s="11"/>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
         <v>43</v>
       </c>
@@ -4148,7 +4437,7 @@
       <c r="D253" s="5"/>
       <c r="E253" s="11"/>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>43</v>
       </c>
@@ -4161,7 +4450,7 @@
       <c r="D254" s="5"/>
       <c r="E254" s="11"/>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>43</v>
       </c>
@@ -4174,7 +4463,7 @@
       <c r="D255" s="5"/>
       <c r="E255" s="11"/>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>43</v>
       </c>
@@ -4187,7 +4476,7 @@
       <c r="D256" s="5"/>
       <c r="E256" s="11"/>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
         <v>43</v>
       </c>
@@ -4200,7 +4489,7 @@
       <c r="D257" s="5"/>
       <c r="E257" s="11"/>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
         <v>43</v>
       </c>
@@ -4213,7 +4502,7 @@
       <c r="D258" s="5"/>
       <c r="E258" s="11"/>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
         <v>43</v>
       </c>
@@ -4226,7 +4515,7 @@
       <c r="D259" s="5"/>
       <c r="E259" s="11"/>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
         <v>43</v>
       </c>
@@ -4239,7 +4528,7 @@
       <c r="D260" s="5"/>
       <c r="E260" s="11"/>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
         <v>43</v>
       </c>
@@ -4252,7 +4541,7 @@
       <c r="D261" s="5"/>
       <c r="E261" s="11"/>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
         <v>43</v>
       </c>
@@ -4265,7 +4554,7 @@
       <c r="D262" s="5"/>
       <c r="E262" s="11"/>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
         <v>43</v>
       </c>
@@ -4278,7 +4567,7 @@
       <c r="D263" s="5"/>
       <c r="E263" s="11"/>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
         <v>43</v>
       </c>
@@ -4291,7 +4580,7 @@
       <c r="D264" s="5"/>
       <c r="E264" s="11"/>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
         <v>43</v>
       </c>
@@ -4304,7 +4593,7 @@
       <c r="D265" s="5"/>
       <c r="E265" s="11"/>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
         <v>43</v>
       </c>
@@ -4317,7 +4606,7 @@
       <c r="D266" s="5"/>
       <c r="E266" s="11"/>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
         <v>43</v>
       </c>
@@ -4330,7 +4619,7 @@
       <c r="D267" s="5"/>
       <c r="E267" s="11"/>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
         <v>43</v>
       </c>
@@ -4343,7 +4632,7 @@
       <c r="D268" s="5"/>
       <c r="E268" s="11"/>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
         <v>43</v>
       </c>
@@ -4356,7 +4645,7 @@
       <c r="D269" s="5"/>
       <c r="E269" s="11"/>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
         <v>43</v>
       </c>
@@ -4369,7 +4658,7 @@
       <c r="D270" s="5"/>
       <c r="E270" s="11"/>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
         <v>43</v>
       </c>
@@ -4382,7 +4671,7 @@
       <c r="D271" s="5"/>
       <c r="E271" s="11"/>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
         <v>43</v>
       </c>
@@ -4395,7 +4684,7 @@
       <c r="D272" s="5"/>
       <c r="E272" s="11"/>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4" t="s">
         <v>43</v>
       </c>
@@ -4408,7 +4697,7 @@
       <c r="D273" s="5"/>
       <c r="E273" s="11"/>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4" t="s">
         <v>43</v>
       </c>
@@ -4421,7 +4710,7 @@
       <c r="D274" s="5"/>
       <c r="E274" s="11"/>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="4" t="s">
         <v>43</v>
       </c>
@@ -4434,7 +4723,7 @@
       <c r="D275" s="5"/>
       <c r="E275" s="11"/>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
         <v>43</v>
       </c>
@@ -4447,7 +4736,7 @@
       <c r="D276" s="5"/>
       <c r="E276" s="11"/>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
         <v>43</v>
       </c>
@@ -4460,7 +4749,7 @@
       <c r="D277" s="5"/>
       <c r="E277" s="11"/>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
         <v>43</v>
       </c>
@@ -4473,7 +4762,7 @@
       <c r="D278" s="5"/>
       <c r="E278" s="11"/>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
         <v>43</v>
       </c>
@@ -4486,7 +4775,7 @@
       <c r="D279" s="5"/>
       <c r="E279" s="11"/>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
         <v>43</v>
       </c>
@@ -4499,7 +4788,7 @@
       <c r="D280" s="5"/>
       <c r="E280" s="11"/>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
         <v>43</v>
       </c>
@@ -4512,7 +4801,7 @@
       <c r="D281" s="5"/>
       <c r="E281" s="11"/>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>43</v>
       </c>
@@ -4525,7 +4814,7 @@
       <c r="D282" s="5"/>
       <c r="E282" s="11"/>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>43</v>
       </c>
@@ -4538,7 +4827,7 @@
       <c r="D283" s="5"/>
       <c r="E283" s="11"/>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>43</v>
       </c>
@@ -4551,7 +4840,7 @@
       <c r="D284" s="5"/>
       <c r="E284" s="11"/>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>43</v>
       </c>
@@ -4564,7 +4853,7 @@
       <c r="D285" s="5"/>
       <c r="E285" s="11"/>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
         <v>43</v>
       </c>
@@ -4577,7 +4866,7 @@
       <c r="D286" s="5"/>
       <c r="E286" s="11"/>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
         <v>43</v>
       </c>
@@ -4590,7 +4879,7 @@
       <c r="D287" s="5"/>
       <c r="E287" s="11"/>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>43</v>
       </c>
@@ -4603,7 +4892,7 @@
       <c r="D288" s="5"/>
       <c r="E288" s="11"/>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
         <v>43</v>
       </c>
@@ -4616,7 +4905,7 @@
       <c r="D289" s="5"/>
       <c r="E289" s="11"/>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>43</v>
       </c>
@@ -4629,7 +4918,7 @@
       <c r="D290" s="5"/>
       <c r="E290" s="11"/>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>43</v>
       </c>
@@ -4642,7 +4931,7 @@
       <c r="D291" s="5"/>
       <c r="E291" s="11"/>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>43</v>
       </c>
@@ -4655,7 +4944,7 @@
       <c r="D292" s="5"/>
       <c r="E292" s="11"/>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>43</v>
       </c>
@@ -4668,7 +4957,7 @@
       <c r="D293" s="5"/>
       <c r="E293" s="11"/>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>43</v>
       </c>
@@ -4681,7 +4970,7 @@
       <c r="D294" s="5"/>
       <c r="E294" s="11"/>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>43</v>
       </c>
@@ -4694,7 +4983,7 @@
       <c r="D295" s="5"/>
       <c r="E295" s="11"/>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>43</v>
       </c>
@@ -4707,7 +4996,7 @@
       <c r="D296" s="5"/>
       <c r="E296" s="11"/>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>43</v>
       </c>
@@ -4720,7 +5009,7 @@
       <c r="D297" s="5"/>
       <c r="E297" s="11"/>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>43</v>
       </c>
@@ -4733,7 +5022,7 @@
       <c r="D298" s="5"/>
       <c r="E298" s="11"/>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>43</v>
       </c>
@@ -4746,7 +5035,7 @@
       <c r="D299" s="5"/>
       <c r="E299" s="11"/>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
         <v>43</v>
       </c>
@@ -4759,7 +5048,7 @@
       <c r="D300" s="5"/>
       <c r="E300" s="11"/>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
         <v>43</v>
       </c>
@@ -4772,7 +5061,7 @@
       <c r="D301" s="5"/>
       <c r="E301" s="11"/>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
         <v>43</v>
       </c>
@@ -4785,7 +5074,7 @@
       <c r="D302" s="5"/>
       <c r="E302" s="11"/>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
         <v>43</v>
       </c>
@@ -4798,7 +5087,7 @@
       <c r="D303" s="5"/>
       <c r="E303" s="11"/>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>43</v>
       </c>
@@ -4811,7 +5100,7 @@
       <c r="D304" s="5"/>
       <c r="E304" s="11"/>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>43</v>
       </c>
@@ -4824,7 +5113,7 @@
       <c r="D305" s="5"/>
       <c r="E305" s="11"/>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>43</v>
       </c>
@@ -4837,7 +5126,7 @@
       <c r="D306" s="5"/>
       <c r="E306" s="11"/>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>43</v>
       </c>
@@ -4850,7 +5139,7 @@
       <c r="D307" s="5"/>
       <c r="E307" s="11"/>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>43</v>
       </c>
@@ -4863,7 +5152,7 @@
       <c r="D308" s="5"/>
       <c r="E308" s="11"/>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
         <v>43</v>
       </c>
@@ -4876,7 +5165,7 @@
       <c r="D309" s="5"/>
       <c r="E309" s="11"/>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
         <v>43</v>
       </c>
@@ -4889,7 +5178,7 @@
       <c r="D310" s="5"/>
       <c r="E310" s="11"/>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
         <v>43</v>
       </c>
@@ -4902,7 +5191,7 @@
       <c r="D311" s="5"/>
       <c r="E311" s="11"/>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
         <v>43</v>
       </c>
@@ -4915,7 +5204,7 @@
       <c r="D312" s="5"/>
       <c r="E312" s="11"/>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
         <v>43</v>
       </c>
@@ -4928,7 +5217,7 @@
       <c r="D313" s="5"/>
       <c r="E313" s="11"/>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
         <v>43</v>
       </c>
@@ -4941,7 +5230,7 @@
       <c r="D314" s="5"/>
       <c r="E314" s="11"/>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
         <v>43</v>
       </c>
@@ -4954,7 +5243,7 @@
       <c r="D315" s="5"/>
       <c r="E315" s="11"/>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
         <v>43</v>
       </c>
@@ -4967,7 +5256,7 @@
       <c r="D316" s="5"/>
       <c r="E316" s="11"/>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
         <v>43</v>
       </c>
@@ -4980,7 +5269,7 @@
       <c r="D317" s="5"/>
       <c r="E317" s="11"/>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
         <v>43</v>
       </c>
@@ -4993,7 +5282,7 @@
       <c r="D318" s="5"/>
       <c r="E318" s="11"/>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
         <v>43</v>
       </c>
@@ -5006,7 +5295,7 @@
       <c r="D319" s="5"/>
       <c r="E319" s="11"/>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
         <v>43</v>
       </c>
@@ -5019,7 +5308,7 @@
       <c r="D320" s="5"/>
       <c r="E320" s="11"/>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
         <v>43</v>
       </c>
@@ -5032,72 +5321,80 @@
       <c r="D321" s="5"/>
       <c r="E321" s="11"/>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A322" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B322" s="4">
-        <v>6</v>
-      </c>
-      <c r="C322" s="4">
+    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A322" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B322" s="2">
+        <v>6</v>
+      </c>
+      <c r="C322" s="2">
+        <v>37</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E322" s="10"/>
+    </row>
+    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A323" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B323" s="2">
+        <v>6</v>
+      </c>
+      <c r="C323" s="2">
+        <v>38</v>
+      </c>
+      <c r="D323" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E323" s="10"/>
+    </row>
+    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A324" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B324" s="2">
+        <v>6</v>
+      </c>
+      <c r="C324" s="2">
+        <v>39</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E324" s="10"/>
+    </row>
+    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A325" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B325" s="2">
+        <v>6</v>
+      </c>
+      <c r="C325" s="2">
+        <v>40</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E325" s="10"/>
+    </row>
+    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A326" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B326" s="4">
+        <v>6</v>
+      </c>
+      <c r="C326" s="4">
         <v>1</v>
-      </c>
-      <c r="D322" s="5"/>
-      <c r="E322" s="11"/>
-    </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A323" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B323" s="4">
-        <v>6</v>
-      </c>
-      <c r="C323" s="4">
-        <v>2</v>
-      </c>
-      <c r="D323" s="5"/>
-      <c r="E323" s="11"/>
-    </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A324" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B324" s="4">
-        <v>6</v>
-      </c>
-      <c r="C324" s="4">
-        <v>3</v>
-      </c>
-      <c r="D324" s="5"/>
-      <c r="E324" s="11"/>
-    </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A325" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B325" s="4">
-        <v>6</v>
-      </c>
-      <c r="C325" s="4">
-        <v>4</v>
-      </c>
-      <c r="D325" s="5"/>
-      <c r="E325" s="11"/>
-    </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A326" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B326" s="4">
-        <v>6</v>
-      </c>
-      <c r="C326" s="4">
-        <v>5</v>
       </c>
       <c r="D326" s="5"/>
       <c r="E326" s="11"/>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="4" t="s">
         <v>44</v>
       </c>
@@ -5105,12 +5402,12 @@
         <v>6</v>
       </c>
       <c r="C327" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D327" s="5"/>
       <c r="E327" s="11"/>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="4" t="s">
         <v>44</v>
       </c>
@@ -5118,12 +5415,12 @@
         <v>6</v>
       </c>
       <c r="C328" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D328" s="5"/>
       <c r="E328" s="11"/>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="4" t="s">
         <v>44</v>
       </c>
@@ -5131,12 +5428,12 @@
         <v>6</v>
       </c>
       <c r="C329" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D329" s="5"/>
       <c r="E329" s="11"/>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="4" t="s">
         <v>44</v>
       </c>
@@ -5144,12 +5441,12 @@
         <v>6</v>
       </c>
       <c r="C330" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D330" s="5"/>
       <c r="E330" s="11"/>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="4" t="s">
         <v>44</v>
       </c>
@@ -5157,12 +5454,12 @@
         <v>6</v>
       </c>
       <c r="C331" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D331" s="5"/>
       <c r="E331" s="11"/>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="4" t="s">
         <v>44</v>
       </c>
@@ -5170,12 +5467,12 @@
         <v>6</v>
       </c>
       <c r="C332" s="4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D332" s="5"/>
       <c r="E332" s="11"/>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="4" t="s">
         <v>44</v>
       </c>
@@ -5183,12 +5480,12 @@
         <v>6</v>
       </c>
       <c r="C333" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D333" s="5"/>
       <c r="E333" s="11"/>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="4" t="s">
         <v>44</v>
       </c>
@@ -5196,12 +5493,12 @@
         <v>6</v>
       </c>
       <c r="C334" s="4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D334" s="5"/>
       <c r="E334" s="11"/>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="4" t="s">
         <v>44</v>
       </c>
@@ -5209,12 +5506,12 @@
         <v>6</v>
       </c>
       <c r="C335" s="4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D335" s="5"/>
       <c r="E335" s="11"/>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="4" t="s">
         <v>44</v>
       </c>
@@ -5222,12 +5519,12 @@
         <v>6</v>
       </c>
       <c r="C336" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D336" s="5"/>
       <c r="E336" s="11"/>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="4" t="s">
         <v>44</v>
       </c>
@@ -5235,12 +5532,12 @@
         <v>6</v>
       </c>
       <c r="C337" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D337" s="5"/>
       <c r="E337" s="11"/>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="4" t="s">
         <v>44</v>
       </c>
@@ -5248,12 +5545,12 @@
         <v>6</v>
       </c>
       <c r="C338" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D338" s="5"/>
       <c r="E338" s="11"/>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="4" t="s">
         <v>44</v>
       </c>
@@ -5261,12 +5558,12 @@
         <v>6</v>
       </c>
       <c r="C339" s="4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D339" s="5"/>
       <c r="E339" s="11"/>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4" t="s">
         <v>44</v>
       </c>
@@ -5274,12 +5571,12 @@
         <v>6</v>
       </c>
       <c r="C340" s="4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D340" s="5"/>
       <c r="E340" s="11"/>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="4" t="s">
         <v>44</v>
       </c>
@@ -5287,12 +5584,12 @@
         <v>6</v>
       </c>
       <c r="C341" s="4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D341" s="5"/>
       <c r="E341" s="11"/>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4" t="s">
         <v>44</v>
       </c>
@@ -5300,12 +5597,12 @@
         <v>6</v>
       </c>
       <c r="C342" s="4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D342" s="5"/>
       <c r="E342" s="11"/>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="4" t="s">
         <v>44</v>
       </c>
@@ -5313,12 +5610,12 @@
         <v>6</v>
       </c>
       <c r="C343" s="4">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D343" s="5"/>
       <c r="E343" s="11"/>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="4" t="s">
         <v>44</v>
       </c>
@@ -5326,12 +5623,12 @@
         <v>6</v>
       </c>
       <c r="C344" s="4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D344" s="5"/>
       <c r="E344" s="11"/>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="4" t="s">
         <v>44</v>
       </c>
@@ -5339,12 +5636,12 @@
         <v>6</v>
       </c>
       <c r="C345" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D345" s="5"/>
       <c r="E345" s="11"/>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="4" t="s">
         <v>44</v>
       </c>
@@ -5352,12 +5649,12 @@
         <v>6</v>
       </c>
       <c r="C346" s="4">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D346" s="5"/>
       <c r="E346" s="11"/>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="4" t="s">
         <v>44</v>
       </c>
@@ -5365,12 +5662,12 @@
         <v>6</v>
       </c>
       <c r="C347" s="4">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D347" s="5"/>
       <c r="E347" s="11"/>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="4" t="s">
         <v>44</v>
       </c>
@@ -5378,12 +5675,12 @@
         <v>6</v>
       </c>
       <c r="C348" s="4">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D348" s="5"/>
       <c r="E348" s="11"/>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="4" t="s">
         <v>44</v>
       </c>
@@ -5391,12 +5688,12 @@
         <v>6</v>
       </c>
       <c r="C349" s="4">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D349" s="5"/>
       <c r="E349" s="11"/>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="4" t="s">
         <v>44</v>
       </c>
@@ -5404,12 +5701,12 @@
         <v>6</v>
       </c>
       <c r="C350" s="4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D350" s="5"/>
       <c r="E350" s="11"/>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="4" t="s">
         <v>44</v>
       </c>
@@ -5417,12 +5714,12 @@
         <v>6</v>
       </c>
       <c r="C351" s="4">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D351" s="5"/>
       <c r="E351" s="11"/>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="4" t="s">
         <v>44</v>
       </c>
@@ -5430,12 +5727,12 @@
         <v>6</v>
       </c>
       <c r="C352" s="4">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D352" s="5"/>
       <c r="E352" s="11"/>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="4" t="s">
         <v>44</v>
       </c>
@@ -5443,12 +5740,12 @@
         <v>6</v>
       </c>
       <c r="C353" s="4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D353" s="5"/>
       <c r="E353" s="11"/>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="4" t="s">
         <v>44</v>
       </c>
@@ -5456,12 +5753,12 @@
         <v>6</v>
       </c>
       <c r="C354" s="4">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D354" s="5"/>
       <c r="E354" s="11"/>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="4" t="s">
         <v>44</v>
       </c>
@@ -5469,12 +5766,12 @@
         <v>6</v>
       </c>
       <c r="C355" s="4">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D355" s="5"/>
       <c r="E355" s="11"/>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="4" t="s">
         <v>44</v>
       </c>
@@ -5482,12 +5779,12 @@
         <v>6</v>
       </c>
       <c r="C356" s="4">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D356" s="5"/>
       <c r="E356" s="11"/>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="4" t="s">
         <v>44</v>
       </c>
@@ -5495,12 +5792,12 @@
         <v>6</v>
       </c>
       <c r="C357" s="4">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D357" s="5"/>
       <c r="E357" s="11"/>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
         <v>44</v>
       </c>
@@ -5508,12 +5805,12 @@
         <v>6</v>
       </c>
       <c r="C358" s="4">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D358" s="5"/>
       <c r="E358" s="11"/>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
         <v>44</v>
       </c>
@@ -5521,12 +5818,12 @@
         <v>6</v>
       </c>
       <c r="C359" s="4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D359" s="5"/>
       <c r="E359" s="11"/>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
         <v>44</v>
       </c>
@@ -5534,12 +5831,12 @@
         <v>6</v>
       </c>
       <c r="C360" s="4">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D360" s="5"/>
       <c r="E360" s="11"/>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
         <v>44</v>
       </c>
@@ -5547,12 +5844,12 @@
         <v>6</v>
       </c>
       <c r="C361" s="4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D361" s="5"/>
       <c r="E361" s="11"/>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
         <v>44</v>
       </c>
@@ -5560,12 +5857,12 @@
         <v>6</v>
       </c>
       <c r="C362" s="4">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D362" s="5"/>
       <c r="E362" s="11"/>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
         <v>44</v>
       </c>
@@ -5573,12 +5870,12 @@
         <v>6</v>
       </c>
       <c r="C363" s="4">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D363" s="5"/>
       <c r="E363" s="11"/>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
         <v>44</v>
       </c>
@@ -5586,12 +5883,12 @@
         <v>6</v>
       </c>
       <c r="C364" s="4">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D364" s="5"/>
       <c r="E364" s="11"/>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
         <v>44</v>
       </c>
@@ -5599,12 +5896,12 @@
         <v>6</v>
       </c>
       <c r="C365" s="4">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D365" s="5"/>
       <c r="E365" s="11"/>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
         <v>44</v>
       </c>
@@ -5612,12 +5909,12 @@
         <v>6</v>
       </c>
       <c r="C366" s="4">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D366" s="5"/>
       <c r="E366" s="11"/>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
         <v>44</v>
       </c>
@@ -5625,12 +5922,12 @@
         <v>6</v>
       </c>
       <c r="C367" s="4">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D367" s="5"/>
       <c r="E367" s="11"/>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
         <v>44</v>
       </c>
@@ -5638,12 +5935,12 @@
         <v>6</v>
       </c>
       <c r="C368" s="4">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D368" s="5"/>
       <c r="E368" s="11"/>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
         <v>44</v>
       </c>
@@ -5651,12 +5948,12 @@
         <v>6</v>
       </c>
       <c r="C369" s="4">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D369" s="5"/>
       <c r="E369" s="11"/>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
         <v>44</v>
       </c>
@@ -5664,12 +5961,12 @@
         <v>6</v>
       </c>
       <c r="C370" s="4">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D370" s="5"/>
       <c r="E370" s="11"/>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
         <v>44</v>
       </c>
@@ -5677,12 +5974,12 @@
         <v>6</v>
       </c>
       <c r="C371" s="4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D371" s="5"/>
       <c r="E371" s="11"/>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
         <v>44</v>
       </c>
@@ -5690,12 +5987,12 @@
         <v>6</v>
       </c>
       <c r="C372" s="4">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D372" s="5"/>
       <c r="E372" s="11"/>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
         <v>44</v>
       </c>
@@ -5703,12 +6000,12 @@
         <v>6</v>
       </c>
       <c r="C373" s="4">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D373" s="5"/>
       <c r="E373" s="11"/>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
         <v>44</v>
       </c>
@@ -5716,12 +6013,12 @@
         <v>6</v>
       </c>
       <c r="C374" s="4">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D374" s="5"/>
       <c r="E374" s="11"/>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
         <v>44</v>
       </c>
@@ -5729,12 +6026,12 @@
         <v>6</v>
       </c>
       <c r="C375" s="4">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D375" s="5"/>
       <c r="E375" s="11"/>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
         <v>44</v>
       </c>
@@ -5742,12 +6039,12 @@
         <v>6</v>
       </c>
       <c r="C376" s="4">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D376" s="5"/>
       <c r="E376" s="11"/>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>44</v>
       </c>
@@ -5760,7 +6057,7 @@
       <c r="D377" s="5"/>
       <c r="E377" s="11"/>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>44</v>
       </c>
@@ -5773,7 +6070,7 @@
       <c r="D378" s="5"/>
       <c r="E378" s="11"/>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>44</v>
       </c>
@@ -5786,7 +6083,7 @@
       <c r="D379" s="5"/>
       <c r="E379" s="11"/>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>44</v>
       </c>
@@ -5799,7 +6096,7 @@
       <c r="D380" s="5"/>
       <c r="E380" s="11"/>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>44</v>
       </c>
@@ -5812,7 +6109,7 @@
       <c r="D381" s="5"/>
       <c r="E381" s="11"/>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>44</v>
       </c>
@@ -5825,7 +6122,7 @@
       <c r="D382" s="5"/>
       <c r="E382" s="11"/>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
         <v>44</v>
       </c>
@@ -5838,7 +6135,7 @@
       <c r="D383" s="5"/>
       <c r="E383" s="11"/>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
         <v>44</v>
       </c>
@@ -5851,7 +6148,7 @@
       <c r="D384" s="5"/>
       <c r="E384" s="11"/>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
         <v>44</v>
       </c>
@@ -5864,7 +6161,7 @@
       <c r="D385" s="5"/>
       <c r="E385" s="11"/>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
         <v>44</v>
       </c>
@@ -5877,7 +6174,7 @@
       <c r="D386" s="5"/>
       <c r="E386" s="11"/>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
         <v>44</v>
       </c>
@@ -5890,7 +6187,7 @@
       <c r="D387" s="5"/>
       <c r="E387" s="11"/>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
         <v>44</v>
       </c>
@@ -5903,7 +6200,7 @@
       <c r="D388" s="5"/>
       <c r="E388" s="11"/>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
         <v>44</v>
       </c>
@@ -5916,7 +6213,7 @@
       <c r="D389" s="5"/>
       <c r="E389" s="11"/>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
         <v>44</v>
       </c>
@@ -5929,7 +6226,7 @@
       <c r="D390" s="5"/>
       <c r="E390" s="11"/>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
         <v>44</v>
       </c>
@@ -5942,7 +6239,7 @@
       <c r="D391" s="5"/>
       <c r="E391" s="11"/>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
         <v>44</v>
       </c>
@@ -5955,7 +6252,7 @@
       <c r="D392" s="5"/>
       <c r="E392" s="11"/>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
         <v>44</v>
       </c>
@@ -5968,7 +6265,7 @@
       <c r="D393" s="5"/>
       <c r="E393" s="11"/>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
         <v>44</v>
       </c>
@@ -5981,7 +6278,7 @@
       <c r="D394" s="5"/>
       <c r="E394" s="11"/>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
         <v>44</v>
       </c>
@@ -5994,7 +6291,7 @@
       <c r="D395" s="5"/>
       <c r="E395" s="11"/>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
         <v>44</v>
       </c>
@@ -6007,7 +6304,7 @@
       <c r="D396" s="5"/>
       <c r="E396" s="11"/>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>44</v>
       </c>
@@ -6020,7 +6317,7 @@
       <c r="D397" s="5"/>
       <c r="E397" s="11"/>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>44</v>
       </c>
@@ -6033,7 +6330,7 @@
       <c r="D398" s="5"/>
       <c r="E398" s="11"/>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
         <v>44</v>
       </c>
@@ -6046,7 +6343,7 @@
       <c r="D399" s="5"/>
       <c r="E399" s="11"/>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
         <v>44</v>
       </c>
@@ -6059,7 +6356,7 @@
       <c r="D400" s="5"/>
       <c r="E400" s="11"/>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>44</v>
       </c>
@@ -6072,7 +6369,7 @@
       <c r="D401" s="5"/>
       <c r="E401" s="11"/>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>44</v>
       </c>
@@ -6085,7 +6382,7 @@
       <c r="D402" s="5"/>
       <c r="E402" s="11"/>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>44</v>
       </c>
@@ -6098,7 +6395,7 @@
       <c r="D403" s="5"/>
       <c r="E403" s="11"/>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>44</v>
       </c>
@@ -6111,7 +6408,7 @@
       <c r="D404" s="5"/>
       <c r="E404" s="11"/>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
         <v>44</v>
       </c>
@@ -6124,7 +6421,7 @@
       <c r="D405" s="5"/>
       <c r="E405" s="11"/>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>44</v>
       </c>
@@ -6137,7 +6434,7 @@
       <c r="D406" s="5"/>
       <c r="E406" s="11"/>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>44</v>
       </c>
@@ -6150,7 +6447,7 @@
       <c r="D407" s="5"/>
       <c r="E407" s="11"/>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>44</v>
       </c>
@@ -6163,7 +6460,7 @@
       <c r="D408" s="5"/>
       <c r="E408" s="11"/>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>44</v>
       </c>
@@ -6176,7 +6473,7 @@
       <c r="D409" s="5"/>
       <c r="E409" s="11"/>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>44</v>
       </c>
@@ -6189,7 +6486,7 @@
       <c r="D410" s="5"/>
       <c r="E410" s="11"/>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>44</v>
       </c>
@@ -6202,7 +6499,7 @@
       <c r="D411" s="5"/>
       <c r="E411" s="11"/>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>44</v>
       </c>
@@ -6215,7 +6512,7 @@
       <c r="D412" s="5"/>
       <c r="E412" s="11"/>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
         <v>44</v>
       </c>
@@ -6228,7 +6525,7 @@
       <c r="D413" s="5"/>
       <c r="E413" s="11"/>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
         <v>44</v>
       </c>
@@ -6241,7 +6538,7 @@
       <c r="D414" s="5"/>
       <c r="E414" s="11"/>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
         <v>44</v>
       </c>
@@ -6254,7 +6551,7 @@
       <c r="D415" s="5"/>
       <c r="E415" s="11"/>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
         <v>44</v>
       </c>
@@ -6267,7 +6564,7 @@
       <c r="D416" s="5"/>
       <c r="E416" s="11"/>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
         <v>44</v>
       </c>
@@ -6280,7 +6577,7 @@
       <c r="D417" s="5"/>
       <c r="E417" s="11"/>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
         <v>44</v>
       </c>
@@ -6293,7 +6590,7 @@
       <c r="D418" s="5"/>
       <c r="E418" s="11"/>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
         <v>44</v>
       </c>
@@ -6306,7 +6603,7 @@
       <c r="D419" s="5"/>
       <c r="E419" s="11"/>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
         <v>44</v>
       </c>
@@ -6319,7 +6616,7 @@
       <c r="D420" s="5"/>
       <c r="E420" s="11"/>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
         <v>44</v>
       </c>
@@ -6332,7 +6629,7 @@
       <c r="D421" s="5"/>
       <c r="E421" s="11"/>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
         <v>44</v>
       </c>
@@ -6345,7 +6642,7 @@
       <c r="D422" s="5"/>
       <c r="E422" s="11"/>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
         <v>44</v>
       </c>
@@ -6358,7 +6655,7 @@
       <c r="D423" s="5"/>
       <c r="E423" s="11"/>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
         <v>44</v>
       </c>
@@ -6371,7 +6668,7 @@
       <c r="D424" s="5"/>
       <c r="E424" s="11"/>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
         <v>44</v>
       </c>
@@ -6384,7 +6681,7 @@
       <c r="D425" s="5"/>
       <c r="E425" s="11"/>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
         <v>44</v>
       </c>
@@ -6397,7 +6694,7 @@
       <c r="D426" s="5"/>
       <c r="E426" s="11"/>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
         <v>44</v>
       </c>
@@ -6410,7 +6707,7 @@
       <c r="D427" s="5"/>
       <c r="E427" s="11"/>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
         <v>44</v>
       </c>
@@ -6423,7 +6720,7 @@
       <c r="D428" s="5"/>
       <c r="E428" s="11"/>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
         <v>44</v>
       </c>
@@ -6436,7 +6733,7 @@
       <c r="D429" s="5"/>
       <c r="E429" s="11"/>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
         <v>44</v>
       </c>
@@ -6449,7 +6746,7 @@
       <c r="D430" s="5"/>
       <c r="E430" s="11"/>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
         <v>44</v>
       </c>
@@ -6462,7 +6759,7 @@
       <c r="D431" s="5"/>
       <c r="E431" s="11"/>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
         <v>44</v>
       </c>
@@ -6475,7 +6772,7 @@
       <c r="D432" s="5"/>
       <c r="E432" s="11"/>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
         <v>44</v>
       </c>
@@ -6488,7 +6785,7 @@
       <c r="D433" s="5"/>
       <c r="E433" s="11"/>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
         <v>44</v>
       </c>
@@ -6501,7 +6798,7 @@
       <c r="D434" s="5"/>
       <c r="E434" s="11"/>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
         <v>44</v>
       </c>
@@ -6514,7 +6811,7 @@
       <c r="D435" s="5"/>
       <c r="E435" s="11"/>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
         <v>44</v>
       </c>
@@ -6527,7 +6824,7 @@
       <c r="D436" s="5"/>
       <c r="E436" s="11"/>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
         <v>44</v>
       </c>
@@ -6540,7 +6837,7 @@
       <c r="D437" s="5"/>
       <c r="E437" s="11"/>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
         <v>44</v>
       </c>
@@ -6553,7 +6850,7 @@
       <c r="D438" s="5"/>
       <c r="E438" s="11"/>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
         <v>44</v>
       </c>
@@ -6566,7 +6863,7 @@
       <c r="D439" s="5"/>
       <c r="E439" s="11"/>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
         <v>44</v>
       </c>
@@ -6579,7 +6876,7 @@
       <c r="D440" s="5"/>
       <c r="E440" s="11"/>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
         <v>44</v>
       </c>
@@ -6592,7 +6889,7 @@
       <c r="D441" s="5"/>
       <c r="E441" s="11"/>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
         <v>44</v>
       </c>
@@ -6605,7 +6902,7 @@
       <c r="D442" s="5"/>
       <c r="E442" s="11"/>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
         <v>44</v>
       </c>
@@ -6618,7 +6915,7 @@
       <c r="D443" s="5"/>
       <c r="E443" s="11"/>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
         <v>44</v>
       </c>
@@ -6631,7 +6928,7 @@
       <c r="D444" s="5"/>
       <c r="E444" s="11"/>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
         <v>44</v>
       </c>
@@ -6644,7 +6941,7 @@
       <c r="D445" s="5"/>
       <c r="E445" s="11"/>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
         <v>44</v>
       </c>
@@ -6657,7 +6954,7 @@
       <c r="D446" s="5"/>
       <c r="E446" s="11"/>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
         <v>44</v>
       </c>
@@ -6670,7 +6967,7 @@
       <c r="D447" s="5"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
         <v>44</v>
       </c>
@@ -6683,7 +6980,7 @@
       <c r="D448" s="5"/>
       <c r="E448" s="11"/>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
         <v>44</v>
       </c>
@@ -6696,7 +6993,7 @@
       <c r="D449" s="5"/>
       <c r="E449" s="11"/>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
         <v>44</v>
       </c>
@@ -6709,7 +7006,7 @@
       <c r="D450" s="5"/>
       <c r="E450" s="11"/>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
         <v>44</v>
       </c>
@@ -6722,7 +7019,7 @@
       <c r="D451" s="5"/>
       <c r="E451" s="11"/>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
         <v>44</v>
       </c>
@@ -6735,7 +7032,7 @@
       <c r="D452" s="5"/>
       <c r="E452" s="11"/>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
         <v>44</v>
       </c>
@@ -6748,7 +7045,7 @@
       <c r="D453" s="5"/>
       <c r="E453" s="11"/>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
         <v>44</v>
       </c>
@@ -6761,7 +7058,7 @@
       <c r="D454" s="5"/>
       <c r="E454" s="11"/>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
         <v>44</v>
       </c>
@@ -6774,7 +7071,7 @@
       <c r="D455" s="5"/>
       <c r="E455" s="11"/>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
         <v>44</v>
       </c>
@@ -6787,7 +7084,7 @@
       <c r="D456" s="5"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
         <v>44</v>
       </c>
@@ -6800,7 +7097,7 @@
       <c r="D457" s="5"/>
       <c r="E457" s="11"/>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
         <v>44</v>
       </c>
@@ -6813,7 +7110,7 @@
       <c r="D458" s="5"/>
       <c r="E458" s="11"/>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
         <v>44</v>
       </c>
@@ -6826,7 +7123,7 @@
       <c r="D459" s="5"/>
       <c r="E459" s="11"/>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
         <v>44</v>
       </c>
@@ -6839,7 +7136,7 @@
       <c r="D460" s="5"/>
       <c r="E460" s="11"/>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
         <v>44</v>
       </c>
@@ -6852,7 +7149,7 @@
       <c r="D461" s="5"/>
       <c r="E461" s="11"/>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
         <v>44</v>
       </c>
@@ -6865,7 +7162,7 @@
       <c r="D462" s="5"/>
       <c r="E462" s="11"/>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
         <v>44</v>
       </c>
@@ -6878,7 +7175,7 @@
       <c r="D463" s="5"/>
       <c r="E463" s="11"/>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
         <v>44</v>
       </c>
@@ -6891,7 +7188,7 @@
       <c r="D464" s="5"/>
       <c r="E464" s="11"/>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
         <v>44</v>
       </c>
@@ -6904,7 +7201,7 @@
       <c r="D465" s="5"/>
       <c r="E465" s="11"/>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
         <v>44</v>
       </c>
@@ -6917,7 +7214,7 @@
       <c r="D466" s="5"/>
       <c r="E466" s="11"/>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
         <v>44</v>
       </c>
@@ -6930,7 +7227,7 @@
       <c r="D467" s="5"/>
       <c r="E467" s="11"/>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
         <v>44</v>
       </c>
@@ -6943,7 +7240,7 @@
       <c r="D468" s="5"/>
       <c r="E468" s="11"/>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
         <v>44</v>
       </c>
@@ -6956,7 +7253,7 @@
       <c r="D469" s="5"/>
       <c r="E469" s="11"/>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
         <v>44</v>
       </c>
@@ -6969,7 +7266,7 @@
       <c r="D470" s="5"/>
       <c r="E470" s="11"/>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
         <v>44</v>
       </c>
@@ -6982,7 +7279,7 @@
       <c r="D471" s="5"/>
       <c r="E471" s="11"/>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
         <v>44</v>
       </c>
@@ -6995,7 +7292,7 @@
       <c r="D472" s="5"/>
       <c r="E472" s="11"/>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
         <v>44</v>
       </c>
@@ -7008,7 +7305,7 @@
       <c r="D473" s="5"/>
       <c r="E473" s="11"/>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
         <v>44</v>
       </c>
@@ -7021,7 +7318,7 @@
       <c r="D474" s="5"/>
       <c r="E474" s="11"/>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
         <v>44</v>
       </c>
@@ -7034,7 +7331,7 @@
       <c r="D475" s="5"/>
       <c r="E475" s="11"/>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
         <v>44</v>
       </c>
@@ -7047,7 +7344,7 @@
       <c r="D476" s="5"/>
       <c r="E476" s="11"/>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
         <v>44</v>
       </c>
@@ -7060,7 +7357,7 @@
       <c r="D477" s="5"/>
       <c r="E477" s="11"/>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
         <v>44</v>
       </c>
@@ -7073,7 +7370,7 @@
       <c r="D478" s="5"/>
       <c r="E478" s="11"/>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
         <v>44</v>
       </c>
@@ -7086,7 +7383,7 @@
       <c r="D479" s="5"/>
       <c r="E479" s="11"/>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
         <v>44</v>
       </c>
@@ -7099,7 +7396,7 @@
       <c r="D480" s="5"/>
       <c r="E480" s="11"/>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
         <v>44</v>
       </c>
@@ -7112,7 +7409,7 @@
       <c r="D481" s="5"/>
       <c r="E481" s="11"/>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
         <v>44</v>
       </c>
@@ -7125,7 +7422,7 @@
       <c r="D482" s="5"/>
       <c r="E482" s="11"/>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
         <v>44</v>
       </c>
@@ -7138,7 +7435,7 @@
       <c r="D483" s="5"/>
       <c r="E483" s="11"/>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
         <v>44</v>
       </c>
@@ -7151,7 +7448,7 @@
       <c r="D484" s="5"/>
       <c r="E484" s="11"/>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
         <v>44</v>
       </c>
@@ -7164,7 +7461,7 @@
       <c r="D485" s="5"/>
       <c r="E485" s="11"/>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
         <v>44</v>
       </c>
@@ -7177,7 +7474,7 @@
       <c r="D486" s="5"/>
       <c r="E486" s="11"/>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="4" t="s">
         <v>44</v>
       </c>
@@ -7190,7 +7487,7 @@
       <c r="D487" s="5"/>
       <c r="E487" s="11"/>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="4" t="s">
         <v>44</v>
       </c>
@@ -7203,7 +7500,7 @@
       <c r="D488" s="5"/>
       <c r="E488" s="11"/>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="4" t="s">
         <v>44</v>
       </c>
@@ -7216,7 +7513,7 @@
       <c r="D489" s="5"/>
       <c r="E489" s="11"/>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="4" t="s">
         <v>44</v>
       </c>
@@ -7229,7 +7526,7 @@
       <c r="D490" s="5"/>
       <c r="E490" s="11"/>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
         <v>44</v>
       </c>
@@ -7242,7 +7539,7 @@
       <c r="D491" s="5"/>
       <c r="E491" s="11"/>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
         <v>44</v>
       </c>
@@ -7255,7 +7552,7 @@
       <c r="D492" s="5"/>
       <c r="E492" s="11"/>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
         <v>44</v>
       </c>
@@ -7268,7 +7565,7 @@
       <c r="D493" s="5"/>
       <c r="E493" s="11"/>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="4" t="s">
         <v>44</v>
       </c>
@@ -7281,7 +7578,7 @@
       <c r="D494" s="5"/>
       <c r="E494" s="11"/>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="4" t="s">
         <v>44</v>
       </c>
@@ -7294,7 +7591,7 @@
       <c r="D495" s="5"/>
       <c r="E495" s="11"/>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="4" t="s">
         <v>44</v>
       </c>
@@ -7307,7 +7604,7 @@
       <c r="D496" s="5"/>
       <c r="E496" s="11"/>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="4" t="s">
         <v>44</v>
       </c>
@@ -7320,7 +7617,7 @@
       <c r="D497" s="5"/>
       <c r="E497" s="11"/>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="4" t="s">
         <v>44</v>
       </c>
@@ -7333,7 +7630,7 @@
       <c r="D498" s="5"/>
       <c r="E498" s="11"/>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="4" t="s">
         <v>44</v>
       </c>
@@ -7346,7 +7643,7 @@
       <c r="D499" s="5"/>
       <c r="E499" s="11"/>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="4" t="s">
         <v>44</v>
       </c>
@@ -7359,7 +7656,7 @@
       <c r="D500" s="5"/>
       <c r="E500" s="11"/>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="4" t="s">
         <v>44</v>
       </c>
@@ -7372,7 +7669,7 @@
       <c r="D501" s="5"/>
       <c r="E501" s="11"/>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="4" t="s">
         <v>44</v>
       </c>
@@ -7385,7 +7682,7 @@
       <c r="D502" s="5"/>
       <c r="E502" s="11"/>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="4" t="s">
         <v>44</v>
       </c>
@@ -7398,7 +7695,7 @@
       <c r="D503" s="5"/>
       <c r="E503" s="11"/>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="4" t="s">
         <v>44</v>
       </c>
@@ -7411,7 +7708,7 @@
       <c r="D504" s="5"/>
       <c r="E504" s="11"/>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="4" t="s">
         <v>44</v>
       </c>
@@ -7424,7 +7721,7 @@
       <c r="D505" s="5"/>
       <c r="E505" s="11"/>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="4" t="s">
         <v>44</v>
       </c>
@@ -7437,7 +7734,7 @@
       <c r="D506" s="5"/>
       <c r="E506" s="11"/>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="4" t="s">
         <v>44</v>
       </c>
@@ -7450,7 +7747,7 @@
       <c r="D507" s="5"/>
       <c r="E507" s="11"/>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
         <v>44</v>
       </c>
@@ -7463,7 +7760,7 @@
       <c r="D508" s="5"/>
       <c r="E508" s="11"/>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="s">
         <v>44</v>
       </c>
@@ -7476,7 +7773,7 @@
       <c r="D509" s="5"/>
       <c r="E509" s="11"/>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="4" t="s">
         <v>44</v>
       </c>
@@ -7489,7 +7786,7 @@
       <c r="D510" s="5"/>
       <c r="E510" s="11"/>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="4" t="s">
         <v>44</v>
       </c>
@@ -7502,7 +7799,7 @@
       <c r="D511" s="5"/>
       <c r="E511" s="11"/>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="4" t="s">
         <v>44</v>
       </c>
@@ -7515,7 +7812,7 @@
       <c r="D512" s="5"/>
       <c r="E512" s="11"/>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="4" t="s">
         <v>44</v>
       </c>
@@ -7528,7 +7825,7 @@
       <c r="D513" s="5"/>
       <c r="E513" s="11"/>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="4" t="s">
         <v>44</v>
       </c>
@@ -7541,7 +7838,7 @@
       <c r="D514" s="5"/>
       <c r="E514" s="11"/>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="4" t="s">
         <v>44</v>
       </c>
@@ -7554,7 +7851,7 @@
       <c r="D515" s="5"/>
       <c r="E515" s="11"/>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="4" t="s">
         <v>44</v>
       </c>
@@ -7567,7 +7864,7 @@
       <c r="D516" s="5"/>
       <c r="E516" s="11"/>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="4" t="s">
         <v>44</v>
       </c>
@@ -7580,7 +7877,7 @@
       <c r="D517" s="5"/>
       <c r="E517" s="11"/>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="4" t="s">
         <v>44</v>
       </c>
@@ -7593,7 +7890,7 @@
       <c r="D518" s="5"/>
       <c r="E518" s="11"/>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="4" t="s">
         <v>44</v>
       </c>
@@ -7606,7 +7903,7 @@
       <c r="D519" s="5"/>
       <c r="E519" s="11"/>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="4" t="s">
         <v>44</v>
       </c>
@@ -7619,7 +7916,7 @@
       <c r="D520" s="5"/>
       <c r="E520" s="11"/>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="4" t="s">
         <v>44</v>
       </c>
@@ -7632,7 +7929,7 @@
       <c r="D521" s="5"/>
       <c r="E521" s="11"/>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="4" t="s">
         <v>44</v>
       </c>
@@ -7645,7 +7942,7 @@
       <c r="D522" s="5"/>
       <c r="E522" s="11"/>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="4" t="s">
         <v>44</v>
       </c>
@@ -7658,7 +7955,7 @@
       <c r="D523" s="5"/>
       <c r="E523" s="11"/>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="4" t="s">
         <v>44</v>
       </c>
@@ -7671,7 +7968,7 @@
       <c r="D524" s="5"/>
       <c r="E524" s="11"/>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="4" t="s">
         <v>44</v>
       </c>
@@ -7684,7 +7981,7 @@
       <c r="D525" s="5"/>
       <c r="E525" s="11"/>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="4" t="s">
         <v>44</v>
       </c>
@@ -7697,7 +7994,7 @@
       <c r="D526" s="5"/>
       <c r="E526" s="11"/>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="4" t="s">
         <v>44</v>
       </c>
@@ -7710,7 +8007,7 @@
       <c r="D527" s="5"/>
       <c r="E527" s="11"/>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="4" t="s">
         <v>44</v>
       </c>
@@ -7723,7 +8020,7 @@
       <c r="D528" s="5"/>
       <c r="E528" s="11"/>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="4" t="s">
         <v>44</v>
       </c>
@@ -7736,7 +8033,7 @@
       <c r="D529" s="5"/>
       <c r="E529" s="11"/>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="4" t="s">
         <v>44</v>
       </c>
@@ -7749,7 +8046,7 @@
       <c r="D530" s="5"/>
       <c r="E530" s="11"/>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="4" t="s">
         <v>44</v>
       </c>
@@ -7762,7 +8059,7 @@
       <c r="D531" s="5"/>
       <c r="E531" s="11"/>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="4" t="s">
         <v>44</v>
       </c>
@@ -7775,7 +8072,7 @@
       <c r="D532" s="5"/>
       <c r="E532" s="11"/>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="4" t="s">
         <v>44</v>
       </c>
@@ -7788,7 +8085,7 @@
       <c r="D533" s="5"/>
       <c r="E533" s="11"/>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="4" t="s">
         <v>44</v>
       </c>
@@ -7801,7 +8098,7 @@
       <c r="D534" s="5"/>
       <c r="E534" s="11"/>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="4" t="s">
         <v>44</v>
       </c>
@@ -7814,7 +8111,7 @@
       <c r="D535" s="5"/>
       <c r="E535" s="11"/>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="4" t="s">
         <v>44</v>
       </c>
@@ -7827,7 +8124,7 @@
       <c r="D536" s="5"/>
       <c r="E536" s="11"/>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="4" t="s">
         <v>44</v>
       </c>
@@ -7840,7 +8137,7 @@
       <c r="D537" s="5"/>
       <c r="E537" s="11"/>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="4" t="s">
         <v>44</v>
       </c>
@@ -7853,7 +8150,7 @@
       <c r="D538" s="5"/>
       <c r="E538" s="11"/>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="4" t="s">
         <v>44</v>
       </c>
@@ -7866,7 +8163,7 @@
       <c r="D539" s="5"/>
       <c r="E539" s="11"/>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="4" t="s">
         <v>44</v>
       </c>
@@ -7879,7 +8176,7 @@
       <c r="D540" s="5"/>
       <c r="E540" s="11"/>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="4" t="s">
         <v>44</v>
       </c>
@@ -7892,59 +8189,59 @@
       <c r="D541" s="5"/>
       <c r="E541" s="11"/>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B542" s="4">
         <v>6</v>
       </c>
       <c r="C542" s="4">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="D542" s="5"/>
       <c r="E542" s="11"/>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B543" s="4">
         <v>6</v>
       </c>
       <c r="C543" s="4">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="D543" s="5"/>
       <c r="E543" s="11"/>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B544" s="4">
         <v>6</v>
       </c>
       <c r="C544" s="4">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="D544" s="5"/>
       <c r="E544" s="11"/>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B545" s="4">
         <v>6</v>
       </c>
       <c r="C545" s="4">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="D545" s="5"/>
       <c r="E545" s="11"/>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="4" t="s">
         <v>45</v>
       </c>
@@ -7952,12 +8249,12 @@
         <v>6</v>
       </c>
       <c r="C546" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D546" s="5"/>
       <c r="E546" s="11"/>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="4" t="s">
         <v>45</v>
       </c>
@@ -7965,12 +8262,12 @@
         <v>6</v>
       </c>
       <c r="C547" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D547" s="5"/>
       <c r="E547" s="11"/>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="4" t="s">
         <v>45</v>
       </c>
@@ -7978,12 +8275,12 @@
         <v>6</v>
       </c>
       <c r="C548" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D548" s="5"/>
       <c r="E548" s="11"/>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="4" t="s">
         <v>45</v>
       </c>
@@ -7991,12 +8288,12 @@
         <v>6</v>
       </c>
       <c r="C549" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D549" s="5"/>
       <c r="E549" s="11"/>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="4" t="s">
         <v>45</v>
       </c>
@@ -8004,12 +8301,12 @@
         <v>6</v>
       </c>
       <c r="C550" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D550" s="5"/>
       <c r="E550" s="11"/>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="4" t="s">
         <v>45</v>
       </c>
@@ -8017,12 +8314,12 @@
         <v>6</v>
       </c>
       <c r="C551" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D551" s="5"/>
       <c r="E551" s="11"/>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
         <v>45</v>
       </c>
@@ -8030,12 +8327,12 @@
         <v>6</v>
       </c>
       <c r="C552" s="4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D552" s="5"/>
       <c r="E552" s="11"/>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="4" t="s">
         <v>45</v>
       </c>
@@ -8043,12 +8340,12 @@
         <v>6</v>
       </c>
       <c r="C553" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D553" s="5"/>
       <c r="E553" s="11"/>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="4" t="s">
         <v>45</v>
       </c>
@@ -8056,12 +8353,12 @@
         <v>6</v>
       </c>
       <c r="C554" s="4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D554" s="5"/>
       <c r="E554" s="11"/>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="4" t="s">
         <v>45</v>
       </c>
@@ -8069,12 +8366,12 @@
         <v>6</v>
       </c>
       <c r="C555" s="4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D555" s="5"/>
       <c r="E555" s="11"/>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="4" t="s">
         <v>45</v>
       </c>
@@ -8082,12 +8379,12 @@
         <v>6</v>
       </c>
       <c r="C556" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D556" s="5"/>
       <c r="E556" s="11"/>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="4" t="s">
         <v>45</v>
       </c>
@@ -8095,12 +8392,12 @@
         <v>6</v>
       </c>
       <c r="C557" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D557" s="5"/>
       <c r="E557" s="11"/>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="4" t="s">
         <v>45</v>
       </c>
@@ -8108,12 +8405,12 @@
         <v>6</v>
       </c>
       <c r="C558" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D558" s="5"/>
       <c r="E558" s="11"/>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="4" t="s">
         <v>45</v>
       </c>
@@ -8121,12 +8418,12 @@
         <v>6</v>
       </c>
       <c r="C559" s="4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D559" s="5"/>
       <c r="E559" s="11"/>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="4" t="s">
         <v>45</v>
       </c>
@@ -8134,12 +8431,12 @@
         <v>6</v>
       </c>
       <c r="C560" s="4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D560" s="5"/>
       <c r="E560" s="11"/>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="4" t="s">
         <v>45</v>
       </c>
@@ -8147,12 +8444,12 @@
         <v>6</v>
       </c>
       <c r="C561" s="4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D561" s="5"/>
       <c r="E561" s="11"/>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="4" t="s">
         <v>45</v>
       </c>
@@ -8160,12 +8457,12 @@
         <v>6</v>
       </c>
       <c r="C562" s="4">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D562" s="5"/>
       <c r="E562" s="11"/>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="4" t="s">
         <v>45</v>
       </c>
@@ -8173,12 +8470,12 @@
         <v>6</v>
       </c>
       <c r="C563" s="4">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D563" s="5"/>
       <c r="E563" s="11"/>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="4" t="s">
         <v>45</v>
       </c>
@@ -8186,12 +8483,12 @@
         <v>6</v>
       </c>
       <c r="C564" s="4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D564" s="5"/>
       <c r="E564" s="11"/>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="4" t="s">
         <v>45</v>
       </c>
@@ -8199,12 +8496,12 @@
         <v>6</v>
       </c>
       <c r="C565" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D565" s="5"/>
       <c r="E565" s="11"/>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="4" t="s">
         <v>45</v>
       </c>
@@ -8212,12 +8509,12 @@
         <v>6</v>
       </c>
       <c r="C566" s="4">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D566" s="5"/>
       <c r="E566" s="11"/>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="4" t="s">
         <v>45</v>
       </c>
@@ -8225,12 +8522,12 @@
         <v>6</v>
       </c>
       <c r="C567" s="4">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D567" s="5"/>
       <c r="E567" s="11"/>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="4" t="s">
         <v>45</v>
       </c>
@@ -8238,12 +8535,12 @@
         <v>6</v>
       </c>
       <c r="C568" s="4">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D568" s="5"/>
       <c r="E568" s="11"/>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="4" t="s">
         <v>45</v>
       </c>
@@ -8251,12 +8548,12 @@
         <v>6</v>
       </c>
       <c r="C569" s="4">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D569" s="5"/>
       <c r="E569" s="11"/>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="4" t="s">
         <v>45</v>
       </c>
@@ -8264,12 +8561,12 @@
         <v>6</v>
       </c>
       <c r="C570" s="4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D570" s="5"/>
       <c r="E570" s="11"/>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="4" t="s">
         <v>45</v>
       </c>
@@ -8277,12 +8574,12 @@
         <v>6</v>
       </c>
       <c r="C571" s="4">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D571" s="5"/>
       <c r="E571" s="11"/>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="4" t="s">
         <v>45</v>
       </c>
@@ -8295,7 +8592,7 @@
       <c r="D572" s="5"/>
       <c r="E572" s="11"/>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="4" t="s">
         <v>45</v>
       </c>
@@ -8308,7 +8605,7 @@
       <c r="D573" s="5"/>
       <c r="E573" s="11"/>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="4" t="s">
         <v>45</v>
       </c>
@@ -8321,7 +8618,7 @@
       <c r="D574" s="5"/>
       <c r="E574" s="11"/>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="4" t="s">
         <v>45</v>
       </c>
@@ -8334,7 +8631,7 @@
       <c r="D575" s="5"/>
       <c r="E575" s="11"/>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="4" t="s">
         <v>45</v>
       </c>
@@ -8347,7 +8644,7 @@
       <c r="D576" s="5"/>
       <c r="E576" s="11"/>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="4" t="s">
         <v>45</v>
       </c>
@@ -8360,7 +8657,7 @@
       <c r="D577" s="5"/>
       <c r="E577" s="11"/>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="4" t="s">
         <v>45</v>
       </c>
@@ -8373,7 +8670,7 @@
       <c r="D578" s="5"/>
       <c r="E578" s="11"/>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="4" t="s">
         <v>45</v>
       </c>
@@ -8386,7 +8683,7 @@
       <c r="D579" s="5"/>
       <c r="E579" s="11"/>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="4" t="s">
         <v>45</v>
       </c>
@@ -8399,7 +8696,7 @@
       <c r="D580" s="5"/>
       <c r="E580" s="11"/>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="4" t="s">
         <v>45</v>
       </c>
@@ -8412,7 +8709,7 @@
       <c r="D581" s="5"/>
       <c r="E581" s="11"/>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="4" t="s">
         <v>45</v>
       </c>
@@ -8425,7 +8722,7 @@
       <c r="D582" s="5"/>
       <c r="E582" s="11"/>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="4" t="s">
         <v>45</v>
       </c>
@@ -8438,7 +8735,7 @@
       <c r="D583" s="5"/>
       <c r="E583" s="11"/>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="4" t="s">
         <v>45</v>
       </c>
@@ -8451,7 +8748,7 @@
       <c r="D584" s="5"/>
       <c r="E584" s="11"/>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="4" t="s">
         <v>45</v>
       </c>
@@ -8464,7 +8761,7 @@
       <c r="D585" s="5"/>
       <c r="E585" s="11"/>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="4" t="s">
         <v>45</v>
       </c>
@@ -8477,7 +8774,7 @@
       <c r="D586" s="5"/>
       <c r="E586" s="11"/>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="4" t="s">
         <v>45</v>
       </c>
@@ -8490,7 +8787,7 @@
       <c r="D587" s="5"/>
       <c r="E587" s="11"/>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="4" t="s">
         <v>45</v>
       </c>
@@ -8503,7 +8800,7 @@
       <c r="D588" s="5"/>
       <c r="E588" s="11"/>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="4" t="s">
         <v>45</v>
       </c>
@@ -8516,7 +8813,7 @@
       <c r="D589" s="5"/>
       <c r="E589" s="11"/>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="4" t="s">
         <v>45</v>
       </c>
@@ -8529,7 +8826,7 @@
       <c r="D590" s="5"/>
       <c r="E590" s="11"/>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="4" t="s">
         <v>45</v>
       </c>
@@ -8542,7 +8839,7 @@
       <c r="D591" s="5"/>
       <c r="E591" s="11"/>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="4" t="s">
         <v>45</v>
       </c>
@@ -8555,7 +8852,7 @@
       <c r="D592" s="5"/>
       <c r="E592" s="11"/>
     </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="4" t="s">
         <v>45</v>
       </c>
@@ -8568,7 +8865,7 @@
       <c r="D593" s="5"/>
       <c r="E593" s="11"/>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="4" t="s">
         <v>45</v>
       </c>
@@ -8581,7 +8878,7 @@
       <c r="D594" s="5"/>
       <c r="E594" s="11"/>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="4" t="s">
         <v>45</v>
       </c>
@@ -8594,7 +8891,7 @@
       <c r="D595" s="5"/>
       <c r="E595" s="11"/>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="4" t="s">
         <v>45</v>
       </c>
@@ -8607,7 +8904,7 @@
       <c r="D596" s="5"/>
       <c r="E596" s="11"/>
     </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="4" t="s">
         <v>45</v>
       </c>
@@ -8620,7 +8917,7 @@
       <c r="D597" s="5"/>
       <c r="E597" s="11"/>
     </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="4" t="s">
         <v>45</v>
       </c>
@@ -8633,7 +8930,7 @@
       <c r="D598" s="5"/>
       <c r="E598" s="11"/>
     </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="4" t="s">
         <v>45</v>
       </c>
@@ -8646,7 +8943,7 @@
       <c r="D599" s="5"/>
       <c r="E599" s="11"/>
     </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="4" t="s">
         <v>45</v>
       </c>
@@ -8659,7 +8956,7 @@
       <c r="D600" s="5"/>
       <c r="E600" s="11"/>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="4" t="s">
         <v>45</v>
       </c>
@@ -8672,7 +8969,7 @@
       <c r="D601" s="5"/>
       <c r="E601" s="11"/>
     </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="4" t="s">
         <v>45</v>
       </c>
@@ -8685,7 +8982,7 @@
       <c r="D602" s="5"/>
       <c r="E602" s="11"/>
     </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="4" t="s">
         <v>45</v>
       </c>
@@ -8698,7 +8995,7 @@
       <c r="D603" s="5"/>
       <c r="E603" s="11"/>
     </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="4" t="s">
         <v>45</v>
       </c>
@@ -8711,7 +9008,7 @@
       <c r="D604" s="5"/>
       <c r="E604" s="11"/>
     </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" s="4" t="s">
         <v>45</v>
       </c>
@@ -8724,7 +9021,7 @@
       <c r="D605" s="5"/>
       <c r="E605" s="11"/>
     </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" s="4" t="s">
         <v>45</v>
       </c>
@@ -8737,7 +9034,7 @@
       <c r="D606" s="5"/>
       <c r="E606" s="11"/>
     </row>
-    <row r="607" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" s="4" t="s">
         <v>45</v>
       </c>
@@ -8750,7 +9047,7 @@
       <c r="D607" s="5"/>
       <c r="E607" s="11"/>
     </row>
-    <row r="608" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="4" t="s">
         <v>45</v>
       </c>
@@ -8763,7 +9060,7 @@
       <c r="D608" s="5"/>
       <c r="E608" s="11"/>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" s="4" t="s">
         <v>45</v>
       </c>
@@ -8776,7 +9073,7 @@
       <c r="D609" s="5"/>
       <c r="E609" s="11"/>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" s="4" t="s">
         <v>45</v>
       </c>
@@ -8789,7 +9086,7 @@
       <c r="D610" s="5"/>
       <c r="E610" s="11"/>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="4" t="s">
         <v>45</v>
       </c>
@@ -8802,7 +9099,7 @@
       <c r="D611" s="5"/>
       <c r="E611" s="11"/>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="4" t="s">
         <v>45</v>
       </c>
@@ -8815,7 +9112,7 @@
       <c r="D612" s="5"/>
       <c r="E612" s="11"/>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="4" t="s">
         <v>45</v>
       </c>
@@ -8828,7 +9125,7 @@
       <c r="D613" s="5"/>
       <c r="E613" s="11"/>
     </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="4" t="s">
         <v>45</v>
       </c>
@@ -8841,7 +9138,7 @@
       <c r="D614" s="5"/>
       <c r="E614" s="11"/>
     </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" s="4" t="s">
         <v>45</v>
       </c>
@@ -8854,7 +9151,7 @@
       <c r="D615" s="5"/>
       <c r="E615" s="11"/>
     </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" s="4" t="s">
         <v>45</v>
       </c>
@@ -8867,7 +9164,7 @@
       <c r="D616" s="5"/>
       <c r="E616" s="11"/>
     </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" s="4" t="s">
         <v>45</v>
       </c>
@@ -8880,7 +9177,7 @@
       <c r="D617" s="5"/>
       <c r="E617" s="11"/>
     </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" s="4" t="s">
         <v>45</v>
       </c>
@@ -8893,7 +9190,7 @@
       <c r="D618" s="5"/>
       <c r="E618" s="11"/>
     </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" s="4" t="s">
         <v>45</v>
       </c>
@@ -8906,7 +9203,7 @@
       <c r="D619" s="5"/>
       <c r="E619" s="11"/>
     </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" s="4" t="s">
         <v>45</v>
       </c>
@@ -8919,7 +9216,7 @@
       <c r="D620" s="5"/>
       <c r="E620" s="11"/>
     </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" s="4" t="s">
         <v>45</v>
       </c>
@@ -8932,7 +9229,7 @@
       <c r="D621" s="5"/>
       <c r="E621" s="11"/>
     </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="4" t="s">
         <v>45</v>
       </c>
@@ -8945,7 +9242,7 @@
       <c r="D622" s="5"/>
       <c r="E622" s="11"/>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="4" t="s">
         <v>45</v>
       </c>
@@ -8958,7 +9255,7 @@
       <c r="D623" s="5"/>
       <c r="E623" s="11"/>
     </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="4" t="s">
         <v>45</v>
       </c>
@@ -8971,7 +9268,7 @@
       <c r="D624" s="5"/>
       <c r="E624" s="11"/>
     </row>
-    <row r="625" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="4" t="s">
         <v>45</v>
       </c>
@@ -8984,7 +9281,7 @@
       <c r="D625" s="5"/>
       <c r="E625" s="11"/>
     </row>
-    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="4" t="s">
         <v>45</v>
       </c>
@@ -8997,7 +9294,7 @@
       <c r="D626" s="5"/>
       <c r="E626" s="11"/>
     </row>
-    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="4" t="s">
         <v>45</v>
       </c>
@@ -9010,7 +9307,7 @@
       <c r="D627" s="5"/>
       <c r="E627" s="11"/>
     </row>
-    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="4" t="s">
         <v>45</v>
       </c>
@@ -9023,7 +9320,7 @@
       <c r="D628" s="5"/>
       <c r="E628" s="11"/>
     </row>
-    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="4" t="s">
         <v>45</v>
       </c>
@@ -9036,7 +9333,7 @@
       <c r="D629" s="5"/>
       <c r="E629" s="11"/>
     </row>
-    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="4" t="s">
         <v>45</v>
       </c>
@@ -9049,7 +9346,7 @@
       <c r="D630" s="5"/>
       <c r="E630" s="11"/>
     </row>
-    <row r="631" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" s="4" t="s">
         <v>45</v>
       </c>
@@ -9062,7 +9359,7 @@
       <c r="D631" s="5"/>
       <c r="E631" s="11"/>
     </row>
-    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" s="4" t="s">
         <v>45</v>
       </c>
@@ -9075,7 +9372,7 @@
       <c r="D632" s="5"/>
       <c r="E632" s="11"/>
     </row>
-    <row r="633" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" s="4" t="s">
         <v>45</v>
       </c>
@@ -9088,7 +9385,7 @@
       <c r="D633" s="5"/>
       <c r="E633" s="11"/>
     </row>
-    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" s="4" t="s">
         <v>45</v>
       </c>
@@ -9101,7 +9398,7 @@
       <c r="D634" s="5"/>
       <c r="E634" s="11"/>
     </row>
-    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" s="4" t="s">
         <v>45</v>
       </c>
@@ -9114,7 +9411,7 @@
       <c r="D635" s="5"/>
       <c r="E635" s="11"/>
     </row>
-    <row r="636" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" s="4" t="s">
         <v>45</v>
       </c>
@@ -9127,7 +9424,7 @@
       <c r="D636" s="5"/>
       <c r="E636" s="11"/>
     </row>
-    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="4" t="s">
         <v>45</v>
       </c>
@@ -9140,7 +9437,7 @@
       <c r="D637" s="5"/>
       <c r="E637" s="11"/>
     </row>
-    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="4" t="s">
         <v>45</v>
       </c>
@@ -9153,7 +9450,7 @@
       <c r="D638" s="5"/>
       <c r="E638" s="11"/>
     </row>
-    <row r="639" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="4" t="s">
         <v>45</v>
       </c>
@@ -9166,7 +9463,7 @@
       <c r="D639" s="5"/>
       <c r="E639" s="11"/>
     </row>
-    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="4" t="s">
         <v>45</v>
       </c>
@@ -9179,7 +9476,7 @@
       <c r="D640" s="5"/>
       <c r="E640" s="11"/>
     </row>
-    <row r="641" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="4" t="s">
         <v>45</v>
       </c>
@@ -9192,7 +9489,7 @@
       <c r="D641" s="5"/>
       <c r="E641" s="11"/>
     </row>
-    <row r="642" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="4" t="s">
         <v>45</v>
       </c>
@@ -9205,7 +9502,7 @@
       <c r="D642" s="5"/>
       <c r="E642" s="11"/>
     </row>
-    <row r="643" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="4" t="s">
         <v>45</v>
       </c>
@@ -9218,7 +9515,7 @@
       <c r="D643" s="5"/>
       <c r="E643" s="11"/>
     </row>
-    <row r="644" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" s="4" t="s">
         <v>45</v>
       </c>
@@ -9231,7 +9528,7 @@
       <c r="D644" s="5"/>
       <c r="E644" s="11"/>
     </row>
-    <row r="645" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" s="4" t="s">
         <v>45</v>
       </c>
@@ -9244,7 +9541,7 @@
       <c r="D645" s="5"/>
       <c r="E645" s="11"/>
     </row>
-    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" s="4" t="s">
         <v>45</v>
       </c>
@@ -9257,7 +9554,7 @@
       <c r="D646" s="5"/>
       <c r="E646" s="11"/>
     </row>
-    <row r="647" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" s="4" t="s">
         <v>45</v>
       </c>
@@ -9270,7 +9567,7 @@
       <c r="D647" s="5"/>
       <c r="E647" s="11"/>
     </row>
-    <row r="648" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" s="4" t="s">
         <v>45</v>
       </c>
@@ -9283,7 +9580,7 @@
       <c r="D648" s="5"/>
       <c r="E648" s="11"/>
     </row>
-    <row r="649" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" s="4" t="s">
         <v>45</v>
       </c>
@@ -9296,7 +9593,7 @@
       <c r="D649" s="5"/>
       <c r="E649" s="11"/>
     </row>
-    <row r="650" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="4" t="s">
         <v>45</v>
       </c>
@@ -9309,7 +9606,7 @@
       <c r="D650" s="5"/>
       <c r="E650" s="11"/>
     </row>
-    <row r="651" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" s="4" t="s">
         <v>45</v>
       </c>
@@ -9322,7 +9619,7 @@
       <c r="D651" s="5"/>
       <c r="E651" s="11"/>
     </row>
-    <row r="652" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" s="4" t="s">
         <v>45</v>
       </c>
@@ -9335,7 +9632,7 @@
       <c r="D652" s="5"/>
       <c r="E652" s="11"/>
     </row>
-    <row r="653" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" s="4" t="s">
         <v>45</v>
       </c>
@@ -9348,7 +9645,7 @@
       <c r="D653" s="5"/>
       <c r="E653" s="11"/>
     </row>
-    <row r="654" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" s="4" t="s">
         <v>45</v>
       </c>
@@ -9361,7 +9658,7 @@
       <c r="D654" s="5"/>
       <c r="E654" s="11"/>
     </row>
-    <row r="655" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" s="4" t="s">
         <v>45</v>
       </c>
@@ -9374,7 +9671,7 @@
       <c r="D655" s="5"/>
       <c r="E655" s="11"/>
     </row>
-    <row r="656" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" s="4" t="s">
         <v>45</v>
       </c>
@@ -9387,7 +9684,7 @@
       <c r="D656" s="5"/>
       <c r="E656" s="11"/>
     </row>
-    <row r="657" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" s="4" t="s">
         <v>45</v>
       </c>
@@ -9400,7 +9697,7 @@
       <c r="D657" s="5"/>
       <c r="E657" s="11"/>
     </row>
-    <row r="658" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" s="4" t="s">
         <v>45</v>
       </c>
@@ -9413,7 +9710,7 @@
       <c r="D658" s="5"/>
       <c r="E658" s="11"/>
     </row>
-    <row r="659" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" s="4" t="s">
         <v>45</v>
       </c>
@@ -9426,7 +9723,7 @@
       <c r="D659" s="5"/>
       <c r="E659" s="11"/>
     </row>
-    <row r="660" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" s="4" t="s">
         <v>45</v>
       </c>
@@ -9439,7 +9736,7 @@
       <c r="D660" s="5"/>
       <c r="E660" s="11"/>
     </row>
-    <row r="661" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" s="4" t="s">
         <v>45</v>
       </c>
@@ -9452,59 +9749,59 @@
       <c r="D661" s="5"/>
       <c r="E661" s="11"/>
     </row>
-    <row r="662" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B662" s="4">
         <v>6</v>
       </c>
       <c r="C662" s="4">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D662" s="5"/>
       <c r="E662" s="11"/>
     </row>
-    <row r="663" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B663" s="4">
         <v>6</v>
       </c>
       <c r="C663" s="4">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D663" s="5"/>
       <c r="E663" s="11"/>
     </row>
-    <row r="664" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B664" s="4">
         <v>6</v>
       </c>
       <c r="C664" s="4">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D664" s="5"/>
       <c r="E664" s="11"/>
     </row>
-    <row r="665" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B665" s="4">
         <v>6</v>
       </c>
       <c r="C665" s="4">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D665" s="5"/>
       <c r="E665" s="11"/>
     </row>
-    <row r="666" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" s="4" t="s">
         <v>46</v>
       </c>
@@ -9512,12 +9809,12 @@
         <v>6</v>
       </c>
       <c r="C666" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D666" s="5"/>
       <c r="E666" s="11"/>
     </row>
-    <row r="667" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" s="4" t="s">
         <v>46</v>
       </c>
@@ -9525,12 +9822,12 @@
         <v>6</v>
       </c>
       <c r="C667" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D667" s="5"/>
       <c r="E667" s="11"/>
     </row>
-    <row r="668" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="4" t="s">
         <v>46</v>
       </c>
@@ -9538,12 +9835,12 @@
         <v>6</v>
       </c>
       <c r="C668" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D668" s="5"/>
       <c r="E668" s="11"/>
     </row>
-    <row r="669" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" s="4" t="s">
         <v>46</v>
       </c>
@@ -9551,12 +9848,12 @@
         <v>6</v>
       </c>
       <c r="C669" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D669" s="5"/>
       <c r="E669" s="11"/>
     </row>
-    <row r="670" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" s="4" t="s">
         <v>46</v>
       </c>
@@ -9564,12 +9861,12 @@
         <v>6</v>
       </c>
       <c r="C670" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D670" s="5"/>
       <c r="E670" s="11"/>
     </row>
-    <row r="671" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" s="4" t="s">
         <v>46</v>
       </c>
@@ -9577,12 +9874,12 @@
         <v>6</v>
       </c>
       <c r="C671" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D671" s="5"/>
       <c r="E671" s="11"/>
     </row>
-    <row r="672" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" s="4" t="s">
         <v>46</v>
       </c>
@@ -9590,12 +9887,12 @@
         <v>6</v>
       </c>
       <c r="C672" s="4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D672" s="5"/>
       <c r="E672" s="11"/>
     </row>
-    <row r="673" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" s="4" t="s">
         <v>46</v>
       </c>
@@ -9603,12 +9900,12 @@
         <v>6</v>
       </c>
       <c r="C673" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D673" s="5"/>
       <c r="E673" s="11"/>
     </row>
-    <row r="674" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" s="4" t="s">
         <v>46</v>
       </c>
@@ -9616,12 +9913,12 @@
         <v>6</v>
       </c>
       <c r="C674" s="4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D674" s="5"/>
       <c r="E674" s="11"/>
     </row>
-    <row r="675" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" s="4" t="s">
         <v>46</v>
       </c>
@@ -9629,12 +9926,12 @@
         <v>6</v>
       </c>
       <c r="C675" s="4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D675" s="5"/>
       <c r="E675" s="11"/>
     </row>
-    <row r="676" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" s="4" t="s">
         <v>46</v>
       </c>
@@ -9642,12 +9939,12 @@
         <v>6</v>
       </c>
       <c r="C676" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D676" s="5"/>
       <c r="E676" s="11"/>
     </row>
-    <row r="677" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" s="4" t="s">
         <v>46</v>
       </c>
@@ -9660,7 +9957,7 @@
       <c r="D677" s="5"/>
       <c r="E677" s="11"/>
     </row>
-    <row r="678" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="4" t="s">
         <v>46</v>
       </c>
@@ -9673,7 +9970,7 @@
       <c r="D678" s="5"/>
       <c r="E678" s="11"/>
     </row>
-    <row r="679" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" s="4" t="s">
         <v>46</v>
       </c>
@@ -9686,7 +9983,7 @@
       <c r="D679" s="5"/>
       <c r="E679" s="11"/>
     </row>
-    <row r="680" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" s="4" t="s">
         <v>46</v>
       </c>
@@ -9699,7 +9996,7 @@
       <c r="D680" s="5"/>
       <c r="E680" s="11"/>
     </row>
-    <row r="681" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" s="4" t="s">
         <v>46</v>
       </c>
@@ -9712,7 +10009,7 @@
       <c r="D681" s="5"/>
       <c r="E681" s="11"/>
     </row>
-    <row r="682" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" s="4" t="s">
         <v>46</v>
       </c>
@@ -9725,7 +10022,7 @@
       <c r="D682" s="5"/>
       <c r="E682" s="11"/>
     </row>
-    <row r="683" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" s="4" t="s">
         <v>46</v>
       </c>
@@ -9738,7 +10035,7 @@
       <c r="D683" s="5"/>
       <c r="E683" s="11"/>
     </row>
-    <row r="684" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" s="4" t="s">
         <v>46</v>
       </c>
@@ -9751,7 +10048,7 @@
       <c r="D684" s="5"/>
       <c r="E684" s="11"/>
     </row>
-    <row r="685" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" s="4" t="s">
         <v>46</v>
       </c>
@@ -9764,7 +10061,7 @@
       <c r="D685" s="5"/>
       <c r="E685" s="11"/>
     </row>
-    <row r="686" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" s="4" t="s">
         <v>46</v>
       </c>
@@ -9777,7 +10074,7 @@
       <c r="D686" s="5"/>
       <c r="E686" s="11"/>
     </row>
-    <row r="687" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" s="4" t="s">
         <v>46</v>
       </c>
@@ -9790,7 +10087,7 @@
       <c r="D687" s="5"/>
       <c r="E687" s="11"/>
     </row>
-    <row r="688" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688" s="4" t="s">
         <v>46</v>
       </c>
@@ -9803,7 +10100,7 @@
       <c r="D688" s="5"/>
       <c r="E688" s="11"/>
     </row>
-    <row r="689" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689" s="4" t="s">
         <v>46</v>
       </c>
@@ -9816,7 +10113,7 @@
       <c r="D689" s="5"/>
       <c r="E689" s="11"/>
     </row>
-    <row r="690" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690" s="4" t="s">
         <v>46</v>
       </c>
@@ -9829,7 +10126,7 @@
       <c r="D690" s="5"/>
       <c r="E690" s="11"/>
     </row>
-    <row r="691" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691" s="4" t="s">
         <v>46</v>
       </c>
@@ -9842,7 +10139,7 @@
       <c r="D691" s="5"/>
       <c r="E691" s="11"/>
     </row>
-    <row r="692" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692" s="4" t="s">
         <v>46</v>
       </c>
@@ -9855,7 +10152,7 @@
       <c r="D692" s="5"/>
       <c r="E692" s="11"/>
     </row>
-    <row r="693" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" s="4" t="s">
         <v>46</v>
       </c>
@@ -9868,7 +10165,7 @@
       <c r="D693" s="5"/>
       <c r="E693" s="11"/>
     </row>
-    <row r="694" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694" s="4" t="s">
         <v>46</v>
       </c>
@@ -9881,7 +10178,7 @@
       <c r="D694" s="5"/>
       <c r="E694" s="11"/>
     </row>
-    <row r="695" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695" s="4" t="s">
         <v>46</v>
       </c>
@@ -9894,7 +10191,7 @@
       <c r="D695" s="5"/>
       <c r="E695" s="11"/>
     </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" s="4" t="s">
         <v>46</v>
       </c>
@@ -9907,7 +10204,7 @@
       <c r="D696" s="5"/>
       <c r="E696" s="11"/>
     </row>
-    <row r="697" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697" s="4" t="s">
         <v>46</v>
       </c>
@@ -9920,7 +10217,7 @@
       <c r="D697" s="5"/>
       <c r="E697" s="11"/>
     </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698" s="4" t="s">
         <v>46</v>
       </c>
@@ -9933,7 +10230,7 @@
       <c r="D698" s="5"/>
       <c r="E698" s="11"/>
     </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699" s="4" t="s">
         <v>46</v>
       </c>
@@ -9946,7 +10243,7 @@
       <c r="D699" s="5"/>
       <c r="E699" s="11"/>
     </row>
-    <row r="700" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" s="4" t="s">
         <v>46</v>
       </c>
@@ -9959,7 +10256,7 @@
       <c r="D700" s="5"/>
       <c r="E700" s="11"/>
     </row>
-    <row r="701" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" s="4" t="s">
         <v>46</v>
       </c>
@@ -9972,7 +10269,7 @@
       <c r="D701" s="5"/>
       <c r="E701" s="11"/>
     </row>
-    <row r="702" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" s="4" t="s">
         <v>46</v>
       </c>
@@ -9985,7 +10282,7 @@
       <c r="D702" s="5"/>
       <c r="E702" s="11"/>
     </row>
-    <row r="703" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" s="4" t="s">
         <v>46</v>
       </c>
@@ -9998,7 +10295,7 @@
       <c r="D703" s="5"/>
       <c r="E703" s="11"/>
     </row>
-    <row r="704" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" s="4" t="s">
         <v>46</v>
       </c>
@@ -10011,7 +10308,7 @@
       <c r="D704" s="5"/>
       <c r="E704" s="11"/>
     </row>
-    <row r="705" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" s="4" t="s">
         <v>46</v>
       </c>
@@ -10024,7 +10321,7 @@
       <c r="D705" s="5"/>
       <c r="E705" s="11"/>
     </row>
-    <row r="706" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" s="4" t="s">
         <v>46</v>
       </c>
@@ -10037,7 +10334,7 @@
       <c r="D706" s="5"/>
       <c r="E706" s="11"/>
     </row>
-    <row r="707" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" s="4" t="s">
         <v>46</v>
       </c>
@@ -10050,7 +10347,7 @@
       <c r="D707" s="5"/>
       <c r="E707" s="11"/>
     </row>
-    <row r="708" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" s="4" t="s">
         <v>46</v>
       </c>
@@ -10063,7 +10360,7 @@
       <c r="D708" s="5"/>
       <c r="E708" s="11"/>
     </row>
-    <row r="709" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" s="4" t="s">
         <v>46</v>
       </c>
@@ -10076,7 +10373,7 @@
       <c r="D709" s="5"/>
       <c r="E709" s="11"/>
     </row>
-    <row r="710" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" s="4" t="s">
         <v>46</v>
       </c>
@@ -10089,7 +10386,7 @@
       <c r="D710" s="5"/>
       <c r="E710" s="11"/>
     </row>
-    <row r="711" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711" s="4" t="s">
         <v>46</v>
       </c>
@@ -10102,7 +10399,7 @@
       <c r="D711" s="5"/>
       <c r="E711" s="11"/>
     </row>
-    <row r="712" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712" s="4" t="s">
         <v>46</v>
       </c>
@@ -10115,7 +10412,7 @@
       <c r="D712" s="5"/>
       <c r="E712" s="11"/>
     </row>
-    <row r="713" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713" s="4" t="s">
         <v>46</v>
       </c>
@@ -10128,7 +10425,7 @@
       <c r="D713" s="5"/>
       <c r="E713" s="11"/>
     </row>
-    <row r="714" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714" s="4" t="s">
         <v>46</v>
       </c>
@@ -10141,7 +10438,7 @@
       <c r="D714" s="5"/>
       <c r="E714" s="11"/>
     </row>
-    <row r="715" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715" s="4" t="s">
         <v>46</v>
       </c>
@@ -10154,7 +10451,7 @@
       <c r="D715" s="5"/>
       <c r="E715" s="11"/>
     </row>
-    <row r="716" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716" s="4" t="s">
         <v>46</v>
       </c>
@@ -10167,7 +10464,7 @@
       <c r="D716" s="5"/>
       <c r="E716" s="11"/>
     </row>
-    <row r="717" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" s="4" t="s">
         <v>46</v>
       </c>
@@ -10180,7 +10477,7 @@
       <c r="D717" s="5"/>
       <c r="E717" s="11"/>
     </row>
-    <row r="718" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718" s="4" t="s">
         <v>46</v>
       </c>
@@ -10193,7 +10490,7 @@
       <c r="D718" s="5"/>
       <c r="E718" s="11"/>
     </row>
-    <row r="719" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719" s="4" t="s">
         <v>46</v>
       </c>
@@ -10206,7 +10503,7 @@
       <c r="D719" s="5"/>
       <c r="E719" s="11"/>
     </row>
-    <row r="720" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720" s="4" t="s">
         <v>46</v>
       </c>
@@ -10219,7 +10516,7 @@
       <c r="D720" s="5"/>
       <c r="E720" s="11"/>
     </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721" s="4" t="s">
         <v>46</v>
       </c>
@@ -10231,6 +10528,103 @@
       </c>
       <c r="D721" s="5"/>
       <c r="E721" s="11"/>
+    </row>
+    <row r="722" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A722" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B722" s="4">
+        <v>6</v>
+      </c>
+      <c r="C722" s="4">
+        <v>12</v>
+      </c>
+      <c r="D722" s="5"/>
+      <c r="E722" s="11"/>
+    </row>
+    <row r="723" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A723" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B723" s="4">
+        <v>6</v>
+      </c>
+      <c r="C723" s="4">
+        <v>13</v>
+      </c>
+      <c r="D723" s="5"/>
+      <c r="E723" s="11"/>
+    </row>
+    <row r="724" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A724" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B724" s="4">
+        <v>6</v>
+      </c>
+      <c r="C724" s="4">
+        <v>14</v>
+      </c>
+      <c r="D724" s="5"/>
+      <c r="E724" s="11"/>
+    </row>
+    <row r="725" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A725" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B725" s="4">
+        <v>6</v>
+      </c>
+      <c r="C725" s="4">
+        <v>15</v>
+      </c>
+      <c r="D725" s="5"/>
+      <c r="E725" s="11"/>
+    </row>
+    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A726" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B726" s="4">
+        <v>6</v>
+      </c>
+      <c r="C726" s="4">
+        <v>45</v>
+      </c>
+      <c r="D726" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A727" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B727" s="4">
+        <v>6</v>
+      </c>
+      <c r="C727" s="4">
+        <v>46</v>
+      </c>
+      <c r="D727" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A728" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B728" s="4">
+        <v>6</v>
+      </c>
+      <c r="C728" s="4">
+        <v>47</v>
+      </c>
+      <c r="D728" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E728" s="11" t="s">
+        <v>116</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10245,13 +10639,13 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A721</xm:sqref>
+          <xm:sqref>A2:A728</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B721</xm:sqref>
+          <xm:sqref>B2:B728</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10260,6 +10654,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0694A9-CD5A-4940-9BE2-B7873F29D0D5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10362,7 +10768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18C9073-4F5F-4CC9-A595-F773C4701ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415C5D06-2D9D-4EAF-8A0A-92890F8A4031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="122">
   <si>
     <t>Категорија</t>
   </si>
@@ -454,6 +454,18 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycby_isP_vyDHE3ZFKeDej4a1VaUVoFOXRYDGYOJpLxTG4fropgziKtDuZQ7EBaA4xBLCGg/exec</t>
+  </si>
+  <si>
+    <t>Подготовка за писмена</t>
+  </si>
+  <si>
+    <t>Писмена работа</t>
+  </si>
+  <si>
+    <t>Анализа</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbybZMWd2XGer0KbhSV1HPwUt09vH_FEQ7WRK1lZjN1Ff77EegbNwu-907aOauef2XvF8Q/exec</t>
   </si>
 </sst>
 </file>
@@ -656,7 +668,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="6"/>
+        <filter val="9"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -968,7 +980,7 @@
     <col min="5" max="5" width="88" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -985,7 +997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>43</v>
       </c>
@@ -1002,7 +1014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>43</v>
       </c>
@@ -1017,7 +1029,7 @@
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
@@ -1032,7 +1044,7 @@
       </c>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>43</v>
       </c>
@@ -1047,7 +1059,7 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>43</v>
       </c>
@@ -1062,7 +1074,7 @@
       </c>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>43</v>
       </c>
@@ -1077,7 +1089,7 @@
       </c>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>43</v>
       </c>
@@ -1092,7 +1104,7 @@
       </c>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>43</v>
       </c>
@@ -1107,7 +1119,7 @@
       </c>
       <c r="E9" s="11"/>
     </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>43</v>
       </c>
@@ -1122,7 +1134,7 @@
       </c>
       <c r="E10" s="11"/>
     </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>43</v>
       </c>
@@ -1137,7 +1149,7 @@
       </c>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>43</v>
       </c>
@@ -1152,7 +1164,7 @@
       </c>
       <c r="E12" s="11"/>
     </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>43</v>
       </c>
@@ -1167,7 +1179,7 @@
       </c>
       <c r="E13" s="11"/>
     </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
@@ -1182,7 +1194,7 @@
       </c>
       <c r="E14" s="11"/>
     </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>43</v>
       </c>
@@ -1197,7 +1209,7 @@
       </c>
       <c r="E15" s="11"/>
     </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>43</v>
       </c>
@@ -1212,7 +1224,7 @@
       </c>
       <c r="E16" s="11"/>
     </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>43</v>
       </c>
@@ -1227,7 +1239,7 @@
       </c>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>43</v>
       </c>
@@ -1242,7 +1254,7 @@
       </c>
       <c r="E18" s="11"/>
     </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>43</v>
       </c>
@@ -1257,7 +1269,7 @@
       </c>
       <c r="E19" s="11"/>
     </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
@@ -1272,7 +1284,7 @@
       </c>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>43</v>
       </c>
@@ -1287,7 +1299,7 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>43</v>
       </c>
@@ -1302,7 +1314,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>43</v>
       </c>
@@ -1317,7 +1329,7 @@
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>43</v>
       </c>
@@ -1332,7 +1344,7 @@
       </c>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>43</v>
       </c>
@@ -1347,7 +1359,7 @@
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>43</v>
       </c>
@@ -1362,7 +1374,7 @@
       </c>
       <c r="E26" s="11"/>
     </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>43</v>
       </c>
@@ -1377,7 +1389,7 @@
       </c>
       <c r="E27" s="11"/>
     </row>
-    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>43</v>
       </c>
@@ -1392,7 +1404,7 @@
       </c>
       <c r="E28" s="11"/>
     </row>
-    <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>43</v>
       </c>
@@ -1407,7 +1419,7 @@
       </c>
       <c r="E29" s="11"/>
     </row>
-    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>43</v>
       </c>
@@ -1422,7 +1434,7 @@
       </c>
       <c r="E30" s="11"/>
     </row>
-    <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>43</v>
       </c>
@@ -1437,7 +1449,7 @@
       </c>
       <c r="E31" s="11"/>
     </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>43</v>
       </c>
@@ -1452,7 +1464,7 @@
       </c>
       <c r="E32" s="11"/>
     </row>
-    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>43</v>
       </c>
@@ -1467,7 +1479,7 @@
       </c>
       <c r="E33" s="11"/>
     </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>43</v>
       </c>
@@ -1482,7 +1494,7 @@
       </c>
       <c r="E34" s="11"/>
     </row>
-    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>43</v>
       </c>
@@ -1497,7 +1509,7 @@
       </c>
       <c r="E35" s="11"/>
     </row>
-    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>43</v>
       </c>
@@ -1512,7 +1524,7 @@
       </c>
       <c r="E36" s="11"/>
     </row>
-    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>43</v>
       </c>
@@ -1527,7 +1539,7 @@
       </c>
       <c r="E37" s="11"/>
     </row>
-    <row r="38" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>43</v>
       </c>
@@ -1542,7 +1554,7 @@
       </c>
       <c r="E38" s="11"/>
     </row>
-    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>43</v>
       </c>
@@ -1557,7 +1569,7 @@
       </c>
       <c r="E39" s="11"/>
     </row>
-    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>43</v>
       </c>
@@ -1572,7 +1584,7 @@
       </c>
       <c r="E40" s="11"/>
     </row>
-    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>43</v>
       </c>
@@ -3155,7 +3167,7 @@
       <c r="D161" s="5"/>
       <c r="E161" s="11"/>
     </row>
-    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>43</v>
       </c>
@@ -3170,7 +3182,7 @@
       </c>
       <c r="E162" s="11"/>
     </row>
-    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>43</v>
       </c>
@@ -3185,7 +3197,7 @@
       </c>
       <c r="E163" s="11"/>
     </row>
-    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>43</v>
       </c>
@@ -3200,7 +3212,7 @@
       </c>
       <c r="E164" s="11"/>
     </row>
-    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>43</v>
       </c>
@@ -4801,7 +4813,7 @@
       <c r="D281" s="5"/>
       <c r="E281" s="11"/>
     </row>
-    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>43</v>
       </c>
@@ -4814,7 +4826,7 @@
       <c r="D282" s="5"/>
       <c r="E282" s="11"/>
     </row>
-    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>43</v>
       </c>
@@ -4827,7 +4839,7 @@
       <c r="D283" s="5"/>
       <c r="E283" s="11"/>
     </row>
-    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>43</v>
       </c>
@@ -4840,7 +4852,7 @@
       <c r="D284" s="5"/>
       <c r="E284" s="11"/>
     </row>
-    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>43</v>
       </c>
@@ -4853,7 +4865,7 @@
       <c r="D285" s="5"/>
       <c r="E285" s="11"/>
     </row>
-    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
         <v>43</v>
       </c>
@@ -4866,7 +4878,7 @@
       <c r="D286" s="5"/>
       <c r="E286" s="11"/>
     </row>
-    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
         <v>43</v>
       </c>
@@ -4879,7 +4891,7 @@
       <c r="D287" s="5"/>
       <c r="E287" s="11"/>
     </row>
-    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>43</v>
       </c>
@@ -4892,7 +4904,7 @@
       <c r="D288" s="5"/>
       <c r="E288" s="11"/>
     </row>
-    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
         <v>43</v>
       </c>
@@ -4905,7 +4917,7 @@
       <c r="D289" s="5"/>
       <c r="E289" s="11"/>
     </row>
-    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>43</v>
       </c>
@@ -4918,7 +4930,7 @@
       <c r="D290" s="5"/>
       <c r="E290" s="11"/>
     </row>
-    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>43</v>
       </c>
@@ -4931,7 +4943,7 @@
       <c r="D291" s="5"/>
       <c r="E291" s="11"/>
     </row>
-    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>43</v>
       </c>
@@ -4944,7 +4956,7 @@
       <c r="D292" s="5"/>
       <c r="E292" s="11"/>
     </row>
-    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>43</v>
       </c>
@@ -4957,7 +4969,7 @@
       <c r="D293" s="5"/>
       <c r="E293" s="11"/>
     </row>
-    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>43</v>
       </c>
@@ -4970,7 +4982,7 @@
       <c r="D294" s="5"/>
       <c r="E294" s="11"/>
     </row>
-    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>43</v>
       </c>
@@ -4983,7 +4995,7 @@
       <c r="D295" s="5"/>
       <c r="E295" s="11"/>
     </row>
-    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>43</v>
       </c>
@@ -4996,7 +5008,7 @@
       <c r="D296" s="5"/>
       <c r="E296" s="11"/>
     </row>
-    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>43</v>
       </c>
@@ -5009,7 +5021,7 @@
       <c r="D297" s="5"/>
       <c r="E297" s="11"/>
     </row>
-    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>43</v>
       </c>
@@ -5022,7 +5034,7 @@
       <c r="D298" s="5"/>
       <c r="E298" s="11"/>
     </row>
-    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>43</v>
       </c>
@@ -5035,7 +5047,7 @@
       <c r="D299" s="5"/>
       <c r="E299" s="11"/>
     </row>
-    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
         <v>43</v>
       </c>
@@ -5048,7 +5060,7 @@
       <c r="D300" s="5"/>
       <c r="E300" s="11"/>
     </row>
-    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
         <v>43</v>
       </c>
@@ -5061,7 +5073,7 @@
       <c r="D301" s="5"/>
       <c r="E301" s="11"/>
     </row>
-    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
         <v>43</v>
       </c>
@@ -5074,7 +5086,7 @@
       <c r="D302" s="5"/>
       <c r="E302" s="11"/>
     </row>
-    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
         <v>43</v>
       </c>
@@ -5087,7 +5099,7 @@
       <c r="D303" s="5"/>
       <c r="E303" s="11"/>
     </row>
-    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>43</v>
       </c>
@@ -5100,7 +5112,7 @@
       <c r="D304" s="5"/>
       <c r="E304" s="11"/>
     </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>43</v>
       </c>
@@ -5113,7 +5125,7 @@
       <c r="D305" s="5"/>
       <c r="E305" s="11"/>
     </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>43</v>
       </c>
@@ -5126,7 +5138,7 @@
       <c r="D306" s="5"/>
       <c r="E306" s="11"/>
     </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>43</v>
       </c>
@@ -5139,7 +5151,7 @@
       <c r="D307" s="5"/>
       <c r="E307" s="11"/>
     </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>43</v>
       </c>
@@ -5152,7 +5164,7 @@
       <c r="D308" s="5"/>
       <c r="E308" s="11"/>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
         <v>43</v>
       </c>
@@ -5165,7 +5177,7 @@
       <c r="D309" s="5"/>
       <c r="E309" s="11"/>
     </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
         <v>43</v>
       </c>
@@ -5178,7 +5190,7 @@
       <c r="D310" s="5"/>
       <c r="E310" s="11"/>
     </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
         <v>43</v>
       </c>
@@ -5191,7 +5203,7 @@
       <c r="D311" s="5"/>
       <c r="E311" s="11"/>
     </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
         <v>43</v>
       </c>
@@ -5204,7 +5216,7 @@
       <c r="D312" s="5"/>
       <c r="E312" s="11"/>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
         <v>43</v>
       </c>
@@ -5217,7 +5229,7 @@
       <c r="D313" s="5"/>
       <c r="E313" s="11"/>
     </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
         <v>43</v>
       </c>
@@ -5230,7 +5242,7 @@
       <c r="D314" s="5"/>
       <c r="E314" s="11"/>
     </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
         <v>43</v>
       </c>
@@ -5243,7 +5255,7 @@
       <c r="D315" s="5"/>
       <c r="E315" s="11"/>
     </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
         <v>43</v>
       </c>
@@ -5256,7 +5268,7 @@
       <c r="D316" s="5"/>
       <c r="E316" s="11"/>
     </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
         <v>43</v>
       </c>
@@ -5269,7 +5281,7 @@
       <c r="D317" s="5"/>
       <c r="E317" s="11"/>
     </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
         <v>43</v>
       </c>
@@ -5279,10 +5291,14 @@
       <c r="C318" s="4">
         <v>37</v>
       </c>
-      <c r="D318" s="5"/>
-      <c r="E318" s="11"/>
-    </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D318" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E318" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
         <v>43</v>
       </c>
@@ -5292,10 +5308,14 @@
       <c r="C319" s="4">
         <v>38</v>
       </c>
-      <c r="D319" s="5"/>
-      <c r="E319" s="11"/>
-    </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D319" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E319" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
         <v>43</v>
       </c>
@@ -5305,10 +5325,12 @@
       <c r="C320" s="4">
         <v>39</v>
       </c>
-      <c r="D320" s="5"/>
+      <c r="D320" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="E320" s="11"/>
     </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
         <v>43</v>
       </c>
@@ -5318,7 +5340,9 @@
       <c r="C321" s="4">
         <v>40</v>
       </c>
-      <c r="D321" s="5"/>
+      <c r="D321" s="5" t="s">
+        <v>120</v>
+      </c>
       <c r="E321" s="11"/>
     </row>
     <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
@@ -10581,7 +10605,7 @@
       <c r="D725" s="5"/>
       <c r="E725" s="11"/>
     </row>
-    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A726" s="4" t="s">
         <v>43</v>
       </c>
@@ -10595,7 +10619,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A727" s="4" t="s">
         <v>43</v>
       </c>
@@ -10609,7 +10633,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A728" s="4" t="s">
         <v>43</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415C5D06-2D9D-4EAF-8A0A-92890F8A4031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F52D549-77E6-4FAD-99FA-08402A77F029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="124">
   <si>
     <t>Категорија</t>
   </si>
@@ -466,6 +466,12 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbybZMWd2XGer0KbhSV1HPwUt09vH_FEQ7WRK1lZjN1Ff77EegbNwu-907aOauef2XvF8Q/exec</t>
+  </si>
+  <si>
+    <t>Решавање неравенки</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbxnOPgC5KjjDQlB0Uc3nB9ppmhGKhDM3zdl9QFILvnd-nANYHLrKTv10ipmsLScCZsV8Q/exec</t>
   </si>
 </sst>
 </file>
@@ -5265,8 +5271,12 @@
       <c r="C316" s="4">
         <v>35</v>
       </c>
-      <c r="D316" s="5"/>
-      <c r="E316" s="11"/>
+      <c r="D316" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E316" s="11" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F52D549-77E6-4FAD-99FA-08402A77F029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE414C5-6794-46D2-BD04-294887ECFEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="127">
   <si>
     <t>Категорија</t>
   </si>
@@ -472,6 +472,15 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbxnOPgC5KjjDQlB0Uc3nB9ppmhGKhDM3zdl9QFILvnd-nANYHLrKTv10ipmsLScCZsV8Q/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbyG6ghTcq0938vVAwwG3wktgobrD3ei2UFg7L9meJG4LLQVtLaGVS_vgj0uM1Zxubqv/exec</t>
+  </si>
+  <si>
+    <t>Класификација и својства на четириаголници</t>
+  </si>
+  <si>
+    <t>Агли на трансверзала</t>
   </si>
 </sst>
 </file>
@@ -669,12 +678,12 @@
   <autoFilter ref="A1:E728" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Алгебра"/>
+        <filter val="Геометрија"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="9"/>
+        <filter val="8"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -4819,7 +4828,7 @@
       <c r="D281" s="5"/>
       <c r="E281" s="11"/>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>43</v>
       </c>
@@ -4832,7 +4841,7 @@
       <c r="D282" s="5"/>
       <c r="E282" s="11"/>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>43</v>
       </c>
@@ -4845,7 +4854,7 @@
       <c r="D283" s="5"/>
       <c r="E283" s="11"/>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>43</v>
       </c>
@@ -4858,7 +4867,7 @@
       <c r="D284" s="5"/>
       <c r="E284" s="11"/>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>43</v>
       </c>
@@ -4871,7 +4880,7 @@
       <c r="D285" s="5"/>
       <c r="E285" s="11"/>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
         <v>43</v>
       </c>
@@ -4884,7 +4893,7 @@
       <c r="D286" s="5"/>
       <c r="E286" s="11"/>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
         <v>43</v>
       </c>
@@ -4897,7 +4906,7 @@
       <c r="D287" s="5"/>
       <c r="E287" s="11"/>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>43</v>
       </c>
@@ -4910,7 +4919,7 @@
       <c r="D288" s="5"/>
       <c r="E288" s="11"/>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
         <v>43</v>
       </c>
@@ -4923,7 +4932,7 @@
       <c r="D289" s="5"/>
       <c r="E289" s="11"/>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>43</v>
       </c>
@@ -4936,7 +4945,7 @@
       <c r="D290" s="5"/>
       <c r="E290" s="11"/>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>43</v>
       </c>
@@ -4949,7 +4958,7 @@
       <c r="D291" s="5"/>
       <c r="E291" s="11"/>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>43</v>
       </c>
@@ -4962,7 +4971,7 @@
       <c r="D292" s="5"/>
       <c r="E292" s="11"/>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>43</v>
       </c>
@@ -4975,7 +4984,7 @@
       <c r="D293" s="5"/>
       <c r="E293" s="11"/>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>43</v>
       </c>
@@ -4988,7 +4997,7 @@
       <c r="D294" s="5"/>
       <c r="E294" s="11"/>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>43</v>
       </c>
@@ -5001,7 +5010,7 @@
       <c r="D295" s="5"/>
       <c r="E295" s="11"/>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>43</v>
       </c>
@@ -5014,7 +5023,7 @@
       <c r="D296" s="5"/>
       <c r="E296" s="11"/>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>43</v>
       </c>
@@ -5027,7 +5036,7 @@
       <c r="D297" s="5"/>
       <c r="E297" s="11"/>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>43</v>
       </c>
@@ -5040,7 +5049,7 @@
       <c r="D298" s="5"/>
       <c r="E298" s="11"/>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>43</v>
       </c>
@@ -5053,7 +5062,7 @@
       <c r="D299" s="5"/>
       <c r="E299" s="11"/>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
         <v>43</v>
       </c>
@@ -5066,7 +5075,7 @@
       <c r="D300" s="5"/>
       <c r="E300" s="11"/>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
         <v>43</v>
       </c>
@@ -5079,7 +5088,7 @@
       <c r="D301" s="5"/>
       <c r="E301" s="11"/>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
         <v>43</v>
       </c>
@@ -5092,7 +5101,7 @@
       <c r="D302" s="5"/>
       <c r="E302" s="11"/>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
         <v>43</v>
       </c>
@@ -5105,7 +5114,7 @@
       <c r="D303" s="5"/>
       <c r="E303" s="11"/>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>43</v>
       </c>
@@ -5118,7 +5127,7 @@
       <c r="D304" s="5"/>
       <c r="E304" s="11"/>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>43</v>
       </c>
@@ -5131,7 +5140,7 @@
       <c r="D305" s="5"/>
       <c r="E305" s="11"/>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>43</v>
       </c>
@@ -5144,7 +5153,7 @@
       <c r="D306" s="5"/>
       <c r="E306" s="11"/>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>43</v>
       </c>
@@ -5157,7 +5166,7 @@
       <c r="D307" s="5"/>
       <c r="E307" s="11"/>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>43</v>
       </c>
@@ -5170,7 +5179,7 @@
       <c r="D308" s="5"/>
       <c r="E308" s="11"/>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
         <v>43</v>
       </c>
@@ -5183,7 +5192,7 @@
       <c r="D309" s="5"/>
       <c r="E309" s="11"/>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
         <v>43</v>
       </c>
@@ -5196,7 +5205,7 @@
       <c r="D310" s="5"/>
       <c r="E310" s="11"/>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
         <v>43</v>
       </c>
@@ -5209,7 +5218,7 @@
       <c r="D311" s="5"/>
       <c r="E311" s="11"/>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
         <v>43</v>
       </c>
@@ -5222,7 +5231,7 @@
       <c r="D312" s="5"/>
       <c r="E312" s="11"/>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
         <v>43</v>
       </c>
@@ -5235,7 +5244,7 @@
       <c r="D313" s="5"/>
       <c r="E313" s="11"/>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
         <v>43</v>
       </c>
@@ -5248,7 +5257,7 @@
       <c r="D314" s="5"/>
       <c r="E314" s="11"/>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
         <v>43</v>
       </c>
@@ -5261,7 +5270,7 @@
       <c r="D315" s="5"/>
       <c r="E315" s="11"/>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
         <v>43</v>
       </c>
@@ -5278,7 +5287,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
         <v>43</v>
       </c>
@@ -5291,7 +5300,7 @@
       <c r="D317" s="5"/>
       <c r="E317" s="11"/>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
         <v>43</v>
       </c>
@@ -5308,7 +5317,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
         <v>43</v>
       </c>
@@ -5325,7 +5334,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
         <v>43</v>
       </c>
@@ -5340,7 +5349,7 @@
       </c>
       <c r="E320" s="11"/>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
         <v>43</v>
       </c>
@@ -6793,7 +6802,7 @@
       <c r="D431" s="5"/>
       <c r="E431" s="11"/>
     </row>
-    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
         <v>44</v>
       </c>
@@ -6803,10 +6812,14 @@
       <c r="C432" s="4">
         <v>1</v>
       </c>
-      <c r="D432" s="5"/>
-      <c r="E432" s="11"/>
-    </row>
-    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D432" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E432" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
         <v>44</v>
       </c>
@@ -6819,7 +6832,7 @@
       <c r="D433" s="5"/>
       <c r="E433" s="11"/>
     </row>
-    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
         <v>44</v>
       </c>
@@ -6829,10 +6842,12 @@
       <c r="C434" s="4">
         <v>3</v>
       </c>
-      <c r="D434" s="5"/>
+      <c r="D434" s="5" t="s">
+        <v>126</v>
+      </c>
       <c r="E434" s="11"/>
     </row>
-    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
         <v>44</v>
       </c>
@@ -6845,7 +6860,7 @@
       <c r="D435" s="5"/>
       <c r="E435" s="11"/>
     </row>
-    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
         <v>44</v>
       </c>
@@ -6858,7 +6873,7 @@
       <c r="D436" s="5"/>
       <c r="E436" s="11"/>
     </row>
-    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
         <v>44</v>
       </c>
@@ -6871,7 +6886,7 @@
       <c r="D437" s="5"/>
       <c r="E437" s="11"/>
     </row>
-    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
         <v>44</v>
       </c>
@@ -6884,7 +6899,7 @@
       <c r="D438" s="5"/>
       <c r="E438" s="11"/>
     </row>
-    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
         <v>44</v>
       </c>
@@ -6897,7 +6912,7 @@
       <c r="D439" s="5"/>
       <c r="E439" s="11"/>
     </row>
-    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
         <v>44</v>
       </c>
@@ -6910,7 +6925,7 @@
       <c r="D440" s="5"/>
       <c r="E440" s="11"/>
     </row>
-    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
         <v>44</v>
       </c>
@@ -6923,7 +6938,7 @@
       <c r="D441" s="5"/>
       <c r="E441" s="11"/>
     </row>
-    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
         <v>44</v>
       </c>
@@ -6936,7 +6951,7 @@
       <c r="D442" s="5"/>
       <c r="E442" s="11"/>
     </row>
-    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
         <v>44</v>
       </c>
@@ -6949,7 +6964,7 @@
       <c r="D443" s="5"/>
       <c r="E443" s="11"/>
     </row>
-    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
         <v>44</v>
       </c>
@@ -6962,7 +6977,7 @@
       <c r="D444" s="5"/>
       <c r="E444" s="11"/>
     </row>
-    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
         <v>44</v>
       </c>
@@ -6975,7 +6990,7 @@
       <c r="D445" s="5"/>
       <c r="E445" s="11"/>
     </row>
-    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
         <v>44</v>
       </c>
@@ -6988,7 +7003,7 @@
       <c r="D446" s="5"/>
       <c r="E446" s="11"/>
     </row>
-    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
         <v>44</v>
       </c>
@@ -7001,7 +7016,7 @@
       <c r="D447" s="5"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
         <v>44</v>
       </c>
@@ -7014,7 +7029,7 @@
       <c r="D448" s="5"/>
       <c r="E448" s="11"/>
     </row>
-    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
         <v>44</v>
       </c>
@@ -7027,7 +7042,7 @@
       <c r="D449" s="5"/>
       <c r="E449" s="11"/>
     </row>
-    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
         <v>44</v>
       </c>
@@ -7040,7 +7055,7 @@
       <c r="D450" s="5"/>
       <c r="E450" s="11"/>
     </row>
-    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
         <v>44</v>
       </c>
@@ -7053,7 +7068,7 @@
       <c r="D451" s="5"/>
       <c r="E451" s="11"/>
     </row>
-    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
         <v>44</v>
       </c>
@@ -7066,7 +7081,7 @@
       <c r="D452" s="5"/>
       <c r="E452" s="11"/>
     </row>
-    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
         <v>44</v>
       </c>
@@ -7079,7 +7094,7 @@
       <c r="D453" s="5"/>
       <c r="E453" s="11"/>
     </row>
-    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
         <v>44</v>
       </c>
@@ -7092,7 +7107,7 @@
       <c r="D454" s="5"/>
       <c r="E454" s="11"/>
     </row>
-    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
         <v>44</v>
       </c>
@@ -7105,7 +7120,7 @@
       <c r="D455" s="5"/>
       <c r="E455" s="11"/>
     </row>
-    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
         <v>44</v>
       </c>
@@ -7118,7 +7133,7 @@
       <c r="D456" s="5"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
         <v>44</v>
       </c>
@@ -7131,7 +7146,7 @@
       <c r="D457" s="5"/>
       <c r="E457" s="11"/>
     </row>
-    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
         <v>44</v>
       </c>
@@ -7144,7 +7159,7 @@
       <c r="D458" s="5"/>
       <c r="E458" s="11"/>
     </row>
-    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
         <v>44</v>
       </c>
@@ -7157,7 +7172,7 @@
       <c r="D459" s="5"/>
       <c r="E459" s="11"/>
     </row>
-    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
         <v>44</v>
       </c>
@@ -7170,7 +7185,7 @@
       <c r="D460" s="5"/>
       <c r="E460" s="11"/>
     </row>
-    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
         <v>44</v>
       </c>
@@ -7183,7 +7198,7 @@
       <c r="D461" s="5"/>
       <c r="E461" s="11"/>
     </row>
-    <row r="462" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
         <v>44</v>
       </c>
@@ -7196,7 +7211,7 @@
       <c r="D462" s="5"/>
       <c r="E462" s="11"/>
     </row>
-    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
         <v>44</v>
       </c>
@@ -7209,7 +7224,7 @@
       <c r="D463" s="5"/>
       <c r="E463" s="11"/>
     </row>
-    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
         <v>44</v>
       </c>
@@ -7222,7 +7237,7 @@
       <c r="D464" s="5"/>
       <c r="E464" s="11"/>
     </row>
-    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
         <v>44</v>
       </c>
@@ -7235,7 +7250,7 @@
       <c r="D465" s="5"/>
       <c r="E465" s="11"/>
     </row>
-    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
         <v>44</v>
       </c>
@@ -7248,7 +7263,7 @@
       <c r="D466" s="5"/>
       <c r="E466" s="11"/>
     </row>
-    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
         <v>44</v>
       </c>
@@ -7261,7 +7276,7 @@
       <c r="D467" s="5"/>
       <c r="E467" s="11"/>
     </row>
-    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
         <v>44</v>
       </c>
@@ -7274,7 +7289,7 @@
       <c r="D468" s="5"/>
       <c r="E468" s="11"/>
     </row>
-    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
         <v>44</v>
       </c>
@@ -7287,7 +7302,7 @@
       <c r="D469" s="5"/>
       <c r="E469" s="11"/>
     </row>
-    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
         <v>44</v>
       </c>
@@ -7300,7 +7315,7 @@
       <c r="D470" s="5"/>
       <c r="E470" s="11"/>
     </row>
-    <row r="471" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
         <v>44</v>
       </c>
@@ -7313,7 +7328,7 @@
       <c r="D471" s="5"/>
       <c r="E471" s="11"/>
     </row>
-    <row r="472" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
         <v>44</v>
       </c>
@@ -7326,7 +7341,7 @@
       <c r="D472" s="5"/>
       <c r="E472" s="11"/>
     </row>
-    <row r="473" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
         <v>44</v>
       </c>
@@ -7339,7 +7354,7 @@
       <c r="D473" s="5"/>
       <c r="E473" s="11"/>
     </row>
-    <row r="474" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
         <v>44</v>
       </c>
@@ -7352,7 +7367,7 @@
       <c r="D474" s="5"/>
       <c r="E474" s="11"/>
     </row>
-    <row r="475" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
         <v>44</v>
       </c>
@@ -7365,7 +7380,7 @@
       <c r="D475" s="5"/>
       <c r="E475" s="11"/>
     </row>
-    <row r="476" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
         <v>44</v>
       </c>
@@ -7378,7 +7393,7 @@
       <c r="D476" s="5"/>
       <c r="E476" s="11"/>
     </row>
-    <row r="477" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
         <v>44</v>
       </c>
@@ -7391,7 +7406,7 @@
       <c r="D477" s="5"/>
       <c r="E477" s="11"/>
     </row>
-    <row r="478" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
         <v>44</v>
       </c>
@@ -7404,7 +7419,7 @@
       <c r="D478" s="5"/>
       <c r="E478" s="11"/>
     </row>
-    <row r="479" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
         <v>44</v>
       </c>
@@ -7417,7 +7432,7 @@
       <c r="D479" s="5"/>
       <c r="E479" s="11"/>
     </row>
-    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
         <v>44</v>
       </c>
@@ -7430,7 +7445,7 @@
       <c r="D480" s="5"/>
       <c r="E480" s="11"/>
     </row>
-    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
         <v>44</v>
       </c>
@@ -7443,7 +7458,7 @@
       <c r="D481" s="5"/>
       <c r="E481" s="11"/>
     </row>
-    <row r="482" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
         <v>44</v>
       </c>
@@ -7456,7 +7471,7 @@
       <c r="D482" s="5"/>
       <c r="E482" s="11"/>
     </row>
-    <row r="483" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
         <v>44</v>
       </c>
@@ -7469,7 +7484,7 @@
       <c r="D483" s="5"/>
       <c r="E483" s="11"/>
     </row>
-    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
         <v>44</v>
       </c>
@@ -7482,7 +7497,7 @@
       <c r="D484" s="5"/>
       <c r="E484" s="11"/>
     </row>
-    <row r="485" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
         <v>44</v>
       </c>
@@ -7495,7 +7510,7 @@
       <c r="D485" s="5"/>
       <c r="E485" s="11"/>
     </row>
-    <row r="486" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
         <v>44</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE414C5-6794-46D2-BD04-294887ECFEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A97E8DE-F79F-4648-9DDC-AF890428E32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="128">
   <si>
     <t>Категорија</t>
   </si>
@@ -481,6 +481,9 @@
   </si>
   <si>
     <t>Агли на трансверзала</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbzRM7STmyfRNEaViuEM806mGS24auoMfJ-AOBhLYeO7CiMMgqPsFAt3-V3PFY_erzQ01Q/exec</t>
   </si>
 </sst>
 </file>
@@ -678,12 +681,12 @@
   <autoFilter ref="A1:E728" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Геометрија"/>
+        <filter val="Мерење"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="8"/>
+        <filter val="7"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -6802,7 +6805,7 @@
       <c r="D431" s="5"/>
       <c r="E431" s="11"/>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
         <v>44</v>
       </c>
@@ -6819,7 +6822,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
         <v>44</v>
       </c>
@@ -6832,7 +6835,7 @@
       <c r="D433" s="5"/>
       <c r="E433" s="11"/>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
         <v>44</v>
       </c>
@@ -6847,7 +6850,7 @@
       </c>
       <c r="E434" s="11"/>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
         <v>44</v>
       </c>
@@ -6860,7 +6863,7 @@
       <c r="D435" s="5"/>
       <c r="E435" s="11"/>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
         <v>44</v>
       </c>
@@ -6873,7 +6876,7 @@
       <c r="D436" s="5"/>
       <c r="E436" s="11"/>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
         <v>44</v>
       </c>
@@ -6886,7 +6889,7 @@
       <c r="D437" s="5"/>
       <c r="E437" s="11"/>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
         <v>44</v>
       </c>
@@ -6899,7 +6902,7 @@
       <c r="D438" s="5"/>
       <c r="E438" s="11"/>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
         <v>44</v>
       </c>
@@ -6912,7 +6915,7 @@
       <c r="D439" s="5"/>
       <c r="E439" s="11"/>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
         <v>44</v>
       </c>
@@ -6925,7 +6928,7 @@
       <c r="D440" s="5"/>
       <c r="E440" s="11"/>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
         <v>44</v>
       </c>
@@ -6938,7 +6941,7 @@
       <c r="D441" s="5"/>
       <c r="E441" s="11"/>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
         <v>44</v>
       </c>
@@ -6951,7 +6954,7 @@
       <c r="D442" s="5"/>
       <c r="E442" s="11"/>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
         <v>44</v>
       </c>
@@ -6964,7 +6967,7 @@
       <c r="D443" s="5"/>
       <c r="E443" s="11"/>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
         <v>44</v>
       </c>
@@ -6977,7 +6980,7 @@
       <c r="D444" s="5"/>
       <c r="E444" s="11"/>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
         <v>44</v>
       </c>
@@ -6990,7 +6993,7 @@
       <c r="D445" s="5"/>
       <c r="E445" s="11"/>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
         <v>44</v>
       </c>
@@ -7003,7 +7006,7 @@
       <c r="D446" s="5"/>
       <c r="E446" s="11"/>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
         <v>44</v>
       </c>
@@ -7016,7 +7019,7 @@
       <c r="D447" s="5"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
         <v>44</v>
       </c>
@@ -7029,7 +7032,7 @@
       <c r="D448" s="5"/>
       <c r="E448" s="11"/>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
         <v>44</v>
       </c>
@@ -7042,7 +7045,7 @@
       <c r="D449" s="5"/>
       <c r="E449" s="11"/>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
         <v>44</v>
       </c>
@@ -7055,7 +7058,7 @@
       <c r="D450" s="5"/>
       <c r="E450" s="11"/>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
         <v>44</v>
       </c>
@@ -7068,7 +7071,7 @@
       <c r="D451" s="5"/>
       <c r="E451" s="11"/>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
         <v>44</v>
       </c>
@@ -7081,7 +7084,7 @@
       <c r="D452" s="5"/>
       <c r="E452" s="11"/>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
         <v>44</v>
       </c>
@@ -7094,7 +7097,7 @@
       <c r="D453" s="5"/>
       <c r="E453" s="11"/>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
         <v>44</v>
       </c>
@@ -7107,7 +7110,7 @@
       <c r="D454" s="5"/>
       <c r="E454" s="11"/>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
         <v>44</v>
       </c>
@@ -7120,7 +7123,7 @@
       <c r="D455" s="5"/>
       <c r="E455" s="11"/>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
         <v>44</v>
       </c>
@@ -7133,7 +7136,7 @@
       <c r="D456" s="5"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
         <v>44</v>
       </c>
@@ -7146,7 +7149,7 @@
       <c r="D457" s="5"/>
       <c r="E457" s="11"/>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
         <v>44</v>
       </c>
@@ -7159,7 +7162,7 @@
       <c r="D458" s="5"/>
       <c r="E458" s="11"/>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
         <v>44</v>
       </c>
@@ -7172,7 +7175,7 @@
       <c r="D459" s="5"/>
       <c r="E459" s="11"/>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
         <v>44</v>
       </c>
@@ -7185,7 +7188,7 @@
       <c r="D460" s="5"/>
       <c r="E460" s="11"/>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
         <v>44</v>
       </c>
@@ -7198,7 +7201,7 @@
       <c r="D461" s="5"/>
       <c r="E461" s="11"/>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
         <v>44</v>
       </c>
@@ -7211,7 +7214,7 @@
       <c r="D462" s="5"/>
       <c r="E462" s="11"/>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
         <v>44</v>
       </c>
@@ -7224,7 +7227,7 @@
       <c r="D463" s="5"/>
       <c r="E463" s="11"/>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
         <v>44</v>
       </c>
@@ -7237,7 +7240,7 @@
       <c r="D464" s="5"/>
       <c r="E464" s="11"/>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
         <v>44</v>
       </c>
@@ -7250,7 +7253,7 @@
       <c r="D465" s="5"/>
       <c r="E465" s="11"/>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
         <v>44</v>
       </c>
@@ -7263,7 +7266,7 @@
       <c r="D466" s="5"/>
       <c r="E466" s="11"/>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
         <v>44</v>
       </c>
@@ -7276,7 +7279,7 @@
       <c r="D467" s="5"/>
       <c r="E467" s="11"/>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
         <v>44</v>
       </c>
@@ -7289,7 +7292,7 @@
       <c r="D468" s="5"/>
       <c r="E468" s="11"/>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
         <v>44</v>
       </c>
@@ -7302,7 +7305,7 @@
       <c r="D469" s="5"/>
       <c r="E469" s="11"/>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
         <v>44</v>
       </c>
@@ -7315,7 +7318,7 @@
       <c r="D470" s="5"/>
       <c r="E470" s="11"/>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
         <v>44</v>
       </c>
@@ -7328,7 +7331,7 @@
       <c r="D471" s="5"/>
       <c r="E471" s="11"/>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
         <v>44</v>
       </c>
@@ -7341,7 +7344,7 @@
       <c r="D472" s="5"/>
       <c r="E472" s="11"/>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
         <v>44</v>
       </c>
@@ -7354,7 +7357,7 @@
       <c r="D473" s="5"/>
       <c r="E473" s="11"/>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
         <v>44</v>
       </c>
@@ -7367,7 +7370,7 @@
       <c r="D474" s="5"/>
       <c r="E474" s="11"/>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
         <v>44</v>
       </c>
@@ -7380,7 +7383,7 @@
       <c r="D475" s="5"/>
       <c r="E475" s="11"/>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
         <v>44</v>
       </c>
@@ -7393,7 +7396,7 @@
       <c r="D476" s="5"/>
       <c r="E476" s="11"/>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
         <v>44</v>
       </c>
@@ -7406,7 +7409,7 @@
       <c r="D477" s="5"/>
       <c r="E477" s="11"/>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
         <v>44</v>
       </c>
@@ -7419,7 +7422,7 @@
       <c r="D478" s="5"/>
       <c r="E478" s="11"/>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
         <v>44</v>
       </c>
@@ -7432,7 +7435,7 @@
       <c r="D479" s="5"/>
       <c r="E479" s="11"/>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
         <v>44</v>
       </c>
@@ -7445,7 +7448,7 @@
       <c r="D480" s="5"/>
       <c r="E480" s="11"/>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
         <v>44</v>
       </c>
@@ -7458,7 +7461,7 @@
       <c r="D481" s="5"/>
       <c r="E481" s="11"/>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
         <v>44</v>
       </c>
@@ -7471,7 +7474,7 @@
       <c r="D482" s="5"/>
       <c r="E482" s="11"/>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
         <v>44</v>
       </c>
@@ -7484,7 +7487,7 @@
       <c r="D483" s="5"/>
       <c r="E483" s="11"/>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
         <v>44</v>
       </c>
@@ -7497,7 +7500,7 @@
       <c r="D484" s="5"/>
       <c r="E484" s="11"/>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
         <v>44</v>
       </c>
@@ -7510,7 +7513,7 @@
       <c r="D485" s="5"/>
       <c r="E485" s="11"/>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
         <v>44</v>
       </c>
@@ -8628,7 +8631,7 @@
       <c r="D571" s="5"/>
       <c r="E571" s="11"/>
     </row>
-    <row r="572" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A572" s="4" t="s">
         <v>45</v>
       </c>
@@ -8641,7 +8644,7 @@
       <c r="D572" s="5"/>
       <c r="E572" s="11"/>
     </row>
-    <row r="573" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A573" s="4" t="s">
         <v>45</v>
       </c>
@@ -8654,7 +8657,7 @@
       <c r="D573" s="5"/>
       <c r="E573" s="11"/>
     </row>
-    <row r="574" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A574" s="4" t="s">
         <v>45</v>
       </c>
@@ -8667,7 +8670,7 @@
       <c r="D574" s="5"/>
       <c r="E574" s="11"/>
     </row>
-    <row r="575" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A575" s="4" t="s">
         <v>45</v>
       </c>
@@ -8680,7 +8683,7 @@
       <c r="D575" s="5"/>
       <c r="E575" s="11"/>
     </row>
-    <row r="576" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A576" s="4" t="s">
         <v>45</v>
       </c>
@@ -8693,7 +8696,7 @@
       <c r="D576" s="5"/>
       <c r="E576" s="11"/>
     </row>
-    <row r="577" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A577" s="4" t="s">
         <v>45</v>
       </c>
@@ -8706,7 +8709,7 @@
       <c r="D577" s="5"/>
       <c r="E577" s="11"/>
     </row>
-    <row r="578" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A578" s="4" t="s">
         <v>45</v>
       </c>
@@ -8719,7 +8722,7 @@
       <c r="D578" s="5"/>
       <c r="E578" s="11"/>
     </row>
-    <row r="579" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A579" s="4" t="s">
         <v>45</v>
       </c>
@@ -8732,7 +8735,7 @@
       <c r="D579" s="5"/>
       <c r="E579" s="11"/>
     </row>
-    <row r="580" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A580" s="4" t="s">
         <v>45</v>
       </c>
@@ -8745,7 +8748,7 @@
       <c r="D580" s="5"/>
       <c r="E580" s="11"/>
     </row>
-    <row r="581" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A581" s="4" t="s">
         <v>45</v>
       </c>
@@ -8758,7 +8761,7 @@
       <c r="D581" s="5"/>
       <c r="E581" s="11"/>
     </row>
-    <row r="582" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A582" s="4" t="s">
         <v>45</v>
       </c>
@@ -8771,7 +8774,7 @@
       <c r="D582" s="5"/>
       <c r="E582" s="11"/>
     </row>
-    <row r="583" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A583" s="4" t="s">
         <v>45</v>
       </c>
@@ -8784,7 +8787,7 @@
       <c r="D583" s="5"/>
       <c r="E583" s="11"/>
     </row>
-    <row r="584" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A584" s="4" t="s">
         <v>45</v>
       </c>
@@ -8797,7 +8800,7 @@
       <c r="D584" s="5"/>
       <c r="E584" s="11"/>
     </row>
-    <row r="585" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A585" s="4" t="s">
         <v>45</v>
       </c>
@@ -8810,7 +8813,7 @@
       <c r="D585" s="5"/>
       <c r="E585" s="11"/>
     </row>
-    <row r="586" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A586" s="4" t="s">
         <v>45</v>
       </c>
@@ -8823,7 +8826,7 @@
       <c r="D586" s="5"/>
       <c r="E586" s="11"/>
     </row>
-    <row r="587" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A587" s="4" t="s">
         <v>45</v>
       </c>
@@ -8836,7 +8839,7 @@
       <c r="D587" s="5"/>
       <c r="E587" s="11"/>
     </row>
-    <row r="588" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A588" s="4" t="s">
         <v>45</v>
       </c>
@@ -8849,7 +8852,7 @@
       <c r="D588" s="5"/>
       <c r="E588" s="11"/>
     </row>
-    <row r="589" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A589" s="4" t="s">
         <v>45</v>
       </c>
@@ -8862,7 +8865,7 @@
       <c r="D589" s="5"/>
       <c r="E589" s="11"/>
     </row>
-    <row r="590" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A590" s="4" t="s">
         <v>45</v>
       </c>
@@ -8875,7 +8878,7 @@
       <c r="D590" s="5"/>
       <c r="E590" s="11"/>
     </row>
-    <row r="591" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A591" s="4" t="s">
         <v>45</v>
       </c>
@@ -8888,7 +8891,7 @@
       <c r="D591" s="5"/>
       <c r="E591" s="11"/>
     </row>
-    <row r="592" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A592" s="4" t="s">
         <v>45</v>
       </c>
@@ -8901,7 +8904,7 @@
       <c r="D592" s="5"/>
       <c r="E592" s="11"/>
     </row>
-    <row r="593" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A593" s="4" t="s">
         <v>45</v>
       </c>
@@ -8914,7 +8917,7 @@
       <c r="D593" s="5"/>
       <c r="E593" s="11"/>
     </row>
-    <row r="594" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A594" s="4" t="s">
         <v>45</v>
       </c>
@@ -8927,7 +8930,7 @@
       <c r="D594" s="5"/>
       <c r="E594" s="11"/>
     </row>
-    <row r="595" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A595" s="4" t="s">
         <v>45</v>
       </c>
@@ -8940,7 +8943,7 @@
       <c r="D595" s="5"/>
       <c r="E595" s="11"/>
     </row>
-    <row r="596" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A596" s="4" t="s">
         <v>45</v>
       </c>
@@ -8953,7 +8956,7 @@
       <c r="D596" s="5"/>
       <c r="E596" s="11"/>
     </row>
-    <row r="597" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A597" s="4" t="s">
         <v>45</v>
       </c>
@@ -8966,7 +8969,7 @@
       <c r="D597" s="5"/>
       <c r="E597" s="11"/>
     </row>
-    <row r="598" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A598" s="4" t="s">
         <v>45</v>
       </c>
@@ -8979,7 +8982,7 @@
       <c r="D598" s="5"/>
       <c r="E598" s="11"/>
     </row>
-    <row r="599" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A599" s="4" t="s">
         <v>45</v>
       </c>
@@ -8989,10 +8992,14 @@
       <c r="C599" s="4">
         <v>28</v>
       </c>
-      <c r="D599" s="5"/>
-      <c r="E599" s="11"/>
-    </row>
-    <row r="600" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D599" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E599" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="600" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A600" s="4" t="s">
         <v>45</v>
       </c>
@@ -9005,7 +9012,7 @@
       <c r="D600" s="5"/>
       <c r="E600" s="11"/>
     </row>
-    <row r="601" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A601" s="4" t="s">
         <v>45</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A97E8DE-F79F-4648-9DDC-AF890428E32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A01D535-0644-482B-8A88-E026E7ABCF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="125">
   <si>
     <t>Категорија</t>
   </si>
@@ -438,18 +438,6 @@
     <t>Собирање и одземање броеви со ист или различен број на децимали - вежби</t>
   </si>
   <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
     <t>https://script.google.com/macros/s/AKfycbyg7vf8E7j9rsw3j1qNjQ9WeHXfAkKzFn1kzwr_gNfqQPNc4NGpcQXVioZI36r1oosA/exec</t>
   </si>
   <si>
@@ -484,6 +472,9 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbzRM7STmyfRNEaViuEM806mGS24auoMfJ-AOBhLYeO7CiMMgqPsFAt3-V3PFY_erzQ01Q/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbx9uucFv8WkyoXSXCYVboZeBERSmR6otJOkngW4jy-GMBQiRTeaHCNZ0eLUo9R1Flk/exec</t>
   </si>
 </sst>
 </file>
@@ -618,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -651,7 +642,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -681,12 +671,12 @@
   <autoFilter ref="A1:E728" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Мерење"/>
+        <filter val="Алгебра"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="7"/>
+        <filter val="9"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -995,7 +985,7 @@
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="58" customWidth="1"/>
-    <col min="5" max="5" width="88" style="12" customWidth="1"/>
+    <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1025,7 +1015,7 @@
       <c r="C2" s="4">
         <v>1</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>67</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -1042,7 +1032,7 @@
       <c r="C3" s="4">
         <v>2</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>68</v>
       </c>
       <c r="E3" s="11"/>
@@ -1057,7 +1047,7 @@
       <c r="C4" s="4">
         <v>3</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>69</v>
       </c>
       <c r="E4" s="11"/>
@@ -1072,7 +1062,7 @@
       <c r="C5" s="4">
         <v>4</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E5" s="11"/>
@@ -1087,7 +1077,7 @@
       <c r="C6" s="4">
         <v>5</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="11"/>
@@ -1102,7 +1092,7 @@
       <c r="C7" s="4">
         <v>6</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>72</v>
       </c>
       <c r="E7" s="11"/>
@@ -1117,7 +1107,7 @@
       <c r="C8" s="4">
         <v>7</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E8" s="11"/>
@@ -1132,7 +1122,7 @@
       <c r="C9" s="4">
         <v>8</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="12" t="s">
         <v>74</v>
       </c>
       <c r="E9" s="11"/>
@@ -1147,7 +1137,7 @@
       <c r="C10" s="4">
         <v>9</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="12" t="s">
         <v>75</v>
       </c>
       <c r="E10" s="11"/>
@@ -1162,7 +1152,7 @@
       <c r="C11" s="4">
         <v>10</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="12" t="s">
         <v>76</v>
       </c>
       <c r="E11" s="11"/>
@@ -1177,7 +1167,7 @@
       <c r="C12" s="4">
         <v>11</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="12" t="s">
         <v>77</v>
       </c>
       <c r="E12" s="11"/>
@@ -1192,7 +1182,7 @@
       <c r="C13" s="4">
         <v>12</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>78</v>
       </c>
       <c r="E13" s="11"/>
@@ -1207,7 +1197,7 @@
       <c r="C14" s="4">
         <v>13</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="12" t="s">
         <v>79</v>
       </c>
       <c r="E14" s="11"/>
@@ -1222,7 +1212,7 @@
       <c r="C15" s="4">
         <v>14</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="12" t="s">
         <v>80</v>
       </c>
       <c r="E15" s="11"/>
@@ -1237,7 +1227,7 @@
       <c r="C16" s="4">
         <v>15</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="12" t="s">
         <v>81</v>
       </c>
       <c r="E16" s="11"/>
@@ -1252,7 +1242,7 @@
       <c r="C17" s="4">
         <v>16</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="12" t="s">
         <v>82</v>
       </c>
       <c r="E17" s="11"/>
@@ -1267,7 +1257,7 @@
       <c r="C18" s="4">
         <v>17</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="12" t="s">
         <v>83</v>
       </c>
       <c r="E18" s="11"/>
@@ -1282,7 +1272,7 @@
       <c r="C19" s="4">
         <v>18</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="12" t="s">
         <v>84</v>
       </c>
       <c r="E19" s="11"/>
@@ -1297,7 +1287,7 @@
       <c r="C20" s="4">
         <v>19</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="12" t="s">
         <v>85</v>
       </c>
       <c r="E20" s="11"/>
@@ -1312,7 +1302,7 @@
       <c r="C21" s="4">
         <v>20</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="12" t="s">
         <v>86</v>
       </c>
       <c r="E21" s="11"/>
@@ -1327,7 +1317,7 @@
       <c r="C22" s="4">
         <v>21</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="12" t="s">
         <v>87</v>
       </c>
       <c r="E22" s="11"/>
@@ -1342,7 +1332,7 @@
       <c r="C23" s="4">
         <v>22</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="12" t="s">
         <v>88</v>
       </c>
       <c r="E23" s="11"/>
@@ -1357,7 +1347,7 @@
       <c r="C24" s="4">
         <v>23</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="12" t="s">
         <v>89</v>
       </c>
       <c r="E24" s="11"/>
@@ -1372,7 +1362,7 @@
       <c r="C25" s="4">
         <v>24</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="12" t="s">
         <v>90</v>
       </c>
       <c r="E25" s="11"/>
@@ -1387,7 +1377,7 @@
       <c r="C26" s="4">
         <v>25</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="12" t="s">
         <v>91</v>
       </c>
       <c r="E26" s="11"/>
@@ -1402,7 +1392,7 @@
       <c r="C27" s="4">
         <v>26</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="12" t="s">
         <v>92</v>
       </c>
       <c r="E27" s="11"/>
@@ -1417,7 +1407,7 @@
       <c r="C28" s="4">
         <v>27</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="12" t="s">
         <v>93</v>
       </c>
       <c r="E28" s="11"/>
@@ -1432,7 +1422,7 @@
       <c r="C29" s="4">
         <v>28</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="12" t="s">
         <v>94</v>
       </c>
       <c r="E29" s="11"/>
@@ -1447,7 +1437,7 @@
       <c r="C30" s="4">
         <v>29</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="12" t="s">
         <v>95</v>
       </c>
       <c r="E30" s="11"/>
@@ -1462,7 +1452,7 @@
       <c r="C31" s="4">
         <v>30</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="12" t="s">
         <v>96</v>
       </c>
       <c r="E31" s="11"/>
@@ -1477,7 +1467,7 @@
       <c r="C32" s="4">
         <v>31</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="12" t="s">
         <v>97</v>
       </c>
       <c r="E32" s="11"/>
@@ -1492,7 +1482,7 @@
       <c r="C33" s="4">
         <v>32</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="12" t="s">
         <v>98</v>
       </c>
       <c r="E33" s="11"/>
@@ -1507,7 +1497,7 @@
       <c r="C34" s="4">
         <v>33</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="12" t="s">
         <v>99</v>
       </c>
       <c r="E34" s="11"/>
@@ -1522,7 +1512,7 @@
       <c r="C35" s="4">
         <v>34</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="12" t="s">
         <v>100</v>
       </c>
       <c r="E35" s="11"/>
@@ -1537,7 +1527,7 @@
       <c r="C36" s="4">
         <v>35</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="12" t="s">
         <v>101</v>
       </c>
       <c r="E36" s="11"/>
@@ -1552,7 +1542,7 @@
       <c r="C37" s="4">
         <v>36</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="12" t="s">
         <v>85</v>
       </c>
       <c r="E37" s="11"/>
@@ -1567,7 +1557,7 @@
       <c r="C38" s="4">
         <v>37</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="12" t="s">
         <v>86</v>
       </c>
       <c r="E38" s="11"/>
@@ -1582,7 +1572,7 @@
       <c r="C39" s="4">
         <v>38</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="12" t="s">
         <v>102</v>
       </c>
       <c r="E39" s="11"/>
@@ -1597,7 +1587,7 @@
       <c r="C40" s="4">
         <v>39</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="12" t="s">
         <v>103</v>
       </c>
       <c r="E40" s="11"/>
@@ -1612,7 +1602,7 @@
       <c r="C41" s="4">
         <v>40</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="12" t="s">
         <v>104</v>
       </c>
       <c r="E41" s="11"/>
@@ -1627,7 +1617,7 @@
       <c r="C42" s="4">
         <v>1</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="12" t="s">
         <v>105</v>
       </c>
       <c r="E42" s="11"/>
@@ -1642,7 +1632,7 @@
       <c r="C43" s="4">
         <v>2</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="12" t="s">
         <v>106</v>
       </c>
       <c r="E43" s="11"/>
@@ -1657,7 +1647,7 @@
       <c r="C44" s="4">
         <v>3</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="12" t="s">
         <v>107</v>
       </c>
       <c r="E44" s="11"/>
@@ -1672,7 +1662,7 @@
       <c r="C45" s="4">
         <v>4</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="12" t="s">
         <v>108</v>
       </c>
       <c r="E45" s="11"/>
@@ -3195,7 +3185,7 @@
       <c r="C162" s="4">
         <v>41</v>
       </c>
-      <c r="D162" s="13" t="s">
+      <c r="D162" s="12" t="s">
         <v>105</v>
       </c>
       <c r="E162" s="11"/>
@@ -3210,7 +3200,7 @@
       <c r="C163" s="4">
         <v>42</v>
       </c>
-      <c r="D163" s="13" t="s">
+      <c r="D163" s="12" t="s">
         <v>106</v>
       </c>
       <c r="E163" s="11"/>
@@ -3225,7 +3215,7 @@
       <c r="C164" s="4">
         <v>43</v>
       </c>
-      <c r="D164" s="13" t="s">
+      <c r="D164" s="12" t="s">
         <v>107</v>
       </c>
       <c r="E164" s="11"/>
@@ -3240,11 +3230,11 @@
       <c r="C165" s="4">
         <v>44</v>
       </c>
-      <c r="D165" s="13" t="s">
+      <c r="D165" s="12" t="s">
         <v>108</v>
       </c>
       <c r="E165" s="11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
@@ -4831,7 +4821,7 @@
       <c r="D281" s="5"/>
       <c r="E281" s="11"/>
     </row>
-    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>43</v>
       </c>
@@ -4844,7 +4834,7 @@
       <c r="D282" s="5"/>
       <c r="E282" s="11"/>
     </row>
-    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>43</v>
       </c>
@@ -4857,7 +4847,7 @@
       <c r="D283" s="5"/>
       <c r="E283" s="11"/>
     </row>
-    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>43</v>
       </c>
@@ -4870,7 +4860,7 @@
       <c r="D284" s="5"/>
       <c r="E284" s="11"/>
     </row>
-    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>43</v>
       </c>
@@ -4883,7 +4873,7 @@
       <c r="D285" s="5"/>
       <c r="E285" s="11"/>
     </row>
-    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
         <v>43</v>
       </c>
@@ -4896,7 +4886,7 @@
       <c r="D286" s="5"/>
       <c r="E286" s="11"/>
     </row>
-    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
         <v>43</v>
       </c>
@@ -4909,7 +4899,7 @@
       <c r="D287" s="5"/>
       <c r="E287" s="11"/>
     </row>
-    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>43</v>
       </c>
@@ -4922,7 +4912,7 @@
       <c r="D288" s="5"/>
       <c r="E288" s="11"/>
     </row>
-    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
         <v>43</v>
       </c>
@@ -4935,7 +4925,7 @@
       <c r="D289" s="5"/>
       <c r="E289" s="11"/>
     </row>
-    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>43</v>
       </c>
@@ -4948,7 +4938,7 @@
       <c r="D290" s="5"/>
       <c r="E290" s="11"/>
     </row>
-    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>43</v>
       </c>
@@ -4961,7 +4951,7 @@
       <c r="D291" s="5"/>
       <c r="E291" s="11"/>
     </row>
-    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>43</v>
       </c>
@@ -4974,7 +4964,7 @@
       <c r="D292" s="5"/>
       <c r="E292" s="11"/>
     </row>
-    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>43</v>
       </c>
@@ -4987,7 +4977,7 @@
       <c r="D293" s="5"/>
       <c r="E293" s="11"/>
     </row>
-    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>43</v>
       </c>
@@ -5000,7 +4990,7 @@
       <c r="D294" s="5"/>
       <c r="E294" s="11"/>
     </row>
-    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>43</v>
       </c>
@@ -5013,7 +5003,7 @@
       <c r="D295" s="5"/>
       <c r="E295" s="11"/>
     </row>
-    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>43</v>
       </c>
@@ -5026,7 +5016,7 @@
       <c r="D296" s="5"/>
       <c r="E296" s="11"/>
     </row>
-    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>43</v>
       </c>
@@ -5039,7 +5029,7 @@
       <c r="D297" s="5"/>
       <c r="E297" s="11"/>
     </row>
-    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>43</v>
       </c>
@@ -5052,7 +5042,7 @@
       <c r="D298" s="5"/>
       <c r="E298" s="11"/>
     </row>
-    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>43</v>
       </c>
@@ -5065,7 +5055,7 @@
       <c r="D299" s="5"/>
       <c r="E299" s="11"/>
     </row>
-    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
         <v>43</v>
       </c>
@@ -5078,7 +5068,7 @@
       <c r="D300" s="5"/>
       <c r="E300" s="11"/>
     </row>
-    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
         <v>43</v>
       </c>
@@ -5091,7 +5081,7 @@
       <c r="D301" s="5"/>
       <c r="E301" s="11"/>
     </row>
-    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
         <v>43</v>
       </c>
@@ -5104,7 +5094,7 @@
       <c r="D302" s="5"/>
       <c r="E302" s="11"/>
     </row>
-    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
         <v>43</v>
       </c>
@@ -5117,7 +5107,7 @@
       <c r="D303" s="5"/>
       <c r="E303" s="11"/>
     </row>
-    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>43</v>
       </c>
@@ -5130,7 +5120,7 @@
       <c r="D304" s="5"/>
       <c r="E304" s="11"/>
     </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>43</v>
       </c>
@@ -5143,7 +5133,7 @@
       <c r="D305" s="5"/>
       <c r="E305" s="11"/>
     </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>43</v>
       </c>
@@ -5156,7 +5146,7 @@
       <c r="D306" s="5"/>
       <c r="E306" s="11"/>
     </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>43</v>
       </c>
@@ -5169,7 +5159,7 @@
       <c r="D307" s="5"/>
       <c r="E307" s="11"/>
     </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>43</v>
       </c>
@@ -5182,7 +5172,7 @@
       <c r="D308" s="5"/>
       <c r="E308" s="11"/>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
         <v>43</v>
       </c>
@@ -5195,7 +5185,7 @@
       <c r="D309" s="5"/>
       <c r="E309" s="11"/>
     </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
         <v>43</v>
       </c>
@@ -5208,7 +5198,7 @@
       <c r="D310" s="5"/>
       <c r="E310" s="11"/>
     </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
         <v>43</v>
       </c>
@@ -5221,7 +5211,7 @@
       <c r="D311" s="5"/>
       <c r="E311" s="11"/>
     </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
         <v>43</v>
       </c>
@@ -5234,7 +5224,7 @@
       <c r="D312" s="5"/>
       <c r="E312" s="11"/>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
         <v>43</v>
       </c>
@@ -5247,7 +5237,7 @@
       <c r="D313" s="5"/>
       <c r="E313" s="11"/>
     </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
         <v>43</v>
       </c>
@@ -5260,7 +5250,7 @@
       <c r="D314" s="5"/>
       <c r="E314" s="11"/>
     </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
         <v>43</v>
       </c>
@@ -5273,7 +5263,7 @@
       <c r="D315" s="5"/>
       <c r="E315" s="11"/>
     </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
         <v>43</v>
       </c>
@@ -5284,13 +5274,13 @@
         <v>35</v>
       </c>
       <c r="D316" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E316" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
         <v>43</v>
       </c>
@@ -5303,7 +5293,7 @@
       <c r="D317" s="5"/>
       <c r="E317" s="11"/>
     </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
         <v>43</v>
       </c>
@@ -5314,13 +5304,13 @@
         <v>37</v>
       </c>
       <c r="D318" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E318" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
         <v>43</v>
       </c>
@@ -5331,13 +5321,13 @@
         <v>38</v>
       </c>
       <c r="D319" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E319" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
         <v>43</v>
       </c>
@@ -5348,11 +5338,11 @@
         <v>39</v>
       </c>
       <c r="D320" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E320" s="11"/>
     </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
         <v>43</v>
       </c>
@@ -5363,7 +5353,7 @@
         <v>40</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E321" s="11"/>
     </row>
@@ -6816,10 +6806,10 @@
         <v>1</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E432" s="11" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
@@ -6846,7 +6836,7 @@
         <v>3</v>
       </c>
       <c r="D434" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E434" s="11"/>
     </row>
@@ -8631,7 +8621,7 @@
       <c r="D571" s="5"/>
       <c r="E571" s="11"/>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="4" t="s">
         <v>45</v>
       </c>
@@ -8644,7 +8634,7 @@
       <c r="D572" s="5"/>
       <c r="E572" s="11"/>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="4" t="s">
         <v>45</v>
       </c>
@@ -8657,7 +8647,7 @@
       <c r="D573" s="5"/>
       <c r="E573" s="11"/>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="4" t="s">
         <v>45</v>
       </c>
@@ -8670,7 +8660,7 @@
       <c r="D574" s="5"/>
       <c r="E574" s="11"/>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="4" t="s">
         <v>45</v>
       </c>
@@ -8683,7 +8673,7 @@
       <c r="D575" s="5"/>
       <c r="E575" s="11"/>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="4" t="s">
         <v>45</v>
       </c>
@@ -8696,7 +8686,7 @@
       <c r="D576" s="5"/>
       <c r="E576" s="11"/>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="4" t="s">
         <v>45</v>
       </c>
@@ -8709,7 +8699,7 @@
       <c r="D577" s="5"/>
       <c r="E577" s="11"/>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="4" t="s">
         <v>45</v>
       </c>
@@ -8722,7 +8712,7 @@
       <c r="D578" s="5"/>
       <c r="E578" s="11"/>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="4" t="s">
         <v>45</v>
       </c>
@@ -8735,7 +8725,7 @@
       <c r="D579" s="5"/>
       <c r="E579" s="11"/>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="4" t="s">
         <v>45</v>
       </c>
@@ -8748,7 +8738,7 @@
       <c r="D580" s="5"/>
       <c r="E580" s="11"/>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="4" t="s">
         <v>45</v>
       </c>
@@ -8761,7 +8751,7 @@
       <c r="D581" s="5"/>
       <c r="E581" s="11"/>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="4" t="s">
         <v>45</v>
       </c>
@@ -8774,7 +8764,7 @@
       <c r="D582" s="5"/>
       <c r="E582" s="11"/>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="4" t="s">
         <v>45</v>
       </c>
@@ -8787,7 +8777,7 @@
       <c r="D583" s="5"/>
       <c r="E583" s="11"/>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="4" t="s">
         <v>45</v>
       </c>
@@ -8800,7 +8790,7 @@
       <c r="D584" s="5"/>
       <c r="E584" s="11"/>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="4" t="s">
         <v>45</v>
       </c>
@@ -8813,7 +8803,7 @@
       <c r="D585" s="5"/>
       <c r="E585" s="11"/>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="4" t="s">
         <v>45</v>
       </c>
@@ -8826,7 +8816,7 @@
       <c r="D586" s="5"/>
       <c r="E586" s="11"/>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="4" t="s">
         <v>45</v>
       </c>
@@ -8839,7 +8829,7 @@
       <c r="D587" s="5"/>
       <c r="E587" s="11"/>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="4" t="s">
         <v>45</v>
       </c>
@@ -8852,7 +8842,7 @@
       <c r="D588" s="5"/>
       <c r="E588" s="11"/>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="4" t="s">
         <v>45</v>
       </c>
@@ -8865,7 +8855,7 @@
       <c r="D589" s="5"/>
       <c r="E589" s="11"/>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="4" t="s">
         <v>45</v>
       </c>
@@ -8878,7 +8868,7 @@
       <c r="D590" s="5"/>
       <c r="E590" s="11"/>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="4" t="s">
         <v>45</v>
       </c>
@@ -8891,7 +8881,7 @@
       <c r="D591" s="5"/>
       <c r="E591" s="11"/>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="4" t="s">
         <v>45</v>
       </c>
@@ -8904,7 +8894,7 @@
       <c r="D592" s="5"/>
       <c r="E592" s="11"/>
     </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="4" t="s">
         <v>45</v>
       </c>
@@ -8917,7 +8907,7 @@
       <c r="D593" s="5"/>
       <c r="E593" s="11"/>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="4" t="s">
         <v>45</v>
       </c>
@@ -8930,7 +8920,7 @@
       <c r="D594" s="5"/>
       <c r="E594" s="11"/>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="4" t="s">
         <v>45</v>
       </c>
@@ -8943,7 +8933,7 @@
       <c r="D595" s="5"/>
       <c r="E595" s="11"/>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="4" t="s">
         <v>45</v>
       </c>
@@ -8956,7 +8946,7 @@
       <c r="D596" s="5"/>
       <c r="E596" s="11"/>
     </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="4" t="s">
         <v>45</v>
       </c>
@@ -8969,7 +8959,7 @@
       <c r="D597" s="5"/>
       <c r="E597" s="11"/>
     </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="4" t="s">
         <v>45</v>
       </c>
@@ -8982,7 +8972,7 @@
       <c r="D598" s="5"/>
       <c r="E598" s="11"/>
     </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="4" t="s">
         <v>45</v>
       </c>
@@ -8996,10 +8986,10 @@
         <v>15</v>
       </c>
       <c r="E599" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="600" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="4" t="s">
         <v>45</v>
       </c>
@@ -9012,7 +9002,7 @@
       <c r="D600" s="5"/>
       <c r="E600" s="11"/>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="4" t="s">
         <v>45</v>
       </c>
@@ -10647,7 +10637,7 @@
       <c r="C726" s="4">
         <v>45</v>
       </c>
-      <c r="D726" s="13" t="s">
+      <c r="D726" s="12" t="s">
         <v>109</v>
       </c>
     </row>
@@ -10661,7 +10651,7 @@
       <c r="C727" s="4">
         <v>46</v>
       </c>
-      <c r="D727" s="13" t="s">
+      <c r="D727" s="12" t="s">
         <v>110</v>
       </c>
     </row>
@@ -10675,11 +10665,11 @@
       <c r="C728" s="4">
         <v>47</v>
       </c>
-      <c r="D728" s="13" t="s">
+      <c r="D728" s="12" t="s">
         <v>111</v>
       </c>
       <c r="E728" s="11" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A01D535-0644-482B-8A88-E026E7ABCF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB593163-9BA6-41A7-8C69-35E0F112DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="128">
   <si>
     <t>Категорија</t>
   </si>
@@ -475,6 +475,15 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbx9uucFv8WkyoXSXCYVboZeBERSmR6otJOkngW4jy-GMBQiRTeaHCNZ0eLUo9R1Flk/exec</t>
+  </si>
+  <si>
+    <t>Множење децимални броеви со една децимала</t>
+  </si>
+  <si>
+    <t>Множење децимални броеви со една децимала - вежби</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbywkU9-7tYeBnYHFXrIYAKB-FnViqXMHO18edK6bmAQUMa54F4T2tw9gWglhrZXQtcXxw/exec</t>
   </si>
 </sst>
 </file>
@@ -609,7 +618,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -645,6 +654,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -667,8 +677,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E728">
-  <autoFilter ref="A1:E728" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E730">
+  <autoFilter ref="A1:E730" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
         <filter val="Алгебра"/>
@@ -676,7 +686,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="9"/>
+        <filter val="8"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -979,7 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E728"/>
+  <dimension ref="A1:E730"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -4301,7 +4311,7 @@
       <c r="D241" s="5"/>
       <c r="E241" s="11"/>
     </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
         <v>43</v>
       </c>
@@ -4314,7 +4324,7 @@
       <c r="D242" s="5"/>
       <c r="E242" s="11"/>
     </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
         <v>43</v>
       </c>
@@ -4327,7 +4337,7 @@
       <c r="D243" s="5"/>
       <c r="E243" s="11"/>
     </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
         <v>43</v>
       </c>
@@ -4337,10 +4347,14 @@
       <c r="C244" s="4">
         <v>3</v>
       </c>
-      <c r="D244" s="5"/>
-      <c r="E244" s="11"/>
-    </row>
-    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D244" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E244" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
         <v>43</v>
       </c>
@@ -4353,7 +4367,7 @@
       <c r="D245" s="5"/>
       <c r="E245" s="11"/>
     </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
         <v>43</v>
       </c>
@@ -4366,7 +4380,7 @@
       <c r="D246" s="5"/>
       <c r="E246" s="11"/>
     </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
         <v>43</v>
       </c>
@@ -4379,7 +4393,7 @@
       <c r="D247" s="5"/>
       <c r="E247" s="11"/>
     </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
         <v>43</v>
       </c>
@@ -4392,7 +4406,7 @@
       <c r="D248" s="5"/>
       <c r="E248" s="11"/>
     </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
         <v>43</v>
       </c>
@@ -4405,7 +4419,7 @@
       <c r="D249" s="5"/>
       <c r="E249" s="11"/>
     </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
         <v>43</v>
       </c>
@@ -4418,7 +4432,7 @@
       <c r="D250" s="5"/>
       <c r="E250" s="11"/>
     </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
         <v>43</v>
       </c>
@@ -4431,7 +4445,7 @@
       <c r="D251" s="5"/>
       <c r="E251" s="11"/>
     </row>
-    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
         <v>43</v>
       </c>
@@ -4444,7 +4458,7 @@
       <c r="D252" s="5"/>
       <c r="E252" s="11"/>
     </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
         <v>43</v>
       </c>
@@ -4457,7 +4471,7 @@
       <c r="D253" s="5"/>
       <c r="E253" s="11"/>
     </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>43</v>
       </c>
@@ -4470,7 +4484,7 @@
       <c r="D254" s="5"/>
       <c r="E254" s="11"/>
     </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>43</v>
       </c>
@@ -4483,7 +4497,7 @@
       <c r="D255" s="5"/>
       <c r="E255" s="11"/>
     </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>43</v>
       </c>
@@ -4496,7 +4510,7 @@
       <c r="D256" s="5"/>
       <c r="E256" s="11"/>
     </row>
-    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
         <v>43</v>
       </c>
@@ -4509,7 +4523,7 @@
       <c r="D257" s="5"/>
       <c r="E257" s="11"/>
     </row>
-    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
         <v>43</v>
       </c>
@@ -4522,7 +4536,7 @@
       <c r="D258" s="5"/>
       <c r="E258" s="11"/>
     </row>
-    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
         <v>43</v>
       </c>
@@ -4535,7 +4549,7 @@
       <c r="D259" s="5"/>
       <c r="E259" s="11"/>
     </row>
-    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
         <v>43</v>
       </c>
@@ -4548,7 +4562,7 @@
       <c r="D260" s="5"/>
       <c r="E260" s="11"/>
     </row>
-    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
         <v>43</v>
       </c>
@@ -4561,7 +4575,7 @@
       <c r="D261" s="5"/>
       <c r="E261" s="11"/>
     </row>
-    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
         <v>43</v>
       </c>
@@ -4574,7 +4588,7 @@
       <c r="D262" s="5"/>
       <c r="E262" s="11"/>
     </row>
-    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
         <v>43</v>
       </c>
@@ -4587,7 +4601,7 @@
       <c r="D263" s="5"/>
       <c r="E263" s="11"/>
     </row>
-    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
         <v>43</v>
       </c>
@@ -4600,7 +4614,7 @@
       <c r="D264" s="5"/>
       <c r="E264" s="11"/>
     </row>
-    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
         <v>43</v>
       </c>
@@ -4613,7 +4627,7 @@
       <c r="D265" s="5"/>
       <c r="E265" s="11"/>
     </row>
-    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
         <v>43</v>
       </c>
@@ -4626,7 +4640,7 @@
       <c r="D266" s="5"/>
       <c r="E266" s="11"/>
     </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
         <v>43</v>
       </c>
@@ -4639,7 +4653,7 @@
       <c r="D267" s="5"/>
       <c r="E267" s="11"/>
     </row>
-    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
         <v>43</v>
       </c>
@@ -4652,7 +4666,7 @@
       <c r="D268" s="5"/>
       <c r="E268" s="11"/>
     </row>
-    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
         <v>43</v>
       </c>
@@ -4665,7 +4679,7 @@
       <c r="D269" s="5"/>
       <c r="E269" s="11"/>
     </row>
-    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
         <v>43</v>
       </c>
@@ -4678,7 +4692,7 @@
       <c r="D270" s="5"/>
       <c r="E270" s="11"/>
     </row>
-    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
         <v>43</v>
       </c>
@@ -4691,7 +4705,7 @@
       <c r="D271" s="5"/>
       <c r="E271" s="11"/>
     </row>
-    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
         <v>43</v>
       </c>
@@ -4704,7 +4718,7 @@
       <c r="D272" s="5"/>
       <c r="E272" s="11"/>
     </row>
-    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" s="4" t="s">
         <v>43</v>
       </c>
@@ -4717,7 +4731,7 @@
       <c r="D273" s="5"/>
       <c r="E273" s="11"/>
     </row>
-    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" s="4" t="s">
         <v>43</v>
       </c>
@@ -4730,7 +4744,7 @@
       <c r="D274" s="5"/>
       <c r="E274" s="11"/>
     </row>
-    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" s="4" t="s">
         <v>43</v>
       </c>
@@ -4743,7 +4757,7 @@
       <c r="D275" s="5"/>
       <c r="E275" s="11"/>
     </row>
-    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
         <v>43</v>
       </c>
@@ -4756,7 +4770,7 @@
       <c r="D276" s="5"/>
       <c r="E276" s="11"/>
     </row>
-    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
         <v>43</v>
       </c>
@@ -4769,7 +4783,7 @@
       <c r="D277" s="5"/>
       <c r="E277" s="11"/>
     </row>
-    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
         <v>43</v>
       </c>
@@ -4782,7 +4796,7 @@
       <c r="D278" s="5"/>
       <c r="E278" s="11"/>
     </row>
-    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
         <v>43</v>
       </c>
@@ -4795,7 +4809,7 @@
       <c r="D279" s="5"/>
       <c r="E279" s="11"/>
     </row>
-    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
         <v>43</v>
       </c>
@@ -4808,7 +4822,7 @@
       <c r="D280" s="5"/>
       <c r="E280" s="11"/>
     </row>
-    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
         <v>43</v>
       </c>
@@ -4821,7 +4835,7 @@
       <c r="D281" s="5"/>
       <c r="E281" s="11"/>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>43</v>
       </c>
@@ -4834,7 +4848,7 @@
       <c r="D282" s="5"/>
       <c r="E282" s="11"/>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>43</v>
       </c>
@@ -4847,7 +4861,7 @@
       <c r="D283" s="5"/>
       <c r="E283" s="11"/>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>43</v>
       </c>
@@ -4860,7 +4874,7 @@
       <c r="D284" s="5"/>
       <c r="E284" s="11"/>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>43</v>
       </c>
@@ -4873,7 +4887,7 @@
       <c r="D285" s="5"/>
       <c r="E285" s="11"/>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
         <v>43</v>
       </c>
@@ -4886,7 +4900,7 @@
       <c r="D286" s="5"/>
       <c r="E286" s="11"/>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
         <v>43</v>
       </c>
@@ -4899,7 +4913,7 @@
       <c r="D287" s="5"/>
       <c r="E287" s="11"/>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>43</v>
       </c>
@@ -4912,7 +4926,7 @@
       <c r="D288" s="5"/>
       <c r="E288" s="11"/>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
         <v>43</v>
       </c>
@@ -4925,7 +4939,7 @@
       <c r="D289" s="5"/>
       <c r="E289" s="11"/>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>43</v>
       </c>
@@ -4938,7 +4952,7 @@
       <c r="D290" s="5"/>
       <c r="E290" s="11"/>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>43</v>
       </c>
@@ -4951,7 +4965,7 @@
       <c r="D291" s="5"/>
       <c r="E291" s="11"/>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>43</v>
       </c>
@@ -4964,7 +4978,7 @@
       <c r="D292" s="5"/>
       <c r="E292" s="11"/>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>43</v>
       </c>
@@ -4977,7 +4991,7 @@
       <c r="D293" s="5"/>
       <c r="E293" s="11"/>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>43</v>
       </c>
@@ -4990,7 +5004,7 @@
       <c r="D294" s="5"/>
       <c r="E294" s="11"/>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>43</v>
       </c>
@@ -5003,7 +5017,7 @@
       <c r="D295" s="5"/>
       <c r="E295" s="11"/>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>43</v>
       </c>
@@ -5016,7 +5030,7 @@
       <c r="D296" s="5"/>
       <c r="E296" s="11"/>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>43</v>
       </c>
@@ -5029,7 +5043,7 @@
       <c r="D297" s="5"/>
       <c r="E297" s="11"/>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>43</v>
       </c>
@@ -5042,7 +5056,7 @@
       <c r="D298" s="5"/>
       <c r="E298" s="11"/>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>43</v>
       </c>
@@ -5055,7 +5069,7 @@
       <c r="D299" s="5"/>
       <c r="E299" s="11"/>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
         <v>43</v>
       </c>
@@ -5068,7 +5082,7 @@
       <c r="D300" s="5"/>
       <c r="E300" s="11"/>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
         <v>43</v>
       </c>
@@ -5081,7 +5095,7 @@
       <c r="D301" s="5"/>
       <c r="E301" s="11"/>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
         <v>43</v>
       </c>
@@ -5094,7 +5108,7 @@
       <c r="D302" s="5"/>
       <c r="E302" s="11"/>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
         <v>43</v>
       </c>
@@ -5107,7 +5121,7 @@
       <c r="D303" s="5"/>
       <c r="E303" s="11"/>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>43</v>
       </c>
@@ -5120,7 +5134,7 @@
       <c r="D304" s="5"/>
       <c r="E304" s="11"/>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>43</v>
       </c>
@@ -5133,7 +5147,7 @@
       <c r="D305" s="5"/>
       <c r="E305" s="11"/>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>43</v>
       </c>
@@ -5146,7 +5160,7 @@
       <c r="D306" s="5"/>
       <c r="E306" s="11"/>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>43</v>
       </c>
@@ -5159,7 +5173,7 @@
       <c r="D307" s="5"/>
       <c r="E307" s="11"/>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>43</v>
       </c>
@@ -5172,7 +5186,7 @@
       <c r="D308" s="5"/>
       <c r="E308" s="11"/>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
         <v>43</v>
       </c>
@@ -5185,7 +5199,7 @@
       <c r="D309" s="5"/>
       <c r="E309" s="11"/>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
         <v>43</v>
       </c>
@@ -5198,7 +5212,7 @@
       <c r="D310" s="5"/>
       <c r="E310" s="11"/>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
         <v>43</v>
       </c>
@@ -5211,7 +5225,7 @@
       <c r="D311" s="5"/>
       <c r="E311" s="11"/>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
         <v>43</v>
       </c>
@@ -5224,7 +5238,7 @@
       <c r="D312" s="5"/>
       <c r="E312" s="11"/>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
         <v>43</v>
       </c>
@@ -5237,7 +5251,7 @@
       <c r="D313" s="5"/>
       <c r="E313" s="11"/>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
         <v>43</v>
       </c>
@@ -5250,7 +5264,7 @@
       <c r="D314" s="5"/>
       <c r="E314" s="11"/>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
         <v>43</v>
       </c>
@@ -5263,7 +5277,7 @@
       <c r="D315" s="5"/>
       <c r="E315" s="11"/>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
         <v>43</v>
       </c>
@@ -5280,7 +5294,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
         <v>43</v>
       </c>
@@ -5293,7 +5307,7 @@
       <c r="D317" s="5"/>
       <c r="E317" s="11"/>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
         <v>43</v>
       </c>
@@ -5310,7 +5324,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
         <v>43</v>
       </c>
@@ -5327,7 +5341,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
         <v>43</v>
       </c>
@@ -5342,7 +5356,7 @@
       </c>
       <c r="E320" s="11"/>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
         <v>43</v>
       </c>
@@ -10671,6 +10685,24 @@
       <c r="E728" s="11" t="s">
         <v>112</v>
       </c>
+    </row>
+    <row r="729" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C729">
+        <v>48</v>
+      </c>
+      <c r="D729" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E729" s="13"/>
+    </row>
+    <row r="730" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C730">
+        <v>49</v>
+      </c>
+      <c r="D730" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E730" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10685,13 +10717,13 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A728</xm:sqref>
+          <xm:sqref>A2:A730</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B728</xm:sqref>
+          <xm:sqref>B2:B730</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB593163-9BA6-41A7-8C69-35E0F112DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B961F39-7C5D-4106-AEFE-8E7758430690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="128">
   <si>
     <t>Категорија</t>
   </si>
@@ -681,7 +681,7 @@
   <autoFilter ref="A1:E730" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Алгебра"/>
+        <filter val="Геометрија"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
@@ -4311,7 +4311,7 @@
       <c r="D241" s="5"/>
       <c r="E241" s="11"/>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
         <v>43</v>
       </c>
@@ -4324,7 +4324,7 @@
       <c r="D242" s="5"/>
       <c r="E242" s="11"/>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
         <v>43</v>
       </c>
@@ -4337,7 +4337,7 @@
       <c r="D243" s="5"/>
       <c r="E243" s="11"/>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
         <v>43</v>
       </c>
@@ -4347,14 +4347,10 @@
       <c r="C244" s="4">
         <v>3</v>
       </c>
-      <c r="D244" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E244" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D244" s="5"/>
+      <c r="E244" s="11"/>
+    </row>
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
         <v>43</v>
       </c>
@@ -4367,7 +4363,7 @@
       <c r="D245" s="5"/>
       <c r="E245" s="11"/>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
         <v>43</v>
       </c>
@@ -4380,7 +4376,7 @@
       <c r="D246" s="5"/>
       <c r="E246" s="11"/>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
         <v>43</v>
       </c>
@@ -4393,7 +4389,7 @@
       <c r="D247" s="5"/>
       <c r="E247" s="11"/>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
         <v>43</v>
       </c>
@@ -4406,7 +4402,7 @@
       <c r="D248" s="5"/>
       <c r="E248" s="11"/>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
         <v>43</v>
       </c>
@@ -4419,7 +4415,7 @@
       <c r="D249" s="5"/>
       <c r="E249" s="11"/>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
         <v>43</v>
       </c>
@@ -4432,7 +4428,7 @@
       <c r="D250" s="5"/>
       <c r="E250" s="11"/>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
         <v>43</v>
       </c>
@@ -4445,7 +4441,7 @@
       <c r="D251" s="5"/>
       <c r="E251" s="11"/>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
         <v>43</v>
       </c>
@@ -4458,7 +4454,7 @@
       <c r="D252" s="5"/>
       <c r="E252" s="11"/>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
         <v>43</v>
       </c>
@@ -4471,7 +4467,7 @@
       <c r="D253" s="5"/>
       <c r="E253" s="11"/>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>43</v>
       </c>
@@ -4484,7 +4480,7 @@
       <c r="D254" s="5"/>
       <c r="E254" s="11"/>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>43</v>
       </c>
@@ -4497,7 +4493,7 @@
       <c r="D255" s="5"/>
       <c r="E255" s="11"/>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>43</v>
       </c>
@@ -4510,7 +4506,7 @@
       <c r="D256" s="5"/>
       <c r="E256" s="11"/>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
         <v>43</v>
       </c>
@@ -4523,7 +4519,7 @@
       <c r="D257" s="5"/>
       <c r="E257" s="11"/>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
         <v>43</v>
       </c>
@@ -4536,7 +4532,7 @@
       <c r="D258" s="5"/>
       <c r="E258" s="11"/>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
         <v>43</v>
       </c>
@@ -4549,7 +4545,7 @@
       <c r="D259" s="5"/>
       <c r="E259" s="11"/>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
         <v>43</v>
       </c>
@@ -4562,7 +4558,7 @@
       <c r="D260" s="5"/>
       <c r="E260" s="11"/>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
         <v>43</v>
       </c>
@@ -4575,7 +4571,7 @@
       <c r="D261" s="5"/>
       <c r="E261" s="11"/>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
         <v>43</v>
       </c>
@@ -4588,7 +4584,7 @@
       <c r="D262" s="5"/>
       <c r="E262" s="11"/>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
         <v>43</v>
       </c>
@@ -4601,7 +4597,7 @@
       <c r="D263" s="5"/>
       <c r="E263" s="11"/>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
         <v>43</v>
       </c>
@@ -4614,7 +4610,7 @@
       <c r="D264" s="5"/>
       <c r="E264" s="11"/>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
         <v>43</v>
       </c>
@@ -4627,7 +4623,7 @@
       <c r="D265" s="5"/>
       <c r="E265" s="11"/>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
         <v>43</v>
       </c>
@@ -4640,7 +4636,7 @@
       <c r="D266" s="5"/>
       <c r="E266" s="11"/>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
         <v>43</v>
       </c>
@@ -4653,7 +4649,7 @@
       <c r="D267" s="5"/>
       <c r="E267" s="11"/>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
         <v>43</v>
       </c>
@@ -4666,7 +4662,7 @@
       <c r="D268" s="5"/>
       <c r="E268" s="11"/>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
         <v>43</v>
       </c>
@@ -4679,7 +4675,7 @@
       <c r="D269" s="5"/>
       <c r="E269" s="11"/>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
         <v>43</v>
       </c>
@@ -4692,7 +4688,7 @@
       <c r="D270" s="5"/>
       <c r="E270" s="11"/>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
         <v>43</v>
       </c>
@@ -4705,7 +4701,7 @@
       <c r="D271" s="5"/>
       <c r="E271" s="11"/>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
         <v>43</v>
       </c>
@@ -4718,7 +4714,7 @@
       <c r="D272" s="5"/>
       <c r="E272" s="11"/>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4" t="s">
         <v>43</v>
       </c>
@@ -4731,7 +4727,7 @@
       <c r="D273" s="5"/>
       <c r="E273" s="11"/>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4" t="s">
         <v>43</v>
       </c>
@@ -4744,7 +4740,7 @@
       <c r="D274" s="5"/>
       <c r="E274" s="11"/>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="4" t="s">
         <v>43</v>
       </c>
@@ -4757,7 +4753,7 @@
       <c r="D275" s="5"/>
       <c r="E275" s="11"/>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
         <v>43</v>
       </c>
@@ -4770,7 +4766,7 @@
       <c r="D276" s="5"/>
       <c r="E276" s="11"/>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
         <v>43</v>
       </c>
@@ -4783,7 +4779,7 @@
       <c r="D277" s="5"/>
       <c r="E277" s="11"/>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
         <v>43</v>
       </c>
@@ -4796,7 +4792,7 @@
       <c r="D278" s="5"/>
       <c r="E278" s="11"/>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
         <v>43</v>
       </c>
@@ -4809,7 +4805,7 @@
       <c r="D279" s="5"/>
       <c r="E279" s="11"/>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
         <v>43</v>
       </c>
@@ -4822,7 +4818,7 @@
       <c r="D280" s="5"/>
       <c r="E280" s="11"/>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
         <v>43</v>
       </c>
@@ -6809,7 +6805,7 @@
       <c r="D431" s="5"/>
       <c r="E431" s="11"/>
     </row>
-    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
         <v>44</v>
       </c>
@@ -6826,7 +6822,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
         <v>44</v>
       </c>
@@ -6839,7 +6835,7 @@
       <c r="D433" s="5"/>
       <c r="E433" s="11"/>
     </row>
-    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
         <v>44</v>
       </c>
@@ -6852,9 +6848,11 @@
       <c r="D434" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E434" s="11"/>
-    </row>
-    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="E434" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
         <v>44</v>
       </c>
@@ -6867,7 +6865,7 @@
       <c r="D435" s="5"/>
       <c r="E435" s="11"/>
     </row>
-    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
         <v>44</v>
       </c>
@@ -6880,7 +6878,7 @@
       <c r="D436" s="5"/>
       <c r="E436" s="11"/>
     </row>
-    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
         <v>44</v>
       </c>
@@ -6893,7 +6891,7 @@
       <c r="D437" s="5"/>
       <c r="E437" s="11"/>
     </row>
-    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
         <v>44</v>
       </c>
@@ -6906,7 +6904,7 @@
       <c r="D438" s="5"/>
       <c r="E438" s="11"/>
     </row>
-    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
         <v>44</v>
       </c>
@@ -6919,7 +6917,7 @@
       <c r="D439" s="5"/>
       <c r="E439" s="11"/>
     </row>
-    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
         <v>44</v>
       </c>
@@ -6932,7 +6930,7 @@
       <c r="D440" s="5"/>
       <c r="E440" s="11"/>
     </row>
-    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
         <v>44</v>
       </c>
@@ -6945,7 +6943,7 @@
       <c r="D441" s="5"/>
       <c r="E441" s="11"/>
     </row>
-    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
         <v>44</v>
       </c>
@@ -6958,7 +6956,7 @@
       <c r="D442" s="5"/>
       <c r="E442" s="11"/>
     </row>
-    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
         <v>44</v>
       </c>
@@ -6971,7 +6969,7 @@
       <c r="D443" s="5"/>
       <c r="E443" s="11"/>
     </row>
-    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
         <v>44</v>
       </c>
@@ -6984,7 +6982,7 @@
       <c r="D444" s="5"/>
       <c r="E444" s="11"/>
     </row>
-    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
         <v>44</v>
       </c>
@@ -6997,7 +6995,7 @@
       <c r="D445" s="5"/>
       <c r="E445" s="11"/>
     </row>
-    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
         <v>44</v>
       </c>
@@ -7010,7 +7008,7 @@
       <c r="D446" s="5"/>
       <c r="E446" s="11"/>
     </row>
-    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
         <v>44</v>
       </c>
@@ -7023,7 +7021,7 @@
       <c r="D447" s="5"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
         <v>44</v>
       </c>
@@ -7036,7 +7034,7 @@
       <c r="D448" s="5"/>
       <c r="E448" s="11"/>
     </row>
-    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
         <v>44</v>
       </c>
@@ -7049,7 +7047,7 @@
       <c r="D449" s="5"/>
       <c r="E449" s="11"/>
     </row>
-    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
         <v>44</v>
       </c>
@@ -7062,7 +7060,7 @@
       <c r="D450" s="5"/>
       <c r="E450" s="11"/>
     </row>
-    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
         <v>44</v>
       </c>
@@ -7075,7 +7073,7 @@
       <c r="D451" s="5"/>
       <c r="E451" s="11"/>
     </row>
-    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
         <v>44</v>
       </c>
@@ -7088,7 +7086,7 @@
       <c r="D452" s="5"/>
       <c r="E452" s="11"/>
     </row>
-    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
         <v>44</v>
       </c>
@@ -7101,7 +7099,7 @@
       <c r="D453" s="5"/>
       <c r="E453" s="11"/>
     </row>
-    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
         <v>44</v>
       </c>
@@ -7114,7 +7112,7 @@
       <c r="D454" s="5"/>
       <c r="E454" s="11"/>
     </row>
-    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
         <v>44</v>
       </c>
@@ -7127,7 +7125,7 @@
       <c r="D455" s="5"/>
       <c r="E455" s="11"/>
     </row>
-    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
         <v>44</v>
       </c>
@@ -7140,7 +7138,7 @@
       <c r="D456" s="5"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
         <v>44</v>
       </c>
@@ -7153,7 +7151,7 @@
       <c r="D457" s="5"/>
       <c r="E457" s="11"/>
     </row>
-    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
         <v>44</v>
       </c>
@@ -7166,7 +7164,7 @@
       <c r="D458" s="5"/>
       <c r="E458" s="11"/>
     </row>
-    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
         <v>44</v>
       </c>
@@ -7179,7 +7177,7 @@
       <c r="D459" s="5"/>
       <c r="E459" s="11"/>
     </row>
-    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
         <v>44</v>
       </c>
@@ -7192,7 +7190,7 @@
       <c r="D460" s="5"/>
       <c r="E460" s="11"/>
     </row>
-    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
         <v>44</v>
       </c>
@@ -7205,7 +7203,7 @@
       <c r="D461" s="5"/>
       <c r="E461" s="11"/>
     </row>
-    <row r="462" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
         <v>44</v>
       </c>
@@ -7218,7 +7216,7 @@
       <c r="D462" s="5"/>
       <c r="E462" s="11"/>
     </row>
-    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
         <v>44</v>
       </c>
@@ -7231,7 +7229,7 @@
       <c r="D463" s="5"/>
       <c r="E463" s="11"/>
     </row>
-    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
         <v>44</v>
       </c>
@@ -7244,7 +7242,7 @@
       <c r="D464" s="5"/>
       <c r="E464" s="11"/>
     </row>
-    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
         <v>44</v>
       </c>
@@ -7257,7 +7255,7 @@
       <c r="D465" s="5"/>
       <c r="E465" s="11"/>
     </row>
-    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
         <v>44</v>
       </c>
@@ -7270,7 +7268,7 @@
       <c r="D466" s="5"/>
       <c r="E466" s="11"/>
     </row>
-    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
         <v>44</v>
       </c>
@@ -7283,7 +7281,7 @@
       <c r="D467" s="5"/>
       <c r="E467" s="11"/>
     </row>
-    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
         <v>44</v>
       </c>
@@ -7296,7 +7294,7 @@
       <c r="D468" s="5"/>
       <c r="E468" s="11"/>
     </row>
-    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
         <v>44</v>
       </c>
@@ -7309,7 +7307,7 @@
       <c r="D469" s="5"/>
       <c r="E469" s="11"/>
     </row>
-    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
         <v>44</v>
       </c>
@@ -7322,7 +7320,7 @@
       <c r="D470" s="5"/>
       <c r="E470" s="11"/>
     </row>
-    <row r="471" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
         <v>44</v>
       </c>
@@ -7335,7 +7333,7 @@
       <c r="D471" s="5"/>
       <c r="E471" s="11"/>
     </row>
-    <row r="472" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
         <v>44</v>
       </c>
@@ -7348,7 +7346,7 @@
       <c r="D472" s="5"/>
       <c r="E472" s="11"/>
     </row>
-    <row r="473" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
         <v>44</v>
       </c>
@@ -7361,7 +7359,7 @@
       <c r="D473" s="5"/>
       <c r="E473" s="11"/>
     </row>
-    <row r="474" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
         <v>44</v>
       </c>
@@ -7374,7 +7372,7 @@
       <c r="D474" s="5"/>
       <c r="E474" s="11"/>
     </row>
-    <row r="475" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
         <v>44</v>
       </c>
@@ -7387,7 +7385,7 @@
       <c r="D475" s="5"/>
       <c r="E475" s="11"/>
     </row>
-    <row r="476" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
         <v>44</v>
       </c>
@@ -7400,7 +7398,7 @@
       <c r="D476" s="5"/>
       <c r="E476" s="11"/>
     </row>
-    <row r="477" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
         <v>44</v>
       </c>
@@ -7413,7 +7411,7 @@
       <c r="D477" s="5"/>
       <c r="E477" s="11"/>
     </row>
-    <row r="478" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
         <v>44</v>
       </c>
@@ -7426,7 +7424,7 @@
       <c r="D478" s="5"/>
       <c r="E478" s="11"/>
     </row>
-    <row r="479" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
         <v>44</v>
       </c>
@@ -7439,7 +7437,7 @@
       <c r="D479" s="5"/>
       <c r="E479" s="11"/>
     </row>
-    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
         <v>44</v>
       </c>
@@ -7452,7 +7450,7 @@
       <c r="D480" s="5"/>
       <c r="E480" s="11"/>
     </row>
-    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
         <v>44</v>
       </c>
@@ -7465,7 +7463,7 @@
       <c r="D481" s="5"/>
       <c r="E481" s="11"/>
     </row>
-    <row r="482" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
         <v>44</v>
       </c>
@@ -7478,7 +7476,7 @@
       <c r="D482" s="5"/>
       <c r="E482" s="11"/>
     </row>
-    <row r="483" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
         <v>44</v>
       </c>
@@ -7491,7 +7489,7 @@
       <c r="D483" s="5"/>
       <c r="E483" s="11"/>
     </row>
-    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
         <v>44</v>
       </c>
@@ -7504,7 +7502,7 @@
       <c r="D484" s="5"/>
       <c r="E484" s="11"/>
     </row>
-    <row r="485" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
         <v>44</v>
       </c>
@@ -7517,7 +7515,7 @@
       <c r="D485" s="5"/>
       <c r="E485" s="11"/>
     </row>
-    <row r="486" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
         <v>44</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B961F39-7C5D-4106-AEFE-8E7758430690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E32F11-46C5-421D-AA74-7D3ACEAEDAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="129">
   <si>
     <t>Категорија</t>
   </si>
@@ -484,6 +484,9 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbywkU9-7tYeBnYHFXrIYAKB-FnViqXMHO18edK6bmAQUMa54F4T2tw9gWglhrZXQtcXxw/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbwGk3j-Jqxl77X6Jsz-T3_CvTZIqIwdFksDTHqy_UUCpGY3ANZNyU1py92Qyqxzp_B03Q/exec</t>
   </si>
 </sst>
 </file>
@@ -677,16 +680,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E730">
-  <autoFilter ref="A1:E730" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E733">
+  <autoFilter ref="A1:E733" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Геометрија"/>
+        <filter val="Алгебра"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="8"/>
+        <filter val="6"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -989,7 +992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E730"/>
+  <dimension ref="A1:E733"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -998,7 +1001,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1015,7 +1018,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>43</v>
       </c>
@@ -1032,7 +1035,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>43</v>
       </c>
@@ -1047,7 +1050,7 @@
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
@@ -1062,7 +1065,7 @@
       </c>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>43</v>
       </c>
@@ -1077,7 +1080,7 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>43</v>
       </c>
@@ -1092,7 +1095,7 @@
       </c>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>43</v>
       </c>
@@ -1107,7 +1110,7 @@
       </c>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>43</v>
       </c>
@@ -1122,7 +1125,7 @@
       </c>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>43</v>
       </c>
@@ -1137,7 +1140,7 @@
       </c>
       <c r="E9" s="11"/>
     </row>
-    <row r="10" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>43</v>
       </c>
@@ -1152,7 +1155,7 @@
       </c>
       <c r="E10" s="11"/>
     </row>
-    <row r="11" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>43</v>
       </c>
@@ -1167,7 +1170,7 @@
       </c>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>43</v>
       </c>
@@ -1182,7 +1185,7 @@
       </c>
       <c r="E12" s="11"/>
     </row>
-    <row r="13" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>43</v>
       </c>
@@ -1197,7 +1200,7 @@
       </c>
       <c r="E13" s="11"/>
     </row>
-    <row r="14" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
@@ -1212,7 +1215,7 @@
       </c>
       <c r="E14" s="11"/>
     </row>
-    <row r="15" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>43</v>
       </c>
@@ -1227,7 +1230,7 @@
       </c>
       <c r="E15" s="11"/>
     </row>
-    <row r="16" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>43</v>
       </c>
@@ -1242,7 +1245,7 @@
       </c>
       <c r="E16" s="11"/>
     </row>
-    <row r="17" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>43</v>
       </c>
@@ -1257,7 +1260,7 @@
       </c>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>43</v>
       </c>
@@ -1272,7 +1275,7 @@
       </c>
       <c r="E18" s="11"/>
     </row>
-    <row r="19" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>43</v>
       </c>
@@ -1287,7 +1290,7 @@
       </c>
       <c r="E19" s="11"/>
     </row>
-    <row r="20" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
@@ -1302,7 +1305,7 @@
       </c>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>43</v>
       </c>
@@ -1317,7 +1320,7 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>43</v>
       </c>
@@ -1332,7 +1335,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>43</v>
       </c>
@@ -1347,7 +1350,7 @@
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>43</v>
       </c>
@@ -1362,7 +1365,7 @@
       </c>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>43</v>
       </c>
@@ -1377,7 +1380,7 @@
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>43</v>
       </c>
@@ -1392,7 +1395,7 @@
       </c>
       <c r="E26" s="11"/>
     </row>
-    <row r="27" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>43</v>
       </c>
@@ -1407,7 +1410,7 @@
       </c>
       <c r="E27" s="11"/>
     </row>
-    <row r="28" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>43</v>
       </c>
@@ -1422,7 +1425,7 @@
       </c>
       <c r="E28" s="11"/>
     </row>
-    <row r="29" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>43</v>
       </c>
@@ -1437,7 +1440,7 @@
       </c>
       <c r="E29" s="11"/>
     </row>
-    <row r="30" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>43</v>
       </c>
@@ -1452,7 +1455,7 @@
       </c>
       <c r="E30" s="11"/>
     </row>
-    <row r="31" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>43</v>
       </c>
@@ -1467,7 +1470,7 @@
       </c>
       <c r="E31" s="11"/>
     </row>
-    <row r="32" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>43</v>
       </c>
@@ -1482,7 +1485,7 @@
       </c>
       <c r="E32" s="11"/>
     </row>
-    <row r="33" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>43</v>
       </c>
@@ -1497,7 +1500,7 @@
       </c>
       <c r="E33" s="11"/>
     </row>
-    <row r="34" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>43</v>
       </c>
@@ -1512,7 +1515,7 @@
       </c>
       <c r="E34" s="11"/>
     </row>
-    <row r="35" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>43</v>
       </c>
@@ -1527,7 +1530,7 @@
       </c>
       <c r="E35" s="11"/>
     </row>
-    <row r="36" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>43</v>
       </c>
@@ -1542,7 +1545,7 @@
       </c>
       <c r="E36" s="11"/>
     </row>
-    <row r="37" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>43</v>
       </c>
@@ -1557,7 +1560,7 @@
       </c>
       <c r="E37" s="11"/>
     </row>
-    <row r="38" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>43</v>
       </c>
@@ -1572,7 +1575,7 @@
       </c>
       <c r="E38" s="11"/>
     </row>
-    <row r="39" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>43</v>
       </c>
@@ -1587,7 +1590,7 @@
       </c>
       <c r="E39" s="11"/>
     </row>
-    <row r="40" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>43</v>
       </c>
@@ -1602,7 +1605,7 @@
       </c>
       <c r="E40" s="11"/>
     </row>
-    <row r="41" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>43</v>
       </c>
@@ -1677,7 +1680,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1690,7 +1693,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1703,7 +1706,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1716,7 +1719,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1729,7 +1732,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -1742,7 +1745,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1755,7 +1758,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1768,7 +1771,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1781,7 +1784,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -1794,7 +1797,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="11"/>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1807,7 +1810,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="11"/>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -1820,7 +1823,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -1833,7 +1836,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -1846,7 +1849,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -1859,7 +1862,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -1872,7 +1875,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -1885,7 +1888,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -1898,7 +1901,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -1911,7 +1914,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -1924,7 +1927,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -1937,7 +1940,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -1950,7 +1953,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -1963,7 +1966,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -1976,7 +1979,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -1989,7 +1992,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2002,7 +2005,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2015,7 +2018,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2028,7 +2031,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2041,7 +2044,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2054,7 +2057,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2067,7 +2070,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2080,7 +2083,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2093,7 +2096,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2106,7 +2109,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2119,7 +2122,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2132,7 +2135,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2145,7 +2148,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2158,7 +2161,7 @@
       <c r="D82" s="5"/>
       <c r="E82" s="11"/>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2171,7 +2174,7 @@
       <c r="D83" s="5"/>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2184,7 +2187,7 @@
       <c r="D84" s="5"/>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2197,7 +2200,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2210,7 +2213,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="11"/>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2223,7 +2226,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="11"/>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2236,7 +2239,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="11"/>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2249,7 +2252,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="11"/>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2262,7 +2265,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="11"/>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2275,7 +2278,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2288,7 +2291,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2301,7 +2304,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2314,7 +2317,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2327,7 +2330,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2340,7 +2343,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2353,7 +2356,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2366,7 +2369,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2379,7 +2382,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2392,7 +2395,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2405,7 +2408,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2418,7 +2421,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2431,7 +2434,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2444,7 +2447,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2457,7 +2460,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2470,7 +2473,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2483,7 +2486,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2496,7 +2499,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2509,7 +2512,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2522,7 +2525,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2535,7 +2538,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2548,7 +2551,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2561,7 +2564,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2574,7 +2577,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2587,7 +2590,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2600,7 +2603,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2613,7 +2616,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2626,7 +2629,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2639,7 +2642,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2652,7 +2655,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>
@@ -2665,7 +2668,7 @@
       <c r="D121" s="5"/>
       <c r="E121" s="11"/>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>5</v>
       </c>
@@ -2678,7 +2681,7 @@
       <c r="D122" s="5"/>
       <c r="E122" s="11"/>
     </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>5</v>
       </c>
@@ -2691,7 +2694,7 @@
       <c r="D123" s="5"/>
       <c r="E123" s="11"/>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>5</v>
       </c>
@@ -2704,7 +2707,7 @@
       <c r="D124" s="5"/>
       <c r="E124" s="11"/>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>5</v>
       </c>
@@ -2717,7 +2720,7 @@
       <c r="D125" s="5"/>
       <c r="E125" s="11"/>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
         <v>5</v>
       </c>
@@ -2730,7 +2733,7 @@
       <c r="D126" s="5"/>
       <c r="E126" s="11"/>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>5</v>
       </c>
@@ -2743,7 +2746,7 @@
       <c r="D127" s="5"/>
       <c r="E127" s="11"/>
     </row>
-    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
         <v>5</v>
       </c>
@@ -2756,7 +2759,7 @@
       <c r="D128" s="5"/>
       <c r="E128" s="11"/>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
         <v>5</v>
       </c>
@@ -2769,7 +2772,7 @@
       <c r="D129" s="5"/>
       <c r="E129" s="11"/>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
         <v>5</v>
       </c>
@@ -2782,7 +2785,7 @@
       <c r="D130" s="5"/>
       <c r="E130" s="11"/>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
         <v>5</v>
       </c>
@@ -2795,7 +2798,7 @@
       <c r="D131" s="5"/>
       <c r="E131" s="11"/>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
         <v>5</v>
       </c>
@@ -2808,7 +2811,7 @@
       <c r="D132" s="5"/>
       <c r="E132" s="11"/>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
         <v>5</v>
       </c>
@@ -2821,7 +2824,7 @@
       <c r="D133" s="5"/>
       <c r="E133" s="11"/>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
         <v>5</v>
       </c>
@@ -2834,7 +2837,7 @@
       <c r="D134" s="5"/>
       <c r="E134" s="11"/>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>5</v>
       </c>
@@ -2847,7 +2850,7 @@
       <c r="D135" s="5"/>
       <c r="E135" s="11"/>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>5</v>
       </c>
@@ -2860,7 +2863,7 @@
       <c r="D136" s="5"/>
       <c r="E136" s="11"/>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>5</v>
       </c>
@@ -2873,7 +2876,7 @@
       <c r="D137" s="5"/>
       <c r="E137" s="11"/>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>5</v>
       </c>
@@ -2886,7 +2889,7 @@
       <c r="D138" s="5"/>
       <c r="E138" s="11"/>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>5</v>
       </c>
@@ -2899,7 +2902,7 @@
       <c r="D139" s="5"/>
       <c r="E139" s="11"/>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>5</v>
       </c>
@@ -2912,7 +2915,7 @@
       <c r="D140" s="5"/>
       <c r="E140" s="11"/>
     </row>
-    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>5</v>
       </c>
@@ -2925,7 +2928,7 @@
       <c r="D141" s="5"/>
       <c r="E141" s="11"/>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>5</v>
       </c>
@@ -2938,7 +2941,7 @@
       <c r="D142" s="5"/>
       <c r="E142" s="11"/>
     </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>5</v>
       </c>
@@ -2951,7 +2954,7 @@
       <c r="D143" s="5"/>
       <c r="E143" s="11"/>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>5</v>
       </c>
@@ -2964,7 +2967,7 @@
       <c r="D144" s="5"/>
       <c r="E144" s="11"/>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>5</v>
       </c>
@@ -2977,7 +2980,7 @@
       <c r="D145" s="5"/>
       <c r="E145" s="11"/>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>5</v>
       </c>
@@ -2990,7 +2993,7 @@
       <c r="D146" s="5"/>
       <c r="E146" s="11"/>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>5</v>
       </c>
@@ -3003,7 +3006,7 @@
       <c r="D147" s="5"/>
       <c r="E147" s="11"/>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>5</v>
       </c>
@@ -3016,7 +3019,7 @@
       <c r="D148" s="5"/>
       <c r="E148" s="11"/>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>5</v>
       </c>
@@ -3029,7 +3032,7 @@
       <c r="D149" s="5"/>
       <c r="E149" s="11"/>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>5</v>
       </c>
@@ -3042,7 +3045,7 @@
       <c r="D150" s="5"/>
       <c r="E150" s="11"/>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>5</v>
       </c>
@@ -3055,7 +3058,7 @@
       <c r="D151" s="5"/>
       <c r="E151" s="11"/>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>5</v>
       </c>
@@ -3068,7 +3071,7 @@
       <c r="D152" s="5"/>
       <c r="E152" s="11"/>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>5</v>
       </c>
@@ -3081,7 +3084,7 @@
       <c r="D153" s="5"/>
       <c r="E153" s="11"/>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>5</v>
       </c>
@@ -3094,7 +3097,7 @@
       <c r="D154" s="5"/>
       <c r="E154" s="11"/>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>5</v>
       </c>
@@ -3107,7 +3110,7 @@
       <c r="D155" s="5"/>
       <c r="E155" s="11"/>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>5</v>
       </c>
@@ -3120,7 +3123,7 @@
       <c r="D156" s="5"/>
       <c r="E156" s="11"/>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>5</v>
       </c>
@@ -3133,7 +3136,7 @@
       <c r="D157" s="5"/>
       <c r="E157" s="11"/>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>5</v>
       </c>
@@ -3146,7 +3149,7 @@
       <c r="D158" s="5"/>
       <c r="E158" s="11"/>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>5</v>
       </c>
@@ -3159,7 +3162,7 @@
       <c r="D159" s="5"/>
       <c r="E159" s="11"/>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>5</v>
       </c>
@@ -3172,7 +3175,7 @@
       <c r="D160" s="5"/>
       <c r="E160" s="11"/>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>5</v>
       </c>
@@ -3185,7 +3188,7 @@
       <c r="D161" s="5"/>
       <c r="E161" s="11"/>
     </row>
-    <row r="162" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>43</v>
       </c>
@@ -3200,7 +3203,7 @@
       </c>
       <c r="E162" s="11"/>
     </row>
-    <row r="163" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>43</v>
       </c>
@@ -3215,7 +3218,7 @@
       </c>
       <c r="E163" s="11"/>
     </row>
-    <row r="164" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>43</v>
       </c>
@@ -3230,7 +3233,7 @@
       </c>
       <c r="E164" s="11"/>
     </row>
-    <row r="165" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>43</v>
       </c>
@@ -3247,7 +3250,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>5</v>
       </c>
@@ -3264,7 +3267,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>5</v>
       </c>
@@ -3281,7 +3284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>5</v>
       </c>
@@ -3296,7 +3299,7 @@
       </c>
       <c r="E168" s="10"/>
     </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>5</v>
       </c>
@@ -3311,7 +3314,7 @@
       </c>
       <c r="E169" s="10"/>
     </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>5</v>
       </c>
@@ -3326,7 +3329,7 @@
       </c>
       <c r="E170" s="10"/>
     </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>5</v>
       </c>
@@ -3341,7 +3344,7 @@
       </c>
       <c r="E171" s="10"/>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>5</v>
       </c>
@@ -3356,7 +3359,7 @@
       </c>
       <c r="E172" s="10"/>
     </row>
-    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>5</v>
       </c>
@@ -3371,7 +3374,7 @@
       </c>
       <c r="E173" s="10"/>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>5</v>
       </c>
@@ -3386,7 +3389,7 @@
       </c>
       <c r="E174" s="10"/>
     </row>
-    <row r="175" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" ht="29.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>5</v>
       </c>
@@ -3401,7 +3404,7 @@
       </c>
       <c r="E175" s="10"/>
     </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>5</v>
       </c>
@@ -3416,7 +3419,7 @@
       </c>
       <c r="E176" s="10"/>
     </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>5</v>
       </c>
@@ -3431,7 +3434,7 @@
       </c>
       <c r="E177" s="10"/>
     </row>
-    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>5</v>
       </c>
@@ -3446,7 +3449,7 @@
       </c>
       <c r="E178" s="10"/>
     </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>5</v>
       </c>
@@ -3461,7 +3464,7 @@
       </c>
       <c r="E179" s="10"/>
     </row>
-    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>5</v>
       </c>
@@ -3476,7 +3479,7 @@
       </c>
       <c r="E180" s="10"/>
     </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>5</v>
       </c>
@@ -3491,7 +3494,7 @@
       </c>
       <c r="E181" s="10"/>
     </row>
-    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>5</v>
       </c>
@@ -3506,7 +3509,7 @@
       </c>
       <c r="E182" s="10"/>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>5</v>
       </c>
@@ -3521,7 +3524,7 @@
       </c>
       <c r="E183" s="10"/>
     </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>5</v>
       </c>
@@ -3536,7 +3539,7 @@
       </c>
       <c r="E184" s="10"/>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>5</v>
       </c>
@@ -3551,7 +3554,7 @@
       </c>
       <c r="E185" s="10"/>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>5</v>
       </c>
@@ -3566,7 +3569,7 @@
       </c>
       <c r="E186" s="10"/>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>5</v>
       </c>
@@ -3581,7 +3584,7 @@
       </c>
       <c r="E187" s="10"/>
     </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>5</v>
       </c>
@@ -3596,7 +3599,7 @@
       </c>
       <c r="E188" s="10"/>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>5</v>
       </c>
@@ -3611,7 +3614,7 @@
       </c>
       <c r="E189" s="10"/>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>5</v>
       </c>
@@ -3626,7 +3629,7 @@
       </c>
       <c r="E190" s="10"/>
     </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>5</v>
       </c>
@@ -3641,7 +3644,7 @@
       </c>
       <c r="E191" s="10"/>
     </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>5</v>
       </c>
@@ -3656,7 +3659,7 @@
       </c>
       <c r="E192" s="10"/>
     </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>5</v>
       </c>
@@ -3671,7 +3674,7 @@
       </c>
       <c r="E193" s="10"/>
     </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>5</v>
       </c>
@@ -3686,7 +3689,7 @@
       </c>
       <c r="E194" s="10"/>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>5</v>
       </c>
@@ -3701,7 +3704,7 @@
       </c>
       <c r="E195" s="10"/>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>5</v>
       </c>
@@ -3716,7 +3719,7 @@
       </c>
       <c r="E196" s="10"/>
     </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>5</v>
       </c>
@@ -3731,7 +3734,7 @@
       </c>
       <c r="E197" s="10"/>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>5</v>
       </c>
@@ -3746,7 +3749,7 @@
       </c>
       <c r="E198" s="10"/>
     </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>5</v>
       </c>
@@ -3761,7 +3764,7 @@
       </c>
       <c r="E199" s="10"/>
     </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>5</v>
       </c>
@@ -3776,7 +3779,7 @@
       </c>
       <c r="E200" s="10"/>
     </row>
-    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>5</v>
       </c>
@@ -3791,7 +3794,7 @@
       </c>
       <c r="E201" s="10"/>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
         <v>43</v>
       </c>
@@ -3804,7 +3807,7 @@
       <c r="D202" s="5"/>
       <c r="E202" s="11"/>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
         <v>43</v>
       </c>
@@ -3817,7 +3820,7 @@
       <c r="D203" s="5"/>
       <c r="E203" s="11"/>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
         <v>43</v>
       </c>
@@ -3830,7 +3833,7 @@
       <c r="D204" s="5"/>
       <c r="E204" s="11"/>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
         <v>43</v>
       </c>
@@ -3843,7 +3846,7 @@
       <c r="D205" s="5"/>
       <c r="E205" s="11"/>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
         <v>43</v>
       </c>
@@ -3856,7 +3859,7 @@
       <c r="D206" s="5"/>
       <c r="E206" s="11"/>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>43</v>
       </c>
@@ -3869,7 +3872,7 @@
       <c r="D207" s="5"/>
       <c r="E207" s="11"/>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
         <v>43</v>
       </c>
@@ -3882,7 +3885,7 @@
       <c r="D208" s="5"/>
       <c r="E208" s="11"/>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
         <v>43</v>
       </c>
@@ -3895,7 +3898,7 @@
       <c r="D209" s="5"/>
       <c r="E209" s="11"/>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
         <v>43</v>
       </c>
@@ -3908,7 +3911,7 @@
       <c r="D210" s="5"/>
       <c r="E210" s="11"/>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
         <v>43</v>
       </c>
@@ -3921,7 +3924,7 @@
       <c r="D211" s="5"/>
       <c r="E211" s="11"/>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
         <v>43</v>
       </c>
@@ -3934,7 +3937,7 @@
       <c r="D212" s="5"/>
       <c r="E212" s="11"/>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
         <v>43</v>
       </c>
@@ -3947,7 +3950,7 @@
       <c r="D213" s="5"/>
       <c r="E213" s="11"/>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
         <v>43</v>
       </c>
@@ -3960,7 +3963,7 @@
       <c r="D214" s="5"/>
       <c r="E214" s="11"/>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
         <v>43</v>
       </c>
@@ -3973,7 +3976,7 @@
       <c r="D215" s="5"/>
       <c r="E215" s="11"/>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
         <v>43</v>
       </c>
@@ -3986,7 +3989,7 @@
       <c r="D216" s="5"/>
       <c r="E216" s="11"/>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
         <v>43</v>
       </c>
@@ -3999,7 +4002,7 @@
       <c r="D217" s="5"/>
       <c r="E217" s="11"/>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
         <v>43</v>
       </c>
@@ -4012,7 +4015,7 @@
       <c r="D218" s="5"/>
       <c r="E218" s="11"/>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
         <v>43</v>
       </c>
@@ -4025,7 +4028,7 @@
       <c r="D219" s="5"/>
       <c r="E219" s="11"/>
     </row>
-    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
         <v>43</v>
       </c>
@@ -4038,7 +4041,7 @@
       <c r="D220" s="5"/>
       <c r="E220" s="11"/>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
         <v>43</v>
       </c>
@@ -4051,7 +4054,7 @@
       <c r="D221" s="5"/>
       <c r="E221" s="11"/>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="s">
         <v>43</v>
       </c>
@@ -4064,7 +4067,7 @@
       <c r="D222" s="5"/>
       <c r="E222" s="11"/>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="4" t="s">
         <v>43</v>
       </c>
@@ -4077,7 +4080,7 @@
       <c r="D223" s="5"/>
       <c r="E223" s="11"/>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
         <v>43</v>
       </c>
@@ -4090,7 +4093,7 @@
       <c r="D224" s="5"/>
       <c r="E224" s="11"/>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
         <v>43</v>
       </c>
@@ -4103,7 +4106,7 @@
       <c r="D225" s="5"/>
       <c r="E225" s="11"/>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
         <v>43</v>
       </c>
@@ -4116,7 +4119,7 @@
       <c r="D226" s="5"/>
       <c r="E226" s="11"/>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
         <v>43</v>
       </c>
@@ -4129,7 +4132,7 @@
       <c r="D227" s="5"/>
       <c r="E227" s="11"/>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
         <v>43</v>
       </c>
@@ -4142,7 +4145,7 @@
       <c r="D228" s="5"/>
       <c r="E228" s="11"/>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
         <v>43</v>
       </c>
@@ -4155,7 +4158,7 @@
       <c r="D229" s="5"/>
       <c r="E229" s="11"/>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
         <v>43</v>
       </c>
@@ -4168,7 +4171,7 @@
       <c r="D230" s="5"/>
       <c r="E230" s="11"/>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
         <v>43</v>
       </c>
@@ -4181,7 +4184,7 @@
       <c r="D231" s="5"/>
       <c r="E231" s="11"/>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
         <v>43</v>
       </c>
@@ -4194,7 +4197,7 @@
       <c r="D232" s="5"/>
       <c r="E232" s="11"/>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
         <v>43</v>
       </c>
@@ -4207,7 +4210,7 @@
       <c r="D233" s="5"/>
       <c r="E233" s="11"/>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
         <v>43</v>
       </c>
@@ -4220,7 +4223,7 @@
       <c r="D234" s="5"/>
       <c r="E234" s="11"/>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
         <v>43</v>
       </c>
@@ -4233,7 +4236,7 @@
       <c r="D235" s="5"/>
       <c r="E235" s="11"/>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
         <v>43</v>
       </c>
@@ -4246,7 +4249,7 @@
       <c r="D236" s="5"/>
       <c r="E236" s="11"/>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
         <v>43</v>
       </c>
@@ -4259,7 +4262,7 @@
       <c r="D237" s="5"/>
       <c r="E237" s="11"/>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
         <v>43</v>
       </c>
@@ -4272,7 +4275,7 @@
       <c r="D238" s="5"/>
       <c r="E238" s="11"/>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
         <v>43</v>
       </c>
@@ -4285,7 +4288,7 @@
       <c r="D239" s="5"/>
       <c r="E239" s="11"/>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
         <v>43</v>
       </c>
@@ -4298,7 +4301,7 @@
       <c r="D240" s="5"/>
       <c r="E240" s="11"/>
     </row>
-    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
         <v>43</v>
       </c>
@@ -4311,7 +4314,7 @@
       <c r="D241" s="5"/>
       <c r="E241" s="11"/>
     </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
         <v>43</v>
       </c>
@@ -4324,7 +4327,7 @@
       <c r="D242" s="5"/>
       <c r="E242" s="11"/>
     </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
         <v>43</v>
       </c>
@@ -4337,7 +4340,7 @@
       <c r="D243" s="5"/>
       <c r="E243" s="11"/>
     </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
         <v>43</v>
       </c>
@@ -4350,7 +4353,7 @@
       <c r="D244" s="5"/>
       <c r="E244" s="11"/>
     </row>
-    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>43</v>
       </c>
@@ -4363,7 +4366,7 @@
       <c r="D245" s="5"/>
       <c r="E245" s="11"/>
     </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
         <v>43</v>
       </c>
@@ -4376,7 +4379,7 @@
       <c r="D246" s="5"/>
       <c r="E246" s="11"/>
     </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
         <v>43</v>
       </c>
@@ -4389,7 +4392,7 @@
       <c r="D247" s="5"/>
       <c r="E247" s="11"/>
     </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
         <v>43</v>
       </c>
@@ -4402,7 +4405,7 @@
       <c r="D248" s="5"/>
       <c r="E248" s="11"/>
     </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
         <v>43</v>
       </c>
@@ -4415,7 +4418,7 @@
       <c r="D249" s="5"/>
       <c r="E249" s="11"/>
     </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
         <v>43</v>
       </c>
@@ -4428,7 +4431,7 @@
       <c r="D250" s="5"/>
       <c r="E250" s="11"/>
     </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>43</v>
       </c>
@@ -4441,7 +4444,7 @@
       <c r="D251" s="5"/>
       <c r="E251" s="11"/>
     </row>
-    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
         <v>43</v>
       </c>
@@ -4454,7 +4457,7 @@
       <c r="D252" s="5"/>
       <c r="E252" s="11"/>
     </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
         <v>43</v>
       </c>
@@ -4467,7 +4470,7 @@
       <c r="D253" s="5"/>
       <c r="E253" s="11"/>
     </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
         <v>43</v>
       </c>
@@ -4480,7 +4483,7 @@
       <c r="D254" s="5"/>
       <c r="E254" s="11"/>
     </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
         <v>43</v>
       </c>
@@ -4493,7 +4496,7 @@
       <c r="D255" s="5"/>
       <c r="E255" s="11"/>
     </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
         <v>43</v>
       </c>
@@ -4506,7 +4509,7 @@
       <c r="D256" s="5"/>
       <c r="E256" s="11"/>
     </row>
-    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
         <v>43</v>
       </c>
@@ -4519,7 +4522,7 @@
       <c r="D257" s="5"/>
       <c r="E257" s="11"/>
     </row>
-    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
         <v>43</v>
       </c>
@@ -4532,7 +4535,7 @@
       <c r="D258" s="5"/>
       <c r="E258" s="11"/>
     </row>
-    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
         <v>43</v>
       </c>
@@ -4545,7 +4548,7 @@
       <c r="D259" s="5"/>
       <c r="E259" s="11"/>
     </row>
-    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
         <v>43</v>
       </c>
@@ -4558,7 +4561,7 @@
       <c r="D260" s="5"/>
       <c r="E260" s="11"/>
     </row>
-    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
         <v>43</v>
       </c>
@@ -4571,7 +4574,7 @@
       <c r="D261" s="5"/>
       <c r="E261" s="11"/>
     </row>
-    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
         <v>43</v>
       </c>
@@ -4584,7 +4587,7 @@
       <c r="D262" s="5"/>
       <c r="E262" s="11"/>
     </row>
-    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
         <v>43</v>
       </c>
@@ -4597,7 +4600,7 @@
       <c r="D263" s="5"/>
       <c r="E263" s="11"/>
     </row>
-    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
         <v>43</v>
       </c>
@@ -4610,7 +4613,7 @@
       <c r="D264" s="5"/>
       <c r="E264" s="11"/>
     </row>
-    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
         <v>43</v>
       </c>
@@ -4623,7 +4626,7 @@
       <c r="D265" s="5"/>
       <c r="E265" s="11"/>
     </row>
-    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
         <v>43</v>
       </c>
@@ -4636,7 +4639,7 @@
       <c r="D266" s="5"/>
       <c r="E266" s="11"/>
     </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
         <v>43</v>
       </c>
@@ -4649,7 +4652,7 @@
       <c r="D267" s="5"/>
       <c r="E267" s="11"/>
     </row>
-    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
         <v>43</v>
       </c>
@@ -4662,7 +4665,7 @@
       <c r="D268" s="5"/>
       <c r="E268" s="11"/>
     </row>
-    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
         <v>43</v>
       </c>
@@ -4675,7 +4678,7 @@
       <c r="D269" s="5"/>
       <c r="E269" s="11"/>
     </row>
-    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
         <v>43</v>
       </c>
@@ -4688,7 +4691,7 @@
       <c r="D270" s="5"/>
       <c r="E270" s="11"/>
     </row>
-    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>43</v>
       </c>
@@ -4701,7 +4704,7 @@
       <c r="D271" s="5"/>
       <c r="E271" s="11"/>
     </row>
-    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
         <v>43</v>
       </c>
@@ -4714,7 +4717,7 @@
       <c r="D272" s="5"/>
       <c r="E272" s="11"/>
     </row>
-    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
         <v>43</v>
       </c>
@@ -4727,7 +4730,7 @@
       <c r="D273" s="5"/>
       <c r="E273" s="11"/>
     </row>
-    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
         <v>43</v>
       </c>
@@ -4740,7 +4743,7 @@
       <c r="D274" s="5"/>
       <c r="E274" s="11"/>
     </row>
-    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
         <v>43</v>
       </c>
@@ -4753,7 +4756,7 @@
       <c r="D275" s="5"/>
       <c r="E275" s="11"/>
     </row>
-    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
         <v>43</v>
       </c>
@@ -4766,7 +4769,7 @@
       <c r="D276" s="5"/>
       <c r="E276" s="11"/>
     </row>
-    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>43</v>
       </c>
@@ -4779,7 +4782,7 @@
       <c r="D277" s="5"/>
       <c r="E277" s="11"/>
     </row>
-    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
         <v>43</v>
       </c>
@@ -4792,7 +4795,7 @@
       <c r="D278" s="5"/>
       <c r="E278" s="11"/>
     </row>
-    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
         <v>43</v>
       </c>
@@ -4805,7 +4808,7 @@
       <c r="D279" s="5"/>
       <c r="E279" s="11"/>
     </row>
-    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
         <v>43</v>
       </c>
@@ -4818,7 +4821,7 @@
       <c r="D280" s="5"/>
       <c r="E280" s="11"/>
     </row>
-    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
         <v>43</v>
       </c>
@@ -4831,7 +4834,7 @@
       <c r="D281" s="5"/>
       <c r="E281" s="11"/>
     </row>
-    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
         <v>43</v>
       </c>
@@ -4844,7 +4847,7 @@
       <c r="D282" s="5"/>
       <c r="E282" s="11"/>
     </row>
-    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>43</v>
       </c>
@@ -4857,7 +4860,7 @@
       <c r="D283" s="5"/>
       <c r="E283" s="11"/>
     </row>
-    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
         <v>43</v>
       </c>
@@ -4870,7 +4873,7 @@
       <c r="D284" s="5"/>
       <c r="E284" s="11"/>
     </row>
-    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>43</v>
       </c>
@@ -4883,7 +4886,7 @@
       <c r="D285" s="5"/>
       <c r="E285" s="11"/>
     </row>
-    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
         <v>43</v>
       </c>
@@ -4896,7 +4899,7 @@
       <c r="D286" s="5"/>
       <c r="E286" s="11"/>
     </row>
-    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
         <v>43</v>
       </c>
@@ -4909,7 +4912,7 @@
       <c r="D287" s="5"/>
       <c r="E287" s="11"/>
     </row>
-    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
         <v>43</v>
       </c>
@@ -4922,7 +4925,7 @@
       <c r="D288" s="5"/>
       <c r="E288" s="11"/>
     </row>
-    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
         <v>43</v>
       </c>
@@ -4935,7 +4938,7 @@
       <c r="D289" s="5"/>
       <c r="E289" s="11"/>
     </row>
-    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
         <v>43</v>
       </c>
@@ -4948,7 +4951,7 @@
       <c r="D290" s="5"/>
       <c r="E290" s="11"/>
     </row>
-    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
         <v>43</v>
       </c>
@@ -4961,7 +4964,7 @@
       <c r="D291" s="5"/>
       <c r="E291" s="11"/>
     </row>
-    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
         <v>43</v>
       </c>
@@ -4974,7 +4977,7 @@
       <c r="D292" s="5"/>
       <c r="E292" s="11"/>
     </row>
-    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
         <v>43</v>
       </c>
@@ -4987,7 +4990,7 @@
       <c r="D293" s="5"/>
       <c r="E293" s="11"/>
     </row>
-    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
         <v>43</v>
       </c>
@@ -5000,7 +5003,7 @@
       <c r="D294" s="5"/>
       <c r="E294" s="11"/>
     </row>
-    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
         <v>43</v>
       </c>
@@ -5013,7 +5016,7 @@
       <c r="D295" s="5"/>
       <c r="E295" s="11"/>
     </row>
-    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
         <v>43</v>
       </c>
@@ -5026,7 +5029,7 @@
       <c r="D296" s="5"/>
       <c r="E296" s="11"/>
     </row>
-    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
         <v>43</v>
       </c>
@@ -5039,7 +5042,7 @@
       <c r="D297" s="5"/>
       <c r="E297" s="11"/>
     </row>
-    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
         <v>43</v>
       </c>
@@ -5052,7 +5055,7 @@
       <c r="D298" s="5"/>
       <c r="E298" s="11"/>
     </row>
-    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
         <v>43</v>
       </c>
@@ -5065,7 +5068,7 @@
       <c r="D299" s="5"/>
       <c r="E299" s="11"/>
     </row>
-    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
         <v>43</v>
       </c>
@@ -5078,7 +5081,7 @@
       <c r="D300" s="5"/>
       <c r="E300" s="11"/>
     </row>
-    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
         <v>43</v>
       </c>
@@ -5091,7 +5094,7 @@
       <c r="D301" s="5"/>
       <c r="E301" s="11"/>
     </row>
-    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
         <v>43</v>
       </c>
@@ -5104,7 +5107,7 @@
       <c r="D302" s="5"/>
       <c r="E302" s="11"/>
     </row>
-    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
         <v>43</v>
       </c>
@@ -5117,7 +5120,7 @@
       <c r="D303" s="5"/>
       <c r="E303" s="11"/>
     </row>
-    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
         <v>43</v>
       </c>
@@ -5130,7 +5133,7 @@
       <c r="D304" s="5"/>
       <c r="E304" s="11"/>
     </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
         <v>43</v>
       </c>
@@ -5143,7 +5146,7 @@
       <c r="D305" s="5"/>
       <c r="E305" s="11"/>
     </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
         <v>43</v>
       </c>
@@ -5156,7 +5159,7 @@
       <c r="D306" s="5"/>
       <c r="E306" s="11"/>
     </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
         <v>43</v>
       </c>
@@ -5169,7 +5172,7 @@
       <c r="D307" s="5"/>
       <c r="E307" s="11"/>
     </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
         <v>43</v>
       </c>
@@ -5182,7 +5185,7 @@
       <c r="D308" s="5"/>
       <c r="E308" s="11"/>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
         <v>43</v>
       </c>
@@ -5195,7 +5198,7 @@
       <c r="D309" s="5"/>
       <c r="E309" s="11"/>
     </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
         <v>43</v>
       </c>
@@ -5208,7 +5211,7 @@
       <c r="D310" s="5"/>
       <c r="E310" s="11"/>
     </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
         <v>43</v>
       </c>
@@ -5221,7 +5224,7 @@
       <c r="D311" s="5"/>
       <c r="E311" s="11"/>
     </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A312" s="4" t="s">
         <v>43</v>
       </c>
@@ -5234,7 +5237,7 @@
       <c r="D312" s="5"/>
       <c r="E312" s="11"/>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A313" s="4" t="s">
         <v>43</v>
       </c>
@@ -5247,7 +5250,7 @@
       <c r="D313" s="5"/>
       <c r="E313" s="11"/>
     </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A314" s="4" t="s">
         <v>43</v>
       </c>
@@ -5260,7 +5263,7 @@
       <c r="D314" s="5"/>
       <c r="E314" s="11"/>
     </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A315" s="4" t="s">
         <v>43</v>
       </c>
@@ -5273,7 +5276,7 @@
       <c r="D315" s="5"/>
       <c r="E315" s="11"/>
     </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A316" s="4" t="s">
         <v>43</v>
       </c>
@@ -5290,7 +5293,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A317" s="4" t="s">
         <v>43</v>
       </c>
@@ -5303,7 +5306,7 @@
       <c r="D317" s="5"/>
       <c r="E317" s="11"/>
     </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A318" s="4" t="s">
         <v>43</v>
       </c>
@@ -5320,7 +5323,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
         <v>43</v>
       </c>
@@ -5337,7 +5340,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
         <v>43</v>
       </c>
@@ -5352,7 +5355,7 @@
       </c>
       <c r="E320" s="11"/>
     </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
         <v>43</v>
       </c>
@@ -5367,7 +5370,7 @@
       </c>
       <c r="E321" s="11"/>
     </row>
-    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A322" s="2" t="s">
         <v>5</v>
       </c>
@@ -5382,7 +5385,7 @@
       </c>
       <c r="E322" s="10"/>
     </row>
-    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2" t="s">
         <v>5</v>
       </c>
@@ -5397,7 +5400,7 @@
       </c>
       <c r="E323" s="10"/>
     </row>
-    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A324" s="2" t="s">
         <v>5</v>
       </c>
@@ -5412,7 +5415,7 @@
       </c>
       <c r="E324" s="10"/>
     </row>
-    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
         <v>5</v>
       </c>
@@ -5427,7 +5430,7 @@
       </c>
       <c r="E325" s="10"/>
     </row>
-    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
         <v>44</v>
       </c>
@@ -5440,7 +5443,7 @@
       <c r="D326" s="5"/>
       <c r="E326" s="11"/>
     </row>
-    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
         <v>44</v>
       </c>
@@ -5453,7 +5456,7 @@
       <c r="D327" s="5"/>
       <c r="E327" s="11"/>
     </row>
-    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
         <v>44</v>
       </c>
@@ -5466,7 +5469,7 @@
       <c r="D328" s="5"/>
       <c r="E328" s="11"/>
     </row>
-    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
         <v>44</v>
       </c>
@@ -5479,7 +5482,7 @@
       <c r="D329" s="5"/>
       <c r="E329" s="11"/>
     </row>
-    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A330" s="4" t="s">
         <v>44</v>
       </c>
@@ -5492,7 +5495,7 @@
       <c r="D330" s="5"/>
       <c r="E330" s="11"/>
     </row>
-    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
         <v>44</v>
       </c>
@@ -5505,7 +5508,7 @@
       <c r="D331" s="5"/>
       <c r="E331" s="11"/>
     </row>
-    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
         <v>44</v>
       </c>
@@ -5518,7 +5521,7 @@
       <c r="D332" s="5"/>
       <c r="E332" s="11"/>
     </row>
-    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A333" s="4" t="s">
         <v>44</v>
       </c>
@@ -5531,7 +5534,7 @@
       <c r="D333" s="5"/>
       <c r="E333" s="11"/>
     </row>
-    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A334" s="4" t="s">
         <v>44</v>
       </c>
@@ -5544,7 +5547,7 @@
       <c r="D334" s="5"/>
       <c r="E334" s="11"/>
     </row>
-    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A335" s="4" t="s">
         <v>44</v>
       </c>
@@ -5557,7 +5560,7 @@
       <c r="D335" s="5"/>
       <c r="E335" s="11"/>
     </row>
-    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
         <v>44</v>
       </c>
@@ -5570,7 +5573,7 @@
       <c r="D336" s="5"/>
       <c r="E336" s="11"/>
     </row>
-    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
         <v>44</v>
       </c>
@@ -5583,7 +5586,7 @@
       <c r="D337" s="5"/>
       <c r="E337" s="11"/>
     </row>
-    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
         <v>44</v>
       </c>
@@ -5596,7 +5599,7 @@
       <c r="D338" s="5"/>
       <c r="E338" s="11"/>
     </row>
-    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
         <v>44</v>
       </c>
@@ -5609,7 +5612,7 @@
       <c r="D339" s="5"/>
       <c r="E339" s="11"/>
     </row>
-    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
         <v>44</v>
       </c>
@@ -5622,7 +5625,7 @@
       <c r="D340" s="5"/>
       <c r="E340" s="11"/>
     </row>
-    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
         <v>44</v>
       </c>
@@ -5635,7 +5638,7 @@
       <c r="D341" s="5"/>
       <c r="E341" s="11"/>
     </row>
-    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A342" s="4" t="s">
         <v>44</v>
       </c>
@@ -5648,7 +5651,7 @@
       <c r="D342" s="5"/>
       <c r="E342" s="11"/>
     </row>
-    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A343" s="4" t="s">
         <v>44</v>
       </c>
@@ -5661,7 +5664,7 @@
       <c r="D343" s="5"/>
       <c r="E343" s="11"/>
     </row>
-    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A344" s="4" t="s">
         <v>44</v>
       </c>
@@ -5674,7 +5677,7 @@
       <c r="D344" s="5"/>
       <c r="E344" s="11"/>
     </row>
-    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A345" s="4" t="s">
         <v>44</v>
       </c>
@@ -5687,7 +5690,7 @@
       <c r="D345" s="5"/>
       <c r="E345" s="11"/>
     </row>
-    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A346" s="4" t="s">
         <v>44</v>
       </c>
@@ -5700,7 +5703,7 @@
       <c r="D346" s="5"/>
       <c r="E346" s="11"/>
     </row>
-    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A347" s="4" t="s">
         <v>44</v>
       </c>
@@ -5713,7 +5716,7 @@
       <c r="D347" s="5"/>
       <c r="E347" s="11"/>
     </row>
-    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A348" s="4" t="s">
         <v>44</v>
       </c>
@@ -5726,7 +5729,7 @@
       <c r="D348" s="5"/>
       <c r="E348" s="11"/>
     </row>
-    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A349" s="4" t="s">
         <v>44</v>
       </c>
@@ -5739,7 +5742,7 @@
       <c r="D349" s="5"/>
       <c r="E349" s="11"/>
     </row>
-    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A350" s="4" t="s">
         <v>44</v>
       </c>
@@ -5752,7 +5755,7 @@
       <c r="D350" s="5"/>
       <c r="E350" s="11"/>
     </row>
-    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
         <v>44</v>
       </c>
@@ -5765,7 +5768,7 @@
       <c r="D351" s="5"/>
       <c r="E351" s="11"/>
     </row>
-    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A352" s="4" t="s">
         <v>44</v>
       </c>
@@ -5778,7 +5781,7 @@
       <c r="D352" s="5"/>
       <c r="E352" s="11"/>
     </row>
-    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A353" s="4" t="s">
         <v>44</v>
       </c>
@@ -5791,7 +5794,7 @@
       <c r="D353" s="5"/>
       <c r="E353" s="11"/>
     </row>
-    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A354" s="4" t="s">
         <v>44</v>
       </c>
@@ -5804,7 +5807,7 @@
       <c r="D354" s="5"/>
       <c r="E354" s="11"/>
     </row>
-    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A355" s="4" t="s">
         <v>44</v>
       </c>
@@ -5817,7 +5820,7 @@
       <c r="D355" s="5"/>
       <c r="E355" s="11"/>
     </row>
-    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A356" s="4" t="s">
         <v>44</v>
       </c>
@@ -5830,7 +5833,7 @@
       <c r="D356" s="5"/>
       <c r="E356" s="11"/>
     </row>
-    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A357" s="4" t="s">
         <v>44</v>
       </c>
@@ -5843,7 +5846,7 @@
       <c r="D357" s="5"/>
       <c r="E357" s="11"/>
     </row>
-    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A358" s="4" t="s">
         <v>44</v>
       </c>
@@ -5856,7 +5859,7 @@
       <c r="D358" s="5"/>
       <c r="E358" s="11"/>
     </row>
-    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
         <v>44</v>
       </c>
@@ -5869,7 +5872,7 @@
       <c r="D359" s="5"/>
       <c r="E359" s="11"/>
     </row>
-    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A360" s="4" t="s">
         <v>44</v>
       </c>
@@ -5882,7 +5885,7 @@
       <c r="D360" s="5"/>
       <c r="E360" s="11"/>
     </row>
-    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A361" s="4" t="s">
         <v>44</v>
       </c>
@@ -5895,7 +5898,7 @@
       <c r="D361" s="5"/>
       <c r="E361" s="11"/>
     </row>
-    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A362" s="4" t="s">
         <v>44</v>
       </c>
@@ -5908,7 +5911,7 @@
       <c r="D362" s="5"/>
       <c r="E362" s="11"/>
     </row>
-    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
         <v>44</v>
       </c>
@@ -5921,7 +5924,7 @@
       <c r="D363" s="5"/>
       <c r="E363" s="11"/>
     </row>
-    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A364" s="4" t="s">
         <v>44</v>
       </c>
@@ -5934,7 +5937,7 @@
       <c r="D364" s="5"/>
       <c r="E364" s="11"/>
     </row>
-    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A365" s="4" t="s">
         <v>44</v>
       </c>
@@ -5947,7 +5950,7 @@
       <c r="D365" s="5"/>
       <c r="E365" s="11"/>
     </row>
-    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A366" s="4" t="s">
         <v>44</v>
       </c>
@@ -5960,7 +5963,7 @@
       <c r="D366" s="5"/>
       <c r="E366" s="11"/>
     </row>
-    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A367" s="4" t="s">
         <v>44</v>
       </c>
@@ -5973,7 +5976,7 @@
       <c r="D367" s="5"/>
       <c r="E367" s="11"/>
     </row>
-    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A368" s="4" t="s">
         <v>44</v>
       </c>
@@ -5986,7 +5989,7 @@
       <c r="D368" s="5"/>
       <c r="E368" s="11"/>
     </row>
-    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A369" s="4" t="s">
         <v>44</v>
       </c>
@@ -5999,7 +6002,7 @@
       <c r="D369" s="5"/>
       <c r="E369" s="11"/>
     </row>
-    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A370" s="4" t="s">
         <v>44</v>
       </c>
@@ -6012,7 +6015,7 @@
       <c r="D370" s="5"/>
       <c r="E370" s="11"/>
     </row>
-    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A371" s="4" t="s">
         <v>44</v>
       </c>
@@ -6025,7 +6028,7 @@
       <c r="D371" s="5"/>
       <c r="E371" s="11"/>
     </row>
-    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A372" s="4" t="s">
         <v>44</v>
       </c>
@@ -6038,7 +6041,7 @@
       <c r="D372" s="5"/>
       <c r="E372" s="11"/>
     </row>
-    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A373" s="4" t="s">
         <v>44</v>
       </c>
@@ -6051,7 +6054,7 @@
       <c r="D373" s="5"/>
       <c r="E373" s="11"/>
     </row>
-    <row r="374" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A374" s="4" t="s">
         <v>44</v>
       </c>
@@ -6064,7 +6067,7 @@
       <c r="D374" s="5"/>
       <c r="E374" s="11"/>
     </row>
-    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
         <v>44</v>
       </c>
@@ -6077,7 +6080,7 @@
       <c r="D375" s="5"/>
       <c r="E375" s="11"/>
     </row>
-    <row r="376" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A376" s="4" t="s">
         <v>44</v>
       </c>
@@ -6090,7 +6093,7 @@
       <c r="D376" s="5"/>
       <c r="E376" s="11"/>
     </row>
-    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A377" s="4" t="s">
         <v>44</v>
       </c>
@@ -6103,7 +6106,7 @@
       <c r="D377" s="5"/>
       <c r="E377" s="11"/>
     </row>
-    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A378" s="4" t="s">
         <v>44</v>
       </c>
@@ -6116,7 +6119,7 @@
       <c r="D378" s="5"/>
       <c r="E378" s="11"/>
     </row>
-    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A379" s="4" t="s">
         <v>44</v>
       </c>
@@ -6129,7 +6132,7 @@
       <c r="D379" s="5"/>
       <c r="E379" s="11"/>
     </row>
-    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A380" s="4" t="s">
         <v>44</v>
       </c>
@@ -6142,7 +6145,7 @@
       <c r="D380" s="5"/>
       <c r="E380" s="11"/>
     </row>
-    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A381" s="4" t="s">
         <v>44</v>
       </c>
@@ -6155,7 +6158,7 @@
       <c r="D381" s="5"/>
       <c r="E381" s="11"/>
     </row>
-    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A382" s="4" t="s">
         <v>44</v>
       </c>
@@ -6168,7 +6171,7 @@
       <c r="D382" s="5"/>
       <c r="E382" s="11"/>
     </row>
-    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A383" s="4" t="s">
         <v>44</v>
       </c>
@@ -6181,7 +6184,7 @@
       <c r="D383" s="5"/>
       <c r="E383" s="11"/>
     </row>
-    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A384" s="4" t="s">
         <v>44</v>
       </c>
@@ -6194,7 +6197,7 @@
       <c r="D384" s="5"/>
       <c r="E384" s="11"/>
     </row>
-    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A385" s="4" t="s">
         <v>44</v>
       </c>
@@ -6207,7 +6210,7 @@
       <c r="D385" s="5"/>
       <c r="E385" s="11"/>
     </row>
-    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A386" s="4" t="s">
         <v>44</v>
       </c>
@@ -6220,7 +6223,7 @@
       <c r="D386" s="5"/>
       <c r="E386" s="11"/>
     </row>
-    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A387" s="4" t="s">
         <v>44</v>
       </c>
@@ -6233,7 +6236,7 @@
       <c r="D387" s="5"/>
       <c r="E387" s="11"/>
     </row>
-    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A388" s="4" t="s">
         <v>44</v>
       </c>
@@ -6246,7 +6249,7 @@
       <c r="D388" s="5"/>
       <c r="E388" s="11"/>
     </row>
-    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A389" s="4" t="s">
         <v>44</v>
       </c>
@@ -6259,7 +6262,7 @@
       <c r="D389" s="5"/>
       <c r="E389" s="11"/>
     </row>
-    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A390" s="4" t="s">
         <v>44</v>
       </c>
@@ -6272,7 +6275,7 @@
       <c r="D390" s="5"/>
       <c r="E390" s="11"/>
     </row>
-    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
         <v>44</v>
       </c>
@@ -6285,7 +6288,7 @@
       <c r="D391" s="5"/>
       <c r="E391" s="11"/>
     </row>
-    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A392" s="4" t="s">
         <v>44</v>
       </c>
@@ -6298,7 +6301,7 @@
       <c r="D392" s="5"/>
       <c r="E392" s="11"/>
     </row>
-    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A393" s="4" t="s">
         <v>44</v>
       </c>
@@ -6311,7 +6314,7 @@
       <c r="D393" s="5"/>
       <c r="E393" s="11"/>
     </row>
-    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
         <v>44</v>
       </c>
@@ -6324,7 +6327,7 @@
       <c r="D394" s="5"/>
       <c r="E394" s="11"/>
     </row>
-    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
         <v>44</v>
       </c>
@@ -6337,7 +6340,7 @@
       <c r="D395" s="5"/>
       <c r="E395" s="11"/>
     </row>
-    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A396" s="4" t="s">
         <v>44</v>
       </c>
@@ -6350,7 +6353,7 @@
       <c r="D396" s="5"/>
       <c r="E396" s="11"/>
     </row>
-    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A397" s="4" t="s">
         <v>44</v>
       </c>
@@ -6363,7 +6366,7 @@
       <c r="D397" s="5"/>
       <c r="E397" s="11"/>
     </row>
-    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A398" s="4" t="s">
         <v>44</v>
       </c>
@@ -6376,7 +6379,7 @@
       <c r="D398" s="5"/>
       <c r="E398" s="11"/>
     </row>
-    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A399" s="4" t="s">
         <v>44</v>
       </c>
@@ -6389,7 +6392,7 @@
       <c r="D399" s="5"/>
       <c r="E399" s="11"/>
     </row>
-    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A400" s="4" t="s">
         <v>44</v>
       </c>
@@ -6402,7 +6405,7 @@
       <c r="D400" s="5"/>
       <c r="E400" s="11"/>
     </row>
-    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A401" s="4" t="s">
         <v>44</v>
       </c>
@@ -6415,7 +6418,7 @@
       <c r="D401" s="5"/>
       <c r="E401" s="11"/>
     </row>
-    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A402" s="4" t="s">
         <v>44</v>
       </c>
@@ -6428,7 +6431,7 @@
       <c r="D402" s="5"/>
       <c r="E402" s="11"/>
     </row>
-    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A403" s="4" t="s">
         <v>44</v>
       </c>
@@ -6441,7 +6444,7 @@
       <c r="D403" s="5"/>
       <c r="E403" s="11"/>
     </row>
-    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A404" s="4" t="s">
         <v>44</v>
       </c>
@@ -6454,7 +6457,7 @@
       <c r="D404" s="5"/>
       <c r="E404" s="11"/>
     </row>
-    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A405" s="4" t="s">
         <v>44</v>
       </c>
@@ -6467,7 +6470,7 @@
       <c r="D405" s="5"/>
       <c r="E405" s="11"/>
     </row>
-    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A406" s="4" t="s">
         <v>44</v>
       </c>
@@ -6480,7 +6483,7 @@
       <c r="D406" s="5"/>
       <c r="E406" s="11"/>
     </row>
-    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A407" s="4" t="s">
         <v>44</v>
       </c>
@@ -6493,7 +6496,7 @@
       <c r="D407" s="5"/>
       <c r="E407" s="11"/>
     </row>
-    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A408" s="4" t="s">
         <v>44</v>
       </c>
@@ -6506,7 +6509,7 @@
       <c r="D408" s="5"/>
       <c r="E408" s="11"/>
     </row>
-    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A409" s="4" t="s">
         <v>44</v>
       </c>
@@ -6519,7 +6522,7 @@
       <c r="D409" s="5"/>
       <c r="E409" s="11"/>
     </row>
-    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A410" s="4" t="s">
         <v>44</v>
       </c>
@@ -6532,7 +6535,7 @@
       <c r="D410" s="5"/>
       <c r="E410" s="11"/>
     </row>
-    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A411" s="4" t="s">
         <v>44</v>
       </c>
@@ -6545,7 +6548,7 @@
       <c r="D411" s="5"/>
       <c r="E411" s="11"/>
     </row>
-    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A412" s="4" t="s">
         <v>44</v>
       </c>
@@ -6558,7 +6561,7 @@
       <c r="D412" s="5"/>
       <c r="E412" s="11"/>
     </row>
-    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A413" s="4" t="s">
         <v>44</v>
       </c>
@@ -6571,7 +6574,7 @@
       <c r="D413" s="5"/>
       <c r="E413" s="11"/>
     </row>
-    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A414" s="4" t="s">
         <v>44</v>
       </c>
@@ -6584,7 +6587,7 @@
       <c r="D414" s="5"/>
       <c r="E414" s="11"/>
     </row>
-    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A415" s="4" t="s">
         <v>44</v>
       </c>
@@ -6597,7 +6600,7 @@
       <c r="D415" s="5"/>
       <c r="E415" s="11"/>
     </row>
-    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A416" s="4" t="s">
         <v>44</v>
       </c>
@@ -6610,7 +6613,7 @@
       <c r="D416" s="5"/>
       <c r="E416" s="11"/>
     </row>
-    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A417" s="4" t="s">
         <v>44</v>
       </c>
@@ -6623,7 +6626,7 @@
       <c r="D417" s="5"/>
       <c r="E417" s="11"/>
     </row>
-    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A418" s="4" t="s">
         <v>44</v>
       </c>
@@ -6636,7 +6639,7 @@
       <c r="D418" s="5"/>
       <c r="E418" s="11"/>
     </row>
-    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A419" s="4" t="s">
         <v>44</v>
       </c>
@@ -6649,7 +6652,7 @@
       <c r="D419" s="5"/>
       <c r="E419" s="11"/>
     </row>
-    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A420" s="4" t="s">
         <v>44</v>
       </c>
@@ -6662,7 +6665,7 @@
       <c r="D420" s="5"/>
       <c r="E420" s="11"/>
     </row>
-    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A421" s="4" t="s">
         <v>44</v>
       </c>
@@ -6675,7 +6678,7 @@
       <c r="D421" s="5"/>
       <c r="E421" s="11"/>
     </row>
-    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A422" s="4" t="s">
         <v>44</v>
       </c>
@@ -6688,7 +6691,7 @@
       <c r="D422" s="5"/>
       <c r="E422" s="11"/>
     </row>
-    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A423" s="4" t="s">
         <v>44</v>
       </c>
@@ -6701,7 +6704,7 @@
       <c r="D423" s="5"/>
       <c r="E423" s="11"/>
     </row>
-    <row r="424" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A424" s="4" t="s">
         <v>44</v>
       </c>
@@ -6714,7 +6717,7 @@
       <c r="D424" s="5"/>
       <c r="E424" s="11"/>
     </row>
-    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A425" s="4" t="s">
         <v>44</v>
       </c>
@@ -6727,7 +6730,7 @@
       <c r="D425" s="5"/>
       <c r="E425" s="11"/>
     </row>
-    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A426" s="4" t="s">
         <v>44</v>
       </c>
@@ -6740,7 +6743,7 @@
       <c r="D426" s="5"/>
       <c r="E426" s="11"/>
     </row>
-    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A427" s="4" t="s">
         <v>44</v>
       </c>
@@ -6753,7 +6756,7 @@
       <c r="D427" s="5"/>
       <c r="E427" s="11"/>
     </row>
-    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A428" s="4" t="s">
         <v>44</v>
       </c>
@@ -6766,7 +6769,7 @@
       <c r="D428" s="5"/>
       <c r="E428" s="11"/>
     </row>
-    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A429" s="4" t="s">
         <v>44</v>
       </c>
@@ -6779,7 +6782,7 @@
       <c r="D429" s="5"/>
       <c r="E429" s="11"/>
     </row>
-    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A430" s="4" t="s">
         <v>44</v>
       </c>
@@ -6792,7 +6795,7 @@
       <c r="D430" s="5"/>
       <c r="E430" s="11"/>
     </row>
-    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A431" s="4" t="s">
         <v>44</v>
       </c>
@@ -6805,7 +6808,7 @@
       <c r="D431" s="5"/>
       <c r="E431" s="11"/>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A432" s="4" t="s">
         <v>44</v>
       </c>
@@ -6822,7 +6825,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A433" s="4" t="s">
         <v>44</v>
       </c>
@@ -6835,7 +6838,7 @@
       <c r="D433" s="5"/>
       <c r="E433" s="11"/>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A434" s="4" t="s">
         <v>44</v>
       </c>
@@ -6852,7 +6855,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A435" s="4" t="s">
         <v>44</v>
       </c>
@@ -6865,7 +6868,7 @@
       <c r="D435" s="5"/>
       <c r="E435" s="11"/>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A436" s="4" t="s">
         <v>44</v>
       </c>
@@ -6878,7 +6881,7 @@
       <c r="D436" s="5"/>
       <c r="E436" s="11"/>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A437" s="4" t="s">
         <v>44</v>
       </c>
@@ -6891,7 +6894,7 @@
       <c r="D437" s="5"/>
       <c r="E437" s="11"/>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A438" s="4" t="s">
         <v>44</v>
       </c>
@@ -6904,7 +6907,7 @@
       <c r="D438" s="5"/>
       <c r="E438" s="11"/>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A439" s="4" t="s">
         <v>44</v>
       </c>
@@ -6917,7 +6920,7 @@
       <c r="D439" s="5"/>
       <c r="E439" s="11"/>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A440" s="4" t="s">
         <v>44</v>
       </c>
@@ -6930,7 +6933,7 @@
       <c r="D440" s="5"/>
       <c r="E440" s="11"/>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A441" s="4" t="s">
         <v>44</v>
       </c>
@@ -6943,7 +6946,7 @@
       <c r="D441" s="5"/>
       <c r="E441" s="11"/>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A442" s="4" t="s">
         <v>44</v>
       </c>
@@ -6956,7 +6959,7 @@
       <c r="D442" s="5"/>
       <c r="E442" s="11"/>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A443" s="4" t="s">
         <v>44</v>
       </c>
@@ -6969,7 +6972,7 @@
       <c r="D443" s="5"/>
       <c r="E443" s="11"/>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A444" s="4" t="s">
         <v>44</v>
       </c>
@@ -6982,7 +6985,7 @@
       <c r="D444" s="5"/>
       <c r="E444" s="11"/>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A445" s="4" t="s">
         <v>44</v>
       </c>
@@ -6995,7 +6998,7 @@
       <c r="D445" s="5"/>
       <c r="E445" s="11"/>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A446" s="4" t="s">
         <v>44</v>
       </c>
@@ -7008,7 +7011,7 @@
       <c r="D446" s="5"/>
       <c r="E446" s="11"/>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A447" s="4" t="s">
         <v>44</v>
       </c>
@@ -7021,7 +7024,7 @@
       <c r="D447" s="5"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A448" s="4" t="s">
         <v>44</v>
       </c>
@@ -7034,7 +7037,7 @@
       <c r="D448" s="5"/>
       <c r="E448" s="11"/>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A449" s="4" t="s">
         <v>44</v>
       </c>
@@ -7047,7 +7050,7 @@
       <c r="D449" s="5"/>
       <c r="E449" s="11"/>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A450" s="4" t="s">
         <v>44</v>
       </c>
@@ -7060,7 +7063,7 @@
       <c r="D450" s="5"/>
       <c r="E450" s="11"/>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A451" s="4" t="s">
         <v>44</v>
       </c>
@@ -7073,7 +7076,7 @@
       <c r="D451" s="5"/>
       <c r="E451" s="11"/>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A452" s="4" t="s">
         <v>44</v>
       </c>
@@ -7086,7 +7089,7 @@
       <c r="D452" s="5"/>
       <c r="E452" s="11"/>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A453" s="4" t="s">
         <v>44</v>
       </c>
@@ -7099,7 +7102,7 @@
       <c r="D453" s="5"/>
       <c r="E453" s="11"/>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A454" s="4" t="s">
         <v>44</v>
       </c>
@@ -7112,7 +7115,7 @@
       <c r="D454" s="5"/>
       <c r="E454" s="11"/>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A455" s="4" t="s">
         <v>44</v>
       </c>
@@ -7125,7 +7128,7 @@
       <c r="D455" s="5"/>
       <c r="E455" s="11"/>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A456" s="4" t="s">
         <v>44</v>
       </c>
@@ -7138,7 +7141,7 @@
       <c r="D456" s="5"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A457" s="4" t="s">
         <v>44</v>
       </c>
@@ -7151,7 +7154,7 @@
       <c r="D457" s="5"/>
       <c r="E457" s="11"/>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A458" s="4" t="s">
         <v>44</v>
       </c>
@@ -7164,7 +7167,7 @@
       <c r="D458" s="5"/>
       <c r="E458" s="11"/>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A459" s="4" t="s">
         <v>44</v>
       </c>
@@ -7177,7 +7180,7 @@
       <c r="D459" s="5"/>
       <c r="E459" s="11"/>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A460" s="4" t="s">
         <v>44</v>
       </c>
@@ -7190,7 +7193,7 @@
       <c r="D460" s="5"/>
       <c r="E460" s="11"/>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A461" s="4" t="s">
         <v>44</v>
       </c>
@@ -7203,7 +7206,7 @@
       <c r="D461" s="5"/>
       <c r="E461" s="11"/>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A462" s="4" t="s">
         <v>44</v>
       </c>
@@ -7216,7 +7219,7 @@
       <c r="D462" s="5"/>
       <c r="E462" s="11"/>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A463" s="4" t="s">
         <v>44</v>
       </c>
@@ -7229,7 +7232,7 @@
       <c r="D463" s="5"/>
       <c r="E463" s="11"/>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A464" s="4" t="s">
         <v>44</v>
       </c>
@@ -7242,7 +7245,7 @@
       <c r="D464" s="5"/>
       <c r="E464" s="11"/>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A465" s="4" t="s">
         <v>44</v>
       </c>
@@ -7255,7 +7258,7 @@
       <c r="D465" s="5"/>
       <c r="E465" s="11"/>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A466" s="4" t="s">
         <v>44</v>
       </c>
@@ -7268,7 +7271,7 @@
       <c r="D466" s="5"/>
       <c r="E466" s="11"/>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A467" s="4" t="s">
         <v>44</v>
       </c>
@@ -7281,7 +7284,7 @@
       <c r="D467" s="5"/>
       <c r="E467" s="11"/>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A468" s="4" t="s">
         <v>44</v>
       </c>
@@ -7294,7 +7297,7 @@
       <c r="D468" s="5"/>
       <c r="E468" s="11"/>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A469" s="4" t="s">
         <v>44</v>
       </c>
@@ -7307,7 +7310,7 @@
       <c r="D469" s="5"/>
       <c r="E469" s="11"/>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A470" s="4" t="s">
         <v>44</v>
       </c>
@@ -7320,7 +7323,7 @@
       <c r="D470" s="5"/>
       <c r="E470" s="11"/>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A471" s="4" t="s">
         <v>44</v>
       </c>
@@ -7333,7 +7336,7 @@
       <c r="D471" s="5"/>
       <c r="E471" s="11"/>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A472" s="4" t="s">
         <v>44</v>
       </c>
@@ -7346,7 +7349,7 @@
       <c r="D472" s="5"/>
       <c r="E472" s="11"/>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A473" s="4" t="s">
         <v>44</v>
       </c>
@@ -7359,7 +7362,7 @@
       <c r="D473" s="5"/>
       <c r="E473" s="11"/>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A474" s="4" t="s">
         <v>44</v>
       </c>
@@ -7372,7 +7375,7 @@
       <c r="D474" s="5"/>
       <c r="E474" s="11"/>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A475" s="4" t="s">
         <v>44</v>
       </c>
@@ -7385,7 +7388,7 @@
       <c r="D475" s="5"/>
       <c r="E475" s="11"/>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A476" s="4" t="s">
         <v>44</v>
       </c>
@@ -7398,7 +7401,7 @@
       <c r="D476" s="5"/>
       <c r="E476" s="11"/>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A477" s="4" t="s">
         <v>44</v>
       </c>
@@ -7411,7 +7414,7 @@
       <c r="D477" s="5"/>
       <c r="E477" s="11"/>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A478" s="4" t="s">
         <v>44</v>
       </c>
@@ -7424,7 +7427,7 @@
       <c r="D478" s="5"/>
       <c r="E478" s="11"/>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A479" s="4" t="s">
         <v>44</v>
       </c>
@@ -7437,7 +7440,7 @@
       <c r="D479" s="5"/>
       <c r="E479" s="11"/>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A480" s="4" t="s">
         <v>44</v>
       </c>
@@ -7450,7 +7453,7 @@
       <c r="D480" s="5"/>
       <c r="E480" s="11"/>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A481" s="4" t="s">
         <v>44</v>
       </c>
@@ -7463,7 +7466,7 @@
       <c r="D481" s="5"/>
       <c r="E481" s="11"/>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A482" s="4" t="s">
         <v>44</v>
       </c>
@@ -7476,7 +7479,7 @@
       <c r="D482" s="5"/>
       <c r="E482" s="11"/>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A483" s="4" t="s">
         <v>44</v>
       </c>
@@ -7489,7 +7492,7 @@
       <c r="D483" s="5"/>
       <c r="E483" s="11"/>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A484" s="4" t="s">
         <v>44</v>
       </c>
@@ -7502,7 +7505,7 @@
       <c r="D484" s="5"/>
       <c r="E484" s="11"/>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A485" s="4" t="s">
         <v>44</v>
       </c>
@@ -7515,7 +7518,7 @@
       <c r="D485" s="5"/>
       <c r="E485" s="11"/>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A486" s="4" t="s">
         <v>44</v>
       </c>
@@ -7528,7 +7531,7 @@
       <c r="D486" s="5"/>
       <c r="E486" s="11"/>
     </row>
-    <row r="487" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A487" s="4" t="s">
         <v>44</v>
       </c>
@@ -7541,7 +7544,7 @@
       <c r="D487" s="5"/>
       <c r="E487" s="11"/>
     </row>
-    <row r="488" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A488" s="4" t="s">
         <v>44</v>
       </c>
@@ -7554,7 +7557,7 @@
       <c r="D488" s="5"/>
       <c r="E488" s="11"/>
     </row>
-    <row r="489" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A489" s="4" t="s">
         <v>44</v>
       </c>
@@ -7567,7 +7570,7 @@
       <c r="D489" s="5"/>
       <c r="E489" s="11"/>
     </row>
-    <row r="490" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A490" s="4" t="s">
         <v>44</v>
       </c>
@@ -7580,7 +7583,7 @@
       <c r="D490" s="5"/>
       <c r="E490" s="11"/>
     </row>
-    <row r="491" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A491" s="4" t="s">
         <v>44</v>
       </c>
@@ -7593,7 +7596,7 @@
       <c r="D491" s="5"/>
       <c r="E491" s="11"/>
     </row>
-    <row r="492" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A492" s="4" t="s">
         <v>44</v>
       </c>
@@ -7606,7 +7609,7 @@
       <c r="D492" s="5"/>
       <c r="E492" s="11"/>
     </row>
-    <row r="493" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A493" s="4" t="s">
         <v>44</v>
       </c>
@@ -7619,7 +7622,7 @@
       <c r="D493" s="5"/>
       <c r="E493" s="11"/>
     </row>
-    <row r="494" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A494" s="4" t="s">
         <v>44</v>
       </c>
@@ -7632,7 +7635,7 @@
       <c r="D494" s="5"/>
       <c r="E494" s="11"/>
     </row>
-    <row r="495" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A495" s="4" t="s">
         <v>44</v>
       </c>
@@ -7645,7 +7648,7 @@
       <c r="D495" s="5"/>
       <c r="E495" s="11"/>
     </row>
-    <row r="496" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A496" s="4" t="s">
         <v>44</v>
       </c>
@@ -7658,7 +7661,7 @@
       <c r="D496" s="5"/>
       <c r="E496" s="11"/>
     </row>
-    <row r="497" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A497" s="4" t="s">
         <v>44</v>
       </c>
@@ -7671,7 +7674,7 @@
       <c r="D497" s="5"/>
       <c r="E497" s="11"/>
     </row>
-    <row r="498" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A498" s="4" t="s">
         <v>44</v>
       </c>
@@ -7684,7 +7687,7 @@
       <c r="D498" s="5"/>
       <c r="E498" s="11"/>
     </row>
-    <row r="499" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A499" s="4" t="s">
         <v>44</v>
       </c>
@@ -7697,7 +7700,7 @@
       <c r="D499" s="5"/>
       <c r="E499" s="11"/>
     </row>
-    <row r="500" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A500" s="4" t="s">
         <v>44</v>
       </c>
@@ -7710,7 +7713,7 @@
       <c r="D500" s="5"/>
       <c r="E500" s="11"/>
     </row>
-    <row r="501" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A501" s="4" t="s">
         <v>44</v>
       </c>
@@ -7723,7 +7726,7 @@
       <c r="D501" s="5"/>
       <c r="E501" s="11"/>
     </row>
-    <row r="502" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A502" s="4" t="s">
         <v>44</v>
       </c>
@@ -7736,7 +7739,7 @@
       <c r="D502" s="5"/>
       <c r="E502" s="11"/>
     </row>
-    <row r="503" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A503" s="4" t="s">
         <v>44</v>
       </c>
@@ -7749,7 +7752,7 @@
       <c r="D503" s="5"/>
       <c r="E503" s="11"/>
     </row>
-    <row r="504" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A504" s="4" t="s">
         <v>44</v>
       </c>
@@ -7762,7 +7765,7 @@
       <c r="D504" s="5"/>
       <c r="E504" s="11"/>
     </row>
-    <row r="505" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A505" s="4" t="s">
         <v>44</v>
       </c>
@@ -7775,7 +7778,7 @@
       <c r="D505" s="5"/>
       <c r="E505" s="11"/>
     </row>
-    <row r="506" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A506" s="4" t="s">
         <v>44</v>
       </c>
@@ -7788,7 +7791,7 @@
       <c r="D506" s="5"/>
       <c r="E506" s="11"/>
     </row>
-    <row r="507" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A507" s="4" t="s">
         <v>44</v>
       </c>
@@ -7801,7 +7804,7 @@
       <c r="D507" s="5"/>
       <c r="E507" s="11"/>
     </row>
-    <row r="508" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A508" s="4" t="s">
         <v>44</v>
       </c>
@@ -7814,7 +7817,7 @@
       <c r="D508" s="5"/>
       <c r="E508" s="11"/>
     </row>
-    <row r="509" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A509" s="4" t="s">
         <v>44</v>
       </c>
@@ -7827,7 +7830,7 @@
       <c r="D509" s="5"/>
       <c r="E509" s="11"/>
     </row>
-    <row r="510" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A510" s="4" t="s">
         <v>44</v>
       </c>
@@ -7840,7 +7843,7 @@
       <c r="D510" s="5"/>
       <c r="E510" s="11"/>
     </row>
-    <row r="511" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A511" s="4" t="s">
         <v>44</v>
       </c>
@@ -7853,7 +7856,7 @@
       <c r="D511" s="5"/>
       <c r="E511" s="11"/>
     </row>
-    <row r="512" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A512" s="4" t="s">
         <v>44</v>
       </c>
@@ -7866,7 +7869,7 @@
       <c r="D512" s="5"/>
       <c r="E512" s="11"/>
     </row>
-    <row r="513" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A513" s="4" t="s">
         <v>44</v>
       </c>
@@ -7879,7 +7882,7 @@
       <c r="D513" s="5"/>
       <c r="E513" s="11"/>
     </row>
-    <row r="514" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A514" s="4" t="s">
         <v>44</v>
       </c>
@@ -7892,7 +7895,7 @@
       <c r="D514" s="5"/>
       <c r="E514" s="11"/>
     </row>
-    <row r="515" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A515" s="4" t="s">
         <v>44</v>
       </c>
@@ -7905,7 +7908,7 @@
       <c r="D515" s="5"/>
       <c r="E515" s="11"/>
     </row>
-    <row r="516" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A516" s="4" t="s">
         <v>44</v>
       </c>
@@ -7918,7 +7921,7 @@
       <c r="D516" s="5"/>
       <c r="E516" s="11"/>
     </row>
-    <row r="517" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A517" s="4" t="s">
         <v>44</v>
       </c>
@@ -7931,7 +7934,7 @@
       <c r="D517" s="5"/>
       <c r="E517" s="11"/>
     </row>
-    <row r="518" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A518" s="4" t="s">
         <v>44</v>
       </c>
@@ -7944,7 +7947,7 @@
       <c r="D518" s="5"/>
       <c r="E518" s="11"/>
     </row>
-    <row r="519" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A519" s="4" t="s">
         <v>44</v>
       </c>
@@ -7957,7 +7960,7 @@
       <c r="D519" s="5"/>
       <c r="E519" s="11"/>
     </row>
-    <row r="520" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A520" s="4" t="s">
         <v>44</v>
       </c>
@@ -7970,7 +7973,7 @@
       <c r="D520" s="5"/>
       <c r="E520" s="11"/>
     </row>
-    <row r="521" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A521" s="4" t="s">
         <v>44</v>
       </c>
@@ -7983,7 +7986,7 @@
       <c r="D521" s="5"/>
       <c r="E521" s="11"/>
     </row>
-    <row r="522" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A522" s="4" t="s">
         <v>44</v>
       </c>
@@ -7996,7 +7999,7 @@
       <c r="D522" s="5"/>
       <c r="E522" s="11"/>
     </row>
-    <row r="523" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A523" s="4" t="s">
         <v>44</v>
       </c>
@@ -8009,7 +8012,7 @@
       <c r="D523" s="5"/>
       <c r="E523" s="11"/>
     </row>
-    <row r="524" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A524" s="4" t="s">
         <v>44</v>
       </c>
@@ -8022,7 +8025,7 @@
       <c r="D524" s="5"/>
       <c r="E524" s="11"/>
     </row>
-    <row r="525" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A525" s="4" t="s">
         <v>44</v>
       </c>
@@ -8035,7 +8038,7 @@
       <c r="D525" s="5"/>
       <c r="E525" s="11"/>
     </row>
-    <row r="526" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A526" s="4" t="s">
         <v>44</v>
       </c>
@@ -8048,7 +8051,7 @@
       <c r="D526" s="5"/>
       <c r="E526" s="11"/>
     </row>
-    <row r="527" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A527" s="4" t="s">
         <v>44</v>
       </c>
@@ -8061,7 +8064,7 @@
       <c r="D527" s="5"/>
       <c r="E527" s="11"/>
     </row>
-    <row r="528" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A528" s="4" t="s">
         <v>44</v>
       </c>
@@ -8074,7 +8077,7 @@
       <c r="D528" s="5"/>
       <c r="E528" s="11"/>
     </row>
-    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A529" s="4" t="s">
         <v>44</v>
       </c>
@@ -8087,7 +8090,7 @@
       <c r="D529" s="5"/>
       <c r="E529" s="11"/>
     </row>
-    <row r="530" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A530" s="4" t="s">
         <v>44</v>
       </c>
@@ -8100,7 +8103,7 @@
       <c r="D530" s="5"/>
       <c r="E530" s="11"/>
     </row>
-    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A531" s="4" t="s">
         <v>44</v>
       </c>
@@ -8113,7 +8116,7 @@
       <c r="D531" s="5"/>
       <c r="E531" s="11"/>
     </row>
-    <row r="532" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A532" s="4" t="s">
         <v>44</v>
       </c>
@@ -8126,7 +8129,7 @@
       <c r="D532" s="5"/>
       <c r="E532" s="11"/>
     </row>
-    <row r="533" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A533" s="4" t="s">
         <v>44</v>
       </c>
@@ -8139,7 +8142,7 @@
       <c r="D533" s="5"/>
       <c r="E533" s="11"/>
     </row>
-    <row r="534" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A534" s="4" t="s">
         <v>44</v>
       </c>
@@ -8152,7 +8155,7 @@
       <c r="D534" s="5"/>
       <c r="E534" s="11"/>
     </row>
-    <row r="535" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A535" s="4" t="s">
         <v>44</v>
       </c>
@@ -8165,7 +8168,7 @@
       <c r="D535" s="5"/>
       <c r="E535" s="11"/>
     </row>
-    <row r="536" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A536" s="4" t="s">
         <v>44</v>
       </c>
@@ -8178,7 +8181,7 @@
       <c r="D536" s="5"/>
       <c r="E536" s="11"/>
     </row>
-    <row r="537" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A537" s="4" t="s">
         <v>44</v>
       </c>
@@ -8191,7 +8194,7 @@
       <c r="D537" s="5"/>
       <c r="E537" s="11"/>
     </row>
-    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A538" s="4" t="s">
         <v>44</v>
       </c>
@@ -8204,7 +8207,7 @@
       <c r="D538" s="5"/>
       <c r="E538" s="11"/>
     </row>
-    <row r="539" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A539" s="4" t="s">
         <v>44</v>
       </c>
@@ -8217,7 +8220,7 @@
       <c r="D539" s="5"/>
       <c r="E539" s="11"/>
     </row>
-    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A540" s="4" t="s">
         <v>44</v>
       </c>
@@ -8230,7 +8233,7 @@
       <c r="D540" s="5"/>
       <c r="E540" s="11"/>
     </row>
-    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A541" s="4" t="s">
         <v>44</v>
       </c>
@@ -8243,7 +8246,7 @@
       <c r="D541" s="5"/>
       <c r="E541" s="11"/>
     </row>
-    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A542" s="4" t="s">
         <v>44</v>
       </c>
@@ -8256,7 +8259,7 @@
       <c r="D542" s="5"/>
       <c r="E542" s="11"/>
     </row>
-    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A543" s="4" t="s">
         <v>44</v>
       </c>
@@ -8269,7 +8272,7 @@
       <c r="D543" s="5"/>
       <c r="E543" s="11"/>
     </row>
-    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A544" s="4" t="s">
         <v>44</v>
       </c>
@@ -8282,7 +8285,7 @@
       <c r="D544" s="5"/>
       <c r="E544" s="11"/>
     </row>
-    <row r="545" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A545" s="4" t="s">
         <v>44</v>
       </c>
@@ -8295,7 +8298,7 @@
       <c r="D545" s="5"/>
       <c r="E545" s="11"/>
     </row>
-    <row r="546" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A546" s="4" t="s">
         <v>45</v>
       </c>
@@ -8308,7 +8311,7 @@
       <c r="D546" s="5"/>
       <c r="E546" s="11"/>
     </row>
-    <row r="547" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A547" s="4" t="s">
         <v>45</v>
       </c>
@@ -8321,7 +8324,7 @@
       <c r="D547" s="5"/>
       <c r="E547" s="11"/>
     </row>
-    <row r="548" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A548" s="4" t="s">
         <v>45</v>
       </c>
@@ -8334,7 +8337,7 @@
       <c r="D548" s="5"/>
       <c r="E548" s="11"/>
     </row>
-    <row r="549" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A549" s="4" t="s">
         <v>45</v>
       </c>
@@ -8347,7 +8350,7 @@
       <c r="D549" s="5"/>
       <c r="E549" s="11"/>
     </row>
-    <row r="550" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A550" s="4" t="s">
         <v>45</v>
       </c>
@@ -8360,7 +8363,7 @@
       <c r="D550" s="5"/>
       <c r="E550" s="11"/>
     </row>
-    <row r="551" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A551" s="4" t="s">
         <v>45</v>
       </c>
@@ -8373,7 +8376,7 @@
       <c r="D551" s="5"/>
       <c r="E551" s="11"/>
     </row>
-    <row r="552" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A552" s="4" t="s">
         <v>45</v>
       </c>
@@ -8386,7 +8389,7 @@
       <c r="D552" s="5"/>
       <c r="E552" s="11"/>
     </row>
-    <row r="553" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A553" s="4" t="s">
         <v>45</v>
       </c>
@@ -8399,7 +8402,7 @@
       <c r="D553" s="5"/>
       <c r="E553" s="11"/>
     </row>
-    <row r="554" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A554" s="4" t="s">
         <v>45</v>
       </c>
@@ -8412,7 +8415,7 @@
       <c r="D554" s="5"/>
       <c r="E554" s="11"/>
     </row>
-    <row r="555" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A555" s="4" t="s">
         <v>45</v>
       </c>
@@ -8425,7 +8428,7 @@
       <c r="D555" s="5"/>
       <c r="E555" s="11"/>
     </row>
-    <row r="556" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A556" s="4" t="s">
         <v>45</v>
       </c>
@@ -8438,7 +8441,7 @@
       <c r="D556" s="5"/>
       <c r="E556" s="11"/>
     </row>
-    <row r="557" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A557" s="4" t="s">
         <v>45</v>
       </c>
@@ -8451,7 +8454,7 @@
       <c r="D557" s="5"/>
       <c r="E557" s="11"/>
     </row>
-    <row r="558" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A558" s="4" t="s">
         <v>45</v>
       </c>
@@ -8464,7 +8467,7 @@
       <c r="D558" s="5"/>
       <c r="E558" s="11"/>
     </row>
-    <row r="559" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A559" s="4" t="s">
         <v>45</v>
       </c>
@@ -8477,7 +8480,7 @@
       <c r="D559" s="5"/>
       <c r="E559" s="11"/>
     </row>
-    <row r="560" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A560" s="4" t="s">
         <v>45</v>
       </c>
@@ -8490,7 +8493,7 @@
       <c r="D560" s="5"/>
       <c r="E560" s="11"/>
     </row>
-    <row r="561" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A561" s="4" t="s">
         <v>45</v>
       </c>
@@ -8503,7 +8506,7 @@
       <c r="D561" s="5"/>
       <c r="E561" s="11"/>
     </row>
-    <row r="562" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A562" s="4" t="s">
         <v>45</v>
       </c>
@@ -8516,7 +8519,7 @@
       <c r="D562" s="5"/>
       <c r="E562" s="11"/>
     </row>
-    <row r="563" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A563" s="4" t="s">
         <v>45</v>
       </c>
@@ -8529,7 +8532,7 @@
       <c r="D563" s="5"/>
       <c r="E563" s="11"/>
     </row>
-    <row r="564" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A564" s="4" t="s">
         <v>45</v>
       </c>
@@ -8542,7 +8545,7 @@
       <c r="D564" s="5"/>
       <c r="E564" s="11"/>
     </row>
-    <row r="565" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A565" s="4" t="s">
         <v>45</v>
       </c>
@@ -8555,7 +8558,7 @@
       <c r="D565" s="5"/>
       <c r="E565" s="11"/>
     </row>
-    <row r="566" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A566" s="4" t="s">
         <v>45</v>
       </c>
@@ -8568,7 +8571,7 @@
       <c r="D566" s="5"/>
       <c r="E566" s="11"/>
     </row>
-    <row r="567" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A567" s="4" t="s">
         <v>45</v>
       </c>
@@ -8581,7 +8584,7 @@
       <c r="D567" s="5"/>
       <c r="E567" s="11"/>
     </row>
-    <row r="568" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A568" s="4" t="s">
         <v>45</v>
       </c>
@@ -8594,7 +8597,7 @@
       <c r="D568" s="5"/>
       <c r="E568" s="11"/>
     </row>
-    <row r="569" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A569" s="4" t="s">
         <v>45</v>
       </c>
@@ -8607,7 +8610,7 @@
       <c r="D569" s="5"/>
       <c r="E569" s="11"/>
     </row>
-    <row r="570" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A570" s="4" t="s">
         <v>45</v>
       </c>
@@ -8620,7 +8623,7 @@
       <c r="D570" s="5"/>
       <c r="E570" s="11"/>
     </row>
-    <row r="571" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A571" s="4" t="s">
         <v>45</v>
       </c>
@@ -8633,7 +8636,7 @@
       <c r="D571" s="5"/>
       <c r="E571" s="11"/>
     </row>
-    <row r="572" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A572" s="4" t="s">
         <v>45</v>
       </c>
@@ -8646,7 +8649,7 @@
       <c r="D572" s="5"/>
       <c r="E572" s="11"/>
     </row>
-    <row r="573" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A573" s="4" t="s">
         <v>45</v>
       </c>
@@ -8659,7 +8662,7 @@
       <c r="D573" s="5"/>
       <c r="E573" s="11"/>
     </row>
-    <row r="574" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A574" s="4" t="s">
         <v>45</v>
       </c>
@@ -8672,7 +8675,7 @@
       <c r="D574" s="5"/>
       <c r="E574" s="11"/>
     </row>
-    <row r="575" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A575" s="4" t="s">
         <v>45</v>
       </c>
@@ -8685,7 +8688,7 @@
       <c r="D575" s="5"/>
       <c r="E575" s="11"/>
     </row>
-    <row r="576" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A576" s="4" t="s">
         <v>45</v>
       </c>
@@ -8698,7 +8701,7 @@
       <c r="D576" s="5"/>
       <c r="E576" s="11"/>
     </row>
-    <row r="577" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A577" s="4" t="s">
         <v>45</v>
       </c>
@@ -8711,7 +8714,7 @@
       <c r="D577" s="5"/>
       <c r="E577" s="11"/>
     </row>
-    <row r="578" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A578" s="4" t="s">
         <v>45</v>
       </c>
@@ -8724,7 +8727,7 @@
       <c r="D578" s="5"/>
       <c r="E578" s="11"/>
     </row>
-    <row r="579" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A579" s="4" t="s">
         <v>45</v>
       </c>
@@ -8737,7 +8740,7 @@
       <c r="D579" s="5"/>
       <c r="E579" s="11"/>
     </row>
-    <row r="580" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A580" s="4" t="s">
         <v>45</v>
       </c>
@@ -8750,7 +8753,7 @@
       <c r="D580" s="5"/>
       <c r="E580" s="11"/>
     </row>
-    <row r="581" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A581" s="4" t="s">
         <v>45</v>
       </c>
@@ -8763,7 +8766,7 @@
       <c r="D581" s="5"/>
       <c r="E581" s="11"/>
     </row>
-    <row r="582" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A582" s="4" t="s">
         <v>45</v>
       </c>
@@ -8776,7 +8779,7 @@
       <c r="D582" s="5"/>
       <c r="E582" s="11"/>
     </row>
-    <row r="583" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A583" s="4" t="s">
         <v>45</v>
       </c>
@@ -8789,7 +8792,7 @@
       <c r="D583" s="5"/>
       <c r="E583" s="11"/>
     </row>
-    <row r="584" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A584" s="4" t="s">
         <v>45</v>
       </c>
@@ -8802,7 +8805,7 @@
       <c r="D584" s="5"/>
       <c r="E584" s="11"/>
     </row>
-    <row r="585" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A585" s="4" t="s">
         <v>45</v>
       </c>
@@ -8815,7 +8818,7 @@
       <c r="D585" s="5"/>
       <c r="E585" s="11"/>
     </row>
-    <row r="586" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A586" s="4" t="s">
         <v>45</v>
       </c>
@@ -8828,7 +8831,7 @@
       <c r="D586" s="5"/>
       <c r="E586" s="11"/>
     </row>
-    <row r="587" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A587" s="4" t="s">
         <v>45</v>
       </c>
@@ -8841,7 +8844,7 @@
       <c r="D587" s="5"/>
       <c r="E587" s="11"/>
     </row>
-    <row r="588" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A588" s="4" t="s">
         <v>45</v>
       </c>
@@ -8854,7 +8857,7 @@
       <c r="D588" s="5"/>
       <c r="E588" s="11"/>
     </row>
-    <row r="589" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A589" s="4" t="s">
         <v>45</v>
       </c>
@@ -8867,7 +8870,7 @@
       <c r="D589" s="5"/>
       <c r="E589" s="11"/>
     </row>
-    <row r="590" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A590" s="4" t="s">
         <v>45</v>
       </c>
@@ -8880,7 +8883,7 @@
       <c r="D590" s="5"/>
       <c r="E590" s="11"/>
     </row>
-    <row r="591" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A591" s="4" t="s">
         <v>45</v>
       </c>
@@ -8893,7 +8896,7 @@
       <c r="D591" s="5"/>
       <c r="E591" s="11"/>
     </row>
-    <row r="592" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A592" s="4" t="s">
         <v>45</v>
       </c>
@@ -8906,7 +8909,7 @@
       <c r="D592" s="5"/>
       <c r="E592" s="11"/>
     </row>
-    <row r="593" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A593" s="4" t="s">
         <v>45</v>
       </c>
@@ -8919,7 +8922,7 @@
       <c r="D593" s="5"/>
       <c r="E593" s="11"/>
     </row>
-    <row r="594" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A594" s="4" t="s">
         <v>45</v>
       </c>
@@ -8932,7 +8935,7 @@
       <c r="D594" s="5"/>
       <c r="E594" s="11"/>
     </row>
-    <row r="595" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A595" s="4" t="s">
         <v>45</v>
       </c>
@@ -8945,7 +8948,7 @@
       <c r="D595" s="5"/>
       <c r="E595" s="11"/>
     </row>
-    <row r="596" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A596" s="4" t="s">
         <v>45</v>
       </c>
@@ -8958,7 +8961,7 @@
       <c r="D596" s="5"/>
       <c r="E596" s="11"/>
     </row>
-    <row r="597" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A597" s="4" t="s">
         <v>45</v>
       </c>
@@ -8971,7 +8974,7 @@
       <c r="D597" s="5"/>
       <c r="E597" s="11"/>
     </row>
-    <row r="598" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A598" s="4" t="s">
         <v>45</v>
       </c>
@@ -8984,7 +8987,7 @@
       <c r="D598" s="5"/>
       <c r="E598" s="11"/>
     </row>
-    <row r="599" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A599" s="4" t="s">
         <v>45</v>
       </c>
@@ -9001,7 +9004,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="600" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A600" s="4" t="s">
         <v>45</v>
       </c>
@@ -9014,7 +9017,7 @@
       <c r="D600" s="5"/>
       <c r="E600" s="11"/>
     </row>
-    <row r="601" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A601" s="4" t="s">
         <v>45</v>
       </c>
@@ -9027,7 +9030,7 @@
       <c r="D601" s="5"/>
       <c r="E601" s="11"/>
     </row>
-    <row r="602" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A602" s="4" t="s">
         <v>45</v>
       </c>
@@ -9040,7 +9043,7 @@
       <c r="D602" s="5"/>
       <c r="E602" s="11"/>
     </row>
-    <row r="603" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A603" s="4" t="s">
         <v>45</v>
       </c>
@@ -9053,7 +9056,7 @@
       <c r="D603" s="5"/>
       <c r="E603" s="11"/>
     </row>
-    <row r="604" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A604" s="4" t="s">
         <v>45</v>
       </c>
@@ -9066,7 +9069,7 @@
       <c r="D604" s="5"/>
       <c r="E604" s="11"/>
     </row>
-    <row r="605" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A605" s="4" t="s">
         <v>45</v>
       </c>
@@ -9079,7 +9082,7 @@
       <c r="D605" s="5"/>
       <c r="E605" s="11"/>
     </row>
-    <row r="606" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A606" s="4" t="s">
         <v>45</v>
       </c>
@@ -9092,7 +9095,7 @@
       <c r="D606" s="5"/>
       <c r="E606" s="11"/>
     </row>
-    <row r="607" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A607" s="4" t="s">
         <v>45</v>
       </c>
@@ -9105,7 +9108,7 @@
       <c r="D607" s="5"/>
       <c r="E607" s="11"/>
     </row>
-    <row r="608" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A608" s="4" t="s">
         <v>45</v>
       </c>
@@ -9118,7 +9121,7 @@
       <c r="D608" s="5"/>
       <c r="E608" s="11"/>
     </row>
-    <row r="609" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A609" s="4" t="s">
         <v>45</v>
       </c>
@@ -9131,7 +9134,7 @@
       <c r="D609" s="5"/>
       <c r="E609" s="11"/>
     </row>
-    <row r="610" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A610" s="4" t="s">
         <v>45</v>
       </c>
@@ -9144,7 +9147,7 @@
       <c r="D610" s="5"/>
       <c r="E610" s="11"/>
     </row>
-    <row r="611" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A611" s="4" t="s">
         <v>45</v>
       </c>
@@ -9157,7 +9160,7 @@
       <c r="D611" s="5"/>
       <c r="E611" s="11"/>
     </row>
-    <row r="612" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A612" s="4" t="s">
         <v>45</v>
       </c>
@@ -9170,7 +9173,7 @@
       <c r="D612" s="5"/>
       <c r="E612" s="11"/>
     </row>
-    <row r="613" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A613" s="4" t="s">
         <v>45</v>
       </c>
@@ -9183,7 +9186,7 @@
       <c r="D613" s="5"/>
       <c r="E613" s="11"/>
     </row>
-    <row r="614" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A614" s="4" t="s">
         <v>45</v>
       </c>
@@ -9196,7 +9199,7 @@
       <c r="D614" s="5"/>
       <c r="E614" s="11"/>
     </row>
-    <row r="615" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A615" s="4" t="s">
         <v>45</v>
       </c>
@@ -9209,7 +9212,7 @@
       <c r="D615" s="5"/>
       <c r="E615" s="11"/>
     </row>
-    <row r="616" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A616" s="4" t="s">
         <v>45</v>
       </c>
@@ -9222,7 +9225,7 @@
       <c r="D616" s="5"/>
       <c r="E616" s="11"/>
     </row>
-    <row r="617" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A617" s="4" t="s">
         <v>45</v>
       </c>
@@ -9235,7 +9238,7 @@
       <c r="D617" s="5"/>
       <c r="E617" s="11"/>
     </row>
-    <row r="618" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A618" s="4" t="s">
         <v>45</v>
       </c>
@@ -9248,7 +9251,7 @@
       <c r="D618" s="5"/>
       <c r="E618" s="11"/>
     </row>
-    <row r="619" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A619" s="4" t="s">
         <v>45</v>
       </c>
@@ -9261,7 +9264,7 @@
       <c r="D619" s="5"/>
       <c r="E619" s="11"/>
     </row>
-    <row r="620" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A620" s="4" t="s">
         <v>45</v>
       </c>
@@ -9274,7 +9277,7 @@
       <c r="D620" s="5"/>
       <c r="E620" s="11"/>
     </row>
-    <row r="621" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A621" s="4" t="s">
         <v>45</v>
       </c>
@@ -9287,7 +9290,7 @@
       <c r="D621" s="5"/>
       <c r="E621" s="11"/>
     </row>
-    <row r="622" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A622" s="4" t="s">
         <v>45</v>
       </c>
@@ -9300,7 +9303,7 @@
       <c r="D622" s="5"/>
       <c r="E622" s="11"/>
     </row>
-    <row r="623" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A623" s="4" t="s">
         <v>45</v>
       </c>
@@ -9313,7 +9316,7 @@
       <c r="D623" s="5"/>
       <c r="E623" s="11"/>
     </row>
-    <row r="624" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A624" s="4" t="s">
         <v>45</v>
       </c>
@@ -9326,7 +9329,7 @@
       <c r="D624" s="5"/>
       <c r="E624" s="11"/>
     </row>
-    <row r="625" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A625" s="4" t="s">
         <v>45</v>
       </c>
@@ -9339,7 +9342,7 @@
       <c r="D625" s="5"/>
       <c r="E625" s="11"/>
     </row>
-    <row r="626" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A626" s="4" t="s">
         <v>45</v>
       </c>
@@ -9352,7 +9355,7 @@
       <c r="D626" s="5"/>
       <c r="E626" s="11"/>
     </row>
-    <row r="627" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A627" s="4" t="s">
         <v>45</v>
       </c>
@@ -9365,7 +9368,7 @@
       <c r="D627" s="5"/>
       <c r="E627" s="11"/>
     </row>
-    <row r="628" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A628" s="4" t="s">
         <v>45</v>
       </c>
@@ -9378,7 +9381,7 @@
       <c r="D628" s="5"/>
       <c r="E628" s="11"/>
     </row>
-    <row r="629" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A629" s="4" t="s">
         <v>45</v>
       </c>
@@ -9391,7 +9394,7 @@
       <c r="D629" s="5"/>
       <c r="E629" s="11"/>
     </row>
-    <row r="630" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A630" s="4" t="s">
         <v>45</v>
       </c>
@@ -9404,7 +9407,7 @@
       <c r="D630" s="5"/>
       <c r="E630" s="11"/>
     </row>
-    <row r="631" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A631" s="4" t="s">
         <v>45</v>
       </c>
@@ -9417,7 +9420,7 @@
       <c r="D631" s="5"/>
       <c r="E631" s="11"/>
     </row>
-    <row r="632" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A632" s="4" t="s">
         <v>45</v>
       </c>
@@ -9430,7 +9433,7 @@
       <c r="D632" s="5"/>
       <c r="E632" s="11"/>
     </row>
-    <row r="633" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A633" s="4" t="s">
         <v>45</v>
       </c>
@@ -9443,7 +9446,7 @@
       <c r="D633" s="5"/>
       <c r="E633" s="11"/>
     </row>
-    <row r="634" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A634" s="4" t="s">
         <v>45</v>
       </c>
@@ -9456,7 +9459,7 @@
       <c r="D634" s="5"/>
       <c r="E634" s="11"/>
     </row>
-    <row r="635" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A635" s="4" t="s">
         <v>45</v>
       </c>
@@ -9469,7 +9472,7 @@
       <c r="D635" s="5"/>
       <c r="E635" s="11"/>
     </row>
-    <row r="636" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A636" s="4" t="s">
         <v>45</v>
       </c>
@@ -9482,7 +9485,7 @@
       <c r="D636" s="5"/>
       <c r="E636" s="11"/>
     </row>
-    <row r="637" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A637" s="4" t="s">
         <v>45</v>
       </c>
@@ -9495,7 +9498,7 @@
       <c r="D637" s="5"/>
       <c r="E637" s="11"/>
     </row>
-    <row r="638" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A638" s="4" t="s">
         <v>45</v>
       </c>
@@ -9508,7 +9511,7 @@
       <c r="D638" s="5"/>
       <c r="E638" s="11"/>
     </row>
-    <row r="639" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A639" s="4" t="s">
         <v>45</v>
       </c>
@@ -9521,7 +9524,7 @@
       <c r="D639" s="5"/>
       <c r="E639" s="11"/>
     </row>
-    <row r="640" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A640" s="4" t="s">
         <v>45</v>
       </c>
@@ -9534,7 +9537,7 @@
       <c r="D640" s="5"/>
       <c r="E640" s="11"/>
     </row>
-    <row r="641" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A641" s="4" t="s">
         <v>45</v>
       </c>
@@ -9547,7 +9550,7 @@
       <c r="D641" s="5"/>
       <c r="E641" s="11"/>
     </row>
-    <row r="642" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A642" s="4" t="s">
         <v>45</v>
       </c>
@@ -9560,7 +9563,7 @@
       <c r="D642" s="5"/>
       <c r="E642" s="11"/>
     </row>
-    <row r="643" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A643" s="4" t="s">
         <v>45</v>
       </c>
@@ -9573,7 +9576,7 @@
       <c r="D643" s="5"/>
       <c r="E643" s="11"/>
     </row>
-    <row r="644" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A644" s="4" t="s">
         <v>45</v>
       </c>
@@ -9586,7 +9589,7 @@
       <c r="D644" s="5"/>
       <c r="E644" s="11"/>
     </row>
-    <row r="645" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A645" s="4" t="s">
         <v>45</v>
       </c>
@@ -9599,7 +9602,7 @@
       <c r="D645" s="5"/>
       <c r="E645" s="11"/>
     </row>
-    <row r="646" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A646" s="4" t="s">
         <v>45</v>
       </c>
@@ -9612,7 +9615,7 @@
       <c r="D646" s="5"/>
       <c r="E646" s="11"/>
     </row>
-    <row r="647" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A647" s="4" t="s">
         <v>45</v>
       </c>
@@ -9625,7 +9628,7 @@
       <c r="D647" s="5"/>
       <c r="E647" s="11"/>
     </row>
-    <row r="648" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A648" s="4" t="s">
         <v>45</v>
       </c>
@@ -9638,7 +9641,7 @@
       <c r="D648" s="5"/>
       <c r="E648" s="11"/>
     </row>
-    <row r="649" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A649" s="4" t="s">
         <v>45</v>
       </c>
@@ -9651,7 +9654,7 @@
       <c r="D649" s="5"/>
       <c r="E649" s="11"/>
     </row>
-    <row r="650" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A650" s="4" t="s">
         <v>45</v>
       </c>
@@ -9664,7 +9667,7 @@
       <c r="D650" s="5"/>
       <c r="E650" s="11"/>
     </row>
-    <row r="651" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A651" s="4" t="s">
         <v>45</v>
       </c>
@@ -9677,7 +9680,7 @@
       <c r="D651" s="5"/>
       <c r="E651" s="11"/>
     </row>
-    <row r="652" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A652" s="4" t="s">
         <v>45</v>
       </c>
@@ -9690,7 +9693,7 @@
       <c r="D652" s="5"/>
       <c r="E652" s="11"/>
     </row>
-    <row r="653" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A653" s="4" t="s">
         <v>45</v>
       </c>
@@ -9703,7 +9706,7 @@
       <c r="D653" s="5"/>
       <c r="E653" s="11"/>
     </row>
-    <row r="654" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A654" s="4" t="s">
         <v>45</v>
       </c>
@@ -9716,7 +9719,7 @@
       <c r="D654" s="5"/>
       <c r="E654" s="11"/>
     </row>
-    <row r="655" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A655" s="4" t="s">
         <v>45</v>
       </c>
@@ -9729,7 +9732,7 @@
       <c r="D655" s="5"/>
       <c r="E655" s="11"/>
     </row>
-    <row r="656" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A656" s="4" t="s">
         <v>45</v>
       </c>
@@ -9742,7 +9745,7 @@
       <c r="D656" s="5"/>
       <c r="E656" s="11"/>
     </row>
-    <row r="657" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A657" s="4" t="s">
         <v>45</v>
       </c>
@@ -9755,7 +9758,7 @@
       <c r="D657" s="5"/>
       <c r="E657" s="11"/>
     </row>
-    <row r="658" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A658" s="4" t="s">
         <v>45</v>
       </c>
@@ -9768,7 +9771,7 @@
       <c r="D658" s="5"/>
       <c r="E658" s="11"/>
     </row>
-    <row r="659" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A659" s="4" t="s">
         <v>45</v>
       </c>
@@ -9781,7 +9784,7 @@
       <c r="D659" s="5"/>
       <c r="E659" s="11"/>
     </row>
-    <row r="660" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A660" s="4" t="s">
         <v>45</v>
       </c>
@@ -9794,7 +9797,7 @@
       <c r="D660" s="5"/>
       <c r="E660" s="11"/>
     </row>
-    <row r="661" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A661" s="4" t="s">
         <v>45</v>
       </c>
@@ -9807,7 +9810,7 @@
       <c r="D661" s="5"/>
       <c r="E661" s="11"/>
     </row>
-    <row r="662" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A662" s="4" t="s">
         <v>45</v>
       </c>
@@ -9820,7 +9823,7 @@
       <c r="D662" s="5"/>
       <c r="E662" s="11"/>
     </row>
-    <row r="663" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A663" s="4" t="s">
         <v>45</v>
       </c>
@@ -9833,7 +9836,7 @@
       <c r="D663" s="5"/>
       <c r="E663" s="11"/>
     </row>
-    <row r="664" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A664" s="4" t="s">
         <v>45</v>
       </c>
@@ -9846,7 +9849,7 @@
       <c r="D664" s="5"/>
       <c r="E664" s="11"/>
     </row>
-    <row r="665" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A665" s="4" t="s">
         <v>45</v>
       </c>
@@ -9859,7 +9862,7 @@
       <c r="D665" s="5"/>
       <c r="E665" s="11"/>
     </row>
-    <row r="666" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A666" s="4" t="s">
         <v>46</v>
       </c>
@@ -9872,7 +9875,7 @@
       <c r="D666" s="5"/>
       <c r="E666" s="11"/>
     </row>
-    <row r="667" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A667" s="4" t="s">
         <v>46</v>
       </c>
@@ -9885,7 +9888,7 @@
       <c r="D667" s="5"/>
       <c r="E667" s="11"/>
     </row>
-    <row r="668" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A668" s="4" t="s">
         <v>46</v>
       </c>
@@ -9898,7 +9901,7 @@
       <c r="D668" s="5"/>
       <c r="E668" s="11"/>
     </row>
-    <row r="669" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A669" s="4" t="s">
         <v>46</v>
       </c>
@@ -9911,7 +9914,7 @@
       <c r="D669" s="5"/>
       <c r="E669" s="11"/>
     </row>
-    <row r="670" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A670" s="4" t="s">
         <v>46</v>
       </c>
@@ -9924,7 +9927,7 @@
       <c r="D670" s="5"/>
       <c r="E670" s="11"/>
     </row>
-    <row r="671" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A671" s="4" t="s">
         <v>46</v>
       </c>
@@ -9937,7 +9940,7 @@
       <c r="D671" s="5"/>
       <c r="E671" s="11"/>
     </row>
-    <row r="672" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A672" s="4" t="s">
         <v>46</v>
       </c>
@@ -9950,7 +9953,7 @@
       <c r="D672" s="5"/>
       <c r="E672" s="11"/>
     </row>
-    <row r="673" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A673" s="4" t="s">
         <v>46</v>
       </c>
@@ -9963,7 +9966,7 @@
       <c r="D673" s="5"/>
       <c r="E673" s="11"/>
     </row>
-    <row r="674" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A674" s="4" t="s">
         <v>46</v>
       </c>
@@ -9976,7 +9979,7 @@
       <c r="D674" s="5"/>
       <c r="E674" s="11"/>
     </row>
-    <row r="675" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A675" s="4" t="s">
         <v>46</v>
       </c>
@@ -9989,7 +9992,7 @@
       <c r="D675" s="5"/>
       <c r="E675" s="11"/>
     </row>
-    <row r="676" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A676" s="4" t="s">
         <v>46</v>
       </c>
@@ -10002,7 +10005,7 @@
       <c r="D676" s="5"/>
       <c r="E676" s="11"/>
     </row>
-    <row r="677" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A677" s="4" t="s">
         <v>46</v>
       </c>
@@ -10015,7 +10018,7 @@
       <c r="D677" s="5"/>
       <c r="E677" s="11"/>
     </row>
-    <row r="678" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A678" s="4" t="s">
         <v>46</v>
       </c>
@@ -10028,7 +10031,7 @@
       <c r="D678" s="5"/>
       <c r="E678" s="11"/>
     </row>
-    <row r="679" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A679" s="4" t="s">
         <v>46</v>
       </c>
@@ -10041,7 +10044,7 @@
       <c r="D679" s="5"/>
       <c r="E679" s="11"/>
     </row>
-    <row r="680" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A680" s="4" t="s">
         <v>46</v>
       </c>
@@ -10054,7 +10057,7 @@
       <c r="D680" s="5"/>
       <c r="E680" s="11"/>
     </row>
-    <row r="681" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A681" s="4" t="s">
         <v>46</v>
       </c>
@@ -10067,7 +10070,7 @@
       <c r="D681" s="5"/>
       <c r="E681" s="11"/>
     </row>
-    <row r="682" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A682" s="4" t="s">
         <v>46</v>
       </c>
@@ -10080,7 +10083,7 @@
       <c r="D682" s="5"/>
       <c r="E682" s="11"/>
     </row>
-    <row r="683" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A683" s="4" t="s">
         <v>46</v>
       </c>
@@ -10093,7 +10096,7 @@
       <c r="D683" s="5"/>
       <c r="E683" s="11"/>
     </row>
-    <row r="684" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A684" s="4" t="s">
         <v>46</v>
       </c>
@@ -10106,7 +10109,7 @@
       <c r="D684" s="5"/>
       <c r="E684" s="11"/>
     </row>
-    <row r="685" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A685" s="4" t="s">
         <v>46</v>
       </c>
@@ -10119,7 +10122,7 @@
       <c r="D685" s="5"/>
       <c r="E685" s="11"/>
     </row>
-    <row r="686" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A686" s="4" t="s">
         <v>46</v>
       </c>
@@ -10132,7 +10135,7 @@
       <c r="D686" s="5"/>
       <c r="E686" s="11"/>
     </row>
-    <row r="687" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A687" s="4" t="s">
         <v>46</v>
       </c>
@@ -10145,7 +10148,7 @@
       <c r="D687" s="5"/>
       <c r="E687" s="11"/>
     </row>
-    <row r="688" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A688" s="4" t="s">
         <v>46</v>
       </c>
@@ -10158,7 +10161,7 @@
       <c r="D688" s="5"/>
       <c r="E688" s="11"/>
     </row>
-    <row r="689" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A689" s="4" t="s">
         <v>46</v>
       </c>
@@ -10171,7 +10174,7 @@
       <c r="D689" s="5"/>
       <c r="E689" s="11"/>
     </row>
-    <row r="690" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A690" s="4" t="s">
         <v>46</v>
       </c>
@@ -10184,7 +10187,7 @@
       <c r="D690" s="5"/>
       <c r="E690" s="11"/>
     </row>
-    <row r="691" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A691" s="4" t="s">
         <v>46</v>
       </c>
@@ -10197,7 +10200,7 @@
       <c r="D691" s="5"/>
       <c r="E691" s="11"/>
     </row>
-    <row r="692" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A692" s="4" t="s">
         <v>46</v>
       </c>
@@ -10210,7 +10213,7 @@
       <c r="D692" s="5"/>
       <c r="E692" s="11"/>
     </row>
-    <row r="693" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A693" s="4" t="s">
         <v>46</v>
       </c>
@@ -10223,7 +10226,7 @@
       <c r="D693" s="5"/>
       <c r="E693" s="11"/>
     </row>
-    <row r="694" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A694" s="4" t="s">
         <v>46</v>
       </c>
@@ -10236,7 +10239,7 @@
       <c r="D694" s="5"/>
       <c r="E694" s="11"/>
     </row>
-    <row r="695" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A695" s="4" t="s">
         <v>46</v>
       </c>
@@ -10249,7 +10252,7 @@
       <c r="D695" s="5"/>
       <c r="E695" s="11"/>
     </row>
-    <row r="696" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A696" s="4" t="s">
         <v>46</v>
       </c>
@@ -10262,7 +10265,7 @@
       <c r="D696" s="5"/>
       <c r="E696" s="11"/>
     </row>
-    <row r="697" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A697" s="4" t="s">
         <v>46</v>
       </c>
@@ -10275,7 +10278,7 @@
       <c r="D697" s="5"/>
       <c r="E697" s="11"/>
     </row>
-    <row r="698" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A698" s="4" t="s">
         <v>46</v>
       </c>
@@ -10288,7 +10291,7 @@
       <c r="D698" s="5"/>
       <c r="E698" s="11"/>
     </row>
-    <row r="699" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A699" s="4" t="s">
         <v>46</v>
       </c>
@@ -10301,7 +10304,7 @@
       <c r="D699" s="5"/>
       <c r="E699" s="11"/>
     </row>
-    <row r="700" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A700" s="4" t="s">
         <v>46</v>
       </c>
@@ -10314,7 +10317,7 @@
       <c r="D700" s="5"/>
       <c r="E700" s="11"/>
     </row>
-    <row r="701" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A701" s="4" t="s">
         <v>46</v>
       </c>
@@ -10327,7 +10330,7 @@
       <c r="D701" s="5"/>
       <c r="E701" s="11"/>
     </row>
-    <row r="702" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A702" s="4" t="s">
         <v>46</v>
       </c>
@@ -10340,7 +10343,7 @@
       <c r="D702" s="5"/>
       <c r="E702" s="11"/>
     </row>
-    <row r="703" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A703" s="4" t="s">
         <v>46</v>
       </c>
@@ -10353,7 +10356,7 @@
       <c r="D703" s="5"/>
       <c r="E703" s="11"/>
     </row>
-    <row r="704" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A704" s="4" t="s">
         <v>46</v>
       </c>
@@ -10366,7 +10369,7 @@
       <c r="D704" s="5"/>
       <c r="E704" s="11"/>
     </row>
-    <row r="705" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A705" s="4" t="s">
         <v>46</v>
       </c>
@@ -10379,7 +10382,7 @@
       <c r="D705" s="5"/>
       <c r="E705" s="11"/>
     </row>
-    <row r="706" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A706" s="4" t="s">
         <v>46</v>
       </c>
@@ -10392,7 +10395,7 @@
       <c r="D706" s="5"/>
       <c r="E706" s="11"/>
     </row>
-    <row r="707" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A707" s="4" t="s">
         <v>46</v>
       </c>
@@ -10405,7 +10408,7 @@
       <c r="D707" s="5"/>
       <c r="E707" s="11"/>
     </row>
-    <row r="708" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A708" s="4" t="s">
         <v>46</v>
       </c>
@@ -10418,7 +10421,7 @@
       <c r="D708" s="5"/>
       <c r="E708" s="11"/>
     </row>
-    <row r="709" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A709" s="4" t="s">
         <v>46</v>
       </c>
@@ -10431,7 +10434,7 @@
       <c r="D709" s="5"/>
       <c r="E709" s="11"/>
     </row>
-    <row r="710" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A710" s="4" t="s">
         <v>46</v>
       </c>
@@ -10444,7 +10447,7 @@
       <c r="D710" s="5"/>
       <c r="E710" s="11"/>
     </row>
-    <row r="711" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A711" s="4" t="s">
         <v>46</v>
       </c>
@@ -10457,7 +10460,7 @@
       <c r="D711" s="5"/>
       <c r="E711" s="11"/>
     </row>
-    <row r="712" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A712" s="4" t="s">
         <v>46</v>
       </c>
@@ -10470,7 +10473,7 @@
       <c r="D712" s="5"/>
       <c r="E712" s="11"/>
     </row>
-    <row r="713" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A713" s="4" t="s">
         <v>46</v>
       </c>
@@ -10483,7 +10486,7 @@
       <c r="D713" s="5"/>
       <c r="E713" s="11"/>
     </row>
-    <row r="714" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A714" s="4" t="s">
         <v>46</v>
       </c>
@@ -10496,7 +10499,7 @@
       <c r="D714" s="5"/>
       <c r="E714" s="11"/>
     </row>
-    <row r="715" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A715" s="4" t="s">
         <v>46</v>
       </c>
@@ -10509,7 +10512,7 @@
       <c r="D715" s="5"/>
       <c r="E715" s="11"/>
     </row>
-    <row r="716" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A716" s="4" t="s">
         <v>46</v>
       </c>
@@ -10522,7 +10525,7 @@
       <c r="D716" s="5"/>
       <c r="E716" s="11"/>
     </row>
-    <row r="717" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A717" s="4" t="s">
         <v>46</v>
       </c>
@@ -10535,7 +10538,7 @@
       <c r="D717" s="5"/>
       <c r="E717" s="11"/>
     </row>
-    <row r="718" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A718" s="4" t="s">
         <v>46</v>
       </c>
@@ -10548,7 +10551,7 @@
       <c r="D718" s="5"/>
       <c r="E718" s="11"/>
     </row>
-    <row r="719" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A719" s="4" t="s">
         <v>46</v>
       </c>
@@ -10561,7 +10564,7 @@
       <c r="D719" s="5"/>
       <c r="E719" s="11"/>
     </row>
-    <row r="720" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A720" s="4" t="s">
         <v>46</v>
       </c>
@@ -10574,7 +10577,7 @@
       <c r="D720" s="5"/>
       <c r="E720" s="11"/>
     </row>
-    <row r="721" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A721" s="4" t="s">
         <v>46</v>
       </c>
@@ -10587,7 +10590,7 @@
       <c r="D721" s="5"/>
       <c r="E721" s="11"/>
     </row>
-    <row r="722" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A722" s="4" t="s">
         <v>46</v>
       </c>
@@ -10600,7 +10603,7 @@
       <c r="D722" s="5"/>
       <c r="E722" s="11"/>
     </row>
-    <row r="723" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A723" s="4" t="s">
         <v>46</v>
       </c>
@@ -10613,7 +10616,7 @@
       <c r="D723" s="5"/>
       <c r="E723" s="11"/>
     </row>
-    <row r="724" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A724" s="4" t="s">
         <v>46</v>
       </c>
@@ -10626,7 +10629,7 @@
       <c r="D724" s="5"/>
       <c r="E724" s="11"/>
     </row>
-    <row r="725" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A725" s="4" t="s">
         <v>46</v>
       </c>
@@ -10639,7 +10642,7 @@
       <c r="D725" s="5"/>
       <c r="E725" s="11"/>
     </row>
-    <row r="726" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A726" s="4" t="s">
         <v>43</v>
       </c>
@@ -10653,7 +10656,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A727" s="4" t="s">
         <v>43</v>
       </c>
@@ -10667,7 +10670,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A728" s="4" t="s">
         <v>43</v>
       </c>
@@ -10701,6 +10704,35 @@
         <v>126</v>
       </c>
       <c r="E730" s="13"/>
+    </row>
+    <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C731">
+        <v>48</v>
+      </c>
+      <c r="D731" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E731" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C732">
+        <v>49</v>
+      </c>
+      <c r="D732" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E732" s="13"/>
+    </row>
+    <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C733">
+        <v>50</v>
+      </c>
+      <c r="D733" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E733" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10715,13 +10747,13 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A730</xm:sqref>
+          <xm:sqref>A2:A733</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B730</xm:sqref>
+          <xm:sqref>B2:B733</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E32F11-46C5-421D-AA74-7D3ACEAEDAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E73160-010C-4F86-A5CC-2741A73BB740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="129">
   <si>
     <t>Категорија</t>
   </si>
@@ -10706,6 +10706,12 @@
       <c r="E730" s="13"/>
     </row>
     <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A731" t="s">
+        <v>43</v>
+      </c>
+      <c r="B731">
+        <v>6</v>
+      </c>
       <c r="C731">
         <v>48</v>
       </c>
@@ -10717,6 +10723,12 @@
       </c>
     </row>
     <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A732" t="s">
+        <v>43</v>
+      </c>
+      <c r="B732">
+        <v>6</v>
+      </c>
       <c r="C732">
         <v>49</v>
       </c>
@@ -10726,6 +10738,12 @@
       <c r="E732" s="13"/>
     </row>
     <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A733" t="s">
+        <v>43</v>
+      </c>
+      <c r="B733">
+        <v>6</v>
+      </c>
       <c r="C733">
         <v>50</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E73160-010C-4F86-A5CC-2741A73BB740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DCE94C-9E23-40AE-88B4-BF1560C64F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="130">
   <si>
     <t>Категорија</t>
   </si>
@@ -487,6 +487,9 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbwGk3j-Jqxl77X6Jsz-T3_CvTZIqIwdFksDTHqy_UUCpGY3ANZNyU1py92Qyqxzp_B03Q/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbxZXRF67GyKW4OBj2Q-8c0khO_rq6g_paWKbWk6f_D_OWIlbXVJp1OncnnujQl7h4_6sw/exec</t>
   </si>
 </sst>
 </file>
@@ -10735,7 +10738,9 @@
       <c r="D732" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E732" s="13"/>
+      <c r="E732" s="13" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A733" t="s">

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DCE94C-9E23-40AE-88B4-BF1560C64F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD53AFC-0B09-4D0F-959C-3E85FF045189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="132">
   <si>
     <t>Категорија</t>
   </si>
@@ -490,6 +490,12 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbxZXRF67GyKW4OBj2Q-8c0khO_rq6g_paWKbWk6f_D_OWIlbXVJp1OncnnujQl7h4_6sw/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbxDuRebeJmD96nC9Gyfq8g4b6SNqOHmQYN7DZ1eAP8as7mDdxTVNHpH0xVb54WQoWs/exec</t>
+  </si>
+  <si>
+    <t>Конвексен и неконвексен многуаголник</t>
   </si>
 </sst>
 </file>
@@ -624,7 +630,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -660,7 +666,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -687,12 +692,12 @@
   <autoFilter ref="A1:E733" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Алгебра"/>
+        <filter val="Геометрија"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="6"/>
+        <filter val="7"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1004,7 +1009,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1021,7 +1026,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>43</v>
       </c>
@@ -1038,7 +1043,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>43</v>
       </c>
@@ -1053,7 +1058,7 @@
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
@@ -1068,7 +1073,7 @@
       </c>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>43</v>
       </c>
@@ -1083,7 +1088,7 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>43</v>
       </c>
@@ -1098,7 +1103,7 @@
       </c>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>43</v>
       </c>
@@ -1113,7 +1118,7 @@
       </c>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>43</v>
       </c>
@@ -1128,7 +1133,7 @@
       </c>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>43</v>
       </c>
@@ -1143,7 +1148,7 @@
       </c>
       <c r="E9" s="11"/>
     </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>43</v>
       </c>
@@ -1158,7 +1163,7 @@
       </c>
       <c r="E10" s="11"/>
     </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>43</v>
       </c>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>43</v>
       </c>
@@ -1188,7 +1193,7 @@
       </c>
       <c r="E12" s="11"/>
     </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>43</v>
       </c>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="E13" s="11"/>
     </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
@@ -1218,7 +1223,7 @@
       </c>
       <c r="E14" s="11"/>
     </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>43</v>
       </c>
@@ -1233,7 +1238,7 @@
       </c>
       <c r="E15" s="11"/>
     </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>43</v>
       </c>
@@ -1248,7 +1253,7 @@
       </c>
       <c r="E16" s="11"/>
     </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>43</v>
       </c>
@@ -1263,7 +1268,7 @@
       </c>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>43</v>
       </c>
@@ -1278,7 +1283,7 @@
       </c>
       <c r="E18" s="11"/>
     </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>43</v>
       </c>
@@ -1293,7 +1298,7 @@
       </c>
       <c r="E19" s="11"/>
     </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
@@ -1308,7 +1313,7 @@
       </c>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>43</v>
       </c>
@@ -1323,7 +1328,7 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>43</v>
       </c>
@@ -1338,7 +1343,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>43</v>
       </c>
@@ -1353,7 +1358,7 @@
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>43</v>
       </c>
@@ -1368,7 +1373,7 @@
       </c>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>43</v>
       </c>
@@ -1383,7 +1388,7 @@
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>43</v>
       </c>
@@ -1398,7 +1403,7 @@
       </c>
       <c r="E26" s="11"/>
     </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>43</v>
       </c>
@@ -1413,7 +1418,7 @@
       </c>
       <c r="E27" s="11"/>
     </row>
-    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>43</v>
       </c>
@@ -1428,7 +1433,7 @@
       </c>
       <c r="E28" s="11"/>
     </row>
-    <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>43</v>
       </c>
@@ -1443,7 +1448,7 @@
       </c>
       <c r="E29" s="11"/>
     </row>
-    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>43</v>
       </c>
@@ -1458,7 +1463,7 @@
       </c>
       <c r="E30" s="11"/>
     </row>
-    <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>43</v>
       </c>
@@ -1473,7 +1478,7 @@
       </c>
       <c r="E31" s="11"/>
     </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>43</v>
       </c>
@@ -1488,7 +1493,7 @@
       </c>
       <c r="E32" s="11"/>
     </row>
-    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>43</v>
       </c>
@@ -1503,7 +1508,7 @@
       </c>
       <c r="E33" s="11"/>
     </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>43</v>
       </c>
@@ -1518,7 +1523,7 @@
       </c>
       <c r="E34" s="11"/>
     </row>
-    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>43</v>
       </c>
@@ -1533,7 +1538,7 @@
       </c>
       <c r="E35" s="11"/>
     </row>
-    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>43</v>
       </c>
@@ -1548,7 +1553,7 @@
       </c>
       <c r="E36" s="11"/>
     </row>
-    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>43</v>
       </c>
@@ -1563,7 +1568,7 @@
       </c>
       <c r="E37" s="11"/>
     </row>
-    <row r="38" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>43</v>
       </c>
@@ -1578,7 +1583,7 @@
       </c>
       <c r="E38" s="11"/>
     </row>
-    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>43</v>
       </c>
@@ -1593,7 +1598,7 @@
       </c>
       <c r="E39" s="11"/>
     </row>
-    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>43</v>
       </c>
@@ -1608,7 +1613,7 @@
       </c>
       <c r="E40" s="11"/>
     </row>
-    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>43</v>
       </c>
@@ -1683,7 +1688,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1696,7 +1701,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1709,7 +1714,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1722,7 +1727,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1735,7 +1740,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -1748,7 +1753,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1761,7 +1766,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1774,7 +1779,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1787,7 +1792,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -1800,7 +1805,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="11"/>
     </row>
-    <row r="55" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1813,7 +1818,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="11"/>
     </row>
-    <row r="56" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -1826,7 +1831,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -1839,7 +1844,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -1852,7 +1857,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -1865,7 +1870,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -1878,7 +1883,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -1891,7 +1896,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -1904,7 +1909,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -1917,7 +1922,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -1930,7 +1935,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -1943,7 +1948,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -1956,7 +1961,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -1969,7 +1974,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -1982,7 +1987,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -1995,7 +2000,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2008,7 +2013,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2021,7 +2026,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2034,7 +2039,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2047,7 +2052,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2060,7 +2065,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2073,7 +2078,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2086,7 +2091,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2099,7 +2104,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2112,7 +2117,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2125,7 +2130,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2138,7 +2143,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2151,7 +2156,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2164,7 +2169,7 @@
       <c r="D82" s="5"/>
       <c r="E82" s="11"/>
     </row>
-    <row r="83" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2177,7 +2182,7 @@
       <c r="D83" s="5"/>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2190,7 +2195,7 @@
       <c r="D84" s="5"/>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2203,7 +2208,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2216,7 +2221,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="11"/>
     </row>
-    <row r="87" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2229,7 +2234,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="11"/>
     </row>
-    <row r="88" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2242,7 +2247,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="11"/>
     </row>
-    <row r="89" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2255,7 +2260,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="11"/>
     </row>
-    <row r="90" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2268,7 +2273,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="11"/>
     </row>
-    <row r="91" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2281,7 +2286,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2294,7 +2299,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2307,7 +2312,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2320,7 +2325,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2333,7 +2338,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2346,7 +2351,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2359,7 +2364,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2372,7 +2377,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2385,7 +2390,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2398,7 +2403,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2411,7 +2416,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2424,7 +2429,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2437,7 +2442,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2450,7 +2455,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2463,7 +2468,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2476,7 +2481,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2489,7 +2494,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2502,7 +2507,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2515,7 +2520,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2528,7 +2533,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2541,7 +2546,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2554,7 +2559,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2567,7 +2572,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2580,7 +2585,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2593,7 +2598,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2606,7 +2611,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2619,7 +2624,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2632,7 +2637,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2645,7 +2650,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2658,7 +2663,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>
@@ -2671,7 +2676,7 @@
       <c r="D121" s="5"/>
       <c r="E121" s="11"/>
     </row>
-    <row r="122" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>5</v>
       </c>
@@ -2684,7 +2689,7 @@
       <c r="D122" s="5"/>
       <c r="E122" s="11"/>
     </row>
-    <row r="123" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>5</v>
       </c>
@@ -2697,7 +2702,7 @@
       <c r="D123" s="5"/>
       <c r="E123" s="11"/>
     </row>
-    <row r="124" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>5</v>
       </c>
@@ -2710,7 +2715,7 @@
       <c r="D124" s="5"/>
       <c r="E124" s="11"/>
     </row>
-    <row r="125" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>5</v>
       </c>
@@ -2723,7 +2728,7 @@
       <c r="D125" s="5"/>
       <c r="E125" s="11"/>
     </row>
-    <row r="126" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>5</v>
       </c>
@@ -2736,7 +2741,7 @@
       <c r="D126" s="5"/>
       <c r="E126" s="11"/>
     </row>
-    <row r="127" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>5</v>
       </c>
@@ -2749,7 +2754,7 @@
       <c r="D127" s="5"/>
       <c r="E127" s="11"/>
     </row>
-    <row r="128" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>5</v>
       </c>
@@ -2762,7 +2767,7 @@
       <c r="D128" s="5"/>
       <c r="E128" s="11"/>
     </row>
-    <row r="129" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>5</v>
       </c>
@@ -2775,7 +2780,7 @@
       <c r="D129" s="5"/>
       <c r="E129" s="11"/>
     </row>
-    <row r="130" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>5</v>
       </c>
@@ -2788,7 +2793,7 @@
       <c r="D130" s="5"/>
       <c r="E130" s="11"/>
     </row>
-    <row r="131" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>5</v>
       </c>
@@ -2801,7 +2806,7 @@
       <c r="D131" s="5"/>
       <c r="E131" s="11"/>
     </row>
-    <row r="132" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>5</v>
       </c>
@@ -2814,7 +2819,7 @@
       <c r="D132" s="5"/>
       <c r="E132" s="11"/>
     </row>
-    <row r="133" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>5</v>
       </c>
@@ -2827,7 +2832,7 @@
       <c r="D133" s="5"/>
       <c r="E133" s="11"/>
     </row>
-    <row r="134" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>5</v>
       </c>
@@ -2840,7 +2845,7 @@
       <c r="D134" s="5"/>
       <c r="E134" s="11"/>
     </row>
-    <row r="135" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>5</v>
       </c>
@@ -2853,7 +2858,7 @@
       <c r="D135" s="5"/>
       <c r="E135" s="11"/>
     </row>
-    <row r="136" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>5</v>
       </c>
@@ -2866,7 +2871,7 @@
       <c r="D136" s="5"/>
       <c r="E136" s="11"/>
     </row>
-    <row r="137" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>5</v>
       </c>
@@ -2879,7 +2884,7 @@
       <c r="D137" s="5"/>
       <c r="E137" s="11"/>
     </row>
-    <row r="138" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>5</v>
       </c>
@@ -2892,7 +2897,7 @@
       <c r="D138" s="5"/>
       <c r="E138" s="11"/>
     </row>
-    <row r="139" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>5</v>
       </c>
@@ -2905,7 +2910,7 @@
       <c r="D139" s="5"/>
       <c r="E139" s="11"/>
     </row>
-    <row r="140" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>5</v>
       </c>
@@ -2918,7 +2923,7 @@
       <c r="D140" s="5"/>
       <c r="E140" s="11"/>
     </row>
-    <row r="141" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>5</v>
       </c>
@@ -2931,7 +2936,7 @@
       <c r="D141" s="5"/>
       <c r="E141" s="11"/>
     </row>
-    <row r="142" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>5</v>
       </c>
@@ -2944,7 +2949,7 @@
       <c r="D142" s="5"/>
       <c r="E142" s="11"/>
     </row>
-    <row r="143" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>5</v>
       </c>
@@ -2957,7 +2962,7 @@
       <c r="D143" s="5"/>
       <c r="E143" s="11"/>
     </row>
-    <row r="144" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>5</v>
       </c>
@@ -2970,7 +2975,7 @@
       <c r="D144" s="5"/>
       <c r="E144" s="11"/>
     </row>
-    <row r="145" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>5</v>
       </c>
@@ -2983,7 +2988,7 @@
       <c r="D145" s="5"/>
       <c r="E145" s="11"/>
     </row>
-    <row r="146" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>5</v>
       </c>
@@ -2996,7 +3001,7 @@
       <c r="D146" s="5"/>
       <c r="E146" s="11"/>
     </row>
-    <row r="147" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>5</v>
       </c>
@@ -3009,7 +3014,7 @@
       <c r="D147" s="5"/>
       <c r="E147" s="11"/>
     </row>
-    <row r="148" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>5</v>
       </c>
@@ -3022,7 +3027,7 @@
       <c r="D148" s="5"/>
       <c r="E148" s="11"/>
     </row>
-    <row r="149" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>5</v>
       </c>
@@ -3035,7 +3040,7 @@
       <c r="D149" s="5"/>
       <c r="E149" s="11"/>
     </row>
-    <row r="150" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>5</v>
       </c>
@@ -3048,7 +3053,7 @@
       <c r="D150" s="5"/>
       <c r="E150" s="11"/>
     </row>
-    <row r="151" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>5</v>
       </c>
@@ -3061,7 +3066,7 @@
       <c r="D151" s="5"/>
       <c r="E151" s="11"/>
     </row>
-    <row r="152" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>5</v>
       </c>
@@ -3074,7 +3079,7 @@
       <c r="D152" s="5"/>
       <c r="E152" s="11"/>
     </row>
-    <row r="153" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>5</v>
       </c>
@@ -3087,7 +3092,7 @@
       <c r="D153" s="5"/>
       <c r="E153" s="11"/>
     </row>
-    <row r="154" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>5</v>
       </c>
@@ -3100,7 +3105,7 @@
       <c r="D154" s="5"/>
       <c r="E154" s="11"/>
     </row>
-    <row r="155" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>5</v>
       </c>
@@ -3113,7 +3118,7 @@
       <c r="D155" s="5"/>
       <c r="E155" s="11"/>
     </row>
-    <row r="156" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>5</v>
       </c>
@@ -3126,7 +3131,7 @@
       <c r="D156" s="5"/>
       <c r="E156" s="11"/>
     </row>
-    <row r="157" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>5</v>
       </c>
@@ -3139,7 +3144,7 @@
       <c r="D157" s="5"/>
       <c r="E157" s="11"/>
     </row>
-    <row r="158" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>5</v>
       </c>
@@ -3152,7 +3157,7 @@
       <c r="D158" s="5"/>
       <c r="E158" s="11"/>
     </row>
-    <row r="159" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>5</v>
       </c>
@@ -3165,7 +3170,7 @@
       <c r="D159" s="5"/>
       <c r="E159" s="11"/>
     </row>
-    <row r="160" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>5</v>
       </c>
@@ -3178,7 +3183,7 @@
       <c r="D160" s="5"/>
       <c r="E160" s="11"/>
     </row>
-    <row r="161" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>5</v>
       </c>
@@ -3191,7 +3196,7 @@
       <c r="D161" s="5"/>
       <c r="E161" s="11"/>
     </row>
-    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>43</v>
       </c>
@@ -3206,7 +3211,7 @@
       </c>
       <c r="E162" s="11"/>
     </row>
-    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>43</v>
       </c>
@@ -3221,7 +3226,7 @@
       </c>
       <c r="E163" s="11"/>
     </row>
-    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>43</v>
       </c>
@@ -3236,7 +3241,7 @@
       </c>
       <c r="E164" s="11"/>
     </row>
-    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>43</v>
       </c>
@@ -3253,7 +3258,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>5</v>
       </c>
@@ -3270,7 +3275,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>5</v>
       </c>
@@ -3287,7 +3292,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>5</v>
       </c>
@@ -3302,7 +3307,7 @@
       </c>
       <c r="E168" s="10"/>
     </row>
-    <row r="169" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>5</v>
       </c>
@@ -3317,7 +3322,7 @@
       </c>
       <c r="E169" s="10"/>
     </row>
-    <row r="170" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>5</v>
       </c>
@@ -3332,7 +3337,7 @@
       </c>
       <c r="E170" s="10"/>
     </row>
-    <row r="171" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>5</v>
       </c>
@@ -3347,7 +3352,7 @@
       </c>
       <c r="E171" s="10"/>
     </row>
-    <row r="172" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>5</v>
       </c>
@@ -3362,7 +3367,7 @@
       </c>
       <c r="E172" s="10"/>
     </row>
-    <row r="173" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>5</v>
       </c>
@@ -3377,7 +3382,7 @@
       </c>
       <c r="E173" s="10"/>
     </row>
-    <row r="174" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>5</v>
       </c>
@@ -3392,7 +3397,7 @@
       </c>
       <c r="E174" s="10"/>
     </row>
-    <row r="175" spans="1:5" ht="29.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>5</v>
       </c>
@@ -3407,7 +3412,7 @@
       </c>
       <c r="E175" s="10"/>
     </row>
-    <row r="176" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>5</v>
       </c>
@@ -3422,7 +3427,7 @@
       </c>
       <c r="E176" s="10"/>
     </row>
-    <row r="177" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>5</v>
       </c>
@@ -3437,7 +3442,7 @@
       </c>
       <c r="E177" s="10"/>
     </row>
-    <row r="178" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>5</v>
       </c>
@@ -3452,7 +3457,7 @@
       </c>
       <c r="E178" s="10"/>
     </row>
-    <row r="179" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>5</v>
       </c>
@@ -3467,7 +3472,7 @@
       </c>
       <c r="E179" s="10"/>
     </row>
-    <row r="180" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>5</v>
       </c>
@@ -3482,7 +3487,7 @@
       </c>
       <c r="E180" s="10"/>
     </row>
-    <row r="181" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>5</v>
       </c>
@@ -3497,7 +3502,7 @@
       </c>
       <c r="E181" s="10"/>
     </row>
-    <row r="182" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>5</v>
       </c>
@@ -3512,7 +3517,7 @@
       </c>
       <c r="E182" s="10"/>
     </row>
-    <row r="183" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>5</v>
       </c>
@@ -3527,7 +3532,7 @@
       </c>
       <c r="E183" s="10"/>
     </row>
-    <row r="184" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>5</v>
       </c>
@@ -3542,7 +3547,7 @@
       </c>
       <c r="E184" s="10"/>
     </row>
-    <row r="185" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>5</v>
       </c>
@@ -3557,7 +3562,7 @@
       </c>
       <c r="E185" s="10"/>
     </row>
-    <row r="186" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>5</v>
       </c>
@@ -3572,7 +3577,7 @@
       </c>
       <c r="E186" s="10"/>
     </row>
-    <row r="187" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>5</v>
       </c>
@@ -3587,7 +3592,7 @@
       </c>
       <c r="E187" s="10"/>
     </row>
-    <row r="188" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>5</v>
       </c>
@@ -3602,7 +3607,7 @@
       </c>
       <c r="E188" s="10"/>
     </row>
-    <row r="189" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>5</v>
       </c>
@@ -3617,7 +3622,7 @@
       </c>
       <c r="E189" s="10"/>
     </row>
-    <row r="190" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>5</v>
       </c>
@@ -3632,7 +3637,7 @@
       </c>
       <c r="E190" s="10"/>
     </row>
-    <row r="191" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>5</v>
       </c>
@@ -3647,7 +3652,7 @@
       </c>
       <c r="E191" s="10"/>
     </row>
-    <row r="192" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>5</v>
       </c>
@@ -3662,7 +3667,7 @@
       </c>
       <c r="E192" s="10"/>
     </row>
-    <row r="193" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>5</v>
       </c>
@@ -3677,7 +3682,7 @@
       </c>
       <c r="E193" s="10"/>
     </row>
-    <row r="194" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>5</v>
       </c>
@@ -3692,7 +3697,7 @@
       </c>
       <c r="E194" s="10"/>
     </row>
-    <row r="195" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>5</v>
       </c>
@@ -3707,7 +3712,7 @@
       </c>
       <c r="E195" s="10"/>
     </row>
-    <row r="196" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>5</v>
       </c>
@@ -3722,7 +3727,7 @@
       </c>
       <c r="E196" s="10"/>
     </row>
-    <row r="197" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>5</v>
       </c>
@@ -3737,7 +3742,7 @@
       </c>
       <c r="E197" s="10"/>
     </row>
-    <row r="198" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>5</v>
       </c>
@@ -3752,7 +3757,7 @@
       </c>
       <c r="E198" s="10"/>
     </row>
-    <row r="199" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>5</v>
       </c>
@@ -3767,7 +3772,7 @@
       </c>
       <c r="E199" s="10"/>
     </row>
-    <row r="200" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>5</v>
       </c>
@@ -3782,7 +3787,7 @@
       </c>
       <c r="E200" s="10"/>
     </row>
-    <row r="201" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>5</v>
       </c>
@@ -3797,7 +3802,7 @@
       </c>
       <c r="E201" s="10"/>
     </row>
-    <row r="202" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
         <v>43</v>
       </c>
@@ -3810,7 +3815,7 @@
       <c r="D202" s="5"/>
       <c r="E202" s="11"/>
     </row>
-    <row r="203" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
         <v>43</v>
       </c>
@@ -3823,7 +3828,7 @@
       <c r="D203" s="5"/>
       <c r="E203" s="11"/>
     </row>
-    <row r="204" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
         <v>43</v>
       </c>
@@ -3836,7 +3841,7 @@
       <c r="D204" s="5"/>
       <c r="E204" s="11"/>
     </row>
-    <row r="205" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
         <v>43</v>
       </c>
@@ -3849,7 +3854,7 @@
       <c r="D205" s="5"/>
       <c r="E205" s="11"/>
     </row>
-    <row r="206" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
         <v>43</v>
       </c>
@@ -3862,7 +3867,7 @@
       <c r="D206" s="5"/>
       <c r="E206" s="11"/>
     </row>
-    <row r="207" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
         <v>43</v>
       </c>
@@ -3875,7 +3880,7 @@
       <c r="D207" s="5"/>
       <c r="E207" s="11"/>
     </row>
-    <row r="208" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
         <v>43</v>
       </c>
@@ -3888,7 +3893,7 @@
       <c r="D208" s="5"/>
       <c r="E208" s="11"/>
     </row>
-    <row r="209" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
         <v>43</v>
       </c>
@@ -3901,7 +3906,7 @@
       <c r="D209" s="5"/>
       <c r="E209" s="11"/>
     </row>
-    <row r="210" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
         <v>43</v>
       </c>
@@ -3914,7 +3919,7 @@
       <c r="D210" s="5"/>
       <c r="E210" s="11"/>
     </row>
-    <row r="211" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
         <v>43</v>
       </c>
@@ -3927,7 +3932,7 @@
       <c r="D211" s="5"/>
       <c r="E211" s="11"/>
     </row>
-    <row r="212" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
         <v>43</v>
       </c>
@@ -3940,7 +3945,7 @@
       <c r="D212" s="5"/>
       <c r="E212" s="11"/>
     </row>
-    <row r="213" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
         <v>43</v>
       </c>
@@ -3953,7 +3958,7 @@
       <c r="D213" s="5"/>
       <c r="E213" s="11"/>
     </row>
-    <row r="214" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
         <v>43</v>
       </c>
@@ -3966,7 +3971,7 @@
       <c r="D214" s="5"/>
       <c r="E214" s="11"/>
     </row>
-    <row r="215" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
         <v>43</v>
       </c>
@@ -3979,7 +3984,7 @@
       <c r="D215" s="5"/>
       <c r="E215" s="11"/>
     </row>
-    <row r="216" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
         <v>43</v>
       </c>
@@ -3992,7 +3997,7 @@
       <c r="D216" s="5"/>
       <c r="E216" s="11"/>
     </row>
-    <row r="217" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
         <v>43</v>
       </c>
@@ -4005,7 +4010,7 @@
       <c r="D217" s="5"/>
       <c r="E217" s="11"/>
     </row>
-    <row r="218" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
         <v>43</v>
       </c>
@@ -4018,7 +4023,7 @@
       <c r="D218" s="5"/>
       <c r="E218" s="11"/>
     </row>
-    <row r="219" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
         <v>43</v>
       </c>
@@ -4031,7 +4036,7 @@
       <c r="D219" s="5"/>
       <c r="E219" s="11"/>
     </row>
-    <row r="220" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
         <v>43</v>
       </c>
@@ -4044,7 +4049,7 @@
       <c r="D220" s="5"/>
       <c r="E220" s="11"/>
     </row>
-    <row r="221" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
         <v>43</v>
       </c>
@@ -4057,7 +4062,7 @@
       <c r="D221" s="5"/>
       <c r="E221" s="11"/>
     </row>
-    <row r="222" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
         <v>43</v>
       </c>
@@ -4070,7 +4075,7 @@
       <c r="D222" s="5"/>
       <c r="E222" s="11"/>
     </row>
-    <row r="223" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
         <v>43</v>
       </c>
@@ -4083,7 +4088,7 @@
       <c r="D223" s="5"/>
       <c r="E223" s="11"/>
     </row>
-    <row r="224" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
         <v>43</v>
       </c>
@@ -4096,7 +4101,7 @@
       <c r="D224" s="5"/>
       <c r="E224" s="11"/>
     </row>
-    <row r="225" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
         <v>43</v>
       </c>
@@ -4109,7 +4114,7 @@
       <c r="D225" s="5"/>
       <c r="E225" s="11"/>
     </row>
-    <row r="226" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
         <v>43</v>
       </c>
@@ -4122,7 +4127,7 @@
       <c r="D226" s="5"/>
       <c r="E226" s="11"/>
     </row>
-    <row r="227" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
         <v>43</v>
       </c>
@@ -4135,7 +4140,7 @@
       <c r="D227" s="5"/>
       <c r="E227" s="11"/>
     </row>
-    <row r="228" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
         <v>43</v>
       </c>
@@ -4148,7 +4153,7 @@
       <c r="D228" s="5"/>
       <c r="E228" s="11"/>
     </row>
-    <row r="229" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
         <v>43</v>
       </c>
@@ -4161,7 +4166,7 @@
       <c r="D229" s="5"/>
       <c r="E229" s="11"/>
     </row>
-    <row r="230" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
         <v>43</v>
       </c>
@@ -4174,7 +4179,7 @@
       <c r="D230" s="5"/>
       <c r="E230" s="11"/>
     </row>
-    <row r="231" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
         <v>43</v>
       </c>
@@ -4187,7 +4192,7 @@
       <c r="D231" s="5"/>
       <c r="E231" s="11"/>
     </row>
-    <row r="232" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
         <v>43</v>
       </c>
@@ -4200,7 +4205,7 @@
       <c r="D232" s="5"/>
       <c r="E232" s="11"/>
     </row>
-    <row r="233" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
         <v>43</v>
       </c>
@@ -4213,7 +4218,7 @@
       <c r="D233" s="5"/>
       <c r="E233" s="11"/>
     </row>
-    <row r="234" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
         <v>43</v>
       </c>
@@ -4226,7 +4231,7 @@
       <c r="D234" s="5"/>
       <c r="E234" s="11"/>
     </row>
-    <row r="235" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
         <v>43</v>
       </c>
@@ -4239,7 +4244,7 @@
       <c r="D235" s="5"/>
       <c r="E235" s="11"/>
     </row>
-    <row r="236" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
         <v>43</v>
       </c>
@@ -4252,7 +4257,7 @@
       <c r="D236" s="5"/>
       <c r="E236" s="11"/>
     </row>
-    <row r="237" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
         <v>43</v>
       </c>
@@ -4265,7 +4270,7 @@
       <c r="D237" s="5"/>
       <c r="E237" s="11"/>
     </row>
-    <row r="238" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
         <v>43</v>
       </c>
@@ -4278,7 +4283,7 @@
       <c r="D238" s="5"/>
       <c r="E238" s="11"/>
     </row>
-    <row r="239" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
         <v>43</v>
       </c>
@@ -4291,7 +4296,7 @@
       <c r="D239" s="5"/>
       <c r="E239" s="11"/>
     </row>
-    <row r="240" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
         <v>43</v>
       </c>
@@ -4304,7 +4309,7 @@
       <c r="D240" s="5"/>
       <c r="E240" s="11"/>
     </row>
-    <row r="241" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
         <v>43</v>
       </c>
@@ -4317,7 +4322,7 @@
       <c r="D241" s="5"/>
       <c r="E241" s="11"/>
     </row>
-    <row r="242" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
         <v>43</v>
       </c>
@@ -4330,7 +4335,7 @@
       <c r="D242" s="5"/>
       <c r="E242" s="11"/>
     </row>
-    <row r="243" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
         <v>43</v>
       </c>
@@ -4343,7 +4348,7 @@
       <c r="D243" s="5"/>
       <c r="E243" s="11"/>
     </row>
-    <row r="244" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
         <v>43</v>
       </c>
@@ -4356,7 +4361,7 @@
       <c r="D244" s="5"/>
       <c r="E244" s="11"/>
     </row>
-    <row r="245" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
         <v>43</v>
       </c>
@@ -4369,7 +4374,7 @@
       <c r="D245" s="5"/>
       <c r="E245" s="11"/>
     </row>
-    <row r="246" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
         <v>43</v>
       </c>
@@ -4382,7 +4387,7 @@
       <c r="D246" s="5"/>
       <c r="E246" s="11"/>
     </row>
-    <row r="247" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
         <v>43</v>
       </c>
@@ -4395,7 +4400,7 @@
       <c r="D247" s="5"/>
       <c r="E247" s="11"/>
     </row>
-    <row r="248" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
         <v>43</v>
       </c>
@@ -4408,7 +4413,7 @@
       <c r="D248" s="5"/>
       <c r="E248" s="11"/>
     </row>
-    <row r="249" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
         <v>43</v>
       </c>
@@ -4421,7 +4426,7 @@
       <c r="D249" s="5"/>
       <c r="E249" s="11"/>
     </row>
-    <row r="250" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
         <v>43</v>
       </c>
@@ -4434,7 +4439,7 @@
       <c r="D250" s="5"/>
       <c r="E250" s="11"/>
     </row>
-    <row r="251" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
         <v>43</v>
       </c>
@@ -4447,7 +4452,7 @@
       <c r="D251" s="5"/>
       <c r="E251" s="11"/>
     </row>
-    <row r="252" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
         <v>43</v>
       </c>
@@ -4460,7 +4465,7 @@
       <c r="D252" s="5"/>
       <c r="E252" s="11"/>
     </row>
-    <row r="253" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
         <v>43</v>
       </c>
@@ -4473,7 +4478,7 @@
       <c r="D253" s="5"/>
       <c r="E253" s="11"/>
     </row>
-    <row r="254" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>43</v>
       </c>
@@ -4486,7 +4491,7 @@
       <c r="D254" s="5"/>
       <c r="E254" s="11"/>
     </row>
-    <row r="255" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>43</v>
       </c>
@@ -4499,7 +4504,7 @@
       <c r="D255" s="5"/>
       <c r="E255" s="11"/>
     </row>
-    <row r="256" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>43</v>
       </c>
@@ -4512,7 +4517,7 @@
       <c r="D256" s="5"/>
       <c r="E256" s="11"/>
     </row>
-    <row r="257" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
         <v>43</v>
       </c>
@@ -4525,7 +4530,7 @@
       <c r="D257" s="5"/>
       <c r="E257" s="11"/>
     </row>
-    <row r="258" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
         <v>43</v>
       </c>
@@ -4538,7 +4543,7 @@
       <c r="D258" s="5"/>
       <c r="E258" s="11"/>
     </row>
-    <row r="259" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
         <v>43</v>
       </c>
@@ -4551,7 +4556,7 @@
       <c r="D259" s="5"/>
       <c r="E259" s="11"/>
     </row>
-    <row r="260" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
         <v>43</v>
       </c>
@@ -4564,7 +4569,7 @@
       <c r="D260" s="5"/>
       <c r="E260" s="11"/>
     </row>
-    <row r="261" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
         <v>43</v>
       </c>
@@ -4577,7 +4582,7 @@
       <c r="D261" s="5"/>
       <c r="E261" s="11"/>
     </row>
-    <row r="262" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
         <v>43</v>
       </c>
@@ -4590,7 +4595,7 @@
       <c r="D262" s="5"/>
       <c r="E262" s="11"/>
     </row>
-    <row r="263" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
         <v>43</v>
       </c>
@@ -4603,7 +4608,7 @@
       <c r="D263" s="5"/>
       <c r="E263" s="11"/>
     </row>
-    <row r="264" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
         <v>43</v>
       </c>
@@ -4616,7 +4621,7 @@
       <c r="D264" s="5"/>
       <c r="E264" s="11"/>
     </row>
-    <row r="265" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
         <v>43</v>
       </c>
@@ -4629,7 +4634,7 @@
       <c r="D265" s="5"/>
       <c r="E265" s="11"/>
     </row>
-    <row r="266" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
         <v>43</v>
       </c>
@@ -4642,7 +4647,7 @@
       <c r="D266" s="5"/>
       <c r="E266" s="11"/>
     </row>
-    <row r="267" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
         <v>43</v>
       </c>
@@ -4655,7 +4660,7 @@
       <c r="D267" s="5"/>
       <c r="E267" s="11"/>
     </row>
-    <row r="268" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
         <v>43</v>
       </c>
@@ -4668,7 +4673,7 @@
       <c r="D268" s="5"/>
       <c r="E268" s="11"/>
     </row>
-    <row r="269" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
         <v>43</v>
       </c>
@@ -4681,7 +4686,7 @@
       <c r="D269" s="5"/>
       <c r="E269" s="11"/>
     </row>
-    <row r="270" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
         <v>43</v>
       </c>
@@ -4694,7 +4699,7 @@
       <c r="D270" s="5"/>
       <c r="E270" s="11"/>
     </row>
-    <row r="271" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
         <v>43</v>
       </c>
@@ -4707,7 +4712,7 @@
       <c r="D271" s="5"/>
       <c r="E271" s="11"/>
     </row>
-    <row r="272" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
         <v>43</v>
       </c>
@@ -4720,7 +4725,7 @@
       <c r="D272" s="5"/>
       <c r="E272" s="11"/>
     </row>
-    <row r="273" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4" t="s">
         <v>43</v>
       </c>
@@ -4733,7 +4738,7 @@
       <c r="D273" s="5"/>
       <c r="E273" s="11"/>
     </row>
-    <row r="274" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4" t="s">
         <v>43</v>
       </c>
@@ -4746,7 +4751,7 @@
       <c r="D274" s="5"/>
       <c r="E274" s="11"/>
     </row>
-    <row r="275" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="4" t="s">
         <v>43</v>
       </c>
@@ -4759,7 +4764,7 @@
       <c r="D275" s="5"/>
       <c r="E275" s="11"/>
     </row>
-    <row r="276" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
         <v>43</v>
       </c>
@@ -4772,7 +4777,7 @@
       <c r="D276" s="5"/>
       <c r="E276" s="11"/>
     </row>
-    <row r="277" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
         <v>43</v>
       </c>
@@ -4785,7 +4790,7 @@
       <c r="D277" s="5"/>
       <c r="E277" s="11"/>
     </row>
-    <row r="278" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
         <v>43</v>
       </c>
@@ -4798,7 +4803,7 @@
       <c r="D278" s="5"/>
       <c r="E278" s="11"/>
     </row>
-    <row r="279" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
         <v>43</v>
       </c>
@@ -4811,7 +4816,7 @@
       <c r="D279" s="5"/>
       <c r="E279" s="11"/>
     </row>
-    <row r="280" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
         <v>43</v>
       </c>
@@ -4824,7 +4829,7 @@
       <c r="D280" s="5"/>
       <c r="E280" s="11"/>
     </row>
-    <row r="281" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
         <v>43</v>
       </c>
@@ -4837,7 +4842,7 @@
       <c r="D281" s="5"/>
       <c r="E281" s="11"/>
     </row>
-    <row r="282" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>43</v>
       </c>
@@ -4850,7 +4855,7 @@
       <c r="D282" s="5"/>
       <c r="E282" s="11"/>
     </row>
-    <row r="283" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>43</v>
       </c>
@@ -4863,7 +4868,7 @@
       <c r="D283" s="5"/>
       <c r="E283" s="11"/>
     </row>
-    <row r="284" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>43</v>
       </c>
@@ -4876,7 +4881,7 @@
       <c r="D284" s="5"/>
       <c r="E284" s="11"/>
     </row>
-    <row r="285" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>43</v>
       </c>
@@ -4889,7 +4894,7 @@
       <c r="D285" s="5"/>
       <c r="E285" s="11"/>
     </row>
-    <row r="286" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
         <v>43</v>
       </c>
@@ -4902,7 +4907,7 @@
       <c r="D286" s="5"/>
       <c r="E286" s="11"/>
     </row>
-    <row r="287" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
         <v>43</v>
       </c>
@@ -4915,7 +4920,7 @@
       <c r="D287" s="5"/>
       <c r="E287" s="11"/>
     </row>
-    <row r="288" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>43</v>
       </c>
@@ -4928,7 +4933,7 @@
       <c r="D288" s="5"/>
       <c r="E288" s="11"/>
     </row>
-    <row r="289" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
         <v>43</v>
       </c>
@@ -4941,7 +4946,7 @@
       <c r="D289" s="5"/>
       <c r="E289" s="11"/>
     </row>
-    <row r="290" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>43</v>
       </c>
@@ -4954,7 +4959,7 @@
       <c r="D290" s="5"/>
       <c r="E290" s="11"/>
     </row>
-    <row r="291" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>43</v>
       </c>
@@ -4967,7 +4972,7 @@
       <c r="D291" s="5"/>
       <c r="E291" s="11"/>
     </row>
-    <row r="292" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>43</v>
       </c>
@@ -4980,7 +4985,7 @@
       <c r="D292" s="5"/>
       <c r="E292" s="11"/>
     </row>
-    <row r="293" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>43</v>
       </c>
@@ -4993,7 +4998,7 @@
       <c r="D293" s="5"/>
       <c r="E293" s="11"/>
     </row>
-    <row r="294" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>43</v>
       </c>
@@ -5006,7 +5011,7 @@
       <c r="D294" s="5"/>
       <c r="E294" s="11"/>
     </row>
-    <row r="295" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>43</v>
       </c>
@@ -5019,7 +5024,7 @@
       <c r="D295" s="5"/>
       <c r="E295" s="11"/>
     </row>
-    <row r="296" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>43</v>
       </c>
@@ -5032,7 +5037,7 @@
       <c r="D296" s="5"/>
       <c r="E296" s="11"/>
     </row>
-    <row r="297" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>43</v>
       </c>
@@ -5045,7 +5050,7 @@
       <c r="D297" s="5"/>
       <c r="E297" s="11"/>
     </row>
-    <row r="298" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>43</v>
       </c>
@@ -5058,7 +5063,7 @@
       <c r="D298" s="5"/>
       <c r="E298" s="11"/>
     </row>
-    <row r="299" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>43</v>
       </c>
@@ -5071,7 +5076,7 @@
       <c r="D299" s="5"/>
       <c r="E299" s="11"/>
     </row>
-    <row r="300" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
         <v>43</v>
       </c>
@@ -5084,7 +5089,7 @@
       <c r="D300" s="5"/>
       <c r="E300" s="11"/>
     </row>
-    <row r="301" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
         <v>43</v>
       </c>
@@ -5097,7 +5102,7 @@
       <c r="D301" s="5"/>
       <c r="E301" s="11"/>
     </row>
-    <row r="302" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
         <v>43</v>
       </c>
@@ -5110,7 +5115,7 @@
       <c r="D302" s="5"/>
       <c r="E302" s="11"/>
     </row>
-    <row r="303" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
         <v>43</v>
       </c>
@@ -5123,7 +5128,7 @@
       <c r="D303" s="5"/>
       <c r="E303" s="11"/>
     </row>
-    <row r="304" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>43</v>
       </c>
@@ -5136,7 +5141,7 @@
       <c r="D304" s="5"/>
       <c r="E304" s="11"/>
     </row>
-    <row r="305" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>43</v>
       </c>
@@ -5149,7 +5154,7 @@
       <c r="D305" s="5"/>
       <c r="E305" s="11"/>
     </row>
-    <row r="306" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>43</v>
       </c>
@@ -5162,7 +5167,7 @@
       <c r="D306" s="5"/>
       <c r="E306" s="11"/>
     </row>
-    <row r="307" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>43</v>
       </c>
@@ -5175,7 +5180,7 @@
       <c r="D307" s="5"/>
       <c r="E307" s="11"/>
     </row>
-    <row r="308" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>43</v>
       </c>
@@ -5188,7 +5193,7 @@
       <c r="D308" s="5"/>
       <c r="E308" s="11"/>
     </row>
-    <row r="309" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
         <v>43</v>
       </c>
@@ -5201,7 +5206,7 @@
       <c r="D309" s="5"/>
       <c r="E309" s="11"/>
     </row>
-    <row r="310" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
         <v>43</v>
       </c>
@@ -5214,7 +5219,7 @@
       <c r="D310" s="5"/>
       <c r="E310" s="11"/>
     </row>
-    <row r="311" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
         <v>43</v>
       </c>
@@ -5227,7 +5232,7 @@
       <c r="D311" s="5"/>
       <c r="E311" s="11"/>
     </row>
-    <row r="312" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
         <v>43</v>
       </c>
@@ -5240,7 +5245,7 @@
       <c r="D312" s="5"/>
       <c r="E312" s="11"/>
     </row>
-    <row r="313" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
         <v>43</v>
       </c>
@@ -5253,7 +5258,7 @@
       <c r="D313" s="5"/>
       <c r="E313" s="11"/>
     </row>
-    <row r="314" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
         <v>43</v>
       </c>
@@ -5266,7 +5271,7 @@
       <c r="D314" s="5"/>
       <c r="E314" s="11"/>
     </row>
-    <row r="315" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
         <v>43</v>
       </c>
@@ -5279,7 +5284,7 @@
       <c r="D315" s="5"/>
       <c r="E315" s="11"/>
     </row>
-    <row r="316" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
         <v>43</v>
       </c>
@@ -5296,7 +5301,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
         <v>43</v>
       </c>
@@ -5309,7 +5314,7 @@
       <c r="D317" s="5"/>
       <c r="E317" s="11"/>
     </row>
-    <row r="318" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
         <v>43</v>
       </c>
@@ -5326,7 +5331,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
         <v>43</v>
       </c>
@@ -5343,7 +5348,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
         <v>43</v>
       </c>
@@ -5358,7 +5363,7 @@
       </c>
       <c r="E320" s="11"/>
     </row>
-    <row r="321" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
         <v>43</v>
       </c>
@@ -5373,7 +5378,7 @@
       </c>
       <c r="E321" s="11"/>
     </row>
-    <row r="322" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
         <v>5</v>
       </c>
@@ -5388,7 +5393,7 @@
       </c>
       <c r="E322" s="10"/>
     </row>
-    <row r="323" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
         <v>5</v>
       </c>
@@ -5403,7 +5408,7 @@
       </c>
       <c r="E323" s="10"/>
     </row>
-    <row r="324" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>5</v>
       </c>
@@ -5418,7 +5423,7 @@
       </c>
       <c r="E324" s="10"/>
     </row>
-    <row r="325" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
         <v>5</v>
       </c>
@@ -5433,7 +5438,7 @@
       </c>
       <c r="E325" s="10"/>
     </row>
-    <row r="326" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="4" t="s">
         <v>44</v>
       </c>
@@ -5446,7 +5451,7 @@
       <c r="D326" s="5"/>
       <c r="E326" s="11"/>
     </row>
-    <row r="327" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="4" t="s">
         <v>44</v>
       </c>
@@ -5459,7 +5464,7 @@
       <c r="D327" s="5"/>
       <c r="E327" s="11"/>
     </row>
-    <row r="328" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="4" t="s">
         <v>44</v>
       </c>
@@ -5472,7 +5477,7 @@
       <c r="D328" s="5"/>
       <c r="E328" s="11"/>
     </row>
-    <row r="329" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="4" t="s">
         <v>44</v>
       </c>
@@ -5485,7 +5490,7 @@
       <c r="D329" s="5"/>
       <c r="E329" s="11"/>
     </row>
-    <row r="330" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="4" t="s">
         <v>44</v>
       </c>
@@ -5498,7 +5503,7 @@
       <c r="D330" s="5"/>
       <c r="E330" s="11"/>
     </row>
-    <row r="331" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="4" t="s">
         <v>44</v>
       </c>
@@ -5511,7 +5516,7 @@
       <c r="D331" s="5"/>
       <c r="E331" s="11"/>
     </row>
-    <row r="332" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="4" t="s">
         <v>44</v>
       </c>
@@ -5524,7 +5529,7 @@
       <c r="D332" s="5"/>
       <c r="E332" s="11"/>
     </row>
-    <row r="333" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="4" t="s">
         <v>44</v>
       </c>
@@ -5537,7 +5542,7 @@
       <c r="D333" s="5"/>
       <c r="E333" s="11"/>
     </row>
-    <row r="334" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="4" t="s">
         <v>44</v>
       </c>
@@ -5550,7 +5555,7 @@
       <c r="D334" s="5"/>
       <c r="E334" s="11"/>
     </row>
-    <row r="335" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="4" t="s">
         <v>44</v>
       </c>
@@ -5563,7 +5568,7 @@
       <c r="D335" s="5"/>
       <c r="E335" s="11"/>
     </row>
-    <row r="336" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="4" t="s">
         <v>44</v>
       </c>
@@ -5576,7 +5581,7 @@
       <c r="D336" s="5"/>
       <c r="E336" s="11"/>
     </row>
-    <row r="337" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="4" t="s">
         <v>44</v>
       </c>
@@ -5589,7 +5594,7 @@
       <c r="D337" s="5"/>
       <c r="E337" s="11"/>
     </row>
-    <row r="338" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="4" t="s">
         <v>44</v>
       </c>
@@ -5602,7 +5607,7 @@
       <c r="D338" s="5"/>
       <c r="E338" s="11"/>
     </row>
-    <row r="339" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="4" t="s">
         <v>44</v>
       </c>
@@ -5615,7 +5620,7 @@
       <c r="D339" s="5"/>
       <c r="E339" s="11"/>
     </row>
-    <row r="340" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4" t="s">
         <v>44</v>
       </c>
@@ -5628,7 +5633,7 @@
       <c r="D340" s="5"/>
       <c r="E340" s="11"/>
     </row>
-    <row r="341" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="4" t="s">
         <v>44</v>
       </c>
@@ -5641,7 +5646,7 @@
       <c r="D341" s="5"/>
       <c r="E341" s="11"/>
     </row>
-    <row r="342" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4" t="s">
         <v>44</v>
       </c>
@@ -5654,7 +5659,7 @@
       <c r="D342" s="5"/>
       <c r="E342" s="11"/>
     </row>
-    <row r="343" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="4" t="s">
         <v>44</v>
       </c>
@@ -5667,7 +5672,7 @@
       <c r="D343" s="5"/>
       <c r="E343" s="11"/>
     </row>
-    <row r="344" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="4" t="s">
         <v>44</v>
       </c>
@@ -5680,7 +5685,7 @@
       <c r="D344" s="5"/>
       <c r="E344" s="11"/>
     </row>
-    <row r="345" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="4" t="s">
         <v>44</v>
       </c>
@@ -5693,7 +5698,7 @@
       <c r="D345" s="5"/>
       <c r="E345" s="11"/>
     </row>
-    <row r="346" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="4" t="s">
         <v>44</v>
       </c>
@@ -5706,7 +5711,7 @@
       <c r="D346" s="5"/>
       <c r="E346" s="11"/>
     </row>
-    <row r="347" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="4" t="s">
         <v>44</v>
       </c>
@@ -5719,7 +5724,7 @@
       <c r="D347" s="5"/>
       <c r="E347" s="11"/>
     </row>
-    <row r="348" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="4" t="s">
         <v>44</v>
       </c>
@@ -5732,7 +5737,7 @@
       <c r="D348" s="5"/>
       <c r="E348" s="11"/>
     </row>
-    <row r="349" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="4" t="s">
         <v>44</v>
       </c>
@@ -5745,7 +5750,7 @@
       <c r="D349" s="5"/>
       <c r="E349" s="11"/>
     </row>
-    <row r="350" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="4" t="s">
         <v>44</v>
       </c>
@@ -5758,7 +5763,7 @@
       <c r="D350" s="5"/>
       <c r="E350" s="11"/>
     </row>
-    <row r="351" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="4" t="s">
         <v>44</v>
       </c>
@@ -5771,7 +5776,7 @@
       <c r="D351" s="5"/>
       <c r="E351" s="11"/>
     </row>
-    <row r="352" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="4" t="s">
         <v>44</v>
       </c>
@@ -5784,7 +5789,7 @@
       <c r="D352" s="5"/>
       <c r="E352" s="11"/>
     </row>
-    <row r="353" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="4" t="s">
         <v>44</v>
       </c>
@@ -5797,7 +5802,7 @@
       <c r="D353" s="5"/>
       <c r="E353" s="11"/>
     </row>
-    <row r="354" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="4" t="s">
         <v>44</v>
       </c>
@@ -5810,7 +5815,7 @@
       <c r="D354" s="5"/>
       <c r="E354" s="11"/>
     </row>
-    <row r="355" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="4" t="s">
         <v>44</v>
       </c>
@@ -5823,7 +5828,7 @@
       <c r="D355" s="5"/>
       <c r="E355" s="11"/>
     </row>
-    <row r="356" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="4" t="s">
         <v>44</v>
       </c>
@@ -5836,7 +5841,7 @@
       <c r="D356" s="5"/>
       <c r="E356" s="11"/>
     </row>
-    <row r="357" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="4" t="s">
         <v>44</v>
       </c>
@@ -5849,7 +5854,7 @@
       <c r="D357" s="5"/>
       <c r="E357" s="11"/>
     </row>
-    <row r="358" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
         <v>44</v>
       </c>
@@ -5862,7 +5867,7 @@
       <c r="D358" s="5"/>
       <c r="E358" s="11"/>
     </row>
-    <row r="359" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
         <v>44</v>
       </c>
@@ -5875,7 +5880,7 @@
       <c r="D359" s="5"/>
       <c r="E359" s="11"/>
     </row>
-    <row r="360" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
         <v>44</v>
       </c>
@@ -5888,7 +5893,7 @@
       <c r="D360" s="5"/>
       <c r="E360" s="11"/>
     </row>
-    <row r="361" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
         <v>44</v>
       </c>
@@ -5901,7 +5906,7 @@
       <c r="D361" s="5"/>
       <c r="E361" s="11"/>
     </row>
-    <row r="362" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
         <v>44</v>
       </c>
@@ -5914,7 +5919,7 @@
       <c r="D362" s="5"/>
       <c r="E362" s="11"/>
     </row>
-    <row r="363" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
         <v>44</v>
       </c>
@@ -5927,7 +5932,7 @@
       <c r="D363" s="5"/>
       <c r="E363" s="11"/>
     </row>
-    <row r="364" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
         <v>44</v>
       </c>
@@ -5940,7 +5945,7 @@
       <c r="D364" s="5"/>
       <c r="E364" s="11"/>
     </row>
-    <row r="365" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
         <v>44</v>
       </c>
@@ -5953,7 +5958,7 @@
       <c r="D365" s="5"/>
       <c r="E365" s="11"/>
     </row>
-    <row r="366" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
         <v>44</v>
       </c>
@@ -5966,7 +5971,7 @@
       <c r="D366" s="5"/>
       <c r="E366" s="11"/>
     </row>
-    <row r="367" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
         <v>44</v>
       </c>
@@ -5979,7 +5984,7 @@
       <c r="D367" s="5"/>
       <c r="E367" s="11"/>
     </row>
-    <row r="368" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
         <v>44</v>
       </c>
@@ -5992,7 +5997,7 @@
       <c r="D368" s="5"/>
       <c r="E368" s="11"/>
     </row>
-    <row r="369" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
         <v>44</v>
       </c>
@@ -6005,7 +6010,7 @@
       <c r="D369" s="5"/>
       <c r="E369" s="11"/>
     </row>
-    <row r="370" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
         <v>44</v>
       </c>
@@ -6018,7 +6023,7 @@
       <c r="D370" s="5"/>
       <c r="E370" s="11"/>
     </row>
-    <row r="371" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
         <v>44</v>
       </c>
@@ -6031,7 +6036,7 @@
       <c r="D371" s="5"/>
       <c r="E371" s="11"/>
     </row>
-    <row r="372" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
         <v>44</v>
       </c>
@@ -6044,7 +6049,7 @@
       <c r="D372" s="5"/>
       <c r="E372" s="11"/>
     </row>
-    <row r="373" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
         <v>44</v>
       </c>
@@ -6057,7 +6062,7 @@
       <c r="D373" s="5"/>
       <c r="E373" s="11"/>
     </row>
-    <row r="374" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
         <v>44</v>
       </c>
@@ -6070,7 +6075,7 @@
       <c r="D374" s="5"/>
       <c r="E374" s="11"/>
     </row>
-    <row r="375" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
         <v>44</v>
       </c>
@@ -6083,7 +6088,7 @@
       <c r="D375" s="5"/>
       <c r="E375" s="11"/>
     </row>
-    <row r="376" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
         <v>44</v>
       </c>
@@ -6096,7 +6101,7 @@
       <c r="D376" s="5"/>
       <c r="E376" s="11"/>
     </row>
-    <row r="377" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>44</v>
       </c>
@@ -6106,10 +6111,14 @@
       <c r="C377" s="4">
         <v>1</v>
       </c>
-      <c r="D377" s="5"/>
-      <c r="E377" s="11"/>
-    </row>
-    <row r="378" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D377" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E377" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>44</v>
       </c>
@@ -6122,7 +6131,7 @@
       <c r="D378" s="5"/>
       <c r="E378" s="11"/>
     </row>
-    <row r="379" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>44</v>
       </c>
@@ -6135,7 +6144,7 @@
       <c r="D379" s="5"/>
       <c r="E379" s="11"/>
     </row>
-    <row r="380" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>44</v>
       </c>
@@ -6148,7 +6157,7 @@
       <c r="D380" s="5"/>
       <c r="E380" s="11"/>
     </row>
-    <row r="381" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>44</v>
       </c>
@@ -6161,7 +6170,7 @@
       <c r="D381" s="5"/>
       <c r="E381" s="11"/>
     </row>
-    <row r="382" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>44</v>
       </c>
@@ -6174,7 +6183,7 @@
       <c r="D382" s="5"/>
       <c r="E382" s="11"/>
     </row>
-    <row r="383" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
         <v>44</v>
       </c>
@@ -6187,7 +6196,7 @@
       <c r="D383" s="5"/>
       <c r="E383" s="11"/>
     </row>
-    <row r="384" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
         <v>44</v>
       </c>
@@ -6200,7 +6209,7 @@
       <c r="D384" s="5"/>
       <c r="E384" s="11"/>
     </row>
-    <row r="385" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
         <v>44</v>
       </c>
@@ -6213,7 +6222,7 @@
       <c r="D385" s="5"/>
       <c r="E385" s="11"/>
     </row>
-    <row r="386" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
         <v>44</v>
       </c>
@@ -6226,7 +6235,7 @@
       <c r="D386" s="5"/>
       <c r="E386" s="11"/>
     </row>
-    <row r="387" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
         <v>44</v>
       </c>
@@ -6239,7 +6248,7 @@
       <c r="D387" s="5"/>
       <c r="E387" s="11"/>
     </row>
-    <row r="388" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
         <v>44</v>
       </c>
@@ -6252,7 +6261,7 @@
       <c r="D388" s="5"/>
       <c r="E388" s="11"/>
     </row>
-    <row r="389" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
         <v>44</v>
       </c>
@@ -6265,7 +6274,7 @@
       <c r="D389" s="5"/>
       <c r="E389" s="11"/>
     </row>
-    <row r="390" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
         <v>44</v>
       </c>
@@ -6278,7 +6287,7 @@
       <c r="D390" s="5"/>
       <c r="E390" s="11"/>
     </row>
-    <row r="391" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
         <v>44</v>
       </c>
@@ -6291,7 +6300,7 @@
       <c r="D391" s="5"/>
       <c r="E391" s="11"/>
     </row>
-    <row r="392" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
         <v>44</v>
       </c>
@@ -6304,7 +6313,7 @@
       <c r="D392" s="5"/>
       <c r="E392" s="11"/>
     </row>
-    <row r="393" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
         <v>44</v>
       </c>
@@ -6317,7 +6326,7 @@
       <c r="D393" s="5"/>
       <c r="E393" s="11"/>
     </row>
-    <row r="394" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
         <v>44</v>
       </c>
@@ -6330,7 +6339,7 @@
       <c r="D394" s="5"/>
       <c r="E394" s="11"/>
     </row>
-    <row r="395" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
         <v>44</v>
       </c>
@@ -6343,7 +6352,7 @@
       <c r="D395" s="5"/>
       <c r="E395" s="11"/>
     </row>
-    <row r="396" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
         <v>44</v>
       </c>
@@ -6356,7 +6365,7 @@
       <c r="D396" s="5"/>
       <c r="E396" s="11"/>
     </row>
-    <row r="397" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>44</v>
       </c>
@@ -6369,7 +6378,7 @@
       <c r="D397" s="5"/>
       <c r="E397" s="11"/>
     </row>
-    <row r="398" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>44</v>
       </c>
@@ -6382,7 +6391,7 @@
       <c r="D398" s="5"/>
       <c r="E398" s="11"/>
     </row>
-    <row r="399" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
         <v>44</v>
       </c>
@@ -6395,7 +6404,7 @@
       <c r="D399" s="5"/>
       <c r="E399" s="11"/>
     </row>
-    <row r="400" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
         <v>44</v>
       </c>
@@ -6408,7 +6417,7 @@
       <c r="D400" s="5"/>
       <c r="E400" s="11"/>
     </row>
-    <row r="401" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>44</v>
       </c>
@@ -6421,7 +6430,7 @@
       <c r="D401" s="5"/>
       <c r="E401" s="11"/>
     </row>
-    <row r="402" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>44</v>
       </c>
@@ -6434,7 +6443,7 @@
       <c r="D402" s="5"/>
       <c r="E402" s="11"/>
     </row>
-    <row r="403" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>44</v>
       </c>
@@ -6447,7 +6456,7 @@
       <c r="D403" s="5"/>
       <c r="E403" s="11"/>
     </row>
-    <row r="404" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>44</v>
       </c>
@@ -6460,7 +6469,7 @@
       <c r="D404" s="5"/>
       <c r="E404" s="11"/>
     </row>
-    <row r="405" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
         <v>44</v>
       </c>
@@ -6473,7 +6482,7 @@
       <c r="D405" s="5"/>
       <c r="E405" s="11"/>
     </row>
-    <row r="406" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>44</v>
       </c>
@@ -6486,7 +6495,7 @@
       <c r="D406" s="5"/>
       <c r="E406" s="11"/>
     </row>
-    <row r="407" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>44</v>
       </c>
@@ -6499,7 +6508,7 @@
       <c r="D407" s="5"/>
       <c r="E407" s="11"/>
     </row>
-    <row r="408" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>44</v>
       </c>
@@ -6512,7 +6521,7 @@
       <c r="D408" s="5"/>
       <c r="E408" s="11"/>
     </row>
-    <row r="409" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>44</v>
       </c>
@@ -6525,7 +6534,7 @@
       <c r="D409" s="5"/>
       <c r="E409" s="11"/>
     </row>
-    <row r="410" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>44</v>
       </c>
@@ -6538,7 +6547,7 @@
       <c r="D410" s="5"/>
       <c r="E410" s="11"/>
     </row>
-    <row r="411" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>44</v>
       </c>
@@ -6551,7 +6560,7 @@
       <c r="D411" s="5"/>
       <c r="E411" s="11"/>
     </row>
-    <row r="412" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>44</v>
       </c>
@@ -6564,7 +6573,7 @@
       <c r="D412" s="5"/>
       <c r="E412" s="11"/>
     </row>
-    <row r="413" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
         <v>44</v>
       </c>
@@ -6577,7 +6586,7 @@
       <c r="D413" s="5"/>
       <c r="E413" s="11"/>
     </row>
-    <row r="414" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
         <v>44</v>
       </c>
@@ -6590,7 +6599,7 @@
       <c r="D414" s="5"/>
       <c r="E414" s="11"/>
     </row>
-    <row r="415" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
         <v>44</v>
       </c>
@@ -6603,7 +6612,7 @@
       <c r="D415" s="5"/>
       <c r="E415" s="11"/>
     </row>
-    <row r="416" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
         <v>44</v>
       </c>
@@ -6616,7 +6625,7 @@
       <c r="D416" s="5"/>
       <c r="E416" s="11"/>
     </row>
-    <row r="417" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
         <v>44</v>
       </c>
@@ -6629,7 +6638,7 @@
       <c r="D417" s="5"/>
       <c r="E417" s="11"/>
     </row>
-    <row r="418" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
         <v>44</v>
       </c>
@@ -6642,7 +6651,7 @@
       <c r="D418" s="5"/>
       <c r="E418" s="11"/>
     </row>
-    <row r="419" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
         <v>44</v>
       </c>
@@ -6655,7 +6664,7 @@
       <c r="D419" s="5"/>
       <c r="E419" s="11"/>
     </row>
-    <row r="420" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
         <v>44</v>
       </c>
@@ -6668,7 +6677,7 @@
       <c r="D420" s="5"/>
       <c r="E420" s="11"/>
     </row>
-    <row r="421" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
         <v>44</v>
       </c>
@@ -6681,7 +6690,7 @@
       <c r="D421" s="5"/>
       <c r="E421" s="11"/>
     </row>
-    <row r="422" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
         <v>44</v>
       </c>
@@ -6694,7 +6703,7 @@
       <c r="D422" s="5"/>
       <c r="E422" s="11"/>
     </row>
-    <row r="423" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
         <v>44</v>
       </c>
@@ -6707,7 +6716,7 @@
       <c r="D423" s="5"/>
       <c r="E423" s="11"/>
     </row>
-    <row r="424" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
         <v>44</v>
       </c>
@@ -6720,7 +6729,7 @@
       <c r="D424" s="5"/>
       <c r="E424" s="11"/>
     </row>
-    <row r="425" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
         <v>44</v>
       </c>
@@ -6733,7 +6742,7 @@
       <c r="D425" s="5"/>
       <c r="E425" s="11"/>
     </row>
-    <row r="426" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
         <v>44</v>
       </c>
@@ -6746,7 +6755,7 @@
       <c r="D426" s="5"/>
       <c r="E426" s="11"/>
     </row>
-    <row r="427" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
         <v>44</v>
       </c>
@@ -6759,7 +6768,7 @@
       <c r="D427" s="5"/>
       <c r="E427" s="11"/>
     </row>
-    <row r="428" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
         <v>44</v>
       </c>
@@ -6772,7 +6781,7 @@
       <c r="D428" s="5"/>
       <c r="E428" s="11"/>
     </row>
-    <row r="429" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
         <v>44</v>
       </c>
@@ -6785,7 +6794,7 @@
       <c r="D429" s="5"/>
       <c r="E429" s="11"/>
     </row>
-    <row r="430" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
         <v>44</v>
       </c>
@@ -6798,7 +6807,7 @@
       <c r="D430" s="5"/>
       <c r="E430" s="11"/>
     </row>
-    <row r="431" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
         <v>44</v>
       </c>
@@ -6811,7 +6820,7 @@
       <c r="D431" s="5"/>
       <c r="E431" s="11"/>
     </row>
-    <row r="432" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
         <v>44</v>
       </c>
@@ -6828,7 +6837,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
         <v>44</v>
       </c>
@@ -6841,7 +6850,7 @@
       <c r="D433" s="5"/>
       <c r="E433" s="11"/>
     </row>
-    <row r="434" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
         <v>44</v>
       </c>
@@ -6858,7 +6867,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
         <v>44</v>
       </c>
@@ -6871,7 +6880,7 @@
       <c r="D435" s="5"/>
       <c r="E435" s="11"/>
     </row>
-    <row r="436" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
         <v>44</v>
       </c>
@@ -6884,7 +6893,7 @@
       <c r="D436" s="5"/>
       <c r="E436" s="11"/>
     </row>
-    <row r="437" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
         <v>44</v>
       </c>
@@ -6897,7 +6906,7 @@
       <c r="D437" s="5"/>
       <c r="E437" s="11"/>
     </row>
-    <row r="438" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
         <v>44</v>
       </c>
@@ -6910,7 +6919,7 @@
       <c r="D438" s="5"/>
       <c r="E438" s="11"/>
     </row>
-    <row r="439" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
         <v>44</v>
       </c>
@@ -6923,7 +6932,7 @@
       <c r="D439" s="5"/>
       <c r="E439" s="11"/>
     </row>
-    <row r="440" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
         <v>44</v>
       </c>
@@ -6936,7 +6945,7 @@
       <c r="D440" s="5"/>
       <c r="E440" s="11"/>
     </row>
-    <row r="441" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
         <v>44</v>
       </c>
@@ -6949,7 +6958,7 @@
       <c r="D441" s="5"/>
       <c r="E441" s="11"/>
     </row>
-    <row r="442" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
         <v>44</v>
       </c>
@@ -6962,7 +6971,7 @@
       <c r="D442" s="5"/>
       <c r="E442" s="11"/>
     </row>
-    <row r="443" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
         <v>44</v>
       </c>
@@ -6975,7 +6984,7 @@
       <c r="D443" s="5"/>
       <c r="E443" s="11"/>
     </row>
-    <row r="444" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
         <v>44</v>
       </c>
@@ -6988,7 +6997,7 @@
       <c r="D444" s="5"/>
       <c r="E444" s="11"/>
     </row>
-    <row r="445" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
         <v>44</v>
       </c>
@@ -7001,7 +7010,7 @@
       <c r="D445" s="5"/>
       <c r="E445" s="11"/>
     </row>
-    <row r="446" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
         <v>44</v>
       </c>
@@ -7014,7 +7023,7 @@
       <c r="D446" s="5"/>
       <c r="E446" s="11"/>
     </row>
-    <row r="447" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
         <v>44</v>
       </c>
@@ -7027,7 +7036,7 @@
       <c r="D447" s="5"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
         <v>44</v>
       </c>
@@ -7040,7 +7049,7 @@
       <c r="D448" s="5"/>
       <c r="E448" s="11"/>
     </row>
-    <row r="449" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
         <v>44</v>
       </c>
@@ -7053,7 +7062,7 @@
       <c r="D449" s="5"/>
       <c r="E449" s="11"/>
     </row>
-    <row r="450" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
         <v>44</v>
       </c>
@@ -7066,7 +7075,7 @@
       <c r="D450" s="5"/>
       <c r="E450" s="11"/>
     </row>
-    <row r="451" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
         <v>44</v>
       </c>
@@ -7079,7 +7088,7 @@
       <c r="D451" s="5"/>
       <c r="E451" s="11"/>
     </row>
-    <row r="452" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
         <v>44</v>
       </c>
@@ -7092,7 +7101,7 @@
       <c r="D452" s="5"/>
       <c r="E452" s="11"/>
     </row>
-    <row r="453" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
         <v>44</v>
       </c>
@@ -7105,7 +7114,7 @@
       <c r="D453" s="5"/>
       <c r="E453" s="11"/>
     </row>
-    <row r="454" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
         <v>44</v>
       </c>
@@ -7118,7 +7127,7 @@
       <c r="D454" s="5"/>
       <c r="E454" s="11"/>
     </row>
-    <row r="455" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
         <v>44</v>
       </c>
@@ -7131,7 +7140,7 @@
       <c r="D455" s="5"/>
       <c r="E455" s="11"/>
     </row>
-    <row r="456" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
         <v>44</v>
       </c>
@@ -7144,7 +7153,7 @@
       <c r="D456" s="5"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
         <v>44</v>
       </c>
@@ -7157,7 +7166,7 @@
       <c r="D457" s="5"/>
       <c r="E457" s="11"/>
     </row>
-    <row r="458" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
         <v>44</v>
       </c>
@@ -7170,7 +7179,7 @@
       <c r="D458" s="5"/>
       <c r="E458" s="11"/>
     </row>
-    <row r="459" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
         <v>44</v>
       </c>
@@ -7183,7 +7192,7 @@
       <c r="D459" s="5"/>
       <c r="E459" s="11"/>
     </row>
-    <row r="460" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
         <v>44</v>
       </c>
@@ -7196,7 +7205,7 @@
       <c r="D460" s="5"/>
       <c r="E460" s="11"/>
     </row>
-    <row r="461" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
         <v>44</v>
       </c>
@@ -7209,7 +7218,7 @@
       <c r="D461" s="5"/>
       <c r="E461" s="11"/>
     </row>
-    <row r="462" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
         <v>44</v>
       </c>
@@ -7222,7 +7231,7 @@
       <c r="D462" s="5"/>
       <c r="E462" s="11"/>
     </row>
-    <row r="463" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
         <v>44</v>
       </c>
@@ -7235,7 +7244,7 @@
       <c r="D463" s="5"/>
       <c r="E463" s="11"/>
     </row>
-    <row r="464" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
         <v>44</v>
       </c>
@@ -7248,7 +7257,7 @@
       <c r="D464" s="5"/>
       <c r="E464" s="11"/>
     </row>
-    <row r="465" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
         <v>44</v>
       </c>
@@ -7261,7 +7270,7 @@
       <c r="D465" s="5"/>
       <c r="E465" s="11"/>
     </row>
-    <row r="466" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
         <v>44</v>
       </c>
@@ -7274,7 +7283,7 @@
       <c r="D466" s="5"/>
       <c r="E466" s="11"/>
     </row>
-    <row r="467" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
         <v>44</v>
       </c>
@@ -7287,7 +7296,7 @@
       <c r="D467" s="5"/>
       <c r="E467" s="11"/>
     </row>
-    <row r="468" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
         <v>44</v>
       </c>
@@ -7300,7 +7309,7 @@
       <c r="D468" s="5"/>
       <c r="E468" s="11"/>
     </row>
-    <row r="469" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
         <v>44</v>
       </c>
@@ -7313,7 +7322,7 @@
       <c r="D469" s="5"/>
       <c r="E469" s="11"/>
     </row>
-    <row r="470" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
         <v>44</v>
       </c>
@@ -7326,7 +7335,7 @@
       <c r="D470" s="5"/>
       <c r="E470" s="11"/>
     </row>
-    <row r="471" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
         <v>44</v>
       </c>
@@ -7339,7 +7348,7 @@
       <c r="D471" s="5"/>
       <c r="E471" s="11"/>
     </row>
-    <row r="472" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
         <v>44</v>
       </c>
@@ -7352,7 +7361,7 @@
       <c r="D472" s="5"/>
       <c r="E472" s="11"/>
     </row>
-    <row r="473" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
         <v>44</v>
       </c>
@@ -7365,7 +7374,7 @@
       <c r="D473" s="5"/>
       <c r="E473" s="11"/>
     </row>
-    <row r="474" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
         <v>44</v>
       </c>
@@ -7378,7 +7387,7 @@
       <c r="D474" s="5"/>
       <c r="E474" s="11"/>
     </row>
-    <row r="475" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
         <v>44</v>
       </c>
@@ -7391,7 +7400,7 @@
       <c r="D475" s="5"/>
       <c r="E475" s="11"/>
     </row>
-    <row r="476" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
         <v>44</v>
       </c>
@@ -7404,7 +7413,7 @@
       <c r="D476" s="5"/>
       <c r="E476" s="11"/>
     </row>
-    <row r="477" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
         <v>44</v>
       </c>
@@ -7417,7 +7426,7 @@
       <c r="D477" s="5"/>
       <c r="E477" s="11"/>
     </row>
-    <row r="478" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
         <v>44</v>
       </c>
@@ -7430,7 +7439,7 @@
       <c r="D478" s="5"/>
       <c r="E478" s="11"/>
     </row>
-    <row r="479" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
         <v>44</v>
       </c>
@@ -7443,7 +7452,7 @@
       <c r="D479" s="5"/>
       <c r="E479" s="11"/>
     </row>
-    <row r="480" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
         <v>44</v>
       </c>
@@ -7456,7 +7465,7 @@
       <c r="D480" s="5"/>
       <c r="E480" s="11"/>
     </row>
-    <row r="481" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
         <v>44</v>
       </c>
@@ -7469,7 +7478,7 @@
       <c r="D481" s="5"/>
       <c r="E481" s="11"/>
     </row>
-    <row r="482" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
         <v>44</v>
       </c>
@@ -7482,7 +7491,7 @@
       <c r="D482" s="5"/>
       <c r="E482" s="11"/>
     </row>
-    <row r="483" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
         <v>44</v>
       </c>
@@ -7495,7 +7504,7 @@
       <c r="D483" s="5"/>
       <c r="E483" s="11"/>
     </row>
-    <row r="484" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
         <v>44</v>
       </c>
@@ -7508,7 +7517,7 @@
       <c r="D484" s="5"/>
       <c r="E484" s="11"/>
     </row>
-    <row r="485" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
         <v>44</v>
       </c>
@@ -7521,7 +7530,7 @@
       <c r="D485" s="5"/>
       <c r="E485" s="11"/>
     </row>
-    <row r="486" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
         <v>44</v>
       </c>
@@ -7534,7 +7543,7 @@
       <c r="D486" s="5"/>
       <c r="E486" s="11"/>
     </row>
-    <row r="487" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="4" t="s">
         <v>44</v>
       </c>
@@ -7547,7 +7556,7 @@
       <c r="D487" s="5"/>
       <c r="E487" s="11"/>
     </row>
-    <row r="488" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="4" t="s">
         <v>44</v>
       </c>
@@ -7560,7 +7569,7 @@
       <c r="D488" s="5"/>
       <c r="E488" s="11"/>
     </row>
-    <row r="489" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="4" t="s">
         <v>44</v>
       </c>
@@ -7573,7 +7582,7 @@
       <c r="D489" s="5"/>
       <c r="E489" s="11"/>
     </row>
-    <row r="490" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="4" t="s">
         <v>44</v>
       </c>
@@ -7586,7 +7595,7 @@
       <c r="D490" s="5"/>
       <c r="E490" s="11"/>
     </row>
-    <row r="491" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
         <v>44</v>
       </c>
@@ -7599,7 +7608,7 @@
       <c r="D491" s="5"/>
       <c r="E491" s="11"/>
     </row>
-    <row r="492" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
         <v>44</v>
       </c>
@@ -7612,7 +7621,7 @@
       <c r="D492" s="5"/>
       <c r="E492" s="11"/>
     </row>
-    <row r="493" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
         <v>44</v>
       </c>
@@ -7625,7 +7634,7 @@
       <c r="D493" s="5"/>
       <c r="E493" s="11"/>
     </row>
-    <row r="494" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="4" t="s">
         <v>44</v>
       </c>
@@ -7638,7 +7647,7 @@
       <c r="D494" s="5"/>
       <c r="E494" s="11"/>
     </row>
-    <row r="495" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="4" t="s">
         <v>44</v>
       </c>
@@ -7651,7 +7660,7 @@
       <c r="D495" s="5"/>
       <c r="E495" s="11"/>
     </row>
-    <row r="496" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="4" t="s">
         <v>44</v>
       </c>
@@ -7664,7 +7673,7 @@
       <c r="D496" s="5"/>
       <c r="E496" s="11"/>
     </row>
-    <row r="497" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="4" t="s">
         <v>44</v>
       </c>
@@ -7677,7 +7686,7 @@
       <c r="D497" s="5"/>
       <c r="E497" s="11"/>
     </row>
-    <row r="498" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="4" t="s">
         <v>44</v>
       </c>
@@ -7690,7 +7699,7 @@
       <c r="D498" s="5"/>
       <c r="E498" s="11"/>
     </row>
-    <row r="499" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="4" t="s">
         <v>44</v>
       </c>
@@ -7703,7 +7712,7 @@
       <c r="D499" s="5"/>
       <c r="E499" s="11"/>
     </row>
-    <row r="500" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="4" t="s">
         <v>44</v>
       </c>
@@ -7716,7 +7725,7 @@
       <c r="D500" s="5"/>
       <c r="E500" s="11"/>
     </row>
-    <row r="501" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="4" t="s">
         <v>44</v>
       </c>
@@ -7729,7 +7738,7 @@
       <c r="D501" s="5"/>
       <c r="E501" s="11"/>
     </row>
-    <row r="502" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="4" t="s">
         <v>44</v>
       </c>
@@ -7742,7 +7751,7 @@
       <c r="D502" s="5"/>
       <c r="E502" s="11"/>
     </row>
-    <row r="503" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="4" t="s">
         <v>44</v>
       </c>
@@ -7755,7 +7764,7 @@
       <c r="D503" s="5"/>
       <c r="E503" s="11"/>
     </row>
-    <row r="504" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="4" t="s">
         <v>44</v>
       </c>
@@ -7768,7 +7777,7 @@
       <c r="D504" s="5"/>
       <c r="E504" s="11"/>
     </row>
-    <row r="505" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="4" t="s">
         <v>44</v>
       </c>
@@ -7781,7 +7790,7 @@
       <c r="D505" s="5"/>
       <c r="E505" s="11"/>
     </row>
-    <row r="506" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="4" t="s">
         <v>44</v>
       </c>
@@ -7794,7 +7803,7 @@
       <c r="D506" s="5"/>
       <c r="E506" s="11"/>
     </row>
-    <row r="507" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="4" t="s">
         <v>44</v>
       </c>
@@ -7807,7 +7816,7 @@
       <c r="D507" s="5"/>
       <c r="E507" s="11"/>
     </row>
-    <row r="508" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
         <v>44</v>
       </c>
@@ -7820,7 +7829,7 @@
       <c r="D508" s="5"/>
       <c r="E508" s="11"/>
     </row>
-    <row r="509" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="s">
         <v>44</v>
       </c>
@@ -7833,7 +7842,7 @@
       <c r="D509" s="5"/>
       <c r="E509" s="11"/>
     </row>
-    <row r="510" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="4" t="s">
         <v>44</v>
       </c>
@@ -7846,7 +7855,7 @@
       <c r="D510" s="5"/>
       <c r="E510" s="11"/>
     </row>
-    <row r="511" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="4" t="s">
         <v>44</v>
       </c>
@@ -7859,7 +7868,7 @@
       <c r="D511" s="5"/>
       <c r="E511" s="11"/>
     </row>
-    <row r="512" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="4" t="s">
         <v>44</v>
       </c>
@@ -7872,7 +7881,7 @@
       <c r="D512" s="5"/>
       <c r="E512" s="11"/>
     </row>
-    <row r="513" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="4" t="s">
         <v>44</v>
       </c>
@@ -7885,7 +7894,7 @@
       <c r="D513" s="5"/>
       <c r="E513" s="11"/>
     </row>
-    <row r="514" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="4" t="s">
         <v>44</v>
       </c>
@@ -7898,7 +7907,7 @@
       <c r="D514" s="5"/>
       <c r="E514" s="11"/>
     </row>
-    <row r="515" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="4" t="s">
         <v>44</v>
       </c>
@@ -7911,7 +7920,7 @@
       <c r="D515" s="5"/>
       <c r="E515" s="11"/>
     </row>
-    <row r="516" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="4" t="s">
         <v>44</v>
       </c>
@@ -7924,7 +7933,7 @@
       <c r="D516" s="5"/>
       <c r="E516" s="11"/>
     </row>
-    <row r="517" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="4" t="s">
         <v>44</v>
       </c>
@@ -7937,7 +7946,7 @@
       <c r="D517" s="5"/>
       <c r="E517" s="11"/>
     </row>
-    <row r="518" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="4" t="s">
         <v>44</v>
       </c>
@@ -7950,7 +7959,7 @@
       <c r="D518" s="5"/>
       <c r="E518" s="11"/>
     </row>
-    <row r="519" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="4" t="s">
         <v>44</v>
       </c>
@@ -7963,7 +7972,7 @@
       <c r="D519" s="5"/>
       <c r="E519" s="11"/>
     </row>
-    <row r="520" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="4" t="s">
         <v>44</v>
       </c>
@@ -7976,7 +7985,7 @@
       <c r="D520" s="5"/>
       <c r="E520" s="11"/>
     </row>
-    <row r="521" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="4" t="s">
         <v>44</v>
       </c>
@@ -7989,7 +7998,7 @@
       <c r="D521" s="5"/>
       <c r="E521" s="11"/>
     </row>
-    <row r="522" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="4" t="s">
         <v>44</v>
       </c>
@@ -8002,7 +8011,7 @@
       <c r="D522" s="5"/>
       <c r="E522" s="11"/>
     </row>
-    <row r="523" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="4" t="s">
         <v>44</v>
       </c>
@@ -8015,7 +8024,7 @@
       <c r="D523" s="5"/>
       <c r="E523" s="11"/>
     </row>
-    <row r="524" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="4" t="s">
         <v>44</v>
       </c>
@@ -8028,7 +8037,7 @@
       <c r="D524" s="5"/>
       <c r="E524" s="11"/>
     </row>
-    <row r="525" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="4" t="s">
         <v>44</v>
       </c>
@@ -8041,7 +8050,7 @@
       <c r="D525" s="5"/>
       <c r="E525" s="11"/>
     </row>
-    <row r="526" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="4" t="s">
         <v>44</v>
       </c>
@@ -8054,7 +8063,7 @@
       <c r="D526" s="5"/>
       <c r="E526" s="11"/>
     </row>
-    <row r="527" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="4" t="s">
         <v>44</v>
       </c>
@@ -8067,7 +8076,7 @@
       <c r="D527" s="5"/>
       <c r="E527" s="11"/>
     </row>
-    <row r="528" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="4" t="s">
         <v>44</v>
       </c>
@@ -8080,7 +8089,7 @@
       <c r="D528" s="5"/>
       <c r="E528" s="11"/>
     </row>
-    <row r="529" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="4" t="s">
         <v>44</v>
       </c>
@@ -8093,7 +8102,7 @@
       <c r="D529" s="5"/>
       <c r="E529" s="11"/>
     </row>
-    <row r="530" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="4" t="s">
         <v>44</v>
       </c>
@@ -8106,7 +8115,7 @@
       <c r="D530" s="5"/>
       <c r="E530" s="11"/>
     </row>
-    <row r="531" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="4" t="s">
         <v>44</v>
       </c>
@@ -8119,7 +8128,7 @@
       <c r="D531" s="5"/>
       <c r="E531" s="11"/>
     </row>
-    <row r="532" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="4" t="s">
         <v>44</v>
       </c>
@@ -8132,7 +8141,7 @@
       <c r="D532" s="5"/>
       <c r="E532" s="11"/>
     </row>
-    <row r="533" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="4" t="s">
         <v>44</v>
       </c>
@@ -8145,7 +8154,7 @@
       <c r="D533" s="5"/>
       <c r="E533" s="11"/>
     </row>
-    <row r="534" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="4" t="s">
         <v>44</v>
       </c>
@@ -8158,7 +8167,7 @@
       <c r="D534" s="5"/>
       <c r="E534" s="11"/>
     </row>
-    <row r="535" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="4" t="s">
         <v>44</v>
       </c>
@@ -8171,7 +8180,7 @@
       <c r="D535" s="5"/>
       <c r="E535" s="11"/>
     </row>
-    <row r="536" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="4" t="s">
         <v>44</v>
       </c>
@@ -8184,7 +8193,7 @@
       <c r="D536" s="5"/>
       <c r="E536" s="11"/>
     </row>
-    <row r="537" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="4" t="s">
         <v>44</v>
       </c>
@@ -8197,7 +8206,7 @@
       <c r="D537" s="5"/>
       <c r="E537" s="11"/>
     </row>
-    <row r="538" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="4" t="s">
         <v>44</v>
       </c>
@@ -8210,7 +8219,7 @@
       <c r="D538" s="5"/>
       <c r="E538" s="11"/>
     </row>
-    <row r="539" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="4" t="s">
         <v>44</v>
       </c>
@@ -8223,7 +8232,7 @@
       <c r="D539" s="5"/>
       <c r="E539" s="11"/>
     </row>
-    <row r="540" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="4" t="s">
         <v>44</v>
       </c>
@@ -8236,7 +8245,7 @@
       <c r="D540" s="5"/>
       <c r="E540" s="11"/>
     </row>
-    <row r="541" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="4" t="s">
         <v>44</v>
       </c>
@@ -8249,7 +8258,7 @@
       <c r="D541" s="5"/>
       <c r="E541" s="11"/>
     </row>
-    <row r="542" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="4" t="s">
         <v>44</v>
       </c>
@@ -8262,7 +8271,7 @@
       <c r="D542" s="5"/>
       <c r="E542" s="11"/>
     </row>
-    <row r="543" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="4" t="s">
         <v>44</v>
       </c>
@@ -8275,7 +8284,7 @@
       <c r="D543" s="5"/>
       <c r="E543" s="11"/>
     </row>
-    <row r="544" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="4" t="s">
         <v>44</v>
       </c>
@@ -8288,7 +8297,7 @@
       <c r="D544" s="5"/>
       <c r="E544" s="11"/>
     </row>
-    <row r="545" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="4" t="s">
         <v>44</v>
       </c>
@@ -8301,7 +8310,7 @@
       <c r="D545" s="5"/>
       <c r="E545" s="11"/>
     </row>
-    <row r="546" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="4" t="s">
         <v>45</v>
       </c>
@@ -8314,7 +8323,7 @@
       <c r="D546" s="5"/>
       <c r="E546" s="11"/>
     </row>
-    <row r="547" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="4" t="s">
         <v>45</v>
       </c>
@@ -8327,7 +8336,7 @@
       <c r="D547" s="5"/>
       <c r="E547" s="11"/>
     </row>
-    <row r="548" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="4" t="s">
         <v>45</v>
       </c>
@@ -8340,7 +8349,7 @@
       <c r="D548" s="5"/>
       <c r="E548" s="11"/>
     </row>
-    <row r="549" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="4" t="s">
         <v>45</v>
       </c>
@@ -8353,7 +8362,7 @@
       <c r="D549" s="5"/>
       <c r="E549" s="11"/>
     </row>
-    <row r="550" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="4" t="s">
         <v>45</v>
       </c>
@@ -8366,7 +8375,7 @@
       <c r="D550" s="5"/>
       <c r="E550" s="11"/>
     </row>
-    <row r="551" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="4" t="s">
         <v>45</v>
       </c>
@@ -8379,7 +8388,7 @@
       <c r="D551" s="5"/>
       <c r="E551" s="11"/>
     </row>
-    <row r="552" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
         <v>45</v>
       </c>
@@ -8392,7 +8401,7 @@
       <c r="D552" s="5"/>
       <c r="E552" s="11"/>
     </row>
-    <row r="553" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="4" t="s">
         <v>45</v>
       </c>
@@ -8405,7 +8414,7 @@
       <c r="D553" s="5"/>
       <c r="E553" s="11"/>
     </row>
-    <row r="554" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="4" t="s">
         <v>45</v>
       </c>
@@ -8418,7 +8427,7 @@
       <c r="D554" s="5"/>
       <c r="E554" s="11"/>
     </row>
-    <row r="555" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="4" t="s">
         <v>45</v>
       </c>
@@ -8431,7 +8440,7 @@
       <c r="D555" s="5"/>
       <c r="E555" s="11"/>
     </row>
-    <row r="556" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="4" t="s">
         <v>45</v>
       </c>
@@ -8444,7 +8453,7 @@
       <c r="D556" s="5"/>
       <c r="E556" s="11"/>
     </row>
-    <row r="557" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="4" t="s">
         <v>45</v>
       </c>
@@ -8457,7 +8466,7 @@
       <c r="D557" s="5"/>
       <c r="E557" s="11"/>
     </row>
-    <row r="558" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="4" t="s">
         <v>45</v>
       </c>
@@ -8470,7 +8479,7 @@
       <c r="D558" s="5"/>
       <c r="E558" s="11"/>
     </row>
-    <row r="559" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="4" t="s">
         <v>45</v>
       </c>
@@ -8483,7 +8492,7 @@
       <c r="D559" s="5"/>
       <c r="E559" s="11"/>
     </row>
-    <row r="560" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="4" t="s">
         <v>45</v>
       </c>
@@ -8496,7 +8505,7 @@
       <c r="D560" s="5"/>
       <c r="E560" s="11"/>
     </row>
-    <row r="561" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="4" t="s">
         <v>45</v>
       </c>
@@ -8509,7 +8518,7 @@
       <c r="D561" s="5"/>
       <c r="E561" s="11"/>
     </row>
-    <row r="562" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="4" t="s">
         <v>45</v>
       </c>
@@ -8522,7 +8531,7 @@
       <c r="D562" s="5"/>
       <c r="E562" s="11"/>
     </row>
-    <row r="563" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="4" t="s">
         <v>45</v>
       </c>
@@ -8535,7 +8544,7 @@
       <c r="D563" s="5"/>
       <c r="E563" s="11"/>
     </row>
-    <row r="564" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="4" t="s">
         <v>45</v>
       </c>
@@ -8548,7 +8557,7 @@
       <c r="D564" s="5"/>
       <c r="E564" s="11"/>
     </row>
-    <row r="565" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="4" t="s">
         <v>45</v>
       </c>
@@ -8561,7 +8570,7 @@
       <c r="D565" s="5"/>
       <c r="E565" s="11"/>
     </row>
-    <row r="566" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="4" t="s">
         <v>45</v>
       </c>
@@ -8574,7 +8583,7 @@
       <c r="D566" s="5"/>
       <c r="E566" s="11"/>
     </row>
-    <row r="567" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="4" t="s">
         <v>45</v>
       </c>
@@ -8587,7 +8596,7 @@
       <c r="D567" s="5"/>
       <c r="E567" s="11"/>
     </row>
-    <row r="568" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="4" t="s">
         <v>45</v>
       </c>
@@ -8600,7 +8609,7 @@
       <c r="D568" s="5"/>
       <c r="E568" s="11"/>
     </row>
-    <row r="569" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="4" t="s">
         <v>45</v>
       </c>
@@ -8613,7 +8622,7 @@
       <c r="D569" s="5"/>
       <c r="E569" s="11"/>
     </row>
-    <row r="570" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="4" t="s">
         <v>45</v>
       </c>
@@ -8626,7 +8635,7 @@
       <c r="D570" s="5"/>
       <c r="E570" s="11"/>
     </row>
-    <row r="571" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="4" t="s">
         <v>45</v>
       </c>
@@ -8639,7 +8648,7 @@
       <c r="D571" s="5"/>
       <c r="E571" s="11"/>
     </row>
-    <row r="572" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="4" t="s">
         <v>45</v>
       </c>
@@ -8652,7 +8661,7 @@
       <c r="D572" s="5"/>
       <c r="E572" s="11"/>
     </row>
-    <row r="573" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="4" t="s">
         <v>45</v>
       </c>
@@ -8665,7 +8674,7 @@
       <c r="D573" s="5"/>
       <c r="E573" s="11"/>
     </row>
-    <row r="574" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="4" t="s">
         <v>45</v>
       </c>
@@ -8678,7 +8687,7 @@
       <c r="D574" s="5"/>
       <c r="E574" s="11"/>
     </row>
-    <row r="575" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="4" t="s">
         <v>45</v>
       </c>
@@ -8691,7 +8700,7 @@
       <c r="D575" s="5"/>
       <c r="E575" s="11"/>
     </row>
-    <row r="576" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="4" t="s">
         <v>45</v>
       </c>
@@ -8704,7 +8713,7 @@
       <c r="D576" s="5"/>
       <c r="E576" s="11"/>
     </row>
-    <row r="577" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="4" t="s">
         <v>45</v>
       </c>
@@ -8717,7 +8726,7 @@
       <c r="D577" s="5"/>
       <c r="E577" s="11"/>
     </row>
-    <row r="578" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="4" t="s">
         <v>45</v>
       </c>
@@ -8730,7 +8739,7 @@
       <c r="D578" s="5"/>
       <c r="E578" s="11"/>
     </row>
-    <row r="579" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="4" t="s">
         <v>45</v>
       </c>
@@ -8743,7 +8752,7 @@
       <c r="D579" s="5"/>
       <c r="E579" s="11"/>
     </row>
-    <row r="580" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="4" t="s">
         <v>45</v>
       </c>
@@ -8756,7 +8765,7 @@
       <c r="D580" s="5"/>
       <c r="E580" s="11"/>
     </row>
-    <row r="581" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="4" t="s">
         <v>45</v>
       </c>
@@ -8769,7 +8778,7 @@
       <c r="D581" s="5"/>
       <c r="E581" s="11"/>
     </row>
-    <row r="582" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="4" t="s">
         <v>45</v>
       </c>
@@ -8782,7 +8791,7 @@
       <c r="D582" s="5"/>
       <c r="E582" s="11"/>
     </row>
-    <row r="583" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="4" t="s">
         <v>45</v>
       </c>
@@ -8795,7 +8804,7 @@
       <c r="D583" s="5"/>
       <c r="E583" s="11"/>
     </row>
-    <row r="584" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="4" t="s">
         <v>45</v>
       </c>
@@ -8808,7 +8817,7 @@
       <c r="D584" s="5"/>
       <c r="E584" s="11"/>
     </row>
-    <row r="585" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="4" t="s">
         <v>45</v>
       </c>
@@ -8821,7 +8830,7 @@
       <c r="D585" s="5"/>
       <c r="E585" s="11"/>
     </row>
-    <row r="586" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="4" t="s">
         <v>45</v>
       </c>
@@ -8834,7 +8843,7 @@
       <c r="D586" s="5"/>
       <c r="E586" s="11"/>
     </row>
-    <row r="587" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="4" t="s">
         <v>45</v>
       </c>
@@ -8847,7 +8856,7 @@
       <c r="D587" s="5"/>
       <c r="E587" s="11"/>
     </row>
-    <row r="588" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="4" t="s">
         <v>45</v>
       </c>
@@ -8860,7 +8869,7 @@
       <c r="D588" s="5"/>
       <c r="E588" s="11"/>
     </row>
-    <row r="589" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="4" t="s">
         <v>45</v>
       </c>
@@ -8873,7 +8882,7 @@
       <c r="D589" s="5"/>
       <c r="E589" s="11"/>
     </row>
-    <row r="590" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="4" t="s">
         <v>45</v>
       </c>
@@ -8886,7 +8895,7 @@
       <c r="D590" s="5"/>
       <c r="E590" s="11"/>
     </row>
-    <row r="591" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="4" t="s">
         <v>45</v>
       </c>
@@ -8899,7 +8908,7 @@
       <c r="D591" s="5"/>
       <c r="E591" s="11"/>
     </row>
-    <row r="592" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="4" t="s">
         <v>45</v>
       </c>
@@ -8912,7 +8921,7 @@
       <c r="D592" s="5"/>
       <c r="E592" s="11"/>
     </row>
-    <row r="593" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="4" t="s">
         <v>45</v>
       </c>
@@ -8925,7 +8934,7 @@
       <c r="D593" s="5"/>
       <c r="E593" s="11"/>
     </row>
-    <row r="594" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="4" t="s">
         <v>45</v>
       </c>
@@ -8938,7 +8947,7 @@
       <c r="D594" s="5"/>
       <c r="E594" s="11"/>
     </row>
-    <row r="595" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="4" t="s">
         <v>45</v>
       </c>
@@ -8951,7 +8960,7 @@
       <c r="D595" s="5"/>
       <c r="E595" s="11"/>
     </row>
-    <row r="596" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="4" t="s">
         <v>45</v>
       </c>
@@ -8964,7 +8973,7 @@
       <c r="D596" s="5"/>
       <c r="E596" s="11"/>
     </row>
-    <row r="597" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="4" t="s">
         <v>45</v>
       </c>
@@ -8977,7 +8986,7 @@
       <c r="D597" s="5"/>
       <c r="E597" s="11"/>
     </row>
-    <row r="598" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="4" t="s">
         <v>45</v>
       </c>
@@ -8990,7 +8999,7 @@
       <c r="D598" s="5"/>
       <c r="E598" s="11"/>
     </row>
-    <row r="599" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="4" t="s">
         <v>45</v>
       </c>
@@ -9007,7 +9016,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="4" t="s">
         <v>45</v>
       </c>
@@ -9020,7 +9029,7 @@
       <c r="D600" s="5"/>
       <c r="E600" s="11"/>
     </row>
-    <row r="601" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="4" t="s">
         <v>45</v>
       </c>
@@ -9033,7 +9042,7 @@
       <c r="D601" s="5"/>
       <c r="E601" s="11"/>
     </row>
-    <row r="602" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="4" t="s">
         <v>45</v>
       </c>
@@ -9046,7 +9055,7 @@
       <c r="D602" s="5"/>
       <c r="E602" s="11"/>
     </row>
-    <row r="603" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="4" t="s">
         <v>45</v>
       </c>
@@ -9059,7 +9068,7 @@
       <c r="D603" s="5"/>
       <c r="E603" s="11"/>
     </row>
-    <row r="604" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="4" t="s">
         <v>45</v>
       </c>
@@ -9072,7 +9081,7 @@
       <c r="D604" s="5"/>
       <c r="E604" s="11"/>
     </row>
-    <row r="605" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" s="4" t="s">
         <v>45</v>
       </c>
@@ -9085,7 +9094,7 @@
       <c r="D605" s="5"/>
       <c r="E605" s="11"/>
     </row>
-    <row r="606" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" s="4" t="s">
         <v>45</v>
       </c>
@@ -9098,7 +9107,7 @@
       <c r="D606" s="5"/>
       <c r="E606" s="11"/>
     </row>
-    <row r="607" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" s="4" t="s">
         <v>45</v>
       </c>
@@ -9111,7 +9120,7 @@
       <c r="D607" s="5"/>
       <c r="E607" s="11"/>
     </row>
-    <row r="608" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="4" t="s">
         <v>45</v>
       </c>
@@ -9124,7 +9133,7 @@
       <c r="D608" s="5"/>
       <c r="E608" s="11"/>
     </row>
-    <row r="609" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" s="4" t="s">
         <v>45</v>
       </c>
@@ -9137,7 +9146,7 @@
       <c r="D609" s="5"/>
       <c r="E609" s="11"/>
     </row>
-    <row r="610" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" s="4" t="s">
         <v>45</v>
       </c>
@@ -9150,7 +9159,7 @@
       <c r="D610" s="5"/>
       <c r="E610" s="11"/>
     </row>
-    <row r="611" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="4" t="s">
         <v>45</v>
       </c>
@@ -9163,7 +9172,7 @@
       <c r="D611" s="5"/>
       <c r="E611" s="11"/>
     </row>
-    <row r="612" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="4" t="s">
         <v>45</v>
       </c>
@@ -9176,7 +9185,7 @@
       <c r="D612" s="5"/>
       <c r="E612" s="11"/>
     </row>
-    <row r="613" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="4" t="s">
         <v>45</v>
       </c>
@@ -9189,7 +9198,7 @@
       <c r="D613" s="5"/>
       <c r="E613" s="11"/>
     </row>
-    <row r="614" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="4" t="s">
         <v>45</v>
       </c>
@@ -9202,7 +9211,7 @@
       <c r="D614" s="5"/>
       <c r="E614" s="11"/>
     </row>
-    <row r="615" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" s="4" t="s">
         <v>45</v>
       </c>
@@ -9215,7 +9224,7 @@
       <c r="D615" s="5"/>
       <c r="E615" s="11"/>
     </row>
-    <row r="616" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" s="4" t="s">
         <v>45</v>
       </c>
@@ -9228,7 +9237,7 @@
       <c r="D616" s="5"/>
       <c r="E616" s="11"/>
     </row>
-    <row r="617" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" s="4" t="s">
         <v>45</v>
       </c>
@@ -9241,7 +9250,7 @@
       <c r="D617" s="5"/>
       <c r="E617" s="11"/>
     </row>
-    <row r="618" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" s="4" t="s">
         <v>45</v>
       </c>
@@ -9254,7 +9263,7 @@
       <c r="D618" s="5"/>
       <c r="E618" s="11"/>
     </row>
-    <row r="619" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" s="4" t="s">
         <v>45</v>
       </c>
@@ -9267,7 +9276,7 @@
       <c r="D619" s="5"/>
       <c r="E619" s="11"/>
     </row>
-    <row r="620" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" s="4" t="s">
         <v>45</v>
       </c>
@@ -9280,7 +9289,7 @@
       <c r="D620" s="5"/>
       <c r="E620" s="11"/>
     </row>
-    <row r="621" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" s="4" t="s">
         <v>45</v>
       </c>
@@ -9293,7 +9302,7 @@
       <c r="D621" s="5"/>
       <c r="E621" s="11"/>
     </row>
-    <row r="622" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="4" t="s">
         <v>45</v>
       </c>
@@ -9306,7 +9315,7 @@
       <c r="D622" s="5"/>
       <c r="E622" s="11"/>
     </row>
-    <row r="623" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="4" t="s">
         <v>45</v>
       </c>
@@ -9319,7 +9328,7 @@
       <c r="D623" s="5"/>
       <c r="E623" s="11"/>
     </row>
-    <row r="624" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="4" t="s">
         <v>45</v>
       </c>
@@ -9332,7 +9341,7 @@
       <c r="D624" s="5"/>
       <c r="E624" s="11"/>
     </row>
-    <row r="625" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="4" t="s">
         <v>45</v>
       </c>
@@ -9345,7 +9354,7 @@
       <c r="D625" s="5"/>
       <c r="E625" s="11"/>
     </row>
-    <row r="626" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="4" t="s">
         <v>45</v>
       </c>
@@ -9358,7 +9367,7 @@
       <c r="D626" s="5"/>
       <c r="E626" s="11"/>
     </row>
-    <row r="627" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="4" t="s">
         <v>45</v>
       </c>
@@ -9371,7 +9380,7 @@
       <c r="D627" s="5"/>
       <c r="E627" s="11"/>
     </row>
-    <row r="628" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="4" t="s">
         <v>45</v>
       </c>
@@ -9384,7 +9393,7 @@
       <c r="D628" s="5"/>
       <c r="E628" s="11"/>
     </row>
-    <row r="629" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="4" t="s">
         <v>45</v>
       </c>
@@ -9397,7 +9406,7 @@
       <c r="D629" s="5"/>
       <c r="E629" s="11"/>
     </row>
-    <row r="630" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="4" t="s">
         <v>45</v>
       </c>
@@ -9410,7 +9419,7 @@
       <c r="D630" s="5"/>
       <c r="E630" s="11"/>
     </row>
-    <row r="631" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" s="4" t="s">
         <v>45</v>
       </c>
@@ -9423,7 +9432,7 @@
       <c r="D631" s="5"/>
       <c r="E631" s="11"/>
     </row>
-    <row r="632" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" s="4" t="s">
         <v>45</v>
       </c>
@@ -9436,7 +9445,7 @@
       <c r="D632" s="5"/>
       <c r="E632" s="11"/>
     </row>
-    <row r="633" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" s="4" t="s">
         <v>45</v>
       </c>
@@ -9449,7 +9458,7 @@
       <c r="D633" s="5"/>
       <c r="E633" s="11"/>
     </row>
-    <row r="634" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" s="4" t="s">
         <v>45</v>
       </c>
@@ -9462,7 +9471,7 @@
       <c r="D634" s="5"/>
       <c r="E634" s="11"/>
     </row>
-    <row r="635" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" s="4" t="s">
         <v>45</v>
       </c>
@@ -9475,7 +9484,7 @@
       <c r="D635" s="5"/>
       <c r="E635" s="11"/>
     </row>
-    <row r="636" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" s="4" t="s">
         <v>45</v>
       </c>
@@ -9488,7 +9497,7 @@
       <c r="D636" s="5"/>
       <c r="E636" s="11"/>
     </row>
-    <row r="637" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="4" t="s">
         <v>45</v>
       </c>
@@ -9501,7 +9510,7 @@
       <c r="D637" s="5"/>
       <c r="E637" s="11"/>
     </row>
-    <row r="638" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="4" t="s">
         <v>45</v>
       </c>
@@ -9514,7 +9523,7 @@
       <c r="D638" s="5"/>
       <c r="E638" s="11"/>
     </row>
-    <row r="639" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="4" t="s">
         <v>45</v>
       </c>
@@ -9527,7 +9536,7 @@
       <c r="D639" s="5"/>
       <c r="E639" s="11"/>
     </row>
-    <row r="640" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="4" t="s">
         <v>45</v>
       </c>
@@ -9540,7 +9549,7 @@
       <c r="D640" s="5"/>
       <c r="E640" s="11"/>
     </row>
-    <row r="641" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="4" t="s">
         <v>45</v>
       </c>
@@ -9553,7 +9562,7 @@
       <c r="D641" s="5"/>
       <c r="E641" s="11"/>
     </row>
-    <row r="642" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="4" t="s">
         <v>45</v>
       </c>
@@ -9566,7 +9575,7 @@
       <c r="D642" s="5"/>
       <c r="E642" s="11"/>
     </row>
-    <row r="643" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="4" t="s">
         <v>45</v>
       </c>
@@ -9579,7 +9588,7 @@
       <c r="D643" s="5"/>
       <c r="E643" s="11"/>
     </row>
-    <row r="644" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" s="4" t="s">
         <v>45</v>
       </c>
@@ -9592,7 +9601,7 @@
       <c r="D644" s="5"/>
       <c r="E644" s="11"/>
     </row>
-    <row r="645" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" s="4" t="s">
         <v>45</v>
       </c>
@@ -9605,7 +9614,7 @@
       <c r="D645" s="5"/>
       <c r="E645" s="11"/>
     </row>
-    <row r="646" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" s="4" t="s">
         <v>45</v>
       </c>
@@ -9618,7 +9627,7 @@
       <c r="D646" s="5"/>
       <c r="E646" s="11"/>
     </row>
-    <row r="647" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" s="4" t="s">
         <v>45</v>
       </c>
@@ -9631,7 +9640,7 @@
       <c r="D647" s="5"/>
       <c r="E647" s="11"/>
     </row>
-    <row r="648" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" s="4" t="s">
         <v>45</v>
       </c>
@@ -9644,7 +9653,7 @@
       <c r="D648" s="5"/>
       <c r="E648" s="11"/>
     </row>
-    <row r="649" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" s="4" t="s">
         <v>45</v>
       </c>
@@ -9657,7 +9666,7 @@
       <c r="D649" s="5"/>
       <c r="E649" s="11"/>
     </row>
-    <row r="650" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="4" t="s">
         <v>45</v>
       </c>
@@ -9670,7 +9679,7 @@
       <c r="D650" s="5"/>
       <c r="E650" s="11"/>
     </row>
-    <row r="651" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" s="4" t="s">
         <v>45</v>
       </c>
@@ -9683,7 +9692,7 @@
       <c r="D651" s="5"/>
       <c r="E651" s="11"/>
     </row>
-    <row r="652" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" s="4" t="s">
         <v>45</v>
       </c>
@@ -9696,7 +9705,7 @@
       <c r="D652" s="5"/>
       <c r="E652" s="11"/>
     </row>
-    <row r="653" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" s="4" t="s">
         <v>45</v>
       </c>
@@ -9709,7 +9718,7 @@
       <c r="D653" s="5"/>
       <c r="E653" s="11"/>
     </row>
-    <row r="654" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" s="4" t="s">
         <v>45</v>
       </c>
@@ -9722,7 +9731,7 @@
       <c r="D654" s="5"/>
       <c r="E654" s="11"/>
     </row>
-    <row r="655" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" s="4" t="s">
         <v>45</v>
       </c>
@@ -9735,7 +9744,7 @@
       <c r="D655" s="5"/>
       <c r="E655" s="11"/>
     </row>
-    <row r="656" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" s="4" t="s">
         <v>45</v>
       </c>
@@ -9748,7 +9757,7 @@
       <c r="D656" s="5"/>
       <c r="E656" s="11"/>
     </row>
-    <row r="657" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" s="4" t="s">
         <v>45</v>
       </c>
@@ -9761,7 +9770,7 @@
       <c r="D657" s="5"/>
       <c r="E657" s="11"/>
     </row>
-    <row r="658" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" s="4" t="s">
         <v>45</v>
       </c>
@@ -9774,7 +9783,7 @@
       <c r="D658" s="5"/>
       <c r="E658" s="11"/>
     </row>
-    <row r="659" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" s="4" t="s">
         <v>45</v>
       </c>
@@ -9787,7 +9796,7 @@
       <c r="D659" s="5"/>
       <c r="E659" s="11"/>
     </row>
-    <row r="660" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" s="4" t="s">
         <v>45</v>
       </c>
@@ -9800,7 +9809,7 @@
       <c r="D660" s="5"/>
       <c r="E660" s="11"/>
     </row>
-    <row r="661" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" s="4" t="s">
         <v>45</v>
       </c>
@@ -9813,7 +9822,7 @@
       <c r="D661" s="5"/>
       <c r="E661" s="11"/>
     </row>
-    <row r="662" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" s="4" t="s">
         <v>45</v>
       </c>
@@ -9826,7 +9835,7 @@
       <c r="D662" s="5"/>
       <c r="E662" s="11"/>
     </row>
-    <row r="663" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="4" t="s">
         <v>45</v>
       </c>
@@ -9839,7 +9848,7 @@
       <c r="D663" s="5"/>
       <c r="E663" s="11"/>
     </row>
-    <row r="664" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="4" t="s">
         <v>45</v>
       </c>
@@ -9852,7 +9861,7 @@
       <c r="D664" s="5"/>
       <c r="E664" s="11"/>
     </row>
-    <row r="665" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="4" t="s">
         <v>45</v>
       </c>
@@ -9865,7 +9874,7 @@
       <c r="D665" s="5"/>
       <c r="E665" s="11"/>
     </row>
-    <row r="666" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" s="4" t="s">
         <v>46</v>
       </c>
@@ -9878,7 +9887,7 @@
       <c r="D666" s="5"/>
       <c r="E666" s="11"/>
     </row>
-    <row r="667" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" s="4" t="s">
         <v>46</v>
       </c>
@@ -9891,7 +9900,7 @@
       <c r="D667" s="5"/>
       <c r="E667" s="11"/>
     </row>
-    <row r="668" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="4" t="s">
         <v>46</v>
       </c>
@@ -9904,7 +9913,7 @@
       <c r="D668" s="5"/>
       <c r="E668" s="11"/>
     </row>
-    <row r="669" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" s="4" t="s">
         <v>46</v>
       </c>
@@ -9917,7 +9926,7 @@
       <c r="D669" s="5"/>
       <c r="E669" s="11"/>
     </row>
-    <row r="670" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" s="4" t="s">
         <v>46</v>
       </c>
@@ -9930,7 +9939,7 @@
       <c r="D670" s="5"/>
       <c r="E670" s="11"/>
     </row>
-    <row r="671" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" s="4" t="s">
         <v>46</v>
       </c>
@@ -9943,7 +9952,7 @@
       <c r="D671" s="5"/>
       <c r="E671" s="11"/>
     </row>
-    <row r="672" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" s="4" t="s">
         <v>46</v>
       </c>
@@ -9956,7 +9965,7 @@
       <c r="D672" s="5"/>
       <c r="E672" s="11"/>
     </row>
-    <row r="673" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" s="4" t="s">
         <v>46</v>
       </c>
@@ -9969,7 +9978,7 @@
       <c r="D673" s="5"/>
       <c r="E673" s="11"/>
     </row>
-    <row r="674" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" s="4" t="s">
         <v>46</v>
       </c>
@@ -9982,7 +9991,7 @@
       <c r="D674" s="5"/>
       <c r="E674" s="11"/>
     </row>
-    <row r="675" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" s="4" t="s">
         <v>46</v>
       </c>
@@ -9995,7 +10004,7 @@
       <c r="D675" s="5"/>
       <c r="E675" s="11"/>
     </row>
-    <row r="676" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" s="4" t="s">
         <v>46</v>
       </c>
@@ -10008,7 +10017,7 @@
       <c r="D676" s="5"/>
       <c r="E676" s="11"/>
     </row>
-    <row r="677" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" s="4" t="s">
         <v>46</v>
       </c>
@@ -10021,7 +10030,7 @@
       <c r="D677" s="5"/>
       <c r="E677" s="11"/>
     </row>
-    <row r="678" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="4" t="s">
         <v>46</v>
       </c>
@@ -10034,7 +10043,7 @@
       <c r="D678" s="5"/>
       <c r="E678" s="11"/>
     </row>
-    <row r="679" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" s="4" t="s">
         <v>46</v>
       </c>
@@ -10047,7 +10056,7 @@
       <c r="D679" s="5"/>
       <c r="E679" s="11"/>
     </row>
-    <row r="680" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" s="4" t="s">
         <v>46</v>
       </c>
@@ -10060,7 +10069,7 @@
       <c r="D680" s="5"/>
       <c r="E680" s="11"/>
     </row>
-    <row r="681" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" s="4" t="s">
         <v>46</v>
       </c>
@@ -10073,7 +10082,7 @@
       <c r="D681" s="5"/>
       <c r="E681" s="11"/>
     </row>
-    <row r="682" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" s="4" t="s">
         <v>46</v>
       </c>
@@ -10086,7 +10095,7 @@
       <c r="D682" s="5"/>
       <c r="E682" s="11"/>
     </row>
-    <row r="683" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" s="4" t="s">
         <v>46</v>
       </c>
@@ -10099,7 +10108,7 @@
       <c r="D683" s="5"/>
       <c r="E683" s="11"/>
     </row>
-    <row r="684" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" s="4" t="s">
         <v>46</v>
       </c>
@@ -10112,7 +10121,7 @@
       <c r="D684" s="5"/>
       <c r="E684" s="11"/>
     </row>
-    <row r="685" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" s="4" t="s">
         <v>46</v>
       </c>
@@ -10125,7 +10134,7 @@
       <c r="D685" s="5"/>
       <c r="E685" s="11"/>
     </row>
-    <row r="686" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" s="4" t="s">
         <v>46</v>
       </c>
@@ -10138,7 +10147,7 @@
       <c r="D686" s="5"/>
       <c r="E686" s="11"/>
     </row>
-    <row r="687" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" s="4" t="s">
         <v>46</v>
       </c>
@@ -10151,7 +10160,7 @@
       <c r="D687" s="5"/>
       <c r="E687" s="11"/>
     </row>
-    <row r="688" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688" s="4" t="s">
         <v>46</v>
       </c>
@@ -10164,7 +10173,7 @@
       <c r="D688" s="5"/>
       <c r="E688" s="11"/>
     </row>
-    <row r="689" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689" s="4" t="s">
         <v>46</v>
       </c>
@@ -10177,7 +10186,7 @@
       <c r="D689" s="5"/>
       <c r="E689" s="11"/>
     </row>
-    <row r="690" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690" s="4" t="s">
         <v>46</v>
       </c>
@@ -10190,7 +10199,7 @@
       <c r="D690" s="5"/>
       <c r="E690" s="11"/>
     </row>
-    <row r="691" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691" s="4" t="s">
         <v>46</v>
       </c>
@@ -10203,7 +10212,7 @@
       <c r="D691" s="5"/>
       <c r="E691" s="11"/>
     </row>
-    <row r="692" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692" s="4" t="s">
         <v>46</v>
       </c>
@@ -10216,7 +10225,7 @@
       <c r="D692" s="5"/>
       <c r="E692" s="11"/>
     </row>
-    <row r="693" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" s="4" t="s">
         <v>46</v>
       </c>
@@ -10229,7 +10238,7 @@
       <c r="D693" s="5"/>
       <c r="E693" s="11"/>
     </row>
-    <row r="694" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694" s="4" t="s">
         <v>46</v>
       </c>
@@ -10242,7 +10251,7 @@
       <c r="D694" s="5"/>
       <c r="E694" s="11"/>
     </row>
-    <row r="695" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695" s="4" t="s">
         <v>46</v>
       </c>
@@ -10255,7 +10264,7 @@
       <c r="D695" s="5"/>
       <c r="E695" s="11"/>
     </row>
-    <row r="696" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" s="4" t="s">
         <v>46</v>
       </c>
@@ -10268,7 +10277,7 @@
       <c r="D696" s="5"/>
       <c r="E696" s="11"/>
     </row>
-    <row r="697" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697" s="4" t="s">
         <v>46</v>
       </c>
@@ -10281,7 +10290,7 @@
       <c r="D697" s="5"/>
       <c r="E697" s="11"/>
     </row>
-    <row r="698" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698" s="4" t="s">
         <v>46</v>
       </c>
@@ -10294,7 +10303,7 @@
       <c r="D698" s="5"/>
       <c r="E698" s="11"/>
     </row>
-    <row r="699" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699" s="4" t="s">
         <v>46</v>
       </c>
@@ -10307,7 +10316,7 @@
       <c r="D699" s="5"/>
       <c r="E699" s="11"/>
     </row>
-    <row r="700" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" s="4" t="s">
         <v>46</v>
       </c>
@@ -10320,7 +10329,7 @@
       <c r="D700" s="5"/>
       <c r="E700" s="11"/>
     </row>
-    <row r="701" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" s="4" t="s">
         <v>46</v>
       </c>
@@ -10333,7 +10342,7 @@
       <c r="D701" s="5"/>
       <c r="E701" s="11"/>
     </row>
-    <row r="702" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" s="4" t="s">
         <v>46</v>
       </c>
@@ -10346,7 +10355,7 @@
       <c r="D702" s="5"/>
       <c r="E702" s="11"/>
     </row>
-    <row r="703" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" s="4" t="s">
         <v>46</v>
       </c>
@@ -10359,7 +10368,7 @@
       <c r="D703" s="5"/>
       <c r="E703" s="11"/>
     </row>
-    <row r="704" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" s="4" t="s">
         <v>46</v>
       </c>
@@ -10372,7 +10381,7 @@
       <c r="D704" s="5"/>
       <c r="E704" s="11"/>
     </row>
-    <row r="705" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" s="4" t="s">
         <v>46</v>
       </c>
@@ -10385,7 +10394,7 @@
       <c r="D705" s="5"/>
       <c r="E705" s="11"/>
     </row>
-    <row r="706" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" s="4" t="s">
         <v>46</v>
       </c>
@@ -10398,7 +10407,7 @@
       <c r="D706" s="5"/>
       <c r="E706" s="11"/>
     </row>
-    <row r="707" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" s="4" t="s">
         <v>46</v>
       </c>
@@ -10411,7 +10420,7 @@
       <c r="D707" s="5"/>
       <c r="E707" s="11"/>
     </row>
-    <row r="708" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" s="4" t="s">
         <v>46</v>
       </c>
@@ -10424,7 +10433,7 @@
       <c r="D708" s="5"/>
       <c r="E708" s="11"/>
     </row>
-    <row r="709" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" s="4" t="s">
         <v>46</v>
       </c>
@@ -10437,7 +10446,7 @@
       <c r="D709" s="5"/>
       <c r="E709" s="11"/>
     </row>
-    <row r="710" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" s="4" t="s">
         <v>46</v>
       </c>
@@ -10450,7 +10459,7 @@
       <c r="D710" s="5"/>
       <c r="E710" s="11"/>
     </row>
-    <row r="711" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711" s="4" t="s">
         <v>46</v>
       </c>
@@ -10463,7 +10472,7 @@
       <c r="D711" s="5"/>
       <c r="E711" s="11"/>
     </row>
-    <row r="712" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712" s="4" t="s">
         <v>46</v>
       </c>
@@ -10476,7 +10485,7 @@
       <c r="D712" s="5"/>
       <c r="E712" s="11"/>
     </row>
-    <row r="713" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713" s="4" t="s">
         <v>46</v>
       </c>
@@ -10489,7 +10498,7 @@
       <c r="D713" s="5"/>
       <c r="E713" s="11"/>
     </row>
-    <row r="714" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714" s="4" t="s">
         <v>46</v>
       </c>
@@ -10502,7 +10511,7 @@
       <c r="D714" s="5"/>
       <c r="E714" s="11"/>
     </row>
-    <row r="715" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715" s="4" t="s">
         <v>46</v>
       </c>
@@ -10515,7 +10524,7 @@
       <c r="D715" s="5"/>
       <c r="E715" s="11"/>
     </row>
-    <row r="716" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716" s="4" t="s">
         <v>46</v>
       </c>
@@ -10528,7 +10537,7 @@
       <c r="D716" s="5"/>
       <c r="E716" s="11"/>
     </row>
-    <row r="717" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" s="4" t="s">
         <v>46</v>
       </c>
@@ -10541,7 +10550,7 @@
       <c r="D717" s="5"/>
       <c r="E717" s="11"/>
     </row>
-    <row r="718" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718" s="4" t="s">
         <v>46</v>
       </c>
@@ -10554,7 +10563,7 @@
       <c r="D718" s="5"/>
       <c r="E718" s="11"/>
     </row>
-    <row r="719" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719" s="4" t="s">
         <v>46</v>
       </c>
@@ -10567,7 +10576,7 @@
       <c r="D719" s="5"/>
       <c r="E719" s="11"/>
     </row>
-    <row r="720" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720" s="4" t="s">
         <v>46</v>
       </c>
@@ -10580,7 +10589,7 @@
       <c r="D720" s="5"/>
       <c r="E720" s="11"/>
     </row>
-    <row r="721" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721" s="4" t="s">
         <v>46</v>
       </c>
@@ -10593,7 +10602,7 @@
       <c r="D721" s="5"/>
       <c r="E721" s="11"/>
     </row>
-    <row r="722" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722" s="4" t="s">
         <v>46</v>
       </c>
@@ -10606,7 +10615,7 @@
       <c r="D722" s="5"/>
       <c r="E722" s="11"/>
     </row>
-    <row r="723" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723" s="4" t="s">
         <v>46</v>
       </c>
@@ -10619,7 +10628,7 @@
       <c r="D723" s="5"/>
       <c r="E723" s="11"/>
     </row>
-    <row r="724" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724" s="4" t="s">
         <v>46</v>
       </c>
@@ -10632,7 +10641,7 @@
       <c r="D724" s="5"/>
       <c r="E724" s="11"/>
     </row>
-    <row r="725" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" s="4" t="s">
         <v>46</v>
       </c>
@@ -10645,7 +10654,7 @@
       <c r="D725" s="5"/>
       <c r="E725" s="11"/>
     </row>
-    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A726" s="4" t="s">
         <v>43</v>
       </c>
@@ -10659,7 +10668,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A727" s="4" t="s">
         <v>43</v>
       </c>
@@ -10673,7 +10682,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A728" s="4" t="s">
         <v>43</v>
       </c>
@@ -10697,7 +10706,6 @@
       <c r="D729" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E729" s="13"/>
     </row>
     <row r="730" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C730">
@@ -10706,9 +10714,8 @@
       <c r="D730" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E730" s="13"/>
-    </row>
-    <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="731" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
         <v>43</v>
       </c>
@@ -10721,11 +10728,11 @@
       <c r="D731" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E731" s="13" t="s">
+      <c r="E731" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
         <v>43</v>
       </c>
@@ -10738,11 +10745,11 @@
       <c r="D732" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E732" s="13" t="s">
+      <c r="E732" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
         <v>43</v>
       </c>
@@ -10755,7 +10762,6 @@
       <c r="D733" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E733" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD53AFC-0B09-4D0F-959C-3E85FF045189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BDAC5D-FCD0-4D52-9F7C-6FE96A2976A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="134">
   <si>
     <t>Категорија</t>
   </si>
@@ -496,6 +496,12 @@
   </si>
   <si>
     <t>Конвексен и неконвексен многуаголник</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbzRNdVvXmAA6btNC3cNZyL-urnj0luUAdY2O0gYPGO5nAZoHy6rOKLrCuLrDLR1ec6VHw/exec</t>
+  </si>
+  <si>
+    <t>Осна симетрија, транслација, ротација</t>
   </si>
 </sst>
 </file>
@@ -697,7 +703,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="7"/>
+        <filter val="8"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -6101,7 +6107,7 @@
       <c r="D376" s="5"/>
       <c r="E376" s="11"/>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>44</v>
       </c>
@@ -6118,7 +6124,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>44</v>
       </c>
@@ -6131,7 +6137,7 @@
       <c r="D378" s="5"/>
       <c r="E378" s="11"/>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>44</v>
       </c>
@@ -6144,7 +6150,7 @@
       <c r="D379" s="5"/>
       <c r="E379" s="11"/>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>44</v>
       </c>
@@ -6157,7 +6163,7 @@
       <c r="D380" s="5"/>
       <c r="E380" s="11"/>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>44</v>
       </c>
@@ -6170,7 +6176,7 @@
       <c r="D381" s="5"/>
       <c r="E381" s="11"/>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>44</v>
       </c>
@@ -6183,7 +6189,7 @@
       <c r="D382" s="5"/>
       <c r="E382" s="11"/>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
         <v>44</v>
       </c>
@@ -6196,7 +6202,7 @@
       <c r="D383" s="5"/>
       <c r="E383" s="11"/>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
         <v>44</v>
       </c>
@@ -6209,7 +6215,7 @@
       <c r="D384" s="5"/>
       <c r="E384" s="11"/>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
         <v>44</v>
       </c>
@@ -6222,7 +6228,7 @@
       <c r="D385" s="5"/>
       <c r="E385" s="11"/>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
         <v>44</v>
       </c>
@@ -6235,7 +6241,7 @@
       <c r="D386" s="5"/>
       <c r="E386" s="11"/>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
         <v>44</v>
       </c>
@@ -6248,7 +6254,7 @@
       <c r="D387" s="5"/>
       <c r="E387" s="11"/>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
         <v>44</v>
       </c>
@@ -6261,7 +6267,7 @@
       <c r="D388" s="5"/>
       <c r="E388" s="11"/>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
         <v>44</v>
       </c>
@@ -6274,7 +6280,7 @@
       <c r="D389" s="5"/>
       <c r="E389" s="11"/>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
         <v>44</v>
       </c>
@@ -6287,7 +6293,7 @@
       <c r="D390" s="5"/>
       <c r="E390" s="11"/>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
         <v>44</v>
       </c>
@@ -6300,7 +6306,7 @@
       <c r="D391" s="5"/>
       <c r="E391" s="11"/>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
         <v>44</v>
       </c>
@@ -6313,7 +6319,7 @@
       <c r="D392" s="5"/>
       <c r="E392" s="11"/>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
         <v>44</v>
       </c>
@@ -6326,7 +6332,7 @@
       <c r="D393" s="5"/>
       <c r="E393" s="11"/>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
         <v>44</v>
       </c>
@@ -6339,7 +6345,7 @@
       <c r="D394" s="5"/>
       <c r="E394" s="11"/>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
         <v>44</v>
       </c>
@@ -6352,7 +6358,7 @@
       <c r="D395" s="5"/>
       <c r="E395" s="11"/>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
         <v>44</v>
       </c>
@@ -6365,7 +6371,7 @@
       <c r="D396" s="5"/>
       <c r="E396" s="11"/>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>44</v>
       </c>
@@ -6378,7 +6384,7 @@
       <c r="D397" s="5"/>
       <c r="E397" s="11"/>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>44</v>
       </c>
@@ -6391,7 +6397,7 @@
       <c r="D398" s="5"/>
       <c r="E398" s="11"/>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
         <v>44</v>
       </c>
@@ -6404,7 +6410,7 @@
       <c r="D399" s="5"/>
       <c r="E399" s="11"/>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
         <v>44</v>
       </c>
@@ -6417,7 +6423,7 @@
       <c r="D400" s="5"/>
       <c r="E400" s="11"/>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>44</v>
       </c>
@@ -6430,7 +6436,7 @@
       <c r="D401" s="5"/>
       <c r="E401" s="11"/>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>44</v>
       </c>
@@ -6443,7 +6449,7 @@
       <c r="D402" s="5"/>
       <c r="E402" s="11"/>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>44</v>
       </c>
@@ -6456,7 +6462,7 @@
       <c r="D403" s="5"/>
       <c r="E403" s="11"/>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>44</v>
       </c>
@@ -6469,7 +6475,7 @@
       <c r="D404" s="5"/>
       <c r="E404" s="11"/>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
         <v>44</v>
       </c>
@@ -6482,7 +6488,7 @@
       <c r="D405" s="5"/>
       <c r="E405" s="11"/>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>44</v>
       </c>
@@ -6495,7 +6501,7 @@
       <c r="D406" s="5"/>
       <c r="E406" s="11"/>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>44</v>
       </c>
@@ -6508,7 +6514,7 @@
       <c r="D407" s="5"/>
       <c r="E407" s="11"/>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>44</v>
       </c>
@@ -6521,7 +6527,7 @@
       <c r="D408" s="5"/>
       <c r="E408" s="11"/>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>44</v>
       </c>
@@ -6534,7 +6540,7 @@
       <c r="D409" s="5"/>
       <c r="E409" s="11"/>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>44</v>
       </c>
@@ -6547,7 +6553,7 @@
       <c r="D410" s="5"/>
       <c r="E410" s="11"/>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>44</v>
       </c>
@@ -6560,7 +6566,7 @@
       <c r="D411" s="5"/>
       <c r="E411" s="11"/>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>44</v>
       </c>
@@ -6573,7 +6579,7 @@
       <c r="D412" s="5"/>
       <c r="E412" s="11"/>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
         <v>44</v>
       </c>
@@ -6586,7 +6592,7 @@
       <c r="D413" s="5"/>
       <c r="E413" s="11"/>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
         <v>44</v>
       </c>
@@ -6599,7 +6605,7 @@
       <c r="D414" s="5"/>
       <c r="E414" s="11"/>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
         <v>44</v>
       </c>
@@ -6612,7 +6618,7 @@
       <c r="D415" s="5"/>
       <c r="E415" s="11"/>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
         <v>44</v>
       </c>
@@ -6625,7 +6631,7 @@
       <c r="D416" s="5"/>
       <c r="E416" s="11"/>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
         <v>44</v>
       </c>
@@ -6638,7 +6644,7 @@
       <c r="D417" s="5"/>
       <c r="E417" s="11"/>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
         <v>44</v>
       </c>
@@ -6651,7 +6657,7 @@
       <c r="D418" s="5"/>
       <c r="E418" s="11"/>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
         <v>44</v>
       </c>
@@ -6664,7 +6670,7 @@
       <c r="D419" s="5"/>
       <c r="E419" s="11"/>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
         <v>44</v>
       </c>
@@ -6677,7 +6683,7 @@
       <c r="D420" s="5"/>
       <c r="E420" s="11"/>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
         <v>44</v>
       </c>
@@ -6690,7 +6696,7 @@
       <c r="D421" s="5"/>
       <c r="E421" s="11"/>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
         <v>44</v>
       </c>
@@ -6703,7 +6709,7 @@
       <c r="D422" s="5"/>
       <c r="E422" s="11"/>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
         <v>44</v>
       </c>
@@ -6716,7 +6722,7 @@
       <c r="D423" s="5"/>
       <c r="E423" s="11"/>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
         <v>44</v>
       </c>
@@ -6729,7 +6735,7 @@
       <c r="D424" s="5"/>
       <c r="E424" s="11"/>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
         <v>44</v>
       </c>
@@ -6742,7 +6748,7 @@
       <c r="D425" s="5"/>
       <c r="E425" s="11"/>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
         <v>44</v>
       </c>
@@ -6755,7 +6761,7 @@
       <c r="D426" s="5"/>
       <c r="E426" s="11"/>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
         <v>44</v>
       </c>
@@ -6768,7 +6774,7 @@
       <c r="D427" s="5"/>
       <c r="E427" s="11"/>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
         <v>44</v>
       </c>
@@ -6781,7 +6787,7 @@
       <c r="D428" s="5"/>
       <c r="E428" s="11"/>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
         <v>44</v>
       </c>
@@ -6794,7 +6800,7 @@
       <c r="D429" s="5"/>
       <c r="E429" s="11"/>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
         <v>44</v>
       </c>
@@ -6807,7 +6813,7 @@
       <c r="D430" s="5"/>
       <c r="E430" s="11"/>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
         <v>44</v>
       </c>
@@ -6820,7 +6826,7 @@
       <c r="D431" s="5"/>
       <c r="E431" s="11"/>
     </row>
-    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
         <v>44</v>
       </c>
@@ -6837,7 +6843,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
         <v>44</v>
       </c>
@@ -6850,7 +6856,7 @@
       <c r="D433" s="5"/>
       <c r="E433" s="11"/>
     </row>
-    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
         <v>44</v>
       </c>
@@ -6867,7 +6873,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
         <v>44</v>
       </c>
@@ -6877,10 +6883,14 @@
       <c r="C435" s="4">
         <v>4</v>
       </c>
-      <c r="D435" s="5"/>
-      <c r="E435" s="11"/>
-    </row>
-    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D435" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E435" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
         <v>44</v>
       </c>
@@ -6893,7 +6903,7 @@
       <c r="D436" s="5"/>
       <c r="E436" s="11"/>
     </row>
-    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
         <v>44</v>
       </c>
@@ -6906,7 +6916,7 @@
       <c r="D437" s="5"/>
       <c r="E437" s="11"/>
     </row>
-    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
         <v>44</v>
       </c>
@@ -6919,7 +6929,7 @@
       <c r="D438" s="5"/>
       <c r="E438" s="11"/>
     </row>
-    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
         <v>44</v>
       </c>
@@ -6932,7 +6942,7 @@
       <c r="D439" s="5"/>
       <c r="E439" s="11"/>
     </row>
-    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
         <v>44</v>
       </c>
@@ -6945,7 +6955,7 @@
       <c r="D440" s="5"/>
       <c r="E440" s="11"/>
     </row>
-    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
         <v>44</v>
       </c>
@@ -6958,7 +6968,7 @@
       <c r="D441" s="5"/>
       <c r="E441" s="11"/>
     </row>
-    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
         <v>44</v>
       </c>
@@ -6971,7 +6981,7 @@
       <c r="D442" s="5"/>
       <c r="E442" s="11"/>
     </row>
-    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
         <v>44</v>
       </c>
@@ -6984,7 +6994,7 @@
       <c r="D443" s="5"/>
       <c r="E443" s="11"/>
     </row>
-    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
         <v>44</v>
       </c>
@@ -6997,7 +7007,7 @@
       <c r="D444" s="5"/>
       <c r="E444" s="11"/>
     </row>
-    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
         <v>44</v>
       </c>
@@ -7010,7 +7020,7 @@
       <c r="D445" s="5"/>
       <c r="E445" s="11"/>
     </row>
-    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
         <v>44</v>
       </c>
@@ -7023,7 +7033,7 @@
       <c r="D446" s="5"/>
       <c r="E446" s="11"/>
     </row>
-    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
         <v>44</v>
       </c>
@@ -7036,7 +7046,7 @@
       <c r="D447" s="5"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
         <v>44</v>
       </c>
@@ -7049,7 +7059,7 @@
       <c r="D448" s="5"/>
       <c r="E448" s="11"/>
     </row>
-    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
         <v>44</v>
       </c>
@@ -7062,7 +7072,7 @@
       <c r="D449" s="5"/>
       <c r="E449" s="11"/>
     </row>
-    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
         <v>44</v>
       </c>
@@ -7075,7 +7085,7 @@
       <c r="D450" s="5"/>
       <c r="E450" s="11"/>
     </row>
-    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
         <v>44</v>
       </c>
@@ -7088,7 +7098,7 @@
       <c r="D451" s="5"/>
       <c r="E451" s="11"/>
     </row>
-    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
         <v>44</v>
       </c>
@@ -7101,7 +7111,7 @@
       <c r="D452" s="5"/>
       <c r="E452" s="11"/>
     </row>
-    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
         <v>44</v>
       </c>
@@ -7114,7 +7124,7 @@
       <c r="D453" s="5"/>
       <c r="E453" s="11"/>
     </row>
-    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
         <v>44</v>
       </c>
@@ -7127,7 +7137,7 @@
       <c r="D454" s="5"/>
       <c r="E454" s="11"/>
     </row>
-    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
         <v>44</v>
       </c>
@@ -7140,7 +7150,7 @@
       <c r="D455" s="5"/>
       <c r="E455" s="11"/>
     </row>
-    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
         <v>44</v>
       </c>
@@ -7153,7 +7163,7 @@
       <c r="D456" s="5"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
         <v>44</v>
       </c>
@@ -7166,7 +7176,7 @@
       <c r="D457" s="5"/>
       <c r="E457" s="11"/>
     </row>
-    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
         <v>44</v>
       </c>
@@ -7179,7 +7189,7 @@
       <c r="D458" s="5"/>
       <c r="E458" s="11"/>
     </row>
-    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
         <v>44</v>
       </c>
@@ -7192,7 +7202,7 @@
       <c r="D459" s="5"/>
       <c r="E459" s="11"/>
     </row>
-    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
         <v>44</v>
       </c>
@@ -7205,7 +7215,7 @@
       <c r="D460" s="5"/>
       <c r="E460" s="11"/>
     </row>
-    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
         <v>44</v>
       </c>
@@ -7218,7 +7228,7 @@
       <c r="D461" s="5"/>
       <c r="E461" s="11"/>
     </row>
-    <row r="462" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
         <v>44</v>
       </c>
@@ -7231,7 +7241,7 @@
       <c r="D462" s="5"/>
       <c r="E462" s="11"/>
     </row>
-    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
         <v>44</v>
       </c>
@@ -7244,7 +7254,7 @@
       <c r="D463" s="5"/>
       <c r="E463" s="11"/>
     </row>
-    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
         <v>44</v>
       </c>
@@ -7257,7 +7267,7 @@
       <c r="D464" s="5"/>
       <c r="E464" s="11"/>
     </row>
-    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
         <v>44</v>
       </c>
@@ -7270,7 +7280,7 @@
       <c r="D465" s="5"/>
       <c r="E465" s="11"/>
     </row>
-    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
         <v>44</v>
       </c>
@@ -7283,7 +7293,7 @@
       <c r="D466" s="5"/>
       <c r="E466" s="11"/>
     </row>
-    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
         <v>44</v>
       </c>
@@ -7296,7 +7306,7 @@
       <c r="D467" s="5"/>
       <c r="E467" s="11"/>
     </row>
-    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
         <v>44</v>
       </c>
@@ -7309,7 +7319,7 @@
       <c r="D468" s="5"/>
       <c r="E468" s="11"/>
     </row>
-    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
         <v>44</v>
       </c>
@@ -7322,7 +7332,7 @@
       <c r="D469" s="5"/>
       <c r="E469" s="11"/>
     </row>
-    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
         <v>44</v>
       </c>
@@ -7335,7 +7345,7 @@
       <c r="D470" s="5"/>
       <c r="E470" s="11"/>
     </row>
-    <row r="471" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
         <v>44</v>
       </c>
@@ -7348,7 +7358,7 @@
       <c r="D471" s="5"/>
       <c r="E471" s="11"/>
     </row>
-    <row r="472" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
         <v>44</v>
       </c>
@@ -7361,7 +7371,7 @@
       <c r="D472" s="5"/>
       <c r="E472" s="11"/>
     </row>
-    <row r="473" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
         <v>44</v>
       </c>
@@ -7374,7 +7384,7 @@
       <c r="D473" s="5"/>
       <c r="E473" s="11"/>
     </row>
-    <row r="474" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
         <v>44</v>
       </c>
@@ -7387,7 +7397,7 @@
       <c r="D474" s="5"/>
       <c r="E474" s="11"/>
     </row>
-    <row r="475" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
         <v>44</v>
       </c>
@@ -7400,7 +7410,7 @@
       <c r="D475" s="5"/>
       <c r="E475" s="11"/>
     </row>
-    <row r="476" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
         <v>44</v>
       </c>
@@ -7413,7 +7423,7 @@
       <c r="D476" s="5"/>
       <c r="E476" s="11"/>
     </row>
-    <row r="477" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
         <v>44</v>
       </c>
@@ -7426,7 +7436,7 @@
       <c r="D477" s="5"/>
       <c r="E477" s="11"/>
     </row>
-    <row r="478" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
         <v>44</v>
       </c>
@@ -7439,7 +7449,7 @@
       <c r="D478" s="5"/>
       <c r="E478" s="11"/>
     </row>
-    <row r="479" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
         <v>44</v>
       </c>
@@ -7452,7 +7462,7 @@
       <c r="D479" s="5"/>
       <c r="E479" s="11"/>
     </row>
-    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
         <v>44</v>
       </c>
@@ -7465,7 +7475,7 @@
       <c r="D480" s="5"/>
       <c r="E480" s="11"/>
     </row>
-    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
         <v>44</v>
       </c>
@@ -7478,7 +7488,7 @@
       <c r="D481" s="5"/>
       <c r="E481" s="11"/>
     </row>
-    <row r="482" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
         <v>44</v>
       </c>
@@ -7491,7 +7501,7 @@
       <c r="D482" s="5"/>
       <c r="E482" s="11"/>
     </row>
-    <row r="483" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
         <v>44</v>
       </c>
@@ -7504,7 +7514,7 @@
       <c r="D483" s="5"/>
       <c r="E483" s="11"/>
     </row>
-    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
         <v>44</v>
       </c>
@@ -7517,7 +7527,7 @@
       <c r="D484" s="5"/>
       <c r="E484" s="11"/>
     </row>
-    <row r="485" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
         <v>44</v>
       </c>
@@ -7530,7 +7540,7 @@
       <c r="D485" s="5"/>
       <c r="E485" s="11"/>
     </row>
-    <row r="486" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
         <v>44</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BDAC5D-FCD0-4D52-9F7C-6FE96A2976A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78AE2BB-54CD-417B-AFDC-D7B20991592C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,9 +492,6 @@
     <t>https://script.google.com/macros/s/AKfycbxZXRF67GyKW4OBj2Q-8c0khO_rq6g_paWKbWk6f_D_OWIlbXVJp1OncnnujQl7h4_6sw/exec</t>
   </si>
   <si>
-    <t>https://script.google.com/macros/s/AKfycbxDuRebeJmD96nC9Gyfq8g4b6SNqOHmQYN7DZ1eAP8as7mDdxTVNHpH0xVb54WQoWs/exec</t>
-  </si>
-  <si>
     <t>Конвексен и неконвексен многуаголник</t>
   </si>
   <si>
@@ -502,6 +499,9 @@
   </si>
   <si>
     <t>Осна симетрија, транслација, ротација</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbzn-nyMUi77uq9t_8cykblz_0spUWYdGg387LS2Dg7XjG0hkrhuo-WESn8sw8hYV0tu/exec</t>
   </si>
 </sst>
 </file>
@@ -703,7 +703,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="8"/>
+        <filter val="7"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -6107,7 +6107,7 @@
       <c r="D376" s="5"/>
       <c r="E376" s="11"/>
     </row>
-    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>44</v>
       </c>
@@ -6118,13 +6118,13 @@
         <v>1</v>
       </c>
       <c r="D377" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E377" s="11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>44</v>
       </c>
@@ -6137,7 +6137,7 @@
       <c r="D378" s="5"/>
       <c r="E378" s="11"/>
     </row>
-    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>44</v>
       </c>
@@ -6150,7 +6150,7 @@
       <c r="D379" s="5"/>
       <c r="E379" s="11"/>
     </row>
-    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>44</v>
       </c>
@@ -6163,7 +6163,7 @@
       <c r="D380" s="5"/>
       <c r="E380" s="11"/>
     </row>
-    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>44</v>
       </c>
@@ -6176,7 +6176,7 @@
       <c r="D381" s="5"/>
       <c r="E381" s="11"/>
     </row>
-    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>44</v>
       </c>
@@ -6189,7 +6189,7 @@
       <c r="D382" s="5"/>
       <c r="E382" s="11"/>
     </row>
-    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
         <v>44</v>
       </c>
@@ -6202,7 +6202,7 @@
       <c r="D383" s="5"/>
       <c r="E383" s="11"/>
     </row>
-    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
         <v>44</v>
       </c>
@@ -6215,7 +6215,7 @@
       <c r="D384" s="5"/>
       <c r="E384" s="11"/>
     </row>
-    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
         <v>44</v>
       </c>
@@ -6228,7 +6228,7 @@
       <c r="D385" s="5"/>
       <c r="E385" s="11"/>
     </row>
-    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
         <v>44</v>
       </c>
@@ -6241,7 +6241,7 @@
       <c r="D386" s="5"/>
       <c r="E386" s="11"/>
     </row>
-    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
         <v>44</v>
       </c>
@@ -6254,7 +6254,7 @@
       <c r="D387" s="5"/>
       <c r="E387" s="11"/>
     </row>
-    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
         <v>44</v>
       </c>
@@ -6267,7 +6267,7 @@
       <c r="D388" s="5"/>
       <c r="E388" s="11"/>
     </row>
-    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
         <v>44</v>
       </c>
@@ -6280,7 +6280,7 @@
       <c r="D389" s="5"/>
       <c r="E389" s="11"/>
     </row>
-    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
         <v>44</v>
       </c>
@@ -6293,7 +6293,7 @@
       <c r="D390" s="5"/>
       <c r="E390" s="11"/>
     </row>
-    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
         <v>44</v>
       </c>
@@ -6306,7 +6306,7 @@
       <c r="D391" s="5"/>
       <c r="E391" s="11"/>
     </row>
-    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
         <v>44</v>
       </c>
@@ -6319,7 +6319,7 @@
       <c r="D392" s="5"/>
       <c r="E392" s="11"/>
     </row>
-    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
         <v>44</v>
       </c>
@@ -6332,7 +6332,7 @@
       <c r="D393" s="5"/>
       <c r="E393" s="11"/>
     </row>
-    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
         <v>44</v>
       </c>
@@ -6345,7 +6345,7 @@
       <c r="D394" s="5"/>
       <c r="E394" s="11"/>
     </row>
-    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
         <v>44</v>
       </c>
@@ -6358,7 +6358,7 @@
       <c r="D395" s="5"/>
       <c r="E395" s="11"/>
     </row>
-    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
         <v>44</v>
       </c>
@@ -6371,7 +6371,7 @@
       <c r="D396" s="5"/>
       <c r="E396" s="11"/>
     </row>
-    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>44</v>
       </c>
@@ -6384,7 +6384,7 @@
       <c r="D397" s="5"/>
       <c r="E397" s="11"/>
     </row>
-    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>44</v>
       </c>
@@ -6397,7 +6397,7 @@
       <c r="D398" s="5"/>
       <c r="E398" s="11"/>
     </row>
-    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
         <v>44</v>
       </c>
@@ -6410,7 +6410,7 @@
       <c r="D399" s="5"/>
       <c r="E399" s="11"/>
     </row>
-    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
         <v>44</v>
       </c>
@@ -6423,7 +6423,7 @@
       <c r="D400" s="5"/>
       <c r="E400" s="11"/>
     </row>
-    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>44</v>
       </c>
@@ -6436,7 +6436,7 @@
       <c r="D401" s="5"/>
       <c r="E401" s="11"/>
     </row>
-    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>44</v>
       </c>
@@ -6449,7 +6449,7 @@
       <c r="D402" s="5"/>
       <c r="E402" s="11"/>
     </row>
-    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>44</v>
       </c>
@@ -6462,7 +6462,7 @@
       <c r="D403" s="5"/>
       <c r="E403" s="11"/>
     </row>
-    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>44</v>
       </c>
@@ -6475,7 +6475,7 @@
       <c r="D404" s="5"/>
       <c r="E404" s="11"/>
     </row>
-    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
         <v>44</v>
       </c>
@@ -6488,7 +6488,7 @@
       <c r="D405" s="5"/>
       <c r="E405" s="11"/>
     </row>
-    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>44</v>
       </c>
@@ -6501,7 +6501,7 @@
       <c r="D406" s="5"/>
       <c r="E406" s="11"/>
     </row>
-    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>44</v>
       </c>
@@ -6514,7 +6514,7 @@
       <c r="D407" s="5"/>
       <c r="E407" s="11"/>
     </row>
-    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>44</v>
       </c>
@@ -6527,7 +6527,7 @@
       <c r="D408" s="5"/>
       <c r="E408" s="11"/>
     </row>
-    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>44</v>
       </c>
@@ -6540,7 +6540,7 @@
       <c r="D409" s="5"/>
       <c r="E409" s="11"/>
     </row>
-    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>44</v>
       </c>
@@ -6553,7 +6553,7 @@
       <c r="D410" s="5"/>
       <c r="E410" s="11"/>
     </row>
-    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>44</v>
       </c>
@@ -6566,7 +6566,7 @@
       <c r="D411" s="5"/>
       <c r="E411" s="11"/>
     </row>
-    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>44</v>
       </c>
@@ -6579,7 +6579,7 @@
       <c r="D412" s="5"/>
       <c r="E412" s="11"/>
     </row>
-    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
         <v>44</v>
       </c>
@@ -6592,7 +6592,7 @@
       <c r="D413" s="5"/>
       <c r="E413" s="11"/>
     </row>
-    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
         <v>44</v>
       </c>
@@ -6605,7 +6605,7 @@
       <c r="D414" s="5"/>
       <c r="E414" s="11"/>
     </row>
-    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
         <v>44</v>
       </c>
@@ -6618,7 +6618,7 @@
       <c r="D415" s="5"/>
       <c r="E415" s="11"/>
     </row>
-    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
         <v>44</v>
       </c>
@@ -6631,7 +6631,7 @@
       <c r="D416" s="5"/>
       <c r="E416" s="11"/>
     </row>
-    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
         <v>44</v>
       </c>
@@ -6644,7 +6644,7 @@
       <c r="D417" s="5"/>
       <c r="E417" s="11"/>
     </row>
-    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
         <v>44</v>
       </c>
@@ -6657,7 +6657,7 @@
       <c r="D418" s="5"/>
       <c r="E418" s="11"/>
     </row>
-    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
         <v>44</v>
       </c>
@@ -6670,7 +6670,7 @@
       <c r="D419" s="5"/>
       <c r="E419" s="11"/>
     </row>
-    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
         <v>44</v>
       </c>
@@ -6683,7 +6683,7 @@
       <c r="D420" s="5"/>
       <c r="E420" s="11"/>
     </row>
-    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
         <v>44</v>
       </c>
@@ -6696,7 +6696,7 @@
       <c r="D421" s="5"/>
       <c r="E421" s="11"/>
     </row>
-    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
         <v>44</v>
       </c>
@@ -6709,7 +6709,7 @@
       <c r="D422" s="5"/>
       <c r="E422" s="11"/>
     </row>
-    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
         <v>44</v>
       </c>
@@ -6722,7 +6722,7 @@
       <c r="D423" s="5"/>
       <c r="E423" s="11"/>
     </row>
-    <row r="424" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
         <v>44</v>
       </c>
@@ -6735,7 +6735,7 @@
       <c r="D424" s="5"/>
       <c r="E424" s="11"/>
     </row>
-    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
         <v>44</v>
       </c>
@@ -6748,7 +6748,7 @@
       <c r="D425" s="5"/>
       <c r="E425" s="11"/>
     </row>
-    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
         <v>44</v>
       </c>
@@ -6761,7 +6761,7 @@
       <c r="D426" s="5"/>
       <c r="E426" s="11"/>
     </row>
-    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
         <v>44</v>
       </c>
@@ -6774,7 +6774,7 @@
       <c r="D427" s="5"/>
       <c r="E427" s="11"/>
     </row>
-    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
         <v>44</v>
       </c>
@@ -6787,7 +6787,7 @@
       <c r="D428" s="5"/>
       <c r="E428" s="11"/>
     </row>
-    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
         <v>44</v>
       </c>
@@ -6800,7 +6800,7 @@
       <c r="D429" s="5"/>
       <c r="E429" s="11"/>
     </row>
-    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
         <v>44</v>
       </c>
@@ -6813,7 +6813,7 @@
       <c r="D430" s="5"/>
       <c r="E430" s="11"/>
     </row>
-    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
         <v>44</v>
       </c>
@@ -6826,7 +6826,7 @@
       <c r="D431" s="5"/>
       <c r="E431" s="11"/>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
         <v>44</v>
       </c>
@@ -6843,7 +6843,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
         <v>44</v>
       </c>
@@ -6856,7 +6856,7 @@
       <c r="D433" s="5"/>
       <c r="E433" s="11"/>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
         <v>44</v>
       </c>
@@ -6873,7 +6873,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
         <v>44</v>
       </c>
@@ -6884,13 +6884,13 @@
         <v>4</v>
       </c>
       <c r="D435" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E435" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
         <v>44</v>
       </c>
@@ -6903,7 +6903,7 @@
       <c r="D436" s="5"/>
       <c r="E436" s="11"/>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
         <v>44</v>
       </c>
@@ -6916,7 +6916,7 @@
       <c r="D437" s="5"/>
       <c r="E437" s="11"/>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
         <v>44</v>
       </c>
@@ -6929,7 +6929,7 @@
       <c r="D438" s="5"/>
       <c r="E438" s="11"/>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
         <v>44</v>
       </c>
@@ -6942,7 +6942,7 @@
       <c r="D439" s="5"/>
       <c r="E439" s="11"/>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
         <v>44</v>
       </c>
@@ -6955,7 +6955,7 @@
       <c r="D440" s="5"/>
       <c r="E440" s="11"/>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
         <v>44</v>
       </c>
@@ -6968,7 +6968,7 @@
       <c r="D441" s="5"/>
       <c r="E441" s="11"/>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
         <v>44</v>
       </c>
@@ -6981,7 +6981,7 @@
       <c r="D442" s="5"/>
       <c r="E442" s="11"/>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
         <v>44</v>
       </c>
@@ -6994,7 +6994,7 @@
       <c r="D443" s="5"/>
       <c r="E443" s="11"/>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
         <v>44</v>
       </c>
@@ -7007,7 +7007,7 @@
       <c r="D444" s="5"/>
       <c r="E444" s="11"/>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
         <v>44</v>
       </c>
@@ -7020,7 +7020,7 @@
       <c r="D445" s="5"/>
       <c r="E445" s="11"/>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
         <v>44</v>
       </c>
@@ -7033,7 +7033,7 @@
       <c r="D446" s="5"/>
       <c r="E446" s="11"/>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
         <v>44</v>
       </c>
@@ -7046,7 +7046,7 @@
       <c r="D447" s="5"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
         <v>44</v>
       </c>
@@ -7059,7 +7059,7 @@
       <c r="D448" s="5"/>
       <c r="E448" s="11"/>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
         <v>44</v>
       </c>
@@ -7072,7 +7072,7 @@
       <c r="D449" s="5"/>
       <c r="E449" s="11"/>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
         <v>44</v>
       </c>
@@ -7085,7 +7085,7 @@
       <c r="D450" s="5"/>
       <c r="E450" s="11"/>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
         <v>44</v>
       </c>
@@ -7098,7 +7098,7 @@
       <c r="D451" s="5"/>
       <c r="E451" s="11"/>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
         <v>44</v>
       </c>
@@ -7111,7 +7111,7 @@
       <c r="D452" s="5"/>
       <c r="E452" s="11"/>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
         <v>44</v>
       </c>
@@ -7124,7 +7124,7 @@
       <c r="D453" s="5"/>
       <c r="E453" s="11"/>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
         <v>44</v>
       </c>
@@ -7137,7 +7137,7 @@
       <c r="D454" s="5"/>
       <c r="E454" s="11"/>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
         <v>44</v>
       </c>
@@ -7150,7 +7150,7 @@
       <c r="D455" s="5"/>
       <c r="E455" s="11"/>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
         <v>44</v>
       </c>
@@ -7163,7 +7163,7 @@
       <c r="D456" s="5"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
         <v>44</v>
       </c>
@@ -7176,7 +7176,7 @@
       <c r="D457" s="5"/>
       <c r="E457" s="11"/>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
         <v>44</v>
       </c>
@@ -7189,7 +7189,7 @@
       <c r="D458" s="5"/>
       <c r="E458" s="11"/>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
         <v>44</v>
       </c>
@@ -7202,7 +7202,7 @@
       <c r="D459" s="5"/>
       <c r="E459" s="11"/>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
         <v>44</v>
       </c>
@@ -7215,7 +7215,7 @@
       <c r="D460" s="5"/>
       <c r="E460" s="11"/>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
         <v>44</v>
       </c>
@@ -7228,7 +7228,7 @@
       <c r="D461" s="5"/>
       <c r="E461" s="11"/>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
         <v>44</v>
       </c>
@@ -7241,7 +7241,7 @@
       <c r="D462" s="5"/>
       <c r="E462" s="11"/>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
         <v>44</v>
       </c>
@@ -7254,7 +7254,7 @@
       <c r="D463" s="5"/>
       <c r="E463" s="11"/>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
         <v>44</v>
       </c>
@@ -7267,7 +7267,7 @@
       <c r="D464" s="5"/>
       <c r="E464" s="11"/>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
         <v>44</v>
       </c>
@@ -7280,7 +7280,7 @@
       <c r="D465" s="5"/>
       <c r="E465" s="11"/>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
         <v>44</v>
       </c>
@@ -7293,7 +7293,7 @@
       <c r="D466" s="5"/>
       <c r="E466" s="11"/>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
         <v>44</v>
       </c>
@@ -7306,7 +7306,7 @@
       <c r="D467" s="5"/>
       <c r="E467" s="11"/>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
         <v>44</v>
       </c>
@@ -7319,7 +7319,7 @@
       <c r="D468" s="5"/>
       <c r="E468" s="11"/>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
         <v>44</v>
       </c>
@@ -7332,7 +7332,7 @@
       <c r="D469" s="5"/>
       <c r="E469" s="11"/>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
         <v>44</v>
       </c>
@@ -7345,7 +7345,7 @@
       <c r="D470" s="5"/>
       <c r="E470" s="11"/>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
         <v>44</v>
       </c>
@@ -7358,7 +7358,7 @@
       <c r="D471" s="5"/>
       <c r="E471" s="11"/>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
         <v>44</v>
       </c>
@@ -7371,7 +7371,7 @@
       <c r="D472" s="5"/>
       <c r="E472" s="11"/>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
         <v>44</v>
       </c>
@@ -7384,7 +7384,7 @@
       <c r="D473" s="5"/>
       <c r="E473" s="11"/>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
         <v>44</v>
       </c>
@@ -7397,7 +7397,7 @@
       <c r="D474" s="5"/>
       <c r="E474" s="11"/>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
         <v>44</v>
       </c>
@@ -7410,7 +7410,7 @@
       <c r="D475" s="5"/>
       <c r="E475" s="11"/>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
         <v>44</v>
       </c>
@@ -7423,7 +7423,7 @@
       <c r="D476" s="5"/>
       <c r="E476" s="11"/>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
         <v>44</v>
       </c>
@@ -7436,7 +7436,7 @@
       <c r="D477" s="5"/>
       <c r="E477" s="11"/>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
         <v>44</v>
       </c>
@@ -7449,7 +7449,7 @@
       <c r="D478" s="5"/>
       <c r="E478" s="11"/>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
         <v>44</v>
       </c>
@@ -7462,7 +7462,7 @@
       <c r="D479" s="5"/>
       <c r="E479" s="11"/>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
         <v>44</v>
       </c>
@@ -7475,7 +7475,7 @@
       <c r="D480" s="5"/>
       <c r="E480" s="11"/>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
         <v>44</v>
       </c>
@@ -7488,7 +7488,7 @@
       <c r="D481" s="5"/>
       <c r="E481" s="11"/>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
         <v>44</v>
       </c>
@@ -7501,7 +7501,7 @@
       <c r="D482" s="5"/>
       <c r="E482" s="11"/>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
         <v>44</v>
       </c>
@@ -7514,7 +7514,7 @@
       <c r="D483" s="5"/>
       <c r="E483" s="11"/>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
         <v>44</v>
       </c>
@@ -7527,7 +7527,7 @@
       <c r="D484" s="5"/>
       <c r="E484" s="11"/>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
         <v>44</v>
       </c>
@@ -7540,7 +7540,7 @@
       <c r="D485" s="5"/>
       <c r="E485" s="11"/>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
         <v>44</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78AE2BB-54CD-417B-AFDC-D7B20991592C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15D84BE-AE4C-45D7-B6EB-992D30315FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="135">
   <si>
     <t>Категорија</t>
   </si>
@@ -501,7 +501,10 @@
     <t>Осна симетрија, транслација, ротација</t>
   </si>
   <si>
-    <t>https://script.google.com/macros/s/AKfycbzn-nyMUi77uq9t_8cykblz_0spUWYdGg387LS2Dg7XjG0hkrhuo-WESn8sw8hYV0tu/exec</t>
+    <t>https://script.google.com/macros/s/AKfycbypFIqhKT_acZtC9nNciWB-Vac7H_fCiufs4v2oxXHUy2zBQyWJ4gEq6IwhktU72Ntn/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbxwXDI3ULjpba7JhDrfw_VDqReJFXYlXLxME7w16XQjOVESuMEpChsDcw0SA4M6Ms-2/exec</t>
   </si>
 </sst>
 </file>
@@ -6121,7 +6124,7 @@
         <v>130</v>
       </c>
       <c r="E377" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.3">
@@ -10771,6 +10774,9 @@
       </c>
       <c r="D733" s="12" t="s">
         <v>126</v>
+      </c>
+      <c r="E733" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15D84BE-AE4C-45D7-B6EB-992D30315FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD27420-E4BD-4842-B931-4B3AA9B21682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="137">
   <si>
     <t>Категорија</t>
   </si>
@@ -505,6 +505,12 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbxwXDI3ULjpba7JhDrfw_VDqReJFXYlXLxME7w16XQjOVESuMEpChsDcw0SA4M6Ms-2/exec</t>
+  </si>
+  <si>
+    <t>Множење децимални броеви со една децимала - вежби2</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycby6jZE_5BhVqFEn4Psk8zfgm4ir44KQEJdUJ61qit1hYUOr8v_SwDiPGUnE-EaM7yxu/exec</t>
   </si>
 </sst>
 </file>
@@ -639,7 +645,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -675,6 +681,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -697,16 +704,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E733">
-  <autoFilter ref="A1:E733" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E734">
+  <autoFilter ref="A1:E734" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Геометрија"/>
+        <filter val="Алгебра"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="7"/>
+        <filter val="6"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1009,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E733"/>
+  <dimension ref="A1:E734"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1018,7 +1025,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1035,7 +1042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>43</v>
       </c>
@@ -1052,7 +1059,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>43</v>
       </c>
@@ -1067,7 +1074,7 @@
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
@@ -1082,7 +1089,7 @@
       </c>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>43</v>
       </c>
@@ -1097,7 +1104,7 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>43</v>
       </c>
@@ -1112,7 +1119,7 @@
       </c>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>43</v>
       </c>
@@ -1127,7 +1134,7 @@
       </c>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>43</v>
       </c>
@@ -1142,7 +1149,7 @@
       </c>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>43</v>
       </c>
@@ -1157,7 +1164,7 @@
       </c>
       <c r="E9" s="11"/>
     </row>
-    <row r="10" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>43</v>
       </c>
@@ -1172,7 +1179,7 @@
       </c>
       <c r="E10" s="11"/>
     </row>
-    <row r="11" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>43</v>
       </c>
@@ -1187,7 +1194,7 @@
       </c>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>43</v>
       </c>
@@ -1202,7 +1209,7 @@
       </c>
       <c r="E12" s="11"/>
     </row>
-    <row r="13" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>43</v>
       </c>
@@ -1217,7 +1224,7 @@
       </c>
       <c r="E13" s="11"/>
     </row>
-    <row r="14" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
@@ -1232,7 +1239,7 @@
       </c>
       <c r="E14" s="11"/>
     </row>
-    <row r="15" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>43</v>
       </c>
@@ -1247,7 +1254,7 @@
       </c>
       <c r="E15" s="11"/>
     </row>
-    <row r="16" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>43</v>
       </c>
@@ -1262,7 +1269,7 @@
       </c>
       <c r="E16" s="11"/>
     </row>
-    <row r="17" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>43</v>
       </c>
@@ -1277,7 +1284,7 @@
       </c>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>43</v>
       </c>
@@ -1292,7 +1299,7 @@
       </c>
       <c r="E18" s="11"/>
     </row>
-    <row r="19" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>43</v>
       </c>
@@ -1307,7 +1314,7 @@
       </c>
       <c r="E19" s="11"/>
     </row>
-    <row r="20" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
@@ -1322,7 +1329,7 @@
       </c>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>43</v>
       </c>
@@ -1337,7 +1344,7 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>43</v>
       </c>
@@ -1352,7 +1359,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>43</v>
       </c>
@@ -1367,7 +1374,7 @@
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>43</v>
       </c>
@@ -1382,7 +1389,7 @@
       </c>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>43</v>
       </c>
@@ -1397,7 +1404,7 @@
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>43</v>
       </c>
@@ -1412,7 +1419,7 @@
       </c>
       <c r="E26" s="11"/>
     </row>
-    <row r="27" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>43</v>
       </c>
@@ -1427,7 +1434,7 @@
       </c>
       <c r="E27" s="11"/>
     </row>
-    <row r="28" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>43</v>
       </c>
@@ -1442,7 +1449,7 @@
       </c>
       <c r="E28" s="11"/>
     </row>
-    <row r="29" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>43</v>
       </c>
@@ -1457,7 +1464,7 @@
       </c>
       <c r="E29" s="11"/>
     </row>
-    <row r="30" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>43</v>
       </c>
@@ -1472,7 +1479,7 @@
       </c>
       <c r="E30" s="11"/>
     </row>
-    <row r="31" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>43</v>
       </c>
@@ -1487,7 +1494,7 @@
       </c>
       <c r="E31" s="11"/>
     </row>
-    <row r="32" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>43</v>
       </c>
@@ -1502,7 +1509,7 @@
       </c>
       <c r="E32" s="11"/>
     </row>
-    <row r="33" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>43</v>
       </c>
@@ -1517,7 +1524,7 @@
       </c>
       <c r="E33" s="11"/>
     </row>
-    <row r="34" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>43</v>
       </c>
@@ -1532,7 +1539,7 @@
       </c>
       <c r="E34" s="11"/>
     </row>
-    <row r="35" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>43</v>
       </c>
@@ -1547,7 +1554,7 @@
       </c>
       <c r="E35" s="11"/>
     </row>
-    <row r="36" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>43</v>
       </c>
@@ -1562,7 +1569,7 @@
       </c>
       <c r="E36" s="11"/>
     </row>
-    <row r="37" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>43</v>
       </c>
@@ -1577,7 +1584,7 @@
       </c>
       <c r="E37" s="11"/>
     </row>
-    <row r="38" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>43</v>
       </c>
@@ -1592,7 +1599,7 @@
       </c>
       <c r="E38" s="11"/>
     </row>
-    <row r="39" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>43</v>
       </c>
@@ -1607,7 +1614,7 @@
       </c>
       <c r="E39" s="11"/>
     </row>
-    <row r="40" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>43</v>
       </c>
@@ -1622,7 +1629,7 @@
       </c>
       <c r="E40" s="11"/>
     </row>
-    <row r="41" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>43</v>
       </c>
@@ -1697,7 +1704,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1710,7 +1717,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1723,7 +1730,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1736,7 +1743,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1749,7 +1756,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -1762,7 +1769,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1775,7 +1782,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1788,7 +1795,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1801,7 +1808,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -1814,7 +1821,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="11"/>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1827,7 +1834,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="11"/>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -1840,7 +1847,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -1853,7 +1860,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -1866,7 +1873,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -1879,7 +1886,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -1892,7 +1899,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -1905,7 +1912,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -1918,7 +1925,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -1931,7 +1938,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -1944,7 +1951,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -1957,7 +1964,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -1970,7 +1977,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -1983,7 +1990,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -1996,7 +2003,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -2009,7 +2016,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2022,7 +2029,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2035,7 +2042,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2048,7 +2055,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2061,7 +2068,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2074,7 +2081,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2087,7 +2094,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2100,7 +2107,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2113,7 +2120,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2126,7 +2133,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2139,7 +2146,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2152,7 +2159,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2165,7 +2172,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2178,7 +2185,7 @@
       <c r="D82" s="5"/>
       <c r="E82" s="11"/>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2191,7 +2198,7 @@
       <c r="D83" s="5"/>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2204,7 +2211,7 @@
       <c r="D84" s="5"/>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2217,7 +2224,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2230,7 +2237,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="11"/>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2243,7 +2250,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="11"/>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2256,7 +2263,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="11"/>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2269,7 +2276,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="11"/>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2282,7 +2289,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="11"/>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2295,7 +2302,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2308,7 +2315,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2321,7 +2328,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2334,7 +2341,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2347,7 +2354,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2360,7 +2367,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2373,7 +2380,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2386,7 +2393,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2399,7 +2406,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2412,7 +2419,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2425,7 +2432,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2438,7 +2445,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2451,7 +2458,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2464,7 +2471,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2477,7 +2484,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2490,7 +2497,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2503,7 +2510,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2516,7 +2523,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2529,7 +2536,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2542,7 +2549,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2555,7 +2562,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2568,7 +2575,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2581,7 +2588,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2594,7 +2601,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2607,7 +2614,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2620,7 +2627,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2633,7 +2640,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2646,7 +2653,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2659,7 +2666,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2672,7 +2679,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>
@@ -2685,7 +2692,7 @@
       <c r="D121" s="5"/>
       <c r="E121" s="11"/>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>5</v>
       </c>
@@ -2698,7 +2705,7 @@
       <c r="D122" s="5"/>
       <c r="E122" s="11"/>
     </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>5</v>
       </c>
@@ -2711,7 +2718,7 @@
       <c r="D123" s="5"/>
       <c r="E123" s="11"/>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>5</v>
       </c>
@@ -2724,7 +2731,7 @@
       <c r="D124" s="5"/>
       <c r="E124" s="11"/>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>5</v>
       </c>
@@ -2737,7 +2744,7 @@
       <c r="D125" s="5"/>
       <c r="E125" s="11"/>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
         <v>5</v>
       </c>
@@ -2750,7 +2757,7 @@
       <c r="D126" s="5"/>
       <c r="E126" s="11"/>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>5</v>
       </c>
@@ -2763,7 +2770,7 @@
       <c r="D127" s="5"/>
       <c r="E127" s="11"/>
     </row>
-    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
         <v>5</v>
       </c>
@@ -2776,7 +2783,7 @@
       <c r="D128" s="5"/>
       <c r="E128" s="11"/>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
         <v>5</v>
       </c>
@@ -2789,7 +2796,7 @@
       <c r="D129" s="5"/>
       <c r="E129" s="11"/>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
         <v>5</v>
       </c>
@@ -2802,7 +2809,7 @@
       <c r="D130" s="5"/>
       <c r="E130" s="11"/>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
         <v>5</v>
       </c>
@@ -2815,7 +2822,7 @@
       <c r="D131" s="5"/>
       <c r="E131" s="11"/>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
         <v>5</v>
       </c>
@@ -2828,7 +2835,7 @@
       <c r="D132" s="5"/>
       <c r="E132" s="11"/>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
         <v>5</v>
       </c>
@@ -2841,7 +2848,7 @@
       <c r="D133" s="5"/>
       <c r="E133" s="11"/>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
         <v>5</v>
       </c>
@@ -2854,7 +2861,7 @@
       <c r="D134" s="5"/>
       <c r="E134" s="11"/>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>5</v>
       </c>
@@ -2867,7 +2874,7 @@
       <c r="D135" s="5"/>
       <c r="E135" s="11"/>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>5</v>
       </c>
@@ -2880,7 +2887,7 @@
       <c r="D136" s="5"/>
       <c r="E136" s="11"/>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>5</v>
       </c>
@@ -2893,7 +2900,7 @@
       <c r="D137" s="5"/>
       <c r="E137" s="11"/>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>5</v>
       </c>
@@ -2906,7 +2913,7 @@
       <c r="D138" s="5"/>
       <c r="E138" s="11"/>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>5</v>
       </c>
@@ -2919,7 +2926,7 @@
       <c r="D139" s="5"/>
       <c r="E139" s="11"/>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>5</v>
       </c>
@@ -2932,7 +2939,7 @@
       <c r="D140" s="5"/>
       <c r="E140" s="11"/>
     </row>
-    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>5</v>
       </c>
@@ -2945,7 +2952,7 @@
       <c r="D141" s="5"/>
       <c r="E141" s="11"/>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>5</v>
       </c>
@@ -2958,7 +2965,7 @@
       <c r="D142" s="5"/>
       <c r="E142" s="11"/>
     </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>5</v>
       </c>
@@ -2971,7 +2978,7 @@
       <c r="D143" s="5"/>
       <c r="E143" s="11"/>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>5</v>
       </c>
@@ -2984,7 +2991,7 @@
       <c r="D144" s="5"/>
       <c r="E144" s="11"/>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>5</v>
       </c>
@@ -2997,7 +3004,7 @@
       <c r="D145" s="5"/>
       <c r="E145" s="11"/>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>5</v>
       </c>
@@ -3010,7 +3017,7 @@
       <c r="D146" s="5"/>
       <c r="E146" s="11"/>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>5</v>
       </c>
@@ -3023,7 +3030,7 @@
       <c r="D147" s="5"/>
       <c r="E147" s="11"/>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>5</v>
       </c>
@@ -3036,7 +3043,7 @@
       <c r="D148" s="5"/>
       <c r="E148" s="11"/>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>5</v>
       </c>
@@ -3049,7 +3056,7 @@
       <c r="D149" s="5"/>
       <c r="E149" s="11"/>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>5</v>
       </c>
@@ -3062,7 +3069,7 @@
       <c r="D150" s="5"/>
       <c r="E150" s="11"/>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>5</v>
       </c>
@@ -3075,7 +3082,7 @@
       <c r="D151" s="5"/>
       <c r="E151" s="11"/>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>5</v>
       </c>
@@ -3088,7 +3095,7 @@
       <c r="D152" s="5"/>
       <c r="E152" s="11"/>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>5</v>
       </c>
@@ -3101,7 +3108,7 @@
       <c r="D153" s="5"/>
       <c r="E153" s="11"/>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>5</v>
       </c>
@@ -3114,7 +3121,7 @@
       <c r="D154" s="5"/>
       <c r="E154" s="11"/>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>5</v>
       </c>
@@ -3127,7 +3134,7 @@
       <c r="D155" s="5"/>
       <c r="E155" s="11"/>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>5</v>
       </c>
@@ -3140,7 +3147,7 @@
       <c r="D156" s="5"/>
       <c r="E156" s="11"/>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>5</v>
       </c>
@@ -3153,7 +3160,7 @@
       <c r="D157" s="5"/>
       <c r="E157" s="11"/>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>5</v>
       </c>
@@ -3166,7 +3173,7 @@
       <c r="D158" s="5"/>
       <c r="E158" s="11"/>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>5</v>
       </c>
@@ -3179,7 +3186,7 @@
       <c r="D159" s="5"/>
       <c r="E159" s="11"/>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>5</v>
       </c>
@@ -3192,7 +3199,7 @@
       <c r="D160" s="5"/>
       <c r="E160" s="11"/>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>5</v>
       </c>
@@ -3205,7 +3212,7 @@
       <c r="D161" s="5"/>
       <c r="E161" s="11"/>
     </row>
-    <row r="162" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>43</v>
       </c>
@@ -3220,7 +3227,7 @@
       </c>
       <c r="E162" s="11"/>
     </row>
-    <row r="163" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>43</v>
       </c>
@@ -3235,7 +3242,7 @@
       </c>
       <c r="E163" s="11"/>
     </row>
-    <row r="164" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>43</v>
       </c>
@@ -3250,7 +3257,7 @@
       </c>
       <c r="E164" s="11"/>
     </row>
-    <row r="165" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>43</v>
       </c>
@@ -3267,7 +3274,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>5</v>
       </c>
@@ -3284,7 +3291,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>5</v>
       </c>
@@ -3301,7 +3308,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>5</v>
       </c>
@@ -3316,7 +3323,7 @@
       </c>
       <c r="E168" s="10"/>
     </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>5</v>
       </c>
@@ -3331,7 +3338,7 @@
       </c>
       <c r="E169" s="10"/>
     </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>5</v>
       </c>
@@ -3346,7 +3353,7 @@
       </c>
       <c r="E170" s="10"/>
     </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>5</v>
       </c>
@@ -3361,7 +3368,7 @@
       </c>
       <c r="E171" s="10"/>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>5</v>
       </c>
@@ -3376,7 +3383,7 @@
       </c>
       <c r="E172" s="10"/>
     </row>
-    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>5</v>
       </c>
@@ -3391,7 +3398,7 @@
       </c>
       <c r="E173" s="10"/>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>5</v>
       </c>
@@ -3406,7 +3413,7 @@
       </c>
       <c r="E174" s="10"/>
     </row>
-    <row r="175" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" ht="29.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>5</v>
       </c>
@@ -3421,7 +3428,7 @@
       </c>
       <c r="E175" s="10"/>
     </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>5</v>
       </c>
@@ -3436,7 +3443,7 @@
       </c>
       <c r="E176" s="10"/>
     </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>5</v>
       </c>
@@ -3451,7 +3458,7 @@
       </c>
       <c r="E177" s="10"/>
     </row>
-    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>5</v>
       </c>
@@ -3466,7 +3473,7 @@
       </c>
       <c r="E178" s="10"/>
     </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>5</v>
       </c>
@@ -3481,7 +3488,7 @@
       </c>
       <c r="E179" s="10"/>
     </row>
-    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>5</v>
       </c>
@@ -3496,7 +3503,7 @@
       </c>
       <c r="E180" s="10"/>
     </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>5</v>
       </c>
@@ -3511,7 +3518,7 @@
       </c>
       <c r="E181" s="10"/>
     </row>
-    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>5</v>
       </c>
@@ -3526,7 +3533,7 @@
       </c>
       <c r="E182" s="10"/>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>5</v>
       </c>
@@ -3541,7 +3548,7 @@
       </c>
       <c r="E183" s="10"/>
     </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>5</v>
       </c>
@@ -3556,7 +3563,7 @@
       </c>
       <c r="E184" s="10"/>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>5</v>
       </c>
@@ -3571,7 +3578,7 @@
       </c>
       <c r="E185" s="10"/>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>5</v>
       </c>
@@ -3586,7 +3593,7 @@
       </c>
       <c r="E186" s="10"/>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>5</v>
       </c>
@@ -3601,7 +3608,7 @@
       </c>
       <c r="E187" s="10"/>
     </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>5</v>
       </c>
@@ -3616,7 +3623,7 @@
       </c>
       <c r="E188" s="10"/>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>5</v>
       </c>
@@ -3631,7 +3638,7 @@
       </c>
       <c r="E189" s="10"/>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>5</v>
       </c>
@@ -3646,7 +3653,7 @@
       </c>
       <c r="E190" s="10"/>
     </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>5</v>
       </c>
@@ -3661,7 +3668,7 @@
       </c>
       <c r="E191" s="10"/>
     </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>5</v>
       </c>
@@ -3676,7 +3683,7 @@
       </c>
       <c r="E192" s="10"/>
     </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>5</v>
       </c>
@@ -3691,7 +3698,7 @@
       </c>
       <c r="E193" s="10"/>
     </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>5</v>
       </c>
@@ -3706,7 +3713,7 @@
       </c>
       <c r="E194" s="10"/>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>5</v>
       </c>
@@ -3721,7 +3728,7 @@
       </c>
       <c r="E195" s="10"/>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>5</v>
       </c>
@@ -3736,7 +3743,7 @@
       </c>
       <c r="E196" s="10"/>
     </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>5</v>
       </c>
@@ -3751,7 +3758,7 @@
       </c>
       <c r="E197" s="10"/>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>5</v>
       </c>
@@ -3766,7 +3773,7 @@
       </c>
       <c r="E198" s="10"/>
     </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>5</v>
       </c>
@@ -3781,7 +3788,7 @@
       </c>
       <c r="E199" s="10"/>
     </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>5</v>
       </c>
@@ -3796,7 +3803,7 @@
       </c>
       <c r="E200" s="10"/>
     </row>
-    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>5</v>
       </c>
@@ -3811,7 +3818,7 @@
       </c>
       <c r="E201" s="10"/>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
         <v>43</v>
       </c>
@@ -3824,7 +3831,7 @@
       <c r="D202" s="5"/>
       <c r="E202" s="11"/>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
         <v>43</v>
       </c>
@@ -3837,7 +3844,7 @@
       <c r="D203" s="5"/>
       <c r="E203" s="11"/>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
         <v>43</v>
       </c>
@@ -3850,7 +3857,7 @@
       <c r="D204" s="5"/>
       <c r="E204" s="11"/>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
         <v>43</v>
       </c>
@@ -3863,7 +3870,7 @@
       <c r="D205" s="5"/>
       <c r="E205" s="11"/>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
         <v>43</v>
       </c>
@@ -3876,7 +3883,7 @@
       <c r="D206" s="5"/>
       <c r="E206" s="11"/>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>43</v>
       </c>
@@ -3889,7 +3896,7 @@
       <c r="D207" s="5"/>
       <c r="E207" s="11"/>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
         <v>43</v>
       </c>
@@ -3902,7 +3909,7 @@
       <c r="D208" s="5"/>
       <c r="E208" s="11"/>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
         <v>43</v>
       </c>
@@ -3915,7 +3922,7 @@
       <c r="D209" s="5"/>
       <c r="E209" s="11"/>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
         <v>43</v>
       </c>
@@ -3928,7 +3935,7 @@
       <c r="D210" s="5"/>
       <c r="E210" s="11"/>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
         <v>43</v>
       </c>
@@ -3941,7 +3948,7 @@
       <c r="D211" s="5"/>
       <c r="E211" s="11"/>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
         <v>43</v>
       </c>
@@ -3954,7 +3961,7 @@
       <c r="D212" s="5"/>
       <c r="E212" s="11"/>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
         <v>43</v>
       </c>
@@ -3967,7 +3974,7 @@
       <c r="D213" s="5"/>
       <c r="E213" s="11"/>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
         <v>43</v>
       </c>
@@ -3980,7 +3987,7 @@
       <c r="D214" s="5"/>
       <c r="E214" s="11"/>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
         <v>43</v>
       </c>
@@ -3993,7 +4000,7 @@
       <c r="D215" s="5"/>
       <c r="E215" s="11"/>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
         <v>43</v>
       </c>
@@ -4006,7 +4013,7 @@
       <c r="D216" s="5"/>
       <c r="E216" s="11"/>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
         <v>43</v>
       </c>
@@ -4019,7 +4026,7 @@
       <c r="D217" s="5"/>
       <c r="E217" s="11"/>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
         <v>43</v>
       </c>
@@ -4032,7 +4039,7 @@
       <c r="D218" s="5"/>
       <c r="E218" s="11"/>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
         <v>43</v>
       </c>
@@ -4045,7 +4052,7 @@
       <c r="D219" s="5"/>
       <c r="E219" s="11"/>
     </row>
-    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
         <v>43</v>
       </c>
@@ -4058,7 +4065,7 @@
       <c r="D220" s="5"/>
       <c r="E220" s="11"/>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
         <v>43</v>
       </c>
@@ -4071,7 +4078,7 @@
       <c r="D221" s="5"/>
       <c r="E221" s="11"/>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="s">
         <v>43</v>
       </c>
@@ -4084,7 +4091,7 @@
       <c r="D222" s="5"/>
       <c r="E222" s="11"/>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="4" t="s">
         <v>43</v>
       </c>
@@ -4097,7 +4104,7 @@
       <c r="D223" s="5"/>
       <c r="E223" s="11"/>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
         <v>43</v>
       </c>
@@ -4110,7 +4117,7 @@
       <c r="D224" s="5"/>
       <c r="E224" s="11"/>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
         <v>43</v>
       </c>
@@ -4123,7 +4130,7 @@
       <c r="D225" s="5"/>
       <c r="E225" s="11"/>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
         <v>43</v>
       </c>
@@ -4136,7 +4143,7 @@
       <c r="D226" s="5"/>
       <c r="E226" s="11"/>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
         <v>43</v>
       </c>
@@ -4149,7 +4156,7 @@
       <c r="D227" s="5"/>
       <c r="E227" s="11"/>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
         <v>43</v>
       </c>
@@ -4162,7 +4169,7 @@
       <c r="D228" s="5"/>
       <c r="E228" s="11"/>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
         <v>43</v>
       </c>
@@ -4175,7 +4182,7 @@
       <c r="D229" s="5"/>
       <c r="E229" s="11"/>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
         <v>43</v>
       </c>
@@ -4188,7 +4195,7 @@
       <c r="D230" s="5"/>
       <c r="E230" s="11"/>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
         <v>43</v>
       </c>
@@ -4201,7 +4208,7 @@
       <c r="D231" s="5"/>
       <c r="E231" s="11"/>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
         <v>43</v>
       </c>
@@ -4214,7 +4221,7 @@
       <c r="D232" s="5"/>
       <c r="E232" s="11"/>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
         <v>43</v>
       </c>
@@ -4227,7 +4234,7 @@
       <c r="D233" s="5"/>
       <c r="E233" s="11"/>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
         <v>43</v>
       </c>
@@ -4240,7 +4247,7 @@
       <c r="D234" s="5"/>
       <c r="E234" s="11"/>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
         <v>43</v>
       </c>
@@ -4253,7 +4260,7 @@
       <c r="D235" s="5"/>
       <c r="E235" s="11"/>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
         <v>43</v>
       </c>
@@ -4266,7 +4273,7 @@
       <c r="D236" s="5"/>
       <c r="E236" s="11"/>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
         <v>43</v>
       </c>
@@ -4279,7 +4286,7 @@
       <c r="D237" s="5"/>
       <c r="E237" s="11"/>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
         <v>43</v>
       </c>
@@ -4292,7 +4299,7 @@
       <c r="D238" s="5"/>
       <c r="E238" s="11"/>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
         <v>43</v>
       </c>
@@ -4305,7 +4312,7 @@
       <c r="D239" s="5"/>
       <c r="E239" s="11"/>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
         <v>43</v>
       </c>
@@ -4318,7 +4325,7 @@
       <c r="D240" s="5"/>
       <c r="E240" s="11"/>
     </row>
-    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
         <v>43</v>
       </c>
@@ -4331,7 +4338,7 @@
       <c r="D241" s="5"/>
       <c r="E241" s="11"/>
     </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
         <v>43</v>
       </c>
@@ -4344,7 +4351,7 @@
       <c r="D242" s="5"/>
       <c r="E242" s="11"/>
     </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
         <v>43</v>
       </c>
@@ -4357,7 +4364,7 @@
       <c r="D243" s="5"/>
       <c r="E243" s="11"/>
     </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
         <v>43</v>
       </c>
@@ -4370,7 +4377,7 @@
       <c r="D244" s="5"/>
       <c r="E244" s="11"/>
     </row>
-    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>43</v>
       </c>
@@ -4383,7 +4390,7 @@
       <c r="D245" s="5"/>
       <c r="E245" s="11"/>
     </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
         <v>43</v>
       </c>
@@ -4396,7 +4403,7 @@
       <c r="D246" s="5"/>
       <c r="E246" s="11"/>
     </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
         <v>43</v>
       </c>
@@ -4409,7 +4416,7 @@
       <c r="D247" s="5"/>
       <c r="E247" s="11"/>
     </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
         <v>43</v>
       </c>
@@ -4422,7 +4429,7 @@
       <c r="D248" s="5"/>
       <c r="E248" s="11"/>
     </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
         <v>43</v>
       </c>
@@ -4435,7 +4442,7 @@
       <c r="D249" s="5"/>
       <c r="E249" s="11"/>
     </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
         <v>43</v>
       </c>
@@ -4448,7 +4455,7 @@
       <c r="D250" s="5"/>
       <c r="E250" s="11"/>
     </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>43</v>
       </c>
@@ -4461,7 +4468,7 @@
       <c r="D251" s="5"/>
       <c r="E251" s="11"/>
     </row>
-    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
         <v>43</v>
       </c>
@@ -4474,7 +4481,7 @@
       <c r="D252" s="5"/>
       <c r="E252" s="11"/>
     </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
         <v>43</v>
       </c>
@@ -4487,7 +4494,7 @@
       <c r="D253" s="5"/>
       <c r="E253" s="11"/>
     </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
         <v>43</v>
       </c>
@@ -4500,7 +4507,7 @@
       <c r="D254" s="5"/>
       <c r="E254" s="11"/>
     </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
         <v>43</v>
       </c>
@@ -4513,7 +4520,7 @@
       <c r="D255" s="5"/>
       <c r="E255" s="11"/>
     </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
         <v>43</v>
       </c>
@@ -4526,7 +4533,7 @@
       <c r="D256" s="5"/>
       <c r="E256" s="11"/>
     </row>
-    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
         <v>43</v>
       </c>
@@ -4539,7 +4546,7 @@
       <c r="D257" s="5"/>
       <c r="E257" s="11"/>
     </row>
-    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
         <v>43</v>
       </c>
@@ -4552,7 +4559,7 @@
       <c r="D258" s="5"/>
       <c r="E258" s="11"/>
     </row>
-    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
         <v>43</v>
       </c>
@@ -4565,7 +4572,7 @@
       <c r="D259" s="5"/>
       <c r="E259" s="11"/>
     </row>
-    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
         <v>43</v>
       </c>
@@ -4578,7 +4585,7 @@
       <c r="D260" s="5"/>
       <c r="E260" s="11"/>
     </row>
-    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
         <v>43</v>
       </c>
@@ -4591,7 +4598,7 @@
       <c r="D261" s="5"/>
       <c r="E261" s="11"/>
     </row>
-    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
         <v>43</v>
       </c>
@@ -4604,7 +4611,7 @@
       <c r="D262" s="5"/>
       <c r="E262" s="11"/>
     </row>
-    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
         <v>43</v>
       </c>
@@ -4617,7 +4624,7 @@
       <c r="D263" s="5"/>
       <c r="E263" s="11"/>
     </row>
-    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
         <v>43</v>
       </c>
@@ -4630,7 +4637,7 @@
       <c r="D264" s="5"/>
       <c r="E264" s="11"/>
     </row>
-    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
         <v>43</v>
       </c>
@@ -4643,7 +4650,7 @@
       <c r="D265" s="5"/>
       <c r="E265" s="11"/>
     </row>
-    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
         <v>43</v>
       </c>
@@ -4656,7 +4663,7 @@
       <c r="D266" s="5"/>
       <c r="E266" s="11"/>
     </row>
-    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
         <v>43</v>
       </c>
@@ -4669,7 +4676,7 @@
       <c r="D267" s="5"/>
       <c r="E267" s="11"/>
     </row>
-    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
         <v>43</v>
       </c>
@@ -4682,7 +4689,7 @@
       <c r="D268" s="5"/>
       <c r="E268" s="11"/>
     </row>
-    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
         <v>43</v>
       </c>
@@ -4695,7 +4702,7 @@
       <c r="D269" s="5"/>
       <c r="E269" s="11"/>
     </row>
-    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
         <v>43</v>
       </c>
@@ -4708,7 +4715,7 @@
       <c r="D270" s="5"/>
       <c r="E270" s="11"/>
     </row>
-    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>43</v>
       </c>
@@ -4721,7 +4728,7 @@
       <c r="D271" s="5"/>
       <c r="E271" s="11"/>
     </row>
-    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
         <v>43</v>
       </c>
@@ -4734,7 +4741,7 @@
       <c r="D272" s="5"/>
       <c r="E272" s="11"/>
     </row>
-    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
         <v>43</v>
       </c>
@@ -4747,7 +4754,7 @@
       <c r="D273" s="5"/>
       <c r="E273" s="11"/>
     </row>
-    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
         <v>43</v>
       </c>
@@ -4760,7 +4767,7 @@
       <c r="D274" s="5"/>
       <c r="E274" s="11"/>
     </row>
-    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
         <v>43</v>
       </c>
@@ -4773,7 +4780,7 @@
       <c r="D275" s="5"/>
       <c r="E275" s="11"/>
     </row>
-    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
         <v>43</v>
       </c>
@@ -4786,7 +4793,7 @@
       <c r="D276" s="5"/>
       <c r="E276" s="11"/>
     </row>
-    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>43</v>
       </c>
@@ -4799,7 +4806,7 @@
       <c r="D277" s="5"/>
       <c r="E277" s="11"/>
     </row>
-    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
         <v>43</v>
       </c>
@@ -4812,7 +4819,7 @@
       <c r="D278" s="5"/>
       <c r="E278" s="11"/>
     </row>
-    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
         <v>43</v>
       </c>
@@ -4825,7 +4832,7 @@
       <c r="D279" s="5"/>
       <c r="E279" s="11"/>
     </row>
-    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
         <v>43</v>
       </c>
@@ -4838,7 +4845,7 @@
       <c r="D280" s="5"/>
       <c r="E280" s="11"/>
     </row>
-    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
         <v>43</v>
       </c>
@@ -4851,7 +4858,7 @@
       <c r="D281" s="5"/>
       <c r="E281" s="11"/>
     </row>
-    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
         <v>43</v>
       </c>
@@ -4864,7 +4871,7 @@
       <c r="D282" s="5"/>
       <c r="E282" s="11"/>
     </row>
-    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>43</v>
       </c>
@@ -4877,7 +4884,7 @@
       <c r="D283" s="5"/>
       <c r="E283" s="11"/>
     </row>
-    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
         <v>43</v>
       </c>
@@ -4890,7 +4897,7 @@
       <c r="D284" s="5"/>
       <c r="E284" s="11"/>
     </row>
-    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>43</v>
       </c>
@@ -4903,7 +4910,7 @@
       <c r="D285" s="5"/>
       <c r="E285" s="11"/>
     </row>
-    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
         <v>43</v>
       </c>
@@ -4916,7 +4923,7 @@
       <c r="D286" s="5"/>
       <c r="E286" s="11"/>
     </row>
-    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
         <v>43</v>
       </c>
@@ -4929,7 +4936,7 @@
       <c r="D287" s="5"/>
       <c r="E287" s="11"/>
     </row>
-    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
         <v>43</v>
       </c>
@@ -4942,7 +4949,7 @@
       <c r="D288" s="5"/>
       <c r="E288" s="11"/>
     </row>
-    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
         <v>43</v>
       </c>
@@ -4955,7 +4962,7 @@
       <c r="D289" s="5"/>
       <c r="E289" s="11"/>
     </row>
-    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
         <v>43</v>
       </c>
@@ -4968,7 +4975,7 @@
       <c r="D290" s="5"/>
       <c r="E290" s="11"/>
     </row>
-    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
         <v>43</v>
       </c>
@@ -4981,7 +4988,7 @@
       <c r="D291" s="5"/>
       <c r="E291" s="11"/>
     </row>
-    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
         <v>43</v>
       </c>
@@ -4994,7 +5001,7 @@
       <c r="D292" s="5"/>
       <c r="E292" s="11"/>
     </row>
-    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
         <v>43</v>
       </c>
@@ -5007,7 +5014,7 @@
       <c r="D293" s="5"/>
       <c r="E293" s="11"/>
     </row>
-    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
         <v>43</v>
       </c>
@@ -5020,7 +5027,7 @@
       <c r="D294" s="5"/>
       <c r="E294" s="11"/>
     </row>
-    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
         <v>43</v>
       </c>
@@ -5033,7 +5040,7 @@
       <c r="D295" s="5"/>
       <c r="E295" s="11"/>
     </row>
-    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
         <v>43</v>
       </c>
@@ -5046,7 +5053,7 @@
       <c r="D296" s="5"/>
       <c r="E296" s="11"/>
     </row>
-    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
         <v>43</v>
       </c>
@@ -5059,7 +5066,7 @@
       <c r="D297" s="5"/>
       <c r="E297" s="11"/>
     </row>
-    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
         <v>43</v>
       </c>
@@ -5072,7 +5079,7 @@
       <c r="D298" s="5"/>
       <c r="E298" s="11"/>
     </row>
-    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
         <v>43</v>
       </c>
@@ -5085,7 +5092,7 @@
       <c r="D299" s="5"/>
       <c r="E299" s="11"/>
     </row>
-    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
         <v>43</v>
       </c>
@@ -5098,7 +5105,7 @@
       <c r="D300" s="5"/>
       <c r="E300" s="11"/>
     </row>
-    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
         <v>43</v>
       </c>
@@ -5111,7 +5118,7 @@
       <c r="D301" s="5"/>
       <c r="E301" s="11"/>
     </row>
-    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
         <v>43</v>
       </c>
@@ -5124,7 +5131,7 @@
       <c r="D302" s="5"/>
       <c r="E302" s="11"/>
     </row>
-    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
         <v>43</v>
       </c>
@@ -5137,7 +5144,7 @@
       <c r="D303" s="5"/>
       <c r="E303" s="11"/>
     </row>
-    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
         <v>43</v>
       </c>
@@ -5150,7 +5157,7 @@
       <c r="D304" s="5"/>
       <c r="E304" s="11"/>
     </row>
-    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
         <v>43</v>
       </c>
@@ -5163,7 +5170,7 @@
       <c r="D305" s="5"/>
       <c r="E305" s="11"/>
     </row>
-    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
         <v>43</v>
       </c>
@@ -5176,7 +5183,7 @@
       <c r="D306" s="5"/>
       <c r="E306" s="11"/>
     </row>
-    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
         <v>43</v>
       </c>
@@ -5189,7 +5196,7 @@
       <c r="D307" s="5"/>
       <c r="E307" s="11"/>
     </row>
-    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
         <v>43</v>
       </c>
@@ -5202,7 +5209,7 @@
       <c r="D308" s="5"/>
       <c r="E308" s="11"/>
     </row>
-    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
         <v>43</v>
       </c>
@@ -5215,7 +5222,7 @@
       <c r="D309" s="5"/>
       <c r="E309" s="11"/>
     </row>
-    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
         <v>43</v>
       </c>
@@ -5228,7 +5235,7 @@
       <c r="D310" s="5"/>
       <c r="E310" s="11"/>
     </row>
-    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
         <v>43</v>
       </c>
@@ -5241,7 +5248,7 @@
       <c r="D311" s="5"/>
       <c r="E311" s="11"/>
     </row>
-    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A312" s="4" t="s">
         <v>43</v>
       </c>
@@ -5254,7 +5261,7 @@
       <c r="D312" s="5"/>
       <c r="E312" s="11"/>
     </row>
-    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A313" s="4" t="s">
         <v>43</v>
       </c>
@@ -5267,7 +5274,7 @@
       <c r="D313" s="5"/>
       <c r="E313" s="11"/>
     </row>
-    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A314" s="4" t="s">
         <v>43</v>
       </c>
@@ -5280,7 +5287,7 @@
       <c r="D314" s="5"/>
       <c r="E314" s="11"/>
     </row>
-    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A315" s="4" t="s">
         <v>43</v>
       </c>
@@ -5293,7 +5300,7 @@
       <c r="D315" s="5"/>
       <c r="E315" s="11"/>
     </row>
-    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A316" s="4" t="s">
         <v>43</v>
       </c>
@@ -5310,7 +5317,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A317" s="4" t="s">
         <v>43</v>
       </c>
@@ -5323,7 +5330,7 @@
       <c r="D317" s="5"/>
       <c r="E317" s="11"/>
     </row>
-    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A318" s="4" t="s">
         <v>43</v>
       </c>
@@ -5340,7 +5347,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
         <v>43</v>
       </c>
@@ -5357,7 +5364,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
         <v>43</v>
       </c>
@@ -5372,7 +5379,7 @@
       </c>
       <c r="E320" s="11"/>
     </row>
-    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
         <v>43</v>
       </c>
@@ -5387,7 +5394,7 @@
       </c>
       <c r="E321" s="11"/>
     </row>
-    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A322" s="2" t="s">
         <v>5</v>
       </c>
@@ -5402,7 +5409,7 @@
       </c>
       <c r="E322" s="10"/>
     </row>
-    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2" t="s">
         <v>5</v>
       </c>
@@ -5417,7 +5424,7 @@
       </c>
       <c r="E323" s="10"/>
     </row>
-    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A324" s="2" t="s">
         <v>5</v>
       </c>
@@ -5432,7 +5439,7 @@
       </c>
       <c r="E324" s="10"/>
     </row>
-    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
         <v>5</v>
       </c>
@@ -5447,7 +5454,7 @@
       </c>
       <c r="E325" s="10"/>
     </row>
-    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
         <v>44</v>
       </c>
@@ -5460,7 +5467,7 @@
       <c r="D326" s="5"/>
       <c r="E326" s="11"/>
     </row>
-    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
         <v>44</v>
       </c>
@@ -5473,7 +5480,7 @@
       <c r="D327" s="5"/>
       <c r="E327" s="11"/>
     </row>
-    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
         <v>44</v>
       </c>
@@ -5486,7 +5493,7 @@
       <c r="D328" s="5"/>
       <c r="E328" s="11"/>
     </row>
-    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
         <v>44</v>
       </c>
@@ -5499,7 +5506,7 @@
       <c r="D329" s="5"/>
       <c r="E329" s="11"/>
     </row>
-    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A330" s="4" t="s">
         <v>44</v>
       </c>
@@ -5512,7 +5519,7 @@
       <c r="D330" s="5"/>
       <c r="E330" s="11"/>
     </row>
-    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
         <v>44</v>
       </c>
@@ -5525,7 +5532,7 @@
       <c r="D331" s="5"/>
       <c r="E331" s="11"/>
     </row>
-    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
         <v>44</v>
       </c>
@@ -5538,7 +5545,7 @@
       <c r="D332" s="5"/>
       <c r="E332" s="11"/>
     </row>
-    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A333" s="4" t="s">
         <v>44</v>
       </c>
@@ -5551,7 +5558,7 @@
       <c r="D333" s="5"/>
       <c r="E333" s="11"/>
     </row>
-    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A334" s="4" t="s">
         <v>44</v>
       </c>
@@ -5564,7 +5571,7 @@
       <c r="D334" s="5"/>
       <c r="E334" s="11"/>
     </row>
-    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A335" s="4" t="s">
         <v>44</v>
       </c>
@@ -5577,7 +5584,7 @@
       <c r="D335" s="5"/>
       <c r="E335" s="11"/>
     </row>
-    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
         <v>44</v>
       </c>
@@ -5590,7 +5597,7 @@
       <c r="D336" s="5"/>
       <c r="E336" s="11"/>
     </row>
-    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
         <v>44</v>
       </c>
@@ -5603,7 +5610,7 @@
       <c r="D337" s="5"/>
       <c r="E337" s="11"/>
     </row>
-    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
         <v>44</v>
       </c>
@@ -5616,7 +5623,7 @@
       <c r="D338" s="5"/>
       <c r="E338" s="11"/>
     </row>
-    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
         <v>44</v>
       </c>
@@ -5629,7 +5636,7 @@
       <c r="D339" s="5"/>
       <c r="E339" s="11"/>
     </row>
-    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
         <v>44</v>
       </c>
@@ -5642,7 +5649,7 @@
       <c r="D340" s="5"/>
       <c r="E340" s="11"/>
     </row>
-    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
         <v>44</v>
       </c>
@@ -5655,7 +5662,7 @@
       <c r="D341" s="5"/>
       <c r="E341" s="11"/>
     </row>
-    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A342" s="4" t="s">
         <v>44</v>
       </c>
@@ -5668,7 +5675,7 @@
       <c r="D342" s="5"/>
       <c r="E342" s="11"/>
     </row>
-    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A343" s="4" t="s">
         <v>44</v>
       </c>
@@ -5681,7 +5688,7 @@
       <c r="D343" s="5"/>
       <c r="E343" s="11"/>
     </row>
-    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A344" s="4" t="s">
         <v>44</v>
       </c>
@@ -5694,7 +5701,7 @@
       <c r="D344" s="5"/>
       <c r="E344" s="11"/>
     </row>
-    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A345" s="4" t="s">
         <v>44</v>
       </c>
@@ -5707,7 +5714,7 @@
       <c r="D345" s="5"/>
       <c r="E345" s="11"/>
     </row>
-    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A346" s="4" t="s">
         <v>44</v>
       </c>
@@ -5720,7 +5727,7 @@
       <c r="D346" s="5"/>
       <c r="E346" s="11"/>
     </row>
-    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A347" s="4" t="s">
         <v>44</v>
       </c>
@@ -5733,7 +5740,7 @@
       <c r="D347" s="5"/>
       <c r="E347" s="11"/>
     </row>
-    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A348" s="4" t="s">
         <v>44</v>
       </c>
@@ -5746,7 +5753,7 @@
       <c r="D348" s="5"/>
       <c r="E348" s="11"/>
     </row>
-    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A349" s="4" t="s">
         <v>44</v>
       </c>
@@ -5759,7 +5766,7 @@
       <c r="D349" s="5"/>
       <c r="E349" s="11"/>
     </row>
-    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A350" s="4" t="s">
         <v>44</v>
       </c>
@@ -5772,7 +5779,7 @@
       <c r="D350" s="5"/>
       <c r="E350" s="11"/>
     </row>
-    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
         <v>44</v>
       </c>
@@ -5785,7 +5792,7 @@
       <c r="D351" s="5"/>
       <c r="E351" s="11"/>
     </row>
-    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A352" s="4" t="s">
         <v>44</v>
       </c>
@@ -5798,7 +5805,7 @@
       <c r="D352" s="5"/>
       <c r="E352" s="11"/>
     </row>
-    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A353" s="4" t="s">
         <v>44</v>
       </c>
@@ -5811,7 +5818,7 @@
       <c r="D353" s="5"/>
       <c r="E353" s="11"/>
     </row>
-    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A354" s="4" t="s">
         <v>44</v>
       </c>
@@ -5824,7 +5831,7 @@
       <c r="D354" s="5"/>
       <c r="E354" s="11"/>
     </row>
-    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A355" s="4" t="s">
         <v>44</v>
       </c>
@@ -5837,7 +5844,7 @@
       <c r="D355" s="5"/>
       <c r="E355" s="11"/>
     </row>
-    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A356" s="4" t="s">
         <v>44</v>
       </c>
@@ -5850,7 +5857,7 @@
       <c r="D356" s="5"/>
       <c r="E356" s="11"/>
     </row>
-    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A357" s="4" t="s">
         <v>44</v>
       </c>
@@ -5863,7 +5870,7 @@
       <c r="D357" s="5"/>
       <c r="E357" s="11"/>
     </row>
-    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A358" s="4" t="s">
         <v>44</v>
       </c>
@@ -5876,7 +5883,7 @@
       <c r="D358" s="5"/>
       <c r="E358" s="11"/>
     </row>
-    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
         <v>44</v>
       </c>
@@ -5889,7 +5896,7 @@
       <c r="D359" s="5"/>
       <c r="E359" s="11"/>
     </row>
-    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A360" s="4" t="s">
         <v>44</v>
       </c>
@@ -5902,7 +5909,7 @@
       <c r="D360" s="5"/>
       <c r="E360" s="11"/>
     </row>
-    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A361" s="4" t="s">
         <v>44</v>
       </c>
@@ -5915,7 +5922,7 @@
       <c r="D361" s="5"/>
       <c r="E361" s="11"/>
     </row>
-    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A362" s="4" t="s">
         <v>44</v>
       </c>
@@ -5928,7 +5935,7 @@
       <c r="D362" s="5"/>
       <c r="E362" s="11"/>
     </row>
-    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
         <v>44</v>
       </c>
@@ -5941,7 +5948,7 @@
       <c r="D363" s="5"/>
       <c r="E363" s="11"/>
     </row>
-    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A364" s="4" t="s">
         <v>44</v>
       </c>
@@ -5954,7 +5961,7 @@
       <c r="D364" s="5"/>
       <c r="E364" s="11"/>
     </row>
-    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A365" s="4" t="s">
         <v>44</v>
       </c>
@@ -5967,7 +5974,7 @@
       <c r="D365" s="5"/>
       <c r="E365" s="11"/>
     </row>
-    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A366" s="4" t="s">
         <v>44</v>
       </c>
@@ -5980,7 +5987,7 @@
       <c r="D366" s="5"/>
       <c r="E366" s="11"/>
     </row>
-    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A367" s="4" t="s">
         <v>44</v>
       </c>
@@ -5993,7 +6000,7 @@
       <c r="D367" s="5"/>
       <c r="E367" s="11"/>
     </row>
-    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A368" s="4" t="s">
         <v>44</v>
       </c>
@@ -6006,7 +6013,7 @@
       <c r="D368" s="5"/>
       <c r="E368" s="11"/>
     </row>
-    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A369" s="4" t="s">
         <v>44</v>
       </c>
@@ -6019,7 +6026,7 @@
       <c r="D369" s="5"/>
       <c r="E369" s="11"/>
     </row>
-    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A370" s="4" t="s">
         <v>44</v>
       </c>
@@ -6032,7 +6039,7 @@
       <c r="D370" s="5"/>
       <c r="E370" s="11"/>
     </row>
-    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A371" s="4" t="s">
         <v>44</v>
       </c>
@@ -6045,7 +6052,7 @@
       <c r="D371" s="5"/>
       <c r="E371" s="11"/>
     </row>
-    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A372" s="4" t="s">
         <v>44</v>
       </c>
@@ -6058,7 +6065,7 @@
       <c r="D372" s="5"/>
       <c r="E372" s="11"/>
     </row>
-    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A373" s="4" t="s">
         <v>44</v>
       </c>
@@ -6071,7 +6078,7 @@
       <c r="D373" s="5"/>
       <c r="E373" s="11"/>
     </row>
-    <row r="374" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A374" s="4" t="s">
         <v>44</v>
       </c>
@@ -6084,7 +6091,7 @@
       <c r="D374" s="5"/>
       <c r="E374" s="11"/>
     </row>
-    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
         <v>44</v>
       </c>
@@ -6097,7 +6104,7 @@
       <c r="D375" s="5"/>
       <c r="E375" s="11"/>
     </row>
-    <row r="376" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A376" s="4" t="s">
         <v>44</v>
       </c>
@@ -6110,7 +6117,7 @@
       <c r="D376" s="5"/>
       <c r="E376" s="11"/>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A377" s="4" t="s">
         <v>44</v>
       </c>
@@ -6127,7 +6134,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A378" s="4" t="s">
         <v>44</v>
       </c>
@@ -6140,7 +6147,7 @@
       <c r="D378" s="5"/>
       <c r="E378" s="11"/>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A379" s="4" t="s">
         <v>44</v>
       </c>
@@ -6153,7 +6160,7 @@
       <c r="D379" s="5"/>
       <c r="E379" s="11"/>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A380" s="4" t="s">
         <v>44</v>
       </c>
@@ -6166,7 +6173,7 @@
       <c r="D380" s="5"/>
       <c r="E380" s="11"/>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A381" s="4" t="s">
         <v>44</v>
       </c>
@@ -6179,7 +6186,7 @@
       <c r="D381" s="5"/>
       <c r="E381" s="11"/>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A382" s="4" t="s">
         <v>44</v>
       </c>
@@ -6192,7 +6199,7 @@
       <c r="D382" s="5"/>
       <c r="E382" s="11"/>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A383" s="4" t="s">
         <v>44</v>
       </c>
@@ -6205,7 +6212,7 @@
       <c r="D383" s="5"/>
       <c r="E383" s="11"/>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A384" s="4" t="s">
         <v>44</v>
       </c>
@@ -6218,7 +6225,7 @@
       <c r="D384" s="5"/>
       <c r="E384" s="11"/>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A385" s="4" t="s">
         <v>44</v>
       </c>
@@ -6231,7 +6238,7 @@
       <c r="D385" s="5"/>
       <c r="E385" s="11"/>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A386" s="4" t="s">
         <v>44</v>
       </c>
@@ -6244,7 +6251,7 @@
       <c r="D386" s="5"/>
       <c r="E386" s="11"/>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A387" s="4" t="s">
         <v>44</v>
       </c>
@@ -6257,7 +6264,7 @@
       <c r="D387" s="5"/>
       <c r="E387" s="11"/>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A388" s="4" t="s">
         <v>44</v>
       </c>
@@ -6270,7 +6277,7 @@
       <c r="D388" s="5"/>
       <c r="E388" s="11"/>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A389" s="4" t="s">
         <v>44</v>
       </c>
@@ -6283,7 +6290,7 @@
       <c r="D389" s="5"/>
       <c r="E389" s="11"/>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A390" s="4" t="s">
         <v>44</v>
       </c>
@@ -6296,7 +6303,7 @@
       <c r="D390" s="5"/>
       <c r="E390" s="11"/>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
         <v>44</v>
       </c>
@@ -6309,7 +6316,7 @@
       <c r="D391" s="5"/>
       <c r="E391" s="11"/>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A392" s="4" t="s">
         <v>44</v>
       </c>
@@ -6322,7 +6329,7 @@
       <c r="D392" s="5"/>
       <c r="E392" s="11"/>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A393" s="4" t="s">
         <v>44</v>
       </c>
@@ -6335,7 +6342,7 @@
       <c r="D393" s="5"/>
       <c r="E393" s="11"/>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
         <v>44</v>
       </c>
@@ -6348,7 +6355,7 @@
       <c r="D394" s="5"/>
       <c r="E394" s="11"/>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
         <v>44</v>
       </c>
@@ -6361,7 +6368,7 @@
       <c r="D395" s="5"/>
       <c r="E395" s="11"/>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A396" s="4" t="s">
         <v>44</v>
       </c>
@@ -6374,7 +6381,7 @@
       <c r="D396" s="5"/>
       <c r="E396" s="11"/>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A397" s="4" t="s">
         <v>44</v>
       </c>
@@ -6387,7 +6394,7 @@
       <c r="D397" s="5"/>
       <c r="E397" s="11"/>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A398" s="4" t="s">
         <v>44</v>
       </c>
@@ -6400,7 +6407,7 @@
       <c r="D398" s="5"/>
       <c r="E398" s="11"/>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A399" s="4" t="s">
         <v>44</v>
       </c>
@@ -6413,7 +6420,7 @@
       <c r="D399" s="5"/>
       <c r="E399" s="11"/>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A400" s="4" t="s">
         <v>44</v>
       </c>
@@ -6426,7 +6433,7 @@
       <c r="D400" s="5"/>
       <c r="E400" s="11"/>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A401" s="4" t="s">
         <v>44</v>
       </c>
@@ -6439,7 +6446,7 @@
       <c r="D401" s="5"/>
       <c r="E401" s="11"/>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A402" s="4" t="s">
         <v>44</v>
       </c>
@@ -6452,7 +6459,7 @@
       <c r="D402" s="5"/>
       <c r="E402" s="11"/>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A403" s="4" t="s">
         <v>44</v>
       </c>
@@ -6465,7 +6472,7 @@
       <c r="D403" s="5"/>
       <c r="E403" s="11"/>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A404" s="4" t="s">
         <v>44</v>
       </c>
@@ -6478,7 +6485,7 @@
       <c r="D404" s="5"/>
       <c r="E404" s="11"/>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A405" s="4" t="s">
         <v>44</v>
       </c>
@@ -6491,7 +6498,7 @@
       <c r="D405" s="5"/>
       <c r="E405" s="11"/>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A406" s="4" t="s">
         <v>44</v>
       </c>
@@ -6504,7 +6511,7 @@
       <c r="D406" s="5"/>
       <c r="E406" s="11"/>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A407" s="4" t="s">
         <v>44</v>
       </c>
@@ -6517,7 +6524,7 @@
       <c r="D407" s="5"/>
       <c r="E407" s="11"/>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A408" s="4" t="s">
         <v>44</v>
       </c>
@@ -6530,7 +6537,7 @@
       <c r="D408" s="5"/>
       <c r="E408" s="11"/>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A409" s="4" t="s">
         <v>44</v>
       </c>
@@ -6543,7 +6550,7 @@
       <c r="D409" s="5"/>
       <c r="E409" s="11"/>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A410" s="4" t="s">
         <v>44</v>
       </c>
@@ -6556,7 +6563,7 @@
       <c r="D410" s="5"/>
       <c r="E410" s="11"/>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A411" s="4" t="s">
         <v>44</v>
       </c>
@@ -6569,7 +6576,7 @@
       <c r="D411" s="5"/>
       <c r="E411" s="11"/>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A412" s="4" t="s">
         <v>44</v>
       </c>
@@ -6582,7 +6589,7 @@
       <c r="D412" s="5"/>
       <c r="E412" s="11"/>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A413" s="4" t="s">
         <v>44</v>
       </c>
@@ -6595,7 +6602,7 @@
       <c r="D413" s="5"/>
       <c r="E413" s="11"/>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A414" s="4" t="s">
         <v>44</v>
       </c>
@@ -6608,7 +6615,7 @@
       <c r="D414" s="5"/>
       <c r="E414" s="11"/>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A415" s="4" t="s">
         <v>44</v>
       </c>
@@ -6621,7 +6628,7 @@
       <c r="D415" s="5"/>
       <c r="E415" s="11"/>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A416" s="4" t="s">
         <v>44</v>
       </c>
@@ -6634,7 +6641,7 @@
       <c r="D416" s="5"/>
       <c r="E416" s="11"/>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A417" s="4" t="s">
         <v>44</v>
       </c>
@@ -6647,7 +6654,7 @@
       <c r="D417" s="5"/>
       <c r="E417" s="11"/>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A418" s="4" t="s">
         <v>44</v>
       </c>
@@ -6660,7 +6667,7 @@
       <c r="D418" s="5"/>
       <c r="E418" s="11"/>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A419" s="4" t="s">
         <v>44</v>
       </c>
@@ -6673,7 +6680,7 @@
       <c r="D419" s="5"/>
       <c r="E419" s="11"/>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A420" s="4" t="s">
         <v>44</v>
       </c>
@@ -6686,7 +6693,7 @@
       <c r="D420" s="5"/>
       <c r="E420" s="11"/>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A421" s="4" t="s">
         <v>44</v>
       </c>
@@ -6699,7 +6706,7 @@
       <c r="D421" s="5"/>
       <c r="E421" s="11"/>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A422" s="4" t="s">
         <v>44</v>
       </c>
@@ -6712,7 +6719,7 @@
       <c r="D422" s="5"/>
       <c r="E422" s="11"/>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A423" s="4" t="s">
         <v>44</v>
       </c>
@@ -6725,7 +6732,7 @@
       <c r="D423" s="5"/>
       <c r="E423" s="11"/>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A424" s="4" t="s">
         <v>44</v>
       </c>
@@ -6738,7 +6745,7 @@
       <c r="D424" s="5"/>
       <c r="E424" s="11"/>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A425" s="4" t="s">
         <v>44</v>
       </c>
@@ -6751,7 +6758,7 @@
       <c r="D425" s="5"/>
       <c r="E425" s="11"/>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A426" s="4" t="s">
         <v>44</v>
       </c>
@@ -6764,7 +6771,7 @@
       <c r="D426" s="5"/>
       <c r="E426" s="11"/>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A427" s="4" t="s">
         <v>44</v>
       </c>
@@ -6777,7 +6784,7 @@
       <c r="D427" s="5"/>
       <c r="E427" s="11"/>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A428" s="4" t="s">
         <v>44</v>
       </c>
@@ -6790,7 +6797,7 @@
       <c r="D428" s="5"/>
       <c r="E428" s="11"/>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A429" s="4" t="s">
         <v>44</v>
       </c>
@@ -6803,7 +6810,7 @@
       <c r="D429" s="5"/>
       <c r="E429" s="11"/>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A430" s="4" t="s">
         <v>44</v>
       </c>
@@ -6816,7 +6823,7 @@
       <c r="D430" s="5"/>
       <c r="E430" s="11"/>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A431" s="4" t="s">
         <v>44</v>
       </c>
@@ -6829,7 +6836,7 @@
       <c r="D431" s="5"/>
       <c r="E431" s="11"/>
     </row>
-    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A432" s="4" t="s">
         <v>44</v>
       </c>
@@ -6846,7 +6853,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A433" s="4" t="s">
         <v>44</v>
       </c>
@@ -6859,7 +6866,7 @@
       <c r="D433" s="5"/>
       <c r="E433" s="11"/>
     </row>
-    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A434" s="4" t="s">
         <v>44</v>
       </c>
@@ -6876,7 +6883,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A435" s="4" t="s">
         <v>44</v>
       </c>
@@ -6893,7 +6900,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A436" s="4" t="s">
         <v>44</v>
       </c>
@@ -6906,7 +6913,7 @@
       <c r="D436" s="5"/>
       <c r="E436" s="11"/>
     </row>
-    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A437" s="4" t="s">
         <v>44</v>
       </c>
@@ -6919,7 +6926,7 @@
       <c r="D437" s="5"/>
       <c r="E437" s="11"/>
     </row>
-    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A438" s="4" t="s">
         <v>44</v>
       </c>
@@ -6932,7 +6939,7 @@
       <c r="D438" s="5"/>
       <c r="E438" s="11"/>
     </row>
-    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A439" s="4" t="s">
         <v>44</v>
       </c>
@@ -6945,7 +6952,7 @@
       <c r="D439" s="5"/>
       <c r="E439" s="11"/>
     </row>
-    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A440" s="4" t="s">
         <v>44</v>
       </c>
@@ -6958,7 +6965,7 @@
       <c r="D440" s="5"/>
       <c r="E440" s="11"/>
     </row>
-    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A441" s="4" t="s">
         <v>44</v>
       </c>
@@ -6971,7 +6978,7 @@
       <c r="D441" s="5"/>
       <c r="E441" s="11"/>
     </row>
-    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A442" s="4" t="s">
         <v>44</v>
       </c>
@@ -6984,7 +6991,7 @@
       <c r="D442" s="5"/>
       <c r="E442" s="11"/>
     </row>
-    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A443" s="4" t="s">
         <v>44</v>
       </c>
@@ -6997,7 +7004,7 @@
       <c r="D443" s="5"/>
       <c r="E443" s="11"/>
     </row>
-    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A444" s="4" t="s">
         <v>44</v>
       </c>
@@ -7010,7 +7017,7 @@
       <c r="D444" s="5"/>
       <c r="E444" s="11"/>
     </row>
-    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A445" s="4" t="s">
         <v>44</v>
       </c>
@@ -7023,7 +7030,7 @@
       <c r="D445" s="5"/>
       <c r="E445" s="11"/>
     </row>
-    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A446" s="4" t="s">
         <v>44</v>
       </c>
@@ -7036,7 +7043,7 @@
       <c r="D446" s="5"/>
       <c r="E446" s="11"/>
     </row>
-    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A447" s="4" t="s">
         <v>44</v>
       </c>
@@ -7049,7 +7056,7 @@
       <c r="D447" s="5"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A448" s="4" t="s">
         <v>44</v>
       </c>
@@ -7062,7 +7069,7 @@
       <c r="D448" s="5"/>
       <c r="E448" s="11"/>
     </row>
-    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A449" s="4" t="s">
         <v>44</v>
       </c>
@@ -7075,7 +7082,7 @@
       <c r="D449" s="5"/>
       <c r="E449" s="11"/>
     </row>
-    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A450" s="4" t="s">
         <v>44</v>
       </c>
@@ -7088,7 +7095,7 @@
       <c r="D450" s="5"/>
       <c r="E450" s="11"/>
     </row>
-    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A451" s="4" t="s">
         <v>44</v>
       </c>
@@ -7101,7 +7108,7 @@
       <c r="D451" s="5"/>
       <c r="E451" s="11"/>
     </row>
-    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A452" s="4" t="s">
         <v>44</v>
       </c>
@@ -7114,7 +7121,7 @@
       <c r="D452" s="5"/>
       <c r="E452" s="11"/>
     </row>
-    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A453" s="4" t="s">
         <v>44</v>
       </c>
@@ -7127,7 +7134,7 @@
       <c r="D453" s="5"/>
       <c r="E453" s="11"/>
     </row>
-    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A454" s="4" t="s">
         <v>44</v>
       </c>
@@ -7140,7 +7147,7 @@
       <c r="D454" s="5"/>
       <c r="E454" s="11"/>
     </row>
-    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A455" s="4" t="s">
         <v>44</v>
       </c>
@@ -7153,7 +7160,7 @@
       <c r="D455" s="5"/>
       <c r="E455" s="11"/>
     </row>
-    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A456" s="4" t="s">
         <v>44</v>
       </c>
@@ -7166,7 +7173,7 @@
       <c r="D456" s="5"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A457" s="4" t="s">
         <v>44</v>
       </c>
@@ -7179,7 +7186,7 @@
       <c r="D457" s="5"/>
       <c r="E457" s="11"/>
     </row>
-    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A458" s="4" t="s">
         <v>44</v>
       </c>
@@ -7192,7 +7199,7 @@
       <c r="D458" s="5"/>
       <c r="E458" s="11"/>
     </row>
-    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A459" s="4" t="s">
         <v>44</v>
       </c>
@@ -7205,7 +7212,7 @@
       <c r="D459" s="5"/>
       <c r="E459" s="11"/>
     </row>
-    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A460" s="4" t="s">
         <v>44</v>
       </c>
@@ -7218,7 +7225,7 @@
       <c r="D460" s="5"/>
       <c r="E460" s="11"/>
     </row>
-    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A461" s="4" t="s">
         <v>44</v>
       </c>
@@ -7231,7 +7238,7 @@
       <c r="D461" s="5"/>
       <c r="E461" s="11"/>
     </row>
-    <row r="462" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A462" s="4" t="s">
         <v>44</v>
       </c>
@@ -7244,7 +7251,7 @@
       <c r="D462" s="5"/>
       <c r="E462" s="11"/>
     </row>
-    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A463" s="4" t="s">
         <v>44</v>
       </c>
@@ -7257,7 +7264,7 @@
       <c r="D463" s="5"/>
       <c r="E463" s="11"/>
     </row>
-    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A464" s="4" t="s">
         <v>44</v>
       </c>
@@ -7270,7 +7277,7 @@
       <c r="D464" s="5"/>
       <c r="E464" s="11"/>
     </row>
-    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A465" s="4" t="s">
         <v>44</v>
       </c>
@@ -7283,7 +7290,7 @@
       <c r="D465" s="5"/>
       <c r="E465" s="11"/>
     </row>
-    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A466" s="4" t="s">
         <v>44</v>
       </c>
@@ -7296,7 +7303,7 @@
       <c r="D466" s="5"/>
       <c r="E466" s="11"/>
     </row>
-    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A467" s="4" t="s">
         <v>44</v>
       </c>
@@ -7309,7 +7316,7 @@
       <c r="D467" s="5"/>
       <c r="E467" s="11"/>
     </row>
-    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A468" s="4" t="s">
         <v>44</v>
       </c>
@@ -7322,7 +7329,7 @@
       <c r="D468" s="5"/>
       <c r="E468" s="11"/>
     </row>
-    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A469" s="4" t="s">
         <v>44</v>
       </c>
@@ -7335,7 +7342,7 @@
       <c r="D469" s="5"/>
       <c r="E469" s="11"/>
     </row>
-    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A470" s="4" t="s">
         <v>44</v>
       </c>
@@ -7348,7 +7355,7 @@
       <c r="D470" s="5"/>
       <c r="E470" s="11"/>
     </row>
-    <row r="471" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A471" s="4" t="s">
         <v>44</v>
       </c>
@@ -7361,7 +7368,7 @@
       <c r="D471" s="5"/>
       <c r="E471" s="11"/>
     </row>
-    <row r="472" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A472" s="4" t="s">
         <v>44</v>
       </c>
@@ -7374,7 +7381,7 @@
       <c r="D472" s="5"/>
       <c r="E472" s="11"/>
     </row>
-    <row r="473" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A473" s="4" t="s">
         <v>44</v>
       </c>
@@ -7387,7 +7394,7 @@
       <c r="D473" s="5"/>
       <c r="E473" s="11"/>
     </row>
-    <row r="474" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A474" s="4" t="s">
         <v>44</v>
       </c>
@@ -7400,7 +7407,7 @@
       <c r="D474" s="5"/>
       <c r="E474" s="11"/>
     </row>
-    <row r="475" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A475" s="4" t="s">
         <v>44</v>
       </c>
@@ -7413,7 +7420,7 @@
       <c r="D475" s="5"/>
       <c r="E475" s="11"/>
     </row>
-    <row r="476" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A476" s="4" t="s">
         <v>44</v>
       </c>
@@ -7426,7 +7433,7 @@
       <c r="D476" s="5"/>
       <c r="E476" s="11"/>
     </row>
-    <row r="477" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A477" s="4" t="s">
         <v>44</v>
       </c>
@@ -7439,7 +7446,7 @@
       <c r="D477" s="5"/>
       <c r="E477" s="11"/>
     </row>
-    <row r="478" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A478" s="4" t="s">
         <v>44</v>
       </c>
@@ -7452,7 +7459,7 @@
       <c r="D478" s="5"/>
       <c r="E478" s="11"/>
     </row>
-    <row r="479" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A479" s="4" t="s">
         <v>44</v>
       </c>
@@ -7465,7 +7472,7 @@
       <c r="D479" s="5"/>
       <c r="E479" s="11"/>
     </row>
-    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A480" s="4" t="s">
         <v>44</v>
       </c>
@@ -7478,7 +7485,7 @@
       <c r="D480" s="5"/>
       <c r="E480" s="11"/>
     </row>
-    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A481" s="4" t="s">
         <v>44</v>
       </c>
@@ -7491,7 +7498,7 @@
       <c r="D481" s="5"/>
       <c r="E481" s="11"/>
     </row>
-    <row r="482" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A482" s="4" t="s">
         <v>44</v>
       </c>
@@ -7504,7 +7511,7 @@
       <c r="D482" s="5"/>
       <c r="E482" s="11"/>
     </row>
-    <row r="483" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A483" s="4" t="s">
         <v>44</v>
       </c>
@@ -7517,7 +7524,7 @@
       <c r="D483" s="5"/>
       <c r="E483" s="11"/>
     </row>
-    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A484" s="4" t="s">
         <v>44</v>
       </c>
@@ -7530,7 +7537,7 @@
       <c r="D484" s="5"/>
       <c r="E484" s="11"/>
     </row>
-    <row r="485" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A485" s="4" t="s">
         <v>44</v>
       </c>
@@ -7543,7 +7550,7 @@
       <c r="D485" s="5"/>
       <c r="E485" s="11"/>
     </row>
-    <row r="486" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A486" s="4" t="s">
         <v>44</v>
       </c>
@@ -7556,7 +7563,7 @@
       <c r="D486" s="5"/>
       <c r="E486" s="11"/>
     </row>
-    <row r="487" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A487" s="4" t="s">
         <v>44</v>
       </c>
@@ -7569,7 +7576,7 @@
       <c r="D487" s="5"/>
       <c r="E487" s="11"/>
     </row>
-    <row r="488" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A488" s="4" t="s">
         <v>44</v>
       </c>
@@ -7582,7 +7589,7 @@
       <c r="D488" s="5"/>
       <c r="E488" s="11"/>
     </row>
-    <row r="489" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A489" s="4" t="s">
         <v>44</v>
       </c>
@@ -7595,7 +7602,7 @@
       <c r="D489" s="5"/>
       <c r="E489" s="11"/>
     </row>
-    <row r="490" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A490" s="4" t="s">
         <v>44</v>
       </c>
@@ -7608,7 +7615,7 @@
       <c r="D490" s="5"/>
       <c r="E490" s="11"/>
     </row>
-    <row r="491" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A491" s="4" t="s">
         <v>44</v>
       </c>
@@ -7621,7 +7628,7 @@
       <c r="D491" s="5"/>
       <c r="E491" s="11"/>
     </row>
-    <row r="492" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A492" s="4" t="s">
         <v>44</v>
       </c>
@@ -7634,7 +7641,7 @@
       <c r="D492" s="5"/>
       <c r="E492" s="11"/>
     </row>
-    <row r="493" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A493" s="4" t="s">
         <v>44</v>
       </c>
@@ -7647,7 +7654,7 @@
       <c r="D493" s="5"/>
       <c r="E493" s="11"/>
     </row>
-    <row r="494" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A494" s="4" t="s">
         <v>44</v>
       </c>
@@ -7660,7 +7667,7 @@
       <c r="D494" s="5"/>
       <c r="E494" s="11"/>
     </row>
-    <row r="495" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A495" s="4" t="s">
         <v>44</v>
       </c>
@@ -7673,7 +7680,7 @@
       <c r="D495" s="5"/>
       <c r="E495" s="11"/>
     </row>
-    <row r="496" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A496" s="4" t="s">
         <v>44</v>
       </c>
@@ -7686,7 +7693,7 @@
       <c r="D496" s="5"/>
       <c r="E496" s="11"/>
     </row>
-    <row r="497" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A497" s="4" t="s">
         <v>44</v>
       </c>
@@ -7699,7 +7706,7 @@
       <c r="D497" s="5"/>
       <c r="E497" s="11"/>
     </row>
-    <row r="498" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A498" s="4" t="s">
         <v>44</v>
       </c>
@@ -7712,7 +7719,7 @@
       <c r="D498" s="5"/>
       <c r="E498" s="11"/>
     </row>
-    <row r="499" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A499" s="4" t="s">
         <v>44</v>
       </c>
@@ -7725,7 +7732,7 @@
       <c r="D499" s="5"/>
       <c r="E499" s="11"/>
     </row>
-    <row r="500" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A500" s="4" t="s">
         <v>44</v>
       </c>
@@ -7738,7 +7745,7 @@
       <c r="D500" s="5"/>
       <c r="E500" s="11"/>
     </row>
-    <row r="501" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A501" s="4" t="s">
         <v>44</v>
       </c>
@@ -7751,7 +7758,7 @@
       <c r="D501" s="5"/>
       <c r="E501" s="11"/>
     </row>
-    <row r="502" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A502" s="4" t="s">
         <v>44</v>
       </c>
@@ -7764,7 +7771,7 @@
       <c r="D502" s="5"/>
       <c r="E502" s="11"/>
     </row>
-    <row r="503" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A503" s="4" t="s">
         <v>44</v>
       </c>
@@ -7777,7 +7784,7 @@
       <c r="D503" s="5"/>
       <c r="E503" s="11"/>
     </row>
-    <row r="504" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A504" s="4" t="s">
         <v>44</v>
       </c>
@@ -7790,7 +7797,7 @@
       <c r="D504" s="5"/>
       <c r="E504" s="11"/>
     </row>
-    <row r="505" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A505" s="4" t="s">
         <v>44</v>
       </c>
@@ -7803,7 +7810,7 @@
       <c r="D505" s="5"/>
       <c r="E505" s="11"/>
     </row>
-    <row r="506" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A506" s="4" t="s">
         <v>44</v>
       </c>
@@ -7816,7 +7823,7 @@
       <c r="D506" s="5"/>
       <c r="E506" s="11"/>
     </row>
-    <row r="507" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A507" s="4" t="s">
         <v>44</v>
       </c>
@@ -7829,7 +7836,7 @@
       <c r="D507" s="5"/>
       <c r="E507" s="11"/>
     </row>
-    <row r="508" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A508" s="4" t="s">
         <v>44</v>
       </c>
@@ -7842,7 +7849,7 @@
       <c r="D508" s="5"/>
       <c r="E508" s="11"/>
     </row>
-    <row r="509" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A509" s="4" t="s">
         <v>44</v>
       </c>
@@ -7855,7 +7862,7 @@
       <c r="D509" s="5"/>
       <c r="E509" s="11"/>
     </row>
-    <row r="510" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A510" s="4" t="s">
         <v>44</v>
       </c>
@@ -7868,7 +7875,7 @@
       <c r="D510" s="5"/>
       <c r="E510" s="11"/>
     </row>
-    <row r="511" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A511" s="4" t="s">
         <v>44</v>
       </c>
@@ -7881,7 +7888,7 @@
       <c r="D511" s="5"/>
       <c r="E511" s="11"/>
     </row>
-    <row r="512" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A512" s="4" t="s">
         <v>44</v>
       </c>
@@ -7894,7 +7901,7 @@
       <c r="D512" s="5"/>
       <c r="E512" s="11"/>
     </row>
-    <row r="513" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A513" s="4" t="s">
         <v>44</v>
       </c>
@@ -7907,7 +7914,7 @@
       <c r="D513" s="5"/>
       <c r="E513" s="11"/>
     </row>
-    <row r="514" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A514" s="4" t="s">
         <v>44</v>
       </c>
@@ -7920,7 +7927,7 @@
       <c r="D514" s="5"/>
       <c r="E514" s="11"/>
     </row>
-    <row r="515" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A515" s="4" t="s">
         <v>44</v>
       </c>
@@ -7933,7 +7940,7 @@
       <c r="D515" s="5"/>
       <c r="E515" s="11"/>
     </row>
-    <row r="516" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A516" s="4" t="s">
         <v>44</v>
       </c>
@@ -7946,7 +7953,7 @@
       <c r="D516" s="5"/>
       <c r="E516" s="11"/>
     </row>
-    <row r="517" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A517" s="4" t="s">
         <v>44</v>
       </c>
@@ -7959,7 +7966,7 @@
       <c r="D517" s="5"/>
       <c r="E517" s="11"/>
     </row>
-    <row r="518" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A518" s="4" t="s">
         <v>44</v>
       </c>
@@ -7972,7 +7979,7 @@
       <c r="D518" s="5"/>
       <c r="E518" s="11"/>
     </row>
-    <row r="519" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A519" s="4" t="s">
         <v>44</v>
       </c>
@@ -7985,7 +7992,7 @@
       <c r="D519" s="5"/>
       <c r="E519" s="11"/>
     </row>
-    <row r="520" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A520" s="4" t="s">
         <v>44</v>
       </c>
@@ -7998,7 +8005,7 @@
       <c r="D520" s="5"/>
       <c r="E520" s="11"/>
     </row>
-    <row r="521" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A521" s="4" t="s">
         <v>44</v>
       </c>
@@ -8011,7 +8018,7 @@
       <c r="D521" s="5"/>
       <c r="E521" s="11"/>
     </row>
-    <row r="522" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A522" s="4" t="s">
         <v>44</v>
       </c>
@@ -8024,7 +8031,7 @@
       <c r="D522" s="5"/>
       <c r="E522" s="11"/>
     </row>
-    <row r="523" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A523" s="4" t="s">
         <v>44</v>
       </c>
@@ -8037,7 +8044,7 @@
       <c r="D523" s="5"/>
       <c r="E523" s="11"/>
     </row>
-    <row r="524" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A524" s="4" t="s">
         <v>44</v>
       </c>
@@ -8050,7 +8057,7 @@
       <c r="D524" s="5"/>
       <c r="E524" s="11"/>
     </row>
-    <row r="525" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A525" s="4" t="s">
         <v>44</v>
       </c>
@@ -8063,7 +8070,7 @@
       <c r="D525" s="5"/>
       <c r="E525" s="11"/>
     </row>
-    <row r="526" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A526" s="4" t="s">
         <v>44</v>
       </c>
@@ -8076,7 +8083,7 @@
       <c r="D526" s="5"/>
       <c r="E526" s="11"/>
     </row>
-    <row r="527" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A527" s="4" t="s">
         <v>44</v>
       </c>
@@ -8089,7 +8096,7 @@
       <c r="D527" s="5"/>
       <c r="E527" s="11"/>
     </row>
-    <row r="528" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A528" s="4" t="s">
         <v>44</v>
       </c>
@@ -8102,7 +8109,7 @@
       <c r="D528" s="5"/>
       <c r="E528" s="11"/>
     </row>
-    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A529" s="4" t="s">
         <v>44</v>
       </c>
@@ -8115,7 +8122,7 @@
       <c r="D529" s="5"/>
       <c r="E529" s="11"/>
     </row>
-    <row r="530" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A530" s="4" t="s">
         <v>44</v>
       </c>
@@ -8128,7 +8135,7 @@
       <c r="D530" s="5"/>
       <c r="E530" s="11"/>
     </row>
-    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A531" s="4" t="s">
         <v>44</v>
       </c>
@@ -8141,7 +8148,7 @@
       <c r="D531" s="5"/>
       <c r="E531" s="11"/>
     </row>
-    <row r="532" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A532" s="4" t="s">
         <v>44</v>
       </c>
@@ -8154,7 +8161,7 @@
       <c r="D532" s="5"/>
       <c r="E532" s="11"/>
     </row>
-    <row r="533" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A533" s="4" t="s">
         <v>44</v>
       </c>
@@ -8167,7 +8174,7 @@
       <c r="D533" s="5"/>
       <c r="E533" s="11"/>
     </row>
-    <row r="534" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A534" s="4" t="s">
         <v>44</v>
       </c>
@@ -8180,7 +8187,7 @@
       <c r="D534" s="5"/>
       <c r="E534" s="11"/>
     </row>
-    <row r="535" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A535" s="4" t="s">
         <v>44</v>
       </c>
@@ -8193,7 +8200,7 @@
       <c r="D535" s="5"/>
       <c r="E535" s="11"/>
     </row>
-    <row r="536" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A536" s="4" t="s">
         <v>44</v>
       </c>
@@ -8206,7 +8213,7 @@
       <c r="D536" s="5"/>
       <c r="E536" s="11"/>
     </row>
-    <row r="537" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A537" s="4" t="s">
         <v>44</v>
       </c>
@@ -8219,7 +8226,7 @@
       <c r="D537" s="5"/>
       <c r="E537" s="11"/>
     </row>
-    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A538" s="4" t="s">
         <v>44</v>
       </c>
@@ -8232,7 +8239,7 @@
       <c r="D538" s="5"/>
       <c r="E538" s="11"/>
     </row>
-    <row r="539" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A539" s="4" t="s">
         <v>44</v>
       </c>
@@ -8245,7 +8252,7 @@
       <c r="D539" s="5"/>
       <c r="E539" s="11"/>
     </row>
-    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A540" s="4" t="s">
         <v>44</v>
       </c>
@@ -8258,7 +8265,7 @@
       <c r="D540" s="5"/>
       <c r="E540" s="11"/>
     </row>
-    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A541" s="4" t="s">
         <v>44</v>
       </c>
@@ -8271,7 +8278,7 @@
       <c r="D541" s="5"/>
       <c r="E541" s="11"/>
     </row>
-    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A542" s="4" t="s">
         <v>44</v>
       </c>
@@ -8284,7 +8291,7 @@
       <c r="D542" s="5"/>
       <c r="E542" s="11"/>
     </row>
-    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A543" s="4" t="s">
         <v>44</v>
       </c>
@@ -8297,7 +8304,7 @@
       <c r="D543" s="5"/>
       <c r="E543" s="11"/>
     </row>
-    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A544" s="4" t="s">
         <v>44</v>
       </c>
@@ -8310,7 +8317,7 @@
       <c r="D544" s="5"/>
       <c r="E544" s="11"/>
     </row>
-    <row r="545" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A545" s="4" t="s">
         <v>44</v>
       </c>
@@ -8323,7 +8330,7 @@
       <c r="D545" s="5"/>
       <c r="E545" s="11"/>
     </row>
-    <row r="546" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A546" s="4" t="s">
         <v>45</v>
       </c>
@@ -8336,7 +8343,7 @@
       <c r="D546" s="5"/>
       <c r="E546" s="11"/>
     </row>
-    <row r="547" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A547" s="4" t="s">
         <v>45</v>
       </c>
@@ -8349,7 +8356,7 @@
       <c r="D547" s="5"/>
       <c r="E547" s="11"/>
     </row>
-    <row r="548" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A548" s="4" t="s">
         <v>45</v>
       </c>
@@ -8362,7 +8369,7 @@
       <c r="D548" s="5"/>
       <c r="E548" s="11"/>
     </row>
-    <row r="549" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A549" s="4" t="s">
         <v>45</v>
       </c>
@@ -8375,7 +8382,7 @@
       <c r="D549" s="5"/>
       <c r="E549" s="11"/>
     </row>
-    <row r="550" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A550" s="4" t="s">
         <v>45</v>
       </c>
@@ -8388,7 +8395,7 @@
       <c r="D550" s="5"/>
       <c r="E550" s="11"/>
     </row>
-    <row r="551" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A551" s="4" t="s">
         <v>45</v>
       </c>
@@ -8401,7 +8408,7 @@
       <c r="D551" s="5"/>
       <c r="E551" s="11"/>
     </row>
-    <row r="552" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A552" s="4" t="s">
         <v>45</v>
       </c>
@@ -8414,7 +8421,7 @@
       <c r="D552" s="5"/>
       <c r="E552" s="11"/>
     </row>
-    <row r="553" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A553" s="4" t="s">
         <v>45</v>
       </c>
@@ -8427,7 +8434,7 @@
       <c r="D553" s="5"/>
       <c r="E553" s="11"/>
     </row>
-    <row r="554" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A554" s="4" t="s">
         <v>45</v>
       </c>
@@ -8440,7 +8447,7 @@
       <c r="D554" s="5"/>
       <c r="E554" s="11"/>
     </row>
-    <row r="555" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A555" s="4" t="s">
         <v>45</v>
       </c>
@@ -8453,7 +8460,7 @@
       <c r="D555" s="5"/>
       <c r="E555" s="11"/>
     </row>
-    <row r="556" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A556" s="4" t="s">
         <v>45</v>
       </c>
@@ -8466,7 +8473,7 @@
       <c r="D556" s="5"/>
       <c r="E556" s="11"/>
     </row>
-    <row r="557" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A557" s="4" t="s">
         <v>45</v>
       </c>
@@ -8479,7 +8486,7 @@
       <c r="D557" s="5"/>
       <c r="E557" s="11"/>
     </row>
-    <row r="558" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A558" s="4" t="s">
         <v>45</v>
       </c>
@@ -8492,7 +8499,7 @@
       <c r="D558" s="5"/>
       <c r="E558" s="11"/>
     </row>
-    <row r="559" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A559" s="4" t="s">
         <v>45</v>
       </c>
@@ -8505,7 +8512,7 @@
       <c r="D559" s="5"/>
       <c r="E559" s="11"/>
     </row>
-    <row r="560" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A560" s="4" t="s">
         <v>45</v>
       </c>
@@ -8518,7 +8525,7 @@
       <c r="D560" s="5"/>
       <c r="E560" s="11"/>
     </row>
-    <row r="561" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A561" s="4" t="s">
         <v>45</v>
       </c>
@@ -8531,7 +8538,7 @@
       <c r="D561" s="5"/>
       <c r="E561" s="11"/>
     </row>
-    <row r="562" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A562" s="4" t="s">
         <v>45</v>
       </c>
@@ -8544,7 +8551,7 @@
       <c r="D562" s="5"/>
       <c r="E562" s="11"/>
     </row>
-    <row r="563" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A563" s="4" t="s">
         <v>45</v>
       </c>
@@ -8557,7 +8564,7 @@
       <c r="D563" s="5"/>
       <c r="E563" s="11"/>
     </row>
-    <row r="564" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A564" s="4" t="s">
         <v>45</v>
       </c>
@@ -8570,7 +8577,7 @@
       <c r="D564" s="5"/>
       <c r="E564" s="11"/>
     </row>
-    <row r="565" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A565" s="4" t="s">
         <v>45</v>
       </c>
@@ -8583,7 +8590,7 @@
       <c r="D565" s="5"/>
       <c r="E565" s="11"/>
     </row>
-    <row r="566" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A566" s="4" t="s">
         <v>45</v>
       </c>
@@ -8596,7 +8603,7 @@
       <c r="D566" s="5"/>
       <c r="E566" s="11"/>
     </row>
-    <row r="567" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A567" s="4" t="s">
         <v>45</v>
       </c>
@@ -8609,7 +8616,7 @@
       <c r="D567" s="5"/>
       <c r="E567" s="11"/>
     </row>
-    <row r="568" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A568" s="4" t="s">
         <v>45</v>
       </c>
@@ -8622,7 +8629,7 @@
       <c r="D568" s="5"/>
       <c r="E568" s="11"/>
     </row>
-    <row r="569" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A569" s="4" t="s">
         <v>45</v>
       </c>
@@ -8635,7 +8642,7 @@
       <c r="D569" s="5"/>
       <c r="E569" s="11"/>
     </row>
-    <row r="570" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A570" s="4" t="s">
         <v>45</v>
       </c>
@@ -8648,7 +8655,7 @@
       <c r="D570" s="5"/>
       <c r="E570" s="11"/>
     </row>
-    <row r="571" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A571" s="4" t="s">
         <v>45</v>
       </c>
@@ -8661,7 +8668,7 @@
       <c r="D571" s="5"/>
       <c r="E571" s="11"/>
     </row>
-    <row r="572" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A572" s="4" t="s">
         <v>45</v>
       </c>
@@ -8674,7 +8681,7 @@
       <c r="D572" s="5"/>
       <c r="E572" s="11"/>
     </row>
-    <row r="573" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A573" s="4" t="s">
         <v>45</v>
       </c>
@@ -8687,7 +8694,7 @@
       <c r="D573" s="5"/>
       <c r="E573" s="11"/>
     </row>
-    <row r="574" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A574" s="4" t="s">
         <v>45</v>
       </c>
@@ -8700,7 +8707,7 @@
       <c r="D574" s="5"/>
       <c r="E574" s="11"/>
     </row>
-    <row r="575" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A575" s="4" t="s">
         <v>45</v>
       </c>
@@ -8713,7 +8720,7 @@
       <c r="D575" s="5"/>
       <c r="E575" s="11"/>
     </row>
-    <row r="576" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A576" s="4" t="s">
         <v>45</v>
       </c>
@@ -8726,7 +8733,7 @@
       <c r="D576" s="5"/>
       <c r="E576" s="11"/>
     </row>
-    <row r="577" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A577" s="4" t="s">
         <v>45</v>
       </c>
@@ -8739,7 +8746,7 @@
       <c r="D577" s="5"/>
       <c r="E577" s="11"/>
     </row>
-    <row r="578" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A578" s="4" t="s">
         <v>45</v>
       </c>
@@ -8752,7 +8759,7 @@
       <c r="D578" s="5"/>
       <c r="E578" s="11"/>
     </row>
-    <row r="579" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A579" s="4" t="s">
         <v>45</v>
       </c>
@@ -8765,7 +8772,7 @@
       <c r="D579" s="5"/>
       <c r="E579" s="11"/>
     </row>
-    <row r="580" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A580" s="4" t="s">
         <v>45</v>
       </c>
@@ -8778,7 +8785,7 @@
       <c r="D580" s="5"/>
       <c r="E580" s="11"/>
     </row>
-    <row r="581" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A581" s="4" t="s">
         <v>45</v>
       </c>
@@ -8791,7 +8798,7 @@
       <c r="D581" s="5"/>
       <c r="E581" s="11"/>
     </row>
-    <row r="582" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A582" s="4" t="s">
         <v>45</v>
       </c>
@@ -8804,7 +8811,7 @@
       <c r="D582" s="5"/>
       <c r="E582" s="11"/>
     </row>
-    <row r="583" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A583" s="4" t="s">
         <v>45</v>
       </c>
@@ -8817,7 +8824,7 @@
       <c r="D583" s="5"/>
       <c r="E583" s="11"/>
     </row>
-    <row r="584" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A584" s="4" t="s">
         <v>45</v>
       </c>
@@ -8830,7 +8837,7 @@
       <c r="D584" s="5"/>
       <c r="E584" s="11"/>
     </row>
-    <row r="585" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A585" s="4" t="s">
         <v>45</v>
       </c>
@@ -8843,7 +8850,7 @@
       <c r="D585" s="5"/>
       <c r="E585" s="11"/>
     </row>
-    <row r="586" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A586" s="4" t="s">
         <v>45</v>
       </c>
@@ -8856,7 +8863,7 @@
       <c r="D586" s="5"/>
       <c r="E586" s="11"/>
     </row>
-    <row r="587" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A587" s="4" t="s">
         <v>45</v>
       </c>
@@ -8869,7 +8876,7 @@
       <c r="D587" s="5"/>
       <c r="E587" s="11"/>
     </row>
-    <row r="588" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A588" s="4" t="s">
         <v>45</v>
       </c>
@@ -8882,7 +8889,7 @@
       <c r="D588" s="5"/>
       <c r="E588" s="11"/>
     </row>
-    <row r="589" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A589" s="4" t="s">
         <v>45</v>
       </c>
@@ -8895,7 +8902,7 @@
       <c r="D589" s="5"/>
       <c r="E589" s="11"/>
     </row>
-    <row r="590" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A590" s="4" t="s">
         <v>45</v>
       </c>
@@ -8908,7 +8915,7 @@
       <c r="D590" s="5"/>
       <c r="E590" s="11"/>
     </row>
-    <row r="591" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A591" s="4" t="s">
         <v>45</v>
       </c>
@@ -8921,7 +8928,7 @@
       <c r="D591" s="5"/>
       <c r="E591" s="11"/>
     </row>
-    <row r="592" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A592" s="4" t="s">
         <v>45</v>
       </c>
@@ -8934,7 +8941,7 @@
       <c r="D592" s="5"/>
       <c r="E592" s="11"/>
     </row>
-    <row r="593" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A593" s="4" t="s">
         <v>45</v>
       </c>
@@ -8947,7 +8954,7 @@
       <c r="D593" s="5"/>
       <c r="E593" s="11"/>
     </row>
-    <row r="594" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A594" s="4" t="s">
         <v>45</v>
       </c>
@@ -8960,7 +8967,7 @@
       <c r="D594" s="5"/>
       <c r="E594" s="11"/>
     </row>
-    <row r="595" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A595" s="4" t="s">
         <v>45</v>
       </c>
@@ -8973,7 +8980,7 @@
       <c r="D595" s="5"/>
       <c r="E595" s="11"/>
     </row>
-    <row r="596" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A596" s="4" t="s">
         <v>45</v>
       </c>
@@ -8986,7 +8993,7 @@
       <c r="D596" s="5"/>
       <c r="E596" s="11"/>
     </row>
-    <row r="597" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A597" s="4" t="s">
         <v>45</v>
       </c>
@@ -8999,7 +9006,7 @@
       <c r="D597" s="5"/>
       <c r="E597" s="11"/>
     </row>
-    <row r="598" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A598" s="4" t="s">
         <v>45</v>
       </c>
@@ -9012,7 +9019,7 @@
       <c r="D598" s="5"/>
       <c r="E598" s="11"/>
     </row>
-    <row r="599" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A599" s="4" t="s">
         <v>45</v>
       </c>
@@ -9029,7 +9036,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="600" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A600" s="4" t="s">
         <v>45</v>
       </c>
@@ -9042,7 +9049,7 @@
       <c r="D600" s="5"/>
       <c r="E600" s="11"/>
     </row>
-    <row r="601" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A601" s="4" t="s">
         <v>45</v>
       </c>
@@ -9055,7 +9062,7 @@
       <c r="D601" s="5"/>
       <c r="E601" s="11"/>
     </row>
-    <row r="602" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A602" s="4" t="s">
         <v>45</v>
       </c>
@@ -9068,7 +9075,7 @@
       <c r="D602" s="5"/>
       <c r="E602" s="11"/>
     </row>
-    <row r="603" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A603" s="4" t="s">
         <v>45</v>
       </c>
@@ -9081,7 +9088,7 @@
       <c r="D603" s="5"/>
       <c r="E603" s="11"/>
     </row>
-    <row r="604" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A604" s="4" t="s">
         <v>45</v>
       </c>
@@ -9094,7 +9101,7 @@
       <c r="D604" s="5"/>
       <c r="E604" s="11"/>
     </row>
-    <row r="605" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A605" s="4" t="s">
         <v>45</v>
       </c>
@@ -9107,7 +9114,7 @@
       <c r="D605" s="5"/>
       <c r="E605" s="11"/>
     </row>
-    <row r="606" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A606" s="4" t="s">
         <v>45</v>
       </c>
@@ -9120,7 +9127,7 @@
       <c r="D606" s="5"/>
       <c r="E606" s="11"/>
     </row>
-    <row r="607" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A607" s="4" t="s">
         <v>45</v>
       </c>
@@ -9133,7 +9140,7 @@
       <c r="D607" s="5"/>
       <c r="E607" s="11"/>
     </row>
-    <row r="608" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A608" s="4" t="s">
         <v>45</v>
       </c>
@@ -9146,7 +9153,7 @@
       <c r="D608" s="5"/>
       <c r="E608" s="11"/>
     </row>
-    <row r="609" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A609" s="4" t="s">
         <v>45</v>
       </c>
@@ -9159,7 +9166,7 @@
       <c r="D609" s="5"/>
       <c r="E609" s="11"/>
     </row>
-    <row r="610" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A610" s="4" t="s">
         <v>45</v>
       </c>
@@ -9172,7 +9179,7 @@
       <c r="D610" s="5"/>
       <c r="E610" s="11"/>
     </row>
-    <row r="611" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A611" s="4" t="s">
         <v>45</v>
       </c>
@@ -9185,7 +9192,7 @@
       <c r="D611" s="5"/>
       <c r="E611" s="11"/>
     </row>
-    <row r="612" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A612" s="4" t="s">
         <v>45</v>
       </c>
@@ -9198,7 +9205,7 @@
       <c r="D612" s="5"/>
       <c r="E612" s="11"/>
     </row>
-    <row r="613" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A613" s="4" t="s">
         <v>45</v>
       </c>
@@ -9211,7 +9218,7 @@
       <c r="D613" s="5"/>
       <c r="E613" s="11"/>
     </row>
-    <row r="614" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A614" s="4" t="s">
         <v>45</v>
       </c>
@@ -9224,7 +9231,7 @@
       <c r="D614" s="5"/>
       <c r="E614" s="11"/>
     </row>
-    <row r="615" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A615" s="4" t="s">
         <v>45</v>
       </c>
@@ -9237,7 +9244,7 @@
       <c r="D615" s="5"/>
       <c r="E615" s="11"/>
     </row>
-    <row r="616" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A616" s="4" t="s">
         <v>45</v>
       </c>
@@ -9250,7 +9257,7 @@
       <c r="D616" s="5"/>
       <c r="E616" s="11"/>
     </row>
-    <row r="617" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A617" s="4" t="s">
         <v>45</v>
       </c>
@@ -9263,7 +9270,7 @@
       <c r="D617" s="5"/>
       <c r="E617" s="11"/>
     </row>
-    <row r="618" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A618" s="4" t="s">
         <v>45</v>
       </c>
@@ -9276,7 +9283,7 @@
       <c r="D618" s="5"/>
       <c r="E618" s="11"/>
     </row>
-    <row r="619" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A619" s="4" t="s">
         <v>45</v>
       </c>
@@ -9289,7 +9296,7 @@
       <c r="D619" s="5"/>
       <c r="E619" s="11"/>
     </row>
-    <row r="620" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A620" s="4" t="s">
         <v>45</v>
       </c>
@@ -9302,7 +9309,7 @@
       <c r="D620" s="5"/>
       <c r="E620" s="11"/>
     </row>
-    <row r="621" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A621" s="4" t="s">
         <v>45</v>
       </c>
@@ -9315,7 +9322,7 @@
       <c r="D621" s="5"/>
       <c r="E621" s="11"/>
     </row>
-    <row r="622" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A622" s="4" t="s">
         <v>45</v>
       </c>
@@ -9328,7 +9335,7 @@
       <c r="D622" s="5"/>
       <c r="E622" s="11"/>
     </row>
-    <row r="623" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A623" s="4" t="s">
         <v>45</v>
       </c>
@@ -9341,7 +9348,7 @@
       <c r="D623" s="5"/>
       <c r="E623" s="11"/>
     </row>
-    <row r="624" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A624" s="4" t="s">
         <v>45</v>
       </c>
@@ -9354,7 +9361,7 @@
       <c r="D624" s="5"/>
       <c r="E624" s="11"/>
     </row>
-    <row r="625" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A625" s="4" t="s">
         <v>45</v>
       </c>
@@ -9367,7 +9374,7 @@
       <c r="D625" s="5"/>
       <c r="E625" s="11"/>
     </row>
-    <row r="626" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A626" s="4" t="s">
         <v>45</v>
       </c>
@@ -9380,7 +9387,7 @@
       <c r="D626" s="5"/>
       <c r="E626" s="11"/>
     </row>
-    <row r="627" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A627" s="4" t="s">
         <v>45</v>
       </c>
@@ -9393,7 +9400,7 @@
       <c r="D627" s="5"/>
       <c r="E627" s="11"/>
     </row>
-    <row r="628" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A628" s="4" t="s">
         <v>45</v>
       </c>
@@ -9406,7 +9413,7 @@
       <c r="D628" s="5"/>
       <c r="E628" s="11"/>
     </row>
-    <row r="629" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A629" s="4" t="s">
         <v>45</v>
       </c>
@@ -9419,7 +9426,7 @@
       <c r="D629" s="5"/>
       <c r="E629" s="11"/>
     </row>
-    <row r="630" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A630" s="4" t="s">
         <v>45</v>
       </c>
@@ -9432,7 +9439,7 @@
       <c r="D630" s="5"/>
       <c r="E630" s="11"/>
     </row>
-    <row r="631" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A631" s="4" t="s">
         <v>45</v>
       </c>
@@ -9445,7 +9452,7 @@
       <c r="D631" s="5"/>
       <c r="E631" s="11"/>
     </row>
-    <row r="632" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A632" s="4" t="s">
         <v>45</v>
       </c>
@@ -9458,7 +9465,7 @@
       <c r="D632" s="5"/>
       <c r="E632" s="11"/>
     </row>
-    <row r="633" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A633" s="4" t="s">
         <v>45</v>
       </c>
@@ -9471,7 +9478,7 @@
       <c r="D633" s="5"/>
       <c r="E633" s="11"/>
     </row>
-    <row r="634" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A634" s="4" t="s">
         <v>45</v>
       </c>
@@ -9484,7 +9491,7 @@
       <c r="D634" s="5"/>
       <c r="E634" s="11"/>
     </row>
-    <row r="635" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A635" s="4" t="s">
         <v>45</v>
       </c>
@@ -9497,7 +9504,7 @@
       <c r="D635" s="5"/>
       <c r="E635" s="11"/>
     </row>
-    <row r="636" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A636" s="4" t="s">
         <v>45</v>
       </c>
@@ -9510,7 +9517,7 @@
       <c r="D636" s="5"/>
       <c r="E636" s="11"/>
     </row>
-    <row r="637" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A637" s="4" t="s">
         <v>45</v>
       </c>
@@ -9523,7 +9530,7 @@
       <c r="D637" s="5"/>
       <c r="E637" s="11"/>
     </row>
-    <row r="638" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A638" s="4" t="s">
         <v>45</v>
       </c>
@@ -9536,7 +9543,7 @@
       <c r="D638" s="5"/>
       <c r="E638" s="11"/>
     </row>
-    <row r="639" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A639" s="4" t="s">
         <v>45</v>
       </c>
@@ -9549,7 +9556,7 @@
       <c r="D639" s="5"/>
       <c r="E639" s="11"/>
     </row>
-    <row r="640" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A640" s="4" t="s">
         <v>45</v>
       </c>
@@ -9562,7 +9569,7 @@
       <c r="D640" s="5"/>
       <c r="E640" s="11"/>
     </row>
-    <row r="641" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A641" s="4" t="s">
         <v>45</v>
       </c>
@@ -9575,7 +9582,7 @@
       <c r="D641" s="5"/>
       <c r="E641" s="11"/>
     </row>
-    <row r="642" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A642" s="4" t="s">
         <v>45</v>
       </c>
@@ -9588,7 +9595,7 @@
       <c r="D642" s="5"/>
       <c r="E642" s="11"/>
     </row>
-    <row r="643" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A643" s="4" t="s">
         <v>45</v>
       </c>
@@ -9601,7 +9608,7 @@
       <c r="D643" s="5"/>
       <c r="E643" s="11"/>
     </row>
-    <row r="644" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A644" s="4" t="s">
         <v>45</v>
       </c>
@@ -9614,7 +9621,7 @@
       <c r="D644" s="5"/>
       <c r="E644" s="11"/>
     </row>
-    <row r="645" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A645" s="4" t="s">
         <v>45</v>
       </c>
@@ -9627,7 +9634,7 @@
       <c r="D645" s="5"/>
       <c r="E645" s="11"/>
     </row>
-    <row r="646" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A646" s="4" t="s">
         <v>45</v>
       </c>
@@ -9640,7 +9647,7 @@
       <c r="D646" s="5"/>
       <c r="E646" s="11"/>
     </row>
-    <row r="647" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A647" s="4" t="s">
         <v>45</v>
       </c>
@@ -9653,7 +9660,7 @@
       <c r="D647" s="5"/>
       <c r="E647" s="11"/>
     </row>
-    <row r="648" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A648" s="4" t="s">
         <v>45</v>
       </c>
@@ -9666,7 +9673,7 @@
       <c r="D648" s="5"/>
       <c r="E648" s="11"/>
     </row>
-    <row r="649" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A649" s="4" t="s">
         <v>45</v>
       </c>
@@ -9679,7 +9686,7 @@
       <c r="D649" s="5"/>
       <c r="E649" s="11"/>
     </row>
-    <row r="650" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A650" s="4" t="s">
         <v>45</v>
       </c>
@@ -9692,7 +9699,7 @@
       <c r="D650" s="5"/>
       <c r="E650" s="11"/>
     </row>
-    <row r="651" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A651" s="4" t="s">
         <v>45</v>
       </c>
@@ -9705,7 +9712,7 @@
       <c r="D651" s="5"/>
       <c r="E651" s="11"/>
     </row>
-    <row r="652" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A652" s="4" t="s">
         <v>45</v>
       </c>
@@ -9718,7 +9725,7 @@
       <c r="D652" s="5"/>
       <c r="E652" s="11"/>
     </row>
-    <row r="653" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A653" s="4" t="s">
         <v>45</v>
       </c>
@@ -9731,7 +9738,7 @@
       <c r="D653" s="5"/>
       <c r="E653" s="11"/>
     </row>
-    <row r="654" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A654" s="4" t="s">
         <v>45</v>
       </c>
@@ -9744,7 +9751,7 @@
       <c r="D654" s="5"/>
       <c r="E654" s="11"/>
     </row>
-    <row r="655" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A655" s="4" t="s">
         <v>45</v>
       </c>
@@ -9757,7 +9764,7 @@
       <c r="D655" s="5"/>
       <c r="E655" s="11"/>
     </row>
-    <row r="656" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A656" s="4" t="s">
         <v>45</v>
       </c>
@@ -9770,7 +9777,7 @@
       <c r="D656" s="5"/>
       <c r="E656" s="11"/>
     </row>
-    <row r="657" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A657" s="4" t="s">
         <v>45</v>
       </c>
@@ -9783,7 +9790,7 @@
       <c r="D657" s="5"/>
       <c r="E657" s="11"/>
     </row>
-    <row r="658" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A658" s="4" t="s">
         <v>45</v>
       </c>
@@ -9796,7 +9803,7 @@
       <c r="D658" s="5"/>
       <c r="E658" s="11"/>
     </row>
-    <row r="659" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A659" s="4" t="s">
         <v>45</v>
       </c>
@@ -9809,7 +9816,7 @@
       <c r="D659" s="5"/>
       <c r="E659" s="11"/>
     </row>
-    <row r="660" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A660" s="4" t="s">
         <v>45</v>
       </c>
@@ -9822,7 +9829,7 @@
       <c r="D660" s="5"/>
       <c r="E660" s="11"/>
     </row>
-    <row r="661" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A661" s="4" t="s">
         <v>45</v>
       </c>
@@ -9835,7 +9842,7 @@
       <c r="D661" s="5"/>
       <c r="E661" s="11"/>
     </row>
-    <row r="662" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A662" s="4" t="s">
         <v>45</v>
       </c>
@@ -9848,7 +9855,7 @@
       <c r="D662" s="5"/>
       <c r="E662" s="11"/>
     </row>
-    <row r="663" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A663" s="4" t="s">
         <v>45</v>
       </c>
@@ -9861,7 +9868,7 @@
       <c r="D663" s="5"/>
       <c r="E663" s="11"/>
     </row>
-    <row r="664" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A664" s="4" t="s">
         <v>45</v>
       </c>
@@ -9874,7 +9881,7 @@
       <c r="D664" s="5"/>
       <c r="E664" s="11"/>
     </row>
-    <row r="665" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A665" s="4" t="s">
         <v>45</v>
       </c>
@@ -9887,7 +9894,7 @@
       <c r="D665" s="5"/>
       <c r="E665" s="11"/>
     </row>
-    <row r="666" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A666" s="4" t="s">
         <v>46</v>
       </c>
@@ -9900,7 +9907,7 @@
       <c r="D666" s="5"/>
       <c r="E666" s="11"/>
     </row>
-    <row r="667" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A667" s="4" t="s">
         <v>46</v>
       </c>
@@ -9913,7 +9920,7 @@
       <c r="D667" s="5"/>
       <c r="E667" s="11"/>
     </row>
-    <row r="668" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A668" s="4" t="s">
         <v>46</v>
       </c>
@@ -9926,7 +9933,7 @@
       <c r="D668" s="5"/>
       <c r="E668" s="11"/>
     </row>
-    <row r="669" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A669" s="4" t="s">
         <v>46</v>
       </c>
@@ -9939,7 +9946,7 @@
       <c r="D669" s="5"/>
       <c r="E669" s="11"/>
     </row>
-    <row r="670" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A670" s="4" t="s">
         <v>46</v>
       </c>
@@ -9952,7 +9959,7 @@
       <c r="D670" s="5"/>
       <c r="E670" s="11"/>
     </row>
-    <row r="671" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A671" s="4" t="s">
         <v>46</v>
       </c>
@@ -9965,7 +9972,7 @@
       <c r="D671" s="5"/>
       <c r="E671" s="11"/>
     </row>
-    <row r="672" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A672" s="4" t="s">
         <v>46</v>
       </c>
@@ -9978,7 +9985,7 @@
       <c r="D672" s="5"/>
       <c r="E672" s="11"/>
     </row>
-    <row r="673" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A673" s="4" t="s">
         <v>46</v>
       </c>
@@ -9991,7 +9998,7 @@
       <c r="D673" s="5"/>
       <c r="E673" s="11"/>
     </row>
-    <row r="674" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A674" s="4" t="s">
         <v>46</v>
       </c>
@@ -10004,7 +10011,7 @@
       <c r="D674" s="5"/>
       <c r="E674" s="11"/>
     </row>
-    <row r="675" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A675" s="4" t="s">
         <v>46</v>
       </c>
@@ -10017,7 +10024,7 @@
       <c r="D675" s="5"/>
       <c r="E675" s="11"/>
     </row>
-    <row r="676" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A676" s="4" t="s">
         <v>46</v>
       </c>
@@ -10030,7 +10037,7 @@
       <c r="D676" s="5"/>
       <c r="E676" s="11"/>
     </row>
-    <row r="677" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A677" s="4" t="s">
         <v>46</v>
       </c>
@@ -10043,7 +10050,7 @@
       <c r="D677" s="5"/>
       <c r="E677" s="11"/>
     </row>
-    <row r="678" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A678" s="4" t="s">
         <v>46</v>
       </c>
@@ -10056,7 +10063,7 @@
       <c r="D678" s="5"/>
       <c r="E678" s="11"/>
     </row>
-    <row r="679" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A679" s="4" t="s">
         <v>46</v>
       </c>
@@ -10069,7 +10076,7 @@
       <c r="D679" s="5"/>
       <c r="E679" s="11"/>
     </row>
-    <row r="680" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A680" s="4" t="s">
         <v>46</v>
       </c>
@@ -10082,7 +10089,7 @@
       <c r="D680" s="5"/>
       <c r="E680" s="11"/>
     </row>
-    <row r="681" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A681" s="4" t="s">
         <v>46</v>
       </c>
@@ -10095,7 +10102,7 @@
       <c r="D681" s="5"/>
       <c r="E681" s="11"/>
     </row>
-    <row r="682" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A682" s="4" t="s">
         <v>46</v>
       </c>
@@ -10108,7 +10115,7 @@
       <c r="D682" s="5"/>
       <c r="E682" s="11"/>
     </row>
-    <row r="683" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A683" s="4" t="s">
         <v>46</v>
       </c>
@@ -10121,7 +10128,7 @@
       <c r="D683" s="5"/>
       <c r="E683" s="11"/>
     </row>
-    <row r="684" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A684" s="4" t="s">
         <v>46</v>
       </c>
@@ -10134,7 +10141,7 @@
       <c r="D684" s="5"/>
       <c r="E684" s="11"/>
     </row>
-    <row r="685" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A685" s="4" t="s">
         <v>46</v>
       </c>
@@ -10147,7 +10154,7 @@
       <c r="D685" s="5"/>
       <c r="E685" s="11"/>
     </row>
-    <row r="686" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A686" s="4" t="s">
         <v>46</v>
       </c>
@@ -10160,7 +10167,7 @@
       <c r="D686" s="5"/>
       <c r="E686" s="11"/>
     </row>
-    <row r="687" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A687" s="4" t="s">
         <v>46</v>
       </c>
@@ -10173,7 +10180,7 @@
       <c r="D687" s="5"/>
       <c r="E687" s="11"/>
     </row>
-    <row r="688" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A688" s="4" t="s">
         <v>46</v>
       </c>
@@ -10186,7 +10193,7 @@
       <c r="D688" s="5"/>
       <c r="E688" s="11"/>
     </row>
-    <row r="689" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A689" s="4" t="s">
         <v>46</v>
       </c>
@@ -10199,7 +10206,7 @@
       <c r="D689" s="5"/>
       <c r="E689" s="11"/>
     </row>
-    <row r="690" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A690" s="4" t="s">
         <v>46</v>
       </c>
@@ -10212,7 +10219,7 @@
       <c r="D690" s="5"/>
       <c r="E690" s="11"/>
     </row>
-    <row r="691" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A691" s="4" t="s">
         <v>46</v>
       </c>
@@ -10225,7 +10232,7 @@
       <c r="D691" s="5"/>
       <c r="E691" s="11"/>
     </row>
-    <row r="692" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A692" s="4" t="s">
         <v>46</v>
       </c>
@@ -10238,7 +10245,7 @@
       <c r="D692" s="5"/>
       <c r="E692" s="11"/>
     </row>
-    <row r="693" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A693" s="4" t="s">
         <v>46</v>
       </c>
@@ -10251,7 +10258,7 @@
       <c r="D693" s="5"/>
       <c r="E693" s="11"/>
     </row>
-    <row r="694" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A694" s="4" t="s">
         <v>46</v>
       </c>
@@ -10264,7 +10271,7 @@
       <c r="D694" s="5"/>
       <c r="E694" s="11"/>
     </row>
-    <row r="695" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A695" s="4" t="s">
         <v>46</v>
       </c>
@@ -10277,7 +10284,7 @@
       <c r="D695" s="5"/>
       <c r="E695" s="11"/>
     </row>
-    <row r="696" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A696" s="4" t="s">
         <v>46</v>
       </c>
@@ -10290,7 +10297,7 @@
       <c r="D696" s="5"/>
       <c r="E696" s="11"/>
     </row>
-    <row r="697" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A697" s="4" t="s">
         <v>46</v>
       </c>
@@ -10303,7 +10310,7 @@
       <c r="D697" s="5"/>
       <c r="E697" s="11"/>
     </row>
-    <row r="698" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A698" s="4" t="s">
         <v>46</v>
       </c>
@@ -10316,7 +10323,7 @@
       <c r="D698" s="5"/>
       <c r="E698" s="11"/>
     </row>
-    <row r="699" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A699" s="4" t="s">
         <v>46</v>
       </c>
@@ -10329,7 +10336,7 @@
       <c r="D699" s="5"/>
       <c r="E699" s="11"/>
     </row>
-    <row r="700" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A700" s="4" t="s">
         <v>46</v>
       </c>
@@ -10342,7 +10349,7 @@
       <c r="D700" s="5"/>
       <c r="E700" s="11"/>
     </row>
-    <row r="701" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A701" s="4" t="s">
         <v>46</v>
       </c>
@@ -10355,7 +10362,7 @@
       <c r="D701" s="5"/>
       <c r="E701" s="11"/>
     </row>
-    <row r="702" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A702" s="4" t="s">
         <v>46</v>
       </c>
@@ -10368,7 +10375,7 @@
       <c r="D702" s="5"/>
       <c r="E702" s="11"/>
     </row>
-    <row r="703" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A703" s="4" t="s">
         <v>46</v>
       </c>
@@ -10381,7 +10388,7 @@
       <c r="D703" s="5"/>
       <c r="E703" s="11"/>
     </row>
-    <row r="704" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A704" s="4" t="s">
         <v>46</v>
       </c>
@@ -10394,7 +10401,7 @@
       <c r="D704" s="5"/>
       <c r="E704" s="11"/>
     </row>
-    <row r="705" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A705" s="4" t="s">
         <v>46</v>
       </c>
@@ -10407,7 +10414,7 @@
       <c r="D705" s="5"/>
       <c r="E705" s="11"/>
     </row>
-    <row r="706" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A706" s="4" t="s">
         <v>46</v>
       </c>
@@ -10420,7 +10427,7 @@
       <c r="D706" s="5"/>
       <c r="E706" s="11"/>
     </row>
-    <row r="707" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A707" s="4" t="s">
         <v>46</v>
       </c>
@@ -10433,7 +10440,7 @@
       <c r="D707" s="5"/>
       <c r="E707" s="11"/>
     </row>
-    <row r="708" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A708" s="4" t="s">
         <v>46</v>
       </c>
@@ -10446,7 +10453,7 @@
       <c r="D708" s="5"/>
       <c r="E708" s="11"/>
     </row>
-    <row r="709" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A709" s="4" t="s">
         <v>46</v>
       </c>
@@ -10459,7 +10466,7 @@
       <c r="D709" s="5"/>
       <c r="E709" s="11"/>
     </row>
-    <row r="710" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A710" s="4" t="s">
         <v>46</v>
       </c>
@@ -10472,7 +10479,7 @@
       <c r="D710" s="5"/>
       <c r="E710" s="11"/>
     </row>
-    <row r="711" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A711" s="4" t="s">
         <v>46</v>
       </c>
@@ -10485,7 +10492,7 @@
       <c r="D711" s="5"/>
       <c r="E711" s="11"/>
     </row>
-    <row r="712" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A712" s="4" t="s">
         <v>46</v>
       </c>
@@ -10498,7 +10505,7 @@
       <c r="D712" s="5"/>
       <c r="E712" s="11"/>
     </row>
-    <row r="713" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A713" s="4" t="s">
         <v>46</v>
       </c>
@@ -10511,7 +10518,7 @@
       <c r="D713" s="5"/>
       <c r="E713" s="11"/>
     </row>
-    <row r="714" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A714" s="4" t="s">
         <v>46</v>
       </c>
@@ -10524,7 +10531,7 @@
       <c r="D714" s="5"/>
       <c r="E714" s="11"/>
     </row>
-    <row r="715" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A715" s="4" t="s">
         <v>46</v>
       </c>
@@ -10537,7 +10544,7 @@
       <c r="D715" s="5"/>
       <c r="E715" s="11"/>
     </row>
-    <row r="716" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A716" s="4" t="s">
         <v>46</v>
       </c>
@@ -10550,7 +10557,7 @@
       <c r="D716" s="5"/>
       <c r="E716" s="11"/>
     </row>
-    <row r="717" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A717" s="4" t="s">
         <v>46</v>
       </c>
@@ -10563,7 +10570,7 @@
       <c r="D717" s="5"/>
       <c r="E717" s="11"/>
     </row>
-    <row r="718" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A718" s="4" t="s">
         <v>46</v>
       </c>
@@ -10576,7 +10583,7 @@
       <c r="D718" s="5"/>
       <c r="E718" s="11"/>
     </row>
-    <row r="719" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A719" s="4" t="s">
         <v>46</v>
       </c>
@@ -10589,7 +10596,7 @@
       <c r="D719" s="5"/>
       <c r="E719" s="11"/>
     </row>
-    <row r="720" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A720" s="4" t="s">
         <v>46</v>
       </c>
@@ -10602,7 +10609,7 @@
       <c r="D720" s="5"/>
       <c r="E720" s="11"/>
     </row>
-    <row r="721" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A721" s="4" t="s">
         <v>46</v>
       </c>
@@ -10615,7 +10622,7 @@
       <c r="D721" s="5"/>
       <c r="E721" s="11"/>
     </row>
-    <row r="722" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A722" s="4" t="s">
         <v>46</v>
       </c>
@@ -10628,7 +10635,7 @@
       <c r="D722" s="5"/>
       <c r="E722" s="11"/>
     </row>
-    <row r="723" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A723" s="4" t="s">
         <v>46</v>
       </c>
@@ -10641,7 +10648,7 @@
       <c r="D723" s="5"/>
       <c r="E723" s="11"/>
     </row>
-    <row r="724" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A724" s="4" t="s">
         <v>46</v>
       </c>
@@ -10654,7 +10661,7 @@
       <c r="D724" s="5"/>
       <c r="E724" s="11"/>
     </row>
-    <row r="725" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A725" s="4" t="s">
         <v>46</v>
       </c>
@@ -10667,7 +10674,7 @@
       <c r="D725" s="5"/>
       <c r="E725" s="11"/>
     </row>
-    <row r="726" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A726" s="4" t="s">
         <v>43</v>
       </c>
@@ -10681,7 +10688,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A727" s="4" t="s">
         <v>43</v>
       </c>
@@ -10695,7 +10702,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A728" s="4" t="s">
         <v>43</v>
       </c>
@@ -10728,7 +10735,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
         <v>43</v>
       </c>
@@ -10745,7 +10752,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
         <v>43</v>
       </c>
@@ -10762,7 +10769,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
         <v>43</v>
       </c>
@@ -10777,6 +10784,23 @@
       </c>
       <c r="E733" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="734" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A734" t="s">
+        <v>43</v>
+      </c>
+      <c r="B734">
+        <v>6</v>
+      </c>
+      <c r="C734">
+        <v>50</v>
+      </c>
+      <c r="D734" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E734" s="13" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -10792,13 +10816,13 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A733</xm:sqref>
+          <xm:sqref>A2:A734</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B733</xm:sqref>
+          <xm:sqref>B2:B734</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD27420-E4BD-4842-B931-4B3AA9B21682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB24385-780D-4977-BB8A-91BB2965824E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="138">
   <si>
     <t>Категорија</t>
   </si>
@@ -511,6 +511,9 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycby6jZE_5BhVqFEn4Psk8zfgm4ir44KQEJdUJ61qit1hYUOr8v_SwDiPGUnE-EaM7yxu/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbxGMT3stdrIkH5gpO7Mez_36YFqvdwHExLRYfjsFUHAsTgYrVpJyCUCDtcULo24x-v2GQ/exec</t>
   </si>
 </sst>
 </file>
@@ -704,8 +707,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E734">
-  <autoFilter ref="A1:E734" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E735">
+  <autoFilter ref="A1:E735" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
         <filter val="Алгебра"/>
@@ -1016,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E734"/>
+  <dimension ref="A1:E735"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -10799,8 +10802,25 @@
       <c r="D734" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E734" s="13" t="s">
+      <c r="E734" t="s">
         <v>136</v>
+      </c>
+    </row>
+    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A735" t="s">
+        <v>43</v>
+      </c>
+      <c r="B735">
+        <v>6</v>
+      </c>
+      <c r="C735">
+        <v>53</v>
+      </c>
+      <c r="D735" t="s">
+        <v>114</v>
+      </c>
+      <c r="E735" s="13" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -10816,13 +10836,13 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A734</xm:sqref>
+          <xm:sqref>A2:A735</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B734</xm:sqref>
+          <xm:sqref>B2:B735</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB24385-780D-4977-BB8A-91BB2965824E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D810CCB-6673-46F6-8C72-C0EF653E6963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="139">
   <si>
     <t>Категорија</t>
   </si>
@@ -514,6 +514,9 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbxGMT3stdrIkH5gpO7Mez_36YFqvdwHExLRYfjsFUHAsTgYrVpJyCUCDtcULo24x-v2GQ/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbwi-rZBkvBqZujk0V4gj-hiwi2xSjF2-tc6Khkjk6MVIvGif3gn5ulvMQ35VjiTknoI/exec</t>
   </si>
 </sst>
 </file>
@@ -707,8 +710,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E735">
-  <autoFilter ref="A1:E735" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LessonsTable" displayName="LessonsTable" ref="A1:E736">
+  <autoFilter ref="A1:E736" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
         <filter val="Алгебра"/>
@@ -1019,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E735"/>
+  <dimension ref="A1:E736"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -10819,8 +10822,25 @@
       <c r="D735" t="s">
         <v>114</v>
       </c>
-      <c r="E735" s="13" t="s">
+      <c r="E735" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A736" t="s">
+        <v>43</v>
+      </c>
+      <c r="B736">
+        <v>6</v>
+      </c>
+      <c r="C736">
+        <v>54</v>
+      </c>
+      <c r="D736" t="s">
+        <v>114</v>
+      </c>
+      <c r="E736" s="13" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -10836,13 +10856,13 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A735</xm:sqref>
+          <xm:sqref>A2:A736</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B735</xm:sqref>
+          <xm:sqref>B2:B736</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D810CCB-6673-46F6-8C72-C0EF653E6963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D954B2-1E99-4E3B-BDA0-F54BEC4132B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="141">
   <si>
     <t>Категорија</t>
   </si>
@@ -517,6 +517,12 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbwi-rZBkvBqZujk0V4gj-hiwi2xSjF2-tc6Khkjk6MVIvGif3gn5ulvMQ35VjiTknoI/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbxknEwpRmQGeJzUVya0v-SqOOaZ_ogFEKGc67sTKV3TeshwuGi3m3gnvRLeM2_V4aAesA/exec</t>
+  </si>
+  <si>
+    <t>Геометриски трансформации</t>
   </si>
 </sst>
 </file>
@@ -651,7 +657,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -687,7 +693,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -714,12 +719,12 @@
   <autoFilter ref="A1:E736" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Алгебра"/>
+        <filter val="Геометрија"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="6"/>
+        <filter val="8"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1031,7 +1036,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1048,7 +1053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>43</v>
       </c>
@@ -1065,7 +1070,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>43</v>
       </c>
@@ -1080,7 +1085,7 @@
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
@@ -1095,7 +1100,7 @@
       </c>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>43</v>
       </c>
@@ -1110,7 +1115,7 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>43</v>
       </c>
@@ -1125,7 +1130,7 @@
       </c>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>43</v>
       </c>
@@ -1140,7 +1145,7 @@
       </c>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>43</v>
       </c>
@@ -1155,7 +1160,7 @@
       </c>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>43</v>
       </c>
@@ -1170,7 +1175,7 @@
       </c>
       <c r="E9" s="11"/>
     </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>43</v>
       </c>
@@ -1185,7 +1190,7 @@
       </c>
       <c r="E10" s="11"/>
     </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>43</v>
       </c>
@@ -1200,7 +1205,7 @@
       </c>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>43</v>
       </c>
@@ -1215,7 +1220,7 @@
       </c>
       <c r="E12" s="11"/>
     </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>43</v>
       </c>
@@ -1230,7 +1235,7 @@
       </c>
       <c r="E13" s="11"/>
     </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>43</v>
       </c>
@@ -1245,7 +1250,7 @@
       </c>
       <c r="E14" s="11"/>
     </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>43</v>
       </c>
@@ -1260,7 +1265,7 @@
       </c>
       <c r="E15" s="11"/>
     </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>43</v>
       </c>
@@ -1275,7 +1280,7 @@
       </c>
       <c r="E16" s="11"/>
     </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>43</v>
       </c>
@@ -1290,7 +1295,7 @@
       </c>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>43</v>
       </c>
@@ -1305,7 +1310,7 @@
       </c>
       <c r="E18" s="11"/>
     </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>43</v>
       </c>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="E19" s="11"/>
     </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
@@ -1335,7 +1340,7 @@
       </c>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>43</v>
       </c>
@@ -1350,7 +1355,7 @@
       </c>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>43</v>
       </c>
@@ -1365,7 +1370,7 @@
       </c>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>43</v>
       </c>
@@ -1380,7 +1385,7 @@
       </c>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>43</v>
       </c>
@@ -1395,7 +1400,7 @@
       </c>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>43</v>
       </c>
@@ -1410,7 +1415,7 @@
       </c>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>43</v>
       </c>
@@ -1425,7 +1430,7 @@
       </c>
       <c r="E26" s="11"/>
     </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>43</v>
       </c>
@@ -1440,7 +1445,7 @@
       </c>
       <c r="E27" s="11"/>
     </row>
-    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>43</v>
       </c>
@@ -1455,7 +1460,7 @@
       </c>
       <c r="E28" s="11"/>
     </row>
-    <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>43</v>
       </c>
@@ -1470,7 +1475,7 @@
       </c>
       <c r="E29" s="11"/>
     </row>
-    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>43</v>
       </c>
@@ -1485,7 +1490,7 @@
       </c>
       <c r="E30" s="11"/>
     </row>
-    <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>43</v>
       </c>
@@ -1500,7 +1505,7 @@
       </c>
       <c r="E31" s="11"/>
     </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>43</v>
       </c>
@@ -1515,7 +1520,7 @@
       </c>
       <c r="E32" s="11"/>
     </row>
-    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>43</v>
       </c>
@@ -1530,7 +1535,7 @@
       </c>
       <c r="E33" s="11"/>
     </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>43</v>
       </c>
@@ -1545,7 +1550,7 @@
       </c>
       <c r="E34" s="11"/>
     </row>
-    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>43</v>
       </c>
@@ -1560,7 +1565,7 @@
       </c>
       <c r="E35" s="11"/>
     </row>
-    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>43</v>
       </c>
@@ -1575,7 +1580,7 @@
       </c>
       <c r="E36" s="11"/>
     </row>
-    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>43</v>
       </c>
@@ -1590,7 +1595,7 @@
       </c>
       <c r="E37" s="11"/>
     </row>
-    <row r="38" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>43</v>
       </c>
@@ -1605,7 +1610,7 @@
       </c>
       <c r="E38" s="11"/>
     </row>
-    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>43</v>
       </c>
@@ -1620,7 +1625,7 @@
       </c>
       <c r="E39" s="11"/>
     </row>
-    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>43</v>
       </c>
@@ -1635,7 +1640,7 @@
       </c>
       <c r="E40" s="11"/>
     </row>
-    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>43</v>
       </c>
@@ -1710,7 +1715,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1723,7 +1728,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1736,7 +1741,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1749,7 +1754,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1762,7 +1767,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -1775,7 +1780,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1788,7 +1793,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1801,7 +1806,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1814,7 +1819,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -1827,7 +1832,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="11"/>
     </row>
-    <row r="55" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1840,7 +1845,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="11"/>
     </row>
-    <row r="56" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -1853,7 +1858,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -1866,7 +1871,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -1879,7 +1884,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -1892,7 +1897,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -1905,7 +1910,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -1918,7 +1923,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -1931,7 +1936,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -1944,7 +1949,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -1957,7 +1962,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -1970,7 +1975,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -1983,7 +1988,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -1996,7 +2001,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -2009,7 +2014,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -2022,7 +2027,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2035,7 +2040,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2048,7 +2053,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2061,7 +2066,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2074,7 +2079,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2087,7 +2092,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2100,7 +2105,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2113,7 +2118,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2126,7 +2131,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2139,7 +2144,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2152,7 +2157,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2165,7 +2170,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2178,7 +2183,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2191,7 +2196,7 @@
       <c r="D82" s="5"/>
       <c r="E82" s="11"/>
     </row>
-    <row r="83" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2204,7 +2209,7 @@
       <c r="D83" s="5"/>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2217,7 +2222,7 @@
       <c r="D84" s="5"/>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2230,7 +2235,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2243,7 +2248,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="11"/>
     </row>
-    <row r="87" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2256,7 +2261,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="11"/>
     </row>
-    <row r="88" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2269,7 +2274,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="11"/>
     </row>
-    <row r="89" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2282,7 +2287,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="11"/>
     </row>
-    <row r="90" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2295,7 +2300,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="11"/>
     </row>
-    <row r="91" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2308,7 +2313,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2321,7 +2326,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2334,7 +2339,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2347,7 +2352,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2360,7 +2365,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2373,7 +2378,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2386,7 +2391,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2399,7 +2404,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2412,7 +2417,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2425,7 +2430,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2438,7 +2443,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2451,7 +2456,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2464,7 +2469,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2477,7 +2482,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2490,7 +2495,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2503,7 +2508,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2516,7 +2521,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2529,7 +2534,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2542,7 +2547,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2555,7 +2560,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2568,7 +2573,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2581,7 +2586,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2594,7 +2599,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2607,7 +2612,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2620,7 +2625,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2633,7 +2638,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2646,7 +2651,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2659,7 +2664,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2672,7 +2677,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2685,7 +2690,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>
@@ -2698,7 +2703,7 @@
       <c r="D121" s="5"/>
       <c r="E121" s="11"/>
     </row>
-    <row r="122" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>5</v>
       </c>
@@ -2711,7 +2716,7 @@
       <c r="D122" s="5"/>
       <c r="E122" s="11"/>
     </row>
-    <row r="123" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>5</v>
       </c>
@@ -2724,7 +2729,7 @@
       <c r="D123" s="5"/>
       <c r="E123" s="11"/>
     </row>
-    <row r="124" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>5</v>
       </c>
@@ -2737,7 +2742,7 @@
       <c r="D124" s="5"/>
       <c r="E124" s="11"/>
     </row>
-    <row r="125" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>5</v>
       </c>
@@ -2750,7 +2755,7 @@
       <c r="D125" s="5"/>
       <c r="E125" s="11"/>
     </row>
-    <row r="126" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>5</v>
       </c>
@@ -2763,7 +2768,7 @@
       <c r="D126" s="5"/>
       <c r="E126" s="11"/>
     </row>
-    <row r="127" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>5</v>
       </c>
@@ -2776,7 +2781,7 @@
       <c r="D127" s="5"/>
       <c r="E127" s="11"/>
     </row>
-    <row r="128" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>5</v>
       </c>
@@ -2789,7 +2794,7 @@
       <c r="D128" s="5"/>
       <c r="E128" s="11"/>
     </row>
-    <row r="129" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>5</v>
       </c>
@@ -2802,7 +2807,7 @@
       <c r="D129" s="5"/>
       <c r="E129" s="11"/>
     </row>
-    <row r="130" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>5</v>
       </c>
@@ -2815,7 +2820,7 @@
       <c r="D130" s="5"/>
       <c r="E130" s="11"/>
     </row>
-    <row r="131" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>5</v>
       </c>
@@ -2828,7 +2833,7 @@
       <c r="D131" s="5"/>
       <c r="E131" s="11"/>
     </row>
-    <row r="132" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>5</v>
       </c>
@@ -2841,7 +2846,7 @@
       <c r="D132" s="5"/>
       <c r="E132" s="11"/>
     </row>
-    <row r="133" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>5</v>
       </c>
@@ -2854,7 +2859,7 @@
       <c r="D133" s="5"/>
       <c r="E133" s="11"/>
     </row>
-    <row r="134" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>5</v>
       </c>
@@ -2867,7 +2872,7 @@
       <c r="D134" s="5"/>
       <c r="E134" s="11"/>
     </row>
-    <row r="135" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>5</v>
       </c>
@@ -2880,7 +2885,7 @@
       <c r="D135" s="5"/>
       <c r="E135" s="11"/>
     </row>
-    <row r="136" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>5</v>
       </c>
@@ -2893,7 +2898,7 @@
       <c r="D136" s="5"/>
       <c r="E136" s="11"/>
     </row>
-    <row r="137" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>5</v>
       </c>
@@ -2906,7 +2911,7 @@
       <c r="D137" s="5"/>
       <c r="E137" s="11"/>
     </row>
-    <row r="138" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>5</v>
       </c>
@@ -2919,7 +2924,7 @@
       <c r="D138" s="5"/>
       <c r="E138" s="11"/>
     </row>
-    <row r="139" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>5</v>
       </c>
@@ -2932,7 +2937,7 @@
       <c r="D139" s="5"/>
       <c r="E139" s="11"/>
     </row>
-    <row r="140" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>5</v>
       </c>
@@ -2945,7 +2950,7 @@
       <c r="D140" s="5"/>
       <c r="E140" s="11"/>
     </row>
-    <row r="141" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>5</v>
       </c>
@@ -2958,7 +2963,7 @@
       <c r="D141" s="5"/>
       <c r="E141" s="11"/>
     </row>
-    <row r="142" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>5</v>
       </c>
@@ -2971,7 +2976,7 @@
       <c r="D142" s="5"/>
       <c r="E142" s="11"/>
     </row>
-    <row r="143" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>5</v>
       </c>
@@ -2984,7 +2989,7 @@
       <c r="D143" s="5"/>
       <c r="E143" s="11"/>
     </row>
-    <row r="144" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>5</v>
       </c>
@@ -2997,7 +3002,7 @@
       <c r="D144" s="5"/>
       <c r="E144" s="11"/>
     </row>
-    <row r="145" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>5</v>
       </c>
@@ -3010,7 +3015,7 @@
       <c r="D145" s="5"/>
       <c r="E145" s="11"/>
     </row>
-    <row r="146" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>5</v>
       </c>
@@ -3023,7 +3028,7 @@
       <c r="D146" s="5"/>
       <c r="E146" s="11"/>
     </row>
-    <row r="147" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>5</v>
       </c>
@@ -3036,7 +3041,7 @@
       <c r="D147" s="5"/>
       <c r="E147" s="11"/>
     </row>
-    <row r="148" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>5</v>
       </c>
@@ -3049,7 +3054,7 @@
       <c r="D148" s="5"/>
       <c r="E148" s="11"/>
     </row>
-    <row r="149" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>5</v>
       </c>
@@ -3062,7 +3067,7 @@
       <c r="D149" s="5"/>
       <c r="E149" s="11"/>
     </row>
-    <row r="150" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>5</v>
       </c>
@@ -3075,7 +3080,7 @@
       <c r="D150" s="5"/>
       <c r="E150" s="11"/>
     </row>
-    <row r="151" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>5</v>
       </c>
@@ -3088,7 +3093,7 @@
       <c r="D151" s="5"/>
       <c r="E151" s="11"/>
     </row>
-    <row r="152" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>5</v>
       </c>
@@ -3101,7 +3106,7 @@
       <c r="D152" s="5"/>
       <c r="E152" s="11"/>
     </row>
-    <row r="153" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>5</v>
       </c>
@@ -3114,7 +3119,7 @@
       <c r="D153" s="5"/>
       <c r="E153" s="11"/>
     </row>
-    <row r="154" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>5</v>
       </c>
@@ -3127,7 +3132,7 @@
       <c r="D154" s="5"/>
       <c r="E154" s="11"/>
     </row>
-    <row r="155" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>5</v>
       </c>
@@ -3140,7 +3145,7 @@
       <c r="D155" s="5"/>
       <c r="E155" s="11"/>
     </row>
-    <row r="156" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>5</v>
       </c>
@@ -3153,7 +3158,7 @@
       <c r="D156" s="5"/>
       <c r="E156" s="11"/>
     </row>
-    <row r="157" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>5</v>
       </c>
@@ -3166,7 +3171,7 @@
       <c r="D157" s="5"/>
       <c r="E157" s="11"/>
     </row>
-    <row r="158" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>5</v>
       </c>
@@ -3179,7 +3184,7 @@
       <c r="D158" s="5"/>
       <c r="E158" s="11"/>
     </row>
-    <row r="159" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>5</v>
       </c>
@@ -3192,7 +3197,7 @@
       <c r="D159" s="5"/>
       <c r="E159" s="11"/>
     </row>
-    <row r="160" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>5</v>
       </c>
@@ -3205,7 +3210,7 @@
       <c r="D160" s="5"/>
       <c r="E160" s="11"/>
     </row>
-    <row r="161" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>5</v>
       </c>
@@ -3218,7 +3223,7 @@
       <c r="D161" s="5"/>
       <c r="E161" s="11"/>
     </row>
-    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>43</v>
       </c>
@@ -3233,7 +3238,7 @@
       </c>
       <c r="E162" s="11"/>
     </row>
-    <row r="163" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>43</v>
       </c>
@@ -3248,7 +3253,7 @@
       </c>
       <c r="E163" s="11"/>
     </row>
-    <row r="164" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>43</v>
       </c>
@@ -3263,7 +3268,7 @@
       </c>
       <c r="E164" s="11"/>
     </row>
-    <row r="165" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>43</v>
       </c>
@@ -3280,7 +3285,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>5</v>
       </c>
@@ -3297,7 +3302,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>5</v>
       </c>
@@ -3314,7 +3319,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>5</v>
       </c>
@@ -3329,7 +3334,7 @@
       </c>
       <c r="E168" s="10"/>
     </row>
-    <row r="169" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>5</v>
       </c>
@@ -3344,7 +3349,7 @@
       </c>
       <c r="E169" s="10"/>
     </row>
-    <row r="170" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>5</v>
       </c>
@@ -3359,7 +3364,7 @@
       </c>
       <c r="E170" s="10"/>
     </row>
-    <row r="171" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>5</v>
       </c>
@@ -3374,7 +3379,7 @@
       </c>
       <c r="E171" s="10"/>
     </row>
-    <row r="172" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>5</v>
       </c>
@@ -3389,7 +3394,7 @@
       </c>
       <c r="E172" s="10"/>
     </row>
-    <row r="173" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>5</v>
       </c>
@@ -3404,7 +3409,7 @@
       </c>
       <c r="E173" s="10"/>
     </row>
-    <row r="174" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>5</v>
       </c>
@@ -3419,7 +3424,7 @@
       </c>
       <c r="E174" s="10"/>
     </row>
-    <row r="175" spans="1:5" ht="29.4" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>5</v>
       </c>
@@ -3434,7 +3439,7 @@
       </c>
       <c r="E175" s="10"/>
     </row>
-    <row r="176" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>5</v>
       </c>
@@ -3449,7 +3454,7 @@
       </c>
       <c r="E176" s="10"/>
     </row>
-    <row r="177" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>5</v>
       </c>
@@ -3464,7 +3469,7 @@
       </c>
       <c r="E177" s="10"/>
     </row>
-    <row r="178" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>5</v>
       </c>
@@ -3479,7 +3484,7 @@
       </c>
       <c r="E178" s="10"/>
     </row>
-    <row r="179" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>5</v>
       </c>
@@ -3494,7 +3499,7 @@
       </c>
       <c r="E179" s="10"/>
     </row>
-    <row r="180" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>5</v>
       </c>
@@ -3509,7 +3514,7 @@
       </c>
       <c r="E180" s="10"/>
     </row>
-    <row r="181" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>5</v>
       </c>
@@ -3524,7 +3529,7 @@
       </c>
       <c r="E181" s="10"/>
     </row>
-    <row r="182" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>5</v>
       </c>
@@ -3539,7 +3544,7 @@
       </c>
       <c r="E182" s="10"/>
     </row>
-    <row r="183" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>5</v>
       </c>
@@ -3554,7 +3559,7 @@
       </c>
       <c r="E183" s="10"/>
     </row>
-    <row r="184" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>5</v>
       </c>
@@ -3569,7 +3574,7 @@
       </c>
       <c r="E184" s="10"/>
     </row>
-    <row r="185" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>5</v>
       </c>
@@ -3584,7 +3589,7 @@
       </c>
       <c r="E185" s="10"/>
     </row>
-    <row r="186" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>5</v>
       </c>
@@ -3599,7 +3604,7 @@
       </c>
       <c r="E186" s="10"/>
     </row>
-    <row r="187" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>5</v>
       </c>
@@ -3614,7 +3619,7 @@
       </c>
       <c r="E187" s="10"/>
     </row>
-    <row r="188" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>5</v>
       </c>
@@ -3629,7 +3634,7 @@
       </c>
       <c r="E188" s="10"/>
     </row>
-    <row r="189" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>5</v>
       </c>
@@ -3644,7 +3649,7 @@
       </c>
       <c r="E189" s="10"/>
     </row>
-    <row r="190" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>5</v>
       </c>
@@ -3659,7 +3664,7 @@
       </c>
       <c r="E190" s="10"/>
     </row>
-    <row r="191" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>5</v>
       </c>
@@ -3674,7 +3679,7 @@
       </c>
       <c r="E191" s="10"/>
     </row>
-    <row r="192" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>5</v>
       </c>
@@ -3689,7 +3694,7 @@
       </c>
       <c r="E192" s="10"/>
     </row>
-    <row r="193" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>5</v>
       </c>
@@ -3704,7 +3709,7 @@
       </c>
       <c r="E193" s="10"/>
     </row>
-    <row r="194" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>5</v>
       </c>
@@ -3719,7 +3724,7 @@
       </c>
       <c r="E194" s="10"/>
     </row>
-    <row r="195" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>5</v>
       </c>
@@ -3734,7 +3739,7 @@
       </c>
       <c r="E195" s="10"/>
     </row>
-    <row r="196" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>5</v>
       </c>
@@ -3749,7 +3754,7 @@
       </c>
       <c r="E196" s="10"/>
     </row>
-    <row r="197" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>5</v>
       </c>
@@ -3764,7 +3769,7 @@
       </c>
       <c r="E197" s="10"/>
     </row>
-    <row r="198" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>5</v>
       </c>
@@ -3779,7 +3784,7 @@
       </c>
       <c r="E198" s="10"/>
     </row>
-    <row r="199" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>5</v>
       </c>
@@ -3794,7 +3799,7 @@
       </c>
       <c r="E199" s="10"/>
     </row>
-    <row r="200" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>5</v>
       </c>
@@ -3809,7 +3814,7 @@
       </c>
       <c r="E200" s="10"/>
     </row>
-    <row r="201" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>5</v>
       </c>
@@ -3824,7 +3829,7 @@
       </c>
       <c r="E201" s="10"/>
     </row>
-    <row r="202" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
         <v>43</v>
       </c>
@@ -3837,7 +3842,7 @@
       <c r="D202" s="5"/>
       <c r="E202" s="11"/>
     </row>
-    <row r="203" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
         <v>43</v>
       </c>
@@ -3850,7 +3855,7 @@
       <c r="D203" s="5"/>
       <c r="E203" s="11"/>
     </row>
-    <row r="204" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
         <v>43</v>
       </c>
@@ -3863,7 +3868,7 @@
       <c r="D204" s="5"/>
       <c r="E204" s="11"/>
     </row>
-    <row r="205" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
         <v>43</v>
       </c>
@@ -3876,7 +3881,7 @@
       <c r="D205" s="5"/>
       <c r="E205" s="11"/>
     </row>
-    <row r="206" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
         <v>43</v>
       </c>
@@ -3889,7 +3894,7 @@
       <c r="D206" s="5"/>
       <c r="E206" s="11"/>
     </row>
-    <row r="207" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
         <v>43</v>
       </c>
@@ -3902,7 +3907,7 @@
       <c r="D207" s="5"/>
       <c r="E207" s="11"/>
     </row>
-    <row r="208" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
         <v>43</v>
       </c>
@@ -3915,7 +3920,7 @@
       <c r="D208" s="5"/>
       <c r="E208" s="11"/>
     </row>
-    <row r="209" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
         <v>43</v>
       </c>
@@ -3928,7 +3933,7 @@
       <c r="D209" s="5"/>
       <c r="E209" s="11"/>
     </row>
-    <row r="210" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
         <v>43</v>
       </c>
@@ -3941,7 +3946,7 @@
       <c r="D210" s="5"/>
       <c r="E210" s="11"/>
     </row>
-    <row r="211" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
         <v>43</v>
       </c>
@@ -3954,7 +3959,7 @@
       <c r="D211" s="5"/>
       <c r="E211" s="11"/>
     </row>
-    <row r="212" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
         <v>43</v>
       </c>
@@ -3967,7 +3972,7 @@
       <c r="D212" s="5"/>
       <c r="E212" s="11"/>
     </row>
-    <row r="213" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
         <v>43</v>
       </c>
@@ -3980,7 +3985,7 @@
       <c r="D213" s="5"/>
       <c r="E213" s="11"/>
     </row>
-    <row r="214" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
         <v>43</v>
       </c>
@@ -3993,7 +3998,7 @@
       <c r="D214" s="5"/>
       <c r="E214" s="11"/>
     </row>
-    <row r="215" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
         <v>43</v>
       </c>
@@ -4006,7 +4011,7 @@
       <c r="D215" s="5"/>
       <c r="E215" s="11"/>
     </row>
-    <row r="216" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
         <v>43</v>
       </c>
@@ -4019,7 +4024,7 @@
       <c r="D216" s="5"/>
       <c r="E216" s="11"/>
     </row>
-    <row r="217" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
         <v>43</v>
       </c>
@@ -4032,7 +4037,7 @@
       <c r="D217" s="5"/>
       <c r="E217" s="11"/>
     </row>
-    <row r="218" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
         <v>43</v>
       </c>
@@ -4045,7 +4050,7 @@
       <c r="D218" s="5"/>
       <c r="E218" s="11"/>
     </row>
-    <row r="219" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
         <v>43</v>
       </c>
@@ -4058,7 +4063,7 @@
       <c r="D219" s="5"/>
       <c r="E219" s="11"/>
     </row>
-    <row r="220" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
         <v>43</v>
       </c>
@@ -4071,7 +4076,7 @@
       <c r="D220" s="5"/>
       <c r="E220" s="11"/>
     </row>
-    <row r="221" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
         <v>43</v>
       </c>
@@ -4084,7 +4089,7 @@
       <c r="D221" s="5"/>
       <c r="E221" s="11"/>
     </row>
-    <row r="222" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
         <v>43</v>
       </c>
@@ -4097,7 +4102,7 @@
       <c r="D222" s="5"/>
       <c r="E222" s="11"/>
     </row>
-    <row r="223" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
         <v>43</v>
       </c>
@@ -4110,7 +4115,7 @@
       <c r="D223" s="5"/>
       <c r="E223" s="11"/>
     </row>
-    <row r="224" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
         <v>43</v>
       </c>
@@ -4123,7 +4128,7 @@
       <c r="D224" s="5"/>
       <c r="E224" s="11"/>
     </row>
-    <row r="225" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
         <v>43</v>
       </c>
@@ -4136,7 +4141,7 @@
       <c r="D225" s="5"/>
       <c r="E225" s="11"/>
     </row>
-    <row r="226" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
         <v>43</v>
       </c>
@@ -4149,7 +4154,7 @@
       <c r="D226" s="5"/>
       <c r="E226" s="11"/>
     </row>
-    <row r="227" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
         <v>43</v>
       </c>
@@ -4162,7 +4167,7 @@
       <c r="D227" s="5"/>
       <c r="E227" s="11"/>
     </row>
-    <row r="228" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
         <v>43</v>
       </c>
@@ -4175,7 +4180,7 @@
       <c r="D228" s="5"/>
       <c r="E228" s="11"/>
     </row>
-    <row r="229" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
         <v>43</v>
       </c>
@@ -4188,7 +4193,7 @@
       <c r="D229" s="5"/>
       <c r="E229" s="11"/>
     </row>
-    <row r="230" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
         <v>43</v>
       </c>
@@ -4201,7 +4206,7 @@
       <c r="D230" s="5"/>
       <c r="E230" s="11"/>
     </row>
-    <row r="231" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
         <v>43</v>
       </c>
@@ -4214,7 +4219,7 @@
       <c r="D231" s="5"/>
       <c r="E231" s="11"/>
     </row>
-    <row r="232" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
         <v>43</v>
       </c>
@@ -4227,7 +4232,7 @@
       <c r="D232" s="5"/>
       <c r="E232" s="11"/>
     </row>
-    <row r="233" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
         <v>43</v>
       </c>
@@ -4240,7 +4245,7 @@
       <c r="D233" s="5"/>
       <c r="E233" s="11"/>
     </row>
-    <row r="234" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
         <v>43</v>
       </c>
@@ -4253,7 +4258,7 @@
       <c r="D234" s="5"/>
       <c r="E234" s="11"/>
     </row>
-    <row r="235" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
         <v>43</v>
       </c>
@@ -4266,7 +4271,7 @@
       <c r="D235" s="5"/>
       <c r="E235" s="11"/>
     </row>
-    <row r="236" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
         <v>43</v>
       </c>
@@ -4279,7 +4284,7 @@
       <c r="D236" s="5"/>
       <c r="E236" s="11"/>
     </row>
-    <row r="237" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
         <v>43</v>
       </c>
@@ -4292,7 +4297,7 @@
       <c r="D237" s="5"/>
       <c r="E237" s="11"/>
     </row>
-    <row r="238" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
         <v>43</v>
       </c>
@@ -4305,7 +4310,7 @@
       <c r="D238" s="5"/>
       <c r="E238" s="11"/>
     </row>
-    <row r="239" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
         <v>43</v>
       </c>
@@ -4318,7 +4323,7 @@
       <c r="D239" s="5"/>
       <c r="E239" s="11"/>
     </row>
-    <row r="240" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
         <v>43</v>
       </c>
@@ -4331,7 +4336,7 @@
       <c r="D240" s="5"/>
       <c r="E240" s="11"/>
     </row>
-    <row r="241" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
         <v>43</v>
       </c>
@@ -4344,7 +4349,7 @@
       <c r="D241" s="5"/>
       <c r="E241" s="11"/>
     </row>
-    <row r="242" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
         <v>43</v>
       </c>
@@ -4357,7 +4362,7 @@
       <c r="D242" s="5"/>
       <c r="E242" s="11"/>
     </row>
-    <row r="243" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
         <v>43</v>
       </c>
@@ -4370,7 +4375,7 @@
       <c r="D243" s="5"/>
       <c r="E243" s="11"/>
     </row>
-    <row r="244" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
         <v>43</v>
       </c>
@@ -4383,7 +4388,7 @@
       <c r="D244" s="5"/>
       <c r="E244" s="11"/>
     </row>
-    <row r="245" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
         <v>43</v>
       </c>
@@ -4396,7 +4401,7 @@
       <c r="D245" s="5"/>
       <c r="E245" s="11"/>
     </row>
-    <row r="246" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
         <v>43</v>
       </c>
@@ -4409,7 +4414,7 @@
       <c r="D246" s="5"/>
       <c r="E246" s="11"/>
     </row>
-    <row r="247" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
         <v>43</v>
       </c>
@@ -4422,7 +4427,7 @@
       <c r="D247" s="5"/>
       <c r="E247" s="11"/>
     </row>
-    <row r="248" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
         <v>43</v>
       </c>
@@ -4435,7 +4440,7 @@
       <c r="D248" s="5"/>
       <c r="E248" s="11"/>
     </row>
-    <row r="249" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
         <v>43</v>
       </c>
@@ -4448,7 +4453,7 @@
       <c r="D249" s="5"/>
       <c r="E249" s="11"/>
     </row>
-    <row r="250" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
         <v>43</v>
       </c>
@@ -4461,7 +4466,7 @@
       <c r="D250" s="5"/>
       <c r="E250" s="11"/>
     </row>
-    <row r="251" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
         <v>43</v>
       </c>
@@ -4474,7 +4479,7 @@
       <c r="D251" s="5"/>
       <c r="E251" s="11"/>
     </row>
-    <row r="252" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
         <v>43</v>
       </c>
@@ -4487,7 +4492,7 @@
       <c r="D252" s="5"/>
       <c r="E252" s="11"/>
     </row>
-    <row r="253" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
         <v>43</v>
       </c>
@@ -4500,7 +4505,7 @@
       <c r="D253" s="5"/>
       <c r="E253" s="11"/>
     </row>
-    <row r="254" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>43</v>
       </c>
@@ -4513,7 +4518,7 @@
       <c r="D254" s="5"/>
       <c r="E254" s="11"/>
     </row>
-    <row r="255" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>43</v>
       </c>
@@ -4526,7 +4531,7 @@
       <c r="D255" s="5"/>
       <c r="E255" s="11"/>
     </row>
-    <row r="256" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>43</v>
       </c>
@@ -4539,7 +4544,7 @@
       <c r="D256" s="5"/>
       <c r="E256" s="11"/>
     </row>
-    <row r="257" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
         <v>43</v>
       </c>
@@ -4552,7 +4557,7 @@
       <c r="D257" s="5"/>
       <c r="E257" s="11"/>
     </row>
-    <row r="258" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
         <v>43</v>
       </c>
@@ -4565,7 +4570,7 @@
       <c r="D258" s="5"/>
       <c r="E258" s="11"/>
     </row>
-    <row r="259" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
         <v>43</v>
       </c>
@@ -4578,7 +4583,7 @@
       <c r="D259" s="5"/>
       <c r="E259" s="11"/>
     </row>
-    <row r="260" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
         <v>43</v>
       </c>
@@ -4591,7 +4596,7 @@
       <c r="D260" s="5"/>
       <c r="E260" s="11"/>
     </row>
-    <row r="261" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
         <v>43</v>
       </c>
@@ -4604,7 +4609,7 @@
       <c r="D261" s="5"/>
       <c r="E261" s="11"/>
     </row>
-    <row r="262" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
         <v>43</v>
       </c>
@@ -4617,7 +4622,7 @@
       <c r="D262" s="5"/>
       <c r="E262" s="11"/>
     </row>
-    <row r="263" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
         <v>43</v>
       </c>
@@ -4630,7 +4635,7 @@
       <c r="D263" s="5"/>
       <c r="E263" s="11"/>
     </row>
-    <row r="264" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
         <v>43</v>
       </c>
@@ -4643,7 +4648,7 @@
       <c r="D264" s="5"/>
       <c r="E264" s="11"/>
     </row>
-    <row r="265" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
         <v>43</v>
       </c>
@@ -4656,7 +4661,7 @@
       <c r="D265" s="5"/>
       <c r="E265" s="11"/>
     </row>
-    <row r="266" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
         <v>43</v>
       </c>
@@ -4669,7 +4674,7 @@
       <c r="D266" s="5"/>
       <c r="E266" s="11"/>
     </row>
-    <row r="267" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
         <v>43</v>
       </c>
@@ -4682,7 +4687,7 @@
       <c r="D267" s="5"/>
       <c r="E267" s="11"/>
     </row>
-    <row r="268" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
         <v>43</v>
       </c>
@@ -4695,7 +4700,7 @@
       <c r="D268" s="5"/>
       <c r="E268" s="11"/>
     </row>
-    <row r="269" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
         <v>43</v>
       </c>
@@ -4708,7 +4713,7 @@
       <c r="D269" s="5"/>
       <c r="E269" s="11"/>
     </row>
-    <row r="270" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
         <v>43</v>
       </c>
@@ -4721,7 +4726,7 @@
       <c r="D270" s="5"/>
       <c r="E270" s="11"/>
     </row>
-    <row r="271" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
         <v>43</v>
       </c>
@@ -4734,7 +4739,7 @@
       <c r="D271" s="5"/>
       <c r="E271" s="11"/>
     </row>
-    <row r="272" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
         <v>43</v>
       </c>
@@ -4747,7 +4752,7 @@
       <c r="D272" s="5"/>
       <c r="E272" s="11"/>
     </row>
-    <row r="273" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4" t="s">
         <v>43</v>
       </c>
@@ -4760,7 +4765,7 @@
       <c r="D273" s="5"/>
       <c r="E273" s="11"/>
     </row>
-    <row r="274" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4" t="s">
         <v>43</v>
       </c>
@@ -4773,7 +4778,7 @@
       <c r="D274" s="5"/>
       <c r="E274" s="11"/>
     </row>
-    <row r="275" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="4" t="s">
         <v>43</v>
       </c>
@@ -4786,7 +4791,7 @@
       <c r="D275" s="5"/>
       <c r="E275" s="11"/>
     </row>
-    <row r="276" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
         <v>43</v>
       </c>
@@ -4799,7 +4804,7 @@
       <c r="D276" s="5"/>
       <c r="E276" s="11"/>
     </row>
-    <row r="277" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
         <v>43</v>
       </c>
@@ -4812,7 +4817,7 @@
       <c r="D277" s="5"/>
       <c r="E277" s="11"/>
     </row>
-    <row r="278" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
         <v>43</v>
       </c>
@@ -4825,7 +4830,7 @@
       <c r="D278" s="5"/>
       <c r="E278" s="11"/>
     </row>
-    <row r="279" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
         <v>43</v>
       </c>
@@ -4838,7 +4843,7 @@
       <c r="D279" s="5"/>
       <c r="E279" s="11"/>
     </row>
-    <row r="280" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
         <v>43</v>
       </c>
@@ -4851,7 +4856,7 @@
       <c r="D280" s="5"/>
       <c r="E280" s="11"/>
     </row>
-    <row r="281" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
         <v>43</v>
       </c>
@@ -4864,7 +4869,7 @@
       <c r="D281" s="5"/>
       <c r="E281" s="11"/>
     </row>
-    <row r="282" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>43</v>
       </c>
@@ -4877,7 +4882,7 @@
       <c r="D282" s="5"/>
       <c r="E282" s="11"/>
     </row>
-    <row r="283" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>43</v>
       </c>
@@ -4890,7 +4895,7 @@
       <c r="D283" s="5"/>
       <c r="E283" s="11"/>
     </row>
-    <row r="284" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>43</v>
       </c>
@@ -4903,7 +4908,7 @@
       <c r="D284" s="5"/>
       <c r="E284" s="11"/>
     </row>
-    <row r="285" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>43</v>
       </c>
@@ -4916,7 +4921,7 @@
       <c r="D285" s="5"/>
       <c r="E285" s="11"/>
     </row>
-    <row r="286" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
         <v>43</v>
       </c>
@@ -4929,7 +4934,7 @@
       <c r="D286" s="5"/>
       <c r="E286" s="11"/>
     </row>
-    <row r="287" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
         <v>43</v>
       </c>
@@ -4942,7 +4947,7 @@
       <c r="D287" s="5"/>
       <c r="E287" s="11"/>
     </row>
-    <row r="288" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>43</v>
       </c>
@@ -4955,7 +4960,7 @@
       <c r="D288" s="5"/>
       <c r="E288" s="11"/>
     </row>
-    <row r="289" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
         <v>43</v>
       </c>
@@ -4968,7 +4973,7 @@
       <c r="D289" s="5"/>
       <c r="E289" s="11"/>
     </row>
-    <row r="290" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>43</v>
       </c>
@@ -4981,7 +4986,7 @@
       <c r="D290" s="5"/>
       <c r="E290" s="11"/>
     </row>
-    <row r="291" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>43</v>
       </c>
@@ -4994,7 +4999,7 @@
       <c r="D291" s="5"/>
       <c r="E291" s="11"/>
     </row>
-    <row r="292" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>43</v>
       </c>
@@ -5007,7 +5012,7 @@
       <c r="D292" s="5"/>
       <c r="E292" s="11"/>
     </row>
-    <row r="293" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>43</v>
       </c>
@@ -5020,7 +5025,7 @@
       <c r="D293" s="5"/>
       <c r="E293" s="11"/>
     </row>
-    <row r="294" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>43</v>
       </c>
@@ -5033,7 +5038,7 @@
       <c r="D294" s="5"/>
       <c r="E294" s="11"/>
     </row>
-    <row r="295" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>43</v>
       </c>
@@ -5046,7 +5051,7 @@
       <c r="D295" s="5"/>
       <c r="E295" s="11"/>
     </row>
-    <row r="296" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>43</v>
       </c>
@@ -5059,7 +5064,7 @@
       <c r="D296" s="5"/>
       <c r="E296" s="11"/>
     </row>
-    <row r="297" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>43</v>
       </c>
@@ -5072,7 +5077,7 @@
       <c r="D297" s="5"/>
       <c r="E297" s="11"/>
     </row>
-    <row r="298" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>43</v>
       </c>
@@ -5085,7 +5090,7 @@
       <c r="D298" s="5"/>
       <c r="E298" s="11"/>
     </row>
-    <row r="299" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>43</v>
       </c>
@@ -5098,7 +5103,7 @@
       <c r="D299" s="5"/>
       <c r="E299" s="11"/>
     </row>
-    <row r="300" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
         <v>43</v>
       </c>
@@ -5111,7 +5116,7 @@
       <c r="D300" s="5"/>
       <c r="E300" s="11"/>
     </row>
-    <row r="301" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
         <v>43</v>
       </c>
@@ -5124,7 +5129,7 @@
       <c r="D301" s="5"/>
       <c r="E301" s="11"/>
     </row>
-    <row r="302" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
         <v>43</v>
       </c>
@@ -5137,7 +5142,7 @@
       <c r="D302" s="5"/>
       <c r="E302" s="11"/>
     </row>
-    <row r="303" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
         <v>43</v>
       </c>
@@ -5150,7 +5155,7 @@
       <c r="D303" s="5"/>
       <c r="E303" s="11"/>
     </row>
-    <row r="304" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>43</v>
       </c>
@@ -5163,7 +5168,7 @@
       <c r="D304" s="5"/>
       <c r="E304" s="11"/>
     </row>
-    <row r="305" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>43</v>
       </c>
@@ -5176,7 +5181,7 @@
       <c r="D305" s="5"/>
       <c r="E305" s="11"/>
     </row>
-    <row r="306" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>43</v>
       </c>
@@ -5189,7 +5194,7 @@
       <c r="D306" s="5"/>
       <c r="E306" s="11"/>
     </row>
-    <row r="307" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>43</v>
       </c>
@@ -5202,7 +5207,7 @@
       <c r="D307" s="5"/>
       <c r="E307" s="11"/>
     </row>
-    <row r="308" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>43</v>
       </c>
@@ -5215,7 +5220,7 @@
       <c r="D308" s="5"/>
       <c r="E308" s="11"/>
     </row>
-    <row r="309" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
         <v>43</v>
       </c>
@@ -5228,7 +5233,7 @@
       <c r="D309" s="5"/>
       <c r="E309" s="11"/>
     </row>
-    <row r="310" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
         <v>43</v>
       </c>
@@ -5241,7 +5246,7 @@
       <c r="D310" s="5"/>
       <c r="E310" s="11"/>
     </row>
-    <row r="311" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
         <v>43</v>
       </c>
@@ -5254,7 +5259,7 @@
       <c r="D311" s="5"/>
       <c r="E311" s="11"/>
     </row>
-    <row r="312" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
         <v>43</v>
       </c>
@@ -5267,7 +5272,7 @@
       <c r="D312" s="5"/>
       <c r="E312" s="11"/>
     </row>
-    <row r="313" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
         <v>43</v>
       </c>
@@ -5280,7 +5285,7 @@
       <c r="D313" s="5"/>
       <c r="E313" s="11"/>
     </row>
-    <row r="314" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
         <v>43</v>
       </c>
@@ -5293,7 +5298,7 @@
       <c r="D314" s="5"/>
       <c r="E314" s="11"/>
     </row>
-    <row r="315" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
         <v>43</v>
       </c>
@@ -5306,7 +5311,7 @@
       <c r="D315" s="5"/>
       <c r="E315" s="11"/>
     </row>
-    <row r="316" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
         <v>43</v>
       </c>
@@ -5323,7 +5328,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="317" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
         <v>43</v>
       </c>
@@ -5336,7 +5341,7 @@
       <c r="D317" s="5"/>
       <c r="E317" s="11"/>
     </row>
-    <row r="318" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
         <v>43</v>
       </c>
@@ -5353,7 +5358,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="319" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
         <v>43</v>
       </c>
@@ -5370,7 +5375,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="320" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
         <v>43</v>
       </c>
@@ -5385,7 +5390,7 @@
       </c>
       <c r="E320" s="11"/>
     </row>
-    <row r="321" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
         <v>43</v>
       </c>
@@ -5400,7 +5405,7 @@
       </c>
       <c r="E321" s="11"/>
     </row>
-    <row r="322" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
         <v>5</v>
       </c>
@@ -5415,7 +5420,7 @@
       </c>
       <c r="E322" s="10"/>
     </row>
-    <row r="323" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
         <v>5</v>
       </c>
@@ -5430,7 +5435,7 @@
       </c>
       <c r="E323" s="10"/>
     </row>
-    <row r="324" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>5</v>
       </c>
@@ -5445,7 +5450,7 @@
       </c>
       <c r="E324" s="10"/>
     </row>
-    <row r="325" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
         <v>5</v>
       </c>
@@ -5460,7 +5465,7 @@
       </c>
       <c r="E325" s="10"/>
     </row>
-    <row r="326" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="4" t="s">
         <v>44</v>
       </c>
@@ -5473,7 +5478,7 @@
       <c r="D326" s="5"/>
       <c r="E326" s="11"/>
     </row>
-    <row r="327" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="4" t="s">
         <v>44</v>
       </c>
@@ -5486,7 +5491,7 @@
       <c r="D327" s="5"/>
       <c r="E327" s="11"/>
     </row>
-    <row r="328" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="4" t="s">
         <v>44</v>
       </c>
@@ -5499,7 +5504,7 @@
       <c r="D328" s="5"/>
       <c r="E328" s="11"/>
     </row>
-    <row r="329" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="4" t="s">
         <v>44</v>
       </c>
@@ -5512,7 +5517,7 @@
       <c r="D329" s="5"/>
       <c r="E329" s="11"/>
     </row>
-    <row r="330" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="4" t="s">
         <v>44</v>
       </c>
@@ -5525,7 +5530,7 @@
       <c r="D330" s="5"/>
       <c r="E330" s="11"/>
     </row>
-    <row r="331" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="4" t="s">
         <v>44</v>
       </c>
@@ -5538,7 +5543,7 @@
       <c r="D331" s="5"/>
       <c r="E331" s="11"/>
     </row>
-    <row r="332" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="4" t="s">
         <v>44</v>
       </c>
@@ -5551,7 +5556,7 @@
       <c r="D332" s="5"/>
       <c r="E332" s="11"/>
     </row>
-    <row r="333" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="4" t="s">
         <v>44</v>
       </c>
@@ -5564,7 +5569,7 @@
       <c r="D333" s="5"/>
       <c r="E333" s="11"/>
     </row>
-    <row r="334" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="4" t="s">
         <v>44</v>
       </c>
@@ -5577,7 +5582,7 @@
       <c r="D334" s="5"/>
       <c r="E334" s="11"/>
     </row>
-    <row r="335" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="4" t="s">
         <v>44</v>
       </c>
@@ -5590,7 +5595,7 @@
       <c r="D335" s="5"/>
       <c r="E335" s="11"/>
     </row>
-    <row r="336" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="4" t="s">
         <v>44</v>
       </c>
@@ -5603,7 +5608,7 @@
       <c r="D336" s="5"/>
       <c r="E336" s="11"/>
     </row>
-    <row r="337" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="4" t="s">
         <v>44</v>
       </c>
@@ -5616,7 +5621,7 @@
       <c r="D337" s="5"/>
       <c r="E337" s="11"/>
     </row>
-    <row r="338" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="4" t="s">
         <v>44</v>
       </c>
@@ -5629,7 +5634,7 @@
       <c r="D338" s="5"/>
       <c r="E338" s="11"/>
     </row>
-    <row r="339" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="4" t="s">
         <v>44</v>
       </c>
@@ -5642,7 +5647,7 @@
       <c r="D339" s="5"/>
       <c r="E339" s="11"/>
     </row>
-    <row r="340" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4" t="s">
         <v>44</v>
       </c>
@@ -5655,7 +5660,7 @@
       <c r="D340" s="5"/>
       <c r="E340" s="11"/>
     </row>
-    <row r="341" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="4" t="s">
         <v>44</v>
       </c>
@@ -5668,7 +5673,7 @@
       <c r="D341" s="5"/>
       <c r="E341" s="11"/>
     </row>
-    <row r="342" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4" t="s">
         <v>44</v>
       </c>
@@ -5681,7 +5686,7 @@
       <c r="D342" s="5"/>
       <c r="E342" s="11"/>
     </row>
-    <row r="343" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="4" t="s">
         <v>44</v>
       </c>
@@ -5694,7 +5699,7 @@
       <c r="D343" s="5"/>
       <c r="E343" s="11"/>
     </row>
-    <row r="344" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="4" t="s">
         <v>44</v>
       </c>
@@ -5707,7 +5712,7 @@
       <c r="D344" s="5"/>
       <c r="E344" s="11"/>
     </row>
-    <row r="345" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="4" t="s">
         <v>44</v>
       </c>
@@ -5720,7 +5725,7 @@
       <c r="D345" s="5"/>
       <c r="E345" s="11"/>
     </row>
-    <row r="346" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="4" t="s">
         <v>44</v>
       </c>
@@ -5733,7 +5738,7 @@
       <c r="D346" s="5"/>
       <c r="E346" s="11"/>
     </row>
-    <row r="347" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="4" t="s">
         <v>44</v>
       </c>
@@ -5746,7 +5751,7 @@
       <c r="D347" s="5"/>
       <c r="E347" s="11"/>
     </row>
-    <row r="348" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="4" t="s">
         <v>44</v>
       </c>
@@ -5759,7 +5764,7 @@
       <c r="D348" s="5"/>
       <c r="E348" s="11"/>
     </row>
-    <row r="349" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="4" t="s">
         <v>44</v>
       </c>
@@ -5772,7 +5777,7 @@
       <c r="D349" s="5"/>
       <c r="E349" s="11"/>
     </row>
-    <row r="350" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="4" t="s">
         <v>44</v>
       </c>
@@ -5785,7 +5790,7 @@
       <c r="D350" s="5"/>
       <c r="E350" s="11"/>
     </row>
-    <row r="351" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="4" t="s">
         <v>44</v>
       </c>
@@ -5798,7 +5803,7 @@
       <c r="D351" s="5"/>
       <c r="E351" s="11"/>
     </row>
-    <row r="352" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="4" t="s">
         <v>44</v>
       </c>
@@ -5811,7 +5816,7 @@
       <c r="D352" s="5"/>
       <c r="E352" s="11"/>
     </row>
-    <row r="353" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="4" t="s">
         <v>44</v>
       </c>
@@ -5824,7 +5829,7 @@
       <c r="D353" s="5"/>
       <c r="E353" s="11"/>
     </row>
-    <row r="354" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="4" t="s">
         <v>44</v>
       </c>
@@ -5837,7 +5842,7 @@
       <c r="D354" s="5"/>
       <c r="E354" s="11"/>
     </row>
-    <row r="355" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="4" t="s">
         <v>44</v>
       </c>
@@ -5850,7 +5855,7 @@
       <c r="D355" s="5"/>
       <c r="E355" s="11"/>
     </row>
-    <row r="356" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="4" t="s">
         <v>44</v>
       </c>
@@ -5863,7 +5868,7 @@
       <c r="D356" s="5"/>
       <c r="E356" s="11"/>
     </row>
-    <row r="357" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="4" t="s">
         <v>44</v>
       </c>
@@ -5876,7 +5881,7 @@
       <c r="D357" s="5"/>
       <c r="E357" s="11"/>
     </row>
-    <row r="358" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
         <v>44</v>
       </c>
@@ -5889,7 +5894,7 @@
       <c r="D358" s="5"/>
       <c r="E358" s="11"/>
     </row>
-    <row r="359" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
         <v>44</v>
       </c>
@@ -5902,7 +5907,7 @@
       <c r="D359" s="5"/>
       <c r="E359" s="11"/>
     </row>
-    <row r="360" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
         <v>44</v>
       </c>
@@ -5915,7 +5920,7 @@
       <c r="D360" s="5"/>
       <c r="E360" s="11"/>
     </row>
-    <row r="361" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
         <v>44</v>
       </c>
@@ -5928,7 +5933,7 @@
       <c r="D361" s="5"/>
       <c r="E361" s="11"/>
     </row>
-    <row r="362" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
         <v>44</v>
       </c>
@@ -5941,7 +5946,7 @@
       <c r="D362" s="5"/>
       <c r="E362" s="11"/>
     </row>
-    <row r="363" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
         <v>44</v>
       </c>
@@ -5954,7 +5959,7 @@
       <c r="D363" s="5"/>
       <c r="E363" s="11"/>
     </row>
-    <row r="364" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
         <v>44</v>
       </c>
@@ -5967,7 +5972,7 @@
       <c r="D364" s="5"/>
       <c r="E364" s="11"/>
     </row>
-    <row r="365" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
         <v>44</v>
       </c>
@@ -5980,7 +5985,7 @@
       <c r="D365" s="5"/>
       <c r="E365" s="11"/>
     </row>
-    <row r="366" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
         <v>44</v>
       </c>
@@ -5993,7 +5998,7 @@
       <c r="D366" s="5"/>
       <c r="E366" s="11"/>
     </row>
-    <row r="367" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
         <v>44</v>
       </c>
@@ -6006,7 +6011,7 @@
       <c r="D367" s="5"/>
       <c r="E367" s="11"/>
     </row>
-    <row r="368" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
         <v>44</v>
       </c>
@@ -6019,7 +6024,7 @@
       <c r="D368" s="5"/>
       <c r="E368" s="11"/>
     </row>
-    <row r="369" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
         <v>44</v>
       </c>
@@ -6032,7 +6037,7 @@
       <c r="D369" s="5"/>
       <c r="E369" s="11"/>
     </row>
-    <row r="370" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
         <v>44</v>
       </c>
@@ -6045,7 +6050,7 @@
       <c r="D370" s="5"/>
       <c r="E370" s="11"/>
     </row>
-    <row r="371" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
         <v>44</v>
       </c>
@@ -6058,7 +6063,7 @@
       <c r="D371" s="5"/>
       <c r="E371" s="11"/>
     </row>
-    <row r="372" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
         <v>44</v>
       </c>
@@ -6071,7 +6076,7 @@
       <c r="D372" s="5"/>
       <c r="E372" s="11"/>
     </row>
-    <row r="373" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
         <v>44</v>
       </c>
@@ -6084,7 +6089,7 @@
       <c r="D373" s="5"/>
       <c r="E373" s="11"/>
     </row>
-    <row r="374" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
         <v>44</v>
       </c>
@@ -6097,7 +6102,7 @@
       <c r="D374" s="5"/>
       <c r="E374" s="11"/>
     </row>
-    <row r="375" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
         <v>44</v>
       </c>
@@ -6110,7 +6115,7 @@
       <c r="D375" s="5"/>
       <c r="E375" s="11"/>
     </row>
-    <row r="376" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
         <v>44</v>
       </c>
@@ -6123,7 +6128,7 @@
       <c r="D376" s="5"/>
       <c r="E376" s="11"/>
     </row>
-    <row r="377" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>44</v>
       </c>
@@ -6140,7 +6145,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="378" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>44</v>
       </c>
@@ -6153,7 +6158,7 @@
       <c r="D378" s="5"/>
       <c r="E378" s="11"/>
     </row>
-    <row r="379" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>44</v>
       </c>
@@ -6166,7 +6171,7 @@
       <c r="D379" s="5"/>
       <c r="E379" s="11"/>
     </row>
-    <row r="380" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>44</v>
       </c>
@@ -6179,7 +6184,7 @@
       <c r="D380" s="5"/>
       <c r="E380" s="11"/>
     </row>
-    <row r="381" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>44</v>
       </c>
@@ -6192,7 +6197,7 @@
       <c r="D381" s="5"/>
       <c r="E381" s="11"/>
     </row>
-    <row r="382" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>44</v>
       </c>
@@ -6205,7 +6210,7 @@
       <c r="D382" s="5"/>
       <c r="E382" s="11"/>
     </row>
-    <row r="383" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
         <v>44</v>
       </c>
@@ -6218,7 +6223,7 @@
       <c r="D383" s="5"/>
       <c r="E383" s="11"/>
     </row>
-    <row r="384" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
         <v>44</v>
       </c>
@@ -6231,7 +6236,7 @@
       <c r="D384" s="5"/>
       <c r="E384" s="11"/>
     </row>
-    <row r="385" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
         <v>44</v>
       </c>
@@ -6244,7 +6249,7 @@
       <c r="D385" s="5"/>
       <c r="E385" s="11"/>
     </row>
-    <row r="386" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
         <v>44</v>
       </c>
@@ -6257,7 +6262,7 @@
       <c r="D386" s="5"/>
       <c r="E386" s="11"/>
     </row>
-    <row r="387" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
         <v>44</v>
       </c>
@@ -6270,7 +6275,7 @@
       <c r="D387" s="5"/>
       <c r="E387" s="11"/>
     </row>
-    <row r="388" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
         <v>44</v>
       </c>
@@ -6283,7 +6288,7 @@
       <c r="D388" s="5"/>
       <c r="E388" s="11"/>
     </row>
-    <row r="389" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
         <v>44</v>
       </c>
@@ -6296,7 +6301,7 @@
       <c r="D389" s="5"/>
       <c r="E389" s="11"/>
     </row>
-    <row r="390" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
         <v>44</v>
       </c>
@@ -6309,7 +6314,7 @@
       <c r="D390" s="5"/>
       <c r="E390" s="11"/>
     </row>
-    <row r="391" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
         <v>44</v>
       </c>
@@ -6322,7 +6327,7 @@
       <c r="D391" s="5"/>
       <c r="E391" s="11"/>
     </row>
-    <row r="392" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
         <v>44</v>
       </c>
@@ -6335,7 +6340,7 @@
       <c r="D392" s="5"/>
       <c r="E392" s="11"/>
     </row>
-    <row r="393" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
         <v>44</v>
       </c>
@@ -6348,7 +6353,7 @@
       <c r="D393" s="5"/>
       <c r="E393" s="11"/>
     </row>
-    <row r="394" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
         <v>44</v>
       </c>
@@ -6361,7 +6366,7 @@
       <c r="D394" s="5"/>
       <c r="E394" s="11"/>
     </row>
-    <row r="395" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
         <v>44</v>
       </c>
@@ -6374,7 +6379,7 @@
       <c r="D395" s="5"/>
       <c r="E395" s="11"/>
     </row>
-    <row r="396" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
         <v>44</v>
       </c>
@@ -6387,7 +6392,7 @@
       <c r="D396" s="5"/>
       <c r="E396" s="11"/>
     </row>
-    <row r="397" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>44</v>
       </c>
@@ -6400,7 +6405,7 @@
       <c r="D397" s="5"/>
       <c r="E397" s="11"/>
     </row>
-    <row r="398" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>44</v>
       </c>
@@ -6413,7 +6418,7 @@
       <c r="D398" s="5"/>
       <c r="E398" s="11"/>
     </row>
-    <row r="399" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
         <v>44</v>
       </c>
@@ -6426,7 +6431,7 @@
       <c r="D399" s="5"/>
       <c r="E399" s="11"/>
     </row>
-    <row r="400" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
         <v>44</v>
       </c>
@@ -6439,7 +6444,7 @@
       <c r="D400" s="5"/>
       <c r="E400" s="11"/>
     </row>
-    <row r="401" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>44</v>
       </c>
@@ -6452,7 +6457,7 @@
       <c r="D401" s="5"/>
       <c r="E401" s="11"/>
     </row>
-    <row r="402" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>44</v>
       </c>
@@ -6465,7 +6470,7 @@
       <c r="D402" s="5"/>
       <c r="E402" s="11"/>
     </row>
-    <row r="403" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>44</v>
       </c>
@@ -6478,7 +6483,7 @@
       <c r="D403" s="5"/>
       <c r="E403" s="11"/>
     </row>
-    <row r="404" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>44</v>
       </c>
@@ -6491,7 +6496,7 @@
       <c r="D404" s="5"/>
       <c r="E404" s="11"/>
     </row>
-    <row r="405" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
         <v>44</v>
       </c>
@@ -6504,7 +6509,7 @@
       <c r="D405" s="5"/>
       <c r="E405" s="11"/>
     </row>
-    <row r="406" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>44</v>
       </c>
@@ -6517,7 +6522,7 @@
       <c r="D406" s="5"/>
       <c r="E406" s="11"/>
     </row>
-    <row r="407" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>44</v>
       </c>
@@ -6530,7 +6535,7 @@
       <c r="D407" s="5"/>
       <c r="E407" s="11"/>
     </row>
-    <row r="408" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>44</v>
       </c>
@@ -6543,7 +6548,7 @@
       <c r="D408" s="5"/>
       <c r="E408" s="11"/>
     </row>
-    <row r="409" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>44</v>
       </c>
@@ -6556,7 +6561,7 @@
       <c r="D409" s="5"/>
       <c r="E409" s="11"/>
     </row>
-    <row r="410" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>44</v>
       </c>
@@ -6569,7 +6574,7 @@
       <c r="D410" s="5"/>
       <c r="E410" s="11"/>
     </row>
-    <row r="411" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>44</v>
       </c>
@@ -6582,7 +6587,7 @@
       <c r="D411" s="5"/>
       <c r="E411" s="11"/>
     </row>
-    <row r="412" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>44</v>
       </c>
@@ -6595,7 +6600,7 @@
       <c r="D412" s="5"/>
       <c r="E412" s="11"/>
     </row>
-    <row r="413" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
         <v>44</v>
       </c>
@@ -6608,7 +6613,7 @@
       <c r="D413" s="5"/>
       <c r="E413" s="11"/>
     </row>
-    <row r="414" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
         <v>44</v>
       </c>
@@ -6621,7 +6626,7 @@
       <c r="D414" s="5"/>
       <c r="E414" s="11"/>
     </row>
-    <row r="415" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
         <v>44</v>
       </c>
@@ -6634,7 +6639,7 @@
       <c r="D415" s="5"/>
       <c r="E415" s="11"/>
     </row>
-    <row r="416" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
         <v>44</v>
       </c>
@@ -6647,7 +6652,7 @@
       <c r="D416" s="5"/>
       <c r="E416" s="11"/>
     </row>
-    <row r="417" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
         <v>44</v>
       </c>
@@ -6660,7 +6665,7 @@
       <c r="D417" s="5"/>
       <c r="E417" s="11"/>
     </row>
-    <row r="418" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
         <v>44</v>
       </c>
@@ -6673,7 +6678,7 @@
       <c r="D418" s="5"/>
       <c r="E418" s="11"/>
     </row>
-    <row r="419" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
         <v>44</v>
       </c>
@@ -6686,7 +6691,7 @@
       <c r="D419" s="5"/>
       <c r="E419" s="11"/>
     </row>
-    <row r="420" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
         <v>44</v>
       </c>
@@ -6699,7 +6704,7 @@
       <c r="D420" s="5"/>
       <c r="E420" s="11"/>
     </row>
-    <row r="421" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
         <v>44</v>
       </c>
@@ -6712,7 +6717,7 @@
       <c r="D421" s="5"/>
       <c r="E421" s="11"/>
     </row>
-    <row r="422" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
         <v>44</v>
       </c>
@@ -6725,7 +6730,7 @@
       <c r="D422" s="5"/>
       <c r="E422" s="11"/>
     </row>
-    <row r="423" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
         <v>44</v>
       </c>
@@ -6738,7 +6743,7 @@
       <c r="D423" s="5"/>
       <c r="E423" s="11"/>
     </row>
-    <row r="424" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
         <v>44</v>
       </c>
@@ -6751,7 +6756,7 @@
       <c r="D424" s="5"/>
       <c r="E424" s="11"/>
     </row>
-    <row r="425" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
         <v>44</v>
       </c>
@@ -6764,7 +6769,7 @@
       <c r="D425" s="5"/>
       <c r="E425" s="11"/>
     </row>
-    <row r="426" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
         <v>44</v>
       </c>
@@ -6777,7 +6782,7 @@
       <c r="D426" s="5"/>
       <c r="E426" s="11"/>
     </row>
-    <row r="427" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
         <v>44</v>
       </c>
@@ -6790,7 +6795,7 @@
       <c r="D427" s="5"/>
       <c r="E427" s="11"/>
     </row>
-    <row r="428" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
         <v>44</v>
       </c>
@@ -6803,7 +6808,7 @@
       <c r="D428" s="5"/>
       <c r="E428" s="11"/>
     </row>
-    <row r="429" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
         <v>44</v>
       </c>
@@ -6816,7 +6821,7 @@
       <c r="D429" s="5"/>
       <c r="E429" s="11"/>
     </row>
-    <row r="430" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
         <v>44</v>
       </c>
@@ -6829,7 +6834,7 @@
       <c r="D430" s="5"/>
       <c r="E430" s="11"/>
     </row>
-    <row r="431" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
         <v>44</v>
       </c>
@@ -6842,7 +6847,7 @@
       <c r="D431" s="5"/>
       <c r="E431" s="11"/>
     </row>
-    <row r="432" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
         <v>44</v>
       </c>
@@ -6859,7 +6864,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="433" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
         <v>44</v>
       </c>
@@ -6872,7 +6877,7 @@
       <c r="D433" s="5"/>
       <c r="E433" s="11"/>
     </row>
-    <row r="434" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
         <v>44</v>
       </c>
@@ -6889,7 +6894,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="435" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
         <v>44</v>
       </c>
@@ -6906,7 +6911,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="436" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
         <v>44</v>
       </c>
@@ -6916,10 +6921,14 @@
       <c r="C436" s="4">
         <v>5</v>
       </c>
-      <c r="D436" s="5"/>
-      <c r="E436" s="11"/>
-    </row>
-    <row r="437" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D436" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E436" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
         <v>44</v>
       </c>
@@ -6932,7 +6941,7 @@
       <c r="D437" s="5"/>
       <c r="E437" s="11"/>
     </row>
-    <row r="438" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
         <v>44</v>
       </c>
@@ -6945,7 +6954,7 @@
       <c r="D438" s="5"/>
       <c r="E438" s="11"/>
     </row>
-    <row r="439" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
         <v>44</v>
       </c>
@@ -6958,7 +6967,7 @@
       <c r="D439" s="5"/>
       <c r="E439" s="11"/>
     </row>
-    <row r="440" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
         <v>44</v>
       </c>
@@ -6971,7 +6980,7 @@
       <c r="D440" s="5"/>
       <c r="E440" s="11"/>
     </row>
-    <row r="441" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
         <v>44</v>
       </c>
@@ -6984,7 +6993,7 @@
       <c r="D441" s="5"/>
       <c r="E441" s="11"/>
     </row>
-    <row r="442" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
         <v>44</v>
       </c>
@@ -6997,7 +7006,7 @@
       <c r="D442" s="5"/>
       <c r="E442" s="11"/>
     </row>
-    <row r="443" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
         <v>44</v>
       </c>
@@ -7010,7 +7019,7 @@
       <c r="D443" s="5"/>
       <c r="E443" s="11"/>
     </row>
-    <row r="444" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
         <v>44</v>
       </c>
@@ -7023,7 +7032,7 @@
       <c r="D444" s="5"/>
       <c r="E444" s="11"/>
     </row>
-    <row r="445" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
         <v>44</v>
       </c>
@@ -7036,7 +7045,7 @@
       <c r="D445" s="5"/>
       <c r="E445" s="11"/>
     </row>
-    <row r="446" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
         <v>44</v>
       </c>
@@ -7049,7 +7058,7 @@
       <c r="D446" s="5"/>
       <c r="E446" s="11"/>
     </row>
-    <row r="447" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
         <v>44</v>
       </c>
@@ -7062,7 +7071,7 @@
       <c r="D447" s="5"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
         <v>44</v>
       </c>
@@ -7075,7 +7084,7 @@
       <c r="D448" s="5"/>
       <c r="E448" s="11"/>
     </row>
-    <row r="449" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
         <v>44</v>
       </c>
@@ -7088,7 +7097,7 @@
       <c r="D449" s="5"/>
       <c r="E449" s="11"/>
     </row>
-    <row r="450" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
         <v>44</v>
       </c>
@@ -7101,7 +7110,7 @@
       <c r="D450" s="5"/>
       <c r="E450" s="11"/>
     </row>
-    <row r="451" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
         <v>44</v>
       </c>
@@ -7114,7 +7123,7 @@
       <c r="D451" s="5"/>
       <c r="E451" s="11"/>
     </row>
-    <row r="452" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
         <v>44</v>
       </c>
@@ -7127,7 +7136,7 @@
       <c r="D452" s="5"/>
       <c r="E452" s="11"/>
     </row>
-    <row r="453" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
         <v>44</v>
       </c>
@@ -7140,7 +7149,7 @@
       <c r="D453" s="5"/>
       <c r="E453" s="11"/>
     </row>
-    <row r="454" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
         <v>44</v>
       </c>
@@ -7153,7 +7162,7 @@
       <c r="D454" s="5"/>
       <c r="E454" s="11"/>
     </row>
-    <row r="455" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
         <v>44</v>
       </c>
@@ -7166,7 +7175,7 @@
       <c r="D455" s="5"/>
       <c r="E455" s="11"/>
     </row>
-    <row r="456" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
         <v>44</v>
       </c>
@@ -7179,7 +7188,7 @@
       <c r="D456" s="5"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
         <v>44</v>
       </c>
@@ -7192,7 +7201,7 @@
       <c r="D457" s="5"/>
       <c r="E457" s="11"/>
     </row>
-    <row r="458" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
         <v>44</v>
       </c>
@@ -7205,7 +7214,7 @@
       <c r="D458" s="5"/>
       <c r="E458" s="11"/>
     </row>
-    <row r="459" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
         <v>44</v>
       </c>
@@ -7218,7 +7227,7 @@
       <c r="D459" s="5"/>
       <c r="E459" s="11"/>
     </row>
-    <row r="460" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
         <v>44</v>
       </c>
@@ -7231,7 +7240,7 @@
       <c r="D460" s="5"/>
       <c r="E460" s="11"/>
     </row>
-    <row r="461" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
         <v>44</v>
       </c>
@@ -7244,7 +7253,7 @@
       <c r="D461" s="5"/>
       <c r="E461" s="11"/>
     </row>
-    <row r="462" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
         <v>44</v>
       </c>
@@ -7257,7 +7266,7 @@
       <c r="D462" s="5"/>
       <c r="E462" s="11"/>
     </row>
-    <row r="463" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
         <v>44</v>
       </c>
@@ -7270,7 +7279,7 @@
       <c r="D463" s="5"/>
       <c r="E463" s="11"/>
     </row>
-    <row r="464" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
         <v>44</v>
       </c>
@@ -7283,7 +7292,7 @@
       <c r="D464" s="5"/>
       <c r="E464" s="11"/>
     </row>
-    <row r="465" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
         <v>44</v>
       </c>
@@ -7296,7 +7305,7 @@
       <c r="D465" s="5"/>
       <c r="E465" s="11"/>
     </row>
-    <row r="466" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
         <v>44</v>
       </c>
@@ -7309,7 +7318,7 @@
       <c r="D466" s="5"/>
       <c r="E466" s="11"/>
     </row>
-    <row r="467" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
         <v>44</v>
       </c>
@@ -7322,7 +7331,7 @@
       <c r="D467" s="5"/>
       <c r="E467" s="11"/>
     </row>
-    <row r="468" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
         <v>44</v>
       </c>
@@ -7335,7 +7344,7 @@
       <c r="D468" s="5"/>
       <c r="E468" s="11"/>
     </row>
-    <row r="469" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
         <v>44</v>
       </c>
@@ -7348,7 +7357,7 @@
       <c r="D469" s="5"/>
       <c r="E469" s="11"/>
     </row>
-    <row r="470" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
         <v>44</v>
       </c>
@@ -7361,7 +7370,7 @@
       <c r="D470" s="5"/>
       <c r="E470" s="11"/>
     </row>
-    <row r="471" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
         <v>44</v>
       </c>
@@ -7374,7 +7383,7 @@
       <c r="D471" s="5"/>
       <c r="E471" s="11"/>
     </row>
-    <row r="472" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
         <v>44</v>
       </c>
@@ -7387,7 +7396,7 @@
       <c r="D472" s="5"/>
       <c r="E472" s="11"/>
     </row>
-    <row r="473" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
         <v>44</v>
       </c>
@@ -7400,7 +7409,7 @@
       <c r="D473" s="5"/>
       <c r="E473" s="11"/>
     </row>
-    <row r="474" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
         <v>44</v>
       </c>
@@ -7413,7 +7422,7 @@
       <c r="D474" s="5"/>
       <c r="E474" s="11"/>
     </row>
-    <row r="475" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
         <v>44</v>
       </c>
@@ -7426,7 +7435,7 @@
       <c r="D475" s="5"/>
       <c r="E475" s="11"/>
     </row>
-    <row r="476" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
         <v>44</v>
       </c>
@@ -7439,7 +7448,7 @@
       <c r="D476" s="5"/>
       <c r="E476" s="11"/>
     </row>
-    <row r="477" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
         <v>44</v>
       </c>
@@ -7452,7 +7461,7 @@
       <c r="D477" s="5"/>
       <c r="E477" s="11"/>
     </row>
-    <row r="478" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
         <v>44</v>
       </c>
@@ -7465,7 +7474,7 @@
       <c r="D478" s="5"/>
       <c r="E478" s="11"/>
     </row>
-    <row r="479" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
         <v>44</v>
       </c>
@@ -7478,7 +7487,7 @@
       <c r="D479" s="5"/>
       <c r="E479" s="11"/>
     </row>
-    <row r="480" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
         <v>44</v>
       </c>
@@ -7491,7 +7500,7 @@
       <c r="D480" s="5"/>
       <c r="E480" s="11"/>
     </row>
-    <row r="481" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
         <v>44</v>
       </c>
@@ -7504,7 +7513,7 @@
       <c r="D481" s="5"/>
       <c r="E481" s="11"/>
     </row>
-    <row r="482" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
         <v>44</v>
       </c>
@@ -7517,7 +7526,7 @@
       <c r="D482" s="5"/>
       <c r="E482" s="11"/>
     </row>
-    <row r="483" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
         <v>44</v>
       </c>
@@ -7530,7 +7539,7 @@
       <c r="D483" s="5"/>
       <c r="E483" s="11"/>
     </row>
-    <row r="484" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
         <v>44</v>
       </c>
@@ -7543,7 +7552,7 @@
       <c r="D484" s="5"/>
       <c r="E484" s="11"/>
     </row>
-    <row r="485" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
         <v>44</v>
       </c>
@@ -7556,7 +7565,7 @@
       <c r="D485" s="5"/>
       <c r="E485" s="11"/>
     </row>
-    <row r="486" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
         <v>44</v>
       </c>
@@ -7569,7 +7578,7 @@
       <c r="D486" s="5"/>
       <c r="E486" s="11"/>
     </row>
-    <row r="487" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="4" t="s">
         <v>44</v>
       </c>
@@ -7582,7 +7591,7 @@
       <c r="D487" s="5"/>
       <c r="E487" s="11"/>
     </row>
-    <row r="488" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="4" t="s">
         <v>44</v>
       </c>
@@ -7595,7 +7604,7 @@
       <c r="D488" s="5"/>
       <c r="E488" s="11"/>
     </row>
-    <row r="489" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="4" t="s">
         <v>44</v>
       </c>
@@ -7608,7 +7617,7 @@
       <c r="D489" s="5"/>
       <c r="E489" s="11"/>
     </row>
-    <row r="490" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="4" t="s">
         <v>44</v>
       </c>
@@ -7621,7 +7630,7 @@
       <c r="D490" s="5"/>
       <c r="E490" s="11"/>
     </row>
-    <row r="491" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
         <v>44</v>
       </c>
@@ -7634,7 +7643,7 @@
       <c r="D491" s="5"/>
       <c r="E491" s="11"/>
     </row>
-    <row r="492" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
         <v>44</v>
       </c>
@@ -7647,7 +7656,7 @@
       <c r="D492" s="5"/>
       <c r="E492" s="11"/>
     </row>
-    <row r="493" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
         <v>44</v>
       </c>
@@ -7660,7 +7669,7 @@
       <c r="D493" s="5"/>
       <c r="E493" s="11"/>
     </row>
-    <row r="494" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="4" t="s">
         <v>44</v>
       </c>
@@ -7673,7 +7682,7 @@
       <c r="D494" s="5"/>
       <c r="E494" s="11"/>
     </row>
-    <row r="495" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="4" t="s">
         <v>44</v>
       </c>
@@ -7686,7 +7695,7 @@
       <c r="D495" s="5"/>
       <c r="E495" s="11"/>
     </row>
-    <row r="496" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="4" t="s">
         <v>44</v>
       </c>
@@ -7699,7 +7708,7 @@
       <c r="D496" s="5"/>
       <c r="E496" s="11"/>
     </row>
-    <row r="497" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="4" t="s">
         <v>44</v>
       </c>
@@ -7712,7 +7721,7 @@
       <c r="D497" s="5"/>
       <c r="E497" s="11"/>
     </row>
-    <row r="498" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="4" t="s">
         <v>44</v>
       </c>
@@ -7725,7 +7734,7 @@
       <c r="D498" s="5"/>
       <c r="E498" s="11"/>
     </row>
-    <row r="499" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="4" t="s">
         <v>44</v>
       </c>
@@ -7738,7 +7747,7 @@
       <c r="D499" s="5"/>
       <c r="E499" s="11"/>
     </row>
-    <row r="500" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="4" t="s">
         <v>44</v>
       </c>
@@ -7751,7 +7760,7 @@
       <c r="D500" s="5"/>
       <c r="E500" s="11"/>
     </row>
-    <row r="501" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="4" t="s">
         <v>44</v>
       </c>
@@ -7764,7 +7773,7 @@
       <c r="D501" s="5"/>
       <c r="E501" s="11"/>
     </row>
-    <row r="502" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="4" t="s">
         <v>44</v>
       </c>
@@ -7777,7 +7786,7 @@
       <c r="D502" s="5"/>
       <c r="E502" s="11"/>
     </row>
-    <row r="503" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="4" t="s">
         <v>44</v>
       </c>
@@ -7790,7 +7799,7 @@
       <c r="D503" s="5"/>
       <c r="E503" s="11"/>
     </row>
-    <row r="504" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="4" t="s">
         <v>44</v>
       </c>
@@ -7803,7 +7812,7 @@
       <c r="D504" s="5"/>
       <c r="E504" s="11"/>
     </row>
-    <row r="505" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="4" t="s">
         <v>44</v>
       </c>
@@ -7816,7 +7825,7 @@
       <c r="D505" s="5"/>
       <c r="E505" s="11"/>
     </row>
-    <row r="506" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="4" t="s">
         <v>44</v>
       </c>
@@ -7829,7 +7838,7 @@
       <c r="D506" s="5"/>
       <c r="E506" s="11"/>
     </row>
-    <row r="507" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="4" t="s">
         <v>44</v>
       </c>
@@ -7842,7 +7851,7 @@
       <c r="D507" s="5"/>
       <c r="E507" s="11"/>
     </row>
-    <row r="508" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
         <v>44</v>
       </c>
@@ -7855,7 +7864,7 @@
       <c r="D508" s="5"/>
       <c r="E508" s="11"/>
     </row>
-    <row r="509" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="s">
         <v>44</v>
       </c>
@@ -7868,7 +7877,7 @@
       <c r="D509" s="5"/>
       <c r="E509" s="11"/>
     </row>
-    <row r="510" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="4" t="s">
         <v>44</v>
       </c>
@@ -7881,7 +7890,7 @@
       <c r="D510" s="5"/>
       <c r="E510" s="11"/>
     </row>
-    <row r="511" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="4" t="s">
         <v>44</v>
       </c>
@@ -7894,7 +7903,7 @@
       <c r="D511" s="5"/>
       <c r="E511" s="11"/>
     </row>
-    <row r="512" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="4" t="s">
         <v>44</v>
       </c>
@@ -7907,7 +7916,7 @@
       <c r="D512" s="5"/>
       <c r="E512" s="11"/>
     </row>
-    <row r="513" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="4" t="s">
         <v>44</v>
       </c>
@@ -7920,7 +7929,7 @@
       <c r="D513" s="5"/>
       <c r="E513" s="11"/>
     </row>
-    <row r="514" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="4" t="s">
         <v>44</v>
       </c>
@@ -7933,7 +7942,7 @@
       <c r="D514" s="5"/>
       <c r="E514" s="11"/>
     </row>
-    <row r="515" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="4" t="s">
         <v>44</v>
       </c>
@@ -7946,7 +7955,7 @@
       <c r="D515" s="5"/>
       <c r="E515" s="11"/>
     </row>
-    <row r="516" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="4" t="s">
         <v>44</v>
       </c>
@@ -7959,7 +7968,7 @@
       <c r="D516" s="5"/>
       <c r="E516" s="11"/>
     </row>
-    <row r="517" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="4" t="s">
         <v>44</v>
       </c>
@@ -7972,7 +7981,7 @@
       <c r="D517" s="5"/>
       <c r="E517" s="11"/>
     </row>
-    <row r="518" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="4" t="s">
         <v>44</v>
       </c>
@@ -7985,7 +7994,7 @@
       <c r="D518" s="5"/>
       <c r="E518" s="11"/>
     </row>
-    <row r="519" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="4" t="s">
         <v>44</v>
       </c>
@@ -7998,7 +8007,7 @@
       <c r="D519" s="5"/>
       <c r="E519" s="11"/>
     </row>
-    <row r="520" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="4" t="s">
         <v>44</v>
       </c>
@@ -8011,7 +8020,7 @@
       <c r="D520" s="5"/>
       <c r="E520" s="11"/>
     </row>
-    <row r="521" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="4" t="s">
         <v>44</v>
       </c>
@@ -8024,7 +8033,7 @@
       <c r="D521" s="5"/>
       <c r="E521" s="11"/>
     </row>
-    <row r="522" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="4" t="s">
         <v>44</v>
       </c>
@@ -8037,7 +8046,7 @@
       <c r="D522" s="5"/>
       <c r="E522" s="11"/>
     </row>
-    <row r="523" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="4" t="s">
         <v>44</v>
       </c>
@@ -8050,7 +8059,7 @@
       <c r="D523" s="5"/>
       <c r="E523" s="11"/>
     </row>
-    <row r="524" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="4" t="s">
         <v>44</v>
       </c>
@@ -8063,7 +8072,7 @@
       <c r="D524" s="5"/>
       <c r="E524" s="11"/>
     </row>
-    <row r="525" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="4" t="s">
         <v>44</v>
       </c>
@@ -8076,7 +8085,7 @@
       <c r="D525" s="5"/>
       <c r="E525" s="11"/>
     </row>
-    <row r="526" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="4" t="s">
         <v>44</v>
       </c>
@@ -8089,7 +8098,7 @@
       <c r="D526" s="5"/>
       <c r="E526" s="11"/>
     </row>
-    <row r="527" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="4" t="s">
         <v>44</v>
       </c>
@@ -8102,7 +8111,7 @@
       <c r="D527" s="5"/>
       <c r="E527" s="11"/>
     </row>
-    <row r="528" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="4" t="s">
         <v>44</v>
       </c>
@@ -8115,7 +8124,7 @@
       <c r="D528" s="5"/>
       <c r="E528" s="11"/>
     </row>
-    <row r="529" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="4" t="s">
         <v>44</v>
       </c>
@@ -8128,7 +8137,7 @@
       <c r="D529" s="5"/>
       <c r="E529" s="11"/>
     </row>
-    <row r="530" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="4" t="s">
         <v>44</v>
       </c>
@@ -8141,7 +8150,7 @@
       <c r="D530" s="5"/>
       <c r="E530" s="11"/>
     </row>
-    <row r="531" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="4" t="s">
         <v>44</v>
       </c>
@@ -8154,7 +8163,7 @@
       <c r="D531" s="5"/>
       <c r="E531" s="11"/>
     </row>
-    <row r="532" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="4" t="s">
         <v>44</v>
       </c>
@@ -8167,7 +8176,7 @@
       <c r="D532" s="5"/>
       <c r="E532" s="11"/>
     </row>
-    <row r="533" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="4" t="s">
         <v>44</v>
       </c>
@@ -8180,7 +8189,7 @@
       <c r="D533" s="5"/>
       <c r="E533" s="11"/>
     </row>
-    <row r="534" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="4" t="s">
         <v>44</v>
       </c>
@@ -8193,7 +8202,7 @@
       <c r="D534" s="5"/>
       <c r="E534" s="11"/>
     </row>
-    <row r="535" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="4" t="s">
         <v>44</v>
       </c>
@@ -8206,7 +8215,7 @@
       <c r="D535" s="5"/>
       <c r="E535" s="11"/>
     </row>
-    <row r="536" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="4" t="s">
         <v>44</v>
       </c>
@@ -8219,7 +8228,7 @@
       <c r="D536" s="5"/>
       <c r="E536" s="11"/>
     </row>
-    <row r="537" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="4" t="s">
         <v>44</v>
       </c>
@@ -8232,7 +8241,7 @@
       <c r="D537" s="5"/>
       <c r="E537" s="11"/>
     </row>
-    <row r="538" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="4" t="s">
         <v>44</v>
       </c>
@@ -8245,7 +8254,7 @@
       <c r="D538" s="5"/>
       <c r="E538" s="11"/>
     </row>
-    <row r="539" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="4" t="s">
         <v>44</v>
       </c>
@@ -8258,7 +8267,7 @@
       <c r="D539" s="5"/>
       <c r="E539" s="11"/>
     </row>
-    <row r="540" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="4" t="s">
         <v>44</v>
       </c>
@@ -8271,7 +8280,7 @@
       <c r="D540" s="5"/>
       <c r="E540" s="11"/>
     </row>
-    <row r="541" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="4" t="s">
         <v>44</v>
       </c>
@@ -8284,7 +8293,7 @@
       <c r="D541" s="5"/>
       <c r="E541" s="11"/>
     </row>
-    <row r="542" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="4" t="s">
         <v>44</v>
       </c>
@@ -8297,7 +8306,7 @@
       <c r="D542" s="5"/>
       <c r="E542" s="11"/>
     </row>
-    <row r="543" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="4" t="s">
         <v>44</v>
       </c>
@@ -8310,7 +8319,7 @@
       <c r="D543" s="5"/>
       <c r="E543" s="11"/>
     </row>
-    <row r="544" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="4" t="s">
         <v>44</v>
       </c>
@@ -8323,7 +8332,7 @@
       <c r="D544" s="5"/>
       <c r="E544" s="11"/>
     </row>
-    <row r="545" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="4" t="s">
         <v>44</v>
       </c>
@@ -8336,7 +8345,7 @@
       <c r="D545" s="5"/>
       <c r="E545" s="11"/>
     </row>
-    <row r="546" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="4" t="s">
         <v>45</v>
       </c>
@@ -8349,7 +8358,7 @@
       <c r="D546" s="5"/>
       <c r="E546" s="11"/>
     </row>
-    <row r="547" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="4" t="s">
         <v>45</v>
       </c>
@@ -8362,7 +8371,7 @@
       <c r="D547" s="5"/>
       <c r="E547" s="11"/>
     </row>
-    <row r="548" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="4" t="s">
         <v>45</v>
       </c>
@@ -8375,7 +8384,7 @@
       <c r="D548" s="5"/>
       <c r="E548" s="11"/>
     </row>
-    <row r="549" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="4" t="s">
         <v>45</v>
       </c>
@@ -8388,7 +8397,7 @@
       <c r="D549" s="5"/>
       <c r="E549" s="11"/>
     </row>
-    <row r="550" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="4" t="s">
         <v>45</v>
       </c>
@@ -8401,7 +8410,7 @@
       <c r="D550" s="5"/>
       <c r="E550" s="11"/>
     </row>
-    <row r="551" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="4" t="s">
         <v>45</v>
       </c>
@@ -8414,7 +8423,7 @@
       <c r="D551" s="5"/>
       <c r="E551" s="11"/>
     </row>
-    <row r="552" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
         <v>45</v>
       </c>
@@ -8427,7 +8436,7 @@
       <c r="D552" s="5"/>
       <c r="E552" s="11"/>
     </row>
-    <row r="553" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="4" t="s">
         <v>45</v>
       </c>
@@ -8440,7 +8449,7 @@
       <c r="D553" s="5"/>
       <c r="E553" s="11"/>
     </row>
-    <row r="554" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="4" t="s">
         <v>45</v>
       </c>
@@ -8453,7 +8462,7 @@
       <c r="D554" s="5"/>
       <c r="E554" s="11"/>
     </row>
-    <row r="555" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="4" t="s">
         <v>45</v>
       </c>
@@ -8466,7 +8475,7 @@
       <c r="D555" s="5"/>
       <c r="E555" s="11"/>
     </row>
-    <row r="556" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="4" t="s">
         <v>45</v>
       </c>
@@ -8479,7 +8488,7 @@
       <c r="D556" s="5"/>
       <c r="E556" s="11"/>
     </row>
-    <row r="557" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="4" t="s">
         <v>45</v>
       </c>
@@ -8492,7 +8501,7 @@
       <c r="D557" s="5"/>
       <c r="E557" s="11"/>
     </row>
-    <row r="558" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="4" t="s">
         <v>45</v>
       </c>
@@ -8505,7 +8514,7 @@
       <c r="D558" s="5"/>
       <c r="E558" s="11"/>
     </row>
-    <row r="559" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="4" t="s">
         <v>45</v>
       </c>
@@ -8518,7 +8527,7 @@
       <c r="D559" s="5"/>
       <c r="E559" s="11"/>
     </row>
-    <row r="560" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="4" t="s">
         <v>45</v>
       </c>
@@ -8531,7 +8540,7 @@
       <c r="D560" s="5"/>
       <c r="E560" s="11"/>
     </row>
-    <row r="561" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="4" t="s">
         <v>45</v>
       </c>
@@ -8544,7 +8553,7 @@
       <c r="D561" s="5"/>
       <c r="E561" s="11"/>
     </row>
-    <row r="562" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="4" t="s">
         <v>45</v>
       </c>
@@ -8557,7 +8566,7 @@
       <c r="D562" s="5"/>
       <c r="E562" s="11"/>
     </row>
-    <row r="563" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="4" t="s">
         <v>45</v>
       </c>
@@ -8570,7 +8579,7 @@
       <c r="D563" s="5"/>
       <c r="E563" s="11"/>
     </row>
-    <row r="564" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="4" t="s">
         <v>45</v>
       </c>
@@ -8583,7 +8592,7 @@
       <c r="D564" s="5"/>
       <c r="E564" s="11"/>
     </row>
-    <row r="565" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="4" t="s">
         <v>45</v>
       </c>
@@ -8596,7 +8605,7 @@
       <c r="D565" s="5"/>
       <c r="E565" s="11"/>
     </row>
-    <row r="566" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="4" t="s">
         <v>45</v>
       </c>
@@ -8609,7 +8618,7 @@
       <c r="D566" s="5"/>
       <c r="E566" s="11"/>
     </row>
-    <row r="567" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="4" t="s">
         <v>45</v>
       </c>
@@ -8622,7 +8631,7 @@
       <c r="D567" s="5"/>
       <c r="E567" s="11"/>
     </row>
-    <row r="568" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="4" t="s">
         <v>45</v>
       </c>
@@ -8635,7 +8644,7 @@
       <c r="D568" s="5"/>
       <c r="E568" s="11"/>
     </row>
-    <row r="569" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="4" t="s">
         <v>45</v>
       </c>
@@ -8648,7 +8657,7 @@
       <c r="D569" s="5"/>
       <c r="E569" s="11"/>
     </row>
-    <row r="570" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="4" t="s">
         <v>45</v>
       </c>
@@ -8661,7 +8670,7 @@
       <c r="D570" s="5"/>
       <c r="E570" s="11"/>
     </row>
-    <row r="571" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="4" t="s">
         <v>45</v>
       </c>
@@ -8674,7 +8683,7 @@
       <c r="D571" s="5"/>
       <c r="E571" s="11"/>
     </row>
-    <row r="572" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="4" t="s">
         <v>45</v>
       </c>
@@ -8687,7 +8696,7 @@
       <c r="D572" s="5"/>
       <c r="E572" s="11"/>
     </row>
-    <row r="573" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="4" t="s">
         <v>45</v>
       </c>
@@ -8700,7 +8709,7 @@
       <c r="D573" s="5"/>
       <c r="E573" s="11"/>
     </row>
-    <row r="574" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="4" t="s">
         <v>45</v>
       </c>
@@ -8713,7 +8722,7 @@
       <c r="D574" s="5"/>
       <c r="E574" s="11"/>
     </row>
-    <row r="575" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="4" t="s">
         <v>45</v>
       </c>
@@ -8726,7 +8735,7 @@
       <c r="D575" s="5"/>
       <c r="E575" s="11"/>
     </row>
-    <row r="576" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="4" t="s">
         <v>45</v>
       </c>
@@ -8739,7 +8748,7 @@
       <c r="D576" s="5"/>
       <c r="E576" s="11"/>
     </row>
-    <row r="577" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="4" t="s">
         <v>45</v>
       </c>
@@ -8752,7 +8761,7 @@
       <c r="D577" s="5"/>
       <c r="E577" s="11"/>
     </row>
-    <row r="578" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="4" t="s">
         <v>45</v>
       </c>
@@ -8765,7 +8774,7 @@
       <c r="D578" s="5"/>
       <c r="E578" s="11"/>
     </row>
-    <row r="579" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="4" t="s">
         <v>45</v>
       </c>
@@ -8778,7 +8787,7 @@
       <c r="D579" s="5"/>
       <c r="E579" s="11"/>
     </row>
-    <row r="580" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="4" t="s">
         <v>45</v>
       </c>
@@ -8791,7 +8800,7 @@
       <c r="D580" s="5"/>
       <c r="E580" s="11"/>
     </row>
-    <row r="581" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="4" t="s">
         <v>45</v>
       </c>
@@ -8804,7 +8813,7 @@
       <c r="D581" s="5"/>
       <c r="E581" s="11"/>
     </row>
-    <row r="582" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="4" t="s">
         <v>45</v>
       </c>
@@ -8817,7 +8826,7 @@
       <c r="D582" s="5"/>
       <c r="E582" s="11"/>
     </row>
-    <row r="583" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="4" t="s">
         <v>45</v>
       </c>
@@ -8830,7 +8839,7 @@
       <c r="D583" s="5"/>
       <c r="E583" s="11"/>
     </row>
-    <row r="584" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="4" t="s">
         <v>45</v>
       </c>
@@ -8843,7 +8852,7 @@
       <c r="D584" s="5"/>
       <c r="E584" s="11"/>
     </row>
-    <row r="585" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="4" t="s">
         <v>45</v>
       </c>
@@ -8856,7 +8865,7 @@
       <c r="D585" s="5"/>
       <c r="E585" s="11"/>
     </row>
-    <row r="586" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="4" t="s">
         <v>45</v>
       </c>
@@ -8869,7 +8878,7 @@
       <c r="D586" s="5"/>
       <c r="E586" s="11"/>
     </row>
-    <row r="587" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="4" t="s">
         <v>45</v>
       </c>
@@ -8882,7 +8891,7 @@
       <c r="D587" s="5"/>
       <c r="E587" s="11"/>
     </row>
-    <row r="588" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="4" t="s">
         <v>45</v>
       </c>
@@ -8895,7 +8904,7 @@
       <c r="D588" s="5"/>
       <c r="E588" s="11"/>
     </row>
-    <row r="589" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="4" t="s">
         <v>45</v>
       </c>
@@ -8908,7 +8917,7 @@
       <c r="D589" s="5"/>
       <c r="E589" s="11"/>
     </row>
-    <row r="590" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="4" t="s">
         <v>45</v>
       </c>
@@ -8921,7 +8930,7 @@
       <c r="D590" s="5"/>
       <c r="E590" s="11"/>
     </row>
-    <row r="591" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="4" t="s">
         <v>45</v>
       </c>
@@ -8934,7 +8943,7 @@
       <c r="D591" s="5"/>
       <c r="E591" s="11"/>
     </row>
-    <row r="592" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="4" t="s">
         <v>45</v>
       </c>
@@ -8947,7 +8956,7 @@
       <c r="D592" s="5"/>
       <c r="E592" s="11"/>
     </row>
-    <row r="593" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="4" t="s">
         <v>45</v>
       </c>
@@ -8960,7 +8969,7 @@
       <c r="D593" s="5"/>
       <c r="E593" s="11"/>
     </row>
-    <row r="594" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="4" t="s">
         <v>45</v>
       </c>
@@ -8973,7 +8982,7 @@
       <c r="D594" s="5"/>
       <c r="E594" s="11"/>
     </row>
-    <row r="595" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="4" t="s">
         <v>45</v>
       </c>
@@ -8986,7 +8995,7 @@
       <c r="D595" s="5"/>
       <c r="E595" s="11"/>
     </row>
-    <row r="596" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="4" t="s">
         <v>45</v>
       </c>
@@ -8999,7 +9008,7 @@
       <c r="D596" s="5"/>
       <c r="E596" s="11"/>
     </row>
-    <row r="597" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="4" t="s">
         <v>45</v>
       </c>
@@ -9012,7 +9021,7 @@
       <c r="D597" s="5"/>
       <c r="E597" s="11"/>
     </row>
-    <row r="598" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="4" t="s">
         <v>45</v>
       </c>
@@ -9025,7 +9034,7 @@
       <c r="D598" s="5"/>
       <c r="E598" s="11"/>
     </row>
-    <row r="599" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="4" t="s">
         <v>45</v>
       </c>
@@ -9042,7 +9051,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="4" t="s">
         <v>45</v>
       </c>
@@ -9055,7 +9064,7 @@
       <c r="D600" s="5"/>
       <c r="E600" s="11"/>
     </row>
-    <row r="601" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="4" t="s">
         <v>45</v>
       </c>
@@ -9068,7 +9077,7 @@
       <c r="D601" s="5"/>
       <c r="E601" s="11"/>
     </row>
-    <row r="602" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="4" t="s">
         <v>45</v>
       </c>
@@ -9081,7 +9090,7 @@
       <c r="D602" s="5"/>
       <c r="E602" s="11"/>
     </row>
-    <row r="603" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="4" t="s">
         <v>45</v>
       </c>
@@ -9094,7 +9103,7 @@
       <c r="D603" s="5"/>
       <c r="E603" s="11"/>
     </row>
-    <row r="604" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="4" t="s">
         <v>45</v>
       </c>
@@ -9107,7 +9116,7 @@
       <c r="D604" s="5"/>
       <c r="E604" s="11"/>
     </row>
-    <row r="605" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" s="4" t="s">
         <v>45</v>
       </c>
@@ -9120,7 +9129,7 @@
       <c r="D605" s="5"/>
       <c r="E605" s="11"/>
     </row>
-    <row r="606" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" s="4" t="s">
         <v>45</v>
       </c>
@@ -9133,7 +9142,7 @@
       <c r="D606" s="5"/>
       <c r="E606" s="11"/>
     </row>
-    <row r="607" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" s="4" t="s">
         <v>45</v>
       </c>
@@ -9146,7 +9155,7 @@
       <c r="D607" s="5"/>
       <c r="E607" s="11"/>
     </row>
-    <row r="608" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="4" t="s">
         <v>45</v>
       </c>
@@ -9159,7 +9168,7 @@
       <c r="D608" s="5"/>
       <c r="E608" s="11"/>
     </row>
-    <row r="609" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" s="4" t="s">
         <v>45</v>
       </c>
@@ -9172,7 +9181,7 @@
       <c r="D609" s="5"/>
       <c r="E609" s="11"/>
     </row>
-    <row r="610" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" s="4" t="s">
         <v>45</v>
       </c>
@@ -9185,7 +9194,7 @@
       <c r="D610" s="5"/>
       <c r="E610" s="11"/>
     </row>
-    <row r="611" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="4" t="s">
         <v>45</v>
       </c>
@@ -9198,7 +9207,7 @@
       <c r="D611" s="5"/>
       <c r="E611" s="11"/>
     </row>
-    <row r="612" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="4" t="s">
         <v>45</v>
       </c>
@@ -9211,7 +9220,7 @@
       <c r="D612" s="5"/>
       <c r="E612" s="11"/>
     </row>
-    <row r="613" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="4" t="s">
         <v>45</v>
       </c>
@@ -9224,7 +9233,7 @@
       <c r="D613" s="5"/>
       <c r="E613" s="11"/>
     </row>
-    <row r="614" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="4" t="s">
         <v>45</v>
       </c>
@@ -9237,7 +9246,7 @@
       <c r="D614" s="5"/>
       <c r="E614" s="11"/>
     </row>
-    <row r="615" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" s="4" t="s">
         <v>45</v>
       </c>
@@ -9250,7 +9259,7 @@
       <c r="D615" s="5"/>
       <c r="E615" s="11"/>
     </row>
-    <row r="616" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" s="4" t="s">
         <v>45</v>
       </c>
@@ -9263,7 +9272,7 @@
       <c r="D616" s="5"/>
       <c r="E616" s="11"/>
     </row>
-    <row r="617" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" s="4" t="s">
         <v>45</v>
       </c>
@@ -9276,7 +9285,7 @@
       <c r="D617" s="5"/>
       <c r="E617" s="11"/>
     </row>
-    <row r="618" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" s="4" t="s">
         <v>45</v>
       </c>
@@ -9289,7 +9298,7 @@
       <c r="D618" s="5"/>
       <c r="E618" s="11"/>
     </row>
-    <row r="619" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" s="4" t="s">
         <v>45</v>
       </c>
@@ -9302,7 +9311,7 @@
       <c r="D619" s="5"/>
       <c r="E619" s="11"/>
     </row>
-    <row r="620" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" s="4" t="s">
         <v>45</v>
       </c>
@@ -9315,7 +9324,7 @@
       <c r="D620" s="5"/>
       <c r="E620" s="11"/>
     </row>
-    <row r="621" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" s="4" t="s">
         <v>45</v>
       </c>
@@ -9328,7 +9337,7 @@
       <c r="D621" s="5"/>
       <c r="E621" s="11"/>
     </row>
-    <row r="622" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="4" t="s">
         <v>45</v>
       </c>
@@ -9341,7 +9350,7 @@
       <c r="D622" s="5"/>
       <c r="E622" s="11"/>
     </row>
-    <row r="623" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="4" t="s">
         <v>45</v>
       </c>
@@ -9354,7 +9363,7 @@
       <c r="D623" s="5"/>
       <c r="E623" s="11"/>
     </row>
-    <row r="624" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="4" t="s">
         <v>45</v>
       </c>
@@ -9367,7 +9376,7 @@
       <c r="D624" s="5"/>
       <c r="E624" s="11"/>
     </row>
-    <row r="625" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="4" t="s">
         <v>45</v>
       </c>
@@ -9380,7 +9389,7 @@
       <c r="D625" s="5"/>
       <c r="E625" s="11"/>
     </row>
-    <row r="626" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="4" t="s">
         <v>45</v>
       </c>
@@ -9393,7 +9402,7 @@
       <c r="D626" s="5"/>
       <c r="E626" s="11"/>
     </row>
-    <row r="627" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="4" t="s">
         <v>45</v>
       </c>
@@ -9406,7 +9415,7 @@
       <c r="D627" s="5"/>
       <c r="E627" s="11"/>
     </row>
-    <row r="628" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="4" t="s">
         <v>45</v>
       </c>
@@ -9419,7 +9428,7 @@
       <c r="D628" s="5"/>
       <c r="E628" s="11"/>
     </row>
-    <row r="629" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="4" t="s">
         <v>45</v>
       </c>
@@ -9432,7 +9441,7 @@
       <c r="D629" s="5"/>
       <c r="E629" s="11"/>
     </row>
-    <row r="630" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="4" t="s">
         <v>45</v>
       </c>
@@ -9445,7 +9454,7 @@
       <c r="D630" s="5"/>
       <c r="E630" s="11"/>
     </row>
-    <row r="631" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" s="4" t="s">
         <v>45</v>
       </c>
@@ -9458,7 +9467,7 @@
       <c r="D631" s="5"/>
       <c r="E631" s="11"/>
     </row>
-    <row r="632" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" s="4" t="s">
         <v>45</v>
       </c>
@@ -9471,7 +9480,7 @@
       <c r="D632" s="5"/>
       <c r="E632" s="11"/>
     </row>
-    <row r="633" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" s="4" t="s">
         <v>45</v>
       </c>
@@ -9484,7 +9493,7 @@
       <c r="D633" s="5"/>
       <c r="E633" s="11"/>
     </row>
-    <row r="634" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" s="4" t="s">
         <v>45</v>
       </c>
@@ -9497,7 +9506,7 @@
       <c r="D634" s="5"/>
       <c r="E634" s="11"/>
     </row>
-    <row r="635" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" s="4" t="s">
         <v>45</v>
       </c>
@@ -9510,7 +9519,7 @@
       <c r="D635" s="5"/>
       <c r="E635" s="11"/>
     </row>
-    <row r="636" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" s="4" t="s">
         <v>45</v>
       </c>
@@ -9523,7 +9532,7 @@
       <c r="D636" s="5"/>
       <c r="E636" s="11"/>
     </row>
-    <row r="637" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="4" t="s">
         <v>45</v>
       </c>
@@ -9536,7 +9545,7 @@
       <c r="D637" s="5"/>
       <c r="E637" s="11"/>
     </row>
-    <row r="638" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="4" t="s">
         <v>45</v>
       </c>
@@ -9549,7 +9558,7 @@
       <c r="D638" s="5"/>
       <c r="E638" s="11"/>
     </row>
-    <row r="639" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="4" t="s">
         <v>45</v>
       </c>
@@ -9562,7 +9571,7 @@
       <c r="D639" s="5"/>
       <c r="E639" s="11"/>
     </row>
-    <row r="640" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="4" t="s">
         <v>45</v>
       </c>
@@ -9575,7 +9584,7 @@
       <c r="D640" s="5"/>
       <c r="E640" s="11"/>
     </row>
-    <row r="641" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="4" t="s">
         <v>45</v>
       </c>
@@ -9588,7 +9597,7 @@
       <c r="D641" s="5"/>
       <c r="E641" s="11"/>
     </row>
-    <row r="642" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="4" t="s">
         <v>45</v>
       </c>
@@ -9601,7 +9610,7 @@
       <c r="D642" s="5"/>
       <c r="E642" s="11"/>
     </row>
-    <row r="643" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="4" t="s">
         <v>45</v>
       </c>
@@ -9614,7 +9623,7 @@
       <c r="D643" s="5"/>
       <c r="E643" s="11"/>
     </row>
-    <row r="644" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" s="4" t="s">
         <v>45</v>
       </c>
@@ -9627,7 +9636,7 @@
       <c r="D644" s="5"/>
       <c r="E644" s="11"/>
     </row>
-    <row r="645" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" s="4" t="s">
         <v>45</v>
       </c>
@@ -9640,7 +9649,7 @@
       <c r="D645" s="5"/>
       <c r="E645" s="11"/>
     </row>
-    <row r="646" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" s="4" t="s">
         <v>45</v>
       </c>
@@ -9653,7 +9662,7 @@
       <c r="D646" s="5"/>
       <c r="E646" s="11"/>
     </row>
-    <row r="647" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" s="4" t="s">
         <v>45</v>
       </c>
@@ -9666,7 +9675,7 @@
       <c r="D647" s="5"/>
       <c r="E647" s="11"/>
     </row>
-    <row r="648" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" s="4" t="s">
         <v>45</v>
       </c>
@@ -9679,7 +9688,7 @@
       <c r="D648" s="5"/>
       <c r="E648" s="11"/>
     </row>
-    <row r="649" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" s="4" t="s">
         <v>45</v>
       </c>
@@ -9692,7 +9701,7 @@
       <c r="D649" s="5"/>
       <c r="E649" s="11"/>
     </row>
-    <row r="650" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="4" t="s">
         <v>45</v>
       </c>
@@ -9705,7 +9714,7 @@
       <c r="D650" s="5"/>
       <c r="E650" s="11"/>
     </row>
-    <row r="651" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" s="4" t="s">
         <v>45</v>
       </c>
@@ -9718,7 +9727,7 @@
       <c r="D651" s="5"/>
       <c r="E651" s="11"/>
     </row>
-    <row r="652" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" s="4" t="s">
         <v>45</v>
       </c>
@@ -9731,7 +9740,7 @@
       <c r="D652" s="5"/>
       <c r="E652" s="11"/>
     </row>
-    <row r="653" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" s="4" t="s">
         <v>45</v>
       </c>
@@ -9744,7 +9753,7 @@
       <c r="D653" s="5"/>
       <c r="E653" s="11"/>
     </row>
-    <row r="654" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" s="4" t="s">
         <v>45</v>
       </c>
@@ -9757,7 +9766,7 @@
       <c r="D654" s="5"/>
       <c r="E654" s="11"/>
     </row>
-    <row r="655" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" s="4" t="s">
         <v>45</v>
       </c>
@@ -9770,7 +9779,7 @@
       <c r="D655" s="5"/>
       <c r="E655" s="11"/>
     </row>
-    <row r="656" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" s="4" t="s">
         <v>45</v>
       </c>
@@ -9783,7 +9792,7 @@
       <c r="D656" s="5"/>
       <c r="E656" s="11"/>
     </row>
-    <row r="657" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" s="4" t="s">
         <v>45</v>
       </c>
@@ -9796,7 +9805,7 @@
       <c r="D657" s="5"/>
       <c r="E657" s="11"/>
     </row>
-    <row r="658" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" s="4" t="s">
         <v>45</v>
       </c>
@@ -9809,7 +9818,7 @@
       <c r="D658" s="5"/>
       <c r="E658" s="11"/>
     </row>
-    <row r="659" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" s="4" t="s">
         <v>45</v>
       </c>
@@ -9822,7 +9831,7 @@
       <c r="D659" s="5"/>
       <c r="E659" s="11"/>
     </row>
-    <row r="660" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" s="4" t="s">
         <v>45</v>
       </c>
@@ -9835,7 +9844,7 @@
       <c r="D660" s="5"/>
       <c r="E660" s="11"/>
     </row>
-    <row r="661" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" s="4" t="s">
         <v>45</v>
       </c>
@@ -9848,7 +9857,7 @@
       <c r="D661" s="5"/>
       <c r="E661" s="11"/>
     </row>
-    <row r="662" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" s="4" t="s">
         <v>45</v>
       </c>
@@ -9861,7 +9870,7 @@
       <c r="D662" s="5"/>
       <c r="E662" s="11"/>
     </row>
-    <row r="663" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="4" t="s">
         <v>45</v>
       </c>
@@ -9874,7 +9883,7 @@
       <c r="D663" s="5"/>
       <c r="E663" s="11"/>
     </row>
-    <row r="664" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="4" t="s">
         <v>45</v>
       </c>
@@ -9887,7 +9896,7 @@
       <c r="D664" s="5"/>
       <c r="E664" s="11"/>
     </row>
-    <row r="665" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="4" t="s">
         <v>45</v>
       </c>
@@ -9900,7 +9909,7 @@
       <c r="D665" s="5"/>
       <c r="E665" s="11"/>
     </row>
-    <row r="666" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" s="4" t="s">
         <v>46</v>
       </c>
@@ -9913,7 +9922,7 @@
       <c r="D666" s="5"/>
       <c r="E666" s="11"/>
     </row>
-    <row r="667" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" s="4" t="s">
         <v>46</v>
       </c>
@@ -9926,7 +9935,7 @@
       <c r="D667" s="5"/>
       <c r="E667" s="11"/>
     </row>
-    <row r="668" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="4" t="s">
         <v>46</v>
       </c>
@@ -9939,7 +9948,7 @@
       <c r="D668" s="5"/>
       <c r="E668" s="11"/>
     </row>
-    <row r="669" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" s="4" t="s">
         <v>46</v>
       </c>
@@ -9952,7 +9961,7 @@
       <c r="D669" s="5"/>
       <c r="E669" s="11"/>
     </row>
-    <row r="670" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" s="4" t="s">
         <v>46</v>
       </c>
@@ -9965,7 +9974,7 @@
       <c r="D670" s="5"/>
       <c r="E670" s="11"/>
     </row>
-    <row r="671" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" s="4" t="s">
         <v>46</v>
       </c>
@@ -9978,7 +9987,7 @@
       <c r="D671" s="5"/>
       <c r="E671" s="11"/>
     </row>
-    <row r="672" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" s="4" t="s">
         <v>46</v>
       </c>
@@ -9991,7 +10000,7 @@
       <c r="D672" s="5"/>
       <c r="E672" s="11"/>
     </row>
-    <row r="673" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" s="4" t="s">
         <v>46</v>
       </c>
@@ -10004,7 +10013,7 @@
       <c r="D673" s="5"/>
       <c r="E673" s="11"/>
     </row>
-    <row r="674" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" s="4" t="s">
         <v>46</v>
       </c>
@@ -10017,7 +10026,7 @@
       <c r="D674" s="5"/>
       <c r="E674" s="11"/>
     </row>
-    <row r="675" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" s="4" t="s">
         <v>46</v>
       </c>
@@ -10030,7 +10039,7 @@
       <c r="D675" s="5"/>
       <c r="E675" s="11"/>
     </row>
-    <row r="676" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" s="4" t="s">
         <v>46</v>
       </c>
@@ -10043,7 +10052,7 @@
       <c r="D676" s="5"/>
       <c r="E676" s="11"/>
     </row>
-    <row r="677" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" s="4" t="s">
         <v>46</v>
       </c>
@@ -10056,7 +10065,7 @@
       <c r="D677" s="5"/>
       <c r="E677" s="11"/>
     </row>
-    <row r="678" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="4" t="s">
         <v>46</v>
       </c>
@@ -10069,7 +10078,7 @@
       <c r="D678" s="5"/>
       <c r="E678" s="11"/>
     </row>
-    <row r="679" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" s="4" t="s">
         <v>46</v>
       </c>
@@ -10082,7 +10091,7 @@
       <c r="D679" s="5"/>
       <c r="E679" s="11"/>
     </row>
-    <row r="680" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" s="4" t="s">
         <v>46</v>
       </c>
@@ -10095,7 +10104,7 @@
       <c r="D680" s="5"/>
       <c r="E680" s="11"/>
     </row>
-    <row r="681" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" s="4" t="s">
         <v>46</v>
       </c>
@@ -10108,7 +10117,7 @@
       <c r="D681" s="5"/>
       <c r="E681" s="11"/>
     </row>
-    <row r="682" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" s="4" t="s">
         <v>46</v>
       </c>
@@ -10121,7 +10130,7 @@
       <c r="D682" s="5"/>
       <c r="E682" s="11"/>
     </row>
-    <row r="683" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" s="4" t="s">
         <v>46</v>
       </c>
@@ -10134,7 +10143,7 @@
       <c r="D683" s="5"/>
       <c r="E683" s="11"/>
     </row>
-    <row r="684" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" s="4" t="s">
         <v>46</v>
       </c>
@@ -10147,7 +10156,7 @@
       <c r="D684" s="5"/>
       <c r="E684" s="11"/>
     </row>
-    <row r="685" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" s="4" t="s">
         <v>46</v>
       </c>
@@ -10160,7 +10169,7 @@
       <c r="D685" s="5"/>
       <c r="E685" s="11"/>
     </row>
-    <row r="686" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" s="4" t="s">
         <v>46</v>
       </c>
@@ -10173,7 +10182,7 @@
       <c r="D686" s="5"/>
       <c r="E686" s="11"/>
     </row>
-    <row r="687" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" s="4" t="s">
         <v>46</v>
       </c>
@@ -10186,7 +10195,7 @@
       <c r="D687" s="5"/>
       <c r="E687" s="11"/>
     </row>
-    <row r="688" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688" s="4" t="s">
         <v>46</v>
       </c>
@@ -10199,7 +10208,7 @@
       <c r="D688" s="5"/>
       <c r="E688" s="11"/>
     </row>
-    <row r="689" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689" s="4" t="s">
         <v>46</v>
       </c>
@@ -10212,7 +10221,7 @@
       <c r="D689" s="5"/>
       <c r="E689" s="11"/>
     </row>
-    <row r="690" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690" s="4" t="s">
         <v>46</v>
       </c>
@@ -10225,7 +10234,7 @@
       <c r="D690" s="5"/>
       <c r="E690" s="11"/>
     </row>
-    <row r="691" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691" s="4" t="s">
         <v>46</v>
       </c>
@@ -10238,7 +10247,7 @@
       <c r="D691" s="5"/>
       <c r="E691" s="11"/>
     </row>
-    <row r="692" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692" s="4" t="s">
         <v>46</v>
       </c>
@@ -10251,7 +10260,7 @@
       <c r="D692" s="5"/>
       <c r="E692" s="11"/>
     </row>
-    <row r="693" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" s="4" t="s">
         <v>46</v>
       </c>
@@ -10264,7 +10273,7 @@
       <c r="D693" s="5"/>
       <c r="E693" s="11"/>
     </row>
-    <row r="694" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694" s="4" t="s">
         <v>46</v>
       </c>
@@ -10277,7 +10286,7 @@
       <c r="D694" s="5"/>
       <c r="E694" s="11"/>
     </row>
-    <row r="695" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695" s="4" t="s">
         <v>46</v>
       </c>
@@ -10290,7 +10299,7 @@
       <c r="D695" s="5"/>
       <c r="E695" s="11"/>
     </row>
-    <row r="696" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" s="4" t="s">
         <v>46</v>
       </c>
@@ -10303,7 +10312,7 @@
       <c r="D696" s="5"/>
       <c r="E696" s="11"/>
     </row>
-    <row r="697" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697" s="4" t="s">
         <v>46</v>
       </c>
@@ -10316,7 +10325,7 @@
       <c r="D697" s="5"/>
       <c r="E697" s="11"/>
     </row>
-    <row r="698" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698" s="4" t="s">
         <v>46</v>
       </c>
@@ -10329,7 +10338,7 @@
       <c r="D698" s="5"/>
       <c r="E698" s="11"/>
     </row>
-    <row r="699" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699" s="4" t="s">
         <v>46</v>
       </c>
@@ -10342,7 +10351,7 @@
       <c r="D699" s="5"/>
       <c r="E699" s="11"/>
     </row>
-    <row r="700" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" s="4" t="s">
         <v>46</v>
       </c>
@@ -10355,7 +10364,7 @@
       <c r="D700" s="5"/>
       <c r="E700" s="11"/>
     </row>
-    <row r="701" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" s="4" t="s">
         <v>46</v>
       </c>
@@ -10368,7 +10377,7 @@
       <c r="D701" s="5"/>
       <c r="E701" s="11"/>
     </row>
-    <row r="702" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" s="4" t="s">
         <v>46</v>
       </c>
@@ -10381,7 +10390,7 @@
       <c r="D702" s="5"/>
       <c r="E702" s="11"/>
     </row>
-    <row r="703" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" s="4" t="s">
         <v>46</v>
       </c>
@@ -10394,7 +10403,7 @@
       <c r="D703" s="5"/>
       <c r="E703" s="11"/>
     </row>
-    <row r="704" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" s="4" t="s">
         <v>46</v>
       </c>
@@ -10407,7 +10416,7 @@
       <c r="D704" s="5"/>
       <c r="E704" s="11"/>
     </row>
-    <row r="705" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" s="4" t="s">
         <v>46</v>
       </c>
@@ -10420,7 +10429,7 @@
       <c r="D705" s="5"/>
       <c r="E705" s="11"/>
     </row>
-    <row r="706" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" s="4" t="s">
         <v>46</v>
       </c>
@@ -10433,7 +10442,7 @@
       <c r="D706" s="5"/>
       <c r="E706" s="11"/>
     </row>
-    <row r="707" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" s="4" t="s">
         <v>46</v>
       </c>
@@ -10446,7 +10455,7 @@
       <c r="D707" s="5"/>
       <c r="E707" s="11"/>
     </row>
-    <row r="708" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" s="4" t="s">
         <v>46</v>
       </c>
@@ -10459,7 +10468,7 @@
       <c r="D708" s="5"/>
       <c r="E708" s="11"/>
     </row>
-    <row r="709" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" s="4" t="s">
         <v>46</v>
       </c>
@@ -10472,7 +10481,7 @@
       <c r="D709" s="5"/>
       <c r="E709" s="11"/>
     </row>
-    <row r="710" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" s="4" t="s">
         <v>46</v>
       </c>
@@ -10485,7 +10494,7 @@
       <c r="D710" s="5"/>
       <c r="E710" s="11"/>
     </row>
-    <row r="711" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711" s="4" t="s">
         <v>46</v>
       </c>
@@ -10498,7 +10507,7 @@
       <c r="D711" s="5"/>
       <c r="E711" s="11"/>
     </row>
-    <row r="712" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712" s="4" t="s">
         <v>46</v>
       </c>
@@ -10511,7 +10520,7 @@
       <c r="D712" s="5"/>
       <c r="E712" s="11"/>
     </row>
-    <row r="713" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713" s="4" t="s">
         <v>46</v>
       </c>
@@ -10524,7 +10533,7 @@
       <c r="D713" s="5"/>
       <c r="E713" s="11"/>
     </row>
-    <row r="714" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714" s="4" t="s">
         <v>46</v>
       </c>
@@ -10537,7 +10546,7 @@
       <c r="D714" s="5"/>
       <c r="E714" s="11"/>
     </row>
-    <row r="715" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715" s="4" t="s">
         <v>46</v>
       </c>
@@ -10550,7 +10559,7 @@
       <c r="D715" s="5"/>
       <c r="E715" s="11"/>
     </row>
-    <row r="716" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716" s="4" t="s">
         <v>46</v>
       </c>
@@ -10563,7 +10572,7 @@
       <c r="D716" s="5"/>
       <c r="E716" s="11"/>
     </row>
-    <row r="717" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" s="4" t="s">
         <v>46</v>
       </c>
@@ -10576,7 +10585,7 @@
       <c r="D717" s="5"/>
       <c r="E717" s="11"/>
     </row>
-    <row r="718" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718" s="4" t="s">
         <v>46</v>
       </c>
@@ -10589,7 +10598,7 @@
       <c r="D718" s="5"/>
       <c r="E718" s="11"/>
     </row>
-    <row r="719" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719" s="4" t="s">
         <v>46</v>
       </c>
@@ -10602,7 +10611,7 @@
       <c r="D719" s="5"/>
       <c r="E719" s="11"/>
     </row>
-    <row r="720" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720" s="4" t="s">
         <v>46</v>
       </c>
@@ -10615,7 +10624,7 @@
       <c r="D720" s="5"/>
       <c r="E720" s="11"/>
     </row>
-    <row r="721" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721" s="4" t="s">
         <v>46</v>
       </c>
@@ -10628,7 +10637,7 @@
       <c r="D721" s="5"/>
       <c r="E721" s="11"/>
     </row>
-    <row r="722" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722" s="4" t="s">
         <v>46</v>
       </c>
@@ -10641,7 +10650,7 @@
       <c r="D722" s="5"/>
       <c r="E722" s="11"/>
     </row>
-    <row r="723" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723" s="4" t="s">
         <v>46</v>
       </c>
@@ -10654,7 +10663,7 @@
       <c r="D723" s="5"/>
       <c r="E723" s="11"/>
     </row>
-    <row r="724" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724" s="4" t="s">
         <v>46</v>
       </c>
@@ -10667,7 +10676,7 @@
       <c r="D724" s="5"/>
       <c r="E724" s="11"/>
     </row>
-    <row r="725" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" s="4" t="s">
         <v>46</v>
       </c>
@@ -10680,7 +10689,7 @@
       <c r="D725" s="5"/>
       <c r="E725" s="11"/>
     </row>
-    <row r="726" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A726" s="4" t="s">
         <v>43</v>
       </c>
@@ -10694,7 +10703,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A727" s="4" t="s">
         <v>43</v>
       </c>
@@ -10708,7 +10717,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A728" s="4" t="s">
         <v>43</v>
       </c>
@@ -10741,7 +10750,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="731" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
         <v>43</v>
       </c>
@@ -10758,7 +10767,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
         <v>43</v>
       </c>
@@ -10775,7 +10784,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="733" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
         <v>43</v>
       </c>
@@ -10792,7 +10801,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="734" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
         <v>43</v>
       </c>
@@ -10809,7 +10818,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>43</v>
       </c>
@@ -10826,7 +10835,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>43</v>
       </c>
@@ -10839,7 +10848,7 @@
       <c r="D736" t="s">
         <v>114</v>
       </c>
-      <c r="E736" s="13" t="s">
+      <c r="E736" t="s">
         <v>138</v>
       </c>
     </row>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D954B2-1E99-4E3B-BDA0-F54BEC4132B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB272265-98BC-47D6-885D-030DD168FC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -100,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="149">
   <si>
     <t>Категорија</t>
   </si>
@@ -523,6 +524,30 @@
   </si>
   <si>
     <t>Геометриски трансформации</t>
+  </si>
+  <si>
+    <t>Круг.Делови на круг. Тетивен четириаголник</t>
+  </si>
+  <si>
+    <t>L и P на круг. Круг во размер</t>
+  </si>
+  <si>
+    <t>P на трапез</t>
+  </si>
+  <si>
+    <t>P на паралелограм и триаголник</t>
+  </si>
+  <si>
+    <t>P на составни делови на 2Д фигури</t>
+  </si>
+  <si>
+    <t>P и V на квадар</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbyn5l0TKlJReKPb-VltK4UoQhFgrS45F1qzzX2wZS6Mp_6Mb2HR8vIEQqMkxejjI2Xc/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbxLigu4aHA21hWlMvI1NmrVSkkWssMKEAoUyDEGHQnsNsVMJJJQlZAKo0im0K_tgMWn/exec</t>
   </si>
 </sst>
 </file>
@@ -719,7 +744,7 @@
   <autoFilter ref="A1:E736" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Геометрија"/>
+        <filter val="Мерење"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
@@ -6847,7 +6872,7 @@
       <c r="D431" s="5"/>
       <c r="E431" s="11"/>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
         <v>44</v>
       </c>
@@ -6864,7 +6889,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
         <v>44</v>
       </c>
@@ -6877,7 +6902,7 @@
       <c r="D433" s="5"/>
       <c r="E433" s="11"/>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
         <v>44</v>
       </c>
@@ -6894,7 +6919,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
         <v>44</v>
       </c>
@@ -6911,7 +6936,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
         <v>44</v>
       </c>
@@ -6928,7 +6953,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
         <v>44</v>
       </c>
@@ -6941,7 +6966,7 @@
       <c r="D437" s="5"/>
       <c r="E437" s="11"/>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
         <v>44</v>
       </c>
@@ -6954,7 +6979,7 @@
       <c r="D438" s="5"/>
       <c r="E438" s="11"/>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
         <v>44</v>
       </c>
@@ -6967,7 +6992,7 @@
       <c r="D439" s="5"/>
       <c r="E439" s="11"/>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
         <v>44</v>
       </c>
@@ -6980,7 +7005,7 @@
       <c r="D440" s="5"/>
       <c r="E440" s="11"/>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
         <v>44</v>
       </c>
@@ -6993,7 +7018,7 @@
       <c r="D441" s="5"/>
       <c r="E441" s="11"/>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
         <v>44</v>
       </c>
@@ -7006,7 +7031,7 @@
       <c r="D442" s="5"/>
       <c r="E442" s="11"/>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
         <v>44</v>
       </c>
@@ -7019,7 +7044,7 @@
       <c r="D443" s="5"/>
       <c r="E443" s="11"/>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
         <v>44</v>
       </c>
@@ -7032,7 +7057,7 @@
       <c r="D444" s="5"/>
       <c r="E444" s="11"/>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
         <v>44</v>
       </c>
@@ -7045,7 +7070,7 @@
       <c r="D445" s="5"/>
       <c r="E445" s="11"/>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
         <v>44</v>
       </c>
@@ -7058,7 +7083,7 @@
       <c r="D446" s="5"/>
       <c r="E446" s="11"/>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
         <v>44</v>
       </c>
@@ -7071,7 +7096,7 @@
       <c r="D447" s="5"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
         <v>44</v>
       </c>
@@ -7084,7 +7109,7 @@
       <c r="D448" s="5"/>
       <c r="E448" s="11"/>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
         <v>44</v>
       </c>
@@ -7097,7 +7122,7 @@
       <c r="D449" s="5"/>
       <c r="E449" s="11"/>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
         <v>44</v>
       </c>
@@ -7110,7 +7135,7 @@
       <c r="D450" s="5"/>
       <c r="E450" s="11"/>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
         <v>44</v>
       </c>
@@ -7123,7 +7148,7 @@
       <c r="D451" s="5"/>
       <c r="E451" s="11"/>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
         <v>44</v>
       </c>
@@ -7136,7 +7161,7 @@
       <c r="D452" s="5"/>
       <c r="E452" s="11"/>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
         <v>44</v>
       </c>
@@ -7149,7 +7174,7 @@
       <c r="D453" s="5"/>
       <c r="E453" s="11"/>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
         <v>44</v>
       </c>
@@ -7162,7 +7187,7 @@
       <c r="D454" s="5"/>
       <c r="E454" s="11"/>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
         <v>44</v>
       </c>
@@ -7175,7 +7200,7 @@
       <c r="D455" s="5"/>
       <c r="E455" s="11"/>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
         <v>44</v>
       </c>
@@ -7188,7 +7213,7 @@
       <c r="D456" s="5"/>
       <c r="E456" s="11"/>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
         <v>44</v>
       </c>
@@ -7201,7 +7226,7 @@
       <c r="D457" s="5"/>
       <c r="E457" s="11"/>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
         <v>44</v>
       </c>
@@ -7214,7 +7239,7 @@
       <c r="D458" s="5"/>
       <c r="E458" s="11"/>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
         <v>44</v>
       </c>
@@ -7227,7 +7252,7 @@
       <c r="D459" s="5"/>
       <c r="E459" s="11"/>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
         <v>44</v>
       </c>
@@ -7240,7 +7265,7 @@
       <c r="D460" s="5"/>
       <c r="E460" s="11"/>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
         <v>44</v>
       </c>
@@ -7253,7 +7278,7 @@
       <c r="D461" s="5"/>
       <c r="E461" s="11"/>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
         <v>44</v>
       </c>
@@ -7266,7 +7291,7 @@
       <c r="D462" s="5"/>
       <c r="E462" s="11"/>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
         <v>44</v>
       </c>
@@ -7279,7 +7304,7 @@
       <c r="D463" s="5"/>
       <c r="E463" s="11"/>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
         <v>44</v>
       </c>
@@ -7292,7 +7317,7 @@
       <c r="D464" s="5"/>
       <c r="E464" s="11"/>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
         <v>44</v>
       </c>
@@ -7305,7 +7330,7 @@
       <c r="D465" s="5"/>
       <c r="E465" s="11"/>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
         <v>44</v>
       </c>
@@ -7318,7 +7343,7 @@
       <c r="D466" s="5"/>
       <c r="E466" s="11"/>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
         <v>44</v>
       </c>
@@ -7331,7 +7356,7 @@
       <c r="D467" s="5"/>
       <c r="E467" s="11"/>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
         <v>44</v>
       </c>
@@ -7344,7 +7369,7 @@
       <c r="D468" s="5"/>
       <c r="E468" s="11"/>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
         <v>44</v>
       </c>
@@ -7357,7 +7382,7 @@
       <c r="D469" s="5"/>
       <c r="E469" s="11"/>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
         <v>44</v>
       </c>
@@ -7370,7 +7395,7 @@
       <c r="D470" s="5"/>
       <c r="E470" s="11"/>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
         <v>44</v>
       </c>
@@ -7383,7 +7408,7 @@
       <c r="D471" s="5"/>
       <c r="E471" s="11"/>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
         <v>44</v>
       </c>
@@ -7396,7 +7421,7 @@
       <c r="D472" s="5"/>
       <c r="E472" s="11"/>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
         <v>44</v>
       </c>
@@ -7409,7 +7434,7 @@
       <c r="D473" s="5"/>
       <c r="E473" s="11"/>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
         <v>44</v>
       </c>
@@ -7422,7 +7447,7 @@
       <c r="D474" s="5"/>
       <c r="E474" s="11"/>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
         <v>44</v>
       </c>
@@ -7435,7 +7460,7 @@
       <c r="D475" s="5"/>
       <c r="E475" s="11"/>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
         <v>44</v>
       </c>
@@ -7448,7 +7473,7 @@
       <c r="D476" s="5"/>
       <c r="E476" s="11"/>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
         <v>44</v>
       </c>
@@ -7461,7 +7486,7 @@
       <c r="D477" s="5"/>
       <c r="E477" s="11"/>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
         <v>44</v>
       </c>
@@ -7474,7 +7499,7 @@
       <c r="D478" s="5"/>
       <c r="E478" s="11"/>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
         <v>44</v>
       </c>
@@ -7487,7 +7512,7 @@
       <c r="D479" s="5"/>
       <c r="E479" s="11"/>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
         <v>44</v>
       </c>
@@ -7500,7 +7525,7 @@
       <c r="D480" s="5"/>
       <c r="E480" s="11"/>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
         <v>44</v>
       </c>
@@ -7513,7 +7538,7 @@
       <c r="D481" s="5"/>
       <c r="E481" s="11"/>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
         <v>44</v>
       </c>
@@ -7526,7 +7551,7 @@
       <c r="D482" s="5"/>
       <c r="E482" s="11"/>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
         <v>44</v>
       </c>
@@ -7539,7 +7564,7 @@
       <c r="D483" s="5"/>
       <c r="E483" s="11"/>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
         <v>44</v>
       </c>
@@ -7552,7 +7577,7 @@
       <c r="D484" s="5"/>
       <c r="E484" s="11"/>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
         <v>44</v>
       </c>
@@ -7565,7 +7590,7 @@
       <c r="D485" s="5"/>
       <c r="E485" s="11"/>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
         <v>44</v>
       </c>
@@ -9077,7 +9102,7 @@
       <c r="D601" s="5"/>
       <c r="E601" s="11"/>
     </row>
-    <row r="602" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A602" s="4" t="s">
         <v>45</v>
       </c>
@@ -9087,10 +9112,12 @@
       <c r="C602" s="4">
         <v>1</v>
       </c>
-      <c r="D602" s="5"/>
+      <c r="D602" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="E602" s="11"/>
     </row>
-    <row r="603" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A603" s="4" t="s">
         <v>45</v>
       </c>
@@ -9100,10 +9127,14 @@
       <c r="C603" s="4">
         <v>2</v>
       </c>
-      <c r="D603" s="5"/>
-      <c r="E603" s="11"/>
-    </row>
-    <row r="604" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D603" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E603" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="604" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A604" s="4" t="s">
         <v>45</v>
       </c>
@@ -9113,10 +9144,12 @@
       <c r="C604" s="4">
         <v>3</v>
       </c>
-      <c r="D604" s="5"/>
+      <c r="D604" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="E604" s="11"/>
     </row>
-    <row r="605" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A605" s="4" t="s">
         <v>45</v>
       </c>
@@ -9126,10 +9159,12 @@
       <c r="C605" s="4">
         <v>4</v>
       </c>
-      <c r="D605" s="5"/>
+      <c r="D605" s="5" t="s">
+        <v>143</v>
+      </c>
       <c r="E605" s="11"/>
     </row>
-    <row r="606" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A606" s="4" t="s">
         <v>45</v>
       </c>
@@ -9139,10 +9174,14 @@
       <c r="C606" s="4">
         <v>5</v>
       </c>
-      <c r="D606" s="5"/>
-      <c r="E606" s="11"/>
-    </row>
-    <row r="607" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D606" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E606" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="607" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A607" s="4" t="s">
         <v>45</v>
       </c>
@@ -9152,10 +9191,12 @@
       <c r="C607" s="4">
         <v>6</v>
       </c>
-      <c r="D607" s="5"/>
+      <c r="D607" s="5" t="s">
+        <v>146</v>
+      </c>
       <c r="E607" s="11"/>
     </row>
-    <row r="608" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A608" s="4" t="s">
         <v>45</v>
       </c>
@@ -9168,7 +9209,7 @@
       <c r="D608" s="5"/>
       <c r="E608" s="11"/>
     </row>
-    <row r="609" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A609" s="4" t="s">
         <v>45</v>
       </c>
@@ -9181,7 +9222,7 @@
       <c r="D609" s="5"/>
       <c r="E609" s="11"/>
     </row>
-    <row r="610" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A610" s="4" t="s">
         <v>45</v>
       </c>
@@ -9194,7 +9235,7 @@
       <c r="D610" s="5"/>
       <c r="E610" s="11"/>
     </row>
-    <row r="611" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A611" s="4" t="s">
         <v>45</v>
       </c>
@@ -9207,7 +9248,7 @@
       <c r="D611" s="5"/>
       <c r="E611" s="11"/>
     </row>
-    <row r="612" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A612" s="4" t="s">
         <v>45</v>
       </c>
@@ -9220,7 +9261,7 @@
       <c r="D612" s="5"/>
       <c r="E612" s="11"/>
     </row>
-    <row r="613" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A613" s="4" t="s">
         <v>45</v>
       </c>
@@ -9233,7 +9274,7 @@
       <c r="D613" s="5"/>
       <c r="E613" s="11"/>
     </row>
-    <row r="614" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A614" s="4" t="s">
         <v>45</v>
       </c>
@@ -9246,7 +9287,7 @@
       <c r="D614" s="5"/>
       <c r="E614" s="11"/>
     </row>
-    <row r="615" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A615" s="4" t="s">
         <v>45</v>
       </c>
@@ -9259,7 +9300,7 @@
       <c r="D615" s="5"/>
       <c r="E615" s="11"/>
     </row>
-    <row r="616" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A616" s="4" t="s">
         <v>45</v>
       </c>
@@ -9272,7 +9313,7 @@
       <c r="D616" s="5"/>
       <c r="E616" s="11"/>
     </row>
-    <row r="617" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A617" s="4" t="s">
         <v>45</v>
       </c>
@@ -9285,7 +9326,7 @@
       <c r="D617" s="5"/>
       <c r="E617" s="11"/>
     </row>
-    <row r="618" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A618" s="4" t="s">
         <v>45</v>
       </c>
@@ -9298,7 +9339,7 @@
       <c r="D618" s="5"/>
       <c r="E618" s="11"/>
     </row>
-    <row r="619" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A619" s="4" t="s">
         <v>45</v>
       </c>
@@ -9311,7 +9352,7 @@
       <c r="D619" s="5"/>
       <c r="E619" s="11"/>
     </row>
-    <row r="620" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A620" s="4" t="s">
         <v>45</v>
       </c>
@@ -9324,7 +9365,7 @@
       <c r="D620" s="5"/>
       <c r="E620" s="11"/>
     </row>
-    <row r="621" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A621" s="4" t="s">
         <v>45</v>
       </c>
@@ -9337,7 +9378,7 @@
       <c r="D621" s="5"/>
       <c r="E621" s="11"/>
     </row>
-    <row r="622" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A622" s="4" t="s">
         <v>45</v>
       </c>
@@ -9350,7 +9391,7 @@
       <c r="D622" s="5"/>
       <c r="E622" s="11"/>
     </row>
-    <row r="623" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A623" s="4" t="s">
         <v>45</v>
       </c>
@@ -9363,7 +9404,7 @@
       <c r="D623" s="5"/>
       <c r="E623" s="11"/>
     </row>
-    <row r="624" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A624" s="4" t="s">
         <v>45</v>
       </c>
@@ -9376,7 +9417,7 @@
       <c r="D624" s="5"/>
       <c r="E624" s="11"/>
     </row>
-    <row r="625" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A625" s="4" t="s">
         <v>45</v>
       </c>
@@ -9389,7 +9430,7 @@
       <c r="D625" s="5"/>
       <c r="E625" s="11"/>
     </row>
-    <row r="626" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A626" s="4" t="s">
         <v>45</v>
       </c>
@@ -9402,7 +9443,7 @@
       <c r="D626" s="5"/>
       <c r="E626" s="11"/>
     </row>
-    <row r="627" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A627" s="4" t="s">
         <v>45</v>
       </c>
@@ -9415,7 +9456,7 @@
       <c r="D627" s="5"/>
       <c r="E627" s="11"/>
     </row>
-    <row r="628" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A628" s="4" t="s">
         <v>45</v>
       </c>
@@ -9428,7 +9469,7 @@
       <c r="D628" s="5"/>
       <c r="E628" s="11"/>
     </row>
-    <row r="629" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A629" s="4" t="s">
         <v>45</v>
       </c>
@@ -9441,7 +9482,7 @@
       <c r="D629" s="5"/>
       <c r="E629" s="11"/>
     </row>
-    <row r="630" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A630" s="4" t="s">
         <v>45</v>
       </c>
@@ -9454,7 +9495,7 @@
       <c r="D630" s="5"/>
       <c r="E630" s="11"/>
     </row>
-    <row r="631" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A631" s="4" t="s">
         <v>45</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB272265-98BC-47D6-885D-030DD168FC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F145D43-5E26-4BF2-BD93-6F3A7FF6C8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="151">
   <si>
     <t>Категорија</t>
   </si>
@@ -548,6 +548,12 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbxLigu4aHA21hWlMvI1NmrVSkkWssMKEAoUyDEGHQnsNsVMJJJQlZAKo0im0K_tgMWn/exec</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbzM8iBpfsIGphJ_bPbhMTLQfkUgmzN-GAL_1bijXqACor8pmtMFsZ7C40y936exKUxSxw/exec</t>
+  </si>
+  <si>
+    <t>Осна симетрија и транслација - вежби</t>
   </si>
 </sst>
 </file>
@@ -744,12 +750,12 @@
   <autoFilter ref="A1:E736" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Мерење"/>
+        <filter val="Геометрија"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="8"/>
+        <filter val="7"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -6153,7 +6159,7 @@
       <c r="D376" s="5"/>
       <c r="E376" s="11"/>
     </row>
-    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>44</v>
       </c>
@@ -6170,7 +6176,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>44</v>
       </c>
@@ -6183,7 +6189,7 @@
       <c r="D378" s="5"/>
       <c r="E378" s="11"/>
     </row>
-    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>44</v>
       </c>
@@ -6196,7 +6202,7 @@
       <c r="D379" s="5"/>
       <c r="E379" s="11"/>
     </row>
-    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>44</v>
       </c>
@@ -6209,7 +6215,7 @@
       <c r="D380" s="5"/>
       <c r="E380" s="11"/>
     </row>
-    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>44</v>
       </c>
@@ -6222,7 +6228,7 @@
       <c r="D381" s="5"/>
       <c r="E381" s="11"/>
     </row>
-    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>44</v>
       </c>
@@ -6235,7 +6241,7 @@
       <c r="D382" s="5"/>
       <c r="E382" s="11"/>
     </row>
-    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
         <v>44</v>
       </c>
@@ -6248,7 +6254,7 @@
       <c r="D383" s="5"/>
       <c r="E383" s="11"/>
     </row>
-    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
         <v>44</v>
       </c>
@@ -6261,7 +6267,7 @@
       <c r="D384" s="5"/>
       <c r="E384" s="11"/>
     </row>
-    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
         <v>44</v>
       </c>
@@ -6274,7 +6280,7 @@
       <c r="D385" s="5"/>
       <c r="E385" s="11"/>
     </row>
-    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
         <v>44</v>
       </c>
@@ -6284,10 +6290,14 @@
       <c r="C386" s="4">
         <v>10</v>
       </c>
-      <c r="D386" s="5"/>
-      <c r="E386" s="11"/>
-    </row>
-    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D386" t="s">
+        <v>150</v>
+      </c>
+      <c r="E386" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
         <v>44</v>
       </c>
@@ -6300,7 +6310,7 @@
       <c r="D387" s="5"/>
       <c r="E387" s="11"/>
     </row>
-    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
         <v>44</v>
       </c>
@@ -6313,7 +6323,7 @@
       <c r="D388" s="5"/>
       <c r="E388" s="11"/>
     </row>
-    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
         <v>44</v>
       </c>
@@ -6326,7 +6336,7 @@
       <c r="D389" s="5"/>
       <c r="E389" s="11"/>
     </row>
-    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
         <v>44</v>
       </c>
@@ -6339,7 +6349,7 @@
       <c r="D390" s="5"/>
       <c r="E390" s="11"/>
     </row>
-    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
         <v>44</v>
       </c>
@@ -6352,7 +6362,7 @@
       <c r="D391" s="5"/>
       <c r="E391" s="11"/>
     </row>
-    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
         <v>44</v>
       </c>
@@ -6365,7 +6375,7 @@
       <c r="D392" s="5"/>
       <c r="E392" s="11"/>
     </row>
-    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
         <v>44</v>
       </c>
@@ -6378,7 +6388,7 @@
       <c r="D393" s="5"/>
       <c r="E393" s="11"/>
     </row>
-    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
         <v>44</v>
       </c>
@@ -6391,7 +6401,7 @@
       <c r="D394" s="5"/>
       <c r="E394" s="11"/>
     </row>
-    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
         <v>44</v>
       </c>
@@ -6404,7 +6414,7 @@
       <c r="D395" s="5"/>
       <c r="E395" s="11"/>
     </row>
-    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
         <v>44</v>
       </c>
@@ -6417,7 +6427,7 @@
       <c r="D396" s="5"/>
       <c r="E396" s="11"/>
     </row>
-    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>44</v>
       </c>
@@ -6430,7 +6440,7 @@
       <c r="D397" s="5"/>
       <c r="E397" s="11"/>
     </row>
-    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>44</v>
       </c>
@@ -6443,7 +6453,7 @@
       <c r="D398" s="5"/>
       <c r="E398" s="11"/>
     </row>
-    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
         <v>44</v>
       </c>
@@ -6456,7 +6466,7 @@
       <c r="D399" s="5"/>
       <c r="E399" s="11"/>
     </row>
-    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
         <v>44</v>
       </c>
@@ -6469,7 +6479,7 @@
       <c r="D400" s="5"/>
       <c r="E400" s="11"/>
     </row>
-    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>44</v>
       </c>
@@ -6482,7 +6492,7 @@
       <c r="D401" s="5"/>
       <c r="E401" s="11"/>
     </row>
-    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>44</v>
       </c>
@@ -6495,7 +6505,7 @@
       <c r="D402" s="5"/>
       <c r="E402" s="11"/>
     </row>
-    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>44</v>
       </c>
@@ -6508,7 +6518,7 @@
       <c r="D403" s="5"/>
       <c r="E403" s="11"/>
     </row>
-    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>44</v>
       </c>
@@ -6521,7 +6531,7 @@
       <c r="D404" s="5"/>
       <c r="E404" s="11"/>
     </row>
-    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
         <v>44</v>
       </c>
@@ -6534,7 +6544,7 @@
       <c r="D405" s="5"/>
       <c r="E405" s="11"/>
     </row>
-    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>44</v>
       </c>
@@ -6547,7 +6557,7 @@
       <c r="D406" s="5"/>
       <c r="E406" s="11"/>
     </row>
-    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>44</v>
       </c>
@@ -6560,7 +6570,7 @@
       <c r="D407" s="5"/>
       <c r="E407" s="11"/>
     </row>
-    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>44</v>
       </c>
@@ -6573,7 +6583,7 @@
       <c r="D408" s="5"/>
       <c r="E408" s="11"/>
     </row>
-    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>44</v>
       </c>
@@ -6586,7 +6596,7 @@
       <c r="D409" s="5"/>
       <c r="E409" s="11"/>
     </row>
-    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>44</v>
       </c>
@@ -6599,7 +6609,7 @@
       <c r="D410" s="5"/>
       <c r="E410" s="11"/>
     </row>
-    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>44</v>
       </c>
@@ -6612,7 +6622,7 @@
       <c r="D411" s="5"/>
       <c r="E411" s="11"/>
     </row>
-    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>44</v>
       </c>
@@ -6625,7 +6635,7 @@
       <c r="D412" s="5"/>
       <c r="E412" s="11"/>
     </row>
-    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
         <v>44</v>
       </c>
@@ -6638,7 +6648,7 @@
       <c r="D413" s="5"/>
       <c r="E413" s="11"/>
     </row>
-    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
         <v>44</v>
       </c>
@@ -6651,7 +6661,7 @@
       <c r="D414" s="5"/>
       <c r="E414" s="11"/>
     </row>
-    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
         <v>44</v>
       </c>
@@ -6664,7 +6674,7 @@
       <c r="D415" s="5"/>
       <c r="E415" s="11"/>
     </row>
-    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
         <v>44</v>
       </c>
@@ -6677,7 +6687,7 @@
       <c r="D416" s="5"/>
       <c r="E416" s="11"/>
     </row>
-    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
         <v>44</v>
       </c>
@@ -6690,7 +6700,7 @@
       <c r="D417" s="5"/>
       <c r="E417" s="11"/>
     </row>
-    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
         <v>44</v>
       </c>
@@ -6703,7 +6713,7 @@
       <c r="D418" s="5"/>
       <c r="E418" s="11"/>
     </row>
-    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
         <v>44</v>
       </c>
@@ -6716,7 +6726,7 @@
       <c r="D419" s="5"/>
       <c r="E419" s="11"/>
     </row>
-    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
         <v>44</v>
       </c>
@@ -6729,7 +6739,7 @@
       <c r="D420" s="5"/>
       <c r="E420" s="11"/>
     </row>
-    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
         <v>44</v>
       </c>
@@ -6742,7 +6752,7 @@
       <c r="D421" s="5"/>
       <c r="E421" s="11"/>
     </row>
-    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
         <v>44</v>
       </c>
@@ -6755,7 +6765,7 @@
       <c r="D422" s="5"/>
       <c r="E422" s="11"/>
     </row>
-    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
         <v>44</v>
       </c>
@@ -6768,7 +6778,7 @@
       <c r="D423" s="5"/>
       <c r="E423" s="11"/>
     </row>
-    <row r="424" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
         <v>44</v>
       </c>
@@ -6781,7 +6791,7 @@
       <c r="D424" s="5"/>
       <c r="E424" s="11"/>
     </row>
-    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
         <v>44</v>
       </c>
@@ -6794,7 +6804,7 @@
       <c r="D425" s="5"/>
       <c r="E425" s="11"/>
     </row>
-    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
         <v>44</v>
       </c>
@@ -6807,7 +6817,7 @@
       <c r="D426" s="5"/>
       <c r="E426" s="11"/>
     </row>
-    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
         <v>44</v>
       </c>
@@ -6820,7 +6830,7 @@
       <c r="D427" s="5"/>
       <c r="E427" s="11"/>
     </row>
-    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
         <v>44</v>
       </c>
@@ -6833,7 +6843,7 @@
       <c r="D428" s="5"/>
       <c r="E428" s="11"/>
     </row>
-    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
         <v>44</v>
       </c>
@@ -6846,7 +6856,7 @@
       <c r="D429" s="5"/>
       <c r="E429" s="11"/>
     </row>
-    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
         <v>44</v>
       </c>
@@ -6859,7 +6869,7 @@
       <c r="D430" s="5"/>
       <c r="E430" s="11"/>
     </row>
-    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
         <v>44</v>
       </c>
@@ -9102,7 +9112,7 @@
       <c r="D601" s="5"/>
       <c r="E601" s="11"/>
     </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="4" t="s">
         <v>45</v>
       </c>
@@ -9117,7 +9127,7 @@
       </c>
       <c r="E602" s="11"/>
     </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="4" t="s">
         <v>45</v>
       </c>
@@ -9134,7 +9144,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="4" t="s">
         <v>45</v>
       </c>
@@ -9149,7 +9159,7 @@
       </c>
       <c r="E604" s="11"/>
     </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" s="4" t="s">
         <v>45</v>
       </c>
@@ -9164,7 +9174,7 @@
       </c>
       <c r="E605" s="11"/>
     </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" s="4" t="s">
         <v>45</v>
       </c>
@@ -9181,7 +9191,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="607" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" s="4" t="s">
         <v>45</v>
       </c>
@@ -9196,7 +9206,7 @@
       </c>
       <c r="E607" s="11"/>
     </row>
-    <row r="608" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="4" t="s">
         <v>45</v>
       </c>
@@ -9209,7 +9219,7 @@
       <c r="D608" s="5"/>
       <c r="E608" s="11"/>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" s="4" t="s">
         <v>45</v>
       </c>
@@ -9222,7 +9232,7 @@
       <c r="D609" s="5"/>
       <c r="E609" s="11"/>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" s="4" t="s">
         <v>45</v>
       </c>
@@ -9235,7 +9245,7 @@
       <c r="D610" s="5"/>
       <c r="E610" s="11"/>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="4" t="s">
         <v>45</v>
       </c>
@@ -9248,7 +9258,7 @@
       <c r="D611" s="5"/>
       <c r="E611" s="11"/>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="4" t="s">
         <v>45</v>
       </c>
@@ -9261,7 +9271,7 @@
       <c r="D612" s="5"/>
       <c r="E612" s="11"/>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="4" t="s">
         <v>45</v>
       </c>
@@ -9274,7 +9284,7 @@
       <c r="D613" s="5"/>
       <c r="E613" s="11"/>
     </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="4" t="s">
         <v>45</v>
       </c>
@@ -9287,7 +9297,7 @@
       <c r="D614" s="5"/>
       <c r="E614" s="11"/>
     </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" s="4" t="s">
         <v>45</v>
       </c>
@@ -9300,7 +9310,7 @@
       <c r="D615" s="5"/>
       <c r="E615" s="11"/>
     </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" s="4" t="s">
         <v>45</v>
       </c>
@@ -9313,7 +9323,7 @@
       <c r="D616" s="5"/>
       <c r="E616" s="11"/>
     </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" s="4" t="s">
         <v>45</v>
       </c>
@@ -9326,7 +9336,7 @@
       <c r="D617" s="5"/>
       <c r="E617" s="11"/>
     </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" s="4" t="s">
         <v>45</v>
       </c>
@@ -9339,7 +9349,7 @@
       <c r="D618" s="5"/>
       <c r="E618" s="11"/>
     </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" s="4" t="s">
         <v>45</v>
       </c>
@@ -9352,7 +9362,7 @@
       <c r="D619" s="5"/>
       <c r="E619" s="11"/>
     </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" s="4" t="s">
         <v>45</v>
       </c>
@@ -9365,7 +9375,7 @@
       <c r="D620" s="5"/>
       <c r="E620" s="11"/>
     </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" s="4" t="s">
         <v>45</v>
       </c>
@@ -9378,7 +9388,7 @@
       <c r="D621" s="5"/>
       <c r="E621" s="11"/>
     </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="4" t="s">
         <v>45</v>
       </c>
@@ -9391,7 +9401,7 @@
       <c r="D622" s="5"/>
       <c r="E622" s="11"/>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="4" t="s">
         <v>45</v>
       </c>
@@ -9404,7 +9414,7 @@
       <c r="D623" s="5"/>
       <c r="E623" s="11"/>
     </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="4" t="s">
         <v>45</v>
       </c>
@@ -9417,7 +9427,7 @@
       <c r="D624" s="5"/>
       <c r="E624" s="11"/>
     </row>
-    <row r="625" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="4" t="s">
         <v>45</v>
       </c>
@@ -9430,7 +9440,7 @@
       <c r="D625" s="5"/>
       <c r="E625" s="11"/>
     </row>
-    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="4" t="s">
         <v>45</v>
       </c>
@@ -9443,7 +9453,7 @@
       <c r="D626" s="5"/>
       <c r="E626" s="11"/>
     </row>
-    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="4" t="s">
         <v>45</v>
       </c>
@@ -9456,7 +9466,7 @@
       <c r="D627" s="5"/>
       <c r="E627" s="11"/>
     </row>
-    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="4" t="s">
         <v>45</v>
       </c>
@@ -9469,7 +9479,7 @@
       <c r="D628" s="5"/>
       <c r="E628" s="11"/>
     </row>
-    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="4" t="s">
         <v>45</v>
       </c>
@@ -9482,7 +9492,7 @@
       <c r="D629" s="5"/>
       <c r="E629" s="11"/>
     </row>
-    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="4" t="s">
         <v>45</v>
       </c>
@@ -9495,7 +9505,7 @@
       <c r="D630" s="5"/>
       <c r="E630" s="11"/>
     </row>
-    <row r="631" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" s="4" t="s">
         <v>45</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F145D43-5E26-4BF2-BD93-6F3A7FF6C8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9A5C30-6465-4101-893B-2A1004CF9F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="153">
   <si>
     <t>Категорија</t>
   </si>
@@ -554,6 +554,12 @@
   </si>
   <si>
     <t>Осна симетрија и транслација - вежби</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbxC1SFz5L4gA7uNJ1fUf_4uoQax8B8U4sIAYGkzhHQLH8Xs9htYpOPCFJyXNNiAxZ6WFA/exec</t>
+  </si>
+  <si>
+    <t>Ротација</t>
   </si>
 </sst>
 </file>
@@ -6307,8 +6313,12 @@
       <c r="C387" s="4">
         <v>11</v>
       </c>
-      <c r="D387" s="5"/>
-      <c r="E387" s="11"/>
+      <c r="D387" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E387" s="11" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9A5C30-6465-4101-893B-2A1004CF9F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5458E66-C6D6-4C7C-A1AC-2F3A7A6FB0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="157">
   <si>
     <t>Категорија</t>
   </si>
@@ -560,6 +560,18 @@
   </si>
   <si>
     <t>Ротација</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbwWuzL2se0T0mLBDvDIgdLRVj4VE3pglcE-WtJjJXiknqhXY6Qm9HRMBmBGIxDVmf2jow/exec</t>
+  </si>
+  <si>
+    <t>Решава проблеми со маса, должина и зафатнина</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbzhquDDP01uVDobJFUVsBTw79132DDxnH21C_sXmCxLZYuI3zCK8r7iDFnzaUvIO9SP/exec</t>
+  </si>
+  <si>
+    <t>Примена на Питагорова теорема</t>
   </si>
 </sst>
 </file>
@@ -756,12 +768,12 @@
   <autoFilter ref="A1:E736" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Геометрија"/>
+        <filter val="Мерење"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="7"/>
+        <filter val="9"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -6165,7 +6177,7 @@
       <c r="D376" s="5"/>
       <c r="E376" s="11"/>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>44</v>
       </c>
@@ -6182,7 +6194,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>44</v>
       </c>
@@ -6195,7 +6207,7 @@
       <c r="D378" s="5"/>
       <c r="E378" s="11"/>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>44</v>
       </c>
@@ -6208,7 +6220,7 @@
       <c r="D379" s="5"/>
       <c r="E379" s="11"/>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>44</v>
       </c>
@@ -6221,7 +6233,7 @@
       <c r="D380" s="5"/>
       <c r="E380" s="11"/>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>44</v>
       </c>
@@ -6234,7 +6246,7 @@
       <c r="D381" s="5"/>
       <c r="E381" s="11"/>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>44</v>
       </c>
@@ -6247,7 +6259,7 @@
       <c r="D382" s="5"/>
       <c r="E382" s="11"/>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
         <v>44</v>
       </c>
@@ -6260,7 +6272,7 @@
       <c r="D383" s="5"/>
       <c r="E383" s="11"/>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
         <v>44</v>
       </c>
@@ -6273,7 +6285,7 @@
       <c r="D384" s="5"/>
       <c r="E384" s="11"/>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
         <v>44</v>
       </c>
@@ -6286,7 +6298,7 @@
       <c r="D385" s="5"/>
       <c r="E385" s="11"/>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
         <v>44</v>
       </c>
@@ -6303,7 +6315,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
         <v>44</v>
       </c>
@@ -6320,7 +6332,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
         <v>44</v>
       </c>
@@ -6333,7 +6345,7 @@
       <c r="D388" s="5"/>
       <c r="E388" s="11"/>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
         <v>44</v>
       </c>
@@ -6346,7 +6358,7 @@
       <c r="D389" s="5"/>
       <c r="E389" s="11"/>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
         <v>44</v>
       </c>
@@ -6359,7 +6371,7 @@
       <c r="D390" s="5"/>
       <c r="E390" s="11"/>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
         <v>44</v>
       </c>
@@ -6372,7 +6384,7 @@
       <c r="D391" s="5"/>
       <c r="E391" s="11"/>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
         <v>44</v>
       </c>
@@ -6385,7 +6397,7 @@
       <c r="D392" s="5"/>
       <c r="E392" s="11"/>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
         <v>44</v>
       </c>
@@ -6398,7 +6410,7 @@
       <c r="D393" s="5"/>
       <c r="E393" s="11"/>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
         <v>44</v>
       </c>
@@ -6411,7 +6423,7 @@
       <c r="D394" s="5"/>
       <c r="E394" s="11"/>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
         <v>44</v>
       </c>
@@ -6424,7 +6436,7 @@
       <c r="D395" s="5"/>
       <c r="E395" s="11"/>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
         <v>44</v>
       </c>
@@ -6437,7 +6449,7 @@
       <c r="D396" s="5"/>
       <c r="E396" s="11"/>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>44</v>
       </c>
@@ -6450,7 +6462,7 @@
       <c r="D397" s="5"/>
       <c r="E397" s="11"/>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>44</v>
       </c>
@@ -6463,7 +6475,7 @@
       <c r="D398" s="5"/>
       <c r="E398" s="11"/>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
         <v>44</v>
       </c>
@@ -6476,7 +6488,7 @@
       <c r="D399" s="5"/>
       <c r="E399" s="11"/>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
         <v>44</v>
       </c>
@@ -6489,7 +6501,7 @@
       <c r="D400" s="5"/>
       <c r="E400" s="11"/>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>44</v>
       </c>
@@ -6502,7 +6514,7 @@
       <c r="D401" s="5"/>
       <c r="E401" s="11"/>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>44</v>
       </c>
@@ -6515,7 +6527,7 @@
       <c r="D402" s="5"/>
       <c r="E402" s="11"/>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>44</v>
       </c>
@@ -6528,7 +6540,7 @@
       <c r="D403" s="5"/>
       <c r="E403" s="11"/>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>44</v>
       </c>
@@ -6541,7 +6553,7 @@
       <c r="D404" s="5"/>
       <c r="E404" s="11"/>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
         <v>44</v>
       </c>
@@ -6554,7 +6566,7 @@
       <c r="D405" s="5"/>
       <c r="E405" s="11"/>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>44</v>
       </c>
@@ -6567,7 +6579,7 @@
       <c r="D406" s="5"/>
       <c r="E406" s="11"/>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>44</v>
       </c>
@@ -6580,7 +6592,7 @@
       <c r="D407" s="5"/>
       <c r="E407" s="11"/>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>44</v>
       </c>
@@ -6593,7 +6605,7 @@
       <c r="D408" s="5"/>
       <c r="E408" s="11"/>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>44</v>
       </c>
@@ -6606,7 +6618,7 @@
       <c r="D409" s="5"/>
       <c r="E409" s="11"/>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>44</v>
       </c>
@@ -6619,7 +6631,7 @@
       <c r="D410" s="5"/>
       <c r="E410" s="11"/>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>44</v>
       </c>
@@ -6632,7 +6644,7 @@
       <c r="D411" s="5"/>
       <c r="E411" s="11"/>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>44</v>
       </c>
@@ -6645,7 +6657,7 @@
       <c r="D412" s="5"/>
       <c r="E412" s="11"/>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
         <v>44</v>
       </c>
@@ -6658,7 +6670,7 @@
       <c r="D413" s="5"/>
       <c r="E413" s="11"/>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
         <v>44</v>
       </c>
@@ -6671,7 +6683,7 @@
       <c r="D414" s="5"/>
       <c r="E414" s="11"/>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
         <v>44</v>
       </c>
@@ -6684,7 +6696,7 @@
       <c r="D415" s="5"/>
       <c r="E415" s="11"/>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
         <v>44</v>
       </c>
@@ -6697,7 +6709,7 @@
       <c r="D416" s="5"/>
       <c r="E416" s="11"/>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
         <v>44</v>
       </c>
@@ -6710,7 +6722,7 @@
       <c r="D417" s="5"/>
       <c r="E417" s="11"/>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
         <v>44</v>
       </c>
@@ -6723,7 +6735,7 @@
       <c r="D418" s="5"/>
       <c r="E418" s="11"/>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
         <v>44</v>
       </c>
@@ -6736,7 +6748,7 @@
       <c r="D419" s="5"/>
       <c r="E419" s="11"/>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
         <v>44</v>
       </c>
@@ -6749,7 +6761,7 @@
       <c r="D420" s="5"/>
       <c r="E420" s="11"/>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
         <v>44</v>
       </c>
@@ -6762,7 +6774,7 @@
       <c r="D421" s="5"/>
       <c r="E421" s="11"/>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
         <v>44</v>
       </c>
@@ -6775,7 +6787,7 @@
       <c r="D422" s="5"/>
       <c r="E422" s="11"/>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
         <v>44</v>
       </c>
@@ -6788,7 +6800,7 @@
       <c r="D423" s="5"/>
       <c r="E423" s="11"/>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
         <v>44</v>
       </c>
@@ -6801,7 +6813,7 @@
       <c r="D424" s="5"/>
       <c r="E424" s="11"/>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
         <v>44</v>
       </c>
@@ -6814,7 +6826,7 @@
       <c r="D425" s="5"/>
       <c r="E425" s="11"/>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
         <v>44</v>
       </c>
@@ -6827,7 +6839,7 @@
       <c r="D426" s="5"/>
       <c r="E426" s="11"/>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
         <v>44</v>
       </c>
@@ -6840,7 +6852,7 @@
       <c r="D427" s="5"/>
       <c r="E427" s="11"/>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
         <v>44</v>
       </c>
@@ -6853,7 +6865,7 @@
       <c r="D428" s="5"/>
       <c r="E428" s="11"/>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
         <v>44</v>
       </c>
@@ -6866,7 +6878,7 @@
       <c r="D429" s="5"/>
       <c r="E429" s="11"/>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
         <v>44</v>
       </c>
@@ -6879,7 +6891,7 @@
       <c r="D430" s="5"/>
       <c r="E430" s="11"/>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
         <v>44</v>
       </c>
@@ -8465,8 +8477,12 @@
       <c r="C551" s="4">
         <v>6</v>
       </c>
-      <c r="D551" s="5"/>
-      <c r="E551" s="11"/>
+      <c r="D551" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E551" s="11" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="552" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
@@ -9528,7 +9544,7 @@
       <c r="D631" s="5"/>
       <c r="E631" s="11"/>
     </row>
-    <row r="632" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A632" s="4" t="s">
         <v>45</v>
       </c>
@@ -9541,7 +9557,7 @@
       <c r="D632" s="5"/>
       <c r="E632" s="11"/>
     </row>
-    <row r="633" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A633" s="4" t="s">
         <v>45</v>
       </c>
@@ -9554,7 +9570,7 @@
       <c r="D633" s="5"/>
       <c r="E633" s="11"/>
     </row>
-    <row r="634" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A634" s="4" t="s">
         <v>45</v>
       </c>
@@ -9567,7 +9583,7 @@
       <c r="D634" s="5"/>
       <c r="E634" s="11"/>
     </row>
-    <row r="635" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A635" s="4" t="s">
         <v>45</v>
       </c>
@@ -9580,7 +9596,7 @@
       <c r="D635" s="5"/>
       <c r="E635" s="11"/>
     </row>
-    <row r="636" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A636" s="4" t="s">
         <v>45</v>
       </c>
@@ -9593,7 +9609,7 @@
       <c r="D636" s="5"/>
       <c r="E636" s="11"/>
     </row>
-    <row r="637" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A637" s="4" t="s">
         <v>45</v>
       </c>
@@ -9606,7 +9622,7 @@
       <c r="D637" s="5"/>
       <c r="E637" s="11"/>
     </row>
-    <row r="638" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A638" s="4" t="s">
         <v>45</v>
       </c>
@@ -9619,7 +9635,7 @@
       <c r="D638" s="5"/>
       <c r="E638" s="11"/>
     </row>
-    <row r="639" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A639" s="4" t="s">
         <v>45</v>
       </c>
@@ -9632,7 +9648,7 @@
       <c r="D639" s="5"/>
       <c r="E639" s="11"/>
     </row>
-    <row r="640" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A640" s="4" t="s">
         <v>45</v>
       </c>
@@ -9645,7 +9661,7 @@
       <c r="D640" s="5"/>
       <c r="E640" s="11"/>
     </row>
-    <row r="641" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A641" s="4" t="s">
         <v>45</v>
       </c>
@@ -9658,7 +9674,7 @@
       <c r="D641" s="5"/>
       <c r="E641" s="11"/>
     </row>
-    <row r="642" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A642" s="4" t="s">
         <v>45</v>
       </c>
@@ -9668,10 +9684,14 @@
       <c r="C642" s="4">
         <v>11</v>
       </c>
-      <c r="D642" s="5"/>
-      <c r="E642" s="11"/>
-    </row>
-    <row r="643" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D642" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E642" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A643" s="4" t="s">
         <v>45</v>
       </c>
@@ -9684,7 +9704,7 @@
       <c r="D643" s="5"/>
       <c r="E643" s="11"/>
     </row>
-    <row r="644" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A644" s="4" t="s">
         <v>45</v>
       </c>
@@ -9697,7 +9717,7 @@
       <c r="D644" s="5"/>
       <c r="E644" s="11"/>
     </row>
-    <row r="645" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A645" s="4" t="s">
         <v>45</v>
       </c>
@@ -9710,7 +9730,7 @@
       <c r="D645" s="5"/>
       <c r="E645" s="11"/>
     </row>
-    <row r="646" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A646" s="4" t="s">
         <v>45</v>
       </c>
@@ -9723,7 +9743,7 @@
       <c r="D646" s="5"/>
       <c r="E646" s="11"/>
     </row>
-    <row r="647" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A647" s="4" t="s">
         <v>45</v>
       </c>
@@ -9736,7 +9756,7 @@
       <c r="D647" s="5"/>
       <c r="E647" s="11"/>
     </row>
-    <row r="648" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A648" s="4" t="s">
         <v>45</v>
       </c>
@@ -9749,7 +9769,7 @@
       <c r="D648" s="5"/>
       <c r="E648" s="11"/>
     </row>
-    <row r="649" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A649" s="4" t="s">
         <v>45</v>
       </c>
@@ -9762,7 +9782,7 @@
       <c r="D649" s="5"/>
       <c r="E649" s="11"/>
     </row>
-    <row r="650" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A650" s="4" t="s">
         <v>45</v>
       </c>
@@ -9775,7 +9795,7 @@
       <c r="D650" s="5"/>
       <c r="E650" s="11"/>
     </row>
-    <row r="651" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A651" s="4" t="s">
         <v>45</v>
       </c>
@@ -9788,7 +9808,7 @@
       <c r="D651" s="5"/>
       <c r="E651" s="11"/>
     </row>
-    <row r="652" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A652" s="4" t="s">
         <v>45</v>
       </c>
@@ -9801,7 +9821,7 @@
       <c r="D652" s="5"/>
       <c r="E652" s="11"/>
     </row>
-    <row r="653" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A653" s="4" t="s">
         <v>45</v>
       </c>
@@ -9814,7 +9834,7 @@
       <c r="D653" s="5"/>
       <c r="E653" s="11"/>
     </row>
-    <row r="654" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A654" s="4" t="s">
         <v>45</v>
       </c>
@@ -9827,7 +9847,7 @@
       <c r="D654" s="5"/>
       <c r="E654" s="11"/>
     </row>
-    <row r="655" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A655" s="4" t="s">
         <v>45</v>
       </c>
@@ -9840,7 +9860,7 @@
       <c r="D655" s="5"/>
       <c r="E655" s="11"/>
     </row>
-    <row r="656" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A656" s="4" t="s">
         <v>45</v>
       </c>
@@ -9853,7 +9873,7 @@
       <c r="D656" s="5"/>
       <c r="E656" s="11"/>
     </row>
-    <row r="657" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A657" s="4" t="s">
         <v>45</v>
       </c>
@@ -9866,7 +9886,7 @@
       <c r="D657" s="5"/>
       <c r="E657" s="11"/>
     </row>
-    <row r="658" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A658" s="4" t="s">
         <v>45</v>
       </c>
@@ -9879,7 +9899,7 @@
       <c r="D658" s="5"/>
       <c r="E658" s="11"/>
     </row>
-    <row r="659" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A659" s="4" t="s">
         <v>45</v>
       </c>
@@ -9892,7 +9912,7 @@
       <c r="D659" s="5"/>
       <c r="E659" s="11"/>
     </row>
-    <row r="660" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A660" s="4" t="s">
         <v>45</v>
       </c>
@@ -9905,7 +9925,7 @@
       <c r="D660" s="5"/>
       <c r="E660" s="11"/>
     </row>
-    <row r="661" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A661" s="4" t="s">
         <v>45</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5458E66-C6D6-4C7C-A1AC-2F3A7A6FB0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A8538D-8EB1-44A6-A653-4DB7C5FEB82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="159">
   <si>
     <t>Категорија</t>
   </si>
@@ -572,6 +572,12 @@
   </si>
   <si>
     <t>Примена на Питагорова теорема</t>
+  </si>
+  <si>
+    <t>Споредување цени дадени во различни валути</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbwm1HrLVb56EXheipy9go4kYrPgHu4cmqg1ocgHqKaM0OfZQfsXj-cWl6DOdDsGJvPEgw/exec</t>
   </si>
 </sst>
 </file>
@@ -773,7 +779,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="9"/>
+        <filter val="6"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -8402,7 +8408,7 @@
       <c r="D545" s="5"/>
       <c r="E545" s="11"/>
     </row>
-    <row r="546" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A546" s="4" t="s">
         <v>45</v>
       </c>
@@ -8415,7 +8421,7 @@
       <c r="D546" s="5"/>
       <c r="E546" s="11"/>
     </row>
-    <row r="547" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A547" s="4" t="s">
         <v>45</v>
       </c>
@@ -8428,7 +8434,7 @@
       <c r="D547" s="5"/>
       <c r="E547" s="11"/>
     </row>
-    <row r="548" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A548" s="4" t="s">
         <v>45</v>
       </c>
@@ -8441,7 +8447,7 @@
       <c r="D548" s="5"/>
       <c r="E548" s="11"/>
     </row>
-    <row r="549" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A549" s="4" t="s">
         <v>45</v>
       </c>
@@ -8454,7 +8460,7 @@
       <c r="D549" s="5"/>
       <c r="E549" s="11"/>
     </row>
-    <row r="550" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A550" s="4" t="s">
         <v>45</v>
       </c>
@@ -8467,7 +8473,7 @@
       <c r="D550" s="5"/>
       <c r="E550" s="11"/>
     </row>
-    <row r="551" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A551" s="4" t="s">
         <v>45</v>
       </c>
@@ -8484,7 +8490,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="552" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
         <v>45</v>
       </c>
@@ -8497,7 +8503,7 @@
       <c r="D552" s="5"/>
       <c r="E552" s="11"/>
     </row>
-    <row r="553" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A553" s="4" t="s">
         <v>45</v>
       </c>
@@ -8510,7 +8516,7 @@
       <c r="D553" s="5"/>
       <c r="E553" s="11"/>
     </row>
-    <row r="554" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A554" s="4" t="s">
         <v>45</v>
       </c>
@@ -8523,7 +8529,7 @@
       <c r="D554" s="5"/>
       <c r="E554" s="11"/>
     </row>
-    <row r="555" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A555" s="4" t="s">
         <v>45</v>
       </c>
@@ -8536,7 +8542,7 @@
       <c r="D555" s="5"/>
       <c r="E555" s="11"/>
     </row>
-    <row r="556" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A556" s="4" t="s">
         <v>45</v>
       </c>
@@ -8549,7 +8555,7 @@
       <c r="D556" s="5"/>
       <c r="E556" s="11"/>
     </row>
-    <row r="557" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A557" s="4" t="s">
         <v>45</v>
       </c>
@@ -8559,10 +8565,14 @@
       <c r="C557" s="4">
         <v>12</v>
       </c>
-      <c r="D557" s="5"/>
-      <c r="E557" s="11"/>
-    </row>
-    <row r="558" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D557" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E557" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A558" s="4" t="s">
         <v>45</v>
       </c>
@@ -8575,7 +8585,7 @@
       <c r="D558" s="5"/>
       <c r="E558" s="11"/>
     </row>
-    <row r="559" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A559" s="4" t="s">
         <v>45</v>
       </c>
@@ -8588,7 +8598,7 @@
       <c r="D559" s="5"/>
       <c r="E559" s="11"/>
     </row>
-    <row r="560" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A560" s="4" t="s">
         <v>45</v>
       </c>
@@ -8601,7 +8611,7 @@
       <c r="D560" s="5"/>
       <c r="E560" s="11"/>
     </row>
-    <row r="561" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A561" s="4" t="s">
         <v>45</v>
       </c>
@@ -8614,7 +8624,7 @@
       <c r="D561" s="5"/>
       <c r="E561" s="11"/>
     </row>
-    <row r="562" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A562" s="4" t="s">
         <v>45</v>
       </c>
@@ -8627,7 +8637,7 @@
       <c r="D562" s="5"/>
       <c r="E562" s="11"/>
     </row>
-    <row r="563" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A563" s="4" t="s">
         <v>45</v>
       </c>
@@ -8640,7 +8650,7 @@
       <c r="D563" s="5"/>
       <c r="E563" s="11"/>
     </row>
-    <row r="564" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A564" s="4" t="s">
         <v>45</v>
       </c>
@@ -8653,7 +8663,7 @@
       <c r="D564" s="5"/>
       <c r="E564" s="11"/>
     </row>
-    <row r="565" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A565" s="4" t="s">
         <v>45</v>
       </c>
@@ -8666,7 +8676,7 @@
       <c r="D565" s="5"/>
       <c r="E565" s="11"/>
     </row>
-    <row r="566" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A566" s="4" t="s">
         <v>45</v>
       </c>
@@ -8679,7 +8689,7 @@
       <c r="D566" s="5"/>
       <c r="E566" s="11"/>
     </row>
-    <row r="567" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A567" s="4" t="s">
         <v>45</v>
       </c>
@@ -8692,7 +8702,7 @@
       <c r="D567" s="5"/>
       <c r="E567" s="11"/>
     </row>
-    <row r="568" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A568" s="4" t="s">
         <v>45</v>
       </c>
@@ -8705,7 +8715,7 @@
       <c r="D568" s="5"/>
       <c r="E568" s="11"/>
     </row>
-    <row r="569" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569" s="4" t="s">
         <v>45</v>
       </c>
@@ -8718,7 +8728,7 @@
       <c r="D569" s="5"/>
       <c r="E569" s="11"/>
     </row>
-    <row r="570" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A570" s="4" t="s">
         <v>45</v>
       </c>
@@ -8731,7 +8741,7 @@
       <c r="D570" s="5"/>
       <c r="E570" s="11"/>
     </row>
-    <row r="571" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A571" s="4" t="s">
         <v>45</v>
       </c>
@@ -9544,7 +9554,7 @@
       <c r="D631" s="5"/>
       <c r="E631" s="11"/>
     </row>
-    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" s="4" t="s">
         <v>45</v>
       </c>
@@ -9557,7 +9567,7 @@
       <c r="D632" s="5"/>
       <c r="E632" s="11"/>
     </row>
-    <row r="633" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" s="4" t="s">
         <v>45</v>
       </c>
@@ -9570,7 +9580,7 @@
       <c r="D633" s="5"/>
       <c r="E633" s="11"/>
     </row>
-    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" s="4" t="s">
         <v>45</v>
       </c>
@@ -9583,7 +9593,7 @@
       <c r="D634" s="5"/>
       <c r="E634" s="11"/>
     </row>
-    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" s="4" t="s">
         <v>45</v>
       </c>
@@ -9596,7 +9606,7 @@
       <c r="D635" s="5"/>
       <c r="E635" s="11"/>
     </row>
-    <row r="636" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" s="4" t="s">
         <v>45</v>
       </c>
@@ -9609,7 +9619,7 @@
       <c r="D636" s="5"/>
       <c r="E636" s="11"/>
     </row>
-    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="4" t="s">
         <v>45</v>
       </c>
@@ -9622,7 +9632,7 @@
       <c r="D637" s="5"/>
       <c r="E637" s="11"/>
     </row>
-    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="4" t="s">
         <v>45</v>
       </c>
@@ -9635,7 +9645,7 @@
       <c r="D638" s="5"/>
       <c r="E638" s="11"/>
     </row>
-    <row r="639" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="4" t="s">
         <v>45</v>
       </c>
@@ -9648,7 +9658,7 @@
       <c r="D639" s="5"/>
       <c r="E639" s="11"/>
     </row>
-    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="4" t="s">
         <v>45</v>
       </c>
@@ -9661,7 +9671,7 @@
       <c r="D640" s="5"/>
       <c r="E640" s="11"/>
     </row>
-    <row r="641" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="4" t="s">
         <v>45</v>
       </c>
@@ -9674,7 +9684,7 @@
       <c r="D641" s="5"/>
       <c r="E641" s="11"/>
     </row>
-    <row r="642" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="4" t="s">
         <v>45</v>
       </c>
@@ -9691,7 +9701,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="643" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="4" t="s">
         <v>45</v>
       </c>
@@ -9704,7 +9714,7 @@
       <c r="D643" s="5"/>
       <c r="E643" s="11"/>
     </row>
-    <row r="644" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" s="4" t="s">
         <v>45</v>
       </c>
@@ -9717,7 +9727,7 @@
       <c r="D644" s="5"/>
       <c r="E644" s="11"/>
     </row>
-    <row r="645" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" s="4" t="s">
         <v>45</v>
       </c>
@@ -9730,7 +9740,7 @@
       <c r="D645" s="5"/>
       <c r="E645" s="11"/>
     </row>
-    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" s="4" t="s">
         <v>45</v>
       </c>
@@ -9743,7 +9753,7 @@
       <c r="D646" s="5"/>
       <c r="E646" s="11"/>
     </row>
-    <row r="647" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" s="4" t="s">
         <v>45</v>
       </c>
@@ -9756,7 +9766,7 @@
       <c r="D647" s="5"/>
       <c r="E647" s="11"/>
     </row>
-    <row r="648" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" s="4" t="s">
         <v>45</v>
       </c>
@@ -9769,7 +9779,7 @@
       <c r="D648" s="5"/>
       <c r="E648" s="11"/>
     </row>
-    <row r="649" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" s="4" t="s">
         <v>45</v>
       </c>
@@ -9782,7 +9792,7 @@
       <c r="D649" s="5"/>
       <c r="E649" s="11"/>
     </row>
-    <row r="650" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="4" t="s">
         <v>45</v>
       </c>
@@ -9795,7 +9805,7 @@
       <c r="D650" s="5"/>
       <c r="E650" s="11"/>
     </row>
-    <row r="651" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" s="4" t="s">
         <v>45</v>
       </c>
@@ -9808,7 +9818,7 @@
       <c r="D651" s="5"/>
       <c r="E651" s="11"/>
     </row>
-    <row r="652" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" s="4" t="s">
         <v>45</v>
       </c>
@@ -9821,7 +9831,7 @@
       <c r="D652" s="5"/>
       <c r="E652" s="11"/>
     </row>
-    <row r="653" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" s="4" t="s">
         <v>45</v>
       </c>
@@ -9834,7 +9844,7 @@
       <c r="D653" s="5"/>
       <c r="E653" s="11"/>
     </row>
-    <row r="654" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" s="4" t="s">
         <v>45</v>
       </c>
@@ -9847,7 +9857,7 @@
       <c r="D654" s="5"/>
       <c r="E654" s="11"/>
     </row>
-    <row r="655" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" s="4" t="s">
         <v>45</v>
       </c>
@@ -9860,7 +9870,7 @@
       <c r="D655" s="5"/>
       <c r="E655" s="11"/>
     </row>
-    <row r="656" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" s="4" t="s">
         <v>45</v>
       </c>
@@ -9873,7 +9883,7 @@
       <c r="D656" s="5"/>
       <c r="E656" s="11"/>
     </row>
-    <row r="657" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" s="4" t="s">
         <v>45</v>
       </c>
@@ -9886,7 +9896,7 @@
       <c r="D657" s="5"/>
       <c r="E657" s="11"/>
     </row>
-    <row r="658" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" s="4" t="s">
         <v>45</v>
       </c>
@@ -9899,7 +9909,7 @@
       <c r="D658" s="5"/>
       <c r="E658" s="11"/>
     </row>
-    <row r="659" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" s="4" t="s">
         <v>45</v>
       </c>
@@ -9912,7 +9922,7 @@
       <c r="D659" s="5"/>
       <c r="E659" s="11"/>
     </row>
-    <row r="660" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" s="4" t="s">
         <v>45</v>
       </c>
@@ -9925,7 +9935,7 @@
       <c r="D660" s="5"/>
       <c r="E660" s="11"/>
     </row>
-    <row r="661" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" s="4" t="s">
         <v>45</v>
       </c>
@@ -9938,7 +9948,7 @@
       <c r="D661" s="5"/>
       <c r="E661" s="11"/>
     </row>
-    <row r="662" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A662" s="4" t="s">
         <v>45</v>
       </c>
@@ -9951,7 +9961,7 @@
       <c r="D662" s="5"/>
       <c r="E662" s="11"/>
     </row>
-    <row r="663" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A663" s="4" t="s">
         <v>45</v>
       </c>
@@ -9964,7 +9974,7 @@
       <c r="D663" s="5"/>
       <c r="E663" s="11"/>
     </row>
-    <row r="664" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A664" s="4" t="s">
         <v>45</v>
       </c>
@@ -9977,7 +9987,7 @@
       <c r="D664" s="5"/>
       <c r="E664" s="11"/>
     </row>
-    <row r="665" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A665" s="4" t="s">
         <v>45</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A8538D-8EB1-44A6-A653-4DB7C5FEB82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6258243-F131-412A-9B05-0E42FF4E63B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -101,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="161">
   <si>
     <t>Категорија</t>
   </si>
@@ -578,13 +577,19 @@
   </si>
   <si>
     <t>https://script.google.com/macros/s/AKfycbwm1HrLVb56EXheipy9go4kYrPgHu4cmqg1ocgHqKaM0OfZQfsXj-cWl6DOdDsGJvPEgw/exec</t>
+  </si>
+  <si>
+    <t>Поим за релација</t>
+  </si>
+  <si>
+    <t>https://ik-cod.github.io/Matematika/data/8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -629,6 +634,14 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -709,10 +722,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -748,8 +762,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -774,12 +792,12 @@
   <autoFilter ref="A1:E736" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Мерење"/>
+        <filter val="Броеви"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="6"/>
+        <filter val="8"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2238,7 +2256,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2248,10 +2266,14 @@
       <c r="C82" s="4">
         <v>1</v>
       </c>
-      <c r="D82" s="5"/>
-      <c r="E82" s="11"/>
-    </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D82" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2264,7 +2286,7 @@
       <c r="D83" s="5"/>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2277,7 +2299,7 @@
       <c r="D84" s="5"/>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2290,7 +2312,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2303,7 +2325,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="11"/>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2316,7 +2338,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="11"/>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2329,7 +2351,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="11"/>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2342,7 +2364,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="11"/>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2355,7 +2377,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="11"/>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2368,7 +2390,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2381,7 +2403,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2394,7 +2416,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2407,7 +2429,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2420,7 +2442,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2433,7 +2455,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2446,7 +2468,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2459,7 +2481,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2472,7 +2494,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2485,7 +2507,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2498,7 +2520,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2511,7 +2533,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2524,7 +2546,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2537,7 +2559,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2550,7 +2572,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2563,7 +2585,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2576,7 +2598,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2589,7 +2611,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2602,7 +2624,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2615,7 +2637,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2628,7 +2650,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2641,7 +2663,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2654,7 +2676,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2667,7 +2689,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2680,7 +2702,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2693,7 +2715,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2706,7 +2728,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2719,7 +2741,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2732,7 +2754,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2745,7 +2767,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>
@@ -8408,7 +8430,7 @@
       <c r="D545" s="5"/>
       <c r="E545" s="11"/>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="4" t="s">
         <v>45</v>
       </c>
@@ -8421,7 +8443,7 @@
       <c r="D546" s="5"/>
       <c r="E546" s="11"/>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="4" t="s">
         <v>45</v>
       </c>
@@ -8434,7 +8456,7 @@
       <c r="D547" s="5"/>
       <c r="E547" s="11"/>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="4" t="s">
         <v>45</v>
       </c>
@@ -8447,7 +8469,7 @@
       <c r="D548" s="5"/>
       <c r="E548" s="11"/>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="4" t="s">
         <v>45</v>
       </c>
@@ -8460,7 +8482,7 @@
       <c r="D549" s="5"/>
       <c r="E549" s="11"/>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="4" t="s">
         <v>45</v>
       </c>
@@ -8473,7 +8495,7 @@
       <c r="D550" s="5"/>
       <c r="E550" s="11"/>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="4" t="s">
         <v>45</v>
       </c>
@@ -8490,7 +8512,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
         <v>45</v>
       </c>
@@ -8503,7 +8525,7 @@
       <c r="D552" s="5"/>
       <c r="E552" s="11"/>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="4" t="s">
         <v>45</v>
       </c>
@@ -8516,7 +8538,7 @@
       <c r="D553" s="5"/>
       <c r="E553" s="11"/>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="4" t="s">
         <v>45</v>
       </c>
@@ -8529,7 +8551,7 @@
       <c r="D554" s="5"/>
       <c r="E554" s="11"/>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="4" t="s">
         <v>45</v>
       </c>
@@ -8542,7 +8564,7 @@
       <c r="D555" s="5"/>
       <c r="E555" s="11"/>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="4" t="s">
         <v>45</v>
       </c>
@@ -8555,7 +8577,7 @@
       <c r="D556" s="5"/>
       <c r="E556" s="11"/>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="4" t="s">
         <v>45</v>
       </c>
@@ -8572,7 +8594,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="4" t="s">
         <v>45</v>
       </c>
@@ -8585,7 +8607,7 @@
       <c r="D558" s="5"/>
       <c r="E558" s="11"/>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="4" t="s">
         <v>45</v>
       </c>
@@ -8598,7 +8620,7 @@
       <c r="D559" s="5"/>
       <c r="E559" s="11"/>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="4" t="s">
         <v>45</v>
       </c>
@@ -8611,7 +8633,7 @@
       <c r="D560" s="5"/>
       <c r="E560" s="11"/>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="4" t="s">
         <v>45</v>
       </c>
@@ -8624,7 +8646,7 @@
       <c r="D561" s="5"/>
       <c r="E561" s="11"/>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="4" t="s">
         <v>45</v>
       </c>
@@ -8637,7 +8659,7 @@
       <c r="D562" s="5"/>
       <c r="E562" s="11"/>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="4" t="s">
         <v>45</v>
       </c>
@@ -8650,7 +8672,7 @@
       <c r="D563" s="5"/>
       <c r="E563" s="11"/>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="4" t="s">
         <v>45</v>
       </c>
@@ -8663,7 +8685,7 @@
       <c r="D564" s="5"/>
       <c r="E564" s="11"/>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="4" t="s">
         <v>45</v>
       </c>
@@ -8676,7 +8698,7 @@
       <c r="D565" s="5"/>
       <c r="E565" s="11"/>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="4" t="s">
         <v>45</v>
       </c>
@@ -8689,7 +8711,7 @@
       <c r="D566" s="5"/>
       <c r="E566" s="11"/>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="4" t="s">
         <v>45</v>
       </c>
@@ -8702,7 +8724,7 @@
       <c r="D567" s="5"/>
       <c r="E567" s="11"/>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="4" t="s">
         <v>45</v>
       </c>
@@ -8715,7 +8737,7 @@
       <c r="D568" s="5"/>
       <c r="E568" s="11"/>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="4" t="s">
         <v>45</v>
       </c>
@@ -8728,7 +8750,7 @@
       <c r="D569" s="5"/>
       <c r="E569" s="11"/>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="4" t="s">
         <v>45</v>
       </c>
@@ -8741,7 +8763,7 @@
       <c r="D570" s="5"/>
       <c r="E570" s="11"/>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="4" t="s">
         <v>45</v>
       </c>
@@ -9176,7 +9198,7 @@
       <c r="D603" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E603" s="11" t="s">
+      <c r="E603" s="13" t="s">
         <v>147</v>
       </c>
     </row>
@@ -9948,7 +9970,7 @@
       <c r="D661" s="5"/>
       <c r="E661" s="11"/>
     </row>
-    <row r="662" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" s="4" t="s">
         <v>45</v>
       </c>
@@ -9961,7 +9983,7 @@
       <c r="D662" s="5"/>
       <c r="E662" s="11"/>
     </row>
-    <row r="663" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="4" t="s">
         <v>45</v>
       </c>
@@ -9974,7 +9996,7 @@
       <c r="D663" s="5"/>
       <c r="E663" s="11"/>
     </row>
-    <row r="664" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="4" t="s">
         <v>45</v>
       </c>
@@ -9987,7 +10009,7 @@
       <c r="D664" s="5"/>
       <c r="E664" s="11"/>
     </row>
-    <row r="665" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="4" t="s">
         <v>45</v>
       </c>
@@ -10944,10 +10966,14 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E603" r:id="rId1" xr:uid="{C4BB2320-73F4-4247-B6EF-4A48501D6F90}"/>
+    <hyperlink ref="E82" r:id="rId2" xr:uid="{822F4467-6A29-45B0-81B1-6A7C3274ED07}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6258243-F131-412A-9B05-0E42FF4E63B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3837C12-4070-451C-9CB1-E5553EFA0333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="163">
   <si>
     <t>Категорија</t>
   </si>
@@ -583,6 +583,12 @@
   </si>
   <si>
     <t>https://ik-cod.github.io/Matematika/data/8</t>
+  </si>
+  <si>
+    <t>Операции со множества</t>
+  </si>
+  <si>
+    <t>https://github.com/IK-cod/Matematika/blob/main/data/7.html</t>
   </si>
 </sst>
 </file>
@@ -797,7 +803,7 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="8"/>
+        <filter val="7"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1109,7 +1115,7 @@
     <col min="5" max="5" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1728,7 +1734,7 @@
       </c>
       <c r="E41" s="11"/>
     </row>
-    <row r="42" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>5</v>
       </c>
@@ -1739,11 +1745,13 @@
         <v>1</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="E42" s="11"/>
-    </row>
-    <row r="43" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
@@ -1758,7 +1766,7 @@
       </c>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -1773,7 +1781,7 @@
       </c>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>5</v>
       </c>
@@ -1788,7 +1796,7 @@
       </c>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1801,7 +1809,7 @@
       <c r="D46" s="5"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -1814,7 +1822,7 @@
       <c r="D47" s="5"/>
       <c r="E47" s="11"/>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -1827,7 +1835,7 @@
       <c r="D48" s="5"/>
       <c r="E48" s="11"/>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -1840,7 +1848,7 @@
       <c r="D49" s="5"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -1853,7 +1861,7 @@
       <c r="D50" s="5"/>
       <c r="E50" s="11"/>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -1866,7 +1874,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="11"/>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -1879,7 +1887,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="11"/>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -1892,7 +1900,7 @@
       <c r="D53" s="5"/>
       <c r="E53" s="11"/>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -1905,7 +1913,7 @@
       <c r="D54" s="5"/>
       <c r="E54" s="11"/>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -1918,7 +1926,7 @@
       <c r="D55" s="5"/>
       <c r="E55" s="11"/>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -1931,7 +1939,7 @@
       <c r="D56" s="5"/>
       <c r="E56" s="11"/>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -1944,7 +1952,7 @@
       <c r="D57" s="5"/>
       <c r="E57" s="11"/>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -1957,7 +1965,7 @@
       <c r="D58" s="5"/>
       <c r="E58" s="11"/>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -1970,7 +1978,7 @@
       <c r="D59" s="5"/>
       <c r="E59" s="11"/>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -1983,7 +1991,7 @@
       <c r="D60" s="5"/>
       <c r="E60" s="11"/>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -1996,7 +2004,7 @@
       <c r="D61" s="5"/>
       <c r="E61" s="11"/>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -2009,7 +2017,7 @@
       <c r="D62" s="5"/>
       <c r="E62" s="11"/>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -2022,7 +2030,7 @@
       <c r="D63" s="5"/>
       <c r="E63" s="11"/>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -2035,7 +2043,7 @@
       <c r="D64" s="5"/>
       <c r="E64" s="11"/>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -2048,7 +2056,7 @@
       <c r="D65" s="5"/>
       <c r="E65" s="11"/>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -2061,7 +2069,7 @@
       <c r="D66" s="5"/>
       <c r="E66" s="11"/>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -2074,7 +2082,7 @@
       <c r="D67" s="5"/>
       <c r="E67" s="11"/>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -2087,7 +2095,7 @@
       <c r="D68" s="5"/>
       <c r="E68" s="11"/>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -2100,7 +2108,7 @@
       <c r="D69" s="5"/>
       <c r="E69" s="11"/>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -2113,7 +2121,7 @@
       <c r="D70" s="5"/>
       <c r="E70" s="11"/>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2126,7 +2134,7 @@
       <c r="D71" s="5"/>
       <c r="E71" s="11"/>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -2139,7 +2147,7 @@
       <c r="D72" s="5"/>
       <c r="E72" s="11"/>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -2152,7 +2160,7 @@
       <c r="D73" s="5"/>
       <c r="E73" s="11"/>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -2165,7 +2173,7 @@
       <c r="D74" s="5"/>
       <c r="E74" s="11"/>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -2178,7 +2186,7 @@
       <c r="D75" s="5"/>
       <c r="E75" s="11"/>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2191,7 +2199,7 @@
       <c r="D76" s="5"/>
       <c r="E76" s="11"/>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -2204,7 +2212,7 @@
       <c r="D77" s="5"/>
       <c r="E77" s="11"/>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -2217,7 +2225,7 @@
       <c r="D78" s="5"/>
       <c r="E78" s="11"/>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -2230,7 +2238,7 @@
       <c r="D79" s="5"/>
       <c r="E79" s="11"/>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -2243,7 +2251,7 @@
       <c r="D80" s="5"/>
       <c r="E80" s="11"/>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2256,7 +2264,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2273,7 +2281,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2286,7 +2294,7 @@
       <c r="D83" s="5"/>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2299,7 +2307,7 @@
       <c r="D84" s="5"/>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2312,7 +2320,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2325,7 +2333,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="11"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2338,7 +2346,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="11"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2351,7 +2359,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="11"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2364,7 +2372,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="11"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2377,7 +2385,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="11"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2390,7 +2398,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2403,7 +2411,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2416,7 +2424,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2429,7 +2437,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2442,7 +2450,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2455,7 +2463,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2468,7 +2476,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2481,7 +2489,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2494,7 +2502,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2507,7 +2515,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2520,7 +2528,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2533,7 +2541,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2546,7 +2554,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2559,7 +2567,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2572,7 +2580,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2585,7 +2593,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2598,7 +2606,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2611,7 +2619,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2624,7 +2632,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2637,7 +2645,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2650,7 +2658,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2663,7 +2671,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2676,7 +2684,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2689,7 +2697,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2702,7 +2710,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2715,7 +2723,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2728,7 +2736,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2741,7 +2749,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2754,7 +2762,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2767,7 +2775,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>

--- a/data/lessons.xlsx
+++ b/data/lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3837C12-4070-451C-9CB1-E5553EFA0333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851F2735-0EFF-48BE-8326-0ECD7233E03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -588,7 +588,7 @@
     <t>Операции со множества</t>
   </si>
   <si>
-    <t>https://github.com/IK-cod/Matematika/blob/main/data/7.html</t>
+    <t>https://ik-cod.github.io/Matematika/data/7</t>
   </si>
 </sst>
 </file>
@@ -804,6 +804,7 @@
     <filterColumn colId="1">
       <filters>
         <filter val="7"/>
+        <filter val="8"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2264,7 +2265,7 @@
       <c r="D81" s="5"/>
       <c r="E81" s="11"/>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -2281,7 +2282,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -2294,7 +2295,7 @@
       <c r="D83" s="5"/>
       <c r="E83" s="11"/>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -2307,7 +2308,7 @@
       <c r="D84" s="5"/>
       <c r="E84" s="11"/>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -2320,7 +2321,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="11"/>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -2333,7 +2334,7 @@
       <c r="D86" s="5"/>
       <c r="E86" s="11"/>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -2346,7 +2347,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="11"/>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -2359,7 +2360,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="11"/>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -2372,7 +2373,7 @@
       <c r="D89" s="5"/>
       <c r="E89" s="11"/>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -2385,7 +2386,7 @@
       <c r="D90" s="5"/>
       <c r="E90" s="11"/>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -2398,7 +2399,7 @@
       <c r="D91" s="5"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -2411,7 +2412,7 @@
       <c r="D92" s="5"/>
       <c r="E92" s="11"/>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -2424,7 +2425,7 @@
       <c r="D93" s="5"/>
       <c r="E93" s="11"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -2437,7 +2438,7 @@
       <c r="D94" s="5"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -2450,7 +2451,7 @@
       <c r="D95" s="5"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2463,7 +2464,7 @@
       <c r="D96" s="5"/>
       <c r="E96" s="11"/>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -2476,7 +2477,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="11"/>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -2489,7 +2490,7 @@
       <c r="D98" s="5"/>
       <c r="E98" s="11"/>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -2502,7 +2503,7 @@
       <c r="D99" s="5"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -2515,7 +2516,7 @@
       <c r="D100" s="5"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2528,7 +2529,7 @@
       <c r="D101" s="5"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -2541,7 +2542,7 @@
       <c r="D102" s="5"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -2554,7 +2555,7 @@
       <c r="D103" s="5"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -2567,7 +2568,7 @@
       <c r="D104" s="5"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -2580,7 +2581,7 @@
       <c r="D105" s="5"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2593,7 +2594,7 @@
       <c r="D106" s="5"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -2606,7 +2607,7 @@
       <c r="D107" s="5"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -2619,7 +2620,7 @@
       <c r="D108" s="5"/>
       <c r="E108" s="11"/>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -2632,7 +2633,7 @@
       <c r="D109" s="5"/>
       <c r="E109" s="11"/>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -2645,7 +2646,7 @@
       <c r="D110" s="5"/>
       <c r="E110" s="11"/>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2658,7 +2659,7 @@
       <c r="D111" s="5"/>
       <c r="E111" s="11"/>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -2671,7 +2672,7 @@
       <c r="D112" s="5"/>
       <c r="E112" s="11"/>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -2684,7 +2685,7 @@
       <c r="D113" s="5"/>
       <c r="E113" s="11"/>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -2697,7 +2698,7 @@
       <c r="D114" s="5"/>
       <c r="E114" s="11"/>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -2710,7 +2711,7 @@
       <c r="D115" s="5"/>
       <c r="E115" s="11"/>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2723,7 +2724,7 @@
       <c r="D116" s="5"/>
       <c r="E116" s="11"/>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -2736,7 +2737,7 @@
       <c r="D117" s="5"/>
       <c r="E117" s="11"/>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -2749,7 +2750,7 @@
       <c r="D118" s="5"/>
       <c r="E118" s="11"/>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -2762,7 +2763,7 @@
       <c r="D119" s="5"/>
       <c r="E119" s="11"/>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -2775,7 +2776,7 @@
       <c r="D120" s="5"/>
       <c r="E120" s="11"/>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>
